--- a/GourmetProject/GameConfig/Datas/item.xlsx
+++ b/GourmetProject/GameConfig/Datas/item.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:U7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,15 +444,80 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>quality</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>specialTags</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>maxLevel</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>nextLevelWeightMultiplier</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>unlockCondition</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>triggerTiming</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>acquireLimit</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>holdLimit</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>consumeOnUse</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>baseWeight</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>hiddenMin</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>hiddenMax</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
           <t>effectType</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>effectValue</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>effectParam</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
         <is>
           <t>icon</t>
         </is>
@@ -486,22 +551,86 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>ItemQuality</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>string</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>ItemTriggerTiming</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
           <t>item_big_plate</t>
@@ -524,22 +653,62 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ScoreBuild</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>3</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>30</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
           <t>FinalAddFlat</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Sprites/Items/big_plate</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
           <t>item_chef_knife</t>
@@ -562,22 +731,62 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>ScoreBuild</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P4" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>45</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
           <t>FinalAddMult</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Sprites/Items/chef_knife</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
           <t>item_pepper_jar</t>
@@ -600,22 +809,67 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>SpicyBuild</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>1</v>
+      </c>
+      <c r="P5" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>35</v>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
           <t>TagBonus</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>tag_spicy</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
         <is>
           <t>Sprites/Items/pepper_jar</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
           <t>item_reroll</t>
@@ -638,22 +892,62 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>BattleActive</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>BeforeEat</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>9</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
           <t>ClearBoard</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Sprites/Items/reroll_bell</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
           <t>item_extra_serve</t>
@@ -676,15 +970,56 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>BattleActive</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>BeforeEat</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>9</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>1</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
           <t>ExtraServe</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Sprites/Items/extra_serve</t>
         </is>

--- a/GourmetProject/GameConfig/Datas/item.xlsx
+++ b/GourmetProject/GameConfig/Datas/item.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U7"/>
+  <dimension ref="A1:U8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -526,202 +526,231 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>##type</t>
+          <t>##comment</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>道具ID</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>道具名称</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>道具描述</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>ItemKind</t>
+          <t>道具类型</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ItemQuality</t>
+          <t>道具品质</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>特殊标签标记</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>最大等级</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>下一级权重倍率</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>解锁条件</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>ItemTriggerTiming</t>
+          <t>触发时机</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>获取次数限制</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>持有数量限制</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>使用后是否消耗</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>随机基础权重</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>出现隐藏分下限</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>出现隐藏分上限</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>效果类型</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>效果数值</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>效果参数</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>图标资源路径</t>
         </is>
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>item_big_plate</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>大餐盘</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>被动：每局结算最终分数额外 +50。</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Passive</t>
+          <t>ItemKind</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>ItemQuality</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>ScoreBuild</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>3</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.65</v>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
-        <v>1</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1</v>
+          <t>ItemTriggerTiming</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="O3" t="n">
-        <v>1</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>30</v>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>FinalAddFlat</t>
+          <t>string</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>string</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>Sprites/Items/big_plate</t>
+          <t>string</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="B4" t="inlineStr">
         <is>
-          <t>item_chef_knife</t>
+          <t>item_big_plate</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>主厨刀</t>
+          <t>大餐盘</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>被动：每局结算最终分数 ×1.2。</t>
+          <t>被动：每局结算最终分数额外 +50。</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -731,7 +760,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Uncommon</t>
+          <t>Common</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -765,41 +794,41 @@
         <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>FinalAddMult</t>
+          <t>FinalAddFlat</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>50</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>Sprites/Items/chef_knife</t>
+          <t>Sprites/Items/big_plate</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
-          <t>item_pepper_jar</t>
+          <t>item_chef_knife</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>胡椒罐</t>
+          <t>主厨刀</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>被动：每道带「麻辣」的菜额外 +10 美味度。</t>
+          <t>被动：每局结算最终分数 ×1.2。</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -814,7 +843,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SpicyBuild</t>
+          <t>ScoreBuild</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -843,124 +872,124 @@
         <v>1</v>
       </c>
       <c r="P5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Q5" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>TagBonus</t>
+          <t>FinalAddMult</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>tag_spicy</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>Sprites/Items/pepper_jar</t>
+          <t>Sprites/Items/chef_knife</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="B6" t="inlineStr">
         <is>
-          <t>item_reroll</t>
+          <t>item_pepper_jar</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>重摆铃</t>
+          <t>胡椒罐</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>主动：清空棋盘上的菜品，可重新上菜。</t>
+          <t>被动：每道带「麻辣」的菜额外 +10 美味度。</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Passive</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>Uncommon</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>BattleActive</t>
+          <t>SpicyBuild</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>0.65</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>BeforeEat</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="O6" t="n">
         <v>1</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>ClearBoard</t>
+          <t>TagBonus</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>tag_spicy</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>Sprites/Items/reroll_bell</t>
+          <t>Sprites/Items/pepper_jar</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
-          <t>item_extra_serve</t>
+          <t>item_reroll</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>加菜券</t>
+          <t>重摆铃</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>主动：立即额外上一道菜。</t>
+          <t>主动：清空棋盘上的菜品，可重新上菜。</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1011,15 +1040,93 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
+          <t>ClearBoard</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sprites/Items/reroll_bell</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>item_extra_serve</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>加菜券</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>主动：立即额外上一道菜。</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>BattleActive</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>BeforeEat</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>9</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
           <t>ExtraServe</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Sprites/Items/extra_serve</t>
         </is>

--- a/GourmetProject/GameConfig/Datas/item.xlsx
+++ b/GourmetProject/GameConfig/Datas/item.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P8"/>
+  <dimension ref="A1:O8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,45 +454,40 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>unlockCondition</t>
+          <t>triggerTiming</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>triggerTiming</t>
+          <t>holdLimit</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>holdLimit</t>
+          <t>effectType</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>effectType</t>
+          <t>effectValue</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>effectValue</t>
+          <t>effectParam</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>effectParam</t>
+          <t>icon</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>icon</t>
+          <t>levelWeightParams</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
-        <is>
-          <t>levelWeightParams</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
         <is>
           <t>hiddenRange</t>
         </is>
@@ -536,45 +531,40 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>解锁条件</t>
+          <t>触发时机</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>触发时机</t>
+          <t>持有数量限制</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>持有数量限制</t>
+          <t>效果类型</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>效果类型</t>
+          <t>效果数值</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>效果数值</t>
+          <t>效果参数</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>效果参数</t>
+          <t>图标资源路径</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>图标资源路径</t>
+          <t>等级权重参数(单元格: maxLevel,nextLevelWeightMultiplier,baseWeight)</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
-        <is>
-          <t>等级权重参数(单元格: maxLevel,nextLevelWeightMultiplier,baseWeight)</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
         <is>
           <t>出现隐藏分区间(单元格: min,max)</t>
         </is>
@@ -618,29 +608,29 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>ItemTriggerTiming</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>string</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>ItemTriggerTiming</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
       <c r="M3" t="inlineStr">
         <is>
           <t>string</t>
@@ -648,22 +638,16 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>LevelWeightParams</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
-        <is>
-          <t>LevelWeightParams</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
         <is>
           <t>HiddenRange</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
           <t>item_big_plate</t>
@@ -694,44 +678,41 @@
           <t>ScoreBuild</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="I4" t="n">
         <v>1</v>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>FinalAddFlat</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>FinalAddFlat</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Sprites/Items/big_plate</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Sprites/Items/big_plate</t>
+          <t>3,0.65,1</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
-        <is>
-          <t>3,0.65,1</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
         <is>
           <t>1,30</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
           <t>item_chef_knife</t>
@@ -762,44 +743,41 @@
           <t>ScoreBuild</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="I5" t="n">
         <v>1</v>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>FinalAddMult</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>FinalAddMult</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Sprites/Items/chef_knife</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Sprites/Items/chef_knife</t>
+          <t>3,0.65,1</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
-        <is>
-          <t>3,0.65,1</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
         <is>
           <t>10,45</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
           <t>item_pepper_jar</t>
@@ -830,48 +808,46 @@
           <t>SpicyBuild</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="I6" t="n">
         <v>1</v>
       </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>TagBonus</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>TagBonus</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>tag_spicy</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>tag_spicy</t>
+          <t>Sprites/Items/pepper_jar</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Sprites/Items/pepper_jar</t>
+          <t>3,0.65,1</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
-        <is>
-          <t>3,0.65,1</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
         <is>
           <t>5,35</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
           <t>item_reroll</t>
@@ -902,44 +878,41 @@
           <t>BattleActive</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>BeforeEat</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="I7" t="n">
         <v>9</v>
       </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>ClearBoard</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>ClearBoard</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Sprites/Items/reroll_bell</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Sprites/Items/reroll_bell</t>
+          <t>1,1,1</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
         <is>
           <t>0,0</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
           <t>item_extra_serve</t>
@@ -970,37 +943,35 @@
           <t>BattleActive</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>BeforeEat</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="I8" t="n">
         <v>9</v>
       </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>ExtraServe</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>ExtraServe</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Sprites/Items/extra_serve</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Sprites/Items/extra_serve</t>
+          <t>1,1,1</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
         <is>
           <t>0,0</t>
         </is>

--- a/GourmetProject/GameConfig/Datas/item.xlsx
+++ b/GourmetProject/GameConfig/Datas/item.xlsx
@@ -1195,7 +1195,7 @@
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>levelWeightParams</t>
+          <t>baseWeight</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>等级权重参数(单元格: maxLevel,nextLevelWeightMultiplier,baseWeight)</t>
+          <t>随机基础权重</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>LevelWeightParams</t>
+          <t>float</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1412,10 +1412,8 @@
           <t>Sprites/Items/big_plate</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>3,0.65,1</t>
-        </is>
+      <c r="N4" t="n">
+        <v>1</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -1477,10 +1475,8 @@
           <t>Sprites/Items/chef_knife</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>3,0.65,1</t>
-        </is>
+      <c r="N5" t="n">
+        <v>1</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1547,10 +1543,8 @@
           <t>Sprites/Items/pepper_jar</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>3,0.65,1</t>
-        </is>
+      <c r="N6" t="n">
+        <v>1</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1612,10 +1606,8 @@
           <t>Sprites/Items/reroll_bell</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
+      <c r="N7" t="n">
+        <v>1</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1677,10 +1669,8 @@
           <t>Sprites/Items/extra_serve</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
+      <c r="N8" t="n">
+        <v>1</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1733,10 +1723,8 @@
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
+      <c r="N9" t="n">
+        <v>1</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1789,10 +1777,8 @@
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
+      <c r="N10" t="n">
+        <v>1</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1845,10 +1831,8 @@
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
+      <c r="N11" t="n">
+        <v>1</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
@@ -1901,10 +1885,8 @@
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
+      <c r="N12" t="n">
+        <v>1</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1957,10 +1939,8 @@
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
+      <c r="N13" t="n">
+        <v>1</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -2013,10 +1993,8 @@
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
+      <c r="N14" t="n">
+        <v>1</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -2069,10 +2047,8 @@
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
+      <c r="N15" t="n">
+        <v>1</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -2125,10 +2101,8 @@
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
+      <c r="N16" t="n">
+        <v>1</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -2181,10 +2155,8 @@
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
+      <c r="N17" t="n">
+        <v>1</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -2241,10 +2213,8 @@
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
+      <c r="N18" t="n">
+        <v>1</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -2301,10 +2271,8 @@
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>3,0.65,1</t>
-        </is>
+      <c r="N19" t="n">
+        <v>1</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -2357,10 +2325,8 @@
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>3,0.65,1</t>
-        </is>
+      <c r="N20" t="n">
+        <v>1</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -2413,10 +2379,8 @@
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>3,0.65,1</t>
-        </is>
+      <c r="N21" t="n">
+        <v>1</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
@@ -2469,10 +2433,8 @@
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>3,0.65,1</t>
-        </is>
+      <c r="N22" t="n">
+        <v>1</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
@@ -2525,10 +2487,8 @@
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>3,0.65,1</t>
-        </is>
+      <c r="N23" t="n">
+        <v>1</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -2581,10 +2541,8 @@
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>3,0.65,1</t>
-        </is>
+      <c r="N24" t="n">
+        <v>1</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
@@ -2637,10 +2595,8 @@
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>3,0.65,1</t>
-        </is>
+      <c r="N25" t="n">
+        <v>1</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
@@ -2693,10 +2649,8 @@
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>3,0.65,1</t>
-        </is>
+      <c r="N26" t="n">
+        <v>1</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
@@ -2749,10 +2703,8 @@
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>3,0.65,1</t>
-        </is>
+      <c r="N27" t="n">
+        <v>1</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
@@ -2805,10 +2757,8 @@
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>3,0.65,1</t>
-        </is>
+      <c r="N28" t="n">
+        <v>1</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
@@ -2861,10 +2811,8 @@
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>3,0.65,1</t>
-        </is>
+      <c r="N29" t="n">
+        <v>1</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
@@ -2921,10 +2869,8 @@
         </is>
       </c>
       <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
+      <c r="N30" t="n">
+        <v>1</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
@@ -2977,10 +2923,8 @@
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>3,0.65,1</t>
-        </is>
+      <c r="N31" t="n">
+        <v>1</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
@@ -3033,10 +2977,8 @@
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>3,0.65,1</t>
-        </is>
+      <c r="N32" t="n">
+        <v>1</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
@@ -3089,10 +3031,8 @@
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>3,0.65,1</t>
-        </is>
+      <c r="N33" t="n">
+        <v>1</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
@@ -3149,10 +3089,8 @@
         </is>
       </c>
       <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>3,0.65,1</t>
-        </is>
+      <c r="N34" t="n">
+        <v>1</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -3209,10 +3147,8 @@
         </is>
       </c>
       <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>3,0.65,1</t>
-        </is>
+      <c r="N35" t="n">
+        <v>1</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
@@ -3265,10 +3201,8 @@
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>3,0.65,1</t>
-        </is>
+      <c r="N36" t="n">
+        <v>1</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
@@ -3321,10 +3255,8 @@
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>3,0.65,1</t>
-        </is>
+      <c r="N37" t="n">
+        <v>1</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
@@ -3377,10 +3309,8 @@
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>3,0.65,1</t>
-        </is>
+      <c r="N38" t="n">
+        <v>1</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
@@ -3437,10 +3367,8 @@
         </is>
       </c>
       <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>3,0.65,1</t>
-        </is>
+      <c r="N39" t="n">
+        <v>1</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
@@ -3497,10 +3425,8 @@
         </is>
       </c>
       <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>3,0.65,1</t>
-        </is>
+      <c r="N40" t="n">
+        <v>1</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
@@ -3553,10 +3479,8 @@
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>3,0.65,1</t>
-        </is>
+      <c r="N41" t="n">
+        <v>1</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
@@ -3609,10 +3533,8 @@
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>3,0.65,1</t>
-        </is>
+      <c r="N42" t="n">
+        <v>1</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
@@ -3665,10 +3587,8 @@
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>3,0.65,1</t>
-        </is>
+      <c r="N43" t="n">
+        <v>1</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
@@ -3721,10 +3641,8 @@
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
+      <c r="N44" t="n">
+        <v>1</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
@@ -3777,10 +3695,8 @@
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>3,0.65,1</t>
-        </is>
+      <c r="N45" t="n">
+        <v>1</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
@@ -3833,10 +3749,8 @@
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>3,0.65,1</t>
-        </is>
+      <c r="N46" t="n">
+        <v>1</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
@@ -3889,10 +3803,8 @@
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>3,0.65,1</t>
-        </is>
+      <c r="N47" t="n">
+        <v>1</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
@@ -3945,10 +3857,8 @@
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>3,0.65,1</t>
-        </is>
+      <c r="N48" t="n">
+        <v>1</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
@@ -4001,10 +3911,8 @@
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>3,0.65,1</t>
-        </is>
+      <c r="N49" t="n">
+        <v>1</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
@@ -4061,10 +3969,8 @@
         </is>
       </c>
       <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
+      <c r="N50" t="n">
+        <v>1</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
@@ -4117,10 +4023,8 @@
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
+      <c r="N51" t="n">
+        <v>1</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
@@ -4173,10 +4077,8 @@
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
+      <c r="N52" t="n">
+        <v>1</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
@@ -4229,10 +4131,8 @@
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
+      <c r="N53" t="n">
+        <v>1</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
@@ -4285,10 +4185,8 @@
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
+      <c r="N54" t="n">
+        <v>1</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
@@ -4341,10 +4239,8 @@
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
+      <c r="N55" t="n">
+        <v>1</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
@@ -4401,10 +4297,8 @@
         </is>
       </c>
       <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>3,0.65,1</t>
-        </is>
+      <c r="N56" t="n">
+        <v>1</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
@@ -4461,10 +4355,8 @@
         </is>
       </c>
       <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>3,0.65,1</t>
-        </is>
+      <c r="N57" t="n">
+        <v>1</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
@@ -4521,10 +4413,8 @@
         </is>
       </c>
       <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>3,0.65,1</t>
-        </is>
+      <c r="N58" t="n">
+        <v>1</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
@@ -4577,10 +4467,8 @@
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>3,0.65,1</t>
-        </is>
+      <c r="N59" t="n">
+        <v>1</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
@@ -4633,10 +4521,8 @@
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>3,0.65,1</t>
-        </is>
+      <c r="N60" t="n">
+        <v>1</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
@@ -4689,10 +4575,8 @@
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>3,0.65,1</t>
-        </is>
+      <c r="N61" t="n">
+        <v>1</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
@@ -4745,10 +4629,8 @@
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
+      <c r="N62" t="n">
+        <v>1</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
@@ -4801,10 +4683,8 @@
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
+      <c r="N63" t="n">
+        <v>1</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
@@ -4857,10 +4737,8 @@
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
+      <c r="N64" t="n">
+        <v>1</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
@@ -4913,10 +4791,8 @@
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
+      <c r="N65" t="n">
+        <v>1</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
@@ -4969,10 +4845,8 @@
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr">
-        <is>
-          <t>3,0.65,1</t>
-        </is>
+      <c r="N66" t="n">
+        <v>1</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
@@ -5025,10 +4899,8 @@
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
+      <c r="N67" t="n">
+        <v>1</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
@@ -5081,10 +4953,8 @@
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
+      <c r="N68" t="n">
+        <v>1</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
@@ -5137,10 +5007,8 @@
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
+      <c r="N69" t="n">
+        <v>1</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
@@ -5193,10 +5061,8 @@
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>3,0.65,1</t>
-        </is>
+      <c r="N70" t="n">
+        <v>1</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
@@ -5249,10 +5115,8 @@
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>3,0.65,1</t>
-        </is>
+      <c r="N71" t="n">
+        <v>1</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
@@ -5305,10 +5169,8 @@
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t>3,0.65,1</t>
-        </is>
+      <c r="N72" t="n">
+        <v>1</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
@@ -5361,10 +5223,8 @@
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>3,0.65,1</t>
-        </is>
+      <c r="N73" t="n">
+        <v>1</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
@@ -5417,10 +5277,8 @@
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
+      <c r="N74" t="n">
+        <v>1</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
@@ -5473,10 +5331,8 @@
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t>3,0.65,1</t>
-        </is>
+      <c r="N75" t="n">
+        <v>1</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
@@ -5529,10 +5385,8 @@
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr">
-        <is>
-          <t>3,0.65,1</t>
-        </is>
+      <c r="N76" t="n">
+        <v>1</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
@@ -5585,10 +5439,8 @@
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr">
-        <is>
-          <t>3,0.65,1</t>
-        </is>
+      <c r="N77" t="n">
+        <v>1</v>
       </c>
       <c r="O77" t="inlineStr">
         <is>
@@ -5645,10 +5497,8 @@
         </is>
       </c>
       <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr">
-        <is>
-          <t>3,0.65,1</t>
-        </is>
+      <c r="N78" t="n">
+        <v>1</v>
       </c>
       <c r="O78" t="inlineStr">
         <is>
@@ -5705,10 +5555,8 @@
         </is>
       </c>
       <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr">
-        <is>
-          <t>3,0.65,1</t>
-        </is>
+      <c r="N79" t="n">
+        <v>1</v>
       </c>
       <c r="O79" t="inlineStr">
         <is>
@@ -5761,10 +5609,8 @@
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
+      <c r="N80" t="n">
+        <v>1</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
@@ -5817,10 +5663,8 @@
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr"/>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
+      <c r="N81" t="n">
+        <v>1</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
@@ -5873,10 +5717,8 @@
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr"/>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
+      <c r="N82" t="n">
+        <v>1</v>
       </c>
       <c r="O82" t="inlineStr">
         <is>
@@ -5933,10 +5775,8 @@
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr"/>
-      <c r="N83" t="inlineStr">
-        <is>
-          <t>3,0.65,1</t>
-        </is>
+      <c r="N83" t="n">
+        <v>1</v>
       </c>
       <c r="O83" t="inlineStr">
         <is>
@@ -5993,10 +5833,8 @@
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr">
-        <is>
-          <t>3,0.65,1</t>
-        </is>
+      <c r="N84" t="n">
+        <v>1</v>
       </c>
       <c r="O84" t="inlineStr">
         <is>
@@ -6053,10 +5891,8 @@
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" t="inlineStr"/>
-      <c r="N85" t="inlineStr">
-        <is>
-          <t>3,0.65,1</t>
-        </is>
+      <c r="N85" t="n">
+        <v>1</v>
       </c>
       <c r="O85" t="inlineStr">
         <is>
@@ -6113,10 +5949,8 @@
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr"/>
-      <c r="N86" t="inlineStr">
-        <is>
-          <t>3,0.65,1</t>
-        </is>
+      <c r="N86" t="n">
+        <v>1</v>
       </c>
       <c r="O86" t="inlineStr">
         <is>
@@ -6173,10 +6007,8 @@
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" t="inlineStr"/>
-      <c r="N87" t="inlineStr">
-        <is>
-          <t>3,0.65,1</t>
-        </is>
+      <c r="N87" t="n">
+        <v>1</v>
       </c>
       <c r="O87" t="inlineStr">
         <is>
@@ -6233,10 +6065,8 @@
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" t="inlineStr"/>
-      <c r="N88" t="inlineStr">
-        <is>
-          <t>3,0.65,1</t>
-        </is>
+      <c r="N88" t="n">
+        <v>1</v>
       </c>
       <c r="O88" t="inlineStr">
         <is>
@@ -6293,10 +6123,8 @@
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr"/>
-      <c r="N89" t="inlineStr">
-        <is>
-          <t>3,0.65,1</t>
-        </is>
+      <c r="N89" t="n">
+        <v>1</v>
       </c>
       <c r="O89" t="inlineStr">
         <is>
@@ -6353,10 +6181,8 @@
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr">
-        <is>
-          <t>3,0.65,1</t>
-        </is>
+      <c r="N90" t="n">
+        <v>1</v>
       </c>
       <c r="O90" t="inlineStr">
         <is>
@@ -6413,10 +6239,8 @@
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" t="inlineStr"/>
-      <c r="N91" t="inlineStr">
-        <is>
-          <t>3,0.65,1</t>
-        </is>
+      <c r="N91" t="n">
+        <v>1</v>
       </c>
       <c r="O91" t="inlineStr">
         <is>
@@ -6469,10 +6293,8 @@
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" t="inlineStr"/>
-      <c r="N92" t="inlineStr">
-        <is>
-          <t>3,0.65,1</t>
-        </is>
+      <c r="N92" t="n">
+        <v>1</v>
       </c>
       <c r="O92" t="inlineStr">
         <is>
@@ -6525,10 +6347,8 @@
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr"/>
-      <c r="N93" t="inlineStr">
-        <is>
-          <t>3,0.65,1</t>
-        </is>
+      <c r="N93" t="n">
+        <v>1</v>
       </c>
       <c r="O93" t="inlineStr">
         <is>
@@ -6581,10 +6401,8 @@
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr"/>
-      <c r="N94" t="inlineStr">
-        <is>
-          <t>3,0.65,1</t>
-        </is>
+      <c r="N94" t="n">
+        <v>1</v>
       </c>
       <c r="O94" t="inlineStr">
         <is>
@@ -6637,10 +6455,8 @@
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr"/>
-      <c r="N95" t="inlineStr">
-        <is>
-          <t>3,0.65,1</t>
-        </is>
+      <c r="N95" t="n">
+        <v>1</v>
       </c>
       <c r="O95" t="inlineStr">
         <is>
@@ -6697,10 +6513,8 @@
         </is>
       </c>
       <c r="M96" t="inlineStr"/>
-      <c r="N96" t="inlineStr">
-        <is>
-          <t>3,0.65,1</t>
-        </is>
+      <c r="N96" t="n">
+        <v>1</v>
       </c>
       <c r="O96" t="inlineStr">
         <is>
@@ -6753,10 +6567,8 @@
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" t="inlineStr"/>
-      <c r="N97" t="inlineStr">
-        <is>
-          <t>3,0.65,1</t>
-        </is>
+      <c r="N97" t="n">
+        <v>1</v>
       </c>
       <c r="O97" t="inlineStr">
         <is>
@@ -6809,10 +6621,8 @@
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" t="inlineStr"/>
-      <c r="N98" t="inlineStr">
-        <is>
-          <t>3,0.65,1</t>
-        </is>
+      <c r="N98" t="n">
+        <v>1</v>
       </c>
       <c r="O98" t="inlineStr">
         <is>
@@ -6865,10 +6675,8 @@
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" t="inlineStr"/>
-      <c r="N99" t="inlineStr">
-        <is>
-          <t>3,0.65,1</t>
-        </is>
+      <c r="N99" t="n">
+        <v>1</v>
       </c>
       <c r="O99" t="inlineStr">
         <is>
@@ -6925,10 +6733,8 @@
         </is>
       </c>
       <c r="M100" t="inlineStr"/>
-      <c r="N100" t="inlineStr">
-        <is>
-          <t>3,0.65,1</t>
-        </is>
+      <c r="N100" t="n">
+        <v>1</v>
       </c>
       <c r="O100" t="inlineStr">
         <is>
@@ -6981,10 +6787,8 @@
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" t="inlineStr"/>
-      <c r="N101" t="inlineStr">
-        <is>
-          <t>3,0.65,1</t>
-        </is>
+      <c r="N101" t="n">
+        <v>1</v>
       </c>
       <c r="O101" t="inlineStr">
         <is>

--- a/GourmetProject/GameConfig/Datas/item.xlsx
+++ b/GourmetProject/GameConfig/Datas/item.xlsx
@@ -2952,8 +2952,8 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="13.0769230769231" customWidth="1"/>
-    <col min="2" max="2" width="17.3846153846154" customWidth="1"/>
-    <col min="3" max="3" width="10.3076923076923" customWidth="1"/>
+    <col min="2" max="2" width="30.3846153846154" customWidth="1"/>
+    <col min="3" max="3" width="15.1538461538462" customWidth="1"/>
     <col min="4" max="4" width="49.3076923076923" customWidth="1"/>
     <col min="5" max="5" width="10.3076923076923" customWidth="1"/>
     <col min="6" max="6" width="12.8461538461538" customWidth="1"/>

--- a/GourmetProject/GameConfig/Datas/item.xlsx
+++ b/GourmetProject/GameConfig/Datas/item.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1193" uniqueCount="634">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1190" uniqueCount="631">
   <si>
     <t>##var</t>
   </si>
@@ -54,9 +54,6 @@
     <t>triggerTiming</t>
   </si>
   <si>
-    <t>holdLimit</t>
-  </si>
-  <si>
     <t>effectType</t>
   </si>
   <si>
@@ -96,9 +93,6 @@
     <t>触发时机</t>
   </si>
   <si>
-    <t>持有数量限制</t>
-  </si>
-  <si>
     <t>效果类型</t>
   </si>
   <si>
@@ -127,9 +121,6 @@
   </si>
   <si>
     <t>ItemTriggerTiming</t>
-  </si>
-  <si>
-    <t>int</t>
   </si>
   <si>
     <t>float</t>
@@ -2948,7 +2939,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N96"/>
+  <dimension ref="A1:M96"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="13.0769230769231" customWidth="1"/>
@@ -2959,15 +2950,14 @@
     <col min="6" max="6" width="12.8461538461538" customWidth="1"/>
     <col min="7" max="7" width="15.1538461538462" customWidth="1"/>
     <col min="8" max="8" width="19.5384615384615" customWidth="1"/>
-    <col min="9" max="9" width="15.1538461538462" customWidth="1"/>
-    <col min="10" max="10" width="14.8461538461538" customWidth="1"/>
-    <col min="11" max="11" width="11.9230769230769" customWidth="1"/>
-    <col min="12" max="12" width="12.6153846153846" customWidth="1"/>
-    <col min="13" max="13" width="73.7692307692308" customWidth="1"/>
-    <col min="14" max="14" width="36" customWidth="1"/>
+    <col min="9" max="9" width="32.0480769230769" customWidth="1"/>
+    <col min="10" max="10" width="11.9230769230769" customWidth="1"/>
+    <col min="11" max="11" width="12.6153846153846" customWidth="1"/>
+    <col min="12" max="12" width="73.7692307692308" customWidth="1"/>
+    <col min="13" max="13" width="36" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:13">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3007,3909 +2997,3621 @@
       <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>15</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>16</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>17</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>18</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>19</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>20</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>21</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>22</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>23</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>24</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>25</v>
       </c>
-      <c r="M2" t="s">
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" t="s">
         <v>26</v>
       </c>
-      <c r="N2" t="s">
+      <c r="B3" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" t="s">
+      <c r="C3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" t="s">
         <v>28</v>
       </c>
-      <c r="B3" t="s">
+      <c r="F3" t="s">
         <v>29</v>
       </c>
-      <c r="C3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="G3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3" t="s">
         <v>30</v>
       </c>
-      <c r="F3" t="s">
+      <c r="I3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J3" t="s">
         <v>31</v>
       </c>
-      <c r="G3" t="s">
-        <v>29</v>
-      </c>
-      <c r="H3" t="s">
+      <c r="K3" t="s">
+        <v>27</v>
+      </c>
+      <c r="L3" t="s">
+        <v>31</v>
+      </c>
+      <c r="M3" t="s">
         <v>32</v>
       </c>
-      <c r="I3" t="s">
+    </row>
+    <row r="4" spans="2:13">
+      <c r="B4" t="s">
         <v>33</v>
       </c>
-      <c r="J3" t="s">
-        <v>29</v>
-      </c>
-      <c r="K3" t="s">
+      <c r="C4" t="s">
         <v>34</v>
       </c>
-      <c r="L3" t="s">
-        <v>29</v>
-      </c>
-      <c r="M3" t="s">
-        <v>34</v>
-      </c>
-      <c r="N3" t="s">
+      <c r="D4" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="4" spans="2:14">
-      <c r="B4" t="s">
+      <c r="E4" t="s">
         <v>36</v>
       </c>
-      <c r="C4" t="s">
+      <c r="F4" t="s">
         <v>37</v>
       </c>
-      <c r="D4" t="s">
-        <v>38</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="G4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H4" t="s">
         <v>39</v>
       </c>
-      <c r="F4" t="s">
+      <c r="I4" t="s">
         <v>40</v>
       </c>
-      <c r="G4" t="s">
+      <c r="J4">
+        <v>2</v>
+      </c>
+      <c r="K4" t="s">
+        <v>38</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4" t="s">
         <v>41</v>
       </c>
-      <c r="H4" t="s">
+    </row>
+    <row r="5" spans="2:13">
+      <c r="B5" t="s">
         <v>42</v>
       </c>
-      <c r="I4">
-        <v>9</v>
-      </c>
-      <c r="J4" t="s">
+      <c r="C5" t="s">
         <v>43</v>
       </c>
-      <c r="K4">
+      <c r="D5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E5" t="s">
+        <v>36</v>
+      </c>
+      <c r="F5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G5" t="s">
+        <v>38</v>
+      </c>
+      <c r="H5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I5" t="s">
+        <v>45</v>
+      </c>
+      <c r="J5">
+        <v>3</v>
+      </c>
+      <c r="K5" t="s">
+        <v>38</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+      <c r="M5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="2:13">
+      <c r="B6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H6" t="s">
+        <v>39</v>
+      </c>
+      <c r="I6" t="s">
+        <v>49</v>
+      </c>
+      <c r="J6">
         <v>2</v>
       </c>
-      <c r="L4" t="s">
+      <c r="K6" t="s">
+        <v>38</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6" t="s">
         <v>41</v>
       </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-      <c r="N4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="5" spans="2:14">
-      <c r="B5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C5" t="s">
-        <v>46</v>
-      </c>
-      <c r="D5" t="s">
-        <v>47</v>
-      </c>
-      <c r="E5" t="s">
+    </row>
+    <row r="7" spans="2:13">
+      <c r="B7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D7" t="s">
+        <v>52</v>
+      </c>
+      <c r="E7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7" t="s">
+        <v>37</v>
+      </c>
+      <c r="G7" t="s">
+        <v>38</v>
+      </c>
+      <c r="H7" t="s">
         <v>39</v>
       </c>
-      <c r="F5" t="s">
-        <v>40</v>
-      </c>
-      <c r="G5" t="s">
+      <c r="I7" t="s">
+        <v>53</v>
+      </c>
+      <c r="J7">
+        <v>3</v>
+      </c>
+      <c r="K7" t="s">
+        <v>38</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="M7" t="s">
         <v>41</v>
       </c>
-      <c r="H5" t="s">
-        <v>42</v>
-      </c>
-      <c r="I5">
-        <v>9</v>
-      </c>
-      <c r="J5" t="s">
-        <v>48</v>
-      </c>
-      <c r="K5">
+    </row>
+    <row r="8" spans="2:13">
+      <c r="B8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D8" t="s">
+        <v>56</v>
+      </c>
+      <c r="E8" t="s">
+        <v>36</v>
+      </c>
+      <c r="F8" t="s">
+        <v>57</v>
+      </c>
+      <c r="G8" t="s">
+        <v>38</v>
+      </c>
+      <c r="H8" t="s">
+        <v>39</v>
+      </c>
+      <c r="I8" t="s">
+        <v>58</v>
+      </c>
+      <c r="J8">
         <v>3</v>
       </c>
-      <c r="L5" t="s">
+      <c r="K8" t="s">
+        <v>38</v>
+      </c>
+      <c r="L8">
+        <v>1</v>
+      </c>
+      <c r="M8" t="s">
         <v>41</v>
       </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-      <c r="N5" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="6" spans="2:14">
-      <c r="B6" t="s">
-        <v>49</v>
-      </c>
-      <c r="C6" t="s">
+    </row>
+    <row r="9" spans="2:13">
+      <c r="B9" t="s">
+        <v>59</v>
+      </c>
+      <c r="C9" t="s">
+        <v>60</v>
+      </c>
+      <c r="D9" t="s">
+        <v>61</v>
+      </c>
+      <c r="E9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F9" t="s">
+        <v>37</v>
+      </c>
+      <c r="G9" t="s">
+        <v>38</v>
+      </c>
+      <c r="H9" t="s">
+        <v>39</v>
+      </c>
+      <c r="I9" t="s">
+        <v>62</v>
+      </c>
+      <c r="J9">
+        <v>3</v>
+      </c>
+      <c r="K9" t="s">
+        <v>38</v>
+      </c>
+      <c r="L9">
+        <v>1</v>
+      </c>
+      <c r="M9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" spans="2:13">
+      <c r="B10" t="s">
+        <v>63</v>
+      </c>
+      <c r="C10" t="s">
+        <v>64</v>
+      </c>
+      <c r="D10" t="s">
+        <v>65</v>
+      </c>
+      <c r="E10" t="s">
+        <v>36</v>
+      </c>
+      <c r="F10" t="s">
+        <v>37</v>
+      </c>
+      <c r="G10" t="s">
+        <v>38</v>
+      </c>
+      <c r="H10" t="s">
+        <v>39</v>
+      </c>
+      <c r="I10" t="s">
+        <v>66</v>
+      </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+      <c r="K10" t="s">
+        <v>38</v>
+      </c>
+      <c r="L10">
+        <v>1</v>
+      </c>
+      <c r="M10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="2:13">
+      <c r="B11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C11" t="s">
+        <v>68</v>
+      </c>
+      <c r="D11" t="s">
+        <v>69</v>
+      </c>
+      <c r="E11" t="s">
+        <v>36</v>
+      </c>
+      <c r="F11" t="s">
+        <v>70</v>
+      </c>
+      <c r="G11" t="s">
+        <v>38</v>
+      </c>
+      <c r="H11" t="s">
+        <v>39</v>
+      </c>
+      <c r="I11" t="s">
+        <v>71</v>
+      </c>
+      <c r="J11">
         <v>50</v>
       </c>
-      <c r="D6" t="s">
-        <v>51</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="K11" t="s">
+        <v>38</v>
+      </c>
+      <c r="L11">
+        <v>1</v>
+      </c>
+      <c r="M11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="12" spans="2:13">
+      <c r="B12" t="s">
+        <v>72</v>
+      </c>
+      <c r="C12" t="s">
+        <v>73</v>
+      </c>
+      <c r="D12" t="s">
+        <v>74</v>
+      </c>
+      <c r="E12" t="s">
+        <v>36</v>
+      </c>
+      <c r="F12" t="s">
+        <v>70</v>
+      </c>
+      <c r="G12" t="s">
+        <v>38</v>
+      </c>
+      <c r="H12" t="s">
         <v>39</v>
       </c>
-      <c r="F6" t="s">
-        <v>40</v>
-      </c>
-      <c r="G6" t="s">
+      <c r="I12" t="s">
+        <v>75</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12" t="s">
+        <v>38</v>
+      </c>
+      <c r="L12">
+        <v>1</v>
+      </c>
+      <c r="M12" t="s">
         <v>41</v>
       </c>
-      <c r="H6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I6">
-        <v>9</v>
-      </c>
-      <c r="J6" t="s">
-        <v>52</v>
-      </c>
-      <c r="K6">
+    </row>
+    <row r="13" spans="2:13">
+      <c r="B13" t="s">
+        <v>76</v>
+      </c>
+      <c r="C13" t="s">
+        <v>77</v>
+      </c>
+      <c r="D13" t="s">
+        <v>78</v>
+      </c>
+      <c r="E13" t="s">
+        <v>36</v>
+      </c>
+      <c r="F13" t="s">
+        <v>57</v>
+      </c>
+      <c r="G13" t="s">
+        <v>38</v>
+      </c>
+      <c r="H13" t="s">
+        <v>39</v>
+      </c>
+      <c r="I13" t="s">
+        <v>79</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13" t="s">
+        <v>80</v>
+      </c>
+      <c r="L13">
+        <v>1</v>
+      </c>
+      <c r="M13" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="14" spans="2:13">
+      <c r="B14" t="s">
+        <v>81</v>
+      </c>
+      <c r="C14" t="s">
+        <v>82</v>
+      </c>
+      <c r="D14" t="s">
+        <v>83</v>
+      </c>
+      <c r="E14" t="s">
+        <v>84</v>
+      </c>
+      <c r="F14" t="s">
+        <v>37</v>
+      </c>
+      <c r="G14" t="s">
+        <v>38</v>
+      </c>
+      <c r="H14" t="s">
+        <v>85</v>
+      </c>
+      <c r="I14" t="s">
+        <v>86</v>
+      </c>
+      <c r="J14">
+        <v>15</v>
+      </c>
+      <c r="K14" t="s">
+        <v>87</v>
+      </c>
+      <c r="L14">
+        <v>1</v>
+      </c>
+      <c r="M14" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="15" spans="2:13">
+      <c r="B15" t="s">
+        <v>89</v>
+      </c>
+      <c r="C15" t="s">
+        <v>90</v>
+      </c>
+      <c r="D15" t="s">
+        <v>91</v>
+      </c>
+      <c r="E15" t="s">
+        <v>84</v>
+      </c>
+      <c r="F15" t="s">
+        <v>37</v>
+      </c>
+      <c r="G15" t="s">
+        <v>38</v>
+      </c>
+      <c r="H15" t="s">
+        <v>85</v>
+      </c>
+      <c r="I15" t="s">
+        <v>92</v>
+      </c>
+      <c r="J15">
+        <v>100</v>
+      </c>
+      <c r="K15" t="s">
+        <v>38</v>
+      </c>
+      <c r="L15">
+        <v>1</v>
+      </c>
+      <c r="M15" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="16" spans="2:13">
+      <c r="B16" t="s">
+        <v>93</v>
+      </c>
+      <c r="C16" t="s">
+        <v>94</v>
+      </c>
+      <c r="D16" t="s">
+        <v>95</v>
+      </c>
+      <c r="E16" t="s">
+        <v>84</v>
+      </c>
+      <c r="F16" t="s">
+        <v>70</v>
+      </c>
+      <c r="G16" t="s">
+        <v>38</v>
+      </c>
+      <c r="H16" t="s">
+        <v>85</v>
+      </c>
+      <c r="I16" t="s">
+        <v>96</v>
+      </c>
+      <c r="J16">
+        <v>0.2</v>
+      </c>
+      <c r="K16" t="s">
+        <v>38</v>
+      </c>
+      <c r="L16">
+        <v>1</v>
+      </c>
+      <c r="M16" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="17" spans="2:13">
+      <c r="B17" t="s">
+        <v>98</v>
+      </c>
+      <c r="C17" t="s">
+        <v>99</v>
+      </c>
+      <c r="D17" t="s">
+        <v>100</v>
+      </c>
+      <c r="E17" t="s">
+        <v>84</v>
+      </c>
+      <c r="F17" t="s">
+        <v>57</v>
+      </c>
+      <c r="G17" t="s">
+        <v>38</v>
+      </c>
+      <c r="H17" t="s">
+        <v>85</v>
+      </c>
+      <c r="I17" t="s">
+        <v>101</v>
+      </c>
+      <c r="J17">
+        <v>0.2</v>
+      </c>
+      <c r="K17" t="s">
+        <v>38</v>
+      </c>
+      <c r="L17">
+        <v>1</v>
+      </c>
+      <c r="M17" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="18" spans="2:13">
+      <c r="B18" t="s">
+        <v>103</v>
+      </c>
+      <c r="C18" t="s">
+        <v>104</v>
+      </c>
+      <c r="D18" t="s">
+        <v>105</v>
+      </c>
+      <c r="E18" t="s">
+        <v>84</v>
+      </c>
+      <c r="F18" t="s">
+        <v>57</v>
+      </c>
+      <c r="G18" t="s">
+        <v>38</v>
+      </c>
+      <c r="H18" t="s">
+        <v>85</v>
+      </c>
+      <c r="I18" t="s">
+        <v>106</v>
+      </c>
+      <c r="J18">
+        <v>0.2</v>
+      </c>
+      <c r="K18" t="s">
+        <v>38</v>
+      </c>
+      <c r="L18">
+        <v>1</v>
+      </c>
+      <c r="M18" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="19" spans="2:13">
+      <c r="B19" t="s">
+        <v>107</v>
+      </c>
+      <c r="C19" t="s">
+        <v>108</v>
+      </c>
+      <c r="D19" t="s">
+        <v>109</v>
+      </c>
+      <c r="E19" t="s">
+        <v>84</v>
+      </c>
+      <c r="F19" t="s">
+        <v>57</v>
+      </c>
+      <c r="G19" t="s">
+        <v>38</v>
+      </c>
+      <c r="H19" t="s">
+        <v>85</v>
+      </c>
+      <c r="I19" t="s">
+        <v>110</v>
+      </c>
+      <c r="J19">
+        <v>0.2</v>
+      </c>
+      <c r="K19" t="s">
+        <v>38</v>
+      </c>
+      <c r="L19">
+        <v>1</v>
+      </c>
+      <c r="M19" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="20" spans="2:13">
+      <c r="B20" t="s">
+        <v>111</v>
+      </c>
+      <c r="C20" t="s">
+        <v>112</v>
+      </c>
+      <c r="D20" t="s">
+        <v>113</v>
+      </c>
+      <c r="E20" t="s">
+        <v>84</v>
+      </c>
+      <c r="F20" t="s">
+        <v>57</v>
+      </c>
+      <c r="G20" t="s">
+        <v>38</v>
+      </c>
+      <c r="H20" t="s">
+        <v>85</v>
+      </c>
+      <c r="I20" t="s">
+        <v>114</v>
+      </c>
+      <c r="J20">
+        <v>0.2</v>
+      </c>
+      <c r="K20" t="s">
+        <v>38</v>
+      </c>
+      <c r="L20">
+        <v>1</v>
+      </c>
+      <c r="M20" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="21" spans="2:13">
+      <c r="B21" t="s">
+        <v>115</v>
+      </c>
+      <c r="C21" t="s">
+        <v>116</v>
+      </c>
+      <c r="D21" t="s">
+        <v>117</v>
+      </c>
+      <c r="E21" t="s">
+        <v>84</v>
+      </c>
+      <c r="F21" t="s">
+        <v>57</v>
+      </c>
+      <c r="G21" t="s">
+        <v>38</v>
+      </c>
+      <c r="H21" t="s">
+        <v>85</v>
+      </c>
+      <c r="I21" t="s">
+        <v>118</v>
+      </c>
+      <c r="J21">
+        <v>0.2</v>
+      </c>
+      <c r="K21" t="s">
+        <v>38</v>
+      </c>
+      <c r="L21">
+        <v>1</v>
+      </c>
+      <c r="M21" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="22" spans="2:13">
+      <c r="B22" t="s">
+        <v>119</v>
+      </c>
+      <c r="C22" t="s">
+        <v>120</v>
+      </c>
+      <c r="D22" t="s">
+        <v>121</v>
+      </c>
+      <c r="E22" t="s">
+        <v>84</v>
+      </c>
+      <c r="F22" t="s">
+        <v>37</v>
+      </c>
+      <c r="G22" t="s">
+        <v>38</v>
+      </c>
+      <c r="H22" t="s">
+        <v>85</v>
+      </c>
+      <c r="I22" t="s">
+        <v>122</v>
+      </c>
+      <c r="J22">
+        <v>30</v>
+      </c>
+      <c r="K22" t="s">
+        <v>38</v>
+      </c>
+      <c r="L22">
+        <v>1</v>
+      </c>
+      <c r="M22" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="23" spans="2:13">
+      <c r="B23" t="s">
+        <v>123</v>
+      </c>
+      <c r="C23" t="s">
+        <v>124</v>
+      </c>
+      <c r="D23" t="s">
+        <v>125</v>
+      </c>
+      <c r="E23" t="s">
+        <v>84</v>
+      </c>
+      <c r="F23" t="s">
+        <v>57</v>
+      </c>
+      <c r="G23" t="s">
+        <v>38</v>
+      </c>
+      <c r="H23" t="s">
+        <v>85</v>
+      </c>
+      <c r="I23" t="s">
+        <v>126</v>
+      </c>
+      <c r="J23">
+        <v>0.2</v>
+      </c>
+      <c r="K23" t="s">
+        <v>38</v>
+      </c>
+      <c r="L23">
+        <v>1</v>
+      </c>
+      <c r="M23" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="24" spans="2:13">
+      <c r="B24" t="s">
+        <v>127</v>
+      </c>
+      <c r="C24" t="s">
+        <v>128</v>
+      </c>
+      <c r="D24" t="s">
+        <v>129</v>
+      </c>
+      <c r="E24" t="s">
+        <v>84</v>
+      </c>
+      <c r="F24" t="s">
+        <v>70</v>
+      </c>
+      <c r="G24" t="s">
+        <v>38</v>
+      </c>
+      <c r="H24" t="s">
+        <v>85</v>
+      </c>
+      <c r="I24" t="s">
+        <v>130</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24" t="s">
+        <v>38</v>
+      </c>
+      <c r="L24">
+        <v>1</v>
+      </c>
+      <c r="M24" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="25" spans="2:13">
+      <c r="B25" t="s">
+        <v>131</v>
+      </c>
+      <c r="C25" t="s">
+        <v>132</v>
+      </c>
+      <c r="D25" t="s">
+        <v>133</v>
+      </c>
+      <c r="E25" t="s">
+        <v>36</v>
+      </c>
+      <c r="F25" t="s">
+        <v>70</v>
+      </c>
+      <c r="G25" t="s">
+        <v>38</v>
+      </c>
+      <c r="H25" t="s">
+        <v>39</v>
+      </c>
+      <c r="I25" t="s">
+        <v>134</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25" t="s">
+        <v>135</v>
+      </c>
+      <c r="L25">
+        <v>1</v>
+      </c>
+      <c r="M25" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="26" spans="2:13">
+      <c r="B26" t="s">
+        <v>136</v>
+      </c>
+      <c r="C26" t="s">
+        <v>137</v>
+      </c>
+      <c r="D26" t="s">
+        <v>138</v>
+      </c>
+      <c r="E26" t="s">
+        <v>84</v>
+      </c>
+      <c r="F26" t="s">
+        <v>37</v>
+      </c>
+      <c r="G26" t="s">
+        <v>38</v>
+      </c>
+      <c r="H26" t="s">
+        <v>85</v>
+      </c>
+      <c r="I26" t="s">
+        <v>139</v>
+      </c>
+      <c r="J26">
+        <v>-0.1</v>
+      </c>
+      <c r="K26" t="s">
+        <v>38</v>
+      </c>
+      <c r="L26">
+        <v>1</v>
+      </c>
+      <c r="M26" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="27" spans="2:13">
+      <c r="B27" t="s">
+        <v>140</v>
+      </c>
+      <c r="C27" t="s">
+        <v>141</v>
+      </c>
+      <c r="D27" t="s">
+        <v>142</v>
+      </c>
+      <c r="E27" t="s">
+        <v>84</v>
+      </c>
+      <c r="F27" t="s">
+        <v>37</v>
+      </c>
+      <c r="G27" t="s">
+        <v>38</v>
+      </c>
+      <c r="H27" t="s">
+        <v>85</v>
+      </c>
+      <c r="I27" t="s">
+        <v>143</v>
+      </c>
+      <c r="J27">
+        <v>-0.1</v>
+      </c>
+      <c r="K27" t="s">
+        <v>38</v>
+      </c>
+      <c r="L27">
+        <v>1</v>
+      </c>
+      <c r="M27" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="28" spans="2:13">
+      <c r="B28" t="s">
+        <v>144</v>
+      </c>
+      <c r="C28" t="s">
+        <v>145</v>
+      </c>
+      <c r="D28" t="s">
+        <v>146</v>
+      </c>
+      <c r="E28" t="s">
+        <v>84</v>
+      </c>
+      <c r="F28" t="s">
+        <v>37</v>
+      </c>
+      <c r="G28" t="s">
+        <v>38</v>
+      </c>
+      <c r="H28" t="s">
+        <v>85</v>
+      </c>
+      <c r="I28" t="s">
+        <v>147</v>
+      </c>
+      <c r="J28">
+        <v>-0.1</v>
+      </c>
+      <c r="K28" t="s">
+        <v>38</v>
+      </c>
+      <c r="L28">
+        <v>1</v>
+      </c>
+      <c r="M28" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="29" spans="2:13">
+      <c r="B29" t="s">
+        <v>148</v>
+      </c>
+      <c r="C29" t="s">
+        <v>149</v>
+      </c>
+      <c r="D29" t="s">
+        <v>150</v>
+      </c>
+      <c r="E29" t="s">
+        <v>84</v>
+      </c>
+      <c r="F29" t="s">
+        <v>37</v>
+      </c>
+      <c r="G29" t="s">
+        <v>38</v>
+      </c>
+      <c r="H29" t="s">
+        <v>85</v>
+      </c>
+      <c r="I29" t="s">
+        <v>151</v>
+      </c>
+      <c r="J29">
+        <v>1.1</v>
+      </c>
+      <c r="K29" t="s">
+        <v>152</v>
+      </c>
+      <c r="L29">
+        <v>1</v>
+      </c>
+      <c r="M29" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="30" spans="2:13">
+      <c r="B30" t="s">
+        <v>153</v>
+      </c>
+      <c r="C30" t="s">
+        <v>154</v>
+      </c>
+      <c r="D30" t="s">
+        <v>155</v>
+      </c>
+      <c r="E30" t="s">
+        <v>84</v>
+      </c>
+      <c r="F30" t="s">
+        <v>37</v>
+      </c>
+      <c r="G30" t="s">
+        <v>38</v>
+      </c>
+      <c r="H30" t="s">
+        <v>85</v>
+      </c>
+      <c r="I30" t="s">
+        <v>151</v>
+      </c>
+      <c r="J30">
+        <v>1.1</v>
+      </c>
+      <c r="K30" t="s">
+        <v>156</v>
+      </c>
+      <c r="L30">
+        <v>1</v>
+      </c>
+      <c r="M30" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="31" spans="2:13">
+      <c r="B31" t="s">
+        <v>157</v>
+      </c>
+      <c r="C31" t="s">
+        <v>158</v>
+      </c>
+      <c r="D31" t="s">
+        <v>159</v>
+      </c>
+      <c r="E31" t="s">
+        <v>84</v>
+      </c>
+      <c r="F31" t="s">
+        <v>70</v>
+      </c>
+      <c r="G31" t="s">
+        <v>38</v>
+      </c>
+      <c r="H31" t="s">
+        <v>85</v>
+      </c>
+      <c r="I31" t="s">
+        <v>160</v>
+      </c>
+      <c r="J31">
+        <v>0.1</v>
+      </c>
+      <c r="K31" t="s">
+        <v>38</v>
+      </c>
+      <c r="L31">
+        <v>1</v>
+      </c>
+      <c r="M31" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="32" spans="2:13">
+      <c r="B32" t="s">
+        <v>161</v>
+      </c>
+      <c r="C32" t="s">
+        <v>162</v>
+      </c>
+      <c r="D32" t="s">
+        <v>163</v>
+      </c>
+      <c r="E32" t="s">
+        <v>84</v>
+      </c>
+      <c r="F32" t="s">
+        <v>70</v>
+      </c>
+      <c r="G32" t="s">
+        <v>38</v>
+      </c>
+      <c r="H32" t="s">
+        <v>85</v>
+      </c>
+      <c r="I32" t="s">
+        <v>164</v>
+      </c>
+      <c r="J32">
+        <v>10</v>
+      </c>
+      <c r="K32" t="s">
+        <v>38</v>
+      </c>
+      <c r="L32">
+        <v>1</v>
+      </c>
+      <c r="M32" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13">
+      <c r="B33" t="s">
+        <v>165</v>
+      </c>
+      <c r="C33" t="s">
+        <v>166</v>
+      </c>
+      <c r="D33" t="s">
+        <v>167</v>
+      </c>
+      <c r="E33" t="s">
+        <v>84</v>
+      </c>
+      <c r="F33" t="s">
+        <v>70</v>
+      </c>
+      <c r="G33" t="s">
+        <v>38</v>
+      </c>
+      <c r="H33" t="s">
+        <v>85</v>
+      </c>
+      <c r="I33" t="s">
+        <v>168</v>
+      </c>
+      <c r="J33">
+        <v>0.2</v>
+      </c>
+      <c r="K33" t="s">
+        <v>38</v>
+      </c>
+      <c r="L33">
+        <v>1</v>
+      </c>
+      <c r="M33" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="34" spans="2:13">
+      <c r="B34" t="s">
+        <v>169</v>
+      </c>
+      <c r="C34" t="s">
+        <v>170</v>
+      </c>
+      <c r="D34" t="s">
+        <v>171</v>
+      </c>
+      <c r="E34" t="s">
+        <v>84</v>
+      </c>
+      <c r="F34" t="s">
+        <v>37</v>
+      </c>
+      <c r="G34" t="s">
+        <v>38</v>
+      </c>
+      <c r="H34" t="s">
+        <v>85</v>
+      </c>
+      <c r="I34" t="s">
+        <v>172</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34" t="s">
+        <v>173</v>
+      </c>
+      <c r="L34">
+        <v>1</v>
+      </c>
+      <c r="M34" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13">
+      <c r="B35" t="s">
+        <v>174</v>
+      </c>
+      <c r="C35" t="s">
+        <v>175</v>
+      </c>
+      <c r="D35" t="s">
+        <v>176</v>
+      </c>
+      <c r="E35" t="s">
+        <v>84</v>
+      </c>
+      <c r="F35" t="s">
+        <v>37</v>
+      </c>
+      <c r="G35" t="s">
+        <v>38</v>
+      </c>
+      <c r="H35" t="s">
+        <v>85</v>
+      </c>
+      <c r="I35" t="s">
+        <v>177</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35" t="s">
+        <v>178</v>
+      </c>
+      <c r="L35">
+        <v>1</v>
+      </c>
+      <c r="M35" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="36" spans="2:13">
+      <c r="B36" t="s">
+        <v>179</v>
+      </c>
+      <c r="C36" t="s">
+        <v>180</v>
+      </c>
+      <c r="D36" t="s">
+        <v>181</v>
+      </c>
+      <c r="E36" t="s">
+        <v>84</v>
+      </c>
+      <c r="F36" t="s">
+        <v>37</v>
+      </c>
+      <c r="G36" t="s">
+        <v>38</v>
+      </c>
+      <c r="H36" t="s">
+        <v>85</v>
+      </c>
+      <c r="I36" t="s">
+        <v>182</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36" t="s">
+        <v>38</v>
+      </c>
+      <c r="L36">
+        <v>1</v>
+      </c>
+      <c r="M36" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="37" spans="2:13">
+      <c r="B37" t="s">
+        <v>183</v>
+      </c>
+      <c r="C37" t="s">
+        <v>184</v>
+      </c>
+      <c r="D37" t="s">
+        <v>185</v>
+      </c>
+      <c r="E37" t="s">
+        <v>84</v>
+      </c>
+      <c r="F37" t="s">
+        <v>57</v>
+      </c>
+      <c r="G37" t="s">
+        <v>38</v>
+      </c>
+      <c r="H37" t="s">
+        <v>85</v>
+      </c>
+      <c r="I37" t="s">
+        <v>186</v>
+      </c>
+      <c r="J37">
+        <v>1</v>
+      </c>
+      <c r="K37" t="s">
+        <v>38</v>
+      </c>
+      <c r="L37">
+        <v>1</v>
+      </c>
+      <c r="M37" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="38" spans="2:13">
+      <c r="B38" t="s">
+        <v>187</v>
+      </c>
+      <c r="C38" t="s">
+        <v>188</v>
+      </c>
+      <c r="D38" t="s">
+        <v>189</v>
+      </c>
+      <c r="E38" t="s">
+        <v>84</v>
+      </c>
+      <c r="F38" t="s">
+        <v>70</v>
+      </c>
+      <c r="G38" t="s">
+        <v>38</v>
+      </c>
+      <c r="H38" t="s">
+        <v>85</v>
+      </c>
+      <c r="I38" t="s">
+        <v>190</v>
+      </c>
+      <c r="J38">
+        <v>0.2</v>
+      </c>
+      <c r="K38" t="s">
+        <v>38</v>
+      </c>
+      <c r="L38">
+        <v>1</v>
+      </c>
+      <c r="M38" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="39" spans="2:13">
+      <c r="B39" t="s">
+        <v>191</v>
+      </c>
+      <c r="C39" t="s">
+        <v>192</v>
+      </c>
+      <c r="D39" t="s">
+        <v>193</v>
+      </c>
+      <c r="E39" t="s">
+        <v>36</v>
+      </c>
+      <c r="F39" t="s">
+        <v>70</v>
+      </c>
+      <c r="G39" t="s">
+        <v>38</v>
+      </c>
+      <c r="H39" t="s">
+        <v>194</v>
+      </c>
+      <c r="I39" t="s">
+        <v>195</v>
+      </c>
+      <c r="J39">
+        <v>5</v>
+      </c>
+      <c r="K39" t="s">
+        <v>38</v>
+      </c>
+      <c r="L39">
+        <v>1</v>
+      </c>
+      <c r="M39" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="40" spans="2:13">
+      <c r="B40" t="s">
+        <v>196</v>
+      </c>
+      <c r="C40" t="s">
+        <v>197</v>
+      </c>
+      <c r="D40" t="s">
+        <v>198</v>
+      </c>
+      <c r="E40" t="s">
+        <v>84</v>
+      </c>
+      <c r="F40" t="s">
+        <v>37</v>
+      </c>
+      <c r="G40" t="s">
+        <v>38</v>
+      </c>
+      <c r="H40" t="s">
+        <v>85</v>
+      </c>
+      <c r="I40" t="s">
+        <v>199</v>
+      </c>
+      <c r="J40">
+        <v>1</v>
+      </c>
+      <c r="K40" t="s">
+        <v>38</v>
+      </c>
+      <c r="L40">
+        <v>1</v>
+      </c>
+      <c r="M40" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="41" spans="2:13">
+      <c r="B41" t="s">
+        <v>200</v>
+      </c>
+      <c r="C41" t="s">
+        <v>201</v>
+      </c>
+      <c r="D41" t="s">
+        <v>202</v>
+      </c>
+      <c r="E41" t="s">
+        <v>84</v>
+      </c>
+      <c r="F41" t="s">
+        <v>37</v>
+      </c>
+      <c r="G41" t="s">
+        <v>38</v>
+      </c>
+      <c r="H41" t="s">
+        <v>85</v>
+      </c>
+      <c r="I41" t="s">
+        <v>203</v>
+      </c>
+      <c r="J41">
+        <v>10</v>
+      </c>
+      <c r="K41" t="s">
+        <v>38</v>
+      </c>
+      <c r="L41">
+        <v>1</v>
+      </c>
+      <c r="M41" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="42" spans="2:13">
+      <c r="B42" t="s">
+        <v>204</v>
+      </c>
+      <c r="C42" t="s">
+        <v>205</v>
+      </c>
+      <c r="D42" t="s">
+        <v>206</v>
+      </c>
+      <c r="E42" t="s">
+        <v>84</v>
+      </c>
+      <c r="F42" t="s">
+        <v>70</v>
+      </c>
+      <c r="G42" t="s">
+        <v>38</v>
+      </c>
+      <c r="H42" t="s">
+        <v>85</v>
+      </c>
+      <c r="I42" t="s">
+        <v>207</v>
+      </c>
+      <c r="J42">
+        <v>1</v>
+      </c>
+      <c r="K42" t="s">
+        <v>38</v>
+      </c>
+      <c r="L42">
+        <v>1</v>
+      </c>
+      <c r="M42" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="43" spans="2:13">
+      <c r="B43" t="s">
+        <v>208</v>
+      </c>
+      <c r="C43" t="s">
+        <v>209</v>
+      </c>
+      <c r="D43" t="s">
+        <v>210</v>
+      </c>
+      <c r="E43" t="s">
+        <v>84</v>
+      </c>
+      <c r="F43" t="s">
+        <v>37</v>
+      </c>
+      <c r="G43" t="s">
+        <v>38</v>
+      </c>
+      <c r="H43" t="s">
+        <v>85</v>
+      </c>
+      <c r="I43" t="s">
+        <v>211</v>
+      </c>
+      <c r="J43">
+        <v>10</v>
+      </c>
+      <c r="K43" t="s">
+        <v>38</v>
+      </c>
+      <c r="L43">
+        <v>1</v>
+      </c>
+      <c r="M43" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="44" spans="2:13">
+      <c r="B44" t="s">
+        <v>212</v>
+      </c>
+      <c r="C44" t="s">
+        <v>213</v>
+      </c>
+      <c r="D44" t="s">
+        <v>214</v>
+      </c>
+      <c r="E44" t="s">
+        <v>84</v>
+      </c>
+      <c r="F44" t="s">
+        <v>70</v>
+      </c>
+      <c r="G44" t="s">
+        <v>38</v>
+      </c>
+      <c r="H44" t="s">
+        <v>85</v>
+      </c>
+      <c r="I44" t="s">
+        <v>215</v>
+      </c>
+      <c r="J44">
+        <v>10</v>
+      </c>
+      <c r="K44" t="s">
+        <v>38</v>
+      </c>
+      <c r="L44">
+        <v>1</v>
+      </c>
+      <c r="M44" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="45" spans="2:13">
+      <c r="B45" t="s">
+        <v>216</v>
+      </c>
+      <c r="C45" t="s">
+        <v>217</v>
+      </c>
+      <c r="D45" t="s">
+        <v>218</v>
+      </c>
+      <c r="E45" t="s">
+        <v>36</v>
+      </c>
+      <c r="F45" t="s">
+        <v>70</v>
+      </c>
+      <c r="G45" t="s">
+        <v>38</v>
+      </c>
+      <c r="H45" t="s">
+        <v>39</v>
+      </c>
+      <c r="I45" t="s">
+        <v>219</v>
+      </c>
+      <c r="J45">
+        <v>300</v>
+      </c>
+      <c r="K45" t="s">
+        <v>220</v>
+      </c>
+      <c r="L45">
+        <v>1</v>
+      </c>
+      <c r="M45" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="46" spans="2:13">
+      <c r="B46" t="s">
+        <v>221</v>
+      </c>
+      <c r="C46" t="s">
+        <v>222</v>
+      </c>
+      <c r="D46" t="s">
+        <v>223</v>
+      </c>
+      <c r="E46" t="s">
+        <v>36</v>
+      </c>
+      <c r="F46" t="s">
+        <v>37</v>
+      </c>
+      <c r="G46" t="s">
+        <v>38</v>
+      </c>
+      <c r="H46" t="s">
+        <v>39</v>
+      </c>
+      <c r="I46" t="s">
+        <v>224</v>
+      </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
+      <c r="K46" t="s">
+        <v>38</v>
+      </c>
+      <c r="L46">
+        <v>1</v>
+      </c>
+      <c r="M46" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="47" spans="2:13">
+      <c r="B47" t="s">
+        <v>225</v>
+      </c>
+      <c r="C47" t="s">
+        <v>226</v>
+      </c>
+      <c r="D47" t="s">
+        <v>227</v>
+      </c>
+      <c r="E47" t="s">
+        <v>36</v>
+      </c>
+      <c r="F47" t="s">
+        <v>70</v>
+      </c>
+      <c r="G47" t="s">
+        <v>38</v>
+      </c>
+      <c r="H47" t="s">
+        <v>39</v>
+      </c>
+      <c r="I47" t="s">
+        <v>228</v>
+      </c>
+      <c r="J47">
+        <v>1</v>
+      </c>
+      <c r="K47" t="s">
+        <v>38</v>
+      </c>
+      <c r="L47">
+        <v>1</v>
+      </c>
+      <c r="M47" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="48" spans="2:13">
+      <c r="B48" t="s">
+        <v>229</v>
+      </c>
+      <c r="C48" t="s">
+        <v>230</v>
+      </c>
+      <c r="D48" t="s">
+        <v>231</v>
+      </c>
+      <c r="E48" t="s">
+        <v>36</v>
+      </c>
+      <c r="F48" t="s">
+        <v>232</v>
+      </c>
+      <c r="G48" t="s">
+        <v>38</v>
+      </c>
+      <c r="H48" t="s">
+        <v>39</v>
+      </c>
+      <c r="I48" t="s">
+        <v>233</v>
+      </c>
+      <c r="J48">
+        <v>1</v>
+      </c>
+      <c r="K48" t="s">
+        <v>38</v>
+      </c>
+      <c r="L48">
+        <v>1</v>
+      </c>
+      <c r="M48" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="49" spans="2:13">
+      <c r="B49" t="s">
+        <v>234</v>
+      </c>
+      <c r="C49" t="s">
+        <v>235</v>
+      </c>
+      <c r="D49" t="s">
+        <v>236</v>
+      </c>
+      <c r="E49" t="s">
+        <v>36</v>
+      </c>
+      <c r="F49" t="s">
+        <v>37</v>
+      </c>
+      <c r="G49" t="s">
+        <v>38</v>
+      </c>
+      <c r="H49" t="s">
+        <v>39</v>
+      </c>
+      <c r="I49" t="s">
+        <v>237</v>
+      </c>
+      <c r="J49">
+        <v>1</v>
+      </c>
+      <c r="K49" t="s">
+        <v>38</v>
+      </c>
+      <c r="L49">
+        <v>1</v>
+      </c>
+      <c r="M49" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="50" spans="2:13">
+      <c r="B50" t="s">
+        <v>238</v>
+      </c>
+      <c r="C50" t="s">
+        <v>239</v>
+      </c>
+      <c r="D50" t="s">
+        <v>240</v>
+      </c>
+      <c r="E50" t="s">
+        <v>36</v>
+      </c>
+      <c r="F50" t="s">
+        <v>37</v>
+      </c>
+      <c r="G50" t="s">
+        <v>38</v>
+      </c>
+      <c r="H50" t="s">
+        <v>39</v>
+      </c>
+      <c r="I50" t="s">
+        <v>241</v>
+      </c>
+      <c r="J50">
+        <v>1</v>
+      </c>
+      <c r="K50" t="s">
+        <v>38</v>
+      </c>
+      <c r="L50">
+        <v>1</v>
+      </c>
+      <c r="M50" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="51" spans="2:13">
+      <c r="B51" t="s">
+        <v>242</v>
+      </c>
+      <c r="C51" t="s">
+        <v>243</v>
+      </c>
+      <c r="D51" t="s">
+        <v>244</v>
+      </c>
+      <c r="E51" t="s">
+        <v>84</v>
+      </c>
+      <c r="F51" t="s">
+        <v>70</v>
+      </c>
+      <c r="G51" t="s">
+        <v>38</v>
+      </c>
+      <c r="H51" t="s">
+        <v>85</v>
+      </c>
+      <c r="I51" t="s">
+        <v>245</v>
+      </c>
+      <c r="J51">
         <v>2</v>
       </c>
-      <c r="L6" t="s">
+      <c r="K51" t="s">
+        <v>246</v>
+      </c>
+      <c r="L51">
+        <v>1</v>
+      </c>
+      <c r="M51" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="52" spans="2:13">
+      <c r="B52" t="s">
+        <v>247</v>
+      </c>
+      <c r="C52" t="s">
+        <v>248</v>
+      </c>
+      <c r="D52" t="s">
+        <v>249</v>
+      </c>
+      <c r="E52" t="s">
+        <v>84</v>
+      </c>
+      <c r="F52" t="s">
+        <v>37</v>
+      </c>
+      <c r="G52" t="s">
+        <v>38</v>
+      </c>
+      <c r="H52" t="s">
+        <v>85</v>
+      </c>
+      <c r="I52" t="s">
+        <v>250</v>
+      </c>
+      <c r="J52">
+        <v>2</v>
+      </c>
+      <c r="K52" t="s">
+        <v>251</v>
+      </c>
+      <c r="L52">
+        <v>1</v>
+      </c>
+      <c r="M52" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="53" spans="2:13">
+      <c r="B53" t="s">
+        <v>252</v>
+      </c>
+      <c r="C53" t="s">
+        <v>253</v>
+      </c>
+      <c r="D53" t="s">
+        <v>254</v>
+      </c>
+      <c r="E53" t="s">
+        <v>84</v>
+      </c>
+      <c r="F53" t="s">
+        <v>37</v>
+      </c>
+      <c r="G53" t="s">
+        <v>38</v>
+      </c>
+      <c r="H53" t="s">
+        <v>85</v>
+      </c>
+      <c r="I53" t="s">
+        <v>250</v>
+      </c>
+      <c r="J53">
+        <v>2</v>
+      </c>
+      <c r="K53" t="s">
+        <v>255</v>
+      </c>
+      <c r="L53">
+        <v>1</v>
+      </c>
+      <c r="M53" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="54" spans="2:13">
+      <c r="B54" t="s">
+        <v>256</v>
+      </c>
+      <c r="C54" t="s">
+        <v>257</v>
+      </c>
+      <c r="D54" t="s">
+        <v>258</v>
+      </c>
+      <c r="E54" t="s">
+        <v>84</v>
+      </c>
+      <c r="F54" t="s">
+        <v>70</v>
+      </c>
+      <c r="G54" t="s">
+        <v>38</v>
+      </c>
+      <c r="H54" t="s">
+        <v>85</v>
+      </c>
+      <c r="I54" t="s">
+        <v>259</v>
+      </c>
+      <c r="J54">
+        <v>2</v>
+      </c>
+      <c r="K54" t="s">
+        <v>38</v>
+      </c>
+      <c r="L54">
+        <v>1</v>
+      </c>
+      <c r="M54" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="55" spans="2:13">
+      <c r="B55" t="s">
+        <v>260</v>
+      </c>
+      <c r="C55" t="s">
+        <v>261</v>
+      </c>
+      <c r="D55" t="s">
+        <v>262</v>
+      </c>
+      <c r="E55" t="s">
+        <v>84</v>
+      </c>
+      <c r="F55" t="s">
+        <v>37</v>
+      </c>
+      <c r="G55" t="s">
+        <v>38</v>
+      </c>
+      <c r="H55" t="s">
+        <v>85</v>
+      </c>
+      <c r="I55" t="s">
+        <v>263</v>
+      </c>
+      <c r="J55">
+        <v>20</v>
+      </c>
+      <c r="K55" t="s">
+        <v>38</v>
+      </c>
+      <c r="L55">
+        <v>1</v>
+      </c>
+      <c r="M55" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="56" spans="2:13">
+      <c r="B56" t="s">
+        <v>264</v>
+      </c>
+      <c r="C56" t="s">
+        <v>265</v>
+      </c>
+      <c r="D56" t="s">
+        <v>266</v>
+      </c>
+      <c r="E56" t="s">
+        <v>84</v>
+      </c>
+      <c r="F56" t="s">
+        <v>232</v>
+      </c>
+      <c r="G56" t="s">
+        <v>38</v>
+      </c>
+      <c r="H56" t="s">
+        <v>85</v>
+      </c>
+      <c r="I56" t="s">
+        <v>267</v>
+      </c>
+      <c r="J56">
+        <v>1000</v>
+      </c>
+      <c r="K56" t="s">
+        <v>38</v>
+      </c>
+      <c r="L56">
+        <v>1</v>
+      </c>
+      <c r="M56" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="57" spans="2:13">
+      <c r="B57" t="s">
+        <v>269</v>
+      </c>
+      <c r="C57" t="s">
+        <v>270</v>
+      </c>
+      <c r="D57" t="s">
+        <v>271</v>
+      </c>
+      <c r="E57" t="s">
+        <v>36</v>
+      </c>
+      <c r="F57" t="s">
+        <v>37</v>
+      </c>
+      <c r="G57" t="s">
+        <v>38</v>
+      </c>
+      <c r="H57" t="s">
+        <v>194</v>
+      </c>
+      <c r="I57" t="s">
+        <v>272</v>
+      </c>
+      <c r="J57">
+        <v>2</v>
+      </c>
+      <c r="K57" t="s">
+        <v>38</v>
+      </c>
+      <c r="L57">
+        <v>1</v>
+      </c>
+      <c r="M57" t="s">
         <v>41</v>
       </c>
-      <c r="M6">
-        <v>1</v>
-      </c>
-      <c r="N6" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="7" spans="2:14">
-      <c r="B7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C7" t="s">
-        <v>54</v>
-      </c>
-      <c r="D7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E7" t="s">
+    </row>
+    <row r="58" spans="2:13">
+      <c r="B58" t="s">
+        <v>273</v>
+      </c>
+      <c r="C58" t="s">
+        <v>274</v>
+      </c>
+      <c r="D58" t="s">
+        <v>275</v>
+      </c>
+      <c r="E58" t="s">
+        <v>36</v>
+      </c>
+      <c r="F58" t="s">
+        <v>37</v>
+      </c>
+      <c r="G58" t="s">
+        <v>38</v>
+      </c>
+      <c r="H58" t="s">
+        <v>194</v>
+      </c>
+      <c r="I58" t="s">
+        <v>276</v>
+      </c>
+      <c r="J58">
+        <v>200</v>
+      </c>
+      <c r="K58" t="s">
+        <v>38</v>
+      </c>
+      <c r="L58">
+        <v>1</v>
+      </c>
+      <c r="M58" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="59" spans="2:13">
+      <c r="B59" t="s">
+        <v>277</v>
+      </c>
+      <c r="C59" t="s">
+        <v>278</v>
+      </c>
+      <c r="D59" t="s">
+        <v>279</v>
+      </c>
+      <c r="E59" t="s">
+        <v>36</v>
+      </c>
+      <c r="F59" t="s">
+        <v>70</v>
+      </c>
+      <c r="G59" t="s">
+        <v>38</v>
+      </c>
+      <c r="H59" t="s">
+        <v>194</v>
+      </c>
+      <c r="I59" t="s">
+        <v>280</v>
+      </c>
+      <c r="J59">
+        <v>0</v>
+      </c>
+      <c r="K59" t="s">
+        <v>38</v>
+      </c>
+      <c r="L59">
+        <v>1</v>
+      </c>
+      <c r="M59" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="60" spans="2:13">
+      <c r="B60" t="s">
+        <v>281</v>
+      </c>
+      <c r="C60" t="s">
+        <v>282</v>
+      </c>
+      <c r="D60" t="s">
+        <v>283</v>
+      </c>
+      <c r="E60" t="s">
+        <v>36</v>
+      </c>
+      <c r="F60" t="s">
+        <v>70</v>
+      </c>
+      <c r="G60" t="s">
+        <v>38</v>
+      </c>
+      <c r="H60" t="s">
+        <v>194</v>
+      </c>
+      <c r="I60" t="s">
+        <v>284</v>
+      </c>
+      <c r="J60">
+        <v>2</v>
+      </c>
+      <c r="K60" t="s">
+        <v>38</v>
+      </c>
+      <c r="L60">
+        <v>1</v>
+      </c>
+      <c r="M60" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="61" spans="2:13">
+      <c r="B61" t="s">
+        <v>285</v>
+      </c>
+      <c r="C61" t="s">
+        <v>286</v>
+      </c>
+      <c r="D61" t="s">
+        <v>287</v>
+      </c>
+      <c r="E61" t="s">
+        <v>84</v>
+      </c>
+      <c r="F61" t="s">
+        <v>232</v>
+      </c>
+      <c r="G61" t="s">
+        <v>38</v>
+      </c>
+      <c r="H61" t="s">
+        <v>85</v>
+      </c>
+      <c r="I61" t="s">
+        <v>288</v>
+      </c>
+      <c r="J61">
+        <v>1</v>
+      </c>
+      <c r="K61" t="s">
+        <v>38</v>
+      </c>
+      <c r="L61">
+        <v>1</v>
+      </c>
+      <c r="M61" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="62" spans="2:13">
+      <c r="B62" t="s">
+        <v>289</v>
+      </c>
+      <c r="C62" t="s">
+        <v>290</v>
+      </c>
+      <c r="D62" t="s">
+        <v>291</v>
+      </c>
+      <c r="E62" t="s">
+        <v>36</v>
+      </c>
+      <c r="F62" t="s">
+        <v>70</v>
+      </c>
+      <c r="G62" t="s">
+        <v>38</v>
+      </c>
+      <c r="H62" t="s">
+        <v>194</v>
+      </c>
+      <c r="I62" t="s">
+        <v>292</v>
+      </c>
+      <c r="J62">
+        <v>1</v>
+      </c>
+      <c r="K62" t="s">
+        <v>38</v>
+      </c>
+      <c r="L62">
+        <v>1</v>
+      </c>
+      <c r="M62" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="63" spans="2:13">
+      <c r="B63" t="s">
+        <v>293</v>
+      </c>
+      <c r="C63" t="s">
+        <v>294</v>
+      </c>
+      <c r="D63" t="s">
+        <v>295</v>
+      </c>
+      <c r="E63" t="s">
+        <v>36</v>
+      </c>
+      <c r="F63" t="s">
+        <v>37</v>
+      </c>
+      <c r="G63" t="s">
+        <v>38</v>
+      </c>
+      <c r="H63" t="s">
+        <v>194</v>
+      </c>
+      <c r="I63" t="s">
+        <v>296</v>
+      </c>
+      <c r="J63">
+        <v>2</v>
+      </c>
+      <c r="K63" t="s">
+        <v>38</v>
+      </c>
+      <c r="L63">
+        <v>1</v>
+      </c>
+      <c r="M63" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="64" spans="2:13">
+      <c r="B64" t="s">
+        <v>297</v>
+      </c>
+      <c r="C64" t="s">
+        <v>298</v>
+      </c>
+      <c r="D64" t="s">
+        <v>299</v>
+      </c>
+      <c r="E64" t="s">
+        <v>36</v>
+      </c>
+      <c r="F64" t="s">
+        <v>70</v>
+      </c>
+      <c r="G64" t="s">
+        <v>38</v>
+      </c>
+      <c r="H64" t="s">
+        <v>194</v>
+      </c>
+      <c r="I64" t="s">
+        <v>300</v>
+      </c>
+      <c r="J64">
+        <v>1</v>
+      </c>
+      <c r="K64" t="s">
+        <v>38</v>
+      </c>
+      <c r="L64">
+        <v>1</v>
+      </c>
+      <c r="M64" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="65" spans="2:13">
+      <c r="B65" t="s">
+        <v>301</v>
+      </c>
+      <c r="C65" t="s">
+        <v>302</v>
+      </c>
+      <c r="D65" t="s">
+        <v>303</v>
+      </c>
+      <c r="E65" t="s">
+        <v>84</v>
+      </c>
+      <c r="F65" t="s">
+        <v>70</v>
+      </c>
+      <c r="G65" t="s">
+        <v>38</v>
+      </c>
+      <c r="H65" t="s">
+        <v>85</v>
+      </c>
+      <c r="I65" t="s">
+        <v>304</v>
+      </c>
+      <c r="J65">
+        <v>4</v>
+      </c>
+      <c r="K65" t="s">
+        <v>38</v>
+      </c>
+      <c r="L65">
+        <v>1</v>
+      </c>
+      <c r="M65" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="66" spans="2:13">
+      <c r="B66" t="s">
+        <v>305</v>
+      </c>
+      <c r="C66" t="s">
+        <v>306</v>
+      </c>
+      <c r="D66" t="s">
+        <v>307</v>
+      </c>
+      <c r="E66" t="s">
+        <v>84</v>
+      </c>
+      <c r="F66" t="s">
+        <v>37</v>
+      </c>
+      <c r="G66" t="s">
+        <v>38</v>
+      </c>
+      <c r="H66" t="s">
+        <v>85</v>
+      </c>
+      <c r="I66" t="s">
+        <v>308</v>
+      </c>
+      <c r="J66">
+        <v>0.2</v>
+      </c>
+      <c r="K66" t="s">
+        <v>38</v>
+      </c>
+      <c r="L66">
+        <v>1</v>
+      </c>
+      <c r="M66" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="67" spans="2:13">
+      <c r="B67" t="s">
+        <v>309</v>
+      </c>
+      <c r="C67" t="s">
+        <v>310</v>
+      </c>
+      <c r="D67" t="s">
+        <v>311</v>
+      </c>
+      <c r="E67" t="s">
+        <v>84</v>
+      </c>
+      <c r="F67" t="s">
+        <v>37</v>
+      </c>
+      <c r="G67" t="s">
+        <v>38</v>
+      </c>
+      <c r="H67" t="s">
+        <v>85</v>
+      </c>
+      <c r="I67" t="s">
+        <v>312</v>
+      </c>
+      <c r="J67">
+        <v>0.2</v>
+      </c>
+      <c r="K67" t="s">
+        <v>38</v>
+      </c>
+      <c r="L67">
+        <v>1</v>
+      </c>
+      <c r="M67" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="68" spans="2:13">
+      <c r="B68" t="s">
+        <v>313</v>
+      </c>
+      <c r="C68" t="s">
+        <v>314</v>
+      </c>
+      <c r="D68" t="s">
+        <v>315</v>
+      </c>
+      <c r="E68" t="s">
+        <v>84</v>
+      </c>
+      <c r="F68" t="s">
+        <v>57</v>
+      </c>
+      <c r="G68" t="s">
+        <v>38</v>
+      </c>
+      <c r="H68" t="s">
+        <v>85</v>
+      </c>
+      <c r="I68" t="s">
+        <v>316</v>
+      </c>
+      <c r="J68">
+        <v>10</v>
+      </c>
+      <c r="K68" t="s">
+        <v>38</v>
+      </c>
+      <c r="L68">
+        <v>1</v>
+      </c>
+      <c r="M68" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="69" spans="2:13">
+      <c r="B69" t="s">
+        <v>317</v>
+      </c>
+      <c r="C69" t="s">
+        <v>318</v>
+      </c>
+      <c r="D69" t="s">
+        <v>319</v>
+      </c>
+      <c r="E69" t="s">
+        <v>36</v>
+      </c>
+      <c r="F69" t="s">
+        <v>57</v>
+      </c>
+      <c r="G69" t="s">
+        <v>38</v>
+      </c>
+      <c r="H69" t="s">
         <v>39</v>
       </c>
-      <c r="F7" t="s">
-        <v>40</v>
-      </c>
-      <c r="G7" t="s">
+      <c r="I69" t="s">
+        <v>320</v>
+      </c>
+      <c r="J69">
+        <v>2</v>
+      </c>
+      <c r="K69" t="s">
+        <v>38</v>
+      </c>
+      <c r="L69">
+        <v>1</v>
+      </c>
+      <c r="M69" t="s">
         <v>41</v>
       </c>
-      <c r="H7" t="s">
-        <v>42</v>
-      </c>
-      <c r="I7">
-        <v>9</v>
-      </c>
-      <c r="J7" t="s">
-        <v>56</v>
-      </c>
-      <c r="K7">
-        <v>3</v>
-      </c>
-      <c r="L7" t="s">
+    </row>
+    <row r="70" spans="2:13">
+      <c r="B70" t="s">
+        <v>321</v>
+      </c>
+      <c r="C70" t="s">
+        <v>322</v>
+      </c>
+      <c r="D70" t="s">
+        <v>323</v>
+      </c>
+      <c r="E70" t="s">
+        <v>84</v>
+      </c>
+      <c r="F70" t="s">
+        <v>70</v>
+      </c>
+      <c r="G70" t="s">
+        <v>38</v>
+      </c>
+      <c r="H70" t="s">
+        <v>85</v>
+      </c>
+      <c r="I70" t="s">
+        <v>324</v>
+      </c>
+      <c r="J70">
+        <v>0</v>
+      </c>
+      <c r="K70" t="s">
+        <v>38</v>
+      </c>
+      <c r="L70">
+        <v>1</v>
+      </c>
+      <c r="M70" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="71" spans="2:13">
+      <c r="B71" t="s">
+        <v>325</v>
+      </c>
+      <c r="C71" t="s">
+        <v>326</v>
+      </c>
+      <c r="D71" t="s">
+        <v>327</v>
+      </c>
+      <c r="E71" t="s">
+        <v>84</v>
+      </c>
+      <c r="F71" t="s">
+        <v>37</v>
+      </c>
+      <c r="G71" t="s">
+        <v>38</v>
+      </c>
+      <c r="H71" t="s">
+        <v>85</v>
+      </c>
+      <c r="I71" t="s">
+        <v>328</v>
+      </c>
+      <c r="J71">
+        <v>1</v>
+      </c>
+      <c r="K71" t="s">
+        <v>38</v>
+      </c>
+      <c r="L71">
+        <v>1</v>
+      </c>
+      <c r="M71" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="72" spans="2:13">
+      <c r="B72" t="s">
+        <v>329</v>
+      </c>
+      <c r="C72" t="s">
+        <v>330</v>
+      </c>
+      <c r="D72" t="s">
+        <v>331</v>
+      </c>
+      <c r="E72" t="s">
+        <v>84</v>
+      </c>
+      <c r="F72" t="s">
+        <v>70</v>
+      </c>
+      <c r="G72" t="s">
+        <v>38</v>
+      </c>
+      <c r="H72" t="s">
+        <v>85</v>
+      </c>
+      <c r="I72" t="s">
+        <v>332</v>
+      </c>
+      <c r="J72">
+        <v>1</v>
+      </c>
+      <c r="K72" t="s">
+        <v>38</v>
+      </c>
+      <c r="L72">
+        <v>1</v>
+      </c>
+      <c r="M72" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="73" spans="2:13">
+      <c r="B73" t="s">
+        <v>333</v>
+      </c>
+      <c r="C73" t="s">
+        <v>334</v>
+      </c>
+      <c r="D73" t="s">
+        <v>335</v>
+      </c>
+      <c r="E73" t="s">
+        <v>84</v>
+      </c>
+      <c r="F73" t="s">
+        <v>70</v>
+      </c>
+      <c r="G73" t="s">
+        <v>38</v>
+      </c>
+      <c r="H73" t="s">
+        <v>85</v>
+      </c>
+      <c r="I73" t="s">
+        <v>336</v>
+      </c>
+      <c r="J73">
+        <v>0</v>
+      </c>
+      <c r="K73" t="s">
+        <v>246</v>
+      </c>
+      <c r="L73">
+        <v>1</v>
+      </c>
+      <c r="M73" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="74" spans="2:13">
+      <c r="B74" t="s">
+        <v>337</v>
+      </c>
+      <c r="C74" t="s">
+        <v>338</v>
+      </c>
+      <c r="D74" t="s">
+        <v>339</v>
+      </c>
+      <c r="E74" t="s">
+        <v>84</v>
+      </c>
+      <c r="F74" t="s">
+        <v>70</v>
+      </c>
+      <c r="G74" t="s">
+        <v>38</v>
+      </c>
+      <c r="H74" t="s">
+        <v>85</v>
+      </c>
+      <c r="I74" t="s">
+        <v>340</v>
+      </c>
+      <c r="J74">
+        <v>0</v>
+      </c>
+      <c r="K74" t="s">
+        <v>246</v>
+      </c>
+      <c r="L74">
+        <v>1</v>
+      </c>
+      <c r="M74" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="75" spans="2:13">
+      <c r="B75" t="s">
+        <v>341</v>
+      </c>
+      <c r="C75" t="s">
+        <v>342</v>
+      </c>
+      <c r="D75" t="s">
+        <v>343</v>
+      </c>
+      <c r="E75" t="s">
+        <v>36</v>
+      </c>
+      <c r="F75" t="s">
+        <v>70</v>
+      </c>
+      <c r="G75" t="s">
+        <v>38</v>
+      </c>
+      <c r="H75" t="s">
+        <v>39</v>
+      </c>
+      <c r="I75" t="s">
+        <v>344</v>
+      </c>
+      <c r="J75">
+        <v>1</v>
+      </c>
+      <c r="K75" t="s">
+        <v>38</v>
+      </c>
+      <c r="L75">
+        <v>1</v>
+      </c>
+      <c r="M75" t="s">
         <v>41</v>
       </c>
-      <c r="M7">
-        <v>1</v>
-      </c>
-      <c r="N7" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="8" spans="2:14">
-      <c r="B8" t="s">
+    </row>
+    <row r="76" spans="2:13">
+      <c r="B76" t="s">
+        <v>345</v>
+      </c>
+      <c r="C76" t="s">
+        <v>346</v>
+      </c>
+      <c r="D76" t="s">
+        <v>347</v>
+      </c>
+      <c r="E76" t="s">
+        <v>36</v>
+      </c>
+      <c r="F76" t="s">
         <v>57</v>
       </c>
-      <c r="C8" t="s">
-        <v>58</v>
-      </c>
-      <c r="D8" t="s">
-        <v>59</v>
-      </c>
-      <c r="E8" t="s">
+      <c r="G76" t="s">
+        <v>38</v>
+      </c>
+      <c r="H76" t="s">
         <v>39</v>
       </c>
-      <c r="F8" t="s">
-        <v>60</v>
-      </c>
-      <c r="G8" t="s">
+      <c r="I76" t="s">
+        <v>348</v>
+      </c>
+      <c r="J76">
+        <v>2</v>
+      </c>
+      <c r="K76" t="s">
+        <v>38</v>
+      </c>
+      <c r="L76">
+        <v>1</v>
+      </c>
+      <c r="M76" t="s">
         <v>41</v>
       </c>
-      <c r="H8" t="s">
-        <v>42</v>
-      </c>
-      <c r="I8">
-        <v>9</v>
-      </c>
-      <c r="J8" t="s">
-        <v>61</v>
-      </c>
-      <c r="K8">
-        <v>3</v>
-      </c>
-      <c r="L8" t="s">
+    </row>
+    <row r="77" spans="2:13">
+      <c r="B77" t="s">
+        <v>349</v>
+      </c>
+      <c r="C77" t="s">
+        <v>350</v>
+      </c>
+      <c r="D77" t="s">
+        <v>351</v>
+      </c>
+      <c r="E77" t="s">
+        <v>36</v>
+      </c>
+      <c r="F77" t="s">
+        <v>37</v>
+      </c>
+      <c r="G77" t="s">
+        <v>38</v>
+      </c>
+      <c r="H77" t="s">
+        <v>39</v>
+      </c>
+      <c r="I77" t="s">
+        <v>352</v>
+      </c>
+      <c r="J77">
+        <v>100</v>
+      </c>
+      <c r="K77" t="s">
+        <v>38</v>
+      </c>
+      <c r="L77">
+        <v>1</v>
+      </c>
+      <c r="M77" t="s">
         <v>41</v>
       </c>
-      <c r="M8">
-        <v>1</v>
-      </c>
-      <c r="N8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="9" spans="2:14">
-      <c r="B9" t="s">
-        <v>62</v>
-      </c>
-      <c r="C9" t="s">
-        <v>63</v>
-      </c>
-      <c r="D9" t="s">
-        <v>64</v>
-      </c>
-      <c r="E9" t="s">
-        <v>39</v>
-      </c>
-      <c r="F9" t="s">
-        <v>40</v>
-      </c>
-      <c r="G9" t="s">
-        <v>41</v>
-      </c>
-      <c r="H9" t="s">
-        <v>42</v>
-      </c>
-      <c r="I9">
-        <v>9</v>
-      </c>
-      <c r="J9" t="s">
-        <v>65</v>
-      </c>
-      <c r="K9">
-        <v>3</v>
-      </c>
-      <c r="L9" t="s">
-        <v>41</v>
-      </c>
-      <c r="M9">
-        <v>1</v>
-      </c>
-      <c r="N9" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="10" spans="2:14">
-      <c r="B10" t="s">
-        <v>66</v>
-      </c>
-      <c r="C10" t="s">
-        <v>67</v>
-      </c>
-      <c r="D10" t="s">
-        <v>68</v>
-      </c>
-      <c r="E10" t="s">
-        <v>39</v>
-      </c>
-      <c r="F10" t="s">
-        <v>40</v>
-      </c>
-      <c r="G10" t="s">
-        <v>41</v>
-      </c>
-      <c r="H10" t="s">
-        <v>42</v>
-      </c>
-      <c r="I10">
-        <v>9</v>
-      </c>
-      <c r="J10" t="s">
-        <v>69</v>
-      </c>
-      <c r="K10">
-        <v>1</v>
-      </c>
-      <c r="L10" t="s">
-        <v>41</v>
-      </c>
-      <c r="M10">
-        <v>1</v>
-      </c>
-      <c r="N10" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="11" spans="2:14">
-      <c r="B11" t="s">
+    </row>
+    <row r="78" spans="2:13">
+      <c r="B78" t="s">
+        <v>353</v>
+      </c>
+      <c r="C78" t="s">
+        <v>354</v>
+      </c>
+      <c r="D78" t="s">
+        <v>355</v>
+      </c>
+      <c r="E78" t="s">
+        <v>84</v>
+      </c>
+      <c r="F78" t="s">
+        <v>57</v>
+      </c>
+      <c r="G78" t="s">
+        <v>356</v>
+      </c>
+      <c r="H78" t="s">
+        <v>85</v>
+      </c>
+      <c r="I78" t="s">
+        <v>96</v>
+      </c>
+      <c r="J78">
+        <v>-0.25</v>
+      </c>
+      <c r="K78" t="s">
+        <v>38</v>
+      </c>
+      <c r="L78">
+        <v>1</v>
+      </c>
+      <c r="M78" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="79" spans="2:13">
+      <c r="B79" t="s">
+        <v>357</v>
+      </c>
+      <c r="C79" t="s">
+        <v>358</v>
+      </c>
+      <c r="D79" t="s">
+        <v>359</v>
+      </c>
+      <c r="E79" t="s">
+        <v>84</v>
+      </c>
+      <c r="F79" t="s">
+        <v>57</v>
+      </c>
+      <c r="G79" t="s">
+        <v>356</v>
+      </c>
+      <c r="H79" t="s">
+        <v>85</v>
+      </c>
+      <c r="I79" t="s">
+        <v>360</v>
+      </c>
+      <c r="J79">
+        <v>0.25</v>
+      </c>
+      <c r="K79" t="s">
+        <v>38</v>
+      </c>
+      <c r="L79">
+        <v>1</v>
+      </c>
+      <c r="M79" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="80" spans="2:13">
+      <c r="B80" t="s">
+        <v>361</v>
+      </c>
+      <c r="C80" t="s">
+        <v>362</v>
+      </c>
+      <c r="D80" t="s">
+        <v>363</v>
+      </c>
+      <c r="E80" t="s">
+        <v>84</v>
+      </c>
+      <c r="F80" t="s">
+        <v>57</v>
+      </c>
+      <c r="G80" t="s">
+        <v>356</v>
+      </c>
+      <c r="H80" t="s">
+        <v>85</v>
+      </c>
+      <c r="I80" t="s">
+        <v>364</v>
+      </c>
+      <c r="J80">
+        <v>0</v>
+      </c>
+      <c r="K80" t="s">
+        <v>38</v>
+      </c>
+      <c r="L80">
+        <v>1</v>
+      </c>
+      <c r="M80" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="81" spans="2:13">
+      <c r="B81" t="s">
+        <v>365</v>
+      </c>
+      <c r="C81" t="s">
+        <v>366</v>
+      </c>
+      <c r="D81" t="s">
+        <v>367</v>
+      </c>
+      <c r="E81" t="s">
+        <v>84</v>
+      </c>
+      <c r="F81" t="s">
+        <v>57</v>
+      </c>
+      <c r="G81" t="s">
+        <v>356</v>
+      </c>
+      <c r="H81" t="s">
+        <v>85</v>
+      </c>
+      <c r="I81" t="s">
+        <v>368</v>
+      </c>
+      <c r="J81">
+        <v>1</v>
+      </c>
+      <c r="K81" t="s">
+        <v>38</v>
+      </c>
+      <c r="L81">
+        <v>1</v>
+      </c>
+      <c r="M81" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="82" spans="2:13">
+      <c r="B82" t="s">
+        <v>369</v>
+      </c>
+      <c r="C82" t="s">
+        <v>370</v>
+      </c>
+      <c r="D82" t="s">
+        <v>371</v>
+      </c>
+      <c r="E82" t="s">
+        <v>84</v>
+      </c>
+      <c r="F82" t="s">
+        <v>57</v>
+      </c>
+      <c r="G82" t="s">
+        <v>356</v>
+      </c>
+      <c r="H82" t="s">
+        <v>85</v>
+      </c>
+      <c r="I82" t="s">
+        <v>372</v>
+      </c>
+      <c r="J82">
+        <v>-1</v>
+      </c>
+      <c r="K82" t="s">
+        <v>38</v>
+      </c>
+      <c r="L82">
+        <v>1</v>
+      </c>
+      <c r="M82" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="83" spans="2:13">
+      <c r="B83" t="s">
+        <v>373</v>
+      </c>
+      <c r="C83" t="s">
+        <v>374</v>
+      </c>
+      <c r="D83" t="s">
+        <v>375</v>
+      </c>
+      <c r="E83" t="s">
+        <v>84</v>
+      </c>
+      <c r="F83" t="s">
+        <v>57</v>
+      </c>
+      <c r="G83" t="s">
+        <v>356</v>
+      </c>
+      <c r="H83" t="s">
+        <v>85</v>
+      </c>
+      <c r="I83" t="s">
+        <v>139</v>
+      </c>
+      <c r="J83">
+        <v>0.1</v>
+      </c>
+      <c r="K83" t="s">
+        <v>38</v>
+      </c>
+      <c r="L83">
+        <v>1</v>
+      </c>
+      <c r="M83" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="84" spans="2:13">
+      <c r="B84" t="s">
+        <v>376</v>
+      </c>
+      <c r="C84" t="s">
+        <v>377</v>
+      </c>
+      <c r="D84" t="s">
+        <v>378</v>
+      </c>
+      <c r="E84" t="s">
+        <v>84</v>
+      </c>
+      <c r="F84" t="s">
+        <v>57</v>
+      </c>
+      <c r="G84" t="s">
+        <v>356</v>
+      </c>
+      <c r="H84" t="s">
+        <v>85</v>
+      </c>
+      <c r="I84" t="s">
+        <v>143</v>
+      </c>
+      <c r="J84">
+        <v>0.1</v>
+      </c>
+      <c r="K84" t="s">
+        <v>38</v>
+      </c>
+      <c r="L84">
+        <v>1</v>
+      </c>
+      <c r="M84" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="85" spans="2:13">
+      <c r="B85" t="s">
+        <v>379</v>
+      </c>
+      <c r="C85" t="s">
+        <v>380</v>
+      </c>
+      <c r="D85" t="s">
+        <v>381</v>
+      </c>
+      <c r="E85" t="s">
+        <v>84</v>
+      </c>
+      <c r="F85" t="s">
+        <v>57</v>
+      </c>
+      <c r="G85" t="s">
+        <v>356</v>
+      </c>
+      <c r="H85" t="s">
+        <v>85</v>
+      </c>
+      <c r="I85" t="s">
+        <v>147</v>
+      </c>
+      <c r="J85">
+        <v>0.1</v>
+      </c>
+      <c r="K85" t="s">
+        <v>38</v>
+      </c>
+      <c r="L85">
+        <v>1</v>
+      </c>
+      <c r="M85" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="86" spans="2:13">
+      <c r="B86" t="s">
+        <v>382</v>
+      </c>
+      <c r="C86" t="s">
+        <v>383</v>
+      </c>
+      <c r="D86" t="s">
+        <v>384</v>
+      </c>
+      <c r="E86" t="s">
+        <v>84</v>
+      </c>
+      <c r="F86" t="s">
+        <v>57</v>
+      </c>
+      <c r="G86" t="s">
+        <v>356</v>
+      </c>
+      <c r="H86" t="s">
+        <v>85</v>
+      </c>
+      <c r="I86" t="s">
+        <v>385</v>
+      </c>
+      <c r="J86">
+        <v>0</v>
+      </c>
+      <c r="K86" t="s">
+        <v>38</v>
+      </c>
+      <c r="L86">
+        <v>1</v>
+      </c>
+      <c r="M86" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="87" spans="2:13">
+      <c r="B87" t="s">
+        <v>386</v>
+      </c>
+      <c r="C87" t="s">
+        <v>387</v>
+      </c>
+      <c r="D87" t="s">
+        <v>388</v>
+      </c>
+      <c r="E87" t="s">
+        <v>84</v>
+      </c>
+      <c r="F87" t="s">
         <v>70</v>
       </c>
-      <c r="C11" t="s">
-        <v>71</v>
-      </c>
-      <c r="D11" t="s">
-        <v>72</v>
-      </c>
-      <c r="E11" t="s">
-        <v>39</v>
-      </c>
-      <c r="F11" t="s">
-        <v>73</v>
-      </c>
-      <c r="G11" t="s">
-        <v>41</v>
-      </c>
-      <c r="H11" t="s">
-        <v>42</v>
-      </c>
-      <c r="I11">
-        <v>9</v>
-      </c>
-      <c r="J11" t="s">
-        <v>74</v>
-      </c>
-      <c r="K11">
-        <v>50</v>
-      </c>
-      <c r="L11" t="s">
-        <v>41</v>
-      </c>
-      <c r="M11">
-        <v>1</v>
-      </c>
-      <c r="N11" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="12" spans="2:14">
-      <c r="B12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C12" t="s">
-        <v>76</v>
-      </c>
-      <c r="D12" t="s">
-        <v>77</v>
-      </c>
-      <c r="E12" t="s">
-        <v>39</v>
-      </c>
-      <c r="F12" t="s">
-        <v>73</v>
-      </c>
-      <c r="G12" t="s">
-        <v>41</v>
-      </c>
-      <c r="H12" t="s">
-        <v>42</v>
-      </c>
-      <c r="I12">
-        <v>9</v>
-      </c>
-      <c r="J12" t="s">
-        <v>78</v>
-      </c>
-      <c r="K12">
-        <v>0</v>
-      </c>
-      <c r="L12" t="s">
-        <v>41</v>
-      </c>
-      <c r="M12">
-        <v>1</v>
-      </c>
-      <c r="N12" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="13" spans="2:14">
-      <c r="B13" t="s">
-        <v>79</v>
-      </c>
-      <c r="C13" t="s">
-        <v>80</v>
-      </c>
-      <c r="D13" t="s">
-        <v>81</v>
-      </c>
-      <c r="E13" t="s">
-        <v>39</v>
-      </c>
-      <c r="F13" t="s">
-        <v>60</v>
-      </c>
-      <c r="G13" t="s">
-        <v>41</v>
-      </c>
-      <c r="H13" t="s">
-        <v>42</v>
-      </c>
-      <c r="I13">
-        <v>9</v>
-      </c>
-      <c r="J13" t="s">
-        <v>82</v>
-      </c>
-      <c r="K13">
-        <v>0</v>
-      </c>
-      <c r="L13" t="s">
-        <v>83</v>
-      </c>
-      <c r="M13">
-        <v>1</v>
-      </c>
-      <c r="N13" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="14" spans="2:14">
-      <c r="B14" t="s">
+      <c r="G87" t="s">
+        <v>38</v>
+      </c>
+      <c r="H87" t="s">
+        <v>85</v>
+      </c>
+      <c r="I87" t="s">
+        <v>389</v>
+      </c>
+      <c r="J87">
+        <v>1</v>
+      </c>
+      <c r="K87" t="s">
+        <v>38</v>
+      </c>
+      <c r="L87">
+        <v>1</v>
+      </c>
+      <c r="M87" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="88" spans="2:13">
+      <c r="B88" t="s">
+        <v>390</v>
+      </c>
+      <c r="C88" t="s">
+        <v>391</v>
+      </c>
+      <c r="D88" t="s">
+        <v>392</v>
+      </c>
+      <c r="E88" t="s">
         <v>84</v>
       </c>
-      <c r="C14" t="s">
+      <c r="F88" t="s">
+        <v>70</v>
+      </c>
+      <c r="G88" t="s">
+        <v>38</v>
+      </c>
+      <c r="H88" t="s">
         <v>85</v>
       </c>
-      <c r="D14" t="s">
-        <v>86</v>
-      </c>
-      <c r="E14" t="s">
-        <v>87</v>
-      </c>
-      <c r="F14" t="s">
-        <v>40</v>
-      </c>
-      <c r="G14" t="s">
-        <v>41</v>
-      </c>
-      <c r="H14" t="s">
+      <c r="I88" t="s">
+        <v>393</v>
+      </c>
+      <c r="J88">
+        <v>1.1</v>
+      </c>
+      <c r="K88" t="s">
+        <v>38</v>
+      </c>
+      <c r="L88">
+        <v>1</v>
+      </c>
+      <c r="M88" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="89" spans="2:13">
+      <c r="B89" t="s">
+        <v>394</v>
+      </c>
+      <c r="C89" t="s">
+        <v>395</v>
+      </c>
+      <c r="D89" t="s">
+        <v>396</v>
+      </c>
+      <c r="E89" t="s">
+        <v>84</v>
+      </c>
+      <c r="F89" t="s">
+        <v>70</v>
+      </c>
+      <c r="G89" t="s">
+        <v>38</v>
+      </c>
+      <c r="H89" t="s">
+        <v>85</v>
+      </c>
+      <c r="I89" t="s">
+        <v>397</v>
+      </c>
+      <c r="J89">
+        <v>1.1</v>
+      </c>
+      <c r="K89" t="s">
+        <v>38</v>
+      </c>
+      <c r="L89">
+        <v>1</v>
+      </c>
+      <c r="M89" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="90" spans="2:13">
+      <c r="B90" t="s">
+        <v>398</v>
+      </c>
+      <c r="C90" t="s">
+        <v>399</v>
+      </c>
+      <c r="D90" t="s">
+        <v>400</v>
+      </c>
+      <c r="E90" t="s">
+        <v>84</v>
+      </c>
+      <c r="F90" t="s">
+        <v>70</v>
+      </c>
+      <c r="G90" t="s">
+        <v>38</v>
+      </c>
+      <c r="H90" t="s">
+        <v>85</v>
+      </c>
+      <c r="I90" t="s">
+        <v>401</v>
+      </c>
+      <c r="J90">
+        <v>0.1</v>
+      </c>
+      <c r="K90" t="s">
+        <v>38</v>
+      </c>
+      <c r="L90">
+        <v>1</v>
+      </c>
+      <c r="M90" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="91" spans="2:13">
+      <c r="B91" t="s">
+        <v>402</v>
+      </c>
+      <c r="C91" t="s">
+        <v>403</v>
+      </c>
+      <c r="D91" t="s">
+        <v>404</v>
+      </c>
+      <c r="E91" t="s">
+        <v>84</v>
+      </c>
+      <c r="F91" t="s">
+        <v>37</v>
+      </c>
+      <c r="G91" t="s">
+        <v>38</v>
+      </c>
+      <c r="H91" t="s">
+        <v>85</v>
+      </c>
+      <c r="I91" t="s">
+        <v>405</v>
+      </c>
+      <c r="J91">
+        <v>10</v>
+      </c>
+      <c r="K91" t="s">
+        <v>406</v>
+      </c>
+      <c r="L91">
+        <v>1</v>
+      </c>
+      <c r="M91" t="s">
         <v>88</v>
       </c>
-      <c r="I14">
-        <v>1</v>
-      </c>
-      <c r="J14" t="s">
-        <v>89</v>
-      </c>
-      <c r="K14">
-        <v>15</v>
-      </c>
-      <c r="L14" t="s">
-        <v>90</v>
-      </c>
-      <c r="M14">
-        <v>1</v>
-      </c>
-      <c r="N14" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="15" spans="2:14">
-      <c r="B15" t="s">
-        <v>92</v>
-      </c>
-      <c r="C15" t="s">
-        <v>93</v>
-      </c>
-      <c r="D15" t="s">
-        <v>94</v>
-      </c>
-      <c r="E15" t="s">
-        <v>87</v>
-      </c>
-      <c r="F15" t="s">
-        <v>40</v>
-      </c>
-      <c r="G15" t="s">
-        <v>41</v>
-      </c>
-      <c r="H15" t="s">
+    </row>
+    <row r="92" spans="2:13">
+      <c r="B92" t="s">
+        <v>407</v>
+      </c>
+      <c r="C92" t="s">
+        <v>408</v>
+      </c>
+      <c r="D92" t="s">
+        <v>409</v>
+      </c>
+      <c r="E92" t="s">
+        <v>84</v>
+      </c>
+      <c r="F92" t="s">
+        <v>70</v>
+      </c>
+      <c r="G92" t="s">
+        <v>38</v>
+      </c>
+      <c r="H92" t="s">
+        <v>85</v>
+      </c>
+      <c r="I92" t="s">
+        <v>410</v>
+      </c>
+      <c r="J92">
+        <v>0.1</v>
+      </c>
+      <c r="K92" t="s">
+        <v>38</v>
+      </c>
+      <c r="L92">
+        <v>1</v>
+      </c>
+      <c r="M92" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="93" spans="2:13">
+      <c r="B93" t="s">
+        <v>411</v>
+      </c>
+      <c r="C93" t="s">
+        <v>412</v>
+      </c>
+      <c r="D93" t="s">
+        <v>413</v>
+      </c>
+      <c r="E93" t="s">
+        <v>84</v>
+      </c>
+      <c r="F93" t="s">
+        <v>37</v>
+      </c>
+      <c r="G93" t="s">
+        <v>38</v>
+      </c>
+      <c r="H93" t="s">
+        <v>85</v>
+      </c>
+      <c r="I93" t="s">
+        <v>414</v>
+      </c>
+      <c r="J93">
+        <v>10</v>
+      </c>
+      <c r="K93" t="s">
+        <v>38</v>
+      </c>
+      <c r="L93">
+        <v>1</v>
+      </c>
+      <c r="M93" t="s">
         <v>88</v>
       </c>
-      <c r="I15">
-        <v>1</v>
-      </c>
-      <c r="J15" t="s">
-        <v>95</v>
-      </c>
-      <c r="K15">
-        <v>100</v>
-      </c>
-      <c r="L15" t="s">
-        <v>41</v>
-      </c>
-      <c r="M15">
-        <v>1</v>
-      </c>
-      <c r="N15" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="16" spans="2:14">
-      <c r="B16" t="s">
-        <v>96</v>
-      </c>
-      <c r="C16" t="s">
+    </row>
+    <row r="94" spans="2:13">
+      <c r="B94" t="s">
+        <v>415</v>
+      </c>
+      <c r="C94" t="s">
+        <v>416</v>
+      </c>
+      <c r="D94" t="s">
+        <v>417</v>
+      </c>
+      <c r="E94" t="s">
+        <v>84</v>
+      </c>
+      <c r="F94" t="s">
+        <v>70</v>
+      </c>
+      <c r="G94" t="s">
+        <v>38</v>
+      </c>
+      <c r="H94" t="s">
+        <v>85</v>
+      </c>
+      <c r="I94" t="s">
+        <v>418</v>
+      </c>
+      <c r="J94">
+        <v>1</v>
+      </c>
+      <c r="K94" t="s">
+        <v>38</v>
+      </c>
+      <c r="L94">
+        <v>1</v>
+      </c>
+      <c r="M94" t="s">
         <v>97</v>
       </c>
-      <c r="D16" t="s">
-        <v>98</v>
-      </c>
-      <c r="E16" t="s">
-        <v>87</v>
-      </c>
-      <c r="F16" t="s">
-        <v>73</v>
-      </c>
-      <c r="G16" t="s">
-        <v>41</v>
-      </c>
-      <c r="H16" t="s">
+    </row>
+    <row r="95" spans="2:13">
+      <c r="B95" t="s">
+        <v>419</v>
+      </c>
+      <c r="C95" t="s">
+        <v>420</v>
+      </c>
+      <c r="D95" t="s">
+        <v>421</v>
+      </c>
+      <c r="E95" t="s">
+        <v>84</v>
+      </c>
+      <c r="F95" t="s">
+        <v>37</v>
+      </c>
+      <c r="G95" t="s">
+        <v>38</v>
+      </c>
+      <c r="H95" t="s">
+        <v>85</v>
+      </c>
+      <c r="I95" t="s">
+        <v>422</v>
+      </c>
+      <c r="J95">
+        <v>10</v>
+      </c>
+      <c r="K95" t="s">
+        <v>423</v>
+      </c>
+      <c r="L95">
+        <v>1</v>
+      </c>
+      <c r="M95" t="s">
         <v>88</v>
       </c>
-      <c r="I16">
-        <v>1</v>
-      </c>
-      <c r="J16" t="s">
-        <v>99</v>
-      </c>
-      <c r="K16">
-        <v>0.2</v>
-      </c>
-      <c r="L16" t="s">
-        <v>41</v>
-      </c>
-      <c r="M16">
-        <v>1</v>
-      </c>
-      <c r="N16" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="17" spans="2:14">
-      <c r="B17" t="s">
-        <v>101</v>
-      </c>
-      <c r="C17" t="s">
-        <v>102</v>
-      </c>
-      <c r="D17" t="s">
-        <v>103</v>
-      </c>
-      <c r="E17" t="s">
-        <v>87</v>
-      </c>
-      <c r="F17" t="s">
-        <v>60</v>
-      </c>
-      <c r="G17" t="s">
-        <v>41</v>
-      </c>
-      <c r="H17" t="s">
+    </row>
+    <row r="96" spans="2:13">
+      <c r="B96" t="s">
+        <v>424</v>
+      </c>
+      <c r="C96" t="s">
+        <v>425</v>
+      </c>
+      <c r="D96" t="s">
+        <v>426</v>
+      </c>
+      <c r="E96" t="s">
+        <v>84</v>
+      </c>
+      <c r="F96" t="s">
+        <v>37</v>
+      </c>
+      <c r="G96" t="s">
+        <v>38</v>
+      </c>
+      <c r="H96" t="s">
+        <v>85</v>
+      </c>
+      <c r="I96" t="s">
+        <v>427</v>
+      </c>
+      <c r="J96">
+        <v>10</v>
+      </c>
+      <c r="K96" t="s">
+        <v>38</v>
+      </c>
+      <c r="L96">
+        <v>1</v>
+      </c>
+      <c r="M96" t="s">
         <v>88</v>
-      </c>
-      <c r="I17">
-        <v>1</v>
-      </c>
-      <c r="J17" t="s">
-        <v>104</v>
-      </c>
-      <c r="K17">
-        <v>0.2</v>
-      </c>
-      <c r="L17" t="s">
-        <v>41</v>
-      </c>
-      <c r="M17">
-        <v>1</v>
-      </c>
-      <c r="N17" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="18" spans="2:14">
-      <c r="B18" t="s">
-        <v>106</v>
-      </c>
-      <c r="C18" t="s">
-        <v>107</v>
-      </c>
-      <c r="D18" t="s">
-        <v>108</v>
-      </c>
-      <c r="E18" t="s">
-        <v>87</v>
-      </c>
-      <c r="F18" t="s">
-        <v>60</v>
-      </c>
-      <c r="G18" t="s">
-        <v>41</v>
-      </c>
-      <c r="H18" t="s">
-        <v>88</v>
-      </c>
-      <c r="I18">
-        <v>1</v>
-      </c>
-      <c r="J18" t="s">
-        <v>109</v>
-      </c>
-      <c r="K18">
-        <v>0.2</v>
-      </c>
-      <c r="L18" t="s">
-        <v>41</v>
-      </c>
-      <c r="M18">
-        <v>1</v>
-      </c>
-      <c r="N18" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="19" spans="2:14">
-      <c r="B19" t="s">
-        <v>110</v>
-      </c>
-      <c r="C19" t="s">
-        <v>111</v>
-      </c>
-      <c r="D19" t="s">
-        <v>112</v>
-      </c>
-      <c r="E19" t="s">
-        <v>87</v>
-      </c>
-      <c r="F19" t="s">
-        <v>60</v>
-      </c>
-      <c r="G19" t="s">
-        <v>41</v>
-      </c>
-      <c r="H19" t="s">
-        <v>88</v>
-      </c>
-      <c r="I19">
-        <v>1</v>
-      </c>
-      <c r="J19" t="s">
-        <v>113</v>
-      </c>
-      <c r="K19">
-        <v>0.2</v>
-      </c>
-      <c r="L19" t="s">
-        <v>41</v>
-      </c>
-      <c r="M19">
-        <v>1</v>
-      </c>
-      <c r="N19" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="20" spans="2:14">
-      <c r="B20" t="s">
-        <v>114</v>
-      </c>
-      <c r="C20" t="s">
-        <v>115</v>
-      </c>
-      <c r="D20" t="s">
-        <v>116</v>
-      </c>
-      <c r="E20" t="s">
-        <v>87</v>
-      </c>
-      <c r="F20" t="s">
-        <v>60</v>
-      </c>
-      <c r="G20" t="s">
-        <v>41</v>
-      </c>
-      <c r="H20" t="s">
-        <v>88</v>
-      </c>
-      <c r="I20">
-        <v>1</v>
-      </c>
-      <c r="J20" t="s">
-        <v>117</v>
-      </c>
-      <c r="K20">
-        <v>0.2</v>
-      </c>
-      <c r="L20" t="s">
-        <v>41</v>
-      </c>
-      <c r="M20">
-        <v>1</v>
-      </c>
-      <c r="N20" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="21" spans="2:14">
-      <c r="B21" t="s">
-        <v>118</v>
-      </c>
-      <c r="C21" t="s">
-        <v>119</v>
-      </c>
-      <c r="D21" t="s">
-        <v>120</v>
-      </c>
-      <c r="E21" t="s">
-        <v>87</v>
-      </c>
-      <c r="F21" t="s">
-        <v>60</v>
-      </c>
-      <c r="G21" t="s">
-        <v>41</v>
-      </c>
-      <c r="H21" t="s">
-        <v>88</v>
-      </c>
-      <c r="I21">
-        <v>1</v>
-      </c>
-      <c r="J21" t="s">
-        <v>121</v>
-      </c>
-      <c r="K21">
-        <v>0.2</v>
-      </c>
-      <c r="L21" t="s">
-        <v>41</v>
-      </c>
-      <c r="M21">
-        <v>1</v>
-      </c>
-      <c r="N21" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="22" spans="2:14">
-      <c r="B22" t="s">
-        <v>122</v>
-      </c>
-      <c r="C22" t="s">
-        <v>123</v>
-      </c>
-      <c r="D22" t="s">
-        <v>124</v>
-      </c>
-      <c r="E22" t="s">
-        <v>87</v>
-      </c>
-      <c r="F22" t="s">
-        <v>40</v>
-      </c>
-      <c r="G22" t="s">
-        <v>41</v>
-      </c>
-      <c r="H22" t="s">
-        <v>88</v>
-      </c>
-      <c r="I22">
-        <v>1</v>
-      </c>
-      <c r="J22" t="s">
-        <v>125</v>
-      </c>
-      <c r="K22">
-        <v>30</v>
-      </c>
-      <c r="L22" t="s">
-        <v>41</v>
-      </c>
-      <c r="M22">
-        <v>1</v>
-      </c>
-      <c r="N22" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="23" spans="2:14">
-      <c r="B23" t="s">
-        <v>126</v>
-      </c>
-      <c r="C23" t="s">
-        <v>127</v>
-      </c>
-      <c r="D23" t="s">
-        <v>128</v>
-      </c>
-      <c r="E23" t="s">
-        <v>87</v>
-      </c>
-      <c r="F23" t="s">
-        <v>60</v>
-      </c>
-      <c r="G23" t="s">
-        <v>41</v>
-      </c>
-      <c r="H23" t="s">
-        <v>88</v>
-      </c>
-      <c r="I23">
-        <v>1</v>
-      </c>
-      <c r="J23" t="s">
-        <v>129</v>
-      </c>
-      <c r="K23">
-        <v>0.2</v>
-      </c>
-      <c r="L23" t="s">
-        <v>41</v>
-      </c>
-      <c r="M23">
-        <v>1</v>
-      </c>
-      <c r="N23" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="24" spans="2:14">
-      <c r="B24" t="s">
-        <v>130</v>
-      </c>
-      <c r="C24" t="s">
-        <v>131</v>
-      </c>
-      <c r="D24" t="s">
-        <v>132</v>
-      </c>
-      <c r="E24" t="s">
-        <v>87</v>
-      </c>
-      <c r="F24" t="s">
-        <v>73</v>
-      </c>
-      <c r="G24" t="s">
-        <v>41</v>
-      </c>
-      <c r="H24" t="s">
-        <v>88</v>
-      </c>
-      <c r="I24">
-        <v>1</v>
-      </c>
-      <c r="J24" t="s">
-        <v>133</v>
-      </c>
-      <c r="K24">
-        <v>0</v>
-      </c>
-      <c r="L24" t="s">
-        <v>41</v>
-      </c>
-      <c r="M24">
-        <v>1</v>
-      </c>
-      <c r="N24" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="25" spans="2:14">
-      <c r="B25" t="s">
-        <v>134</v>
-      </c>
-      <c r="C25" t="s">
-        <v>135</v>
-      </c>
-      <c r="D25" t="s">
-        <v>136</v>
-      </c>
-      <c r="E25" t="s">
-        <v>39</v>
-      </c>
-      <c r="F25" t="s">
-        <v>73</v>
-      </c>
-      <c r="G25" t="s">
-        <v>41</v>
-      </c>
-      <c r="H25" t="s">
-        <v>42</v>
-      </c>
-      <c r="I25">
-        <v>9</v>
-      </c>
-      <c r="J25" t="s">
-        <v>137</v>
-      </c>
-      <c r="K25">
-        <v>0</v>
-      </c>
-      <c r="L25" t="s">
-        <v>138</v>
-      </c>
-      <c r="M25">
-        <v>1</v>
-      </c>
-      <c r="N25" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="26" spans="2:14">
-      <c r="B26" t="s">
-        <v>139</v>
-      </c>
-      <c r="C26" t="s">
-        <v>140</v>
-      </c>
-      <c r="D26" t="s">
-        <v>141</v>
-      </c>
-      <c r="E26" t="s">
-        <v>87</v>
-      </c>
-      <c r="F26" t="s">
-        <v>40</v>
-      </c>
-      <c r="G26" t="s">
-        <v>41</v>
-      </c>
-      <c r="H26" t="s">
-        <v>88</v>
-      </c>
-      <c r="I26">
-        <v>1</v>
-      </c>
-      <c r="J26" t="s">
-        <v>142</v>
-      </c>
-      <c r="K26">
-        <v>-0.1</v>
-      </c>
-      <c r="L26" t="s">
-        <v>41</v>
-      </c>
-      <c r="M26">
-        <v>1</v>
-      </c>
-      <c r="N26" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="27" spans="2:14">
-      <c r="B27" t="s">
-        <v>143</v>
-      </c>
-      <c r="C27" t="s">
-        <v>144</v>
-      </c>
-      <c r="D27" t="s">
-        <v>145</v>
-      </c>
-      <c r="E27" t="s">
-        <v>87</v>
-      </c>
-      <c r="F27" t="s">
-        <v>40</v>
-      </c>
-      <c r="G27" t="s">
-        <v>41</v>
-      </c>
-      <c r="H27" t="s">
-        <v>88</v>
-      </c>
-      <c r="I27">
-        <v>1</v>
-      </c>
-      <c r="J27" t="s">
-        <v>146</v>
-      </c>
-      <c r="K27">
-        <v>-0.1</v>
-      </c>
-      <c r="L27" t="s">
-        <v>41</v>
-      </c>
-      <c r="M27">
-        <v>1</v>
-      </c>
-      <c r="N27" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="28" spans="2:14">
-      <c r="B28" t="s">
-        <v>147</v>
-      </c>
-      <c r="C28" t="s">
-        <v>148</v>
-      </c>
-      <c r="D28" t="s">
-        <v>149</v>
-      </c>
-      <c r="E28" t="s">
-        <v>87</v>
-      </c>
-      <c r="F28" t="s">
-        <v>40</v>
-      </c>
-      <c r="G28" t="s">
-        <v>41</v>
-      </c>
-      <c r="H28" t="s">
-        <v>88</v>
-      </c>
-      <c r="I28">
-        <v>1</v>
-      </c>
-      <c r="J28" t="s">
-        <v>150</v>
-      </c>
-      <c r="K28">
-        <v>-0.1</v>
-      </c>
-      <c r="L28" t="s">
-        <v>41</v>
-      </c>
-      <c r="M28">
-        <v>1</v>
-      </c>
-      <c r="N28" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="29" spans="2:14">
-      <c r="B29" t="s">
-        <v>151</v>
-      </c>
-      <c r="C29" t="s">
-        <v>152</v>
-      </c>
-      <c r="D29" t="s">
-        <v>153</v>
-      </c>
-      <c r="E29" t="s">
-        <v>87</v>
-      </c>
-      <c r="F29" t="s">
-        <v>40</v>
-      </c>
-      <c r="G29" t="s">
-        <v>41</v>
-      </c>
-      <c r="H29" t="s">
-        <v>88</v>
-      </c>
-      <c r="I29">
-        <v>1</v>
-      </c>
-      <c r="J29" t="s">
-        <v>154</v>
-      </c>
-      <c r="K29">
-        <v>1.1</v>
-      </c>
-      <c r="L29" t="s">
-        <v>155</v>
-      </c>
-      <c r="M29">
-        <v>1</v>
-      </c>
-      <c r="N29" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="30" spans="2:14">
-      <c r="B30" t="s">
-        <v>156</v>
-      </c>
-      <c r="C30" t="s">
-        <v>157</v>
-      </c>
-      <c r="D30" t="s">
-        <v>158</v>
-      </c>
-      <c r="E30" t="s">
-        <v>87</v>
-      </c>
-      <c r="F30" t="s">
-        <v>40</v>
-      </c>
-      <c r="G30" t="s">
-        <v>41</v>
-      </c>
-      <c r="H30" t="s">
-        <v>88</v>
-      </c>
-      <c r="I30">
-        <v>1</v>
-      </c>
-      <c r="J30" t="s">
-        <v>154</v>
-      </c>
-      <c r="K30">
-        <v>1.1</v>
-      </c>
-      <c r="L30" t="s">
-        <v>159</v>
-      </c>
-      <c r="M30">
-        <v>1</v>
-      </c>
-      <c r="N30" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="31" spans="2:14">
-      <c r="B31" t="s">
-        <v>160</v>
-      </c>
-      <c r="C31" t="s">
-        <v>161</v>
-      </c>
-      <c r="D31" t="s">
-        <v>162</v>
-      </c>
-      <c r="E31" t="s">
-        <v>87</v>
-      </c>
-      <c r="F31" t="s">
-        <v>73</v>
-      </c>
-      <c r="G31" t="s">
-        <v>41</v>
-      </c>
-      <c r="H31" t="s">
-        <v>88</v>
-      </c>
-      <c r="I31">
-        <v>1</v>
-      </c>
-      <c r="J31" t="s">
-        <v>163</v>
-      </c>
-      <c r="K31">
-        <v>0.1</v>
-      </c>
-      <c r="L31" t="s">
-        <v>41</v>
-      </c>
-      <c r="M31">
-        <v>1</v>
-      </c>
-      <c r="N31" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="32" spans="2:14">
-      <c r="B32" t="s">
-        <v>164</v>
-      </c>
-      <c r="C32" t="s">
-        <v>165</v>
-      </c>
-      <c r="D32" t="s">
-        <v>166</v>
-      </c>
-      <c r="E32" t="s">
-        <v>87</v>
-      </c>
-      <c r="F32" t="s">
-        <v>73</v>
-      </c>
-      <c r="G32" t="s">
-        <v>41</v>
-      </c>
-      <c r="H32" t="s">
-        <v>88</v>
-      </c>
-      <c r="I32">
-        <v>1</v>
-      </c>
-      <c r="J32" t="s">
-        <v>167</v>
-      </c>
-      <c r="K32">
-        <v>10</v>
-      </c>
-      <c r="L32" t="s">
-        <v>41</v>
-      </c>
-      <c r="M32">
-        <v>1</v>
-      </c>
-      <c r="N32" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="33" spans="2:14">
-      <c r="B33" t="s">
-        <v>168</v>
-      </c>
-      <c r="C33" t="s">
-        <v>169</v>
-      </c>
-      <c r="D33" t="s">
-        <v>170</v>
-      </c>
-      <c r="E33" t="s">
-        <v>87</v>
-      </c>
-      <c r="F33" t="s">
-        <v>73</v>
-      </c>
-      <c r="G33" t="s">
-        <v>41</v>
-      </c>
-      <c r="H33" t="s">
-        <v>88</v>
-      </c>
-      <c r="I33">
-        <v>1</v>
-      </c>
-      <c r="J33" t="s">
-        <v>171</v>
-      </c>
-      <c r="K33">
-        <v>0.2</v>
-      </c>
-      <c r="L33" t="s">
-        <v>41</v>
-      </c>
-      <c r="M33">
-        <v>1</v>
-      </c>
-      <c r="N33" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="34" spans="2:14">
-      <c r="B34" t="s">
-        <v>172</v>
-      </c>
-      <c r="C34" t="s">
-        <v>173</v>
-      </c>
-      <c r="D34" t="s">
-        <v>174</v>
-      </c>
-      <c r="E34" t="s">
-        <v>87</v>
-      </c>
-      <c r="F34" t="s">
-        <v>40</v>
-      </c>
-      <c r="G34" t="s">
-        <v>41</v>
-      </c>
-      <c r="H34" t="s">
-        <v>88</v>
-      </c>
-      <c r="I34">
-        <v>1</v>
-      </c>
-      <c r="J34" t="s">
-        <v>175</v>
-      </c>
-      <c r="K34">
-        <v>0</v>
-      </c>
-      <c r="L34" t="s">
-        <v>176</v>
-      </c>
-      <c r="M34">
-        <v>1</v>
-      </c>
-      <c r="N34" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="35" spans="2:14">
-      <c r="B35" t="s">
-        <v>177</v>
-      </c>
-      <c r="C35" t="s">
-        <v>178</v>
-      </c>
-      <c r="D35" t="s">
-        <v>179</v>
-      </c>
-      <c r="E35" t="s">
-        <v>87</v>
-      </c>
-      <c r="F35" t="s">
-        <v>40</v>
-      </c>
-      <c r="G35" t="s">
-        <v>41</v>
-      </c>
-      <c r="H35" t="s">
-        <v>88</v>
-      </c>
-      <c r="I35">
-        <v>1</v>
-      </c>
-      <c r="J35" t="s">
-        <v>180</v>
-      </c>
-      <c r="K35">
-        <v>0</v>
-      </c>
-      <c r="L35" t="s">
-        <v>181</v>
-      </c>
-      <c r="M35">
-        <v>1</v>
-      </c>
-      <c r="N35" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="36" spans="2:14">
-      <c r="B36" t="s">
-        <v>182</v>
-      </c>
-      <c r="C36" t="s">
-        <v>183</v>
-      </c>
-      <c r="D36" t="s">
-        <v>184</v>
-      </c>
-      <c r="E36" t="s">
-        <v>87</v>
-      </c>
-      <c r="F36" t="s">
-        <v>40</v>
-      </c>
-      <c r="G36" t="s">
-        <v>41</v>
-      </c>
-      <c r="H36" t="s">
-        <v>88</v>
-      </c>
-      <c r="I36">
-        <v>1</v>
-      </c>
-      <c r="J36" t="s">
-        <v>185</v>
-      </c>
-      <c r="K36">
-        <v>0</v>
-      </c>
-      <c r="L36" t="s">
-        <v>41</v>
-      </c>
-      <c r="M36">
-        <v>1</v>
-      </c>
-      <c r="N36" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="37" spans="2:14">
-      <c r="B37" t="s">
-        <v>186</v>
-      </c>
-      <c r="C37" t="s">
-        <v>187</v>
-      </c>
-      <c r="D37" t="s">
-        <v>188</v>
-      </c>
-      <c r="E37" t="s">
-        <v>87</v>
-      </c>
-      <c r="F37" t="s">
-        <v>60</v>
-      </c>
-      <c r="G37" t="s">
-        <v>41</v>
-      </c>
-      <c r="H37" t="s">
-        <v>88</v>
-      </c>
-      <c r="I37">
-        <v>1</v>
-      </c>
-      <c r="J37" t="s">
-        <v>189</v>
-      </c>
-      <c r="K37">
-        <v>1</v>
-      </c>
-      <c r="L37" t="s">
-        <v>41</v>
-      </c>
-      <c r="M37">
-        <v>1</v>
-      </c>
-      <c r="N37" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="38" spans="2:14">
-      <c r="B38" t="s">
-        <v>190</v>
-      </c>
-      <c r="C38" t="s">
-        <v>191</v>
-      </c>
-      <c r="D38" t="s">
-        <v>192</v>
-      </c>
-      <c r="E38" t="s">
-        <v>87</v>
-      </c>
-      <c r="F38" t="s">
-        <v>73</v>
-      </c>
-      <c r="G38" t="s">
-        <v>41</v>
-      </c>
-      <c r="H38" t="s">
-        <v>88</v>
-      </c>
-      <c r="I38">
-        <v>1</v>
-      </c>
-      <c r="J38" t="s">
-        <v>193</v>
-      </c>
-      <c r="K38">
-        <v>0.2</v>
-      </c>
-      <c r="L38" t="s">
-        <v>41</v>
-      </c>
-      <c r="M38">
-        <v>1</v>
-      </c>
-      <c r="N38" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="39" spans="2:14">
-      <c r="B39" t="s">
-        <v>194</v>
-      </c>
-      <c r="C39" t="s">
-        <v>195</v>
-      </c>
-      <c r="D39" t="s">
-        <v>196</v>
-      </c>
-      <c r="E39" t="s">
-        <v>39</v>
-      </c>
-      <c r="F39" t="s">
-        <v>73</v>
-      </c>
-      <c r="G39" t="s">
-        <v>41</v>
-      </c>
-      <c r="H39" t="s">
-        <v>197</v>
-      </c>
-      <c r="I39">
-        <v>9</v>
-      </c>
-      <c r="J39" t="s">
-        <v>198</v>
-      </c>
-      <c r="K39">
-        <v>5</v>
-      </c>
-      <c r="L39" t="s">
-        <v>41</v>
-      </c>
-      <c r="M39">
-        <v>1</v>
-      </c>
-      <c r="N39" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="40" spans="2:14">
-      <c r="B40" t="s">
-        <v>199</v>
-      </c>
-      <c r="C40" t="s">
-        <v>200</v>
-      </c>
-      <c r="D40" t="s">
-        <v>201</v>
-      </c>
-      <c r="E40" t="s">
-        <v>87</v>
-      </c>
-      <c r="F40" t="s">
-        <v>40</v>
-      </c>
-      <c r="G40" t="s">
-        <v>41</v>
-      </c>
-      <c r="H40" t="s">
-        <v>88</v>
-      </c>
-      <c r="I40">
-        <v>1</v>
-      </c>
-      <c r="J40" t="s">
-        <v>202</v>
-      </c>
-      <c r="K40">
-        <v>1</v>
-      </c>
-      <c r="L40" t="s">
-        <v>41</v>
-      </c>
-      <c r="M40">
-        <v>1</v>
-      </c>
-      <c r="N40" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="41" spans="2:14">
-      <c r="B41" t="s">
-        <v>203</v>
-      </c>
-      <c r="C41" t="s">
-        <v>204</v>
-      </c>
-      <c r="D41" t="s">
-        <v>205</v>
-      </c>
-      <c r="E41" t="s">
-        <v>87</v>
-      </c>
-      <c r="F41" t="s">
-        <v>40</v>
-      </c>
-      <c r="G41" t="s">
-        <v>41</v>
-      </c>
-      <c r="H41" t="s">
-        <v>88</v>
-      </c>
-      <c r="I41">
-        <v>1</v>
-      </c>
-      <c r="J41" t="s">
-        <v>206</v>
-      </c>
-      <c r="K41">
-        <v>10</v>
-      </c>
-      <c r="L41" t="s">
-        <v>41</v>
-      </c>
-      <c r="M41">
-        <v>1</v>
-      </c>
-      <c r="N41" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="42" spans="2:14">
-      <c r="B42" t="s">
-        <v>207</v>
-      </c>
-      <c r="C42" t="s">
-        <v>208</v>
-      </c>
-      <c r="D42" t="s">
-        <v>209</v>
-      </c>
-      <c r="E42" t="s">
-        <v>87</v>
-      </c>
-      <c r="F42" t="s">
-        <v>73</v>
-      </c>
-      <c r="G42" t="s">
-        <v>41</v>
-      </c>
-      <c r="H42" t="s">
-        <v>88</v>
-      </c>
-      <c r="I42">
-        <v>1</v>
-      </c>
-      <c r="J42" t="s">
-        <v>210</v>
-      </c>
-      <c r="K42">
-        <v>1</v>
-      </c>
-      <c r="L42" t="s">
-        <v>41</v>
-      </c>
-      <c r="M42">
-        <v>1</v>
-      </c>
-      <c r="N42" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="43" spans="2:14">
-      <c r="B43" t="s">
-        <v>211</v>
-      </c>
-      <c r="C43" t="s">
-        <v>212</v>
-      </c>
-      <c r="D43" t="s">
-        <v>213</v>
-      </c>
-      <c r="E43" t="s">
-        <v>87</v>
-      </c>
-      <c r="F43" t="s">
-        <v>40</v>
-      </c>
-      <c r="G43" t="s">
-        <v>41</v>
-      </c>
-      <c r="H43" t="s">
-        <v>88</v>
-      </c>
-      <c r="I43">
-        <v>1</v>
-      </c>
-      <c r="J43" t="s">
-        <v>214</v>
-      </c>
-      <c r="K43">
-        <v>10</v>
-      </c>
-      <c r="L43" t="s">
-        <v>41</v>
-      </c>
-      <c r="M43">
-        <v>1</v>
-      </c>
-      <c r="N43" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="44" spans="2:14">
-      <c r="B44" t="s">
-        <v>215</v>
-      </c>
-      <c r="C44" t="s">
-        <v>216</v>
-      </c>
-      <c r="D44" t="s">
-        <v>217</v>
-      </c>
-      <c r="E44" t="s">
-        <v>87</v>
-      </c>
-      <c r="F44" t="s">
-        <v>73</v>
-      </c>
-      <c r="G44" t="s">
-        <v>41</v>
-      </c>
-      <c r="H44" t="s">
-        <v>88</v>
-      </c>
-      <c r="I44">
-        <v>1</v>
-      </c>
-      <c r="J44" t="s">
-        <v>218</v>
-      </c>
-      <c r="K44">
-        <v>10</v>
-      </c>
-      <c r="L44" t="s">
-        <v>41</v>
-      </c>
-      <c r="M44">
-        <v>1</v>
-      </c>
-      <c r="N44" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="45" spans="2:14">
-      <c r="B45" t="s">
-        <v>219</v>
-      </c>
-      <c r="C45" t="s">
-        <v>220</v>
-      </c>
-      <c r="D45" t="s">
-        <v>221</v>
-      </c>
-      <c r="E45" t="s">
-        <v>39</v>
-      </c>
-      <c r="F45" t="s">
-        <v>73</v>
-      </c>
-      <c r="G45" t="s">
-        <v>41</v>
-      </c>
-      <c r="H45" t="s">
-        <v>42</v>
-      </c>
-      <c r="I45">
-        <v>9</v>
-      </c>
-      <c r="J45" t="s">
-        <v>222</v>
-      </c>
-      <c r="K45">
-        <v>300</v>
-      </c>
-      <c r="L45" t="s">
-        <v>223</v>
-      </c>
-      <c r="M45">
-        <v>1</v>
-      </c>
-      <c r="N45" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="46" spans="2:14">
-      <c r="B46" t="s">
-        <v>224</v>
-      </c>
-      <c r="C46" t="s">
-        <v>225</v>
-      </c>
-      <c r="D46" t="s">
-        <v>226</v>
-      </c>
-      <c r="E46" t="s">
-        <v>39</v>
-      </c>
-      <c r="F46" t="s">
-        <v>40</v>
-      </c>
-      <c r="G46" t="s">
-        <v>41</v>
-      </c>
-      <c r="H46" t="s">
-        <v>42</v>
-      </c>
-      <c r="I46">
-        <v>9</v>
-      </c>
-      <c r="J46" t="s">
-        <v>227</v>
-      </c>
-      <c r="K46">
-        <v>0</v>
-      </c>
-      <c r="L46" t="s">
-        <v>41</v>
-      </c>
-      <c r="M46">
-        <v>1</v>
-      </c>
-      <c r="N46" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="47" spans="2:14">
-      <c r="B47" t="s">
-        <v>228</v>
-      </c>
-      <c r="C47" t="s">
-        <v>229</v>
-      </c>
-      <c r="D47" t="s">
-        <v>230</v>
-      </c>
-      <c r="E47" t="s">
-        <v>39</v>
-      </c>
-      <c r="F47" t="s">
-        <v>73</v>
-      </c>
-      <c r="G47" t="s">
-        <v>41</v>
-      </c>
-      <c r="H47" t="s">
-        <v>42</v>
-      </c>
-      <c r="I47">
-        <v>9</v>
-      </c>
-      <c r="J47" t="s">
-        <v>231</v>
-      </c>
-      <c r="K47">
-        <v>1</v>
-      </c>
-      <c r="L47" t="s">
-        <v>41</v>
-      </c>
-      <c r="M47">
-        <v>1</v>
-      </c>
-      <c r="N47" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="48" spans="2:14">
-      <c r="B48" t="s">
-        <v>232</v>
-      </c>
-      <c r="C48" t="s">
-        <v>233</v>
-      </c>
-      <c r="D48" t="s">
-        <v>234</v>
-      </c>
-      <c r="E48" t="s">
-        <v>39</v>
-      </c>
-      <c r="F48" t="s">
-        <v>235</v>
-      </c>
-      <c r="G48" t="s">
-        <v>41</v>
-      </c>
-      <c r="H48" t="s">
-        <v>42</v>
-      </c>
-      <c r="I48">
-        <v>9</v>
-      </c>
-      <c r="J48" t="s">
-        <v>236</v>
-      </c>
-      <c r="K48">
-        <v>1</v>
-      </c>
-      <c r="L48" t="s">
-        <v>41</v>
-      </c>
-      <c r="M48">
-        <v>1</v>
-      </c>
-      <c r="N48" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="49" spans="2:14">
-      <c r="B49" t="s">
-        <v>237</v>
-      </c>
-      <c r="C49" t="s">
-        <v>238</v>
-      </c>
-      <c r="D49" t="s">
-        <v>239</v>
-      </c>
-      <c r="E49" t="s">
-        <v>39</v>
-      </c>
-      <c r="F49" t="s">
-        <v>40</v>
-      </c>
-      <c r="G49" t="s">
-        <v>41</v>
-      </c>
-      <c r="H49" t="s">
-        <v>42</v>
-      </c>
-      <c r="I49">
-        <v>9</v>
-      </c>
-      <c r="J49" t="s">
-        <v>240</v>
-      </c>
-      <c r="K49">
-        <v>1</v>
-      </c>
-      <c r="L49" t="s">
-        <v>41</v>
-      </c>
-      <c r="M49">
-        <v>1</v>
-      </c>
-      <c r="N49" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="50" spans="2:14">
-      <c r="B50" t="s">
-        <v>241</v>
-      </c>
-      <c r="C50" t="s">
-        <v>242</v>
-      </c>
-      <c r="D50" t="s">
-        <v>243</v>
-      </c>
-      <c r="E50" t="s">
-        <v>39</v>
-      </c>
-      <c r="F50" t="s">
-        <v>40</v>
-      </c>
-      <c r="G50" t="s">
-        <v>41</v>
-      </c>
-      <c r="H50" t="s">
-        <v>42</v>
-      </c>
-      <c r="I50">
-        <v>9</v>
-      </c>
-      <c r="J50" t="s">
-        <v>244</v>
-      </c>
-      <c r="K50">
-        <v>1</v>
-      </c>
-      <c r="L50" t="s">
-        <v>41</v>
-      </c>
-      <c r="M50">
-        <v>1</v>
-      </c>
-      <c r="N50" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="51" spans="2:14">
-      <c r="B51" t="s">
-        <v>245</v>
-      </c>
-      <c r="C51" t="s">
-        <v>246</v>
-      </c>
-      <c r="D51" t="s">
-        <v>247</v>
-      </c>
-      <c r="E51" t="s">
-        <v>87</v>
-      </c>
-      <c r="F51" t="s">
-        <v>73</v>
-      </c>
-      <c r="G51" t="s">
-        <v>41</v>
-      </c>
-      <c r="H51" t="s">
-        <v>88</v>
-      </c>
-      <c r="I51">
-        <v>1</v>
-      </c>
-      <c r="J51" t="s">
-        <v>248</v>
-      </c>
-      <c r="K51">
-        <v>2</v>
-      </c>
-      <c r="L51" t="s">
-        <v>249</v>
-      </c>
-      <c r="M51">
-        <v>1</v>
-      </c>
-      <c r="N51" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="52" spans="2:14">
-      <c r="B52" t="s">
-        <v>250</v>
-      </c>
-      <c r="C52" t="s">
-        <v>251</v>
-      </c>
-      <c r="D52" t="s">
-        <v>252</v>
-      </c>
-      <c r="E52" t="s">
-        <v>87</v>
-      </c>
-      <c r="F52" t="s">
-        <v>40</v>
-      </c>
-      <c r="G52" t="s">
-        <v>41</v>
-      </c>
-      <c r="H52" t="s">
-        <v>88</v>
-      </c>
-      <c r="I52">
-        <v>1</v>
-      </c>
-      <c r="J52" t="s">
-        <v>253</v>
-      </c>
-      <c r="K52">
-        <v>2</v>
-      </c>
-      <c r="L52" t="s">
-        <v>254</v>
-      </c>
-      <c r="M52">
-        <v>1</v>
-      </c>
-      <c r="N52" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="53" spans="2:14">
-      <c r="B53" t="s">
-        <v>255</v>
-      </c>
-      <c r="C53" t="s">
-        <v>256</v>
-      </c>
-      <c r="D53" t="s">
-        <v>257</v>
-      </c>
-      <c r="E53" t="s">
-        <v>87</v>
-      </c>
-      <c r="F53" t="s">
-        <v>40</v>
-      </c>
-      <c r="G53" t="s">
-        <v>41</v>
-      </c>
-      <c r="H53" t="s">
-        <v>88</v>
-      </c>
-      <c r="I53">
-        <v>1</v>
-      </c>
-      <c r="J53" t="s">
-        <v>253</v>
-      </c>
-      <c r="K53">
-        <v>2</v>
-      </c>
-      <c r="L53" t="s">
-        <v>258</v>
-      </c>
-      <c r="M53">
-        <v>1</v>
-      </c>
-      <c r="N53" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="54" spans="2:14">
-      <c r="B54" t="s">
-        <v>259</v>
-      </c>
-      <c r="C54" t="s">
-        <v>260</v>
-      </c>
-      <c r="D54" t="s">
-        <v>261</v>
-      </c>
-      <c r="E54" t="s">
-        <v>87</v>
-      </c>
-      <c r="F54" t="s">
-        <v>73</v>
-      </c>
-      <c r="G54" t="s">
-        <v>41</v>
-      </c>
-      <c r="H54" t="s">
-        <v>88</v>
-      </c>
-      <c r="I54">
-        <v>1</v>
-      </c>
-      <c r="J54" t="s">
-        <v>262</v>
-      </c>
-      <c r="K54">
-        <v>2</v>
-      </c>
-      <c r="L54" t="s">
-        <v>41</v>
-      </c>
-      <c r="M54">
-        <v>1</v>
-      </c>
-      <c r="N54" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="55" spans="2:14">
-      <c r="B55" t="s">
-        <v>263</v>
-      </c>
-      <c r="C55" t="s">
-        <v>264</v>
-      </c>
-      <c r="D55" t="s">
-        <v>265</v>
-      </c>
-      <c r="E55" t="s">
-        <v>87</v>
-      </c>
-      <c r="F55" t="s">
-        <v>40</v>
-      </c>
-      <c r="G55" t="s">
-        <v>41</v>
-      </c>
-      <c r="H55" t="s">
-        <v>88</v>
-      </c>
-      <c r="I55">
-        <v>1</v>
-      </c>
-      <c r="J55" t="s">
-        <v>266</v>
-      </c>
-      <c r="K55">
-        <v>20</v>
-      </c>
-      <c r="L55" t="s">
-        <v>41</v>
-      </c>
-      <c r="M55">
-        <v>1</v>
-      </c>
-      <c r="N55" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="56" spans="2:14">
-      <c r="B56" t="s">
-        <v>267</v>
-      </c>
-      <c r="C56" t="s">
-        <v>268</v>
-      </c>
-      <c r="D56" t="s">
-        <v>269</v>
-      </c>
-      <c r="E56" t="s">
-        <v>87</v>
-      </c>
-      <c r="F56" t="s">
-        <v>235</v>
-      </c>
-      <c r="G56" t="s">
-        <v>41</v>
-      </c>
-      <c r="H56" t="s">
-        <v>88</v>
-      </c>
-      <c r="I56">
-        <v>1</v>
-      </c>
-      <c r="J56" t="s">
-        <v>270</v>
-      </c>
-      <c r="K56">
-        <v>1000</v>
-      </c>
-      <c r="L56" t="s">
-        <v>41</v>
-      </c>
-      <c r="M56">
-        <v>1</v>
-      </c>
-      <c r="N56" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="57" spans="2:14">
-      <c r="B57" t="s">
-        <v>272</v>
-      </c>
-      <c r="C57" t="s">
-        <v>273</v>
-      </c>
-      <c r="D57" t="s">
-        <v>274</v>
-      </c>
-      <c r="E57" t="s">
-        <v>39</v>
-      </c>
-      <c r="F57" t="s">
-        <v>40</v>
-      </c>
-      <c r="G57" t="s">
-        <v>41</v>
-      </c>
-      <c r="H57" t="s">
-        <v>197</v>
-      </c>
-      <c r="I57">
-        <v>9</v>
-      </c>
-      <c r="J57" t="s">
-        <v>275</v>
-      </c>
-      <c r="K57">
-        <v>2</v>
-      </c>
-      <c r="L57" t="s">
-        <v>41</v>
-      </c>
-      <c r="M57">
-        <v>1</v>
-      </c>
-      <c r="N57" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="58" spans="2:14">
-      <c r="B58" t="s">
-        <v>276</v>
-      </c>
-      <c r="C58" t="s">
-        <v>277</v>
-      </c>
-      <c r="D58" t="s">
-        <v>278</v>
-      </c>
-      <c r="E58" t="s">
-        <v>39</v>
-      </c>
-      <c r="F58" t="s">
-        <v>40</v>
-      </c>
-      <c r="G58" t="s">
-        <v>41</v>
-      </c>
-      <c r="H58" t="s">
-        <v>197</v>
-      </c>
-      <c r="I58">
-        <v>9</v>
-      </c>
-      <c r="J58" t="s">
-        <v>279</v>
-      </c>
-      <c r="K58">
-        <v>200</v>
-      </c>
-      <c r="L58" t="s">
-        <v>41</v>
-      </c>
-      <c r="M58">
-        <v>1</v>
-      </c>
-      <c r="N58" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="59" spans="2:14">
-      <c r="B59" t="s">
-        <v>280</v>
-      </c>
-      <c r="C59" t="s">
-        <v>281</v>
-      </c>
-      <c r="D59" t="s">
-        <v>282</v>
-      </c>
-      <c r="E59" t="s">
-        <v>39</v>
-      </c>
-      <c r="F59" t="s">
-        <v>73</v>
-      </c>
-      <c r="G59" t="s">
-        <v>41</v>
-      </c>
-      <c r="H59" t="s">
-        <v>197</v>
-      </c>
-      <c r="I59">
-        <v>9</v>
-      </c>
-      <c r="J59" t="s">
-        <v>283</v>
-      </c>
-      <c r="K59">
-        <v>0</v>
-      </c>
-      <c r="L59" t="s">
-        <v>41</v>
-      </c>
-      <c r="M59">
-        <v>1</v>
-      </c>
-      <c r="N59" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="60" spans="2:14">
-      <c r="B60" t="s">
-        <v>284</v>
-      </c>
-      <c r="C60" t="s">
-        <v>285</v>
-      </c>
-      <c r="D60" t="s">
-        <v>286</v>
-      </c>
-      <c r="E60" t="s">
-        <v>39</v>
-      </c>
-      <c r="F60" t="s">
-        <v>73</v>
-      </c>
-      <c r="G60" t="s">
-        <v>41</v>
-      </c>
-      <c r="H60" t="s">
-        <v>197</v>
-      </c>
-      <c r="I60">
-        <v>9</v>
-      </c>
-      <c r="J60" t="s">
-        <v>287</v>
-      </c>
-      <c r="K60">
-        <v>2</v>
-      </c>
-      <c r="L60" t="s">
-        <v>41</v>
-      </c>
-      <c r="M60">
-        <v>1</v>
-      </c>
-      <c r="N60" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="61" spans="2:14">
-      <c r="B61" t="s">
-        <v>288</v>
-      </c>
-      <c r="C61" t="s">
-        <v>289</v>
-      </c>
-      <c r="D61" t="s">
-        <v>290</v>
-      </c>
-      <c r="E61" t="s">
-        <v>87</v>
-      </c>
-      <c r="F61" t="s">
-        <v>235</v>
-      </c>
-      <c r="G61" t="s">
-        <v>41</v>
-      </c>
-      <c r="H61" t="s">
-        <v>88</v>
-      </c>
-      <c r="I61">
-        <v>1</v>
-      </c>
-      <c r="J61" t="s">
-        <v>291</v>
-      </c>
-      <c r="K61">
-        <v>1</v>
-      </c>
-      <c r="L61" t="s">
-        <v>41</v>
-      </c>
-      <c r="M61">
-        <v>1</v>
-      </c>
-      <c r="N61" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="62" spans="2:14">
-      <c r="B62" t="s">
-        <v>292</v>
-      </c>
-      <c r="C62" t="s">
-        <v>293</v>
-      </c>
-      <c r="D62" t="s">
-        <v>294</v>
-      </c>
-      <c r="E62" t="s">
-        <v>39</v>
-      </c>
-      <c r="F62" t="s">
-        <v>73</v>
-      </c>
-      <c r="G62" t="s">
-        <v>41</v>
-      </c>
-      <c r="H62" t="s">
-        <v>197</v>
-      </c>
-      <c r="I62">
-        <v>9</v>
-      </c>
-      <c r="J62" t="s">
-        <v>295</v>
-      </c>
-      <c r="K62">
-        <v>1</v>
-      </c>
-      <c r="L62" t="s">
-        <v>41</v>
-      </c>
-      <c r="M62">
-        <v>1</v>
-      </c>
-      <c r="N62" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="63" spans="2:14">
-      <c r="B63" t="s">
-        <v>296</v>
-      </c>
-      <c r="C63" t="s">
-        <v>297</v>
-      </c>
-      <c r="D63" t="s">
-        <v>298</v>
-      </c>
-      <c r="E63" t="s">
-        <v>39</v>
-      </c>
-      <c r="F63" t="s">
-        <v>40</v>
-      </c>
-      <c r="G63" t="s">
-        <v>41</v>
-      </c>
-      <c r="H63" t="s">
-        <v>197</v>
-      </c>
-      <c r="I63">
-        <v>9</v>
-      </c>
-      <c r="J63" t="s">
-        <v>299</v>
-      </c>
-      <c r="K63">
-        <v>2</v>
-      </c>
-      <c r="L63" t="s">
-        <v>41</v>
-      </c>
-      <c r="M63">
-        <v>1</v>
-      </c>
-      <c r="N63" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="64" spans="2:14">
-      <c r="B64" t="s">
-        <v>300</v>
-      </c>
-      <c r="C64" t="s">
-        <v>301</v>
-      </c>
-      <c r="D64" t="s">
-        <v>302</v>
-      </c>
-      <c r="E64" t="s">
-        <v>39</v>
-      </c>
-      <c r="F64" t="s">
-        <v>73</v>
-      </c>
-      <c r="G64" t="s">
-        <v>41</v>
-      </c>
-      <c r="H64" t="s">
-        <v>197</v>
-      </c>
-      <c r="I64">
-        <v>9</v>
-      </c>
-      <c r="J64" t="s">
-        <v>303</v>
-      </c>
-      <c r="K64">
-        <v>1</v>
-      </c>
-      <c r="L64" t="s">
-        <v>41</v>
-      </c>
-      <c r="M64">
-        <v>1</v>
-      </c>
-      <c r="N64" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="65" spans="2:14">
-      <c r="B65" t="s">
-        <v>304</v>
-      </c>
-      <c r="C65" t="s">
-        <v>305</v>
-      </c>
-      <c r="D65" t="s">
-        <v>306</v>
-      </c>
-      <c r="E65" t="s">
-        <v>87</v>
-      </c>
-      <c r="F65" t="s">
-        <v>73</v>
-      </c>
-      <c r="G65" t="s">
-        <v>41</v>
-      </c>
-      <c r="H65" t="s">
-        <v>88</v>
-      </c>
-      <c r="I65">
-        <v>1</v>
-      </c>
-      <c r="J65" t="s">
-        <v>307</v>
-      </c>
-      <c r="K65">
-        <v>4</v>
-      </c>
-      <c r="L65" t="s">
-        <v>41</v>
-      </c>
-      <c r="M65">
-        <v>1</v>
-      </c>
-      <c r="N65" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="66" spans="2:14">
-      <c r="B66" t="s">
-        <v>308</v>
-      </c>
-      <c r="C66" t="s">
-        <v>309</v>
-      </c>
-      <c r="D66" t="s">
-        <v>310</v>
-      </c>
-      <c r="E66" t="s">
-        <v>87</v>
-      </c>
-      <c r="F66" t="s">
-        <v>40</v>
-      </c>
-      <c r="G66" t="s">
-        <v>41</v>
-      </c>
-      <c r="H66" t="s">
-        <v>88</v>
-      </c>
-      <c r="I66">
-        <v>1</v>
-      </c>
-      <c r="J66" t="s">
-        <v>311</v>
-      </c>
-      <c r="K66">
-        <v>0.2</v>
-      </c>
-      <c r="L66" t="s">
-        <v>41</v>
-      </c>
-      <c r="M66">
-        <v>1</v>
-      </c>
-      <c r="N66" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="67" spans="2:14">
-      <c r="B67" t="s">
-        <v>312</v>
-      </c>
-      <c r="C67" t="s">
-        <v>313</v>
-      </c>
-      <c r="D67" t="s">
-        <v>314</v>
-      </c>
-      <c r="E67" t="s">
-        <v>87</v>
-      </c>
-      <c r="F67" t="s">
-        <v>40</v>
-      </c>
-      <c r="G67" t="s">
-        <v>41</v>
-      </c>
-      <c r="H67" t="s">
-        <v>88</v>
-      </c>
-      <c r="I67">
-        <v>1</v>
-      </c>
-      <c r="J67" t="s">
-        <v>315</v>
-      </c>
-      <c r="K67">
-        <v>0.2</v>
-      </c>
-      <c r="L67" t="s">
-        <v>41</v>
-      </c>
-      <c r="M67">
-        <v>1</v>
-      </c>
-      <c r="N67" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="68" spans="2:14">
-      <c r="B68" t="s">
-        <v>316</v>
-      </c>
-      <c r="C68" t="s">
-        <v>317</v>
-      </c>
-      <c r="D68" t="s">
-        <v>318</v>
-      </c>
-      <c r="E68" t="s">
-        <v>87</v>
-      </c>
-      <c r="F68" t="s">
-        <v>60</v>
-      </c>
-      <c r="G68" t="s">
-        <v>41</v>
-      </c>
-      <c r="H68" t="s">
-        <v>88</v>
-      </c>
-      <c r="I68">
-        <v>1</v>
-      </c>
-      <c r="J68" t="s">
-        <v>319</v>
-      </c>
-      <c r="K68">
-        <v>10</v>
-      </c>
-      <c r="L68" t="s">
-        <v>41</v>
-      </c>
-      <c r="M68">
-        <v>1</v>
-      </c>
-      <c r="N68" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="69" spans="2:14">
-      <c r="B69" t="s">
-        <v>320</v>
-      </c>
-      <c r="C69" t="s">
-        <v>321</v>
-      </c>
-      <c r="D69" t="s">
-        <v>322</v>
-      </c>
-      <c r="E69" t="s">
-        <v>39</v>
-      </c>
-      <c r="F69" t="s">
-        <v>60</v>
-      </c>
-      <c r="G69" t="s">
-        <v>41</v>
-      </c>
-      <c r="H69" t="s">
-        <v>42</v>
-      </c>
-      <c r="I69">
-        <v>9</v>
-      </c>
-      <c r="J69" t="s">
-        <v>323</v>
-      </c>
-      <c r="K69">
-        <v>2</v>
-      </c>
-      <c r="L69" t="s">
-        <v>41</v>
-      </c>
-      <c r="M69">
-        <v>1</v>
-      </c>
-      <c r="N69" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="70" spans="2:14">
-      <c r="B70" t="s">
-        <v>324</v>
-      </c>
-      <c r="C70" t="s">
-        <v>325</v>
-      </c>
-      <c r="D70" t="s">
-        <v>326</v>
-      </c>
-      <c r="E70" t="s">
-        <v>87</v>
-      </c>
-      <c r="F70" t="s">
-        <v>73</v>
-      </c>
-      <c r="G70" t="s">
-        <v>41</v>
-      </c>
-      <c r="H70" t="s">
-        <v>88</v>
-      </c>
-      <c r="I70">
-        <v>1</v>
-      </c>
-      <c r="J70" t="s">
-        <v>327</v>
-      </c>
-      <c r="K70">
-        <v>0</v>
-      </c>
-      <c r="L70" t="s">
-        <v>41</v>
-      </c>
-      <c r="M70">
-        <v>1</v>
-      </c>
-      <c r="N70" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="71" spans="2:14">
-      <c r="B71" t="s">
-        <v>328</v>
-      </c>
-      <c r="C71" t="s">
-        <v>329</v>
-      </c>
-      <c r="D71" t="s">
-        <v>330</v>
-      </c>
-      <c r="E71" t="s">
-        <v>87</v>
-      </c>
-      <c r="F71" t="s">
-        <v>40</v>
-      </c>
-      <c r="G71" t="s">
-        <v>41</v>
-      </c>
-      <c r="H71" t="s">
-        <v>88</v>
-      </c>
-      <c r="I71">
-        <v>1</v>
-      </c>
-      <c r="J71" t="s">
-        <v>331</v>
-      </c>
-      <c r="K71">
-        <v>1</v>
-      </c>
-      <c r="L71" t="s">
-        <v>41</v>
-      </c>
-      <c r="M71">
-        <v>1</v>
-      </c>
-      <c r="N71" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="72" spans="2:14">
-      <c r="B72" t="s">
-        <v>332</v>
-      </c>
-      <c r="C72" t="s">
-        <v>333</v>
-      </c>
-      <c r="D72" t="s">
-        <v>334</v>
-      </c>
-      <c r="E72" t="s">
-        <v>87</v>
-      </c>
-      <c r="F72" t="s">
-        <v>73</v>
-      </c>
-      <c r="G72" t="s">
-        <v>41</v>
-      </c>
-      <c r="H72" t="s">
-        <v>88</v>
-      </c>
-      <c r="I72">
-        <v>1</v>
-      </c>
-      <c r="J72" t="s">
-        <v>335</v>
-      </c>
-      <c r="K72">
-        <v>1</v>
-      </c>
-      <c r="L72" t="s">
-        <v>41</v>
-      </c>
-      <c r="M72">
-        <v>1</v>
-      </c>
-      <c r="N72" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="73" spans="2:14">
-      <c r="B73" t="s">
-        <v>336</v>
-      </c>
-      <c r="C73" t="s">
-        <v>337</v>
-      </c>
-      <c r="D73" t="s">
-        <v>338</v>
-      </c>
-      <c r="E73" t="s">
-        <v>87</v>
-      </c>
-      <c r="F73" t="s">
-        <v>73</v>
-      </c>
-      <c r="G73" t="s">
-        <v>41</v>
-      </c>
-      <c r="H73" t="s">
-        <v>88</v>
-      </c>
-      <c r="I73">
-        <v>1</v>
-      </c>
-      <c r="J73" t="s">
-        <v>339</v>
-      </c>
-      <c r="K73">
-        <v>0</v>
-      </c>
-      <c r="L73" t="s">
-        <v>249</v>
-      </c>
-      <c r="M73">
-        <v>1</v>
-      </c>
-      <c r="N73" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="74" spans="2:14">
-      <c r="B74" t="s">
-        <v>340</v>
-      </c>
-      <c r="C74" t="s">
-        <v>341</v>
-      </c>
-      <c r="D74" t="s">
-        <v>342</v>
-      </c>
-      <c r="E74" t="s">
-        <v>87</v>
-      </c>
-      <c r="F74" t="s">
-        <v>73</v>
-      </c>
-      <c r="G74" t="s">
-        <v>41</v>
-      </c>
-      <c r="H74" t="s">
-        <v>88</v>
-      </c>
-      <c r="I74">
-        <v>1</v>
-      </c>
-      <c r="J74" t="s">
-        <v>343</v>
-      </c>
-      <c r="K74">
-        <v>0</v>
-      </c>
-      <c r="L74" t="s">
-        <v>249</v>
-      </c>
-      <c r="M74">
-        <v>1</v>
-      </c>
-      <c r="N74" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="75" spans="2:14">
-      <c r="B75" t="s">
-        <v>344</v>
-      </c>
-      <c r="C75" t="s">
-        <v>345</v>
-      </c>
-      <c r="D75" t="s">
-        <v>346</v>
-      </c>
-      <c r="E75" t="s">
-        <v>39</v>
-      </c>
-      <c r="F75" t="s">
-        <v>73</v>
-      </c>
-      <c r="G75" t="s">
-        <v>41</v>
-      </c>
-      <c r="H75" t="s">
-        <v>42</v>
-      </c>
-      <c r="I75">
-        <v>9</v>
-      </c>
-      <c r="J75" t="s">
-        <v>347</v>
-      </c>
-      <c r="K75">
-        <v>1</v>
-      </c>
-      <c r="L75" t="s">
-        <v>41</v>
-      </c>
-      <c r="M75">
-        <v>1</v>
-      </c>
-      <c r="N75" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="76" spans="2:14">
-      <c r="B76" t="s">
-        <v>348</v>
-      </c>
-      <c r="C76" t="s">
-        <v>349</v>
-      </c>
-      <c r="D76" t="s">
-        <v>350</v>
-      </c>
-      <c r="E76" t="s">
-        <v>39</v>
-      </c>
-      <c r="F76" t="s">
-        <v>60</v>
-      </c>
-      <c r="G76" t="s">
-        <v>41</v>
-      </c>
-      <c r="H76" t="s">
-        <v>42</v>
-      </c>
-      <c r="I76">
-        <v>9</v>
-      </c>
-      <c r="J76" t="s">
-        <v>351</v>
-      </c>
-      <c r="K76">
-        <v>2</v>
-      </c>
-      <c r="L76" t="s">
-        <v>41</v>
-      </c>
-      <c r="M76">
-        <v>1</v>
-      </c>
-      <c r="N76" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="77" spans="2:14">
-      <c r="B77" t="s">
-        <v>352</v>
-      </c>
-      <c r="C77" t="s">
-        <v>353</v>
-      </c>
-      <c r="D77" t="s">
-        <v>354</v>
-      </c>
-      <c r="E77" t="s">
-        <v>39</v>
-      </c>
-      <c r="F77" t="s">
-        <v>40</v>
-      </c>
-      <c r="G77" t="s">
-        <v>41</v>
-      </c>
-      <c r="H77" t="s">
-        <v>42</v>
-      </c>
-      <c r="I77">
-        <v>9</v>
-      </c>
-      <c r="J77" t="s">
-        <v>355</v>
-      </c>
-      <c r="K77">
-        <v>100</v>
-      </c>
-      <c r="L77" t="s">
-        <v>41</v>
-      </c>
-      <c r="M77">
-        <v>1</v>
-      </c>
-      <c r="N77" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="78" spans="2:14">
-      <c r="B78" t="s">
-        <v>356</v>
-      </c>
-      <c r="C78" t="s">
-        <v>357</v>
-      </c>
-      <c r="D78" t="s">
-        <v>358</v>
-      </c>
-      <c r="E78" t="s">
-        <v>87</v>
-      </c>
-      <c r="F78" t="s">
-        <v>60</v>
-      </c>
-      <c r="G78" t="s">
-        <v>359</v>
-      </c>
-      <c r="H78" t="s">
-        <v>88</v>
-      </c>
-      <c r="I78">
-        <v>1</v>
-      </c>
-      <c r="J78" t="s">
-        <v>99</v>
-      </c>
-      <c r="K78">
-        <v>-0.25</v>
-      </c>
-      <c r="L78" t="s">
-        <v>41</v>
-      </c>
-      <c r="M78">
-        <v>1</v>
-      </c>
-      <c r="N78" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="79" spans="2:14">
-      <c r="B79" t="s">
-        <v>360</v>
-      </c>
-      <c r="C79" t="s">
-        <v>361</v>
-      </c>
-      <c r="D79" t="s">
-        <v>362</v>
-      </c>
-      <c r="E79" t="s">
-        <v>87</v>
-      </c>
-      <c r="F79" t="s">
-        <v>60</v>
-      </c>
-      <c r="G79" t="s">
-        <v>359</v>
-      </c>
-      <c r="H79" t="s">
-        <v>88</v>
-      </c>
-      <c r="I79">
-        <v>1</v>
-      </c>
-      <c r="J79" t="s">
-        <v>363</v>
-      </c>
-      <c r="K79">
-        <v>0.25</v>
-      </c>
-      <c r="L79" t="s">
-        <v>41</v>
-      </c>
-      <c r="M79">
-        <v>1</v>
-      </c>
-      <c r="N79" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="80" spans="2:14">
-      <c r="B80" t="s">
-        <v>364</v>
-      </c>
-      <c r="C80" t="s">
-        <v>365</v>
-      </c>
-      <c r="D80" t="s">
-        <v>366</v>
-      </c>
-      <c r="E80" t="s">
-        <v>87</v>
-      </c>
-      <c r="F80" t="s">
-        <v>60</v>
-      </c>
-      <c r="G80" t="s">
-        <v>359</v>
-      </c>
-      <c r="H80" t="s">
-        <v>88</v>
-      </c>
-      <c r="I80">
-        <v>1</v>
-      </c>
-      <c r="J80" t="s">
-        <v>367</v>
-      </c>
-      <c r="K80">
-        <v>0</v>
-      </c>
-      <c r="L80" t="s">
-        <v>41</v>
-      </c>
-      <c r="M80">
-        <v>1</v>
-      </c>
-      <c r="N80" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="81" spans="2:14">
-      <c r="B81" t="s">
-        <v>368</v>
-      </c>
-      <c r="C81" t="s">
-        <v>369</v>
-      </c>
-      <c r="D81" t="s">
-        <v>370</v>
-      </c>
-      <c r="E81" t="s">
-        <v>87</v>
-      </c>
-      <c r="F81" t="s">
-        <v>60</v>
-      </c>
-      <c r="G81" t="s">
-        <v>359</v>
-      </c>
-      <c r="H81" t="s">
-        <v>88</v>
-      </c>
-      <c r="I81">
-        <v>1</v>
-      </c>
-      <c r="J81" t="s">
-        <v>371</v>
-      </c>
-      <c r="K81">
-        <v>1</v>
-      </c>
-      <c r="L81" t="s">
-        <v>41</v>
-      </c>
-      <c r="M81">
-        <v>1</v>
-      </c>
-      <c r="N81" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="82" spans="2:14">
-      <c r="B82" t="s">
-        <v>372</v>
-      </c>
-      <c r="C82" t="s">
-        <v>373</v>
-      </c>
-      <c r="D82" t="s">
-        <v>374</v>
-      </c>
-      <c r="E82" t="s">
-        <v>87</v>
-      </c>
-      <c r="F82" t="s">
-        <v>60</v>
-      </c>
-      <c r="G82" t="s">
-        <v>359</v>
-      </c>
-      <c r="H82" t="s">
-        <v>88</v>
-      </c>
-      <c r="I82">
-        <v>1</v>
-      </c>
-      <c r="J82" t="s">
-        <v>375</v>
-      </c>
-      <c r="K82">
-        <v>-1</v>
-      </c>
-      <c r="L82" t="s">
-        <v>41</v>
-      </c>
-      <c r="M82">
-        <v>1</v>
-      </c>
-      <c r="N82" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="83" spans="2:14">
-      <c r="B83" t="s">
-        <v>376</v>
-      </c>
-      <c r="C83" t="s">
-        <v>377</v>
-      </c>
-      <c r="D83" t="s">
-        <v>378</v>
-      </c>
-      <c r="E83" t="s">
-        <v>87</v>
-      </c>
-      <c r="F83" t="s">
-        <v>60</v>
-      </c>
-      <c r="G83" t="s">
-        <v>359</v>
-      </c>
-      <c r="H83" t="s">
-        <v>88</v>
-      </c>
-      <c r="I83">
-        <v>1</v>
-      </c>
-      <c r="J83" t="s">
-        <v>142</v>
-      </c>
-      <c r="K83">
-        <v>0.1</v>
-      </c>
-      <c r="L83" t="s">
-        <v>41</v>
-      </c>
-      <c r="M83">
-        <v>1</v>
-      </c>
-      <c r="N83" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="84" spans="2:14">
-      <c r="B84" t="s">
-        <v>379</v>
-      </c>
-      <c r="C84" t="s">
-        <v>380</v>
-      </c>
-      <c r="D84" t="s">
-        <v>381</v>
-      </c>
-      <c r="E84" t="s">
-        <v>87</v>
-      </c>
-      <c r="F84" t="s">
-        <v>60</v>
-      </c>
-      <c r="G84" t="s">
-        <v>359</v>
-      </c>
-      <c r="H84" t="s">
-        <v>88</v>
-      </c>
-      <c r="I84">
-        <v>1</v>
-      </c>
-      <c r="J84" t="s">
-        <v>146</v>
-      </c>
-      <c r="K84">
-        <v>0.1</v>
-      </c>
-      <c r="L84" t="s">
-        <v>41</v>
-      </c>
-      <c r="M84">
-        <v>1</v>
-      </c>
-      <c r="N84" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="85" spans="2:14">
-      <c r="B85" t="s">
-        <v>382</v>
-      </c>
-      <c r="C85" t="s">
-        <v>383</v>
-      </c>
-      <c r="D85" t="s">
-        <v>384</v>
-      </c>
-      <c r="E85" t="s">
-        <v>87</v>
-      </c>
-      <c r="F85" t="s">
-        <v>60</v>
-      </c>
-      <c r="G85" t="s">
-        <v>359</v>
-      </c>
-      <c r="H85" t="s">
-        <v>88</v>
-      </c>
-      <c r="I85">
-        <v>1</v>
-      </c>
-      <c r="J85" t="s">
-        <v>150</v>
-      </c>
-      <c r="K85">
-        <v>0.1</v>
-      </c>
-      <c r="L85" t="s">
-        <v>41</v>
-      </c>
-      <c r="M85">
-        <v>1</v>
-      </c>
-      <c r="N85" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="86" spans="2:14">
-      <c r="B86" t="s">
-        <v>385</v>
-      </c>
-      <c r="C86" t="s">
-        <v>386</v>
-      </c>
-      <c r="D86" t="s">
-        <v>387</v>
-      </c>
-      <c r="E86" t="s">
-        <v>87</v>
-      </c>
-      <c r="F86" t="s">
-        <v>60</v>
-      </c>
-      <c r="G86" t="s">
-        <v>359</v>
-      </c>
-      <c r="H86" t="s">
-        <v>88</v>
-      </c>
-      <c r="I86">
-        <v>1</v>
-      </c>
-      <c r="J86" t="s">
-        <v>388</v>
-      </c>
-      <c r="K86">
-        <v>0</v>
-      </c>
-      <c r="L86" t="s">
-        <v>41</v>
-      </c>
-      <c r="M86">
-        <v>1</v>
-      </c>
-      <c r="N86" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="87" spans="2:14">
-      <c r="B87" t="s">
-        <v>389</v>
-      </c>
-      <c r="C87" t="s">
-        <v>390</v>
-      </c>
-      <c r="D87" t="s">
-        <v>391</v>
-      </c>
-      <c r="E87" t="s">
-        <v>87</v>
-      </c>
-      <c r="F87" t="s">
-        <v>73</v>
-      </c>
-      <c r="G87" t="s">
-        <v>41</v>
-      </c>
-      <c r="H87" t="s">
-        <v>88</v>
-      </c>
-      <c r="I87">
-        <v>1</v>
-      </c>
-      <c r="J87" t="s">
-        <v>392</v>
-      </c>
-      <c r="K87">
-        <v>1</v>
-      </c>
-      <c r="L87" t="s">
-        <v>41</v>
-      </c>
-      <c r="M87">
-        <v>1</v>
-      </c>
-      <c r="N87" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="88" spans="2:14">
-      <c r="B88" t="s">
-        <v>393</v>
-      </c>
-      <c r="C88" t="s">
-        <v>394</v>
-      </c>
-      <c r="D88" t="s">
-        <v>395</v>
-      </c>
-      <c r="E88" t="s">
-        <v>87</v>
-      </c>
-      <c r="F88" t="s">
-        <v>73</v>
-      </c>
-      <c r="G88" t="s">
-        <v>41</v>
-      </c>
-      <c r="H88" t="s">
-        <v>88</v>
-      </c>
-      <c r="I88">
-        <v>1</v>
-      </c>
-      <c r="J88" t="s">
-        <v>396</v>
-      </c>
-      <c r="K88">
-        <v>1.1</v>
-      </c>
-      <c r="L88" t="s">
-        <v>41</v>
-      </c>
-      <c r="M88">
-        <v>1</v>
-      </c>
-      <c r="N88" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="89" spans="2:14">
-      <c r="B89" t="s">
-        <v>397</v>
-      </c>
-      <c r="C89" t="s">
-        <v>398</v>
-      </c>
-      <c r="D89" t="s">
-        <v>399</v>
-      </c>
-      <c r="E89" t="s">
-        <v>87</v>
-      </c>
-      <c r="F89" t="s">
-        <v>73</v>
-      </c>
-      <c r="G89" t="s">
-        <v>41</v>
-      </c>
-      <c r="H89" t="s">
-        <v>88</v>
-      </c>
-      <c r="I89">
-        <v>1</v>
-      </c>
-      <c r="J89" t="s">
-        <v>400</v>
-      </c>
-      <c r="K89">
-        <v>1.1</v>
-      </c>
-      <c r="L89" t="s">
-        <v>41</v>
-      </c>
-      <c r="M89">
-        <v>1</v>
-      </c>
-      <c r="N89" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="90" spans="2:14">
-      <c r="B90" t="s">
-        <v>401</v>
-      </c>
-      <c r="C90" t="s">
-        <v>402</v>
-      </c>
-      <c r="D90" t="s">
-        <v>403</v>
-      </c>
-      <c r="E90" t="s">
-        <v>87</v>
-      </c>
-      <c r="F90" t="s">
-        <v>73</v>
-      </c>
-      <c r="G90" t="s">
-        <v>41</v>
-      </c>
-      <c r="H90" t="s">
-        <v>88</v>
-      </c>
-      <c r="I90">
-        <v>1</v>
-      </c>
-      <c r="J90" t="s">
-        <v>404</v>
-      </c>
-      <c r="K90">
-        <v>0.1</v>
-      </c>
-      <c r="L90" t="s">
-        <v>41</v>
-      </c>
-      <c r="M90">
-        <v>1</v>
-      </c>
-      <c r="N90" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="91" spans="2:14">
-      <c r="B91" t="s">
-        <v>405</v>
-      </c>
-      <c r="C91" t="s">
-        <v>406</v>
-      </c>
-      <c r="D91" t="s">
-        <v>407</v>
-      </c>
-      <c r="E91" t="s">
-        <v>87</v>
-      </c>
-      <c r="F91" t="s">
-        <v>40</v>
-      </c>
-      <c r="G91" t="s">
-        <v>41</v>
-      </c>
-      <c r="H91" t="s">
-        <v>88</v>
-      </c>
-      <c r="I91">
-        <v>1</v>
-      </c>
-      <c r="J91" t="s">
-        <v>408</v>
-      </c>
-      <c r="K91">
-        <v>10</v>
-      </c>
-      <c r="L91" t="s">
-        <v>409</v>
-      </c>
-      <c r="M91">
-        <v>1</v>
-      </c>
-      <c r="N91" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="92" spans="2:14">
-      <c r="B92" t="s">
-        <v>410</v>
-      </c>
-      <c r="C92" t="s">
-        <v>411</v>
-      </c>
-      <c r="D92" t="s">
-        <v>412</v>
-      </c>
-      <c r="E92" t="s">
-        <v>87</v>
-      </c>
-      <c r="F92" t="s">
-        <v>73</v>
-      </c>
-      <c r="G92" t="s">
-        <v>41</v>
-      </c>
-      <c r="H92" t="s">
-        <v>88</v>
-      </c>
-      <c r="I92">
-        <v>1</v>
-      </c>
-      <c r="J92" t="s">
-        <v>413</v>
-      </c>
-      <c r="K92">
-        <v>0.1</v>
-      </c>
-      <c r="L92" t="s">
-        <v>41</v>
-      </c>
-      <c r="M92">
-        <v>1</v>
-      </c>
-      <c r="N92" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="93" spans="2:14">
-      <c r="B93" t="s">
-        <v>414</v>
-      </c>
-      <c r="C93" t="s">
-        <v>415</v>
-      </c>
-      <c r="D93" t="s">
-        <v>416</v>
-      </c>
-      <c r="E93" t="s">
-        <v>87</v>
-      </c>
-      <c r="F93" t="s">
-        <v>40</v>
-      </c>
-      <c r="G93" t="s">
-        <v>41</v>
-      </c>
-      <c r="H93" t="s">
-        <v>88</v>
-      </c>
-      <c r="I93">
-        <v>1</v>
-      </c>
-      <c r="J93" t="s">
-        <v>417</v>
-      </c>
-      <c r="K93">
-        <v>10</v>
-      </c>
-      <c r="L93" t="s">
-        <v>41</v>
-      </c>
-      <c r="M93">
-        <v>1</v>
-      </c>
-      <c r="N93" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="94" spans="2:14">
-      <c r="B94" t="s">
-        <v>418</v>
-      </c>
-      <c r="C94" t="s">
-        <v>419</v>
-      </c>
-      <c r="D94" t="s">
-        <v>420</v>
-      </c>
-      <c r="E94" t="s">
-        <v>87</v>
-      </c>
-      <c r="F94" t="s">
-        <v>73</v>
-      </c>
-      <c r="G94" t="s">
-        <v>41</v>
-      </c>
-      <c r="H94" t="s">
-        <v>88</v>
-      </c>
-      <c r="I94">
-        <v>1</v>
-      </c>
-      <c r="J94" t="s">
-        <v>421</v>
-      </c>
-      <c r="K94">
-        <v>1</v>
-      </c>
-      <c r="L94" t="s">
-        <v>41</v>
-      </c>
-      <c r="M94">
-        <v>1</v>
-      </c>
-      <c r="N94" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="95" spans="2:14">
-      <c r="B95" t="s">
-        <v>422</v>
-      </c>
-      <c r="C95" t="s">
-        <v>423</v>
-      </c>
-      <c r="D95" t="s">
-        <v>424</v>
-      </c>
-      <c r="E95" t="s">
-        <v>87</v>
-      </c>
-      <c r="F95" t="s">
-        <v>40</v>
-      </c>
-      <c r="G95" t="s">
-        <v>41</v>
-      </c>
-      <c r="H95" t="s">
-        <v>88</v>
-      </c>
-      <c r="I95">
-        <v>1</v>
-      </c>
-      <c r="J95" t="s">
-        <v>425</v>
-      </c>
-      <c r="K95">
-        <v>10</v>
-      </c>
-      <c r="L95" t="s">
-        <v>426</v>
-      </c>
-      <c r="M95">
-        <v>1</v>
-      </c>
-      <c r="N95" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="96" spans="2:14">
-      <c r="B96" t="s">
-        <v>427</v>
-      </c>
-      <c r="C96" t="s">
-        <v>428</v>
-      </c>
-      <c r="D96" t="s">
-        <v>429</v>
-      </c>
-      <c r="E96" t="s">
-        <v>87</v>
-      </c>
-      <c r="F96" t="s">
-        <v>40</v>
-      </c>
-      <c r="G96" t="s">
-        <v>41</v>
-      </c>
-      <c r="H96" t="s">
-        <v>88</v>
-      </c>
-      <c r="I96">
-        <v>1</v>
-      </c>
-      <c r="J96" t="s">
-        <v>430</v>
-      </c>
-      <c r="K96">
-        <v>10</v>
-      </c>
-      <c r="L96" t="s">
-        <v>41</v>
-      </c>
-      <c r="M96">
-        <v>1</v>
-      </c>
-      <c r="N96" t="s">
-        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -6933,36 +6635,36 @@
   <sheetData>
     <row r="1" customHeight="1" spans="2:9">
       <c r="B1" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>431</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="H1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="2" t="s">
         <v>432</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>433</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>434</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>435</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="2:9">
       <c r="B2" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>436</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>437</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>438</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>439</v>
       </c>
       <c r="H2" s="1">
         <v>1</v>
@@ -6976,10 +6678,10 @@
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
       <c r="D3" s="3" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="H3" s="1">
         <v>2</v>
@@ -6993,10 +6695,10 @@
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
       <c r="D4" s="3" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="H4" s="1">
         <v>3</v>
@@ -7010,10 +6712,10 @@
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
       <c r="D5" s="3" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="H5" s="1">
         <v>4</v>
@@ -7027,10 +6729,10 @@
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
       <c r="D6" s="3" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="H6" s="1">
         <v>5</v>
@@ -7044,10 +6746,10 @@
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
       <c r="D7" s="3" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="H7" s="1">
         <v>6</v>
@@ -7061,10 +6763,10 @@
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
       <c r="D8" s="3" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="H8" s="1">
         <v>7</v>
@@ -7078,10 +6780,10 @@
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
       <c r="D9" s="3" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="H9" s="1">
         <v>8</v>
@@ -7095,10 +6797,10 @@
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
       <c r="D10" s="3" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="H10" s="1">
         <v>9</v>
@@ -7111,13 +6813,13 @@
     <row r="11" customHeight="1" spans="2:9">
       <c r="B11" s="4"/>
       <c r="C11" s="3" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="H11" s="1">
         <v>10</v>
@@ -7131,10 +6833,10 @@
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
       <c r="D12" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="H12" s="1">
         <v>11</v>
@@ -7148,10 +6850,10 @@
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
       <c r="D13" s="3" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="H13" s="1">
         <v>12</v>
@@ -7165,10 +6867,10 @@
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
       <c r="D14" s="3" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="H14" s="1">
         <v>13</v>
@@ -7181,13 +6883,13 @@
     <row r="15" customHeight="1" spans="2:9">
       <c r="B15" s="4"/>
       <c r="C15" s="3" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="H15" s="1">
         <v>14</v>
@@ -7201,10 +6903,10 @@
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
       <c r="D16" s="3" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H16" s="1">
         <v>15</v>
@@ -7218,10 +6920,10 @@
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
       <c r="D17" s="3" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H17" s="1">
         <v>16</v>
@@ -7235,10 +6937,10 @@
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
       <c r="D18" s="3" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="H18" s="1">
         <v>17</v>
@@ -7252,10 +6954,10 @@
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
       <c r="D19" s="3" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="H19" s="1">
         <v>18</v>
@@ -7269,10 +6971,10 @@
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
       <c r="D20" s="3" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="H20" s="1">
         <v>19</v>
@@ -7286,10 +6988,10 @@
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
       <c r="D21" s="3" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="H21" s="1">
         <v>20</v>
@@ -7302,13 +7004,13 @@
     <row r="22" customHeight="1" spans="2:9">
       <c r="B22" s="4"/>
       <c r="C22" s="3" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H22" s="1">
         <v>21</v>
@@ -7321,13 +7023,13 @@
     <row r="23" customHeight="1" spans="2:9">
       <c r="B23" s="4"/>
       <c r="C23" s="3" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="H23" s="1">
         <v>22</v>
@@ -7341,10 +7043,10 @@
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
       <c r="D24" s="3" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="H24" s="1">
         <v>23</v>
@@ -7358,10 +7060,10 @@
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
       <c r="D25" s="3" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="H25" s="1">
         <v>24</v>
@@ -7375,10 +7077,10 @@
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
       <c r="D26" s="3" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="H26" s="1">
         <v>25</v>
@@ -7391,13 +7093,13 @@
     <row r="27" customHeight="1" spans="2:9">
       <c r="B27" s="4"/>
       <c r="C27" s="3" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="H27" s="1">
         <v>26</v>
@@ -7411,10 +7113,10 @@
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
       <c r="D28" s="3" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="H28" s="1">
         <v>27</v>
@@ -7427,13 +7129,13 @@
     <row r="29" customHeight="1" spans="2:9">
       <c r="B29" s="4"/>
       <c r="C29" s="3" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="H29" s="1">
         <v>28</v>
@@ -7446,13 +7148,13 @@
     <row r="30" customHeight="1" spans="2:9">
       <c r="B30" s="4"/>
       <c r="C30" s="3" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="H30" s="1">
         <v>29</v>
@@ -7465,13 +7167,13 @@
     <row r="31" customHeight="1" spans="2:9">
       <c r="B31" s="4"/>
       <c r="C31" s="3" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="D31" s="3" t="s">
+        <v>493</v>
+      </c>
+      <c r="E31" s="5" t="s">
         <v>496</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>499</v>
       </c>
       <c r="H31" s="1">
         <v>30</v>
@@ -7484,13 +7186,13 @@
     <row r="32" customHeight="1" spans="2:9">
       <c r="B32" s="4"/>
       <c r="C32" s="3" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="H32" s="1">
         <v>31</v>
@@ -7504,10 +7206,10 @@
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
       <c r="D33" s="3" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="H33" s="1">
         <v>32</v>
@@ -7521,10 +7223,10 @@
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
       <c r="D34" s="3" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="H34" s="1">
         <v>33</v>
@@ -7537,13 +7239,13 @@
     <row r="35" customHeight="1" spans="2:9">
       <c r="B35" s="4"/>
       <c r="C35" s="5" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="H35" s="1">
         <v>34</v>
@@ -7557,10 +7259,10 @@
       <c r="B36" s="4"/>
       <c r="C36" s="5"/>
       <c r="D36" s="6" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="H36" s="1">
         <v>35</v>
@@ -7573,13 +7275,13 @@
     <row r="37" customHeight="1" spans="2:9">
       <c r="B37" s="4"/>
       <c r="C37" s="3" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="H37" s="1">
         <v>36</v>
@@ -7592,13 +7294,13 @@
     <row r="38" customHeight="1" spans="2:9">
       <c r="B38" s="4"/>
       <c r="C38" s="3" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="H38" s="1">
         <v>37</v>
@@ -7612,10 +7314,10 @@
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
       <c r="D39" s="3" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="H39" s="1">
         <v>38</v>
@@ -7629,10 +7331,10 @@
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
       <c r="D40" s="3" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="H40" s="1">
         <v>39</v>
@@ -7646,10 +7348,10 @@
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
       <c r="D41" s="3" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="H41" s="1">
         <v>40</v>
@@ -7663,10 +7365,10 @@
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
       <c r="D42" s="3" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="H42" s="1">
         <v>41</v>
@@ -7680,10 +7382,10 @@
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
       <c r="D43" s="3" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="H43" s="1">
         <v>42</v>
@@ -7696,13 +7398,13 @@
     <row r="44" customHeight="1" spans="2:9">
       <c r="B44" s="4"/>
       <c r="C44" s="3" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="H44" s="1">
         <v>43</v>
@@ -7716,10 +7418,10 @@
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
       <c r="D45" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="H45" s="1">
         <v>44</v>
@@ -7733,10 +7435,10 @@
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
       <c r="D46" s="3" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="H46" s="1">
         <v>45</v>
@@ -7750,10 +7452,10 @@
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
       <c r="D47" s="3" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="H47" s="1">
         <v>46</v>
@@ -7767,10 +7469,10 @@
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
       <c r="D48" s="3" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="H48" s="1">
         <v>47</v>
@@ -7783,13 +7485,13 @@
     <row r="49" customHeight="1" spans="2:9">
       <c r="B49" s="4"/>
       <c r="C49" s="3" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="H49" s="1">
         <v>48</v>
@@ -7803,10 +7505,10 @@
       <c r="B50" s="4"/>
       <c r="C50" s="4"/>
       <c r="D50" s="3" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="H50" s="1">
         <v>49</v>
@@ -7820,10 +7522,10 @@
       <c r="B51" s="4"/>
       <c r="C51" s="4"/>
       <c r="D51" s="3" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="H51" s="1">
         <v>50</v>
@@ -7836,13 +7538,13 @@
     <row r="52" customHeight="1" spans="2:9">
       <c r="B52" s="4"/>
       <c r="C52" s="3" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="H52" s="1">
         <v>51</v>
@@ -7856,10 +7558,10 @@
       <c r="B53" s="4"/>
       <c r="C53" s="4"/>
       <c r="D53" s="3" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="H53" s="1">
         <v>52</v>
@@ -7873,10 +7575,10 @@
       <c r="B54" s="4"/>
       <c r="C54" s="4"/>
       <c r="D54" s="3" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="H54" s="1">
         <v>53</v>
@@ -7889,13 +7591,13 @@
     <row r="55" customHeight="1" spans="2:9">
       <c r="B55" s="4"/>
       <c r="C55" s="3" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="H55" s="1">
         <v>54</v>
@@ -7909,10 +7611,10 @@
       <c r="B56" s="4"/>
       <c r="C56" s="4"/>
       <c r="D56" s="3" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="H56" s="1">
         <v>55</v>
@@ -7926,10 +7628,10 @@
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
       <c r="D57" s="3" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="H57" s="1">
         <v>56</v>
@@ -7943,10 +7645,10 @@
       <c r="B58" s="4"/>
       <c r="C58" s="4"/>
       <c r="D58" s="3" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="H58" s="1">
         <v>57</v>
@@ -7960,10 +7662,10 @@
       <c r="B59" s="4"/>
       <c r="C59" s="4"/>
       <c r="D59" s="3" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="H59" s="1">
         <v>58</v>
@@ -7977,10 +7679,10 @@
       <c r="B60" s="4"/>
       <c r="C60" s="4"/>
       <c r="D60" s="3" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="H60" s="1">
         <v>59</v>
@@ -7993,13 +7695,13 @@
     <row r="61" customHeight="1" spans="2:9">
       <c r="B61" s="4"/>
       <c r="C61" s="3" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="H61" s="1">
         <v>60</v>
@@ -8013,10 +7715,10 @@
       <c r="B62" s="4"/>
       <c r="C62" s="4"/>
       <c r="D62" s="3" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="H62" s="1">
         <v>61</v>
@@ -8029,13 +7731,13 @@
     <row r="63" customHeight="1" spans="2:9">
       <c r="B63" s="4"/>
       <c r="C63" s="3" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="H63" s="1">
         <v>62</v>
@@ -8049,10 +7751,10 @@
       <c r="B64" s="4"/>
       <c r="C64" s="4"/>
       <c r="D64" s="3" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="H64" s="1">
         <v>63</v>
@@ -8066,10 +7768,10 @@
       <c r="B65" s="4"/>
       <c r="C65" s="4"/>
       <c r="D65" s="3" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="H65" s="1">
         <v>64</v>
@@ -8083,10 +7785,10 @@
       <c r="B66" s="4"/>
       <c r="C66" s="4"/>
       <c r="D66" s="3" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="H66" s="1">
         <v>65</v>
@@ -8100,10 +7802,10 @@
       <c r="B67" s="4"/>
       <c r="C67" s="4"/>
       <c r="D67" s="3" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="H67" s="1">
         <v>66</v>
@@ -8116,13 +7818,13 @@
     <row r="68" customHeight="1" spans="2:9">
       <c r="B68" s="4"/>
       <c r="C68" s="3" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="H68" s="1">
         <v>67</v>
@@ -8135,13 +7837,13 @@
     <row r="69" customHeight="1" spans="2:9">
       <c r="B69" s="4"/>
       <c r="C69" s="3" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="H69" s="1">
         <v>68</v>
@@ -8155,10 +7857,10 @@
       <c r="B70" s="4"/>
       <c r="C70" s="4"/>
       <c r="D70" s="3" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="H70" s="1">
         <v>69</v>
@@ -8172,10 +7874,10 @@
       <c r="B71" s="4"/>
       <c r="C71" s="4"/>
       <c r="D71" s="3" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="H71" s="1">
         <v>70</v>
@@ -8189,10 +7891,10 @@
       <c r="B72" s="4"/>
       <c r="C72" s="4"/>
       <c r="D72" s="3" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="H72" s="1">
         <v>71</v>
@@ -8206,10 +7908,10 @@
       <c r="B73" s="4"/>
       <c r="C73" s="4"/>
       <c r="D73" s="3" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="H73" s="1">
         <v>72</v>
@@ -8222,13 +7924,13 @@
     <row r="74" customHeight="1" spans="2:9">
       <c r="B74" s="4"/>
       <c r="C74" s="3" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="H74" s="1">
         <v>73</v>
@@ -8242,10 +7944,10 @@
       <c r="B75" s="4"/>
       <c r="C75" s="3"/>
       <c r="D75" s="3" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="H75" s="1">
         <v>74</v>
@@ -8257,16 +7959,16 @@
     </row>
     <row r="76" customHeight="1" spans="2:9">
       <c r="B76" s="3" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="H76" s="1">
         <v>75</v>
@@ -8280,10 +7982,10 @@
       <c r="B77" s="4"/>
       <c r="C77" s="4"/>
       <c r="D77" s="3" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="H77" s="1">
         <v>76</v>
@@ -8297,10 +7999,10 @@
       <c r="B78" s="4"/>
       <c r="C78" s="4"/>
       <c r="D78" s="3" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="H78" s="1">
         <v>77</v>
@@ -8314,10 +8016,10 @@
       <c r="B79" s="4"/>
       <c r="C79" s="4"/>
       <c r="D79" s="3" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="H79" s="1">
         <v>78</v>
@@ -8331,10 +8033,10 @@
       <c r="B80" s="4"/>
       <c r="C80" s="4"/>
       <c r="D80" s="3" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="H80" s="1">
         <v>79</v>
@@ -8348,10 +8050,10 @@
       <c r="B81" s="4"/>
       <c r="C81" s="4"/>
       <c r="D81" s="5" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="H81" s="1">
         <v>80</v>
@@ -8365,10 +8067,10 @@
       <c r="B82" s="4"/>
       <c r="C82" s="4"/>
       <c r="D82" s="5" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="H82" s="1">
         <v>81</v>
@@ -8382,10 +8084,10 @@
       <c r="B83" s="4"/>
       <c r="C83" s="4"/>
       <c r="D83" s="5" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="H83" s="1">
         <v>82</v>
@@ -8399,10 +8101,10 @@
       <c r="B84" s="4"/>
       <c r="C84" s="4"/>
       <c r="D84" s="3" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="H84" s="1">
         <v>83</v>
@@ -8414,16 +8116,16 @@
     </row>
     <row r="85" customHeight="1" spans="2:9">
       <c r="B85" s="3" t="s">
+        <v>608</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>609</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>610</v>
+      </c>
+      <c r="E85" s="3" t="s">
         <v>611</v>
-      </c>
-      <c r="C85" s="3" t="s">
-        <v>612</v>
-      </c>
-      <c r="D85" s="3" t="s">
-        <v>613</v>
-      </c>
-      <c r="E85" s="3" t="s">
-        <v>614</v>
       </c>
       <c r="H85" s="1">
         <v>84</v>
@@ -8436,13 +8138,13 @@
     <row r="86" customHeight="1" spans="2:9">
       <c r="B86" s="4"/>
       <c r="C86" s="3" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="H86" s="1">
         <v>85</v>
@@ -8456,10 +8158,10 @@
       <c r="B87" s="4"/>
       <c r="C87" s="4"/>
       <c r="D87" s="3" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="H87" s="1">
         <v>86</v>
@@ -8473,10 +8175,10 @@
       <c r="B88" s="4"/>
       <c r="C88" s="4"/>
       <c r="D88" s="3" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="H88" s="1">
         <v>87</v>
@@ -8490,10 +8192,10 @@
       <c r="B89" s="4"/>
       <c r="C89" s="4"/>
       <c r="D89" s="3" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="H89" s="1">
         <v>88</v>
@@ -8505,13 +8207,13 @@
     </row>
     <row r="90" customHeight="1" spans="3:9">
       <c r="C90" s="3" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="H90" s="1">
         <v>89</v>
@@ -8525,10 +8227,10 @@
       <c r="B91" s="4"/>
       <c r="C91" s="4"/>
       <c r="D91" s="3" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="H91" s="1">
         <v>90</v>
@@ -8542,10 +8244,10 @@
       <c r="B92" s="4"/>
       <c r="C92" s="4"/>
       <c r="D92" s="3" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="H92" s="1">
         <v>91</v>
@@ -8559,10 +8261,10 @@
       <c r="B93" s="4"/>
       <c r="C93" s="4"/>
       <c r="D93" s="3" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="H93" s="1">
         <v>92</v>
@@ -8576,10 +8278,10 @@
       <c r="B94" s="4"/>
       <c r="C94" s="4"/>
       <c r="D94" s="3" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="H94" s="1">
         <v>93</v>

--- a/GourmetProject/GameConfig/Datas/item.xlsx
+++ b/GourmetProject/GameConfig/Datas/item.xlsx
@@ -1356,7 +1356,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Passive</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1364,10 +1364,9 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>RewardScreen</t>
+          <t>OnAcquire</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1378,7 +1377,6 @@
       <c r="J4" t="n">
         <v>2</v>
       </c>
-      <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
         <v>1</v>
       </c>
@@ -1416,7 +1414,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Passive</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1424,10 +1422,9 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>RewardScreen</t>
+          <t>OnAcquire</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1438,7 +1435,6 @@
       <c r="J5" t="n">
         <v>3</v>
       </c>
-      <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
         <v>1</v>
       </c>
@@ -1476,7 +1472,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Passive</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1484,10 +1480,9 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>RewardScreen</t>
+          <t>OnAcquire</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1498,7 +1493,6 @@
       <c r="J6" t="n">
         <v>2</v>
       </c>
-      <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
         <v>1</v>
       </c>
@@ -1536,7 +1530,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Passive</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1544,10 +1538,9 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>RewardScreen</t>
+          <t>OnAcquire</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1558,7 +1551,6 @@
       <c r="J7" t="n">
         <v>3</v>
       </c>
-      <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
         <v>1</v>
       </c>
@@ -1596,7 +1588,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Passive</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1604,10 +1596,9 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>RewardScreen</t>
+          <t>OnAcquire</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1618,7 +1609,6 @@
       <c r="J8" t="n">
         <v>3</v>
       </c>
-      <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
         <v>1</v>
       </c>
@@ -1656,7 +1646,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Passive</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1664,10 +1654,9 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>RewardScreen</t>
+          <t>OnAcquire</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1678,7 +1667,6 @@
       <c r="J9" t="n">
         <v>3</v>
       </c>
-      <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
         <v>1</v>
       </c>
@@ -1716,7 +1704,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Passive</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1724,10 +1712,9 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>RewardScreen</t>
+          <t>OnAcquire</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1738,7 +1725,6 @@
       <c r="J10" t="n">
         <v>1</v>
       </c>
-      <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
         <v>1</v>
       </c>
@@ -1776,7 +1762,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Passive</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1784,10 +1770,9 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>RewardScreen</t>
+          <t>OnAcquire</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1798,7 +1783,6 @@
       <c r="J11" t="n">
         <v>50</v>
       </c>
-      <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
         <v>1</v>
       </c>
@@ -1836,7 +1820,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Passive</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1844,10 +1828,9 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>RewardScreen</t>
+          <t>OnAcquire</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1858,7 +1841,6 @@
       <c r="J12" t="n">
         <v>0</v>
       </c>
-      <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
         <v>1</v>
       </c>
@@ -1896,7 +1878,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Passive</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1904,10 +1886,9 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>RewardScreen</t>
+          <t>OnAcquire</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1968,10 +1949,9 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>OnAcquire</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2032,7 +2012,6 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
           <t>None</t>
@@ -2046,7 +2025,6 @@
       <c r="J15" t="n">
         <v>100</v>
       </c>
-      <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
         <v>1</v>
       </c>
@@ -2092,7 +2070,6 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
           <t>None</t>
@@ -2106,7 +2083,6 @@
       <c r="J16" t="n">
         <v>0.2</v>
       </c>
-      <c r="K16" t="inlineStr"/>
       <c r="L16" t="n">
         <v>1</v>
       </c>
@@ -2152,7 +2128,6 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
           <t>None</t>
@@ -2166,7 +2141,6 @@
       <c r="J17" t="n">
         <v>0.2</v>
       </c>
-      <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
         <v>1</v>
       </c>
@@ -2212,7 +2186,6 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
           <t>None</t>
@@ -2226,7 +2199,6 @@
       <c r="J18" t="n">
         <v>0.2</v>
       </c>
-      <c r="K18" t="inlineStr"/>
       <c r="L18" t="n">
         <v>1</v>
       </c>
@@ -2272,7 +2244,6 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
           <t>None</t>
@@ -2286,7 +2257,6 @@
       <c r="J19" t="n">
         <v>0.2</v>
       </c>
-      <c r="K19" t="inlineStr"/>
       <c r="L19" t="n">
         <v>1</v>
       </c>
@@ -2332,7 +2302,6 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
           <t>None</t>
@@ -2346,7 +2315,6 @@
       <c r="J20" t="n">
         <v>0.2</v>
       </c>
-      <c r="K20" t="inlineStr"/>
       <c r="L20" t="n">
         <v>1</v>
       </c>
@@ -2392,7 +2360,6 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
           <t>None</t>
@@ -2406,7 +2373,6 @@
       <c r="J21" t="n">
         <v>0.2</v>
       </c>
-      <c r="K21" t="inlineStr"/>
       <c r="L21" t="n">
         <v>1</v>
       </c>
@@ -2452,7 +2418,6 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
           <t>None</t>
@@ -2466,7 +2431,6 @@
       <c r="J22" t="n">
         <v>30</v>
       </c>
-      <c r="K22" t="inlineStr"/>
       <c r="L22" t="n">
         <v>1</v>
       </c>
@@ -2512,7 +2476,6 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
           <t>None</t>
@@ -2526,7 +2489,6 @@
       <c r="J23" t="n">
         <v>0.2</v>
       </c>
-      <c r="K23" t="inlineStr"/>
       <c r="L23" t="n">
         <v>1</v>
       </c>
@@ -2572,7 +2534,6 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
           <t>None</t>
@@ -2586,7 +2547,6 @@
       <c r="J24" t="n">
         <v>0</v>
       </c>
-      <c r="K24" t="inlineStr"/>
       <c r="L24" t="n">
         <v>1</v>
       </c>
@@ -2624,7 +2584,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Passive</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2632,10 +2592,9 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
-          <t>RewardScreen</t>
+          <t>OnAcquire</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2696,7 +2655,6 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
           <t>None</t>
@@ -2710,7 +2668,6 @@
       <c r="J26" t="n">
         <v>-0.1</v>
       </c>
-      <c r="K26" t="inlineStr"/>
       <c r="L26" t="n">
         <v>1</v>
       </c>
@@ -2756,7 +2713,6 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
           <t>None</t>
@@ -2770,7 +2726,6 @@
       <c r="J27" t="n">
         <v>-0.1</v>
       </c>
-      <c r="K27" t="inlineStr"/>
       <c r="L27" t="n">
         <v>1</v>
       </c>
@@ -2816,7 +2771,6 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
           <t>None</t>
@@ -2830,7 +2784,6 @@
       <c r="J28" t="n">
         <v>-0.1</v>
       </c>
-      <c r="K28" t="inlineStr"/>
       <c r="L28" t="n">
         <v>1</v>
       </c>
@@ -2876,7 +2829,6 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
           <t>None</t>
@@ -2940,7 +2892,6 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
           <t>None</t>
@@ -3004,7 +2955,6 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
           <t>None</t>
@@ -3018,7 +2968,6 @@
       <c r="J31" t="n">
         <v>0.1</v>
       </c>
-      <c r="K31" t="inlineStr"/>
       <c r="L31" t="n">
         <v>1</v>
       </c>
@@ -3064,7 +3013,6 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
           <t>None</t>
@@ -3078,7 +3026,6 @@
       <c r="J32" t="n">
         <v>10</v>
       </c>
-      <c r="K32" t="inlineStr"/>
       <c r="L32" t="n">
         <v>1</v>
       </c>
@@ -3124,7 +3071,6 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
           <t>None</t>
@@ -3138,7 +3084,6 @@
       <c r="J33" t="n">
         <v>0.2</v>
       </c>
-      <c r="K33" t="inlineStr"/>
       <c r="L33" t="n">
         <v>1</v>
       </c>
@@ -3184,7 +3129,6 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
           <t>None</t>
@@ -3248,7 +3192,6 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
           <t>None</t>
@@ -3312,7 +3255,6 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
           <t>None</t>
@@ -3326,7 +3268,6 @@
       <c r="J36" t="n">
         <v>0</v>
       </c>
-      <c r="K36" t="inlineStr"/>
       <c r="L36" t="n">
         <v>1</v>
       </c>
@@ -3372,7 +3313,6 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
           <t>None</t>
@@ -3386,7 +3326,6 @@
       <c r="J37" t="n">
         <v>1</v>
       </c>
-      <c r="K37" t="inlineStr"/>
       <c r="L37" t="n">
         <v>1</v>
       </c>
@@ -3432,7 +3371,6 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
           <t>None</t>
@@ -3446,7 +3384,6 @@
       <c r="J38" t="n">
         <v>0.2</v>
       </c>
-      <c r="K38" t="inlineStr"/>
       <c r="L38" t="n">
         <v>1</v>
       </c>
@@ -3484,7 +3421,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Passive</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -3492,10 +3429,9 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
-          <t>BeforeEat</t>
+          <t>OnAcquire</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -3506,7 +3442,6 @@
       <c r="J39" t="n">
         <v>5</v>
       </c>
-      <c r="K39" t="inlineStr"/>
       <c r="L39" t="n">
         <v>1</v>
       </c>
@@ -3552,7 +3487,6 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
           <t>None</t>
@@ -3566,7 +3500,6 @@
       <c r="J40" t="n">
         <v>1</v>
       </c>
-      <c r="K40" t="inlineStr"/>
       <c r="L40" t="n">
         <v>1</v>
       </c>
@@ -3612,7 +3545,6 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
           <t>None</t>
@@ -3626,7 +3558,6 @@
       <c r="J41" t="n">
         <v>10</v>
       </c>
-      <c r="K41" t="inlineStr"/>
       <c r="L41" t="n">
         <v>1</v>
       </c>
@@ -3672,7 +3603,6 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
           <t>None</t>
@@ -3686,7 +3616,6 @@
       <c r="J42" t="n">
         <v>1</v>
       </c>
-      <c r="K42" t="inlineStr"/>
       <c r="L42" t="n">
         <v>1</v>
       </c>
@@ -3732,7 +3661,6 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
           <t>None</t>
@@ -3746,7 +3674,6 @@
       <c r="J43" t="n">
         <v>10</v>
       </c>
-      <c r="K43" t="inlineStr"/>
       <c r="L43" t="n">
         <v>1</v>
       </c>
@@ -3792,7 +3719,6 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
           <t>None</t>
@@ -3806,7 +3732,6 @@
       <c r="J44" t="n">
         <v>10</v>
       </c>
-      <c r="K44" t="inlineStr"/>
       <c r="L44" t="n">
         <v>1</v>
       </c>
@@ -3844,7 +3769,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Passive</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -3852,10 +3777,9 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
-          <t>RewardScreen</t>
+          <t>OnAcquire</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3908,7 +3832,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Passive</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3916,10 +3840,9 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
-          <t>RewardScreen</t>
+          <t>OnAcquire</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3930,7 +3853,6 @@
       <c r="J46" t="n">
         <v>0</v>
       </c>
-      <c r="K46" t="inlineStr"/>
       <c r="L46" t="n">
         <v>1</v>
       </c>
@@ -3968,7 +3890,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Passive</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3976,10 +3898,9 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
-          <t>RewardScreen</t>
+          <t>OnAcquire</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3990,7 +3911,6 @@
       <c r="J47" t="n">
         <v>1</v>
       </c>
-      <c r="K47" t="inlineStr"/>
       <c r="L47" t="n">
         <v>1</v>
       </c>
@@ -4028,7 +3948,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Passive</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -4036,10 +3956,9 @@
           <t>Epic</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
-          <t>RewardScreen</t>
+          <t>OnAcquire</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4050,7 +3969,6 @@
       <c r="J48" t="n">
         <v>1</v>
       </c>
-      <c r="K48" t="inlineStr"/>
       <c r="L48" t="n">
         <v>1</v>
       </c>
@@ -4088,7 +4006,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Passive</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -4096,10 +4014,9 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
-          <t>RewardScreen</t>
+          <t>OnAcquire</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -4110,7 +4027,6 @@
       <c r="J49" t="n">
         <v>1</v>
       </c>
-      <c r="K49" t="inlineStr"/>
       <c r="L49" t="n">
         <v>1</v>
       </c>
@@ -4148,7 +4064,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Passive</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -4156,10 +4072,9 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
-          <t>RewardScreen</t>
+          <t>OnAcquire</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -4170,7 +4085,6 @@
       <c r="J50" t="n">
         <v>1</v>
       </c>
-      <c r="K50" t="inlineStr"/>
       <c r="L50" t="n">
         <v>1</v>
       </c>
@@ -4216,7 +4130,6 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr">
         <is>
           <t>None</t>
@@ -4280,7 +4193,6 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr">
         <is>
           <t>None</t>
@@ -4344,7 +4256,6 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
           <t>None</t>
@@ -4408,7 +4319,6 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
           <t>None</t>
@@ -4422,7 +4332,6 @@
       <c r="J54" t="n">
         <v>2</v>
       </c>
-      <c r="K54" t="inlineStr"/>
       <c r="L54" t="n">
         <v>1</v>
       </c>
@@ -4468,7 +4377,6 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
           <t>None</t>
@@ -4482,7 +4390,6 @@
       <c r="J55" t="n">
         <v>20</v>
       </c>
-      <c r="K55" t="inlineStr"/>
       <c r="L55" t="n">
         <v>1</v>
       </c>
@@ -4528,7 +4435,6 @@
           <t>Epic</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
           <t>None</t>
@@ -4542,7 +4448,6 @@
       <c r="J56" t="n">
         <v>1000</v>
       </c>
-      <c r="K56" t="inlineStr"/>
       <c r="L56" t="n">
         <v>1</v>
       </c>
@@ -4580,7 +4485,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Passive</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -4588,10 +4493,9 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
-          <t>BeforeEat</t>
+          <t>OnAcquire</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -4602,7 +4506,6 @@
       <c r="J57" t="n">
         <v>2</v>
       </c>
-      <c r="K57" t="inlineStr"/>
       <c r="L57" t="n">
         <v>1</v>
       </c>
@@ -4640,7 +4543,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Passive</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -4648,10 +4551,9 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
         <is>
-          <t>BeforeEat</t>
+          <t>OnAcquire</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4662,7 +4564,6 @@
       <c r="J58" t="n">
         <v>200</v>
       </c>
-      <c r="K58" t="inlineStr"/>
       <c r="L58" t="n">
         <v>1</v>
       </c>
@@ -4700,7 +4601,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Passive</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -4708,10 +4609,9 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
-          <t>BeforeEat</t>
+          <t>OnAcquire</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4722,7 +4622,6 @@
       <c r="J59" t="n">
         <v>0</v>
       </c>
-      <c r="K59" t="inlineStr"/>
       <c r="L59" t="n">
         <v>1</v>
       </c>
@@ -4760,7 +4659,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Passive</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -4768,10 +4667,9 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr">
         <is>
-          <t>BeforeEat</t>
+          <t>OnAcquire</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4782,7 +4680,6 @@
       <c r="J60" t="n">
         <v>2</v>
       </c>
-      <c r="K60" t="inlineStr"/>
       <c r="L60" t="n">
         <v>1</v>
       </c>
@@ -4828,7 +4725,6 @@
           <t>Epic</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
           <t>None</t>
@@ -4842,7 +4738,6 @@
       <c r="J61" t="n">
         <v>1</v>
       </c>
-      <c r="K61" t="inlineStr"/>
       <c r="L61" t="n">
         <v>1</v>
       </c>
@@ -4880,7 +4775,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Passive</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -4888,10 +4783,9 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr">
         <is>
-          <t>BeforeEat</t>
+          <t>OnAcquire</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4902,7 +4796,6 @@
       <c r="J62" t="n">
         <v>1</v>
       </c>
-      <c r="K62" t="inlineStr"/>
       <c r="L62" t="n">
         <v>1</v>
       </c>
@@ -4940,7 +4833,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Passive</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -4948,10 +4841,9 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr">
         <is>
-          <t>BeforeEat</t>
+          <t>OnAcquire</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4962,7 +4854,6 @@
       <c r="J63" t="n">
         <v>2</v>
       </c>
-      <c r="K63" t="inlineStr"/>
       <c r="L63" t="n">
         <v>1</v>
       </c>
@@ -5000,7 +4891,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Passive</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -5008,10 +4899,9 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr">
         <is>
-          <t>BeforeEat</t>
+          <t>OnAcquire</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -5022,7 +4912,6 @@
       <c r="J64" t="n">
         <v>1</v>
       </c>
-      <c r="K64" t="inlineStr"/>
       <c r="L64" t="n">
         <v>1</v>
       </c>
@@ -5068,7 +4957,6 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr">
         <is>
           <t>None</t>
@@ -5082,7 +4970,6 @@
       <c r="J65" t="n">
         <v>4</v>
       </c>
-      <c r="K65" t="inlineStr"/>
       <c r="L65" t="n">
         <v>1</v>
       </c>
@@ -5128,7 +5015,6 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
           <t>None</t>
@@ -5142,7 +5028,6 @@
       <c r="J66" t="n">
         <v>0.2</v>
       </c>
-      <c r="K66" t="inlineStr"/>
       <c r="L66" t="n">
         <v>1</v>
       </c>
@@ -5188,7 +5073,6 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
         <is>
           <t>None</t>
@@ -5202,7 +5086,6 @@
       <c r="J67" t="n">
         <v>0.2</v>
       </c>
-      <c r="K67" t="inlineStr"/>
       <c r="L67" t="n">
         <v>1</v>
       </c>
@@ -5248,7 +5131,6 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr">
         <is>
           <t>None</t>
@@ -5262,7 +5144,6 @@
       <c r="J68" t="n">
         <v>10</v>
       </c>
-      <c r="K68" t="inlineStr"/>
       <c r="L68" t="n">
         <v>1</v>
       </c>
@@ -5300,7 +5181,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Passive</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -5308,10 +5189,9 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
-          <t>RewardScreen</t>
+          <t>OnAcquire</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -5322,7 +5202,6 @@
       <c r="J69" t="n">
         <v>2</v>
       </c>
-      <c r="K69" t="inlineStr"/>
       <c r="L69" t="n">
         <v>1</v>
       </c>
@@ -5368,7 +5247,6 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
         <is>
           <t>None</t>
@@ -5382,7 +5260,6 @@
       <c r="J70" t="n">
         <v>0</v>
       </c>
-      <c r="K70" t="inlineStr"/>
       <c r="L70" t="n">
         <v>1</v>
       </c>
@@ -5428,7 +5305,6 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr">
         <is>
           <t>None</t>
@@ -5442,7 +5318,6 @@
       <c r="J71" t="n">
         <v>1</v>
       </c>
-      <c r="K71" t="inlineStr"/>
       <c r="L71" t="n">
         <v>1</v>
       </c>
@@ -5488,7 +5363,6 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr">
         <is>
           <t>None</t>
@@ -5502,7 +5376,6 @@
       <c r="J72" t="n">
         <v>1</v>
       </c>
-      <c r="K72" t="inlineStr"/>
       <c r="L72" t="n">
         <v>1</v>
       </c>
@@ -5548,7 +5421,6 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr">
         <is>
           <t>None</t>
@@ -5612,7 +5484,6 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr">
         <is>
           <t>None</t>
@@ -5668,7 +5539,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Passive</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -5676,10 +5547,9 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr">
         <is>
-          <t>RewardScreen</t>
+          <t>OnAcquire</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5690,7 +5560,6 @@
       <c r="J75" t="n">
         <v>1</v>
       </c>
-      <c r="K75" t="inlineStr"/>
       <c r="L75" t="n">
         <v>1</v>
       </c>
@@ -5728,7 +5597,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Passive</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -5736,10 +5605,9 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr">
         <is>
-          <t>RewardScreen</t>
+          <t>OnAcquire</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5750,7 +5618,6 @@
       <c r="J76" t="n">
         <v>2</v>
       </c>
-      <c r="K76" t="inlineStr"/>
       <c r="L76" t="n">
         <v>1</v>
       </c>
@@ -5788,7 +5655,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Passive</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -5796,10 +5663,9 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr">
         <is>
-          <t>RewardScreen</t>
+          <t>OnAcquire</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5810,7 +5676,6 @@
       <c r="J77" t="n">
         <v>100</v>
       </c>
-      <c r="K77" t="inlineStr"/>
       <c r="L77" t="n">
         <v>1</v>
       </c>
@@ -5874,7 +5739,6 @@
       <c r="J78" t="n">
         <v>-0.25</v>
       </c>
-      <c r="K78" t="inlineStr"/>
       <c r="L78" t="n">
         <v>1</v>
       </c>
@@ -5938,7 +5802,6 @@
       <c r="J79" t="n">
         <v>0.25</v>
       </c>
-      <c r="K79" t="inlineStr"/>
       <c r="L79" t="n">
         <v>1</v>
       </c>
@@ -6002,7 +5865,6 @@
       <c r="J80" t="n">
         <v>0</v>
       </c>
-      <c r="K80" t="inlineStr"/>
       <c r="L80" t="n">
         <v>1</v>
       </c>
@@ -6066,7 +5928,6 @@
       <c r="J81" t="n">
         <v>1</v>
       </c>
-      <c r="K81" t="inlineStr"/>
       <c r="L81" t="n">
         <v>1</v>
       </c>
@@ -6130,7 +5991,6 @@
       <c r="J82" t="n">
         <v>-1</v>
       </c>
-      <c r="K82" t="inlineStr"/>
       <c r="L82" t="n">
         <v>1</v>
       </c>
@@ -6194,7 +6054,6 @@
       <c r="J83" t="n">
         <v>0.1</v>
       </c>
-      <c r="K83" t="inlineStr"/>
       <c r="L83" t="n">
         <v>1</v>
       </c>
@@ -6258,7 +6117,6 @@
       <c r="J84" t="n">
         <v>0.1</v>
       </c>
-      <c r="K84" t="inlineStr"/>
       <c r="L84" t="n">
         <v>1</v>
       </c>
@@ -6322,7 +6180,6 @@
       <c r="J85" t="n">
         <v>0.1</v>
       </c>
-      <c r="K85" t="inlineStr"/>
       <c r="L85" t="n">
         <v>1</v>
       </c>
@@ -6386,7 +6243,6 @@
       <c r="J86" t="n">
         <v>0</v>
       </c>
-      <c r="K86" t="inlineStr"/>
       <c r="L86" t="n">
         <v>1</v>
       </c>
@@ -6432,7 +6288,6 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr">
         <is>
           <t>None</t>
@@ -6446,7 +6301,6 @@
       <c r="J87" t="n">
         <v>1</v>
       </c>
-      <c r="K87" t="inlineStr"/>
       <c r="L87" t="n">
         <v>1</v>
       </c>
@@ -6492,7 +6346,6 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr">
         <is>
           <t>None</t>
@@ -6506,7 +6359,6 @@
       <c r="J88" t="n">
         <v>1.1</v>
       </c>
-      <c r="K88" t="inlineStr"/>
       <c r="L88" t="n">
         <v>1</v>
       </c>
@@ -6552,7 +6404,6 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr">
         <is>
           <t>None</t>
@@ -6566,7 +6417,6 @@
       <c r="J89" t="n">
         <v>1.1</v>
       </c>
-      <c r="K89" t="inlineStr"/>
       <c r="L89" t="n">
         <v>1</v>
       </c>
@@ -6612,7 +6462,6 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr">
         <is>
           <t>None</t>
@@ -6626,7 +6475,6 @@
       <c r="J90" t="n">
         <v>0.1</v>
       </c>
-      <c r="K90" t="inlineStr"/>
       <c r="L90" t="n">
         <v>1</v>
       </c>
@@ -6672,7 +6520,6 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr">
         <is>
           <t>None</t>
@@ -6736,7 +6583,6 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr">
         <is>
           <t>None</t>
@@ -6750,7 +6596,6 @@
       <c r="J92" t="n">
         <v>0.1</v>
       </c>
-      <c r="K92" t="inlineStr"/>
       <c r="L92" t="n">
         <v>1</v>
       </c>
@@ -6796,7 +6641,6 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr">
         <is>
           <t>None</t>
@@ -6810,7 +6654,6 @@
       <c r="J93" t="n">
         <v>10</v>
       </c>
-      <c r="K93" t="inlineStr"/>
       <c r="L93" t="n">
         <v>1</v>
       </c>
@@ -6856,7 +6699,6 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr">
         <is>
           <t>None</t>
@@ -6870,7 +6712,6 @@
       <c r="J94" t="n">
         <v>1</v>
       </c>
-      <c r="K94" t="inlineStr"/>
       <c r="L94" t="n">
         <v>1</v>
       </c>
@@ -6916,7 +6757,6 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr">
         <is>
           <t>None</t>
@@ -6980,7 +6820,6 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr">
         <is>
           <t>None</t>
@@ -6994,7 +6833,6 @@
       <c r="J96" t="n">
         <v>10</v>
       </c>
-      <c r="K96" t="inlineStr"/>
       <c r="L96" t="n">
         <v>1</v>
       </c>

--- a/GourmetProject/GameConfig/Datas/item.xlsx
+++ b/GourmetProject/GameConfig/Datas/item.xlsx
@@ -1089,7 +1089,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O96"/>
+  <dimension ref="A1:N96"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="13.0769230769231" customWidth="1" min="1" max="1"/>
@@ -1145,40 +1145,35 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>triggerTiming</t>
+          <t>effectType</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>effectType</t>
+          <t>effectValue</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>effectValue</t>
+          <t>effectParam</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>effectParam</t>
+          <t>baseWeight</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>baseWeight</t>
+          <t>hiddenRange</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>hiddenRange</t>
+          <t>targetKind</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
-        <is>
-          <t>targetKind</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
         <is>
           <t>targetCount</t>
         </is>
@@ -1222,40 +1217,35 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>触发时机</t>
+          <t>效果类型</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>效果类型</t>
+          <t>效果数值</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>效果数值</t>
+          <t>效果参数</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>效果参数</t>
+          <t>随机基础权重</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>随机基础权重</t>
+          <t>出现隐藏分区间(单元格: min,max)</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>出现隐藏分区间(单元格: min,max)</t>
+          <t>主动道具目标类型(作用对象;决定可用情境)</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
-        <is>
-          <t>主动道具目标类型(作用对象;决定可用情境)</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
         <is>
           <t>选目标数量(1/N;0=无目标或全部)</t>
         </is>
@@ -1299,40 +1289,35 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>ItemTriggerTiming</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>string</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>HiddenRange</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>HiddenRange</t>
+          <t>ItemTargetKind</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
-        <is>
-          <t>ItemTargetKind</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
         <is>
           <t>int</t>
         </is>
@@ -1366,31 +1351,26 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>OnAcquire</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
           <t>GrantRandomPassive</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="I4" t="n">
         <v>2</v>
       </c>
-      <c r="L4" t="n">
-        <v>1</v>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1424,31 +1404,26 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>OnAcquire</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
           <t>ChooseOnePassive</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="I5" t="n">
         <v>3</v>
       </c>
-      <c r="L5" t="n">
-        <v>1</v>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1482,31 +1457,26 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>OnAcquire</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
           <t>GrantRandomActive</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="I6" t="n">
         <v>2</v>
       </c>
-      <c r="L6" t="n">
-        <v>1</v>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1540,31 +1510,26 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>OnAcquire</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
           <t>ChooseOneActive</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="I7" t="n">
         <v>3</v>
       </c>
-      <c r="L7" t="n">
-        <v>1</v>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1598,31 +1563,26 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>OnAcquire</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
           <t>ChooseOneFood</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="I8" t="n">
         <v>3</v>
       </c>
-      <c r="L8" t="n">
-        <v>1</v>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1656,31 +1616,26 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>OnAcquire</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
           <t>ChooseOneFragment</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="I9" t="n">
         <v>3</v>
       </c>
-      <c r="L9" t="n">
-        <v>1</v>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1714,31 +1669,26 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>OnAcquire</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
           <t>GrantRecipe</t>
         </is>
       </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1</v>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1772,31 +1722,26 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>OnAcquire</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
           <t>FamilyPack</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="I11" t="n">
         <v>50</v>
       </c>
-      <c r="L11" t="n">
-        <v>1</v>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1830,31 +1775,26 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>OnAcquire</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
           <t>RandomizeItems</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="I12" t="n">
         <v>0</v>
       </c>
-      <c r="L12" t="n">
-        <v>1</v>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1888,36 +1828,31 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>OnAcquire</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
           <t>GoldNow</t>
         </is>
       </c>
-      <c r="J13" t="n">
+      <c r="I13" t="n">
         <v>0</v>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>range:1,100</t>
         </is>
       </c>
-      <c r="L13" t="n">
-        <v>1</v>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1951,36 +1886,31 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>OnAcquire</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
           <t>GoldMealBonus</t>
         </is>
       </c>
-      <c r="J14" t="n">
+      <c r="I14" t="n">
         <v>15</v>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>meals:10</t>
         </is>
       </c>
-      <c r="L14" t="n">
-        <v>1</v>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>5,45</t>
+        </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>5,45</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -2014,31 +1944,26 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
           <t>GoldOnBossComplete</t>
         </is>
       </c>
-      <c r="J15" t="n">
+      <c r="I15" t="n">
         <v>100</v>
       </c>
-      <c r="L15" t="n">
-        <v>1</v>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>5,45</t>
+        </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>5,45</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -2072,31 +1997,26 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
           <t>GoldMealPercent</t>
         </is>
       </c>
-      <c r="J16" t="n">
+      <c r="I16" t="n">
         <v>0.2</v>
       </c>
-      <c r="L16" t="n">
-        <v>1</v>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>20,65</t>
+        </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>20,65</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -2130,31 +2050,26 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
           <t>ShopDiscountFood</t>
         </is>
       </c>
-      <c r="J17" t="n">
+      <c r="I17" t="n">
         <v>0.2</v>
       </c>
-      <c r="L17" t="n">
-        <v>1</v>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>1,30</t>
+        </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>1,30</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -2188,31 +2103,26 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
           <t>ShopDiscountFragment</t>
         </is>
       </c>
-      <c r="J18" t="n">
+      <c r="I18" t="n">
         <v>0.2</v>
       </c>
-      <c r="L18" t="n">
-        <v>1</v>
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>1,30</t>
+        </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>1,30</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -2246,31 +2156,26 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
           <t>ShopDiscountActive</t>
         </is>
       </c>
-      <c r="J19" t="n">
+      <c r="I19" t="n">
         <v>0.2</v>
       </c>
-      <c r="L19" t="n">
-        <v>1</v>
+      <c r="K19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>1,30</t>
+        </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>1,30</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -2304,31 +2209,26 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
           <t>ShopDiscountPassive</t>
         </is>
       </c>
-      <c r="J20" t="n">
+      <c r="I20" t="n">
         <v>0.2</v>
       </c>
-      <c r="L20" t="n">
-        <v>1</v>
+      <c r="K20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>1,30</t>
+        </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>1,30</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -2362,31 +2262,26 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
           <t>ShopDiscountRemove</t>
         </is>
       </c>
-      <c r="J21" t="n">
+      <c r="I21" t="n">
         <v>0.2</v>
       </c>
-      <c r="L21" t="n">
-        <v>1</v>
+      <c r="K21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>1,30</t>
+        </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>1,30</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -2420,31 +2315,26 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
           <t>RemovePriceFixed</t>
         </is>
       </c>
-      <c r="J22" t="n">
+      <c r="I22" t="n">
         <v>30</v>
       </c>
-      <c r="L22" t="n">
-        <v>1</v>
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>5,45</t>
+        </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>5,45</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -2478,31 +2368,26 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
           <t>ShopDiscountRecipe</t>
         </is>
       </c>
-      <c r="J23" t="n">
+      <c r="I23" t="n">
         <v>0.2</v>
       </c>
-      <c r="L23" t="n">
-        <v>1</v>
+      <c r="K23" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>1,30</t>
+        </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>1,30</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -2536,31 +2421,26 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
           <t>Undying</t>
         </is>
       </c>
-      <c r="J24" t="n">
+      <c r="I24" t="n">
         <v>0</v>
       </c>
-      <c r="L24" t="n">
-        <v>1</v>
+      <c r="K24" t="n">
+        <v>1</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>20,65</t>
+        </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>20,65</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -2594,36 +2474,31 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>OnAcquire</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
           <t>RequiredScoreToOne</t>
         </is>
       </c>
-      <c r="J25" t="n">
+      <c r="I25" t="n">
         <v>0</v>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>meals:3</t>
         </is>
       </c>
-      <c r="L25" t="n">
-        <v>1</v>
+      <c r="K25" t="n">
+        <v>1</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -2657,31 +2532,26 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
           <t>RequiredScoreNormalPct</t>
         </is>
       </c>
-      <c r="J26" t="n">
+      <c r="I26" t="n">
         <v>-0.1</v>
       </c>
-      <c r="L26" t="n">
-        <v>1</v>
+      <c r="K26" t="n">
+        <v>1</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>5,45</t>
+        </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>5,45</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -2715,31 +2585,26 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
           <t>RequiredScoreSuperPct</t>
         </is>
       </c>
-      <c r="J27" t="n">
+      <c r="I27" t="n">
         <v>-0.1</v>
       </c>
-      <c r="L27" t="n">
-        <v>1</v>
+      <c r="K27" t="n">
+        <v>1</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>5,45</t>
+        </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>5,45</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -2773,31 +2638,26 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
           <t>RequiredScoreFeastPct</t>
         </is>
       </c>
-      <c r="J28" t="n">
+      <c r="I28" t="n">
         <v>-0.1</v>
       </c>
-      <c r="L28" t="n">
-        <v>1</v>
+      <c r="K28" t="n">
+        <v>1</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>5,45</t>
+        </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>5,45</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -2831,36 +2691,31 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
           <t>CountThresholdFinalMult</t>
         </is>
       </c>
-      <c r="J29" t="n">
+      <c r="I29" t="n">
         <v>1.1</v>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>lte:10</t>
         </is>
       </c>
-      <c r="L29" t="n">
-        <v>1</v>
+      <c r="K29" t="n">
+        <v>1</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>5,45</t>
+        </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>5,45</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -2894,36 +2749,31 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
           <t>CountThresholdFinalMult</t>
         </is>
       </c>
-      <c r="J30" t="n">
+      <c r="I30" t="n">
         <v>1.1</v>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>gte:10</t>
         </is>
       </c>
-      <c r="L30" t="n">
-        <v>1</v>
+      <c r="K30" t="n">
+        <v>1</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>5,45</t>
+        </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>5,45</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -2957,31 +2807,26 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
           <t>PerDishSettledMultFlat</t>
         </is>
       </c>
-      <c r="J31" t="n">
+      <c r="I31" t="n">
         <v>0.1</v>
       </c>
-      <c r="L31" t="n">
-        <v>1</v>
+      <c r="K31" t="n">
+        <v>1</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>20,65</t>
+        </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>20,65</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -3015,31 +2860,26 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
           <t>PermanentAddFlatAll</t>
         </is>
       </c>
-      <c r="J32" t="n">
+      <c r="I32" t="n">
         <v>10</v>
       </c>
-      <c r="L32" t="n">
-        <v>1</v>
+      <c r="K32" t="n">
+        <v>1</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>20,65</t>
+        </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>20,65</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -3073,31 +2913,26 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
           <t>PermanentAddMultAll</t>
         </is>
       </c>
-      <c r="J33" t="n">
+      <c r="I33" t="n">
         <v>0.2</v>
       </c>
-      <c r="L33" t="n">
-        <v>1</v>
+      <c r="K33" t="n">
+        <v>1</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>20,65</t>
+        </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>20,65</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -3131,36 +2966,31 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
           <t>StarGazeEveryN</t>
         </is>
       </c>
-      <c r="J34" t="n">
+      <c r="I34" t="n">
         <v>0</v>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>every:5</t>
         </is>
       </c>
-      <c r="L34" t="n">
-        <v>1</v>
+      <c r="K34" t="n">
+        <v>1</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>5,45</t>
+        </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>5,45</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -3194,36 +3024,31 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
           <t>StarGazeFirstN</t>
         </is>
       </c>
-      <c r="J35" t="n">
+      <c r="I35" t="n">
         <v>0</v>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>first:3</t>
         </is>
       </c>
-      <c r="L35" t="n">
-        <v>1</v>
+      <c r="K35" t="n">
+        <v>1</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>5,45</t>
+        </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>5,45</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -3257,31 +3082,26 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
           <t>FreeMoveFirst</t>
         </is>
       </c>
-      <c r="J36" t="n">
+      <c r="I36" t="n">
         <v>0</v>
       </c>
-      <c r="L36" t="n">
-        <v>1</v>
+      <c r="K36" t="n">
+        <v>1</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>5,45</t>
+        </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>5,45</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -3315,31 +3135,26 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
           <t>AdjustCountBonus</t>
         </is>
       </c>
-      <c r="J37" t="n">
-        <v>1</v>
-      </c>
-      <c r="L37" t="n">
-        <v>1</v>
+      <c r="I37" t="n">
+        <v>1</v>
+      </c>
+      <c r="K37" t="n">
+        <v>1</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>1,30</t>
+        </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>1,30</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -3373,31 +3188,26 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
           <t>AdjustToMult</t>
         </is>
       </c>
-      <c r="J38" t="n">
+      <c r="I38" t="n">
         <v>0.2</v>
       </c>
-      <c r="L38" t="n">
-        <v>1</v>
+      <c r="K38" t="n">
+        <v>1</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>20,65</t>
+        </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>20,65</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -3431,31 +3241,26 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>OnAcquire</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
           <t>FoodConvert</t>
         </is>
       </c>
-      <c r="J39" t="n">
+      <c r="I39" t="n">
         <v>5</v>
       </c>
-      <c r="L39" t="n">
-        <v>1</v>
+      <c r="K39" t="n">
+        <v>1</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -3489,31 +3294,26 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
           <t>GoldPerUnusedAdjust</t>
         </is>
       </c>
-      <c r="J40" t="n">
-        <v>1</v>
-      </c>
-      <c r="L40" t="n">
-        <v>1</v>
+      <c r="I40" t="n">
+        <v>1</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>5,45</t>
+        </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>5,45</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -3547,31 +3347,26 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
           <t>GoldOnShopEnter</t>
         </is>
       </c>
-      <c r="J41" t="n">
+      <c r="I41" t="n">
         <v>10</v>
       </c>
-      <c r="L41" t="n">
-        <v>1</v>
+      <c r="K41" t="n">
+        <v>1</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>5,45</t>
+        </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>5,45</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -3605,31 +3400,26 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
           <t>ExtraInterest</t>
         </is>
       </c>
-      <c r="J42" t="n">
-        <v>1</v>
-      </c>
-      <c r="L42" t="n">
-        <v>1</v>
+      <c r="I42" t="n">
+        <v>1</v>
+      </c>
+      <c r="K42" t="n">
+        <v>1</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>20,65</t>
+        </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>20,65</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O42" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -3663,31 +3453,26 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
           <t>MinGoldGuarantee</t>
         </is>
       </c>
-      <c r="J43" t="n">
+      <c r="I43" t="n">
         <v>10</v>
       </c>
-      <c r="L43" t="n">
-        <v>1</v>
+      <c r="K43" t="n">
+        <v>1</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>5,45</t>
+        </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>5,45</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O43" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -3721,31 +3506,26 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
           <t>InterestCapBonus</t>
         </is>
       </c>
-      <c r="J44" t="n">
+      <c r="I44" t="n">
         <v>10</v>
       </c>
-      <c r="L44" t="n">
-        <v>1</v>
+      <c r="K44" t="n">
+        <v>1</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>20,65</t>
+        </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>20,65</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O44" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -3779,36 +3559,31 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>OnAcquire</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
           <t>Loan</t>
         </is>
       </c>
-      <c r="J45" t="n">
+      <c r="I45" t="n">
         <v>300</v>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>repay:600</t>
         </is>
       </c>
-      <c r="L45" t="n">
-        <v>1</v>
+      <c r="K45" t="n">
+        <v>1</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O45" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -3842,31 +3617,26 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>OnAcquire</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
           <t>TimelineRandomize</t>
         </is>
       </c>
-      <c r="J46" t="n">
+      <c r="I46" t="n">
         <v>0</v>
       </c>
-      <c r="L46" t="n">
-        <v>1</v>
+      <c r="K46" t="n">
+        <v>1</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O46" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -3900,31 +3670,26 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>OnAcquire</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
           <t>TimelineExtraDay</t>
         </is>
       </c>
-      <c r="J47" t="n">
-        <v>1</v>
-      </c>
-      <c r="L47" t="n">
-        <v>1</v>
+      <c r="I47" t="n">
+        <v>1</v>
+      </c>
+      <c r="K47" t="n">
+        <v>1</v>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O47" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -3958,31 +3723,26 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>OnAcquire</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
           <t>TimelineWeekMinus</t>
         </is>
       </c>
-      <c r="J48" t="n">
-        <v>1</v>
-      </c>
-      <c r="L48" t="n">
-        <v>1</v>
+      <c r="I48" t="n">
+        <v>1</v>
+      </c>
+      <c r="K48" t="n">
+        <v>1</v>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -4016,31 +3776,26 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>OnAcquire</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
           <t>TimelineAddRewardNode</t>
         </is>
       </c>
-      <c r="J49" t="n">
-        <v>1</v>
-      </c>
-      <c r="L49" t="n">
-        <v>1</v>
+      <c r="I49" t="n">
+        <v>1</v>
+      </c>
+      <c r="K49" t="n">
+        <v>1</v>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -4074,31 +3829,26 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>OnAcquire</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
           <t>TimelineAddInterestNode</t>
         </is>
       </c>
-      <c r="J50" t="n">
-        <v>1</v>
-      </c>
-      <c r="L50" t="n">
-        <v>1</v>
+      <c r="I50" t="n">
+        <v>1</v>
+      </c>
+      <c r="K50" t="n">
+        <v>1</v>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O50" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -4132,36 +3882,31 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
           <t>EveryNthServeMult</t>
         </is>
       </c>
-      <c r="J51" t="n">
+      <c r="I51" t="n">
         <v>2</v>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t>every:3</t>
         </is>
       </c>
-      <c r="L51" t="n">
-        <v>1</v>
+      <c r="K51" t="n">
+        <v>1</v>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>20,65</t>
+        </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>20,65</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O51" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -4195,36 +3940,31 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
           <t>NthServeMult</t>
         </is>
       </c>
-      <c r="J52" t="n">
+      <c r="I52" t="n">
         <v>2</v>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t>index:1</t>
         </is>
       </c>
-      <c r="L52" t="n">
-        <v>1</v>
+      <c r="K52" t="n">
+        <v>1</v>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>5,45</t>
+        </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>5,45</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O52" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -4258,36 +3998,31 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
           <t>NthServeMult</t>
         </is>
       </c>
-      <c r="J53" t="n">
+      <c r="I53" t="n">
         <v>2</v>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t>index:-1</t>
         </is>
       </c>
-      <c r="L53" t="n">
-        <v>1</v>
+      <c r="K53" t="n">
+        <v>1</v>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>5,45</t>
+        </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>5,45</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O53" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -4321,31 +4056,26 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
           <t>ExtraActiveSlot</t>
         </is>
       </c>
-      <c r="J54" t="n">
+      <c r="I54" t="n">
         <v>2</v>
       </c>
-      <c r="L54" t="n">
-        <v>1</v>
+      <c r="K54" t="n">
+        <v>1</v>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>20,65</t>
+        </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>20,65</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O54" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -4379,31 +4109,26 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
           <t>GoldOnActiveUse</t>
         </is>
       </c>
-      <c r="J55" t="n">
+      <c r="I55" t="n">
         <v>20</v>
       </c>
-      <c r="L55" t="n">
-        <v>1</v>
+      <c r="K55" t="n">
+        <v>1</v>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>5,45</t>
+        </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>5,45</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O55" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -4437,31 +4162,26 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
           <t>BlockActive</t>
         </is>
       </c>
-      <c r="J56" t="n">
+      <c r="I56" t="n">
         <v>1000</v>
       </c>
-      <c r="L56" t="n">
-        <v>1</v>
+      <c r="K56" t="n">
+        <v>1</v>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>40,85</t>
+        </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>40,85</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O56" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -4495,31 +4215,26 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>OnAcquire</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
           <t>FlavorEnhance</t>
         </is>
       </c>
-      <c r="J57" t="n">
+      <c r="I57" t="n">
         <v>2</v>
       </c>
-      <c r="L57" t="n">
-        <v>1</v>
+      <c r="K57" t="n">
+        <v>1</v>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O57" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -4553,31 +4268,26 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>OnAcquire</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
           <t>FlavorRemoveForGold</t>
         </is>
       </c>
-      <c r="J58" t="n">
+      <c r="I58" t="n">
         <v>200</v>
       </c>
-      <c r="L58" t="n">
-        <v>1</v>
+      <c r="K58" t="n">
+        <v>1</v>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O58" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -4611,31 +4321,26 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>OnAcquire</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
           <t>FlavorRemoveCopySkill</t>
         </is>
       </c>
-      <c r="J59" t="n">
+      <c r="I59" t="n">
         <v>0</v>
       </c>
-      <c r="L59" t="n">
-        <v>1</v>
+      <c r="K59" t="n">
+        <v>1</v>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O59" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -4669,31 +4374,26 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>OnAcquire</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
           <t>FlavorRemoveDoubleScore</t>
         </is>
       </c>
-      <c r="J60" t="n">
+      <c r="I60" t="n">
         <v>2</v>
       </c>
-      <c r="L60" t="n">
-        <v>1</v>
+      <c r="K60" t="n">
+        <v>1</v>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O60" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -4727,31 +4427,26 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
           <t>FlavorDoubleSlot</t>
         </is>
       </c>
-      <c r="J61" t="n">
-        <v>1</v>
-      </c>
-      <c r="L61" t="n">
-        <v>1</v>
+      <c r="I61" t="n">
+        <v>1</v>
+      </c>
+      <c r="K61" t="n">
+        <v>1</v>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>40,85</t>
+        </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>40,85</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O61" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -4785,31 +4480,26 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>OnAcquire</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
           <t>FlavorContagion</t>
         </is>
       </c>
-      <c r="J62" t="n">
-        <v>1</v>
-      </c>
-      <c r="L62" t="n">
-        <v>1</v>
+      <c r="I62" t="n">
+        <v>1</v>
+      </c>
+      <c r="K62" t="n">
+        <v>1</v>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O62" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -4843,31 +4533,26 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>OnAcquire</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
           <t>CellTagEnhance</t>
         </is>
       </c>
-      <c r="J63" t="n">
+      <c r="I63" t="n">
         <v>2</v>
       </c>
-      <c r="L63" t="n">
-        <v>1</v>
+      <c r="K63" t="n">
+        <v>1</v>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O63" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -4901,31 +4586,26 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>OnAcquire</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
           <t>CellTagContagion</t>
         </is>
       </c>
-      <c r="J64" t="n">
-        <v>1</v>
-      </c>
-      <c r="L64" t="n">
-        <v>1</v>
+      <c r="I64" t="n">
+        <v>1</v>
+      </c>
+      <c r="K64" t="n">
+        <v>1</v>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O64" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -4959,31 +4639,26 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
           <t>LuckyEventGuarantee</t>
         </is>
       </c>
-      <c r="J65" t="n">
+      <c r="I65" t="n">
         <v>4</v>
       </c>
-      <c r="L65" t="n">
-        <v>1</v>
+      <c r="K65" t="n">
+        <v>1</v>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>20,65</t>
+        </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>20,65</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O65" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -5017,31 +4692,26 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
           <t>LuckyEventChance</t>
         </is>
       </c>
-      <c r="J66" t="n">
+      <c r="I66" t="n">
         <v>0.2</v>
       </c>
-      <c r="L66" t="n">
-        <v>1</v>
+      <c r="K66" t="n">
+        <v>1</v>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>5,45</t>
+        </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>5,45</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O66" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -5075,31 +4745,26 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
           <t>MoreEvents</t>
         </is>
       </c>
-      <c r="J67" t="n">
+      <c r="I67" t="n">
         <v>0.2</v>
       </c>
-      <c r="L67" t="n">
-        <v>1</v>
+      <c r="K67" t="n">
+        <v>1</v>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>5,45</t>
+        </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>5,45</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O67" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -5133,31 +4798,26 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
           <t>GoldOnEventComplete</t>
         </is>
       </c>
-      <c r="J68" t="n">
+      <c r="I68" t="n">
         <v>10</v>
       </c>
-      <c r="L68" t="n">
-        <v>1</v>
+      <c r="K68" t="n">
+        <v>1</v>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>1,30</t>
+        </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>1,30</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O68" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -5191,31 +4851,26 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>OnAcquire</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
           <t>RerollAction</t>
         </is>
       </c>
-      <c r="J69" t="n">
+      <c r="I69" t="n">
         <v>2</v>
       </c>
-      <c r="L69" t="n">
-        <v>1</v>
+      <c r="K69" t="n">
+        <v>1</v>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O69" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -5249,31 +4904,26 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
           <t>ShopRestock</t>
         </is>
       </c>
-      <c r="J70" t="n">
+      <c r="I70" t="n">
         <v>0</v>
       </c>
-      <c r="L70" t="n">
-        <v>1</v>
+      <c r="K70" t="n">
+        <v>1</v>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>20,65</t>
+        </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>20,65</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O70" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -5307,31 +4957,26 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
           <t>ChoiceCountBonus</t>
         </is>
       </c>
-      <c r="J71" t="n">
-        <v>1</v>
-      </c>
-      <c r="L71" t="n">
-        <v>1</v>
+      <c r="I71" t="n">
+        <v>1</v>
+      </c>
+      <c r="K71" t="n">
+        <v>1</v>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>5,45</t>
+        </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>5,45</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O71" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -5365,31 +5010,26 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
           <t>ChoiceTimesBonus</t>
         </is>
       </c>
-      <c r="J72" t="n">
-        <v>1</v>
-      </c>
-      <c r="L72" t="n">
-        <v>1</v>
+      <c r="I72" t="n">
+        <v>1</v>
+      </c>
+      <c r="K72" t="n">
+        <v>1</v>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>20,65</t>
+        </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>20,65</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O72" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -5423,36 +5063,31 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
           <t>ExtraFoodChoice</t>
         </is>
       </c>
-      <c r="J73" t="n">
+      <c r="I73" t="n">
         <v>0</v>
       </c>
-      <c r="K73" t="inlineStr">
+      <c r="J73" t="inlineStr">
         <is>
           <t>every:3</t>
         </is>
       </c>
-      <c r="L73" t="n">
-        <v>1</v>
+      <c r="K73" t="n">
+        <v>1</v>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>20,65</t>
+        </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>20,65</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O73" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -5486,36 +5121,31 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
           <t>ExtraItemChoice</t>
         </is>
       </c>
-      <c r="J74" t="n">
+      <c r="I74" t="n">
         <v>0</v>
       </c>
-      <c r="K74" t="inlineStr">
+      <c r="J74" t="inlineStr">
         <is>
           <t>every:3</t>
         </is>
       </c>
-      <c r="L74" t="n">
-        <v>1</v>
+      <c r="K74" t="n">
+        <v>1</v>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>20,65</t>
+        </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>20,65</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O74" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -5549,31 +5179,26 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>OnAcquire</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
           <t>CopyFood</t>
         </is>
       </c>
-      <c r="J75" t="n">
-        <v>1</v>
-      </c>
-      <c r="L75" t="n">
-        <v>1</v>
+      <c r="I75" t="n">
+        <v>1</v>
+      </c>
+      <c r="K75" t="n">
+        <v>1</v>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O75" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -5607,31 +5232,26 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>OnAcquire</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
           <t>DiscardNegative</t>
         </is>
       </c>
-      <c r="J76" t="n">
+      <c r="I76" t="n">
         <v>2</v>
       </c>
-      <c r="L76" t="n">
-        <v>1</v>
+      <c r="K76" t="n">
+        <v>1</v>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O76" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -5665,31 +5285,26 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>OnAcquire</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
           <t>DiscardNegativeForGold</t>
         </is>
       </c>
-      <c r="J77" t="n">
+      <c r="I77" t="n">
         <v>100</v>
       </c>
-      <c r="L77" t="n">
-        <v>1</v>
+      <c r="K77" t="n">
+        <v>1</v>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O77" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -5728,31 +5343,26 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
           <t>GoldMealPercent</t>
         </is>
       </c>
-      <c r="J78" t="n">
+      <c r="I78" t="n">
         <v>-0.25</v>
       </c>
-      <c r="L78" t="n">
-        <v>1</v>
+      <c r="K78" t="n">
+        <v>1</v>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>1,30</t>
+        </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>1,30</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O78" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -5791,31 +5401,26 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
           <t>ShopPriceUp</t>
         </is>
       </c>
-      <c r="J79" t="n">
+      <c r="I79" t="n">
         <v>0.25</v>
       </c>
-      <c r="L79" t="n">
-        <v>1</v>
+      <c r="K79" t="n">
+        <v>1</v>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>1,30</t>
+        </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>1,30</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O79" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -5854,31 +5459,26 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
           <t>NoRemoveDish</t>
         </is>
       </c>
-      <c r="J80" t="n">
+      <c r="I80" t="n">
         <v>0</v>
       </c>
-      <c r="L80" t="n">
-        <v>1</v>
+      <c r="K80" t="n">
+        <v>1</v>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>1,30</t>
+        </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>1,30</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O80" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -5917,31 +5517,26 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
           <t>TimelineSkipNode</t>
         </is>
       </c>
-      <c r="J81" t="n">
-        <v>1</v>
-      </c>
-      <c r="L81" t="n">
-        <v>1</v>
+      <c r="I81" t="n">
+        <v>1</v>
+      </c>
+      <c r="K81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>1,30</t>
+        </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>1,30</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O81" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -5980,31 +5575,26 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
           <t>ChoiceCountPenalty</t>
         </is>
       </c>
-      <c r="J82" t="n">
+      <c r="I82" t="n">
         <v>-1</v>
       </c>
-      <c r="L82" t="n">
-        <v>1</v>
+      <c r="K82" t="n">
+        <v>1</v>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>1,30</t>
+        </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>1,30</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O82" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -6043,31 +5633,26 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
           <t>RequiredScoreNormalPct</t>
         </is>
       </c>
-      <c r="J83" t="n">
+      <c r="I83" t="n">
         <v>0.1</v>
       </c>
-      <c r="L83" t="n">
-        <v>1</v>
+      <c r="K83" t="n">
+        <v>1</v>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>1,30</t>
+        </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>1,30</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O83" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -6106,31 +5691,26 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
           <t>RequiredScoreSuperPct</t>
         </is>
       </c>
-      <c r="J84" t="n">
+      <c r="I84" t="n">
         <v>0.1</v>
       </c>
-      <c r="L84" t="n">
-        <v>1</v>
+      <c r="K84" t="n">
+        <v>1</v>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>1,30</t>
+        </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>1,30</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O84" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -6169,31 +5749,26 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
           <t>RequiredScoreFeastPct</t>
         </is>
       </c>
-      <c r="J85" t="n">
+      <c r="I85" t="n">
         <v>0.1</v>
       </c>
-      <c r="L85" t="n">
-        <v>1</v>
+      <c r="K85" t="n">
+        <v>1</v>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>1,30</t>
+        </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>1,30</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O85" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -6232,31 +5807,26 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
           <t>GoldWeekClear</t>
         </is>
       </c>
-      <c r="J86" t="n">
+      <c r="I86" t="n">
         <v>0</v>
       </c>
-      <c r="L86" t="n">
-        <v>1</v>
+      <c r="K86" t="n">
+        <v>1</v>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>1,30</t>
+        </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>1,30</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O86" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -6290,31 +5860,26 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
           <t>CountAsBonusAll</t>
         </is>
       </c>
-      <c r="J87" t="n">
-        <v>1</v>
-      </c>
-      <c r="L87" t="n">
-        <v>1</v>
+      <c r="I87" t="n">
+        <v>1</v>
+      </c>
+      <c r="K87" t="n">
+        <v>1</v>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>20,65</t>
+        </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>20,65</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O87" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -6348,31 +5913,26 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
           <t>TransferTargetMult</t>
         </is>
       </c>
-      <c r="J88" t="n">
+      <c r="I88" t="n">
         <v>1.1</v>
       </c>
-      <c r="L88" t="n">
-        <v>1</v>
+      <c r="K88" t="n">
+        <v>1</v>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>20,65</t>
+        </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>20,65</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O88" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -6406,31 +5966,26 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
           <t>TransferSourceMult</t>
         </is>
       </c>
-      <c r="J89" t="n">
+      <c r="I89" t="n">
         <v>1.1</v>
       </c>
-      <c r="L89" t="n">
-        <v>1</v>
+      <c r="K89" t="n">
+        <v>1</v>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>20,65</t>
+        </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>20,65</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O89" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -6464,31 +6019,26 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
           <t>PerSkillMultFlat</t>
         </is>
       </c>
-      <c r="J90" t="n">
+      <c r="I90" t="n">
         <v>0.1</v>
       </c>
-      <c r="L90" t="n">
-        <v>1</v>
+      <c r="K90" t="n">
+        <v>1</v>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>20,65</t>
+        </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>20,65</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O90" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -6522,36 +6072,31 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
           <t>GoldOnTransferCount</t>
         </is>
       </c>
-      <c r="J91" t="n">
+      <c r="I91" t="n">
         <v>10</v>
       </c>
-      <c r="K91" t="inlineStr">
+      <c r="J91" t="inlineStr">
         <is>
           <t>count:10</t>
         </is>
       </c>
-      <c r="L91" t="n">
-        <v>1</v>
+      <c r="K91" t="n">
+        <v>1</v>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>5,45</t>
+        </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>5,45</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O91" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -6585,31 +6130,26 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
           <t>CakeLayerRetain</t>
         </is>
       </c>
-      <c r="J92" t="n">
+      <c r="I92" t="n">
         <v>0.1</v>
       </c>
-      <c r="L92" t="n">
-        <v>1</v>
+      <c r="K92" t="n">
+        <v>1</v>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>20,65</t>
+        </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>20,65</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O92" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -6643,31 +6183,26 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
           <t>CakeLayerInitBonus</t>
         </is>
       </c>
-      <c r="J93" t="n">
+      <c r="I93" t="n">
         <v>10</v>
       </c>
-      <c r="L93" t="n">
-        <v>1</v>
+      <c r="K93" t="n">
+        <v>1</v>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>5,45</t>
+        </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>5,45</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O93" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -6701,31 +6236,26 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
           <t>CakeLayerAccel</t>
         </is>
       </c>
-      <c r="J94" t="n">
-        <v>1</v>
-      </c>
-      <c r="L94" t="n">
-        <v>1</v>
+      <c r="I94" t="n">
+        <v>1</v>
+      </c>
+      <c r="K94" t="n">
+        <v>1</v>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>20,65</t>
+        </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>20,65</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O94" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -6759,36 +6289,31 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
           <t>GoldOnCakeLayers</t>
         </is>
       </c>
-      <c r="J95" t="n">
+      <c r="I95" t="n">
         <v>10</v>
       </c>
-      <c r="K95" t="inlineStr">
+      <c r="J95" t="inlineStr">
         <is>
           <t>threshold:100</t>
         </is>
       </c>
-      <c r="L95" t="n">
-        <v>1</v>
+      <c r="K95" t="n">
+        <v>1</v>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>5,45</t>
+        </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>5,45</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O95" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -6822,31 +6347,26 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
           <t>CakeLayerReqMinus</t>
         </is>
       </c>
-      <c r="J96" t="n">
+      <c r="I96" t="n">
         <v>10</v>
       </c>
-      <c r="L96" t="n">
-        <v>1</v>
+      <c r="K96" t="n">
+        <v>1</v>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>5,45</t>
+        </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>5,45</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O96" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/GourmetProject/GameConfig/Datas/item.xlsx
+++ b/GourmetProject/GameConfig/Datas/item.xlsx
@@ -12,8 +12,8 @@
     <sheet name="道具设计" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">被动道具!$A$1:$M$96</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">主动道具!$A$1:$L$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">主动道具!$A$1:$K$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">被动道具!$A$1:$K$96</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -5540,9 +5540,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:M96" etc:filterBottomFollowUsedRange="0">
-    <extLst/>
-  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -5682,9 +5679,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L3" etc:filterBottomFollowUsedRange="0">
-    <extLst/>
-  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>

--- a/GourmetProject/GameConfig/Datas/item.xlsx
+++ b/GourmetProject/GameConfig/Datas/item.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16760" activeTab="1"/>
+    <workbookView windowHeight="16760"/>
   </bookViews>
   <sheets>
     <sheet name="被动道具" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="929" uniqueCount="613">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="929" uniqueCount="612">
   <si>
     <t>##var</t>
   </si>
@@ -535,7 +535,7 @@
     <t>命运骰子</t>
   </si>
   <si>
-    <t>随机化事件轴的节点时间。</t>
+    <t>随机化时间轴的节点事件。</t>
   </si>
   <si>
     <t>item_extra_day</t>
@@ -649,7 +649,7 @@
     <t>风味喷雾</t>
   </si>
   <si>
-    <t>强化两个随机风味到无风味食物上。</t>
+    <t>给两个无风味的食物添加随机风味。</t>
   </si>
   <si>
     <t>item_flavor_remove_gold</t>
@@ -1547,9 +1547,6 @@
   </si>
   <si>
     <t>时间轴</t>
-  </si>
-  <si>
-    <t>随机化事件轴的节点时间</t>
   </si>
   <si>
     <t>增加第八天</t>
@@ -6786,24 +6783,24 @@
         <v>431</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>506</v>
+        <v>168</v>
       </c>
       <c r="H44" s="1">
         <v>43</v>
       </c>
       <c r="I44" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>随机化事件轴的节点时间</v>
+        <v>随机化时间轴的节点事件。</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="2:9">
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
       <c r="D45" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="E45" s="3" t="s">
         <v>507</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>508</v>
       </c>
       <c r="H45" s="1">
         <v>44</v>
@@ -6817,10 +6814,10 @@
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
       <c r="D46" s="3" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H46" s="1">
         <v>45</v>
@@ -6834,10 +6831,10 @@
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
       <c r="D47" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="E47" s="3" t="s">
         <v>510</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>511</v>
       </c>
       <c r="H47" s="1">
         <v>46</v>
@@ -6851,10 +6848,10 @@
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
       <c r="D48" s="3" t="s">
+        <v>511</v>
+      </c>
+      <c r="E48" s="3" t="s">
         <v>512</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>513</v>
       </c>
       <c r="H48" s="1">
         <v>47</v>
@@ -6867,13 +6864,13 @@
     <row r="49" customHeight="1" spans="2:9">
       <c r="B49" s="4"/>
       <c r="C49" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="D49" s="3" t="s">
         <v>514</v>
       </c>
-      <c r="D49" s="3" t="s">
+      <c r="E49" s="5" t="s">
         <v>515</v>
-      </c>
-      <c r="E49" s="5" t="s">
-        <v>516</v>
       </c>
       <c r="H49" s="1">
         <v>48</v>
@@ -6887,10 +6884,10 @@
       <c r="B50" s="4"/>
       <c r="C50" s="4"/>
       <c r="D50" s="3" t="s">
+        <v>516</v>
+      </c>
+      <c r="E50" s="5" t="s">
         <v>517</v>
-      </c>
-      <c r="E50" s="5" t="s">
-        <v>518</v>
       </c>
       <c r="H50" s="1">
         <v>49</v>
@@ -6904,10 +6901,10 @@
       <c r="B51" s="4"/>
       <c r="C51" s="4"/>
       <c r="D51" s="3" t="s">
+        <v>518</v>
+      </c>
+      <c r="E51" s="3" t="s">
         <v>519</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>520</v>
       </c>
       <c r="H51" s="1">
         <v>50</v>
@@ -6920,13 +6917,13 @@
     <row r="52" customHeight="1" spans="2:9">
       <c r="B52" s="4"/>
       <c r="C52" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="D52" s="3" t="s">
         <v>521</v>
       </c>
-      <c r="D52" s="3" t="s">
+      <c r="E52" s="3" t="s">
         <v>522</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>523</v>
       </c>
       <c r="H52" s="1">
         <v>51</v>
@@ -6943,7 +6940,7 @@
         <v>433</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H53" s="1">
         <v>52</v>
@@ -6957,10 +6954,10 @@
       <c r="B54" s="4"/>
       <c r="C54" s="4"/>
       <c r="D54" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="E54" s="5" t="s">
         <v>525</v>
-      </c>
-      <c r="E54" s="5" t="s">
-        <v>526</v>
       </c>
       <c r="H54" s="1">
         <v>53</v>
@@ -6973,13 +6970,13 @@
     <row r="55" customHeight="1" spans="2:9">
       <c r="B55" s="4"/>
       <c r="C55" s="3" t="s">
+        <v>526</v>
+      </c>
+      <c r="D55" s="3" t="s">
         <v>527</v>
       </c>
-      <c r="D55" s="3" t="s">
+      <c r="E55" s="3" t="s">
         <v>528</v>
-      </c>
-      <c r="E55" s="3" t="s">
-        <v>529</v>
       </c>
       <c r="H55" s="1">
         <v>54</v>
@@ -6993,10 +6990,10 @@
       <c r="B56" s="4"/>
       <c r="C56" s="4"/>
       <c r="D56" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="E56" s="5" t="s">
         <v>530</v>
-      </c>
-      <c r="E56" s="5" t="s">
-        <v>531</v>
       </c>
       <c r="H56" s="1">
         <v>55</v>
@@ -7010,10 +7007,10 @@
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
       <c r="D57" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="E57" s="3" t="s">
         <v>532</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>533</v>
       </c>
       <c r="H57" s="1">
         <v>56</v>
@@ -7027,10 +7024,10 @@
       <c r="B58" s="4"/>
       <c r="C58" s="4"/>
       <c r="D58" s="3" t="s">
+        <v>533</v>
+      </c>
+      <c r="E58" s="3" t="s">
         <v>534</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>535</v>
       </c>
       <c r="H58" s="1">
         <v>57</v>
@@ -7044,10 +7041,10 @@
       <c r="B59" s="4"/>
       <c r="C59" s="4"/>
       <c r="D59" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="E59" s="3" t="s">
         <v>536</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>537</v>
       </c>
       <c r="H59" s="1">
         <v>58</v>
@@ -7064,7 +7061,7 @@
         <v>220</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H60" s="1">
         <v>59</v>
@@ -7077,13 +7074,13 @@
     <row r="61" customHeight="1" spans="2:9">
       <c r="B61" s="4"/>
       <c r="C61" s="3" t="s">
+        <v>538</v>
+      </c>
+      <c r="D61" s="3" t="s">
         <v>539</v>
       </c>
-      <c r="D61" s="3" t="s">
+      <c r="E61" s="3" t="s">
         <v>540</v>
-      </c>
-      <c r="E61" s="3" t="s">
-        <v>541</v>
       </c>
       <c r="H61" s="1">
         <v>60</v>
@@ -7100,7 +7097,7 @@
         <v>226</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H62" s="1">
         <v>61</v>
@@ -7113,13 +7110,13 @@
     <row r="63" customHeight="1" spans="2:9">
       <c r="B63" s="4"/>
       <c r="C63" s="3" t="s">
+        <v>542</v>
+      </c>
+      <c r="D63" s="3" t="s">
         <v>543</v>
       </c>
-      <c r="D63" s="3" t="s">
+      <c r="E63" s="3" t="s">
         <v>544</v>
-      </c>
-      <c r="E63" s="3" t="s">
-        <v>545</v>
       </c>
       <c r="H63" s="1">
         <v>62</v>
@@ -7133,10 +7130,10 @@
       <c r="B64" s="4"/>
       <c r="C64" s="4"/>
       <c r="D64" s="3" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H64" s="1">
         <v>63</v>
@@ -7150,10 +7147,10 @@
       <c r="B65" s="4"/>
       <c r="C65" s="4"/>
       <c r="D65" s="3" t="s">
+        <v>546</v>
+      </c>
+      <c r="E65" s="3" t="s">
         <v>547</v>
-      </c>
-      <c r="E65" s="3" t="s">
-        <v>548</v>
       </c>
       <c r="H65" s="1">
         <v>64</v>
@@ -7167,10 +7164,10 @@
       <c r="B66" s="4"/>
       <c r="C66" s="4"/>
       <c r="D66" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="E66" s="3" t="s">
         <v>549</v>
-      </c>
-      <c r="E66" s="3" t="s">
-        <v>550</v>
       </c>
       <c r="H66" s="1">
         <v>65</v>
@@ -7184,10 +7181,10 @@
       <c r="B67" s="4"/>
       <c r="C67" s="4"/>
       <c r="D67" s="3" t="s">
+        <v>550</v>
+      </c>
+      <c r="E67" s="3" t="s">
         <v>551</v>
-      </c>
-      <c r="E67" s="3" t="s">
-        <v>552</v>
       </c>
       <c r="H67" s="1">
         <v>66</v>
@@ -7200,13 +7197,13 @@
     <row r="68" customHeight="1" spans="2:9">
       <c r="B68" s="4"/>
       <c r="C68" s="3" t="s">
+        <v>552</v>
+      </c>
+      <c r="D68" s="3" t="s">
         <v>553</v>
       </c>
-      <c r="D68" s="3" t="s">
+      <c r="E68" s="3" t="s">
         <v>554</v>
-      </c>
-      <c r="E68" s="3" t="s">
-        <v>555</v>
       </c>
       <c r="H68" s="1">
         <v>67</v>
@@ -7219,13 +7216,13 @@
     <row r="69" customHeight="1" spans="2:9">
       <c r="B69" s="4"/>
       <c r="C69" s="3" t="s">
+        <v>555</v>
+      </c>
+      <c r="D69" s="3" t="s">
         <v>556</v>
       </c>
-      <c r="D69" s="3" t="s">
+      <c r="E69" s="3" t="s">
         <v>557</v>
-      </c>
-      <c r="E69" s="3" t="s">
-        <v>558</v>
       </c>
       <c r="H69" s="1">
         <v>68</v>
@@ -7239,10 +7236,10 @@
       <c r="B70" s="4"/>
       <c r="C70" s="4"/>
       <c r="D70" s="3" t="s">
+        <v>558</v>
+      </c>
+      <c r="E70" s="3" t="s">
         <v>559</v>
-      </c>
-      <c r="E70" s="3" t="s">
-        <v>560</v>
       </c>
       <c r="H70" s="1">
         <v>69</v>
@@ -7256,10 +7253,10 @@
       <c r="B71" s="4"/>
       <c r="C71" s="4"/>
       <c r="D71" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="E71" s="5" t="s">
         <v>561</v>
-      </c>
-      <c r="E71" s="5" t="s">
-        <v>562</v>
       </c>
       <c r="H71" s="1">
         <v>70</v>
@@ -7273,10 +7270,10 @@
       <c r="B72" s="4"/>
       <c r="C72" s="4"/>
       <c r="D72" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="E72" s="5" t="s">
         <v>563</v>
-      </c>
-      <c r="E72" s="5" t="s">
-        <v>564</v>
       </c>
       <c r="H72" s="1">
         <v>71</v>
@@ -7293,7 +7290,7 @@
         <v>259</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H73" s="1">
         <v>72</v>
@@ -7306,13 +7303,13 @@
     <row r="74" customHeight="1" spans="2:9">
       <c r="B74" s="4"/>
       <c r="C74" s="3" t="s">
+        <v>565</v>
+      </c>
+      <c r="D74" s="3" t="s">
         <v>566</v>
       </c>
-      <c r="D74" s="3" t="s">
+      <c r="E74" s="3" t="s">
         <v>567</v>
-      </c>
-      <c r="E74" s="3" t="s">
-        <v>568</v>
       </c>
       <c r="H74" s="1">
         <v>73</v>
@@ -7326,10 +7323,10 @@
       <c r="B75" s="4"/>
       <c r="C75" s="3"/>
       <c r="D75" s="3" t="s">
+        <v>568</v>
+      </c>
+      <c r="E75" s="3" t="s">
         <v>569</v>
-      </c>
-      <c r="E75" s="3" t="s">
-        <v>570</v>
       </c>
       <c r="H75" s="1">
         <v>74</v>
@@ -7341,16 +7338,16 @@
     </row>
     <row r="76" customHeight="1" spans="2:9">
       <c r="B76" s="3" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C76" s="3" t="s">
         <v>492</v>
       </c>
       <c r="D76" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="E76" s="3" t="s">
         <v>572</v>
-      </c>
-      <c r="E76" s="3" t="s">
-        <v>573</v>
       </c>
       <c r="H76" s="1">
         <v>75</v>
@@ -7364,10 +7361,10 @@
       <c r="B77" s="4"/>
       <c r="C77" s="4"/>
       <c r="D77" s="3" t="s">
+        <v>573</v>
+      </c>
+      <c r="E77" s="3" t="s">
         <v>574</v>
-      </c>
-      <c r="E77" s="3" t="s">
-        <v>575</v>
       </c>
       <c r="H77" s="1">
         <v>76</v>
@@ -7381,10 +7378,10 @@
       <c r="B78" s="4"/>
       <c r="C78" s="4"/>
       <c r="D78" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="E78" s="3" t="s">
         <v>576</v>
-      </c>
-      <c r="E78" s="3" t="s">
-        <v>577</v>
       </c>
       <c r="H78" s="1">
         <v>77</v>
@@ -7398,10 +7395,10 @@
       <c r="B79" s="4"/>
       <c r="C79" s="4"/>
       <c r="D79" s="3" t="s">
+        <v>577</v>
+      </c>
+      <c r="E79" s="3" t="s">
         <v>578</v>
-      </c>
-      <c r="E79" s="3" t="s">
-        <v>579</v>
       </c>
       <c r="H79" s="1">
         <v>78</v>
@@ -7415,10 +7412,10 @@
       <c r="B80" s="4"/>
       <c r="C80" s="4"/>
       <c r="D80" s="3" t="s">
+        <v>579</v>
+      </c>
+      <c r="E80" s="3" t="s">
         <v>580</v>
-      </c>
-      <c r="E80" s="3" t="s">
-        <v>581</v>
       </c>
       <c r="H80" s="1">
         <v>79</v>
@@ -7432,10 +7429,10 @@
       <c r="B81" s="4"/>
       <c r="C81" s="4"/>
       <c r="D81" s="5" t="s">
+        <v>581</v>
+      </c>
+      <c r="E81" s="5" t="s">
         <v>582</v>
-      </c>
-      <c r="E81" s="5" t="s">
-        <v>583</v>
       </c>
       <c r="H81" s="1">
         <v>80</v>
@@ -7449,10 +7446,10 @@
       <c r="B82" s="4"/>
       <c r="C82" s="4"/>
       <c r="D82" s="5" t="s">
+        <v>583</v>
+      </c>
+      <c r="E82" s="5" t="s">
         <v>584</v>
-      </c>
-      <c r="E82" s="5" t="s">
-        <v>585</v>
       </c>
       <c r="H82" s="1">
         <v>81</v>
@@ -7466,10 +7463,10 @@
       <c r="B83" s="4"/>
       <c r="C83" s="4"/>
       <c r="D83" s="5" t="s">
+        <v>585</v>
+      </c>
+      <c r="E83" s="5" t="s">
         <v>586</v>
-      </c>
-      <c r="E83" s="5" t="s">
-        <v>587</v>
       </c>
       <c r="H83" s="1">
         <v>82</v>
@@ -7483,10 +7480,10 @@
       <c r="B84" s="4"/>
       <c r="C84" s="4"/>
       <c r="D84" s="3" t="s">
+        <v>587</v>
+      </c>
+      <c r="E84" s="3" t="s">
         <v>588</v>
-      </c>
-      <c r="E84" s="3" t="s">
-        <v>589</v>
       </c>
       <c r="H84" s="1">
         <v>83</v>
@@ -7498,16 +7495,16 @@
     </row>
     <row r="85" customHeight="1" spans="2:9">
       <c r="B85" s="3" t="s">
+        <v>589</v>
+      </c>
+      <c r="C85" s="3" t="s">
         <v>590</v>
       </c>
-      <c r="C85" s="3" t="s">
+      <c r="D85" s="3" t="s">
         <v>591</v>
       </c>
-      <c r="D85" s="3" t="s">
+      <c r="E85" s="3" t="s">
         <v>592</v>
-      </c>
-      <c r="E85" s="3" t="s">
-        <v>593</v>
       </c>
       <c r="H85" s="1">
         <v>84</v>
@@ -7520,13 +7517,13 @@
     <row r="86" customHeight="1" spans="2:9">
       <c r="B86" s="4"/>
       <c r="C86" s="3" t="s">
+        <v>593</v>
+      </c>
+      <c r="D86" s="3" t="s">
         <v>594</v>
       </c>
-      <c r="D86" s="3" t="s">
+      <c r="E86" s="5" t="s">
         <v>595</v>
-      </c>
-      <c r="E86" s="5" t="s">
-        <v>596</v>
       </c>
       <c r="H86" s="1">
         <v>85</v>
@@ -7540,10 +7537,10 @@
       <c r="B87" s="4"/>
       <c r="C87" s="4"/>
       <c r="D87" s="3" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="H87" s="1">
         <v>86</v>
@@ -7557,10 +7554,10 @@
       <c r="B88" s="4"/>
       <c r="C88" s="4"/>
       <c r="D88" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="E88" s="5" t="s">
         <v>598</v>
-      </c>
-      <c r="E88" s="5" t="s">
-        <v>599</v>
       </c>
       <c r="H88" s="1">
         <v>87</v>
@@ -7574,10 +7571,10 @@
       <c r="B89" s="4"/>
       <c r="C89" s="4"/>
       <c r="D89" s="3" t="s">
+        <v>599</v>
+      </c>
+      <c r="E89" s="3" t="s">
         <v>600</v>
-      </c>
-      <c r="E89" s="3" t="s">
-        <v>601</v>
       </c>
       <c r="H89" s="1">
         <v>88</v>
@@ -7589,13 +7586,13 @@
     </row>
     <row r="90" customHeight="1" spans="3:9">
       <c r="C90" s="3" t="s">
+        <v>601</v>
+      </c>
+      <c r="D90" s="3" t="s">
         <v>602</v>
       </c>
-      <c r="D90" s="3" t="s">
+      <c r="E90" s="5" t="s">
         <v>603</v>
-      </c>
-      <c r="E90" s="5" t="s">
-        <v>604</v>
       </c>
       <c r="H90" s="1">
         <v>89</v>
@@ -7609,10 +7606,10 @@
       <c r="B91" s="4"/>
       <c r="C91" s="4"/>
       <c r="D91" s="3" t="s">
+        <v>604</v>
+      </c>
+      <c r="E91" s="5" t="s">
         <v>605</v>
-      </c>
-      <c r="E91" s="5" t="s">
-        <v>606</v>
       </c>
       <c r="H91" s="1">
         <v>90</v>
@@ -7626,10 +7623,10 @@
       <c r="B92" s="4"/>
       <c r="C92" s="4"/>
       <c r="D92" s="3" t="s">
+        <v>606</v>
+      </c>
+      <c r="E92" s="3" t="s">
         <v>607</v>
-      </c>
-      <c r="E92" s="3" t="s">
-        <v>608</v>
       </c>
       <c r="H92" s="1">
         <v>91</v>
@@ -7643,10 +7640,10 @@
       <c r="B93" s="4"/>
       <c r="C93" s="4"/>
       <c r="D93" s="3" t="s">
+        <v>608</v>
+      </c>
+      <c r="E93" s="5" t="s">
         <v>609</v>
-      </c>
-      <c r="E93" s="5" t="s">
-        <v>610</v>
       </c>
       <c r="H93" s="1">
         <v>92</v>
@@ -7660,10 +7657,10 @@
       <c r="B94" s="4"/>
       <c r="C94" s="4"/>
       <c r="D94" s="3" t="s">
+        <v>610</v>
+      </c>
+      <c r="E94" s="5" t="s">
         <v>611</v>
-      </c>
-      <c r="E94" s="5" t="s">
-        <v>612</v>
       </c>
       <c r="H94" s="1">
         <v>93</v>

--- a/GourmetProject/GameConfig/Datas/item.xlsx
+++ b/GourmetProject/GameConfig/Datas/item.xlsx
@@ -2881,2330 +2881,5280 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr/>
-  <dimension ref="A1:J96"/>
+  <dimension ref="A1:P96"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
-  <cols>
-    <col min="1" max="1" width="13.0769230769231" customWidth="1"/>
-    <col min="2" max="2" width="30.3846153846154" customWidth="1"/>
-    <col min="3" max="3" width="15.1538461538462" customWidth="1"/>
-    <col min="4" max="4" width="50" customWidth="1"/>
-    <col min="5" max="5" width="12.8461538461538" customWidth="1"/>
-    <col min="6" max="6" width="15.1538461538462" customWidth="1"/>
-    <col min="7" max="7" width="11.9230769230769" customWidth="1"/>
-    <col min="8" max="8" width="13.7692307692308" customWidth="1"/>
-    <col min="9" max="9" width="15.1538461538462" customWidth="1"/>
-    <col min="10" max="10" width="36" customWidth="1"/>
-    <col min="11" max="11" width="73.7692307692308" customWidth="1"/>
-    <col min="12" max="12" width="36" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I2" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="2:10">
-      <c r="B4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E4" t="s">
-        <v>28</v>
-      </c>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>desc</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>quality</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>specialTags</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>effectValue</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>effectParam</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>baseWeight</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>hiddenRange</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>targetScoreHiddenOffset</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>dishHiddenOffset</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>passiveItemHiddenOffset</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>activeItemHiddenOffset</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>fragmentHiddenOffset</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>goldHiddenOffset</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>##comment</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>道具ID</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>道具名称</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>道具描述</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>道具品质</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>特殊标签标记</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>效果数值</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>效果参数</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>随机基础权重</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>出现隐藏分区间(单元格: min,max)</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>目标分隐藏分常驻修正。</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>食物奖励隐藏分常驻修正。</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>被动道具奖励隐藏分常驻修正。</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>主动道具奖励隐藏分常驻修正。</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>餐桌格子奖励隐藏分常驻修正。</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>金币奖励隐藏分常驻修正。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>ItemQuality</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>HiddenRange</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>item_grant_two_passive</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>随机被动包</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>获得两个随机被动道具。</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F4"/>
       <c r="G4">
         <v>2</v>
       </c>
+      <c r="H4"/>
       <c r="I4">
         <v>1</v>
       </c>
-      <c r="J4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="2:10">
-      <c r="B5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E5" t="s">
-        <v>28</v>
-      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>item_choose_one_passive</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>被动三选一</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>从多个被动道具中选择一个获得。</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F5"/>
       <c r="G5">
         <v>3</v>
       </c>
+      <c r="H5"/>
       <c r="I5">
         <v>1</v>
       </c>
-      <c r="J5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="6" spans="2:10">
-      <c r="B6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C6" t="s">
-        <v>34</v>
-      </c>
-      <c r="D6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E6" t="s">
-        <v>28</v>
-      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>item_grant_two_active</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>随机主动包</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>获得两个随机主动道具。</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F6"/>
       <c r="G6">
         <v>2</v>
       </c>
+      <c r="H6"/>
       <c r="I6">
         <v>1</v>
       </c>
-      <c r="J6" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="7" spans="2:10">
-      <c r="B7" t="s">
-        <v>36</v>
-      </c>
-      <c r="C7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D7" t="s">
-        <v>38</v>
-      </c>
-      <c r="E7" t="s">
-        <v>28</v>
-      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>item_choose_one_active</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>主动三选一</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>从多个主动道具中选择一个获得。</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F7"/>
       <c r="G7">
         <v>3</v>
       </c>
+      <c r="H7"/>
       <c r="I7">
         <v>1</v>
       </c>
-      <c r="J7" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="8" spans="2:10">
-      <c r="B8" t="s">
-        <v>39</v>
-      </c>
-      <c r="C8" t="s">
-        <v>40</v>
-      </c>
-      <c r="D8" t="s">
-        <v>41</v>
-      </c>
-      <c r="E8" t="s">
-        <v>42</v>
-      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>item_choose_one_food</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>食物三选一</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>从多个食物中选择一个获得。</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="F8"/>
       <c r="G8">
         <v>3</v>
       </c>
+      <c r="H8"/>
       <c r="I8">
         <v>1</v>
       </c>
-      <c r="J8" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="9" spans="2:10">
-      <c r="B9" t="s">
-        <v>43</v>
-      </c>
-      <c r="C9" t="s">
-        <v>44</v>
-      </c>
-      <c r="D9" t="s">
-        <v>45</v>
-      </c>
-      <c r="E9" t="s">
-        <v>28</v>
-      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>item_choose_one_fragment</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>碎片三选一</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>从多个胃部碎片中选择一个获得。</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F9"/>
       <c r="G9">
         <v>3</v>
       </c>
+      <c r="H9"/>
       <c r="I9">
         <v>1</v>
       </c>
-      <c r="J9" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="10" spans="2:10">
-      <c r="B10" t="s">
-        <v>46</v>
-      </c>
-      <c r="C10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D10" t="s">
-        <v>48</v>
-      </c>
-      <c r="E10" t="s">
-        <v>28</v>
-      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>item_grant_recipe</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>菜谱券</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>获得一个菜谱。</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F10"/>
       <c r="G10">
         <v>1</v>
       </c>
+      <c r="H10"/>
       <c r="I10">
         <v>1</v>
       </c>
-      <c r="J10" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="11" spans="2:10">
-      <c r="B11" t="s">
-        <v>49</v>
-      </c>
-      <c r="C11" t="s">
-        <v>50</v>
-      </c>
-      <c r="D11" t="s">
-        <v>51</v>
-      </c>
-      <c r="E11" t="s">
-        <v>52</v>
-      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>item_family_pack</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>全家福</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>获得一个随机被动道具、随机食物、50金币。</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F11"/>
       <c r="G11">
         <v>50</v>
       </c>
+      <c r="H11"/>
       <c r="I11">
         <v>1</v>
       </c>
-      <c r="J11" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="12" spans="2:10">
-      <c r="B12" t="s">
-        <v>53</v>
-      </c>
-      <c r="C12" t="s">
-        <v>54</v>
-      </c>
-      <c r="D12" t="s">
-        <v>55</v>
-      </c>
-      <c r="E12" t="s">
-        <v>52</v>
-      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>item_randomize_items</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>混沌重置</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>所有道具替换为随机道具。</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F12"/>
       <c r="G12">
         <v>0</v>
       </c>
+      <c r="H12"/>
       <c r="I12">
         <v>1</v>
       </c>
-      <c r="J12" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="13" spans="2:10">
-      <c r="B13" t="s">
-        <v>56</v>
-      </c>
-      <c r="C13" t="s">
-        <v>57</v>
-      </c>
-      <c r="D13" t="s">
-        <v>58</v>
-      </c>
-      <c r="E13" t="s">
-        <v>42</v>
-      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>item_gold_random</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>随机金币</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>获得 1~100 个金币。</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="F13"/>
       <c r="G13">
         <v>0</v>
       </c>
-      <c r="H13" t="s">
-        <v>59</v>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>range:1,100</t>
+        </is>
       </c>
       <c r="I13">
         <v>1</v>
       </c>
-      <c r="J13" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="14" spans="2:10">
-      <c r="B14" t="s">
-        <v>60</v>
-      </c>
-      <c r="C14" t="s">
-        <v>61</v>
-      </c>
-      <c r="D14" t="s">
-        <v>62</v>
-      </c>
-      <c r="E14" t="s">
-        <v>28</v>
-      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>item_gold_meal_bonus</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>美食分红</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>接下来10局美食，额外获得15金币。</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F14"/>
       <c r="G14">
         <v>15</v>
       </c>
-      <c r="H14" t="s">
-        <v>63</v>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>meals:10</t>
+        </is>
       </c>
       <c r="I14">
         <v>1</v>
       </c>
-      <c r="J14" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="15" spans="2:10">
-      <c r="B15" t="s">
-        <v>65</v>
-      </c>
-      <c r="C15" t="s">
-        <v>66</v>
-      </c>
-      <c r="D15" t="s">
-        <v>67</v>
-      </c>
-      <c r="E15" t="s">
-        <v>28</v>
-      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>5,45</t>
+        </is>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>item_gold_boss</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Boss赏金</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>完成本次 Boss 后，额外获得100金币。</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F15"/>
       <c r="G15">
         <v>100</v>
       </c>
+      <c r="H15"/>
       <c r="I15">
         <v>1</v>
       </c>
-      <c r="J15" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="16" spans="2:10">
-      <c r="B16" t="s">
-        <v>68</v>
-      </c>
-      <c r="C16" t="s">
-        <v>69</v>
-      </c>
-      <c r="D16" t="s">
-        <v>70</v>
-      </c>
-      <c r="E16" t="s">
-        <v>52</v>
-      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>5,45</t>
+        </is>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>item_gold_percent</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>利润提成</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>美食结束获得的金币，额外获得20%。</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F16"/>
       <c r="G16">
         <v>0.2</v>
       </c>
+      <c r="H16"/>
       <c r="I16">
         <v>1</v>
       </c>
-      <c r="J16" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="17" spans="2:10">
-      <c r="B17" t="s">
-        <v>72</v>
-      </c>
-      <c r="C17" t="s">
-        <v>73</v>
-      </c>
-      <c r="D17" t="s">
-        <v>74</v>
-      </c>
-      <c r="E17" t="s">
-        <v>42</v>
-      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>20,65</t>
+        </is>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>item_discount_food</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>食材优惠券</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>购买食物打折20%。</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="F17"/>
       <c r="G17">
         <v>0.2</v>
       </c>
+      <c r="H17"/>
       <c r="I17">
         <v>1</v>
       </c>
-      <c r="J17" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="18" spans="2:10">
-      <c r="B18" t="s">
-        <v>76</v>
-      </c>
-      <c r="C18" t="s">
-        <v>77</v>
-      </c>
-      <c r="D18" t="s">
-        <v>78</v>
-      </c>
-      <c r="E18" t="s">
-        <v>42</v>
-      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>1,30</t>
+        </is>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>item_discount_fragment</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>碎片优惠券</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>购买碎片打折20%。</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="F18"/>
       <c r="G18">
         <v>0.2</v>
       </c>
+      <c r="H18"/>
       <c r="I18">
         <v>1</v>
       </c>
-      <c r="J18" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="19" spans="2:10">
-      <c r="B19" t="s">
-        <v>79</v>
-      </c>
-      <c r="C19" t="s">
-        <v>80</v>
-      </c>
-      <c r="D19" t="s">
-        <v>81</v>
-      </c>
-      <c r="E19" t="s">
-        <v>42</v>
-      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>1,30</t>
+        </is>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>item_discount_active</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>主动道具券</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>购买主动道具打折20%。</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="F19"/>
       <c r="G19">
         <v>0.2</v>
       </c>
+      <c r="H19"/>
       <c r="I19">
         <v>1</v>
       </c>
-      <c r="J19" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="20" spans="2:10">
-      <c r="B20" t="s">
-        <v>82</v>
-      </c>
-      <c r="C20" t="s">
-        <v>83</v>
-      </c>
-      <c r="D20" t="s">
-        <v>84</v>
-      </c>
-      <c r="E20" t="s">
-        <v>42</v>
-      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>1,30</t>
+        </is>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>item_discount_passive</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>被动道具券</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>购买被动道具打折20%。</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="F20"/>
       <c r="G20">
         <v>0.2</v>
       </c>
+      <c r="H20"/>
       <c r="I20">
         <v>1</v>
       </c>
-      <c r="J20" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="21" spans="2:10">
-      <c r="B21" t="s">
-        <v>85</v>
-      </c>
-      <c r="C21" t="s">
-        <v>86</v>
-      </c>
-      <c r="D21" t="s">
-        <v>87</v>
-      </c>
-      <c r="E21" t="s">
-        <v>42</v>
-      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>1,30</t>
+        </is>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>item_discount_remove</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>删牌优惠</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>删牌价格打折20%。</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="F21"/>
       <c r="G21">
         <v>0.2</v>
       </c>
+      <c r="H21"/>
       <c r="I21">
         <v>1</v>
       </c>
-      <c r="J21" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="22" spans="2:10">
-      <c r="B22" t="s">
-        <v>88</v>
-      </c>
-      <c r="C22" t="s">
-        <v>89</v>
-      </c>
-      <c r="D22" t="s">
-        <v>90</v>
-      </c>
-      <c r="E22" t="s">
-        <v>28</v>
-      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>1,30</t>
+        </is>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>item_remove_fixed_30</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>固定删牌价</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>删牌价格固定为30金币。</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F22"/>
       <c r="G22">
         <v>30</v>
       </c>
+      <c r="H22"/>
       <c r="I22">
         <v>1</v>
       </c>
-      <c r="J22" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="23" spans="2:10">
-      <c r="B23" t="s">
-        <v>91</v>
-      </c>
-      <c r="C23" t="s">
-        <v>92</v>
-      </c>
-      <c r="D23" t="s">
-        <v>93</v>
-      </c>
-      <c r="E23" t="s">
-        <v>42</v>
-      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>5,45</t>
+        </is>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>item_discount_recipe</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>菜谱优惠</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>购买菜谱打折20%。</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="F23"/>
       <c r="G23">
         <v>0.2</v>
       </c>
+      <c r="H23"/>
       <c r="I23">
         <v>1</v>
       </c>
-      <c r="J23" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="24" spans="2:10">
-      <c r="B24" t="s">
-        <v>94</v>
-      </c>
-      <c r="C24" t="s">
-        <v>95</v>
-      </c>
-      <c r="D24" t="s">
-        <v>96</v>
-      </c>
-      <c r="E24" t="s">
-        <v>52</v>
-      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>1,30</t>
+        </is>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>item_famous_knife</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>名刀·加护</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>分数未达标时不失败，但会失去此道具。</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F24"/>
       <c r="G24">
         <v>0</v>
       </c>
+      <c r="H24"/>
       <c r="I24">
         <v>1</v>
       </c>
-      <c r="J24" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="25" spans="2:10">
-      <c r="B25" t="s">
-        <v>97</v>
-      </c>
-      <c r="C25" t="s">
-        <v>98</v>
-      </c>
-      <c r="D25" t="s">
-        <v>99</v>
-      </c>
-      <c r="E25" t="s">
-        <v>52</v>
-      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>20,65</t>
+        </is>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>item_score_to_one</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>免检通行证</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>接下来3局非盛宴，分数要求为1。</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F25"/>
       <c r="G25">
         <v>0</v>
       </c>
-      <c r="H25" t="s">
-        <v>100</v>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>meals:3</t>
+        </is>
       </c>
       <c r="I25">
         <v>1</v>
       </c>
-      <c r="J25" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="26" spans="2:10">
-      <c r="B26" t="s">
-        <v>101</v>
-      </c>
-      <c r="C26" t="s">
-        <v>102</v>
-      </c>
-      <c r="D26" t="s">
-        <v>103</v>
-      </c>
-      <c r="E26" t="s">
-        <v>28</v>
-      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25">
+        <v>0</v>
+      </c>
+      <c r="P25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>item_req_normal_down</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>家常减负</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>普通美食要求分数-10%。</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F26"/>
       <c r="G26">
         <v>-0.1</v>
       </c>
+      <c r="H26"/>
       <c r="I26">
         <v>1</v>
       </c>
-      <c r="J26" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="27" spans="2:10">
-      <c r="B27" t="s">
-        <v>104</v>
-      </c>
-      <c r="C27" t="s">
-        <v>105</v>
-      </c>
-      <c r="D27" t="s">
-        <v>106</v>
-      </c>
-      <c r="E27" t="s">
-        <v>28</v>
-      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>5,45</t>
+        </is>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="O26">
+        <v>0</v>
+      </c>
+      <c r="P26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>item_req_super_down</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>超级减负</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>超级美食要求分数-10%。</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F27"/>
       <c r="G27">
         <v>-0.1</v>
       </c>
+      <c r="H27"/>
       <c r="I27">
         <v>1</v>
       </c>
-      <c r="J27" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="28" spans="2:10">
-      <c r="B28" t="s">
-        <v>107</v>
-      </c>
-      <c r="C28" t="s">
-        <v>108</v>
-      </c>
-      <c r="D28" t="s">
-        <v>109</v>
-      </c>
-      <c r="E28" t="s">
-        <v>28</v>
-      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>5,45</t>
+        </is>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27">
+        <v>0</v>
+      </c>
+      <c r="O27">
+        <v>0</v>
+      </c>
+      <c r="P27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>item_req_feast_down</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>盛宴减负</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>盛宴美食要求分数-10%。</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F28"/>
       <c r="G28">
         <v>-0.1</v>
       </c>
+      <c r="H28"/>
       <c r="I28">
         <v>1</v>
       </c>
-      <c r="J28" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="29" spans="2:10">
-      <c r="B29" t="s">
-        <v>110</v>
-      </c>
-      <c r="C29" t="s">
-        <v>111</v>
-      </c>
-      <c r="D29" t="s">
-        <v>112</v>
-      </c>
-      <c r="E29" t="s">
-        <v>28</v>
-      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>5,45</t>
+        </is>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="O28">
+        <v>0</v>
+      </c>
+      <c r="P28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>item_count_le_mult</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>精致料理</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>结算时食物数量&lt;=10，所有美食倍率×1.1。</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F29"/>
       <c r="G29">
         <v>1.1</v>
       </c>
-      <c r="H29" t="s">
-        <v>113</v>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>lte:10</t>
+        </is>
       </c>
       <c r="I29">
         <v>1</v>
       </c>
-      <c r="J29" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="30" spans="2:10">
-      <c r="B30" t="s">
-        <v>114</v>
-      </c>
-      <c r="C30" t="s">
-        <v>115</v>
-      </c>
-      <c r="D30" t="s">
-        <v>116</v>
-      </c>
-      <c r="E30" t="s">
-        <v>28</v>
-      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>5,45</t>
+        </is>
+      </c>
+      <c r="K29">
+        <v>0</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29">
+        <v>0</v>
+      </c>
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>item_count_ge_mult</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>丰盛大餐</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>结算时食物数量&gt;=10，所有美食倍率×1.1。</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F30"/>
       <c r="G30">
         <v>1.1</v>
       </c>
-      <c r="H30" t="s">
-        <v>117</v>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>gte:10</t>
+        </is>
       </c>
       <c r="I30">
         <v>1</v>
       </c>
-      <c r="J30" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="31" spans="2:10">
-      <c r="B31" t="s">
-        <v>118</v>
-      </c>
-      <c r="C31" t="s">
-        <v>119</v>
-      </c>
-      <c r="D31" t="s">
-        <v>120</v>
-      </c>
-      <c r="E31" t="s">
-        <v>52</v>
-      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>5,45</t>
+        </is>
+      </c>
+      <c r="K30">
+        <v>0</v>
+      </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30">
+        <v>0</v>
+      </c>
+      <c r="N30">
+        <v>0</v>
+      </c>
+      <c r="O30">
+        <v>0</v>
+      </c>
+      <c r="P30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>item_per_dish_mult</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>流水席</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>结算时每结算1个食物，所有食物倍率+0.1。</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F31"/>
       <c r="G31">
         <v>0.1</v>
       </c>
+      <c r="H31"/>
       <c r="I31">
         <v>1</v>
       </c>
-      <c r="J31" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="32" spans="2:10">
-      <c r="B32" t="s">
-        <v>121</v>
-      </c>
-      <c r="C32" t="s">
-        <v>122</v>
-      </c>
-      <c r="D32" t="s">
-        <v>123</v>
-      </c>
-      <c r="E32" t="s">
-        <v>52</v>
-      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>20,65</t>
+        </is>
+      </c>
+      <c r="K31">
+        <v>0</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31">
+        <v>0</v>
+      </c>
+      <c r="N31">
+        <v>0</v>
+      </c>
+      <c r="O31">
+        <v>0</v>
+      </c>
+      <c r="P31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>item_perma_flat_all</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>增鲜剂</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>所有食物基础分数永久+10。</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F32"/>
       <c r="G32">
         <v>10</v>
       </c>
+      <c r="H32"/>
       <c r="I32">
         <v>1</v>
       </c>
-      <c r="J32" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="33" spans="2:10">
-      <c r="B33" t="s">
-        <v>124</v>
-      </c>
-      <c r="C33" t="s">
-        <v>125</v>
-      </c>
-      <c r="D33" t="s">
-        <v>126</v>
-      </c>
-      <c r="E33" t="s">
-        <v>52</v>
-      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>20,65</t>
+        </is>
+      </c>
+      <c r="K32">
+        <v>0</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+      <c r="N32">
+        <v>0</v>
+      </c>
+      <c r="O32">
+        <v>0</v>
+      </c>
+      <c r="P32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>item_perma_mult_all</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>浓缩精华</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>所有食物基础倍率永久+0.2。</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F33"/>
       <c r="G33">
         <v>0.2</v>
       </c>
+      <c r="H33"/>
       <c r="I33">
         <v>1</v>
       </c>
-      <c r="J33" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="34" spans="2:10">
-      <c r="B34" t="s">
-        <v>127</v>
-      </c>
-      <c r="C34" t="s">
-        <v>128</v>
-      </c>
-      <c r="D34" t="s">
-        <v>129</v>
-      </c>
-      <c r="E34" t="s">
-        <v>28</v>
-      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>20,65</t>
+        </is>
+      </c>
+      <c r="K33">
+        <v>0</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33">
+        <v>0</v>
+      </c>
+      <c r="N33">
+        <v>0</v>
+      </c>
+      <c r="O33">
+        <v>0</v>
+      </c>
+      <c r="P33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>item_stargaze_every5</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>观星仪</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>每5次上菜后，下一次上菜可预见食物。</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F34"/>
       <c r="G34">
         <v>0</v>
       </c>
-      <c r="H34" t="s">
-        <v>130</v>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>every:5</t>
+        </is>
       </c>
       <c r="I34">
         <v>1</v>
       </c>
-      <c r="J34" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="35" spans="2:10">
-      <c r="B35" t="s">
-        <v>131</v>
-      </c>
-      <c r="C35" t="s">
-        <v>132</v>
-      </c>
-      <c r="D35" t="s">
-        <v>133</v>
-      </c>
-      <c r="E35" t="s">
-        <v>28</v>
-      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>5,45</t>
+        </is>
+      </c>
+      <c r="K34">
+        <v>0</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34">
+        <v>0</v>
+      </c>
+      <c r="N34">
+        <v>0</v>
+      </c>
+      <c r="O34">
+        <v>0</v>
+      </c>
+      <c r="P34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>item_stargaze_first3</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>开局观星</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>每局前三次上菜可预见食物。</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F35"/>
       <c r="G35">
         <v>0</v>
       </c>
-      <c r="H35" t="s">
-        <v>134</v>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>first:3</t>
+        </is>
       </c>
       <c r="I35">
         <v>1</v>
       </c>
-      <c r="J35" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="36" spans="2:10">
-      <c r="B36" t="s">
-        <v>135</v>
-      </c>
-      <c r="C36" t="s">
-        <v>136</v>
-      </c>
-      <c r="D36" t="s">
-        <v>137</v>
-      </c>
-      <c r="E36" t="s">
-        <v>28</v>
-      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>5,45</t>
+        </is>
+      </c>
+      <c r="K35">
+        <v>0</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35">
+        <v>0</v>
+      </c>
+      <c r="N35">
+        <v>0</v>
+      </c>
+      <c r="O35">
+        <v>0</v>
+      </c>
+      <c r="P35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>item_free_move_first</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>免费调整</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>每局第一次上菜后，可不消耗修正次数移动。</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F36"/>
       <c r="G36">
         <v>0</v>
       </c>
+      <c r="H36"/>
       <c r="I36">
         <v>1</v>
       </c>
-      <c r="J36" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="37" spans="2:10">
-      <c r="B37" t="s">
-        <v>138</v>
-      </c>
-      <c r="C37" t="s">
-        <v>139</v>
-      </c>
-      <c r="D37" t="s">
-        <v>140</v>
-      </c>
-      <c r="E37" t="s">
-        <v>42</v>
-      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>5,45</t>
+        </is>
+      </c>
+      <c r="K36">
+        <v>0</v>
+      </c>
+      <c r="L36">
+        <v>0</v>
+      </c>
+      <c r="M36">
+        <v>0</v>
+      </c>
+      <c r="N36">
+        <v>0</v>
+      </c>
+      <c r="O36">
+        <v>0</v>
+      </c>
+      <c r="P36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>item_adjust_plus1</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>熟练的手</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>调整次数+1。</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="F37"/>
       <c r="G37">
         <v>1</v>
       </c>
+      <c r="H37"/>
       <c r="I37">
         <v>1</v>
       </c>
-      <c r="J37" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="38" spans="2:10">
-      <c r="B38" t="s">
-        <v>141</v>
-      </c>
-      <c r="C38" t="s">
-        <v>142</v>
-      </c>
-      <c r="D38" t="s">
-        <v>143</v>
-      </c>
-      <c r="E38" t="s">
-        <v>52</v>
-      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>1,30</t>
+        </is>
+      </c>
+      <c r="K37">
+        <v>0</v>
+      </c>
+      <c r="L37">
+        <v>0</v>
+      </c>
+      <c r="M37">
+        <v>0</v>
+      </c>
+      <c r="N37">
+        <v>0</v>
+      </c>
+      <c r="O37">
+        <v>0</v>
+      </c>
+      <c r="P37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>item_adjust_to_mult</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>节俭加成</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>每1个未使用的调整次数，使倍率+0.2。</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F38"/>
       <c r="G38">
         <v>0.2</v>
       </c>
+      <c r="H38"/>
       <c r="I38">
         <v>1</v>
       </c>
-      <c r="J38" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="39" spans="2:10">
-      <c r="B39" t="s">
-        <v>144</v>
-      </c>
-      <c r="C39" t="s">
-        <v>145</v>
-      </c>
-      <c r="D39" t="s">
-        <v>146</v>
-      </c>
-      <c r="E39" t="s">
-        <v>52</v>
-      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>20,65</t>
+        </is>
+      </c>
+      <c r="K38">
+        <v>0</v>
+      </c>
+      <c r="L38">
+        <v>0</v>
+      </c>
+      <c r="M38">
+        <v>0</v>
+      </c>
+      <c r="N38">
+        <v>0</v>
+      </c>
+      <c r="O38">
+        <v>0</v>
+      </c>
+      <c r="P38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>item_food_convert</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>点石成金</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>随机将5个食物变为至少同品质的食物。</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F39"/>
       <c r="G39">
         <v>5</v>
       </c>
+      <c r="H39"/>
       <c r="I39">
         <v>1</v>
       </c>
-      <c r="J39" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="40" spans="2:10">
-      <c r="B40" t="s">
-        <v>147</v>
-      </c>
-      <c r="C40" t="s">
-        <v>148</v>
-      </c>
-      <c r="D40" t="s">
-        <v>149</v>
-      </c>
-      <c r="E40" t="s">
-        <v>28</v>
-      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="K39">
+        <v>0</v>
+      </c>
+      <c r="L39">
+        <v>0</v>
+      </c>
+      <c r="M39">
+        <v>0</v>
+      </c>
+      <c r="N39">
+        <v>0</v>
+      </c>
+      <c r="O39">
+        <v>0</v>
+      </c>
+      <c r="P39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>item_adjust_to_gold</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>变卖技巧</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>每个未使用的调整次数，获得1金币。</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F40"/>
       <c r="G40">
         <v>1</v>
       </c>
+      <c r="H40"/>
       <c r="I40">
         <v>1</v>
       </c>
-      <c r="J40" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="41" spans="2:10">
-      <c r="B41" t="s">
-        <v>150</v>
-      </c>
-      <c r="C41" t="s">
-        <v>151</v>
-      </c>
-      <c r="D41" t="s">
-        <v>152</v>
-      </c>
-      <c r="E41" t="s">
-        <v>28</v>
-      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>5,45</t>
+        </is>
+      </c>
+      <c r="K40">
+        <v>0</v>
+      </c>
+      <c r="L40">
+        <v>0</v>
+      </c>
+      <c r="M40">
+        <v>0</v>
+      </c>
+      <c r="N40">
+        <v>0</v>
+      </c>
+      <c r="O40">
+        <v>0</v>
+      </c>
+      <c r="P40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>item_gold_on_shop</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>商会返利</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>进入商店时，获得10金币。</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F41"/>
       <c r="G41">
         <v>10</v>
       </c>
+      <c r="H41"/>
       <c r="I41">
         <v>1</v>
       </c>
-      <c r="J41" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="42" spans="2:10">
-      <c r="B42" t="s">
-        <v>153</v>
-      </c>
-      <c r="C42" t="s">
-        <v>154</v>
-      </c>
-      <c r="D42" t="s">
-        <v>155</v>
-      </c>
-      <c r="E42" t="s">
-        <v>52</v>
-      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>5,45</t>
+        </is>
+      </c>
+      <c r="K41">
+        <v>0</v>
+      </c>
+      <c r="L41">
+        <v>0</v>
+      </c>
+      <c r="M41">
+        <v>0</v>
+      </c>
+      <c r="N41">
+        <v>0</v>
+      </c>
+      <c r="O41">
+        <v>0</v>
+      </c>
+      <c r="P41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>item_extra_interest</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>复利账户</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>每周结束额外执行一次利息。</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F42"/>
       <c r="G42">
         <v>1</v>
       </c>
+      <c r="H42"/>
       <c r="I42">
         <v>1</v>
       </c>
-      <c r="J42" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="43" spans="2:10">
-      <c r="B43" t="s">
-        <v>156</v>
-      </c>
-      <c r="C43" t="s">
-        <v>157</v>
-      </c>
-      <c r="D43" t="s">
-        <v>158</v>
-      </c>
-      <c r="E43" t="s">
-        <v>28</v>
-      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>20,65</t>
+        </is>
+      </c>
+      <c r="K42">
+        <v>0</v>
+      </c>
+      <c r="L42">
+        <v>0</v>
+      </c>
+      <c r="M42">
+        <v>0</v>
+      </c>
+      <c r="N42">
+        <v>0</v>
+      </c>
+      <c r="O42">
+        <v>0</v>
+      </c>
+      <c r="P42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>item_min_gold</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>保底基金</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>回合结束金币&lt;10时，补足到10金币。</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F43"/>
       <c r="G43">
         <v>10</v>
       </c>
+      <c r="H43"/>
       <c r="I43">
         <v>1</v>
       </c>
-      <c r="J43" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="44" spans="2:10">
-      <c r="B44" t="s">
-        <v>159</v>
-      </c>
-      <c r="C44" t="s">
-        <v>160</v>
-      </c>
-      <c r="D44" t="s">
-        <v>161</v>
-      </c>
-      <c r="E44" t="s">
-        <v>52</v>
-      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>5,45</t>
+        </is>
+      </c>
+      <c r="K43">
+        <v>0</v>
+      </c>
+      <c r="L43">
+        <v>0</v>
+      </c>
+      <c r="M43">
+        <v>0</v>
+      </c>
+      <c r="N43">
+        <v>0</v>
+      </c>
+      <c r="O43">
+        <v>0</v>
+      </c>
+      <c r="P43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>item_interest_cap</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>高息账户</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>利息上限扩展到10金币。</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F44"/>
       <c r="G44">
         <v>10</v>
       </c>
+      <c r="H44"/>
       <c r="I44">
         <v>1</v>
       </c>
-      <c r="J44" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="45" spans="2:10">
-      <c r="B45" t="s">
-        <v>162</v>
-      </c>
-      <c r="C45" t="s">
-        <v>163</v>
-      </c>
-      <c r="D45" t="s">
-        <v>164</v>
-      </c>
-      <c r="E45" t="s">
-        <v>52</v>
-      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>20,65</t>
+        </is>
+      </c>
+      <c r="K44">
+        <v>0</v>
+      </c>
+      <c r="L44">
+        <v>0</v>
+      </c>
+      <c r="M44">
+        <v>0</v>
+      </c>
+      <c r="N44">
+        <v>0</v>
+      </c>
+      <c r="O44">
+        <v>0</v>
+      </c>
+      <c r="P44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>item_loan</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>高利贷</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>临时获得300金币，下一周失去600金币。</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F45"/>
       <c r="G45">
         <v>300</v>
       </c>
-      <c r="H45" t="s">
-        <v>165</v>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>repay:600</t>
+        </is>
       </c>
       <c r="I45">
         <v>1</v>
       </c>
-      <c r="J45" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="46" spans="2:10">
-      <c r="B46" t="s">
-        <v>166</v>
-      </c>
-      <c r="C46" t="s">
-        <v>167</v>
-      </c>
-      <c r="D46" t="s">
-        <v>168</v>
-      </c>
-      <c r="E46" t="s">
-        <v>28</v>
-      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="K45">
+        <v>0</v>
+      </c>
+      <c r="L45">
+        <v>0</v>
+      </c>
+      <c r="M45">
+        <v>0</v>
+      </c>
+      <c r="N45">
+        <v>0</v>
+      </c>
+      <c r="O45">
+        <v>0</v>
+      </c>
+      <c r="P45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>item_timeline_random</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>命运骰子</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>随机化时间轴的节点事件。</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F46"/>
       <c r="G46">
         <v>0</v>
       </c>
+      <c r="H46"/>
       <c r="I46">
         <v>1</v>
       </c>
-      <c r="J46" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="47" spans="2:10">
-      <c r="B47" t="s">
-        <v>169</v>
-      </c>
-      <c r="C47" t="s">
-        <v>170</v>
-      </c>
-      <c r="D47" t="s">
-        <v>171</v>
-      </c>
-      <c r="E47" t="s">
-        <v>52</v>
-      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="K46">
+        <v>0</v>
+      </c>
+      <c r="L46">
+        <v>0</v>
+      </c>
+      <c r="M46">
+        <v>0</v>
+      </c>
+      <c r="N46">
+        <v>0</v>
+      </c>
+      <c r="O46">
+        <v>0</v>
+      </c>
+      <c r="P46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>item_extra_day</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>加班一天</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>延后所有 Boss 一天。</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F47"/>
       <c r="G47">
         <v>1</v>
       </c>
+      <c r="H47"/>
       <c r="I47">
         <v>1</v>
       </c>
-      <c r="J47" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="48" spans="2:10">
-      <c r="B48" t="s">
-        <v>172</v>
-      </c>
-      <c r="C48" t="s">
-        <v>173</v>
-      </c>
-      <c r="D48" t="s">
-        <v>174</v>
-      </c>
-      <c r="E48" t="s">
-        <v>175</v>
-      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="K47">
+        <v>0</v>
+      </c>
+      <c r="L47">
+        <v>0</v>
+      </c>
+      <c r="M47">
+        <v>0</v>
+      </c>
+      <c r="N47">
+        <v>0</v>
+      </c>
+      <c r="O47">
+        <v>0</v>
+      </c>
+      <c r="P47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>item_week_minus</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>时光倒流</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>周数-1。</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="F48"/>
       <c r="G48">
         <v>1</v>
       </c>
+      <c r="H48"/>
       <c r="I48">
         <v>1</v>
       </c>
-      <c r="J48" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="49" spans="2:10">
-      <c r="B49" t="s">
-        <v>176</v>
-      </c>
-      <c r="C49" t="s">
-        <v>177</v>
-      </c>
-      <c r="D49" t="s">
-        <v>178</v>
-      </c>
-      <c r="E49" t="s">
-        <v>28</v>
-      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="K48">
+        <v>0</v>
+      </c>
+      <c r="L48">
+        <v>0</v>
+      </c>
+      <c r="M48">
+        <v>0</v>
+      </c>
+      <c r="N48">
+        <v>0</v>
+      </c>
+      <c r="O48">
+        <v>0</v>
+      </c>
+      <c r="P48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>item_add_reward_node</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>额外奖励</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>增加一个奖励节点到时间轴上。</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F49"/>
       <c r="G49">
         <v>1</v>
       </c>
+      <c r="H49"/>
       <c r="I49">
         <v>1</v>
       </c>
-      <c r="J49" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="50" spans="2:10">
-      <c r="B50" t="s">
-        <v>179</v>
-      </c>
-      <c r="C50" t="s">
-        <v>180</v>
-      </c>
-      <c r="D50" t="s">
-        <v>181</v>
-      </c>
-      <c r="E50" t="s">
-        <v>28</v>
-      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="K49">
+        <v>0</v>
+      </c>
+      <c r="L49">
+        <v>0</v>
+      </c>
+      <c r="M49">
+        <v>0</v>
+      </c>
+      <c r="N49">
+        <v>0</v>
+      </c>
+      <c r="O49">
+        <v>0</v>
+      </c>
+      <c r="P49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>item_add_interest_node</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>额外利息节点</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>增加一个利息节点到时间轴上。</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F50"/>
       <c r="G50">
         <v>1</v>
       </c>
+      <c r="H50"/>
       <c r="I50">
         <v>1</v>
       </c>
-      <c r="J50" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="51" spans="2:10">
-      <c r="B51" t="s">
-        <v>182</v>
-      </c>
-      <c r="C51" t="s">
-        <v>183</v>
-      </c>
-      <c r="D51" t="s">
-        <v>184</v>
-      </c>
-      <c r="E51" t="s">
-        <v>52</v>
-      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="K50">
+        <v>0</v>
+      </c>
+      <c r="L50">
+        <v>0</v>
+      </c>
+      <c r="M50">
+        <v>0</v>
+      </c>
+      <c r="N50">
+        <v>0</v>
+      </c>
+      <c r="O50">
+        <v>0</v>
+      </c>
+      <c r="P50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>item_every3_next_mult</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>节奏大师</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>每上3个食物后，下一个食物倍率+2。</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F51"/>
       <c r="G51">
         <v>2</v>
       </c>
-      <c r="H51" t="s">
-        <v>185</v>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>every:3</t>
+        </is>
       </c>
       <c r="I51">
         <v>1</v>
       </c>
-      <c r="J51" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="52" spans="2:10">
-      <c r="B52" t="s">
-        <v>186</v>
-      </c>
-      <c r="C52" t="s">
-        <v>187</v>
-      </c>
-      <c r="D52" t="s">
-        <v>188</v>
-      </c>
-      <c r="E52" t="s">
-        <v>28</v>
-      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>20,65</t>
+        </is>
+      </c>
+      <c r="K51">
+        <v>0</v>
+      </c>
+      <c r="L51">
+        <v>0</v>
+      </c>
+      <c r="M51">
+        <v>0</v>
+      </c>
+      <c r="N51">
+        <v>0</v>
+      </c>
+      <c r="O51">
+        <v>0</v>
+      </c>
+      <c r="P51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>item_first_x2</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>开门红</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>第一个上的食物，倍率×2。</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F52"/>
       <c r="G52">
         <v>2</v>
       </c>
-      <c r="H52" t="s">
-        <v>189</v>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>index:1</t>
+        </is>
       </c>
       <c r="I52">
         <v>1</v>
       </c>
-      <c r="J52" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="53" spans="2:10">
-      <c r="B53" t="s">
-        <v>190</v>
-      </c>
-      <c r="C53" t="s">
-        <v>191</v>
-      </c>
-      <c r="D53" t="s">
-        <v>192</v>
-      </c>
-      <c r="E53" t="s">
-        <v>28</v>
-      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>5,45</t>
+        </is>
+      </c>
+      <c r="K52">
+        <v>0</v>
+      </c>
+      <c r="L52">
+        <v>0</v>
+      </c>
+      <c r="M52">
+        <v>0</v>
+      </c>
+      <c r="N52">
+        <v>0</v>
+      </c>
+      <c r="O52">
+        <v>0</v>
+      </c>
+      <c r="P52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>item_last_x2</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>压轴好戏</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>最后一个上的食物，倍率×2。</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F53"/>
       <c r="G53">
         <v>2</v>
       </c>
-      <c r="H53" t="s">
-        <v>193</v>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>index:-1</t>
+        </is>
       </c>
       <c r="I53">
         <v>1</v>
       </c>
-      <c r="J53" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="54" spans="2:10">
-      <c r="B54" t="s">
-        <v>194</v>
-      </c>
-      <c r="C54" t="s">
-        <v>195</v>
-      </c>
-      <c r="D54" t="s">
-        <v>196</v>
-      </c>
-      <c r="E54" t="s">
-        <v>52</v>
-      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>5,45</t>
+        </is>
+      </c>
+      <c r="K53">
+        <v>0</v>
+      </c>
+      <c r="L53">
+        <v>0</v>
+      </c>
+      <c r="M53">
+        <v>0</v>
+      </c>
+      <c r="N53">
+        <v>0</v>
+      </c>
+      <c r="O53">
+        <v>0</v>
+      </c>
+      <c r="P53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>item_extra_active_slots</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>工具箱</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>增加2个额外主动道具栏。</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F54"/>
       <c r="G54">
         <v>2</v>
       </c>
+      <c r="H54"/>
       <c r="I54">
         <v>1</v>
       </c>
-      <c r="J54" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="55" spans="2:10">
-      <c r="B55" t="s">
-        <v>197</v>
-      </c>
-      <c r="C55" t="s">
-        <v>198</v>
-      </c>
-      <c r="D55" t="s">
-        <v>199</v>
-      </c>
-      <c r="E55" t="s">
-        <v>28</v>
-      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>20,65</t>
+        </is>
+      </c>
+      <c r="K54">
+        <v>0</v>
+      </c>
+      <c r="L54">
+        <v>0</v>
+      </c>
+      <c r="M54">
+        <v>0</v>
+      </c>
+      <c r="N54">
+        <v>0</v>
+      </c>
+      <c r="O54">
+        <v>0</v>
+      </c>
+      <c r="P54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>item_gold_on_active</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>以用换钱</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>使用主动道具时，获得20金币。</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F55"/>
       <c r="G55">
         <v>20</v>
       </c>
+      <c r="H55"/>
       <c r="I55">
         <v>1</v>
       </c>
-      <c r="J55" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="56" spans="2:10">
-      <c r="B56" t="s">
-        <v>200</v>
-      </c>
-      <c r="C56" t="s">
-        <v>201</v>
-      </c>
-      <c r="D56" t="s">
-        <v>202</v>
-      </c>
-      <c r="E56" t="s">
-        <v>175</v>
-      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>5,45</t>
+        </is>
+      </c>
+      <c r="K55">
+        <v>0</v>
+      </c>
+      <c r="L55">
+        <v>0</v>
+      </c>
+      <c r="M55">
+        <v>0</v>
+      </c>
+      <c r="N55">
+        <v>0</v>
+      </c>
+      <c r="O55">
+        <v>0</v>
+      </c>
+      <c r="P55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>item_block_active</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>极简主义</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>无法获得主动道具，立即获得1000金币。</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="F56"/>
       <c r="G56">
         <v>1000</v>
       </c>
+      <c r="H56"/>
       <c r="I56">
         <v>1</v>
       </c>
-      <c r="J56" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="57" spans="2:10">
-      <c r="B57" t="s">
-        <v>204</v>
-      </c>
-      <c r="C57" t="s">
-        <v>205</v>
-      </c>
-      <c r="D57" t="s">
-        <v>206</v>
-      </c>
-      <c r="E57" t="s">
-        <v>28</v>
-      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>40,85</t>
+        </is>
+      </c>
+      <c r="K56">
+        <v>0</v>
+      </c>
+      <c r="L56">
+        <v>0</v>
+      </c>
+      <c r="M56">
+        <v>0</v>
+      </c>
+      <c r="N56">
+        <v>0</v>
+      </c>
+      <c r="O56">
+        <v>0</v>
+      </c>
+      <c r="P56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>item_flavor_enhance</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>风味喷雾</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>给两个无风味的食物添加随机风味。</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F57"/>
       <c r="G57">
         <v>2</v>
       </c>
+      <c r="H57"/>
       <c r="I57">
         <v>1</v>
       </c>
-      <c r="J57" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="58" spans="2:10">
-      <c r="B58" t="s">
-        <v>207</v>
-      </c>
-      <c r="C58" t="s">
-        <v>208</v>
-      </c>
-      <c r="D58" t="s">
-        <v>209</v>
-      </c>
-      <c r="E58" t="s">
-        <v>28</v>
-      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="K57">
+        <v>0</v>
+      </c>
+      <c r="L57">
+        <v>0</v>
+      </c>
+      <c r="M57">
+        <v>0</v>
+      </c>
+      <c r="N57">
+        <v>0</v>
+      </c>
+      <c r="O57">
+        <v>0</v>
+      </c>
+      <c r="P57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>item_flavor_remove_gold</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>风味回收</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>移除一个食物的风味，获得200金币。</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F58"/>
       <c r="G58">
         <v>200</v>
       </c>
+      <c r="H58"/>
       <c r="I58">
         <v>1</v>
       </c>
-      <c r="J58" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="59" spans="2:10">
-      <c r="B59" t="s">
-        <v>210</v>
-      </c>
-      <c r="C59" t="s">
-        <v>211</v>
-      </c>
-      <c r="D59" t="s">
-        <v>212</v>
-      </c>
-      <c r="E59" t="s">
-        <v>52</v>
-      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="K58">
+        <v>0</v>
+      </c>
+      <c r="L58">
+        <v>0</v>
+      </c>
+      <c r="M58">
+        <v>0</v>
+      </c>
+      <c r="N58">
+        <v>0</v>
+      </c>
+      <c r="O58">
+        <v>0</v>
+      </c>
+      <c r="P58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>item_flavor_remove_copyskill</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>风味转化</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>移除一个食物的风味，其技能复制。</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F59"/>
       <c r="G59">
         <v>0</v>
       </c>
+      <c r="H59"/>
       <c r="I59">
         <v>1</v>
       </c>
-      <c r="J59" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="60" spans="2:10">
-      <c r="B60" t="s">
-        <v>213</v>
-      </c>
-      <c r="C60" t="s">
-        <v>214</v>
-      </c>
-      <c r="D60" t="s">
-        <v>215</v>
-      </c>
-      <c r="E60" t="s">
-        <v>52</v>
-      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="K59">
+        <v>0</v>
+      </c>
+      <c r="L59">
+        <v>0</v>
+      </c>
+      <c r="M59">
+        <v>0</v>
+      </c>
+      <c r="N59">
+        <v>0</v>
+      </c>
+      <c r="O59">
+        <v>0</v>
+      </c>
+      <c r="P59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>item_flavor_remove_double</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>风味浓缩</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>移除一个食物的风味，其分数翻倍。</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F60"/>
       <c r="G60">
         <v>2</v>
       </c>
+      <c r="H60"/>
       <c r="I60">
         <v>1</v>
       </c>
-      <c r="J60" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="61" spans="2:10">
-      <c r="B61" t="s">
-        <v>216</v>
-      </c>
-      <c r="C61" t="s">
-        <v>217</v>
-      </c>
-      <c r="D61" t="s">
-        <v>218</v>
-      </c>
-      <c r="E61" t="s">
-        <v>175</v>
-      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="K60">
+        <v>0</v>
+      </c>
+      <c r="L60">
+        <v>0</v>
+      </c>
+      <c r="M60">
+        <v>0</v>
+      </c>
+      <c r="N60">
+        <v>0</v>
+      </c>
+      <c r="O60">
+        <v>0</v>
+      </c>
+      <c r="P60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>item_flavor_double_slot</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>双重风味</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>允许一个食物拥有两个风味。</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="F61"/>
       <c r="G61">
         <v>1</v>
       </c>
+      <c r="H61"/>
       <c r="I61">
         <v>1</v>
       </c>
-      <c r="J61" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="62" spans="2:10">
-      <c r="B62" t="s">
-        <v>219</v>
-      </c>
-      <c r="C62" t="s">
-        <v>220</v>
-      </c>
-      <c r="D62" t="s">
-        <v>221</v>
-      </c>
-      <c r="E62" t="s">
-        <v>52</v>
-      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>40,85</t>
+        </is>
+      </c>
+      <c r="K61">
+        <v>0</v>
+      </c>
+      <c r="L61">
+        <v>0</v>
+      </c>
+      <c r="M61">
+        <v>0</v>
+      </c>
+      <c r="N61">
+        <v>0</v>
+      </c>
+      <c r="O61">
+        <v>0</v>
+      </c>
+      <c r="P61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>item_flavor_contagion</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>风味传染</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>将一个食物的风味强化到无风味食物上。</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F62"/>
       <c r="G62">
         <v>1</v>
       </c>
+      <c r="H62"/>
       <c r="I62">
         <v>1</v>
       </c>
-      <c r="J62" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="63" spans="2:10">
-      <c r="B63" t="s">
-        <v>222</v>
-      </c>
-      <c r="C63" t="s">
-        <v>223</v>
-      </c>
-      <c r="D63" t="s">
-        <v>224</v>
-      </c>
-      <c r="E63" t="s">
-        <v>28</v>
-      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="K62">
+        <v>0</v>
+      </c>
+      <c r="L62">
+        <v>0</v>
+      </c>
+      <c r="M62">
+        <v>0</v>
+      </c>
+      <c r="N62">
+        <v>0</v>
+      </c>
+      <c r="O62">
+        <v>0</v>
+      </c>
+      <c r="P62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>item_celltag_enhance</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>标签强化</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>强化两个随机标签到胃部格子上。</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F63"/>
       <c r="G63">
         <v>2</v>
       </c>
+      <c r="H63"/>
       <c r="I63">
         <v>1</v>
       </c>
-      <c r="J63" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="64" spans="2:10">
-      <c r="B64" t="s">
-        <v>225</v>
-      </c>
-      <c r="C64" t="s">
-        <v>226</v>
-      </c>
-      <c r="D64" t="s">
-        <v>227</v>
-      </c>
-      <c r="E64" t="s">
-        <v>52</v>
-      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="K63">
+        <v>0</v>
+      </c>
+      <c r="L63">
+        <v>0</v>
+      </c>
+      <c r="M63">
+        <v>0</v>
+      </c>
+      <c r="N63">
+        <v>0</v>
+      </c>
+      <c r="O63">
+        <v>0</v>
+      </c>
+      <c r="P63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>item_celltag_contagion</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>标签传染</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>将一个格子的标签强化到其他格子上。</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F64"/>
       <c r="G64">
         <v>1</v>
       </c>
+      <c r="H64"/>
       <c r="I64">
         <v>1</v>
       </c>
-      <c r="J64" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="65" spans="2:10">
-      <c r="B65" t="s">
-        <v>228</v>
-      </c>
-      <c r="C65" t="s">
-        <v>229</v>
-      </c>
-      <c r="D65" t="s">
-        <v>230</v>
-      </c>
-      <c r="E65" t="s">
-        <v>52</v>
-      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="K64">
+        <v>0</v>
+      </c>
+      <c r="L64">
+        <v>0</v>
+      </c>
+      <c r="M64">
+        <v>0</v>
+      </c>
+      <c r="N64">
+        <v>0</v>
+      </c>
+      <c r="O64">
+        <v>0</v>
+      </c>
+      <c r="P64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>item_lucky_guarantee</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>好运连连</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>每4个事件的最后一个是奖励事件。</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F65"/>
       <c r="G65">
         <v>4</v>
       </c>
+      <c r="H65"/>
       <c r="I65">
         <v>1</v>
       </c>
-      <c r="J65" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="66" spans="2:10">
-      <c r="B66" t="s">
-        <v>231</v>
-      </c>
-      <c r="C66" t="s">
-        <v>232</v>
-      </c>
-      <c r="D66" t="s">
-        <v>233</v>
-      </c>
-      <c r="E66" t="s">
-        <v>28</v>
-      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>20,65</t>
+        </is>
+      </c>
+      <c r="K65">
+        <v>0</v>
+      </c>
+      <c r="L65">
+        <v>0</v>
+      </c>
+      <c r="M65">
+        <v>0</v>
+      </c>
+      <c r="N65">
+        <v>0</v>
+      </c>
+      <c r="O65">
+        <v>0</v>
+      </c>
+      <c r="P65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>item_lucky_chance</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>幸运符</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>事件中遇到奖励的概率提高。</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F66"/>
       <c r="G66">
         <v>0.2</v>
       </c>
+      <c r="H66"/>
       <c r="I66">
         <v>1</v>
       </c>
-      <c r="J66" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="67" spans="2:10">
-      <c r="B67" t="s">
-        <v>234</v>
-      </c>
-      <c r="C67" t="s">
-        <v>235</v>
-      </c>
-      <c r="D67" t="s">
-        <v>236</v>
-      </c>
-      <c r="E67" t="s">
-        <v>28</v>
-      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>5,45</t>
+        </is>
+      </c>
+      <c r="K66">
+        <v>0</v>
+      </c>
+      <c r="L66">
+        <v>0</v>
+      </c>
+      <c r="M66">
+        <v>0</v>
+      </c>
+      <c r="N66">
+        <v>0</v>
+      </c>
+      <c r="O66">
+        <v>0</v>
+      </c>
+      <c r="P66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>item_more_events</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>热闹街区</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>遇到事件的概率提高。</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F67"/>
       <c r="G67">
         <v>0.2</v>
       </c>
+      <c r="H67"/>
       <c r="I67">
         <v>1</v>
       </c>
-      <c r="J67" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="68" spans="2:10">
-      <c r="B68" t="s">
-        <v>237</v>
-      </c>
-      <c r="C68" t="s">
-        <v>238</v>
-      </c>
-      <c r="D68" t="s">
-        <v>239</v>
-      </c>
-      <c r="E68" t="s">
-        <v>42</v>
-      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>5,45</t>
+        </is>
+      </c>
+      <c r="K67">
+        <v>0</v>
+      </c>
+      <c r="L67">
+        <v>0</v>
+      </c>
+      <c r="M67">
+        <v>0</v>
+      </c>
+      <c r="N67">
+        <v>0</v>
+      </c>
+      <c r="O67">
+        <v>0</v>
+      </c>
+      <c r="P67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>item_gold_on_event</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>事件红包</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>完成一个事件，获得10金币。</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="F68"/>
       <c r="G68">
         <v>10</v>
       </c>
+      <c r="H68"/>
       <c r="I68">
         <v>1</v>
       </c>
-      <c r="J68" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="69" spans="2:10">
-      <c r="B69" t="s">
-        <v>240</v>
-      </c>
-      <c r="C69" t="s">
-        <v>241</v>
-      </c>
-      <c r="D69" t="s">
-        <v>242</v>
-      </c>
-      <c r="E69" t="s">
-        <v>42</v>
-      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>1,30</t>
+        </is>
+      </c>
+      <c r="K68">
+        <v>0</v>
+      </c>
+      <c r="L68">
+        <v>0</v>
+      </c>
+      <c r="M68">
+        <v>0</v>
+      </c>
+      <c r="N68">
+        <v>0</v>
+      </c>
+      <c r="O68">
+        <v>0</v>
+      </c>
+      <c r="P68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>item_reroll_action</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>重掷行动</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>获得2次重新随机行动的机会。</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="F69"/>
       <c r="G69">
         <v>2</v>
       </c>
+      <c r="H69"/>
       <c r="I69">
         <v>1</v>
       </c>
-      <c r="J69" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="70" spans="2:10">
-      <c r="B70" t="s">
-        <v>243</v>
-      </c>
-      <c r="C70" t="s">
-        <v>244</v>
-      </c>
-      <c r="D70" t="s">
-        <v>245</v>
-      </c>
-      <c r="E70" t="s">
-        <v>52</v>
-      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="K69">
+        <v>0</v>
+      </c>
+      <c r="L69">
+        <v>0</v>
+      </c>
+      <c r="M69">
+        <v>0</v>
+      </c>
+      <c r="N69">
+        <v>0</v>
+      </c>
+      <c r="O69">
+        <v>0</v>
+      </c>
+      <c r="P69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>item_shop_restock</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>自动补货</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>商店会自动补货。</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F70"/>
       <c r="G70">
         <v>0</v>
       </c>
+      <c r="H70"/>
       <c r="I70">
         <v>1</v>
       </c>
-      <c r="J70" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="71" spans="2:10">
-      <c r="B71" t="s">
-        <v>246</v>
-      </c>
-      <c r="C71" t="s">
-        <v>247</v>
-      </c>
-      <c r="D71" t="s">
-        <v>248</v>
-      </c>
-      <c r="E71" t="s">
-        <v>28</v>
-      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>20,65</t>
+        </is>
+      </c>
+      <c r="K70">
+        <v>0</v>
+      </c>
+      <c r="L70">
+        <v>0</v>
+      </c>
+      <c r="M70">
+        <v>0</v>
+      </c>
+      <c r="N70">
+        <v>0</v>
+      </c>
+      <c r="O70">
+        <v>0</v>
+      </c>
+      <c r="P70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>item_choice_count_plus1</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>琳琅满目</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>多选一食物时，可选数量+1。</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F71"/>
       <c r="G71">
         <v>1</v>
       </c>
+      <c r="H71"/>
       <c r="I71">
         <v>1</v>
       </c>
-      <c r="J71" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="72" spans="2:10">
-      <c r="B72" t="s">
-        <v>249</v>
-      </c>
-      <c r="C72" t="s">
-        <v>250</v>
-      </c>
-      <c r="D72" t="s">
-        <v>251</v>
-      </c>
-      <c r="E72" t="s">
-        <v>52</v>
-      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>5,45</t>
+        </is>
+      </c>
+      <c r="K71">
+        <v>0</v>
+      </c>
+      <c r="L71">
+        <v>0</v>
+      </c>
+      <c r="M71">
+        <v>0</v>
+      </c>
+      <c r="N71">
+        <v>0</v>
+      </c>
+      <c r="O71">
+        <v>0</v>
+      </c>
+      <c r="P71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>item_choice_times_plus1</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>细嚼慢咽</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>多选一食物时，可选次数+1，可选数量-1。</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F72"/>
       <c r="G72">
         <v>1</v>
       </c>
+      <c r="H72"/>
       <c r="I72">
         <v>1</v>
       </c>
-      <c r="J72" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="73" spans="2:10">
-      <c r="B73" t="s">
-        <v>252</v>
-      </c>
-      <c r="C73" t="s">
-        <v>253</v>
-      </c>
-      <c r="D73" t="s">
-        <v>254</v>
-      </c>
-      <c r="E73" t="s">
-        <v>52</v>
-      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>20,65</t>
+        </is>
+      </c>
+      <c r="K72">
+        <v>0</v>
+      </c>
+      <c r="L72">
+        <v>0</v>
+      </c>
+      <c r="M72">
+        <v>0</v>
+      </c>
+      <c r="N72">
+        <v>0</v>
+      </c>
+      <c r="O72">
+        <v>0</v>
+      </c>
+      <c r="P72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>item_extra_food_choice</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>加餐</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>每3次普通美食，额外获得一个多选一美食。</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F73"/>
       <c r="G73">
         <v>0</v>
       </c>
-      <c r="H73" t="s">
-        <v>185</v>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>every:3</t>
+        </is>
       </c>
       <c r="I73">
         <v>1</v>
       </c>
-      <c r="J73" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="74" spans="2:10">
-      <c r="B74" t="s">
-        <v>255</v>
-      </c>
-      <c r="C74" t="s">
-        <v>256</v>
-      </c>
-      <c r="D74" t="s">
-        <v>257</v>
-      </c>
-      <c r="E74" t="s">
-        <v>52</v>
-      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>20,65</t>
+        </is>
+      </c>
+      <c r="K73">
+        <v>0</v>
+      </c>
+      <c r="L73">
+        <v>0</v>
+      </c>
+      <c r="M73">
+        <v>0</v>
+      </c>
+      <c r="N73">
+        <v>0</v>
+      </c>
+      <c r="O73">
+        <v>0</v>
+      </c>
+      <c r="P73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>item_extra_item_choice</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>加料</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>每3次超级美食，额外获得一个多选一物品。</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F74"/>
       <c r="G74">
         <v>0</v>
       </c>
-      <c r="H74" t="s">
-        <v>185</v>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>every:3</t>
+        </is>
       </c>
       <c r="I74">
         <v>1</v>
       </c>
-      <c r="J74" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="75" spans="2:10">
-      <c r="B75" t="s">
-        <v>258</v>
-      </c>
-      <c r="C75" t="s">
-        <v>259</v>
-      </c>
-      <c r="D75" t="s">
-        <v>260</v>
-      </c>
-      <c r="E75" t="s">
-        <v>52</v>
-      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>20,65</t>
+        </is>
+      </c>
+      <c r="K74">
+        <v>0</v>
+      </c>
+      <c r="L74">
+        <v>0</v>
+      </c>
+      <c r="M74">
+        <v>0</v>
+      </c>
+      <c r="N74">
+        <v>0</v>
+      </c>
+      <c r="O74">
+        <v>0</v>
+      </c>
+      <c r="P74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>item_copy_food</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>复制美食</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>随机复制一个美食。</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F75"/>
       <c r="G75">
         <v>1</v>
       </c>
+      <c r="H75"/>
       <c r="I75">
         <v>1</v>
       </c>
-      <c r="J75" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="76" spans="2:10">
-      <c r="B76" t="s">
-        <v>261</v>
-      </c>
-      <c r="C76" t="s">
-        <v>262</v>
-      </c>
-      <c r="D76" t="s">
-        <v>263</v>
-      </c>
-      <c r="E76" t="s">
-        <v>42</v>
-      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="K75">
+        <v>0</v>
+      </c>
+      <c r="L75">
+        <v>0</v>
+      </c>
+      <c r="M75">
+        <v>0</v>
+      </c>
+      <c r="N75">
+        <v>0</v>
+      </c>
+      <c r="O75">
+        <v>0</v>
+      </c>
+      <c r="P75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>item_discard_negative</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>断舍离</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>丢弃两个负面道具。</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="F76"/>
       <c r="G76">
         <v>2</v>
       </c>
+      <c r="H76"/>
       <c r="I76">
         <v>1</v>
       </c>
-      <c r="J76" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="77" spans="2:10">
-      <c r="B77" t="s">
-        <v>264</v>
-      </c>
-      <c r="C77" t="s">
-        <v>265</v>
-      </c>
-      <c r="D77" t="s">
-        <v>266</v>
-      </c>
-      <c r="E77" t="s">
-        <v>28</v>
-      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="K76">
+        <v>0</v>
+      </c>
+      <c r="L76">
+        <v>0</v>
+      </c>
+      <c r="M76">
+        <v>0</v>
+      </c>
+      <c r="N76">
+        <v>0</v>
+      </c>
+      <c r="O76">
+        <v>0</v>
+      </c>
+      <c r="P76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>item_discard_negative_gold</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>变废为宝</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>丢弃所有负面道具，每丢弃一个获得100金币。</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F77"/>
       <c r="G77">
         <v>100</v>
       </c>
+      <c r="H77"/>
       <c r="I77">
         <v>1</v>
       </c>
-      <c r="J77" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="78" spans="2:10">
-      <c r="B78" t="s">
-        <v>267</v>
-      </c>
-      <c r="C78" t="s">
-        <v>268</v>
-      </c>
-      <c r="D78" t="s">
-        <v>269</v>
-      </c>
-      <c r="E78" t="s">
-        <v>42</v>
-      </c>
-      <c r="F78" t="s">
-        <v>270</v>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="K77">
+        <v>0</v>
+      </c>
+      <c r="L77">
+        <v>0</v>
+      </c>
+      <c r="M77">
+        <v>0</v>
+      </c>
+      <c r="N77">
+        <v>0</v>
+      </c>
+      <c r="O77">
+        <v>0</v>
+      </c>
+      <c r="P77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>item_gold_meal_penalty</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>克扣工钱</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>美食获得的金币减少25%。</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
       </c>
       <c r="G78">
         <v>-0.25</v>
       </c>
+      <c r="H78"/>
       <c r="I78">
         <v>1</v>
       </c>
-      <c r="J78" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="79" spans="2:10">
-      <c r="B79" t="s">
-        <v>271</v>
-      </c>
-      <c r="C79" t="s">
-        <v>272</v>
-      </c>
-      <c r="D79" t="s">
-        <v>273</v>
-      </c>
-      <c r="E79" t="s">
-        <v>42</v>
-      </c>
-      <c r="F79" t="s">
-        <v>270</v>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>1,30</t>
+        </is>
+      </c>
+      <c r="K78">
+        <v>0</v>
+      </c>
+      <c r="L78">
+        <v>0</v>
+      </c>
+      <c r="M78">
+        <v>0</v>
+      </c>
+      <c r="N78">
+        <v>0</v>
+      </c>
+      <c r="O78">
+        <v>0</v>
+      </c>
+      <c r="P78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>item_shop_price_up</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>涨价</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>商店的价格变高25%。</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
       </c>
       <c r="G79">
         <v>0.25</v>
       </c>
+      <c r="H79"/>
       <c r="I79">
         <v>1</v>
       </c>
-      <c r="J79" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="80" spans="2:10">
-      <c r="B80" t="s">
-        <v>274</v>
-      </c>
-      <c r="C80" t="s">
-        <v>275</v>
-      </c>
-      <c r="D80" t="s">
-        <v>276</v>
-      </c>
-      <c r="E80" t="s">
-        <v>42</v>
-      </c>
-      <c r="F80" t="s">
-        <v>270</v>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>1,30</t>
+        </is>
+      </c>
+      <c r="K79">
+        <v>0</v>
+      </c>
+      <c r="L79">
+        <v>0</v>
+      </c>
+      <c r="M79">
+        <v>0</v>
+      </c>
+      <c r="N79">
+        <v>0</v>
+      </c>
+      <c r="O79">
+        <v>0</v>
+      </c>
+      <c r="P79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>item_no_remove</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>囤积癖</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>无法再删除食物。</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
       </c>
       <c r="G80">
         <v>0</v>
       </c>
+      <c r="H80"/>
       <c r="I80">
         <v>1</v>
       </c>
-      <c r="J80" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="81" spans="2:10">
-      <c r="B81" t="s">
-        <v>277</v>
-      </c>
-      <c r="C81" t="s">
-        <v>278</v>
-      </c>
-      <c r="D81" t="s">
-        <v>279</v>
-      </c>
-      <c r="E81" t="s">
-        <v>42</v>
-      </c>
-      <c r="F81" t="s">
-        <v>270</v>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>1,30</t>
+        </is>
+      </c>
+      <c r="K80">
+        <v>0</v>
+      </c>
+      <c r="L80">
+        <v>0</v>
+      </c>
+      <c r="M80">
+        <v>0</v>
+      </c>
+      <c r="N80">
+        <v>0</v>
+      </c>
+      <c r="O80">
+        <v>0</v>
+      </c>
+      <c r="P80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>item_skip_node</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>停业整顿</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>跳过下一个商店或利息节点。</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
       </c>
       <c r="G81">
         <v>1</v>
       </c>
+      <c r="H81"/>
       <c r="I81">
         <v>1</v>
       </c>
-      <c r="J81" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="82" spans="2:10">
-      <c r="B82" t="s">
-        <v>280</v>
-      </c>
-      <c r="C82" t="s">
-        <v>281</v>
-      </c>
-      <c r="D82" t="s">
-        <v>282</v>
-      </c>
-      <c r="E82" t="s">
-        <v>42</v>
-      </c>
-      <c r="F82" t="s">
-        <v>270</v>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>1,30</t>
+        </is>
+      </c>
+      <c r="K81">
+        <v>0</v>
+      </c>
+      <c r="L81">
+        <v>0</v>
+      </c>
+      <c r="M81">
+        <v>0</v>
+      </c>
+      <c r="N81">
+        <v>0</v>
+      </c>
+      <c r="O81">
+        <v>0</v>
+      </c>
+      <c r="P81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>item_choice_minus1</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>选择困难</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>多选一食物时，可选数量-1。</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
       </c>
       <c r="G82">
         <v>-1</v>
       </c>
+      <c r="H82"/>
       <c r="I82">
         <v>1</v>
       </c>
-      <c r="J82" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="83" spans="2:10">
-      <c r="B83" t="s">
-        <v>283</v>
-      </c>
-      <c r="C83" t="s">
-        <v>284</v>
-      </c>
-      <c r="D83" t="s">
-        <v>285</v>
-      </c>
-      <c r="E83" t="s">
-        <v>42</v>
-      </c>
-      <c r="F83" t="s">
-        <v>270</v>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>1,30</t>
+        </is>
+      </c>
+      <c r="K82">
+        <v>0</v>
+      </c>
+      <c r="L82">
+        <v>0</v>
+      </c>
+      <c r="M82">
+        <v>0</v>
+      </c>
+      <c r="N82">
+        <v>0</v>
+      </c>
+      <c r="O82">
+        <v>0</v>
+      </c>
+      <c r="P82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>item_req_normal_up</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>家常加码</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>普通美食要求分数+10%。</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
       </c>
       <c r="G83">
         <v>0.1</v>
       </c>
+      <c r="H83"/>
       <c r="I83">
         <v>1</v>
       </c>
-      <c r="J83" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="84" spans="2:10">
-      <c r="B84" t="s">
-        <v>286</v>
-      </c>
-      <c r="C84" t="s">
-        <v>287</v>
-      </c>
-      <c r="D84" t="s">
-        <v>288</v>
-      </c>
-      <c r="E84" t="s">
-        <v>42</v>
-      </c>
-      <c r="F84" t="s">
-        <v>270</v>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>1,30</t>
+        </is>
+      </c>
+      <c r="K83">
+        <v>0</v>
+      </c>
+      <c r="L83">
+        <v>0</v>
+      </c>
+      <c r="M83">
+        <v>0</v>
+      </c>
+      <c r="N83">
+        <v>0</v>
+      </c>
+      <c r="O83">
+        <v>0</v>
+      </c>
+      <c r="P83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>item_req_super_up</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>超级加码</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>超级美食要求分数+10%。</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
       </c>
       <c r="G84">
         <v>0.1</v>
       </c>
+      <c r="H84"/>
       <c r="I84">
         <v>1</v>
       </c>
-      <c r="J84" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="85" spans="2:10">
-      <c r="B85" t="s">
-        <v>289</v>
-      </c>
-      <c r="C85" t="s">
-        <v>290</v>
-      </c>
-      <c r="D85" t="s">
-        <v>291</v>
-      </c>
-      <c r="E85" t="s">
-        <v>42</v>
-      </c>
-      <c r="F85" t="s">
-        <v>270</v>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>1,30</t>
+        </is>
+      </c>
+      <c r="K84">
+        <v>0</v>
+      </c>
+      <c r="L84">
+        <v>0</v>
+      </c>
+      <c r="M84">
+        <v>0</v>
+      </c>
+      <c r="N84">
+        <v>0</v>
+      </c>
+      <c r="O84">
+        <v>0</v>
+      </c>
+      <c r="P84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>item_req_feast_up</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>盛宴加码</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>盛宴美食要求分数+10%。</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
       </c>
       <c r="G85">
         <v>0.1</v>
       </c>
+      <c r="H85"/>
       <c r="I85">
         <v>1</v>
       </c>
-      <c r="J85" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="86" spans="2:10">
-      <c r="B86" t="s">
-        <v>292</v>
-      </c>
-      <c r="C86" t="s">
-        <v>293</v>
-      </c>
-      <c r="D86" t="s">
-        <v>294</v>
-      </c>
-      <c r="E86" t="s">
-        <v>42</v>
-      </c>
-      <c r="F86" t="s">
-        <v>270</v>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>1,30</t>
+        </is>
+      </c>
+      <c r="K85">
+        <v>0</v>
+      </c>
+      <c r="L85">
+        <v>0</v>
+      </c>
+      <c r="M85">
+        <v>0</v>
+      </c>
+      <c r="N85">
+        <v>0</v>
+      </c>
+      <c r="O85">
+        <v>0</v>
+      </c>
+      <c r="P85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>item_gold_week_clear</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>月光族</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>本周结束时，金币清空。</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
       </c>
       <c r="G86">
         <v>0</v>
       </c>
+      <c r="H86"/>
       <c r="I86">
         <v>1</v>
       </c>
-      <c r="J86" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="87" spans="2:10">
-      <c r="B87" t="s">
-        <v>295</v>
-      </c>
-      <c r="C87" t="s">
-        <v>296</v>
-      </c>
-      <c r="D87" t="s">
-        <v>297</v>
-      </c>
-      <c r="E87" t="s">
-        <v>52</v>
-      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>1,30</t>
+        </is>
+      </c>
+      <c r="K86">
+        <v>0</v>
+      </c>
+      <c r="L86">
+        <v>0</v>
+      </c>
+      <c r="M86">
+        <v>0</v>
+      </c>
+      <c r="N86">
+        <v>0</v>
+      </c>
+      <c r="O86">
+        <v>0</v>
+      </c>
+      <c r="P86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>item_count_as_all</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>小份主义</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>所有食物额外被视为1个食物。</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F87"/>
       <c r="G87">
         <v>1</v>
       </c>
+      <c r="H87"/>
       <c r="I87">
         <v>1</v>
       </c>
-      <c r="J87" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="88" spans="2:10">
-      <c r="B88" t="s">
-        <v>298</v>
-      </c>
-      <c r="C88" t="s">
-        <v>299</v>
-      </c>
-      <c r="D88" t="s">
-        <v>300</v>
-      </c>
-      <c r="E88" t="s">
-        <v>52</v>
-      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>20,65</t>
+        </is>
+      </c>
+      <c r="K87">
+        <v>0</v>
+      </c>
+      <c r="L87">
+        <v>0</v>
+      </c>
+      <c r="M87">
+        <v>0</v>
+      </c>
+      <c r="N87">
+        <v>0</v>
+      </c>
+      <c r="O87">
+        <v>0</v>
+      </c>
+      <c r="P87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>item_transfer_target_mult</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>传递受益</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>传递时，被传递方倍率×1.1。</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F88"/>
       <c r="G88">
         <v>1.1</v>
       </c>
+      <c r="H88"/>
       <c r="I88">
         <v>1</v>
       </c>
-      <c r="J88" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="89" spans="2:10">
-      <c r="B89" t="s">
-        <v>301</v>
-      </c>
-      <c r="C89" t="s">
-        <v>302</v>
-      </c>
-      <c r="D89" t="s">
-        <v>303</v>
-      </c>
-      <c r="E89" t="s">
-        <v>52</v>
-      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>20,65</t>
+        </is>
+      </c>
+      <c r="K88">
+        <v>0</v>
+      </c>
+      <c r="L88">
+        <v>0</v>
+      </c>
+      <c r="M88">
+        <v>0</v>
+      </c>
+      <c r="N88">
+        <v>0</v>
+      </c>
+      <c r="O88">
+        <v>0</v>
+      </c>
+      <c r="P88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>item_transfer_source_mult</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>传递奉献</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>传递时，传递方倍率×1.1。</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F89"/>
       <c r="G89">
         <v>1.1</v>
       </c>
+      <c r="H89"/>
       <c r="I89">
         <v>1</v>
       </c>
-      <c r="J89" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="90" spans="2:10">
-      <c r="B90" t="s">
-        <v>304</v>
-      </c>
-      <c r="C90" t="s">
-        <v>305</v>
-      </c>
-      <c r="D90" t="s">
-        <v>306</v>
-      </c>
-      <c r="E90" t="s">
-        <v>52</v>
-      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>20,65</t>
+        </is>
+      </c>
+      <c r="K89">
+        <v>0</v>
+      </c>
+      <c r="L89">
+        <v>0</v>
+      </c>
+      <c r="M89">
+        <v>0</v>
+      </c>
+      <c r="N89">
+        <v>0</v>
+      </c>
+      <c r="O89">
+        <v>0</v>
+      </c>
+      <c r="P89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>item_skill_count_mult</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>技法大师</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>结算时每一个技能，所有食物倍率+0.1。</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F90"/>
       <c r="G90">
         <v>0.1</v>
       </c>
+      <c r="H90"/>
       <c r="I90">
         <v>1</v>
       </c>
-      <c r="J90" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="91" spans="2:10">
-      <c r="B91" t="s">
-        <v>307</v>
-      </c>
-      <c r="C91" t="s">
-        <v>308</v>
-      </c>
-      <c r="D91" t="s">
-        <v>309</v>
-      </c>
-      <c r="E91" t="s">
-        <v>28</v>
-      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>20,65</t>
+        </is>
+      </c>
+      <c r="K90">
+        <v>0</v>
+      </c>
+      <c r="L90">
+        <v>0</v>
+      </c>
+      <c r="M90">
+        <v>0</v>
+      </c>
+      <c r="N90">
+        <v>0</v>
+      </c>
+      <c r="O90">
+        <v>0</v>
+      </c>
+      <c r="P90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>item_gold_on_transfer</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>传递分红</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>传递10次后，获得10金币。</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F91"/>
       <c r="G91">
         <v>10</v>
       </c>
-      <c r="H91" t="s">
-        <v>310</v>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>count:10</t>
+        </is>
       </c>
       <c r="I91">
         <v>1</v>
       </c>
-      <c r="J91" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="92" spans="2:10">
-      <c r="B92" t="s">
-        <v>311</v>
-      </c>
-      <c r="C92" t="s">
-        <v>312</v>
-      </c>
-      <c r="D92" t="s">
-        <v>313</v>
-      </c>
-      <c r="E92" t="s">
-        <v>52</v>
-      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>5,45</t>
+        </is>
+      </c>
+      <c r="K91">
+        <v>0</v>
+      </c>
+      <c r="L91">
+        <v>0</v>
+      </c>
+      <c r="M91">
+        <v>0</v>
+      </c>
+      <c r="N91">
+        <v>0</v>
+      </c>
+      <c r="O91">
+        <v>0</v>
+      </c>
+      <c r="P91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>item_cake_retain</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>蛋糕保鲜</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>每次保留10%的蛋糕层数至下一次美食。</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F92"/>
       <c r="G92">
         <v>0.1</v>
       </c>
+      <c r="H92"/>
       <c r="I92">
         <v>1</v>
       </c>
-      <c r="J92" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="93" spans="2:10">
-      <c r="B93" t="s">
-        <v>314</v>
-      </c>
-      <c r="C93" t="s">
-        <v>315</v>
-      </c>
-      <c r="D93" t="s">
-        <v>316</v>
-      </c>
-      <c r="E93" t="s">
-        <v>28</v>
-      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>20,65</t>
+        </is>
+      </c>
+      <c r="K92">
+        <v>0</v>
+      </c>
+      <c r="L92">
+        <v>0</v>
+      </c>
+      <c r="M92">
+        <v>0</v>
+      </c>
+      <c r="N92">
+        <v>0</v>
+      </c>
+      <c r="O92">
+        <v>0</v>
+      </c>
+      <c r="P92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>item_cake_init_bonus</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>蛋糕打底</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>蛋糕层数初始额外获得10层。</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F93"/>
       <c r="G93">
         <v>10</v>
       </c>
+      <c r="H93"/>
       <c r="I93">
         <v>1</v>
       </c>
-      <c r="J93" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="94" spans="2:10">
-      <c r="B94" t="s">
-        <v>317</v>
-      </c>
-      <c r="C94" t="s">
-        <v>318</v>
-      </c>
-      <c r="D94" t="s">
-        <v>319</v>
-      </c>
-      <c r="E94" t="s">
-        <v>52</v>
-      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>5,45</t>
+        </is>
+      </c>
+      <c r="K93">
+        <v>0</v>
+      </c>
+      <c r="L93">
+        <v>0</v>
+      </c>
+      <c r="M93">
+        <v>0</v>
+      </c>
+      <c r="N93">
+        <v>0</v>
+      </c>
+      <c r="O93">
+        <v>0</v>
+      </c>
+      <c r="P93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>item_cake_accel</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>蛋糕膨胀</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>蛋糕层数增加时，额外加1层。</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F94"/>
       <c r="G94">
         <v>1</v>
       </c>
+      <c r="H94"/>
       <c r="I94">
         <v>1</v>
       </c>
-      <c r="J94" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="95" spans="2:10">
-      <c r="B95" t="s">
-        <v>320</v>
-      </c>
-      <c r="C95" t="s">
-        <v>321</v>
-      </c>
-      <c r="D95" t="s">
-        <v>322</v>
-      </c>
-      <c r="E95" t="s">
-        <v>28</v>
-      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>20,65</t>
+        </is>
+      </c>
+      <c r="K94">
+        <v>0</v>
+      </c>
+      <c r="L94">
+        <v>0</v>
+      </c>
+      <c r="M94">
+        <v>0</v>
+      </c>
+      <c r="N94">
+        <v>0</v>
+      </c>
+      <c r="O94">
+        <v>0</v>
+      </c>
+      <c r="P94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>item_cake_to_gold</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>蛋糕变现</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>蛋糕层数大于100层时，获得10金币。</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F95"/>
       <c r="G95">
         <v>10</v>
       </c>
-      <c r="H95" t="s">
-        <v>323</v>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>threshold:100</t>
+        </is>
       </c>
       <c r="I95">
         <v>1</v>
       </c>
-      <c r="J95" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="96" spans="2:10">
-      <c r="B96" t="s">
-        <v>324</v>
-      </c>
-      <c r="C96" t="s">
-        <v>325</v>
-      </c>
-      <c r="D96" t="s">
-        <v>326</v>
-      </c>
-      <c r="E96" t="s">
-        <v>28</v>
-      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>5,45</t>
+        </is>
+      </c>
+      <c r="K95">
+        <v>0</v>
+      </c>
+      <c r="L95">
+        <v>0</v>
+      </c>
+      <c r="M95">
+        <v>0</v>
+      </c>
+      <c r="N95">
+        <v>0</v>
+      </c>
+      <c r="O95">
+        <v>0</v>
+      </c>
+      <c r="P95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>item_cake_req_minus</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>蛋糕捷径</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>蛋糕效果需求的层数-10。</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F96"/>
       <c r="G96">
         <v>10</v>
       </c>
+      <c r="H96"/>
       <c r="I96">
         <v>1</v>
       </c>
-      <c r="J96" t="s">
-        <v>64</v>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>5,45</t>
+        </is>
+      </c>
+      <c r="K96">
+        <v>0</v>
+      </c>
+      <c r="L96">
+        <v>0</v>
+      </c>
+      <c r="M96">
+        <v>0</v>
+      </c>
+      <c r="N96">
+        <v>0</v>
+      </c>
+      <c r="O96">
+        <v>0</v>
+      </c>
+      <c r="P96">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/GourmetProject/GameConfig/Datas/item.xlsx
+++ b/GourmetProject/GameConfig/Datas/item.xlsx
@@ -4,32 +4,19 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16760"/>
+    <workbookView windowHeight="15200"/>
   </bookViews>
   <sheets>
     <sheet name="被动道具" sheetId="1" r:id="rId1"/>
     <sheet name="主动道具" sheetId="2" r:id="rId2"/>
     <sheet name="道具设计" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="929" uniqueCount="612">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="947" uniqueCount="624">
   <si>
     <t>##var</t>
   </si>
@@ -61,6 +48,24 @@
     <t>hiddenRange</t>
   </si>
   <si>
+    <t>targetScoreHiddenOffset</t>
+  </si>
+  <si>
+    <t>dishHiddenOffset</t>
+  </si>
+  <si>
+    <t>passiveItemHiddenOffset</t>
+  </si>
+  <si>
+    <t>activeItemHiddenOffset</t>
+  </si>
+  <si>
+    <t>fragmentHiddenOffset</t>
+  </si>
+  <si>
+    <t>goldHiddenOffset</t>
+  </si>
+  <si>
     <t>##comment</t>
   </si>
   <si>
@@ -91,6 +96,24 @@
     <t>出现隐藏分区间(单元格: min,max)</t>
   </si>
   <si>
+    <t>目标分隐藏分常驻修正。</t>
+  </si>
+  <si>
+    <t>食物奖励隐藏分常驻修正。</t>
+  </si>
+  <si>
+    <t>被动道具奖励隐藏分常驻修正。</t>
+  </si>
+  <si>
+    <t>主动道具奖励隐藏分常驻修正。</t>
+  </si>
+  <si>
+    <t>餐桌格子奖励隐藏分常驻修正。</t>
+  </si>
+  <si>
+    <t>金币奖励隐藏分常驻修正。</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -106,6 +129,9 @@
     <t>HiddenRange</t>
   </si>
   <si>
+    <t>int</t>
+  </si>
+  <si>
     <t>item_grant_two_passive</t>
   </si>
   <si>
@@ -1031,9 +1057,6 @@
   </si>
   <si>
     <t>ItemTargetKind</t>
-  </si>
-  <si>
-    <t>int</t>
   </si>
   <si>
     <t/>
@@ -1870,7 +1893,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -2881,290 +2904,198 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:P96"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <cols>
+    <col min="1" max="1" width="13.0769230769231" customWidth="1"/>
+    <col min="2" max="2" width="30.3846153846154" customWidth="1"/>
+    <col min="3" max="3" width="15.1538461538462" customWidth="1"/>
+    <col min="4" max="4" width="50" customWidth="1"/>
+    <col min="5" max="5" width="12.8461538461538" customWidth="1"/>
+    <col min="6" max="6" width="15.1538461538462" customWidth="1"/>
+    <col min="7" max="7" width="11.9230769230769" customWidth="1"/>
+    <col min="8" max="8" width="13.7692307692308" customWidth="1"/>
+    <col min="9" max="9" width="15.1538461538462" customWidth="1"/>
+    <col min="10" max="10" width="36" customWidth="1"/>
+    <col min="11" max="11" width="27.3076923076923" customWidth="1"/>
+    <col min="12" max="12" width="29.6923076923077" customWidth="1"/>
+    <col min="13" max="15" width="34.5384615384615" customWidth="1"/>
+    <col min="16" max="16" width="29.6923076923077" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>##var</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>desc</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>quality</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>specialTags</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>effectValue</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>effectParam</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>baseWeight</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>hiddenRange</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>targetScoreHiddenOffset</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>dishHiddenOffset</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>passiveItemHiddenOffset</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>activeItemHiddenOffset</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>fragmentHiddenOffset</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>goldHiddenOffset</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>##comment</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>道具ID</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>道具名称</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>道具描述</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>道具品质</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>特殊标签标记</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>效果数值</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>效果参数</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>随机基础权重</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>出现隐藏分区间(单元格: min,max)</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>目标分隐藏分常驻修正。</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>食物奖励隐藏分常驻修正。</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>被动道具奖励隐藏分常驻修正。</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>主动道具奖励隐藏分常驻修正。</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>餐桌格子奖励隐藏分常驻修正。</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>金币奖励隐藏分常驻修正。</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>##type</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>ItemQuality</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>HiddenRange</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>item_grant_two_passive</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>随机被动包</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>获得两个随机被动道具。</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="F4"/>
+    <row r="1" spans="1:16">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
+      <c r="A2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K2" t="s">
+        <v>26</v>
+      </c>
+      <c r="L2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N2" t="s">
+        <v>29</v>
+      </c>
+      <c r="O2" t="s">
+        <v>30</v>
+      </c>
+      <c r="P2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
+      <c r="A3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I3" t="s">
+        <v>35</v>
+      </c>
+      <c r="J3" t="s">
+        <v>36</v>
+      </c>
+      <c r="K3" t="s">
+        <v>37</v>
+      </c>
+      <c r="L3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M3" t="s">
+        <v>37</v>
+      </c>
+      <c r="N3" t="s">
+        <v>37</v>
+      </c>
+      <c r="O3" t="s">
+        <v>37</v>
+      </c>
+      <c r="P3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="2:16">
+      <c r="B4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E4" t="s">
+        <v>41</v>
+      </c>
       <c r="G4">
         <v>2</v>
       </c>
-      <c r="H4"/>
       <c r="I4">
         <v>1</v>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
+      <c r="J4" t="s">
+        <v>42</v>
       </c>
       <c r="K4">
         <v>0</v>
@@ -3185,39 +3116,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>item_choose_one_passive</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>被动三选一</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>从多个被动道具中选择一个获得。</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="F5"/>
+    <row r="5" spans="2:16">
+      <c r="B5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D5" t="s">
+        <v>45</v>
+      </c>
+      <c r="E5" t="s">
+        <v>41</v>
+      </c>
       <c r="G5">
         <v>3</v>
       </c>
-      <c r="H5"/>
       <c r="I5">
         <v>1</v>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
+      <c r="J5" t="s">
+        <v>42</v>
       </c>
       <c r="K5">
         <v>0</v>
@@ -3238,39 +3157,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6">
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>item_grant_two_active</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>随机主动包</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>获得两个随机主动道具。</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="F6"/>
+    <row r="6" spans="2:16">
+      <c r="B6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E6" t="s">
+        <v>41</v>
+      </c>
       <c r="G6">
         <v>2</v>
       </c>
-      <c r="H6"/>
       <c r="I6">
         <v>1</v>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
+      <c r="J6" t="s">
+        <v>42</v>
       </c>
       <c r="K6">
         <v>0</v>
@@ -3291,39 +3198,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7">
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>item_choose_one_active</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>主动三选一</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>从多个主动道具中选择一个获得。</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="F7"/>
+    <row r="7" spans="2:16">
+      <c r="B7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C7" t="s">
+        <v>50</v>
+      </c>
+      <c r="D7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E7" t="s">
+        <v>41</v>
+      </c>
       <c r="G7">
         <v>3</v>
       </c>
-      <c r="H7"/>
       <c r="I7">
         <v>1</v>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
+      <c r="J7" t="s">
+        <v>42</v>
       </c>
       <c r="K7">
         <v>0</v>
@@ -3344,39 +3239,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8">
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>item_choose_one_food</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>食物三选一</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>从多个食物中选择一个获得。</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="F8"/>
+    <row r="8" spans="2:16">
+      <c r="B8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C8" t="s">
+        <v>53</v>
+      </c>
+      <c r="D8" t="s">
+        <v>54</v>
+      </c>
+      <c r="E8" t="s">
+        <v>55</v>
+      </c>
       <c r="G8">
         <v>3</v>
       </c>
-      <c r="H8"/>
       <c r="I8">
         <v>1</v>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
+      <c r="J8" t="s">
+        <v>42</v>
       </c>
       <c r="K8">
         <v>0</v>
@@ -3397,39 +3280,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9">
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>item_choose_one_fragment</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>碎片三选一</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>从多个胃部碎片中选择一个获得。</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="F9"/>
+    <row r="9" spans="2:16">
+      <c r="B9" t="s">
+        <v>56</v>
+      </c>
+      <c r="C9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D9" t="s">
+        <v>58</v>
+      </c>
+      <c r="E9" t="s">
+        <v>41</v>
+      </c>
       <c r="G9">
         <v>3</v>
       </c>
-      <c r="H9"/>
       <c r="I9">
         <v>1</v>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
+      <c r="J9" t="s">
+        <v>42</v>
       </c>
       <c r="K9">
         <v>0</v>
@@ -3450,39 +3321,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10">
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>item_grant_recipe</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>菜谱券</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>获得一个菜谱。</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="F10"/>
+    <row r="10" spans="2:16">
+      <c r="B10" t="s">
+        <v>59</v>
+      </c>
+      <c r="C10" t="s">
+        <v>60</v>
+      </c>
+      <c r="D10" t="s">
+        <v>61</v>
+      </c>
+      <c r="E10" t="s">
+        <v>41</v>
+      </c>
       <c r="G10">
         <v>1</v>
       </c>
-      <c r="H10"/>
       <c r="I10">
         <v>1</v>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
+      <c r="J10" t="s">
+        <v>42</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -3503,39 +3362,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11">
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>item_family_pack</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>全家福</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>获得一个随机被动道具、随机食物、50金币。</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="F11"/>
+    <row r="11" spans="2:16">
+      <c r="B11" t="s">
+        <v>62</v>
+      </c>
+      <c r="C11" t="s">
+        <v>63</v>
+      </c>
+      <c r="D11" t="s">
+        <v>64</v>
+      </c>
+      <c r="E11" t="s">
+        <v>65</v>
+      </c>
       <c r="G11">
         <v>50</v>
       </c>
-      <c r="H11"/>
       <c r="I11">
         <v>1</v>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
+      <c r="J11" t="s">
+        <v>42</v>
       </c>
       <c r="K11">
         <v>0</v>
@@ -3556,39 +3403,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12">
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>item_randomize_items</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>混沌重置</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>所有道具替换为随机道具。</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="F12"/>
+    <row r="12" spans="2:16">
+      <c r="B12" t="s">
+        <v>66</v>
+      </c>
+      <c r="C12" t="s">
+        <v>67</v>
+      </c>
+      <c r="D12" t="s">
+        <v>68</v>
+      </c>
+      <c r="E12" t="s">
+        <v>65</v>
+      </c>
       <c r="G12">
         <v>0</v>
       </c>
-      <c r="H12"/>
       <c r="I12">
         <v>1</v>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
+      <c r="J12" t="s">
+        <v>42</v>
       </c>
       <c r="K12">
         <v>0</v>
@@ -3609,43 +3444,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13">
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>item_gold_random</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>随机金币</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>获得 1~100 个金币。</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="F13"/>
+    <row r="13" spans="2:16">
+      <c r="B13" t="s">
+        <v>69</v>
+      </c>
+      <c r="C13" t="s">
+        <v>70</v>
+      </c>
+      <c r="D13" t="s">
+        <v>71</v>
+      </c>
+      <c r="E13" t="s">
+        <v>55</v>
+      </c>
       <c r="G13">
         <v>0</v>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>range:1,100</t>
-        </is>
+      <c r="H13" t="s">
+        <v>72</v>
       </c>
       <c r="I13">
         <v>1</v>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
+      <c r="J13" t="s">
+        <v>42</v>
       </c>
       <c r="K13">
         <v>0</v>
@@ -3666,43 +3488,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14">
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>item_gold_meal_bonus</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>美食分红</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>接下来10局美食，额外获得15金币。</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="F14"/>
+    <row r="14" spans="2:16">
+      <c r="B14" t="s">
+        <v>73</v>
+      </c>
+      <c r="C14" t="s">
+        <v>74</v>
+      </c>
+      <c r="D14" t="s">
+        <v>75</v>
+      </c>
+      <c r="E14" t="s">
+        <v>41</v>
+      </c>
       <c r="G14">
         <v>15</v>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>meals:10</t>
-        </is>
+      <c r="H14" t="s">
+        <v>76</v>
       </c>
       <c r="I14">
         <v>1</v>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>5,45</t>
-        </is>
+      <c r="J14" t="s">
+        <v>77</v>
       </c>
       <c r="K14">
         <v>0</v>
@@ -3723,39 +3532,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15">
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>item_gold_boss</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Boss赏金</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>完成本次 Boss 后，额外获得100金币。</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="F15"/>
+    <row r="15" spans="2:16">
+      <c r="B15" t="s">
+        <v>78</v>
+      </c>
+      <c r="C15" t="s">
+        <v>79</v>
+      </c>
+      <c r="D15" t="s">
+        <v>80</v>
+      </c>
+      <c r="E15" t="s">
+        <v>41</v>
+      </c>
       <c r="G15">
         <v>100</v>
       </c>
-      <c r="H15"/>
       <c r="I15">
         <v>1</v>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>5,45</t>
-        </is>
+      <c r="J15" t="s">
+        <v>77</v>
       </c>
       <c r="K15">
         <v>0</v>
@@ -3776,39 +3573,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16">
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>item_gold_percent</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>利润提成</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>美食结束获得的金币，额外获得20%。</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="F16"/>
+    <row r="16" spans="2:16">
+      <c r="B16" t="s">
+        <v>81</v>
+      </c>
+      <c r="C16" t="s">
+        <v>82</v>
+      </c>
+      <c r="D16" t="s">
+        <v>83</v>
+      </c>
+      <c r="E16" t="s">
+        <v>65</v>
+      </c>
       <c r="G16">
         <v>0.2</v>
       </c>
-      <c r="H16"/>
       <c r="I16">
         <v>1</v>
       </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>20,65</t>
-        </is>
+      <c r="J16" t="s">
+        <v>84</v>
       </c>
       <c r="K16">
         <v>0</v>
@@ -3829,39 +3614,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17">
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>item_discount_food</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>食材优惠券</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>购买食物打折20%。</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="F17"/>
+    <row r="17" spans="2:16">
+      <c r="B17" t="s">
+        <v>85</v>
+      </c>
+      <c r="C17" t="s">
+        <v>86</v>
+      </c>
+      <c r="D17" t="s">
+        <v>87</v>
+      </c>
+      <c r="E17" t="s">
+        <v>55</v>
+      </c>
       <c r="G17">
         <v>0.2</v>
       </c>
-      <c r="H17"/>
       <c r="I17">
         <v>1</v>
       </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>1,30</t>
-        </is>
+      <c r="J17" t="s">
+        <v>88</v>
       </c>
       <c r="K17">
         <v>0</v>
@@ -3882,39 +3655,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18">
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>item_discount_fragment</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>碎片优惠券</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>购买碎片打折20%。</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="F18"/>
+    <row r="18" spans="2:16">
+      <c r="B18" t="s">
+        <v>89</v>
+      </c>
+      <c r="C18" t="s">
+        <v>90</v>
+      </c>
+      <c r="D18" t="s">
+        <v>91</v>
+      </c>
+      <c r="E18" t="s">
+        <v>55</v>
+      </c>
       <c r="G18">
         <v>0.2</v>
       </c>
-      <c r="H18"/>
       <c r="I18">
         <v>1</v>
       </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>1,30</t>
-        </is>
+      <c r="J18" t="s">
+        <v>88</v>
       </c>
       <c r="K18">
         <v>0</v>
@@ -3935,39 +3696,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19">
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>item_discount_active</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>主动道具券</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>购买主动道具打折20%。</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="F19"/>
+    <row r="19" spans="2:16">
+      <c r="B19" t="s">
+        <v>92</v>
+      </c>
+      <c r="C19" t="s">
+        <v>93</v>
+      </c>
+      <c r="D19" t="s">
+        <v>94</v>
+      </c>
+      <c r="E19" t="s">
+        <v>55</v>
+      </c>
       <c r="G19">
         <v>0.2</v>
       </c>
-      <c r="H19"/>
       <c r="I19">
         <v>1</v>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>1,30</t>
-        </is>
+      <c r="J19" t="s">
+        <v>88</v>
       </c>
       <c r="K19">
         <v>0</v>
@@ -3988,39 +3737,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20">
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>item_discount_passive</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>被动道具券</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>购买被动道具打折20%。</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="F20"/>
+    <row r="20" spans="2:16">
+      <c r="B20" t="s">
+        <v>95</v>
+      </c>
+      <c r="C20" t="s">
+        <v>96</v>
+      </c>
+      <c r="D20" t="s">
+        <v>97</v>
+      </c>
+      <c r="E20" t="s">
+        <v>55</v>
+      </c>
       <c r="G20">
         <v>0.2</v>
       </c>
-      <c r="H20"/>
       <c r="I20">
         <v>1</v>
       </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>1,30</t>
-        </is>
+      <c r="J20" t="s">
+        <v>88</v>
       </c>
       <c r="K20">
         <v>0</v>
@@ -4041,39 +3778,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21">
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>item_discount_remove</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>删牌优惠</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>删牌价格打折20%。</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="F21"/>
+    <row r="21" spans="2:16">
+      <c r="B21" t="s">
+        <v>98</v>
+      </c>
+      <c r="C21" t="s">
+        <v>99</v>
+      </c>
+      <c r="D21" t="s">
+        <v>100</v>
+      </c>
+      <c r="E21" t="s">
+        <v>55</v>
+      </c>
       <c r="G21">
         <v>0.2</v>
       </c>
-      <c r="H21"/>
       <c r="I21">
         <v>1</v>
       </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>1,30</t>
-        </is>
+      <c r="J21" t="s">
+        <v>88</v>
       </c>
       <c r="K21">
         <v>0</v>
@@ -4094,39 +3819,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22">
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>item_remove_fixed_30</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>固定删牌价</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>删牌价格固定为30金币。</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="F22"/>
+    <row r="22" spans="2:16">
+      <c r="B22" t="s">
+        <v>101</v>
+      </c>
+      <c r="C22" t="s">
+        <v>102</v>
+      </c>
+      <c r="D22" t="s">
+        <v>103</v>
+      </c>
+      <c r="E22" t="s">
+        <v>41</v>
+      </c>
       <c r="G22">
         <v>30</v>
       </c>
-      <c r="H22"/>
       <c r="I22">
         <v>1</v>
       </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>5,45</t>
-        </is>
+      <c r="J22" t="s">
+        <v>77</v>
       </c>
       <c r="K22">
         <v>0</v>
@@ -4147,39 +3860,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23">
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>item_discount_recipe</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>菜谱优惠</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>购买菜谱打折20%。</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="F23"/>
+    <row r="23" spans="2:16">
+      <c r="B23" t="s">
+        <v>104</v>
+      </c>
+      <c r="C23" t="s">
+        <v>105</v>
+      </c>
+      <c r="D23" t="s">
+        <v>106</v>
+      </c>
+      <c r="E23" t="s">
+        <v>55</v>
+      </c>
       <c r="G23">
         <v>0.2</v>
       </c>
-      <c r="H23"/>
       <c r="I23">
         <v>1</v>
       </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>1,30</t>
-        </is>
+      <c r="J23" t="s">
+        <v>88</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -4200,39 +3901,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24">
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>item_famous_knife</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>名刀·加护</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>分数未达标时不失败，但会失去此道具。</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="F24"/>
+    <row r="24" spans="2:16">
+      <c r="B24" t="s">
+        <v>107</v>
+      </c>
+      <c r="C24" t="s">
+        <v>108</v>
+      </c>
+      <c r="D24" t="s">
+        <v>109</v>
+      </c>
+      <c r="E24" t="s">
+        <v>65</v>
+      </c>
       <c r="G24">
         <v>0</v>
       </c>
-      <c r="H24"/>
       <c r="I24">
         <v>1</v>
       </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>20,65</t>
-        </is>
+      <c r="J24" t="s">
+        <v>84</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -4253,43 +3942,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25">
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>item_score_to_one</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>免检通行证</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>接下来3局非盛宴，分数要求为1。</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="F25"/>
+    <row r="25" spans="2:16">
+      <c r="B25" t="s">
+        <v>110</v>
+      </c>
+      <c r="C25" t="s">
+        <v>111</v>
+      </c>
+      <c r="D25" t="s">
+        <v>112</v>
+      </c>
+      <c r="E25" t="s">
+        <v>65</v>
+      </c>
       <c r="G25">
         <v>0</v>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>meals:3</t>
-        </is>
+      <c r="H25" t="s">
+        <v>113</v>
       </c>
       <c r="I25">
         <v>1</v>
       </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
+      <c r="J25" t="s">
+        <v>42</v>
       </c>
       <c r="K25">
         <v>0</v>
@@ -4310,39 +3986,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26">
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>item_req_normal_down</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>家常减负</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>普通美食要求分数-10%。</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="F26"/>
+    <row r="26" spans="2:16">
+      <c r="B26" t="s">
+        <v>114</v>
+      </c>
+      <c r="C26" t="s">
+        <v>115</v>
+      </c>
+      <c r="D26" t="s">
+        <v>116</v>
+      </c>
+      <c r="E26" t="s">
+        <v>41</v>
+      </c>
       <c r="G26">
         <v>-0.1</v>
       </c>
-      <c r="H26"/>
       <c r="I26">
         <v>1</v>
       </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>5,45</t>
-        </is>
+      <c r="J26" t="s">
+        <v>77</v>
       </c>
       <c r="K26">
         <v>0</v>
@@ -4363,39 +4027,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>item_req_super_down</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>超级减负</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>超级美食要求分数-10%。</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="F27"/>
+    <row r="27" spans="2:16">
+      <c r="B27" t="s">
+        <v>117</v>
+      </c>
+      <c r="C27" t="s">
+        <v>118</v>
+      </c>
+      <c r="D27" t="s">
+        <v>119</v>
+      </c>
+      <c r="E27" t="s">
+        <v>41</v>
+      </c>
       <c r="G27">
         <v>-0.1</v>
       </c>
-      <c r="H27"/>
       <c r="I27">
         <v>1</v>
       </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>5,45</t>
-        </is>
+      <c r="J27" t="s">
+        <v>77</v>
       </c>
       <c r="K27">
         <v>0</v>
@@ -4416,39 +4068,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28">
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>item_req_feast_down</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>盛宴减负</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>盛宴美食要求分数-10%。</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="F28"/>
+    <row r="28" spans="2:16">
+      <c r="B28" t="s">
+        <v>120</v>
+      </c>
+      <c r="C28" t="s">
+        <v>121</v>
+      </c>
+      <c r="D28" t="s">
+        <v>122</v>
+      </c>
+      <c r="E28" t="s">
+        <v>41</v>
+      </c>
       <c r="G28">
         <v>-0.1</v>
       </c>
-      <c r="H28"/>
       <c r="I28">
         <v>1</v>
       </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>5,45</t>
-        </is>
+      <c r="J28" t="s">
+        <v>77</v>
       </c>
       <c r="K28">
         <v>0</v>
@@ -4469,43 +4109,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29">
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>item_count_le_mult</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>精致料理</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>结算时食物数量&lt;=10，所有美食倍率×1.1。</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="F29"/>
+    <row r="29" spans="2:16">
+      <c r="B29" t="s">
+        <v>123</v>
+      </c>
+      <c r="C29" t="s">
+        <v>124</v>
+      </c>
+      <c r="D29" t="s">
+        <v>125</v>
+      </c>
+      <c r="E29" t="s">
+        <v>41</v>
+      </c>
       <c r="G29">
         <v>1.1</v>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>lte:10</t>
-        </is>
+      <c r="H29" t="s">
+        <v>126</v>
       </c>
       <c r="I29">
         <v>1</v>
       </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>5,45</t>
-        </is>
+      <c r="J29" t="s">
+        <v>77</v>
       </c>
       <c r="K29">
         <v>0</v>
@@ -4526,43 +4153,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30">
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>item_count_ge_mult</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>丰盛大餐</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>结算时食物数量&gt;=10，所有美食倍率×1.1。</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="F30"/>
+    <row r="30" spans="2:16">
+      <c r="B30" t="s">
+        <v>127</v>
+      </c>
+      <c r="C30" t="s">
+        <v>128</v>
+      </c>
+      <c r="D30" t="s">
+        <v>129</v>
+      </c>
+      <c r="E30" t="s">
+        <v>41</v>
+      </c>
       <c r="G30">
         <v>1.1</v>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>gte:10</t>
-        </is>
+      <c r="H30" t="s">
+        <v>130</v>
       </c>
       <c r="I30">
         <v>1</v>
       </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>5,45</t>
-        </is>
+      <c r="J30" t="s">
+        <v>77</v>
       </c>
       <c r="K30">
         <v>0</v>
@@ -4583,39 +4197,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31">
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>item_per_dish_mult</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>流水席</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>结算时每结算1个食物，所有食物倍率+0.1。</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="F31"/>
+    <row r="31" spans="2:16">
+      <c r="B31" t="s">
+        <v>131</v>
+      </c>
+      <c r="C31" t="s">
+        <v>132</v>
+      </c>
+      <c r="D31" t="s">
+        <v>133</v>
+      </c>
+      <c r="E31" t="s">
+        <v>65</v>
+      </c>
       <c r="G31">
         <v>0.1</v>
       </c>
-      <c r="H31"/>
       <c r="I31">
         <v>1</v>
       </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>20,65</t>
-        </is>
+      <c r="J31" t="s">
+        <v>84</v>
       </c>
       <c r="K31">
         <v>0</v>
@@ -4636,39 +4238,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32">
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>item_perma_flat_all</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>增鲜剂</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>所有食物基础分数永久+10。</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="F32"/>
+    <row r="32" spans="2:16">
+      <c r="B32" t="s">
+        <v>134</v>
+      </c>
+      <c r="C32" t="s">
+        <v>135</v>
+      </c>
+      <c r="D32" t="s">
+        <v>136</v>
+      </c>
+      <c r="E32" t="s">
+        <v>65</v>
+      </c>
       <c r="G32">
         <v>10</v>
       </c>
-      <c r="H32"/>
       <c r="I32">
         <v>1</v>
       </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>20,65</t>
-        </is>
+      <c r="J32" t="s">
+        <v>84</v>
       </c>
       <c r="K32">
         <v>0</v>
@@ -4689,39 +4279,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33">
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>item_perma_mult_all</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>浓缩精华</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>所有食物基础倍率永久+0.2。</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="F33"/>
+    <row r="33" spans="2:16">
+      <c r="B33" t="s">
+        <v>137</v>
+      </c>
+      <c r="C33" t="s">
+        <v>138</v>
+      </c>
+      <c r="D33" t="s">
+        <v>139</v>
+      </c>
+      <c r="E33" t="s">
+        <v>65</v>
+      </c>
       <c r="G33">
         <v>0.2</v>
       </c>
-      <c r="H33"/>
       <c r="I33">
         <v>1</v>
       </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>20,65</t>
-        </is>
+      <c r="J33" t="s">
+        <v>84</v>
       </c>
       <c r="K33">
         <v>0</v>
@@ -4742,43 +4320,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34">
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>item_stargaze_every5</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>观星仪</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>每5次上菜后，下一次上菜可预见食物。</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="F34"/>
+    <row r="34" spans="2:16">
+      <c r="B34" t="s">
+        <v>140</v>
+      </c>
+      <c r="C34" t="s">
+        <v>141</v>
+      </c>
+      <c r="D34" t="s">
+        <v>142</v>
+      </c>
+      <c r="E34" t="s">
+        <v>41</v>
+      </c>
       <c r="G34">
         <v>0</v>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>every:5</t>
-        </is>
+      <c r="H34" t="s">
+        <v>143</v>
       </c>
       <c r="I34">
         <v>1</v>
       </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>5,45</t>
-        </is>
+      <c r="J34" t="s">
+        <v>77</v>
       </c>
       <c r="K34">
         <v>0</v>
@@ -4799,43 +4364,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35">
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>item_stargaze_first3</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>开局观星</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>每局前三次上菜可预见食物。</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="F35"/>
+    <row r="35" spans="2:16">
+      <c r="B35" t="s">
+        <v>144</v>
+      </c>
+      <c r="C35" t="s">
+        <v>145</v>
+      </c>
+      <c r="D35" t="s">
+        <v>146</v>
+      </c>
+      <c r="E35" t="s">
+        <v>41</v>
+      </c>
       <c r="G35">
         <v>0</v>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>first:3</t>
-        </is>
+      <c r="H35" t="s">
+        <v>147</v>
       </c>
       <c r="I35">
         <v>1</v>
       </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>5,45</t>
-        </is>
+      <c r="J35" t="s">
+        <v>77</v>
       </c>
       <c r="K35">
         <v>0</v>
@@ -4856,39 +4408,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36">
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>item_free_move_first</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>免费调整</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>每局第一次上菜后，可不消耗修正次数移动。</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="F36"/>
+    <row r="36" spans="2:16">
+      <c r="B36" t="s">
+        <v>148</v>
+      </c>
+      <c r="C36" t="s">
+        <v>149</v>
+      </c>
+      <c r="D36" t="s">
+        <v>150</v>
+      </c>
+      <c r="E36" t="s">
+        <v>41</v>
+      </c>
       <c r="G36">
         <v>0</v>
       </c>
-      <c r="H36"/>
       <c r="I36">
         <v>1</v>
       </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>5,45</t>
-        </is>
+      <c r="J36" t="s">
+        <v>77</v>
       </c>
       <c r="K36">
         <v>0</v>
@@ -4909,39 +4449,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37">
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>item_adjust_plus1</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>熟练的手</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>调整次数+1。</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="F37"/>
+    <row r="37" spans="2:16">
+      <c r="B37" t="s">
+        <v>151</v>
+      </c>
+      <c r="C37" t="s">
+        <v>152</v>
+      </c>
+      <c r="D37" t="s">
+        <v>153</v>
+      </c>
+      <c r="E37" t="s">
+        <v>55</v>
+      </c>
       <c r="G37">
         <v>1</v>
       </c>
-      <c r="H37"/>
       <c r="I37">
         <v>1</v>
       </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>1,30</t>
-        </is>
+      <c r="J37" t="s">
+        <v>88</v>
       </c>
       <c r="K37">
         <v>0</v>
@@ -4962,39 +4490,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38">
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>item_adjust_to_mult</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>节俭加成</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>每1个未使用的调整次数，使倍率+0.2。</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="F38"/>
+    <row r="38" spans="2:16">
+      <c r="B38" t="s">
+        <v>154</v>
+      </c>
+      <c r="C38" t="s">
+        <v>155</v>
+      </c>
+      <c r="D38" t="s">
+        <v>156</v>
+      </c>
+      <c r="E38" t="s">
+        <v>65</v>
+      </c>
       <c r="G38">
         <v>0.2</v>
       </c>
-      <c r="H38"/>
       <c r="I38">
         <v>1</v>
       </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>20,65</t>
-        </is>
+      <c r="J38" t="s">
+        <v>84</v>
       </c>
       <c r="K38">
         <v>0</v>
@@ -5015,39 +4531,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39">
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>item_food_convert</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>点石成金</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>随机将5个食物变为至少同品质的食物。</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="F39"/>
+    <row r="39" spans="2:16">
+      <c r="B39" t="s">
+        <v>157</v>
+      </c>
+      <c r="C39" t="s">
+        <v>158</v>
+      </c>
+      <c r="D39" t="s">
+        <v>159</v>
+      </c>
+      <c r="E39" t="s">
+        <v>65</v>
+      </c>
       <c r="G39">
         <v>5</v>
       </c>
-      <c r="H39"/>
       <c r="I39">
         <v>1</v>
       </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
+      <c r="J39" t="s">
+        <v>42</v>
       </c>
       <c r="K39">
         <v>0</v>
@@ -5068,39 +4572,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40">
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>item_adjust_to_gold</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>变卖技巧</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>每个未使用的调整次数，获得1金币。</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="F40"/>
+    <row r="40" spans="2:16">
+      <c r="B40" t="s">
+        <v>160</v>
+      </c>
+      <c r="C40" t="s">
+        <v>161</v>
+      </c>
+      <c r="D40" t="s">
+        <v>162</v>
+      </c>
+      <c r="E40" t="s">
+        <v>41</v>
+      </c>
       <c r="G40">
         <v>1</v>
       </c>
-      <c r="H40"/>
       <c r="I40">
         <v>1</v>
       </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>5,45</t>
-        </is>
+      <c r="J40" t="s">
+        <v>77</v>
       </c>
       <c r="K40">
         <v>0</v>
@@ -5121,39 +4613,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41">
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>item_gold_on_shop</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>商会返利</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>进入商店时，获得10金币。</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="F41"/>
+    <row r="41" spans="2:16">
+      <c r="B41" t="s">
+        <v>163</v>
+      </c>
+      <c r="C41" t="s">
+        <v>164</v>
+      </c>
+      <c r="D41" t="s">
+        <v>165</v>
+      </c>
+      <c r="E41" t="s">
+        <v>41</v>
+      </c>
       <c r="G41">
         <v>10</v>
       </c>
-      <c r="H41"/>
       <c r="I41">
         <v>1</v>
       </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>5,45</t>
-        </is>
+      <c r="J41" t="s">
+        <v>77</v>
       </c>
       <c r="K41">
         <v>0</v>
@@ -5174,39 +4654,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42">
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>item_extra_interest</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>复利账户</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>每周结束额外执行一次利息。</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="F42"/>
+    <row r="42" spans="2:16">
+      <c r="B42" t="s">
+        <v>166</v>
+      </c>
+      <c r="C42" t="s">
+        <v>167</v>
+      </c>
+      <c r="D42" t="s">
+        <v>168</v>
+      </c>
+      <c r="E42" t="s">
+        <v>65</v>
+      </c>
       <c r="G42">
         <v>1</v>
       </c>
-      <c r="H42"/>
       <c r="I42">
         <v>1</v>
       </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>20,65</t>
-        </is>
+      <c r="J42" t="s">
+        <v>84</v>
       </c>
       <c r="K42">
         <v>0</v>
@@ -5227,39 +4695,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43">
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>item_min_gold</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>保底基金</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>回合结束金币&lt;10时，补足到10金币。</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="F43"/>
+    <row r="43" spans="2:16">
+      <c r="B43" t="s">
+        <v>169</v>
+      </c>
+      <c r="C43" t="s">
+        <v>170</v>
+      </c>
+      <c r="D43" t="s">
+        <v>171</v>
+      </c>
+      <c r="E43" t="s">
+        <v>41</v>
+      </c>
       <c r="G43">
         <v>10</v>
       </c>
-      <c r="H43"/>
       <c r="I43">
         <v>1</v>
       </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>5,45</t>
-        </is>
+      <c r="J43" t="s">
+        <v>77</v>
       </c>
       <c r="K43">
         <v>0</v>
@@ -5280,39 +4736,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44">
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>item_interest_cap</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>高息账户</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>利息上限扩展到10金币。</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="F44"/>
+    <row r="44" spans="2:16">
+      <c r="B44" t="s">
+        <v>172</v>
+      </c>
+      <c r="C44" t="s">
+        <v>173</v>
+      </c>
+      <c r="D44" t="s">
+        <v>174</v>
+      </c>
+      <c r="E44" t="s">
+        <v>65</v>
+      </c>
       <c r="G44">
         <v>10</v>
       </c>
-      <c r="H44"/>
       <c r="I44">
         <v>1</v>
       </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>20,65</t>
-        </is>
+      <c r="J44" t="s">
+        <v>84</v>
       </c>
       <c r="K44">
         <v>0</v>
@@ -5333,43 +4777,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45">
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>item_loan</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>高利贷</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>临时获得300金币，下一周失去600金币。</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="F45"/>
+    <row r="45" spans="2:16">
+      <c r="B45" t="s">
+        <v>175</v>
+      </c>
+      <c r="C45" t="s">
+        <v>176</v>
+      </c>
+      <c r="D45" t="s">
+        <v>177</v>
+      </c>
+      <c r="E45" t="s">
+        <v>65</v>
+      </c>
       <c r="G45">
         <v>300</v>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>repay:600</t>
-        </is>
+      <c r="H45" t="s">
+        <v>178</v>
       </c>
       <c r="I45">
         <v>1</v>
       </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
+      <c r="J45" t="s">
+        <v>42</v>
       </c>
       <c r="K45">
         <v>0</v>
@@ -5390,39 +4821,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46">
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>item_timeline_random</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>命运骰子</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>随机化时间轴的节点事件。</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="F46"/>
+    <row r="46" spans="2:16">
+      <c r="B46" t="s">
+        <v>179</v>
+      </c>
+      <c r="C46" t="s">
+        <v>180</v>
+      </c>
+      <c r="D46" t="s">
+        <v>181</v>
+      </c>
+      <c r="E46" t="s">
+        <v>41</v>
+      </c>
       <c r="G46">
         <v>0</v>
       </c>
-      <c r="H46"/>
       <c r="I46">
         <v>1</v>
       </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
+      <c r="J46" t="s">
+        <v>42</v>
       </c>
       <c r="K46">
         <v>0</v>
@@ -5443,39 +4862,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47">
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>item_extra_day</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>加班一天</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>延后所有 Boss 一天。</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="F47"/>
+    <row r="47" spans="2:16">
+      <c r="B47" t="s">
+        <v>182</v>
+      </c>
+      <c r="C47" t="s">
+        <v>183</v>
+      </c>
+      <c r="D47" t="s">
+        <v>184</v>
+      </c>
+      <c r="E47" t="s">
+        <v>65</v>
+      </c>
       <c r="G47">
         <v>1</v>
       </c>
-      <c r="H47"/>
       <c r="I47">
         <v>1</v>
       </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
+      <c r="J47" t="s">
+        <v>42</v>
       </c>
       <c r="K47">
         <v>0</v>
@@ -5496,39 +4903,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48">
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>item_week_minus</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>时光倒流</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>周数-1。</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Epic</t>
-        </is>
-      </c>
-      <c r="F48"/>
+    <row r="48" spans="2:16">
+      <c r="B48" t="s">
+        <v>185</v>
+      </c>
+      <c r="C48" t="s">
+        <v>186</v>
+      </c>
+      <c r="D48" t="s">
+        <v>187</v>
+      </c>
+      <c r="E48" t="s">
+        <v>188</v>
+      </c>
       <c r="G48">
         <v>1</v>
       </c>
-      <c r="H48"/>
       <c r="I48">
         <v>1</v>
       </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
+      <c r="J48" t="s">
+        <v>42</v>
       </c>
       <c r="K48">
         <v>0</v>
@@ -5549,39 +4944,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49">
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>item_add_reward_node</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>额外奖励</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>增加一个奖励节点到时间轴上。</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="F49"/>
+    <row r="49" spans="2:16">
+      <c r="B49" t="s">
+        <v>189</v>
+      </c>
+      <c r="C49" t="s">
+        <v>190</v>
+      </c>
+      <c r="D49" t="s">
+        <v>191</v>
+      </c>
+      <c r="E49" t="s">
+        <v>41</v>
+      </c>
       <c r="G49">
         <v>1</v>
       </c>
-      <c r="H49"/>
       <c r="I49">
         <v>1</v>
       </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
+      <c r="J49" t="s">
+        <v>42</v>
       </c>
       <c r="K49">
         <v>0</v>
@@ -5602,39 +4985,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50">
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>item_add_interest_node</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>额外利息节点</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>增加一个利息节点到时间轴上。</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="F50"/>
+    <row r="50" spans="2:16">
+      <c r="B50" t="s">
+        <v>192</v>
+      </c>
+      <c r="C50" t="s">
+        <v>193</v>
+      </c>
+      <c r="D50" t="s">
+        <v>194</v>
+      </c>
+      <c r="E50" t="s">
+        <v>41</v>
+      </c>
       <c r="G50">
         <v>1</v>
       </c>
-      <c r="H50"/>
       <c r="I50">
         <v>1</v>
       </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
+      <c r="J50" t="s">
+        <v>42</v>
       </c>
       <c r="K50">
         <v>0</v>
@@ -5655,43 +5026,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51">
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>item_every3_next_mult</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>节奏大师</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>每上3个食物后，下一个食物倍率+2。</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="F51"/>
+    <row r="51" spans="2:16">
+      <c r="B51" t="s">
+        <v>195</v>
+      </c>
+      <c r="C51" t="s">
+        <v>196</v>
+      </c>
+      <c r="D51" t="s">
+        <v>197</v>
+      </c>
+      <c r="E51" t="s">
+        <v>65</v>
+      </c>
       <c r="G51">
         <v>2</v>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>every:3</t>
-        </is>
+      <c r="H51" t="s">
+        <v>198</v>
       </c>
       <c r="I51">
         <v>1</v>
       </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>20,65</t>
-        </is>
+      <c r="J51" t="s">
+        <v>84</v>
       </c>
       <c r="K51">
         <v>0</v>
@@ -5712,43 +5070,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52">
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>item_first_x2</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>开门红</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>第一个上的食物，倍率×2。</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="F52"/>
+    <row r="52" spans="2:16">
+      <c r="B52" t="s">
+        <v>199</v>
+      </c>
+      <c r="C52" t="s">
+        <v>200</v>
+      </c>
+      <c r="D52" t="s">
+        <v>201</v>
+      </c>
+      <c r="E52" t="s">
+        <v>41</v>
+      </c>
       <c r="G52">
         <v>2</v>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>index:1</t>
-        </is>
+      <c r="H52" t="s">
+        <v>202</v>
       </c>
       <c r="I52">
         <v>1</v>
       </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>5,45</t>
-        </is>
+      <c r="J52" t="s">
+        <v>77</v>
       </c>
       <c r="K52">
         <v>0</v>
@@ -5769,43 +5114,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53">
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>item_last_x2</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>压轴好戏</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>最后一个上的食物，倍率×2。</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="F53"/>
+    <row r="53" spans="2:16">
+      <c r="B53" t="s">
+        <v>203</v>
+      </c>
+      <c r="C53" t="s">
+        <v>204</v>
+      </c>
+      <c r="D53" t="s">
+        <v>205</v>
+      </c>
+      <c r="E53" t="s">
+        <v>41</v>
+      </c>
       <c r="G53">
         <v>2</v>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>index:-1</t>
-        </is>
+      <c r="H53" t="s">
+        <v>206</v>
       </c>
       <c r="I53">
         <v>1</v>
       </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>5,45</t>
-        </is>
+      <c r="J53" t="s">
+        <v>77</v>
       </c>
       <c r="K53">
         <v>0</v>
@@ -5826,39 +5158,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54">
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>item_extra_active_slots</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>工具箱</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>增加2个额外主动道具栏。</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="F54"/>
+    <row r="54" spans="2:16">
+      <c r="B54" t="s">
+        <v>207</v>
+      </c>
+      <c r="C54" t="s">
+        <v>208</v>
+      </c>
+      <c r="D54" t="s">
+        <v>209</v>
+      </c>
+      <c r="E54" t="s">
+        <v>65</v>
+      </c>
       <c r="G54">
         <v>2</v>
       </c>
-      <c r="H54"/>
       <c r="I54">
         <v>1</v>
       </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>20,65</t>
-        </is>
+      <c r="J54" t="s">
+        <v>84</v>
       </c>
       <c r="K54">
         <v>0</v>
@@ -5879,39 +5199,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55">
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>item_gold_on_active</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>以用换钱</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>使用主动道具时，获得20金币。</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="F55"/>
+    <row r="55" spans="2:16">
+      <c r="B55" t="s">
+        <v>210</v>
+      </c>
+      <c r="C55" t="s">
+        <v>211</v>
+      </c>
+      <c r="D55" t="s">
+        <v>212</v>
+      </c>
+      <c r="E55" t="s">
+        <v>41</v>
+      </c>
       <c r="G55">
         <v>20</v>
       </c>
-      <c r="H55"/>
       <c r="I55">
         <v>1</v>
       </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>5,45</t>
-        </is>
+      <c r="J55" t="s">
+        <v>77</v>
       </c>
       <c r="K55">
         <v>0</v>
@@ -5932,39 +5240,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56">
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>item_block_active</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>极简主义</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>无法获得主动道具，立即获得1000金币。</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Epic</t>
-        </is>
-      </c>
-      <c r="F56"/>
+    <row r="56" spans="2:16">
+      <c r="B56" t="s">
+        <v>213</v>
+      </c>
+      <c r="C56" t="s">
+        <v>214</v>
+      </c>
+      <c r="D56" t="s">
+        <v>215</v>
+      </c>
+      <c r="E56" t="s">
+        <v>188</v>
+      </c>
       <c r="G56">
         <v>1000</v>
       </c>
-      <c r="H56"/>
       <c r="I56">
         <v>1</v>
       </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>40,85</t>
-        </is>
+      <c r="J56" t="s">
+        <v>216</v>
       </c>
       <c r="K56">
         <v>0</v>
@@ -5985,39 +5281,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57">
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>item_flavor_enhance</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>风味喷雾</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>给两个无风味的食物添加随机风味。</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="F57"/>
+    <row r="57" spans="2:16">
+      <c r="B57" t="s">
+        <v>217</v>
+      </c>
+      <c r="C57" t="s">
+        <v>218</v>
+      </c>
+      <c r="D57" t="s">
+        <v>219</v>
+      </c>
+      <c r="E57" t="s">
+        <v>41</v>
+      </c>
       <c r="G57">
         <v>2</v>
       </c>
-      <c r="H57"/>
       <c r="I57">
         <v>1</v>
       </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
+      <c r="J57" t="s">
+        <v>42</v>
       </c>
       <c r="K57">
         <v>0</v>
@@ -6038,39 +5322,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58">
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>item_flavor_remove_gold</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>风味回收</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>移除一个食物的风味，获得200金币。</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="F58"/>
+    <row r="58" spans="2:16">
+      <c r="B58" t="s">
+        <v>220</v>
+      </c>
+      <c r="C58" t="s">
+        <v>221</v>
+      </c>
+      <c r="D58" t="s">
+        <v>222</v>
+      </c>
+      <c r="E58" t="s">
+        <v>41</v>
+      </c>
       <c r="G58">
         <v>200</v>
       </c>
-      <c r="H58"/>
       <c r="I58">
         <v>1</v>
       </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
+      <c r="J58" t="s">
+        <v>42</v>
       </c>
       <c r="K58">
         <v>0</v>
@@ -6091,39 +5363,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59">
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>item_flavor_remove_copyskill</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>风味转化</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>移除一个食物的风味，其技能复制。</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="F59"/>
+    <row r="59" spans="2:16">
+      <c r="B59" t="s">
+        <v>223</v>
+      </c>
+      <c r="C59" t="s">
+        <v>224</v>
+      </c>
+      <c r="D59" t="s">
+        <v>225</v>
+      </c>
+      <c r="E59" t="s">
+        <v>65</v>
+      </c>
       <c r="G59">
         <v>0</v>
       </c>
-      <c r="H59"/>
       <c r="I59">
         <v>1</v>
       </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
+      <c r="J59" t="s">
+        <v>42</v>
       </c>
       <c r="K59">
         <v>0</v>
@@ -6144,39 +5404,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60">
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>item_flavor_remove_double</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>风味浓缩</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>移除一个食物的风味，其分数翻倍。</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="F60"/>
+    <row r="60" spans="2:16">
+      <c r="B60" t="s">
+        <v>226</v>
+      </c>
+      <c r="C60" t="s">
+        <v>227</v>
+      </c>
+      <c r="D60" t="s">
+        <v>228</v>
+      </c>
+      <c r="E60" t="s">
+        <v>65</v>
+      </c>
       <c r="G60">
         <v>2</v>
       </c>
-      <c r="H60"/>
       <c r="I60">
         <v>1</v>
       </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
+      <c r="J60" t="s">
+        <v>42</v>
       </c>
       <c r="K60">
         <v>0</v>
@@ -6197,39 +5445,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61">
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>item_flavor_double_slot</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>双重风味</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>允许一个食物拥有两个风味。</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>Epic</t>
-        </is>
-      </c>
-      <c r="F61"/>
+    <row r="61" spans="2:16">
+      <c r="B61" t="s">
+        <v>229</v>
+      </c>
+      <c r="C61" t="s">
+        <v>230</v>
+      </c>
+      <c r="D61" t="s">
+        <v>231</v>
+      </c>
+      <c r="E61" t="s">
+        <v>188</v>
+      </c>
       <c r="G61">
         <v>1</v>
       </c>
-      <c r="H61"/>
       <c r="I61">
         <v>1</v>
       </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>40,85</t>
-        </is>
+      <c r="J61" t="s">
+        <v>216</v>
       </c>
       <c r="K61">
         <v>0</v>
@@ -6250,39 +5486,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62">
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>item_flavor_contagion</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>风味传染</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>将一个食物的风味强化到无风味食物上。</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="F62"/>
+    <row r="62" spans="2:16">
+      <c r="B62" t="s">
+        <v>232</v>
+      </c>
+      <c r="C62" t="s">
+        <v>233</v>
+      </c>
+      <c r="D62" t="s">
+        <v>234</v>
+      </c>
+      <c r="E62" t="s">
+        <v>65</v>
+      </c>
       <c r="G62">
         <v>1</v>
       </c>
-      <c r="H62"/>
       <c r="I62">
         <v>1</v>
       </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
+      <c r="J62" t="s">
+        <v>42</v>
       </c>
       <c r="K62">
         <v>0</v>
@@ -6303,39 +5527,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63">
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>item_celltag_enhance</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>标签强化</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>强化两个随机标签到胃部格子上。</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="F63"/>
+    <row r="63" spans="2:16">
+      <c r="B63" t="s">
+        <v>235</v>
+      </c>
+      <c r="C63" t="s">
+        <v>236</v>
+      </c>
+      <c r="D63" t="s">
+        <v>237</v>
+      </c>
+      <c r="E63" t="s">
+        <v>41</v>
+      </c>
       <c r="G63">
         <v>2</v>
       </c>
-      <c r="H63"/>
       <c r="I63">
         <v>1</v>
       </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
+      <c r="J63" t="s">
+        <v>42</v>
       </c>
       <c r="K63">
         <v>0</v>
@@ -6356,39 +5568,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64">
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>item_celltag_contagion</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>标签传染</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>将一个格子的标签强化到其他格子上。</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="F64"/>
+    <row r="64" spans="2:16">
+      <c r="B64" t="s">
+        <v>238</v>
+      </c>
+      <c r="C64" t="s">
+        <v>239</v>
+      </c>
+      <c r="D64" t="s">
+        <v>240</v>
+      </c>
+      <c r="E64" t="s">
+        <v>65</v>
+      </c>
       <c r="G64">
         <v>1</v>
       </c>
-      <c r="H64"/>
       <c r="I64">
         <v>1</v>
       </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
+      <c r="J64" t="s">
+        <v>42</v>
       </c>
       <c r="K64">
         <v>0</v>
@@ -6409,39 +5609,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65">
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>item_lucky_guarantee</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>好运连连</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>每4个事件的最后一个是奖励事件。</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="F65"/>
+    <row r="65" spans="2:16">
+      <c r="B65" t="s">
+        <v>241</v>
+      </c>
+      <c r="C65" t="s">
+        <v>242</v>
+      </c>
+      <c r="D65" t="s">
+        <v>243</v>
+      </c>
+      <c r="E65" t="s">
+        <v>65</v>
+      </c>
       <c r="G65">
         <v>4</v>
       </c>
-      <c r="H65"/>
       <c r="I65">
         <v>1</v>
       </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>20,65</t>
-        </is>
+      <c r="J65" t="s">
+        <v>84</v>
       </c>
       <c r="K65">
         <v>0</v>
@@ -6462,39 +5650,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66">
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>item_lucky_chance</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>幸运符</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>事件中遇到奖励的概率提高。</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="F66"/>
+    <row r="66" spans="2:16">
+      <c r="B66" t="s">
+        <v>244</v>
+      </c>
+      <c r="C66" t="s">
+        <v>245</v>
+      </c>
+      <c r="D66" t="s">
+        <v>246</v>
+      </c>
+      <c r="E66" t="s">
+        <v>41</v>
+      </c>
       <c r="G66">
         <v>0.2</v>
       </c>
-      <c r="H66"/>
       <c r="I66">
         <v>1</v>
       </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>5,45</t>
-        </is>
+      <c r="J66" t="s">
+        <v>77</v>
       </c>
       <c r="K66">
         <v>0</v>
@@ -6515,39 +5691,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67">
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>item_more_events</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>热闹街区</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>遇到事件的概率提高。</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="F67"/>
+    <row r="67" spans="2:16">
+      <c r="B67" t="s">
+        <v>247</v>
+      </c>
+      <c r="C67" t="s">
+        <v>248</v>
+      </c>
+      <c r="D67" t="s">
+        <v>249</v>
+      </c>
+      <c r="E67" t="s">
+        <v>41</v>
+      </c>
       <c r="G67">
         <v>0.2</v>
       </c>
-      <c r="H67"/>
       <c r="I67">
         <v>1</v>
       </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>5,45</t>
-        </is>
+      <c r="J67" t="s">
+        <v>77</v>
       </c>
       <c r="K67">
         <v>0</v>
@@ -6568,39 +5732,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68">
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>item_gold_on_event</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>事件红包</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>完成一个事件，获得10金币。</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="F68"/>
+    <row r="68" spans="2:16">
+      <c r="B68" t="s">
+        <v>250</v>
+      </c>
+      <c r="C68" t="s">
+        <v>251</v>
+      </c>
+      <c r="D68" t="s">
+        <v>252</v>
+      </c>
+      <c r="E68" t="s">
+        <v>55</v>
+      </c>
       <c r="G68">
         <v>10</v>
       </c>
-      <c r="H68"/>
       <c r="I68">
         <v>1</v>
       </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>1,30</t>
-        </is>
+      <c r="J68" t="s">
+        <v>88</v>
       </c>
       <c r="K68">
         <v>0</v>
@@ -6621,39 +5773,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69">
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>item_reroll_action</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>重掷行动</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>获得2次重新随机行动的机会。</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="F69"/>
+    <row r="69" spans="2:16">
+      <c r="B69" t="s">
+        <v>253</v>
+      </c>
+      <c r="C69" t="s">
+        <v>254</v>
+      </c>
+      <c r="D69" t="s">
+        <v>255</v>
+      </c>
+      <c r="E69" t="s">
+        <v>55</v>
+      </c>
       <c r="G69">
         <v>2</v>
       </c>
-      <c r="H69"/>
       <c r="I69">
         <v>1</v>
       </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
+      <c r="J69" t="s">
+        <v>42</v>
       </c>
       <c r="K69">
         <v>0</v>
@@ -6674,39 +5814,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70">
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>item_shop_restock</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>自动补货</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>商店会自动补货。</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="F70"/>
+    <row r="70" spans="2:16">
+      <c r="B70" t="s">
+        <v>256</v>
+      </c>
+      <c r="C70" t="s">
+        <v>257</v>
+      </c>
+      <c r="D70" t="s">
+        <v>258</v>
+      </c>
+      <c r="E70" t="s">
+        <v>65</v>
+      </c>
       <c r="G70">
         <v>0</v>
       </c>
-      <c r="H70"/>
       <c r="I70">
         <v>1</v>
       </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>20,65</t>
-        </is>
+      <c r="J70" t="s">
+        <v>84</v>
       </c>
       <c r="K70">
         <v>0</v>
@@ -6727,39 +5855,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71">
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>item_choice_count_plus1</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>琳琅满目</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>多选一食物时，可选数量+1。</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="F71"/>
+    <row r="71" spans="2:16">
+      <c r="B71" t="s">
+        <v>259</v>
+      </c>
+      <c r="C71" t="s">
+        <v>260</v>
+      </c>
+      <c r="D71" t="s">
+        <v>261</v>
+      </c>
+      <c r="E71" t="s">
+        <v>41</v>
+      </c>
       <c r="G71">
         <v>1</v>
       </c>
-      <c r="H71"/>
       <c r="I71">
         <v>1</v>
       </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>5,45</t>
-        </is>
+      <c r="J71" t="s">
+        <v>77</v>
       </c>
       <c r="K71">
         <v>0</v>
@@ -6780,39 +5896,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72">
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>item_choice_times_plus1</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>细嚼慢咽</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>多选一食物时，可选次数+1，可选数量-1。</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="F72"/>
+    <row r="72" spans="2:16">
+      <c r="B72" t="s">
+        <v>262</v>
+      </c>
+      <c r="C72" t="s">
+        <v>263</v>
+      </c>
+      <c r="D72" t="s">
+        <v>264</v>
+      </c>
+      <c r="E72" t="s">
+        <v>65</v>
+      </c>
       <c r="G72">
         <v>1</v>
       </c>
-      <c r="H72"/>
       <c r="I72">
         <v>1</v>
       </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>20,65</t>
-        </is>
+      <c r="J72" t="s">
+        <v>84</v>
       </c>
       <c r="K72">
         <v>0</v>
@@ -6833,43 +5937,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73">
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>item_extra_food_choice</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>加餐</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>每3次普通美食，额外获得一个多选一美食。</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="F73"/>
+    <row r="73" spans="2:16">
+      <c r="B73" t="s">
+        <v>265</v>
+      </c>
+      <c r="C73" t="s">
+        <v>266</v>
+      </c>
+      <c r="D73" t="s">
+        <v>267</v>
+      </c>
+      <c r="E73" t="s">
+        <v>65</v>
+      </c>
       <c r="G73">
         <v>0</v>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>every:3</t>
-        </is>
+      <c r="H73" t="s">
+        <v>198</v>
       </c>
       <c r="I73">
         <v>1</v>
       </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>20,65</t>
-        </is>
+      <c r="J73" t="s">
+        <v>84</v>
       </c>
       <c r="K73">
         <v>0</v>
@@ -6890,43 +5981,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74">
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>item_extra_item_choice</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>加料</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>每3次超级美食，额外获得一个多选一物品。</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="F74"/>
+    <row r="74" spans="2:16">
+      <c r="B74" t="s">
+        <v>268</v>
+      </c>
+      <c r="C74" t="s">
+        <v>269</v>
+      </c>
+      <c r="D74" t="s">
+        <v>270</v>
+      </c>
+      <c r="E74" t="s">
+        <v>65</v>
+      </c>
       <c r="G74">
         <v>0</v>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>every:3</t>
-        </is>
+      <c r="H74" t="s">
+        <v>198</v>
       </c>
       <c r="I74">
         <v>1</v>
       </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>20,65</t>
-        </is>
+      <c r="J74" t="s">
+        <v>84</v>
       </c>
       <c r="K74">
         <v>0</v>
@@ -6947,39 +6025,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75">
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>item_copy_food</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>复制美食</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>随机复制一个美食。</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="F75"/>
+    <row r="75" spans="2:16">
+      <c r="B75" t="s">
+        <v>271</v>
+      </c>
+      <c r="C75" t="s">
+        <v>272</v>
+      </c>
+      <c r="D75" t="s">
+        <v>273</v>
+      </c>
+      <c r="E75" t="s">
+        <v>65</v>
+      </c>
       <c r="G75">
         <v>1</v>
       </c>
-      <c r="H75"/>
       <c r="I75">
         <v>1</v>
       </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
+      <c r="J75" t="s">
+        <v>42</v>
       </c>
       <c r="K75">
         <v>0</v>
@@ -7000,39 +6066,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76">
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>item_discard_negative</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>断舍离</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>丢弃两个负面道具。</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="F76"/>
+    <row r="76" spans="2:16">
+      <c r="B76" t="s">
+        <v>274</v>
+      </c>
+      <c r="C76" t="s">
+        <v>275</v>
+      </c>
+      <c r="D76" t="s">
+        <v>276</v>
+      </c>
+      <c r="E76" t="s">
+        <v>55</v>
+      </c>
       <c r="G76">
         <v>2</v>
       </c>
-      <c r="H76"/>
       <c r="I76">
         <v>1</v>
       </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
+      <c r="J76" t="s">
+        <v>42</v>
       </c>
       <c r="K76">
         <v>0</v>
@@ -7053,39 +6107,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77">
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>item_discard_negative_gold</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>变废为宝</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>丢弃所有负面道具，每丢弃一个获得100金币。</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="F77"/>
+    <row r="77" spans="2:16">
+      <c r="B77" t="s">
+        <v>277</v>
+      </c>
+      <c r="C77" t="s">
+        <v>278</v>
+      </c>
+      <c r="D77" t="s">
+        <v>279</v>
+      </c>
+      <c r="E77" t="s">
+        <v>41</v>
+      </c>
       <c r="G77">
         <v>100</v>
       </c>
-      <c r="H77"/>
       <c r="I77">
         <v>1</v>
       </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
+      <c r="J77" t="s">
+        <v>42</v>
       </c>
       <c r="K77">
         <v>0</v>
@@ -7106,43 +6148,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78">
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>item_gold_meal_penalty</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>克扣工钱</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>美食获得的金币减少25%。</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
+    <row r="78" spans="2:16">
+      <c r="B78" t="s">
+        <v>280</v>
+      </c>
+      <c r="C78" t="s">
+        <v>281</v>
+      </c>
+      <c r="D78" t="s">
+        <v>282</v>
+      </c>
+      <c r="E78" t="s">
+        <v>55</v>
+      </c>
+      <c r="F78" t="s">
+        <v>283</v>
       </c>
       <c r="G78">
         <v>-0.25</v>
       </c>
-      <c r="H78"/>
       <c r="I78">
         <v>1</v>
       </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>1,30</t>
-        </is>
+      <c r="J78" t="s">
+        <v>88</v>
       </c>
       <c r="K78">
         <v>0</v>
@@ -7163,43 +6192,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79">
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>item_shop_price_up</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>涨价</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>商店的价格变高25%。</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
+    <row r="79" spans="2:16">
+      <c r="B79" t="s">
+        <v>284</v>
+      </c>
+      <c r="C79" t="s">
+        <v>285</v>
+      </c>
+      <c r="D79" t="s">
+        <v>286</v>
+      </c>
+      <c r="E79" t="s">
+        <v>55</v>
+      </c>
+      <c r="F79" t="s">
+        <v>283</v>
       </c>
       <c r="G79">
         <v>0.25</v>
       </c>
-      <c r="H79"/>
       <c r="I79">
         <v>1</v>
       </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>1,30</t>
-        </is>
+      <c r="J79" t="s">
+        <v>88</v>
       </c>
       <c r="K79">
         <v>0</v>
@@ -7220,43 +6236,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80">
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>item_no_remove</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>囤积癖</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>无法再删除食物。</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
+    <row r="80" spans="2:16">
+      <c r="B80" t="s">
+        <v>287</v>
+      </c>
+      <c r="C80" t="s">
+        <v>288</v>
+      </c>
+      <c r="D80" t="s">
+        <v>289</v>
+      </c>
+      <c r="E80" t="s">
+        <v>55</v>
+      </c>
+      <c r="F80" t="s">
+        <v>283</v>
       </c>
       <c r="G80">
         <v>0</v>
       </c>
-      <c r="H80"/>
       <c r="I80">
         <v>1</v>
       </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>1,30</t>
-        </is>
+      <c r="J80" t="s">
+        <v>88</v>
       </c>
       <c r="K80">
         <v>0</v>
@@ -7277,43 +6280,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81">
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>item_skip_node</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>停业整顿</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>跳过下一个商店或利息节点。</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
+    <row r="81" spans="2:16">
+      <c r="B81" t="s">
+        <v>290</v>
+      </c>
+      <c r="C81" t="s">
+        <v>291</v>
+      </c>
+      <c r="D81" t="s">
+        <v>292</v>
+      </c>
+      <c r="E81" t="s">
+        <v>55</v>
+      </c>
+      <c r="F81" t="s">
+        <v>283</v>
       </c>
       <c r="G81">
         <v>1</v>
       </c>
-      <c r="H81"/>
       <c r="I81">
         <v>1</v>
       </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>1,30</t>
-        </is>
+      <c r="J81" t="s">
+        <v>88</v>
       </c>
       <c r="K81">
         <v>0</v>
@@ -7334,43 +6324,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82">
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>item_choice_minus1</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>选择困难</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>多选一食物时，可选数量-1。</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
+    <row r="82" spans="2:16">
+      <c r="B82" t="s">
+        <v>293</v>
+      </c>
+      <c r="C82" t="s">
+        <v>294</v>
+      </c>
+      <c r="D82" t="s">
+        <v>295</v>
+      </c>
+      <c r="E82" t="s">
+        <v>55</v>
+      </c>
+      <c r="F82" t="s">
+        <v>283</v>
       </c>
       <c r="G82">
         <v>-1</v>
       </c>
-      <c r="H82"/>
       <c r="I82">
         <v>1</v>
       </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>1,30</t>
-        </is>
+      <c r="J82" t="s">
+        <v>88</v>
       </c>
       <c r="K82">
         <v>0</v>
@@ -7391,43 +6368,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83">
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>item_req_normal_up</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>家常加码</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>普通美食要求分数+10%。</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
+    <row r="83" spans="2:16">
+      <c r="B83" t="s">
+        <v>296</v>
+      </c>
+      <c r="C83" t="s">
+        <v>297</v>
+      </c>
+      <c r="D83" t="s">
+        <v>298</v>
+      </c>
+      <c r="E83" t="s">
+        <v>55</v>
+      </c>
+      <c r="F83" t="s">
+        <v>283</v>
       </c>
       <c r="G83">
         <v>0.1</v>
       </c>
-      <c r="H83"/>
       <c r="I83">
         <v>1</v>
       </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>1,30</t>
-        </is>
+      <c r="J83" t="s">
+        <v>88</v>
       </c>
       <c r="K83">
         <v>0</v>
@@ -7448,43 +6412,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84">
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>item_req_super_up</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>超级加码</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>超级美食要求分数+10%。</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
+    <row r="84" spans="2:16">
+      <c r="B84" t="s">
+        <v>299</v>
+      </c>
+      <c r="C84" t="s">
+        <v>300</v>
+      </c>
+      <c r="D84" t="s">
+        <v>301</v>
+      </c>
+      <c r="E84" t="s">
+        <v>55</v>
+      </c>
+      <c r="F84" t="s">
+        <v>283</v>
       </c>
       <c r="G84">
         <v>0.1</v>
       </c>
-      <c r="H84"/>
       <c r="I84">
         <v>1</v>
       </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>1,30</t>
-        </is>
+      <c r="J84" t="s">
+        <v>88</v>
       </c>
       <c r="K84">
         <v>0</v>
@@ -7505,43 +6456,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85">
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>item_req_feast_up</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>盛宴加码</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>盛宴美食要求分数+10%。</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
+    <row r="85" spans="2:16">
+      <c r="B85" t="s">
+        <v>302</v>
+      </c>
+      <c r="C85" t="s">
+        <v>303</v>
+      </c>
+      <c r="D85" t="s">
+        <v>304</v>
+      </c>
+      <c r="E85" t="s">
+        <v>55</v>
+      </c>
+      <c r="F85" t="s">
+        <v>283</v>
       </c>
       <c r="G85">
         <v>0.1</v>
       </c>
-      <c r="H85"/>
       <c r="I85">
         <v>1</v>
       </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>1,30</t>
-        </is>
+      <c r="J85" t="s">
+        <v>88</v>
       </c>
       <c r="K85">
         <v>0</v>
@@ -7562,43 +6500,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86">
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>item_gold_week_clear</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>月光族</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>本周结束时，金币清空。</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
+    <row r="86" spans="2:16">
+      <c r="B86" t="s">
+        <v>305</v>
+      </c>
+      <c r="C86" t="s">
+        <v>306</v>
+      </c>
+      <c r="D86" t="s">
+        <v>307</v>
+      </c>
+      <c r="E86" t="s">
+        <v>55</v>
+      </c>
+      <c r="F86" t="s">
+        <v>283</v>
       </c>
       <c r="G86">
         <v>0</v>
       </c>
-      <c r="H86"/>
       <c r="I86">
         <v>1</v>
       </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>1,30</t>
-        </is>
+      <c r="J86" t="s">
+        <v>88</v>
       </c>
       <c r="K86">
         <v>0</v>
@@ -7619,39 +6544,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87">
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>item_count_as_all</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>小份主义</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>所有食物额外被视为1个食物。</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="F87"/>
+    <row r="87" spans="2:16">
+      <c r="B87" t="s">
+        <v>308</v>
+      </c>
+      <c r="C87" t="s">
+        <v>309</v>
+      </c>
+      <c r="D87" t="s">
+        <v>310</v>
+      </c>
+      <c r="E87" t="s">
+        <v>65</v>
+      </c>
       <c r="G87">
         <v>1</v>
       </c>
-      <c r="H87"/>
       <c r="I87">
         <v>1</v>
       </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>20,65</t>
-        </is>
+      <c r="J87" t="s">
+        <v>84</v>
       </c>
       <c r="K87">
         <v>0</v>
@@ -7672,39 +6585,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88">
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>item_transfer_target_mult</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>传递受益</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>传递时，被传递方倍率×1.1。</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="F88"/>
+    <row r="88" spans="2:16">
+      <c r="B88" t="s">
+        <v>311</v>
+      </c>
+      <c r="C88" t="s">
+        <v>312</v>
+      </c>
+      <c r="D88" t="s">
+        <v>313</v>
+      </c>
+      <c r="E88" t="s">
+        <v>65</v>
+      </c>
       <c r="G88">
         <v>1.1</v>
       </c>
-      <c r="H88"/>
       <c r="I88">
         <v>1</v>
       </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>20,65</t>
-        </is>
+      <c r="J88" t="s">
+        <v>84</v>
       </c>
       <c r="K88">
         <v>0</v>
@@ -7725,39 +6626,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89">
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>item_transfer_source_mult</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>传递奉献</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>传递时，传递方倍率×1.1。</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="F89"/>
+    <row r="89" spans="2:16">
+      <c r="B89" t="s">
+        <v>314</v>
+      </c>
+      <c r="C89" t="s">
+        <v>315</v>
+      </c>
+      <c r="D89" t="s">
+        <v>316</v>
+      </c>
+      <c r="E89" t="s">
+        <v>65</v>
+      </c>
       <c r="G89">
         <v>1.1</v>
       </c>
-      <c r="H89"/>
       <c r="I89">
         <v>1</v>
       </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>20,65</t>
-        </is>
+      <c r="J89" t="s">
+        <v>84</v>
       </c>
       <c r="K89">
         <v>0</v>
@@ -7778,39 +6667,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90">
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>item_skill_count_mult</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>技法大师</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>结算时每一个技能，所有食物倍率+0.1。</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="F90"/>
+    <row r="90" spans="2:16">
+      <c r="B90" t="s">
+        <v>317</v>
+      </c>
+      <c r="C90" t="s">
+        <v>318</v>
+      </c>
+      <c r="D90" t="s">
+        <v>319</v>
+      </c>
+      <c r="E90" t="s">
+        <v>65</v>
+      </c>
       <c r="G90">
         <v>0.1</v>
       </c>
-      <c r="H90"/>
       <c r="I90">
         <v>1</v>
       </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>20,65</t>
-        </is>
+      <c r="J90" t="s">
+        <v>84</v>
       </c>
       <c r="K90">
         <v>0</v>
@@ -7831,43 +6708,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91">
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>item_gold_on_transfer</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>传递分红</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>传递10次后，获得10金币。</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="F91"/>
+    <row r="91" spans="2:16">
+      <c r="B91" t="s">
+        <v>320</v>
+      </c>
+      <c r="C91" t="s">
+        <v>321</v>
+      </c>
+      <c r="D91" t="s">
+        <v>322</v>
+      </c>
+      <c r="E91" t="s">
+        <v>41</v>
+      </c>
       <c r="G91">
         <v>10</v>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>count:10</t>
-        </is>
+      <c r="H91" t="s">
+        <v>323</v>
       </c>
       <c r="I91">
         <v>1</v>
       </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>5,45</t>
-        </is>
+      <c r="J91" t="s">
+        <v>77</v>
       </c>
       <c r="K91">
         <v>0</v>
@@ -7888,39 +6752,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92">
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>item_cake_retain</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>蛋糕保鲜</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>每次保留10%的蛋糕层数至下一次美食。</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="F92"/>
+    <row r="92" spans="2:16">
+      <c r="B92" t="s">
+        <v>324</v>
+      </c>
+      <c r="C92" t="s">
+        <v>325</v>
+      </c>
+      <c r="D92" t="s">
+        <v>326</v>
+      </c>
+      <c r="E92" t="s">
+        <v>65</v>
+      </c>
       <c r="G92">
         <v>0.1</v>
       </c>
-      <c r="H92"/>
       <c r="I92">
         <v>1</v>
       </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>20,65</t>
-        </is>
+      <c r="J92" t="s">
+        <v>84</v>
       </c>
       <c r="K92">
         <v>0</v>
@@ -7941,39 +6793,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93">
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>item_cake_init_bonus</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>蛋糕打底</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>蛋糕层数初始额外获得10层。</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="F93"/>
+    <row r="93" spans="2:16">
+      <c r="B93" t="s">
+        <v>327</v>
+      </c>
+      <c r="C93" t="s">
+        <v>328</v>
+      </c>
+      <c r="D93" t="s">
+        <v>329</v>
+      </c>
+      <c r="E93" t="s">
+        <v>41</v>
+      </c>
       <c r="G93">
         <v>10</v>
       </c>
-      <c r="H93"/>
       <c r="I93">
         <v>1</v>
       </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>5,45</t>
-        </is>
+      <c r="J93" t="s">
+        <v>77</v>
       </c>
       <c r="K93">
         <v>0</v>
@@ -7994,39 +6834,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94">
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>item_cake_accel</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>蛋糕膨胀</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>蛋糕层数增加时，额外加1层。</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="F94"/>
+    <row r="94" spans="2:16">
+      <c r="B94" t="s">
+        <v>330</v>
+      </c>
+      <c r="C94" t="s">
+        <v>331</v>
+      </c>
+      <c r="D94" t="s">
+        <v>332</v>
+      </c>
+      <c r="E94" t="s">
+        <v>65</v>
+      </c>
       <c r="G94">
         <v>1</v>
       </c>
-      <c r="H94"/>
       <c r="I94">
         <v>1</v>
       </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>20,65</t>
-        </is>
+      <c r="J94" t="s">
+        <v>84</v>
       </c>
       <c r="K94">
         <v>0</v>
@@ -8047,43 +6875,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95">
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>item_cake_to_gold</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>蛋糕变现</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>蛋糕层数大于100层时，获得10金币。</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="F95"/>
+    <row r="95" spans="2:16">
+      <c r="B95" t="s">
+        <v>333</v>
+      </c>
+      <c r="C95" t="s">
+        <v>334</v>
+      </c>
+      <c r="D95" t="s">
+        <v>335</v>
+      </c>
+      <c r="E95" t="s">
+        <v>41</v>
+      </c>
       <c r="G95">
         <v>10</v>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>threshold:100</t>
-        </is>
+      <c r="H95" t="s">
+        <v>336</v>
       </c>
       <c r="I95">
         <v>1</v>
       </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>5,45</t>
-        </is>
+      <c r="J95" t="s">
+        <v>77</v>
       </c>
       <c r="K95">
         <v>0</v>
@@ -8104,39 +6919,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96">
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>item_cake_req_minus</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>蛋糕捷径</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>蛋糕效果需求的层数-10。</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="F96"/>
+    <row r="96" spans="2:16">
+      <c r="B96" t="s">
+        <v>337</v>
+      </c>
+      <c r="C96" t="s">
+        <v>338</v>
+      </c>
+      <c r="D96" t="s">
+        <v>339</v>
+      </c>
+      <c r="E96" t="s">
+        <v>41</v>
+      </c>
       <c r="G96">
         <v>10</v>
       </c>
-      <c r="H96"/>
       <c r="I96">
         <v>1</v>
       </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>5,45</t>
-        </is>
+      <c r="J96" t="s">
+        <v>77</v>
       </c>
       <c r="K96">
         <v>0</v>
@@ -8203,7 +7006,7 @@
         <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>327</v>
+        <v>340</v>
       </c>
       <c r="H1" t="s">
         <v>6</v>
@@ -8215,121 +7018,121 @@
         <v>8</v>
       </c>
       <c r="K1" t="s">
-        <v>328</v>
+        <v>341</v>
       </c>
       <c r="L1" t="s">
-        <v>329</v>
+        <v>342</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F2" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G2" t="s">
-        <v>330</v>
+        <v>343</v>
       </c>
       <c r="H2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J2" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="K2" t="s">
-        <v>331</v>
+        <v>344</v>
       </c>
       <c r="L2" t="s">
-        <v>332</v>
+        <v>345</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="D3" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="E3" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="F3" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="G3" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="H3" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="I3" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="J3" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="K3" t="s">
-        <v>333</v>
+        <v>346</v>
       </c>
       <c r="L3" t="s">
-        <v>334</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="B4" t="s">
-        <v>336</v>
+        <v>348</v>
       </c>
       <c r="C4" t="s">
-        <v>337</v>
+        <v>349</v>
       </c>
       <c r="D4" t="s">
-        <v>338</v>
+        <v>350</v>
       </c>
       <c r="E4" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="F4" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="G4" t="s">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="H4">
         <v>0</v>
       </c>
       <c r="I4" t="s">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="J4">
         <v>1</v>
       </c>
       <c r="K4" t="s">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="L4">
         <v>1</v>
@@ -8337,37 +7140,37 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="B5" t="s">
-        <v>342</v>
+        <v>354</v>
       </c>
       <c r="C5" t="s">
-        <v>343</v>
+        <v>355</v>
       </c>
       <c r="D5" t="s">
-        <v>344</v>
+        <v>356</v>
       </c>
       <c r="E5" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="F5" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="G5" t="s">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="H5">
         <v>0</v>
       </c>
       <c r="I5" t="s">
-        <v>345</v>
+        <v>357</v>
       </c>
       <c r="J5">
         <v>1</v>
       </c>
       <c r="K5" t="s">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="L5">
         <v>1</v>
@@ -8375,37 +7178,37 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="B6" t="s">
-        <v>346</v>
+        <v>358</v>
       </c>
       <c r="C6" t="s">
+        <v>359</v>
+      </c>
+      <c r="D6" t="s">
+        <v>360</v>
+      </c>
+      <c r="E6" t="s">
+        <v>41</v>
+      </c>
+      <c r="F6" t="s">
         <v>347</v>
       </c>
-      <c r="D6" t="s">
-        <v>348</v>
-      </c>
-      <c r="E6" t="s">
-        <v>28</v>
-      </c>
-      <c r="F6" t="s">
-        <v>335</v>
-      </c>
       <c r="G6" t="s">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="H6">
         <v>0</v>
       </c>
       <c r="I6" t="s">
-        <v>349</v>
+        <v>361</v>
       </c>
       <c r="J6">
         <v>1</v>
       </c>
       <c r="K6" t="s">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="L6">
         <v>1</v>
@@ -8413,37 +7216,37 @@
     </row>
     <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="B7" t="s">
-        <v>350</v>
+        <v>362</v>
       </c>
       <c r="C7" t="s">
+        <v>363</v>
+      </c>
+      <c r="D7" t="s">
+        <v>364</v>
+      </c>
+      <c r="E7" t="s">
+        <v>41</v>
+      </c>
+      <c r="F7" t="s">
+        <v>347</v>
+      </c>
+      <c r="G7" t="s">
         <v>351</v>
       </c>
-      <c r="D7" t="s">
-        <v>352</v>
-      </c>
-      <c r="E7" t="s">
-        <v>28</v>
-      </c>
-      <c r="F7" t="s">
-        <v>335</v>
-      </c>
-      <c r="G7" t="s">
-        <v>339</v>
-      </c>
       <c r="H7">
         <v>0</v>
       </c>
       <c r="I7" t="s">
+        <v>365</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7" t="s">
         <v>353</v>
-      </c>
-      <c r="J7">
-        <v>1</v>
-      </c>
-      <c r="K7" t="s">
-        <v>341</v>
       </c>
       <c r="L7">
         <v>1</v>
@@ -8451,37 +7254,37 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="B8" t="s">
-        <v>354</v>
+        <v>366</v>
       </c>
       <c r="C8" t="s">
-        <v>355</v>
+        <v>367</v>
       </c>
       <c r="D8" t="s">
-        <v>356</v>
+        <v>368</v>
       </c>
       <c r="E8" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="F8" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="G8" t="s">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="H8">
         <v>0</v>
       </c>
       <c r="I8" t="s">
-        <v>357</v>
+        <v>369</v>
       </c>
       <c r="J8">
         <v>1</v>
       </c>
       <c r="K8" t="s">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="L8">
         <v>1</v>
@@ -8489,37 +7292,37 @@
     </row>
     <row r="9" spans="1:12">
       <c r="A9" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="B9" t="s">
-        <v>358</v>
+        <v>370</v>
       </c>
       <c r="C9" t="s">
-        <v>359</v>
+        <v>371</v>
       </c>
       <c r="D9" t="s">
-        <v>360</v>
+        <v>372</v>
       </c>
       <c r="E9" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="F9" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="G9" t="s">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="H9">
         <v>0</v>
       </c>
       <c r="I9" t="s">
-        <v>361</v>
+        <v>373</v>
       </c>
       <c r="J9">
         <v>1</v>
       </c>
       <c r="K9" t="s">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="L9">
         <v>1</v>
@@ -8527,37 +7330,37 @@
     </row>
     <row r="10" spans="1:12">
       <c r="A10" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="B10" t="s">
-        <v>362</v>
+        <v>374</v>
       </c>
       <c r="C10" t="s">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c r="D10" t="s">
-        <v>364</v>
+        <v>376</v>
       </c>
       <c r="E10" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="F10" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="G10" t="s">
-        <v>365</v>
+        <v>377</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="I10" t="s">
-        <v>366</v>
+        <v>378</v>
       </c>
       <c r="J10">
         <v>1</v>
       </c>
       <c r="K10" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="L10">
         <v>1</v>
@@ -8565,37 +7368,37 @@
     </row>
     <row r="11" spans="1:12">
       <c r="A11" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="B11" t="s">
-        <v>368</v>
+        <v>380</v>
       </c>
       <c r="C11" t="s">
-        <v>369</v>
+        <v>381</v>
       </c>
       <c r="D11" t="s">
-        <v>370</v>
+        <v>382</v>
       </c>
       <c r="E11" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="F11" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="G11" t="s">
-        <v>365</v>
+        <v>377</v>
       </c>
       <c r="H11">
         <v>0</v>
       </c>
       <c r="I11" t="s">
-        <v>371</v>
+        <v>383</v>
       </c>
       <c r="J11">
         <v>1</v>
       </c>
       <c r="K11" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="L11">
         <v>1</v>
@@ -8603,37 +7406,37 @@
     </row>
     <row r="12" spans="1:12">
       <c r="A12" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="B12" t="s">
-        <v>372</v>
+        <v>384</v>
       </c>
       <c r="C12" t="s">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="D12" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="E12" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="F12" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="G12" t="s">
-        <v>365</v>
+        <v>377</v>
       </c>
       <c r="H12">
         <v>0</v>
       </c>
       <c r="I12" t="s">
-        <v>375</v>
+        <v>387</v>
       </c>
       <c r="J12">
         <v>1</v>
       </c>
       <c r="K12" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="L12">
         <v>1</v>
@@ -8641,37 +7444,37 @@
     </row>
     <row r="13" spans="1:12">
       <c r="A13" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="B13" t="s">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="C13" t="s">
+        <v>389</v>
+      </c>
+      <c r="D13" t="s">
+        <v>390</v>
+      </c>
+      <c r="E13" t="s">
+        <v>41</v>
+      </c>
+      <c r="F13" t="s">
+        <v>347</v>
+      </c>
+      <c r="G13" t="s">
         <v>377</v>
       </c>
-      <c r="D13" t="s">
-        <v>378</v>
-      </c>
-      <c r="E13" t="s">
-        <v>28</v>
-      </c>
-      <c r="F13" t="s">
-        <v>335</v>
-      </c>
-      <c r="G13" t="s">
-        <v>365</v>
-      </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="I13" t="s">
+        <v>391</v>
+      </c>
+      <c r="J13">
+        <v>1</v>
+      </c>
+      <c r="K13" t="s">
         <v>379</v>
-      </c>
-      <c r="J13">
-        <v>1</v>
-      </c>
-      <c r="K13" t="s">
-        <v>367</v>
       </c>
       <c r="L13">
         <v>1</v>
@@ -8679,37 +7482,37 @@
     </row>
     <row r="14" spans="1:12">
       <c r="A14" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="B14" t="s">
-        <v>380</v>
+        <v>392</v>
       </c>
       <c r="C14" t="s">
-        <v>381</v>
+        <v>393</v>
       </c>
       <c r="D14" t="s">
-        <v>382</v>
+        <v>394</v>
       </c>
       <c r="E14" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="F14" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="G14" t="s">
-        <v>365</v>
+        <v>377</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="I14" t="s">
-        <v>383</v>
+        <v>395</v>
       </c>
       <c r="J14">
         <v>1</v>
       </c>
       <c r="K14" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="L14">
         <v>1</v>
@@ -8717,37 +7520,37 @@
     </row>
     <row r="15" spans="1:12">
       <c r="A15" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="B15" t="s">
-        <v>384</v>
+        <v>396</v>
       </c>
       <c r="C15" t="s">
-        <v>385</v>
+        <v>397</v>
       </c>
       <c r="D15" t="s">
-        <v>386</v>
+        <v>398</v>
       </c>
       <c r="E15" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="F15" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="G15" t="s">
-        <v>365</v>
+        <v>377</v>
       </c>
       <c r="H15">
         <v>0</v>
       </c>
       <c r="I15" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="J15">
         <v>1</v>
       </c>
       <c r="K15" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="L15">
         <v>1</v>
@@ -8755,37 +7558,37 @@
     </row>
     <row r="16" spans="1:12">
       <c r="A16" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="B16" t="s">
-        <v>388</v>
+        <v>400</v>
       </c>
       <c r="C16" t="s">
-        <v>389</v>
+        <v>401</v>
       </c>
       <c r="D16" t="s">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="E16" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="F16" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="G16" t="s">
-        <v>365</v>
+        <v>377</v>
       </c>
       <c r="H16">
         <v>0</v>
       </c>
       <c r="I16" t="s">
-        <v>391</v>
+        <v>403</v>
       </c>
       <c r="J16">
         <v>1</v>
       </c>
       <c r="K16" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="L16">
         <v>1</v>
@@ -8793,37 +7596,37 @@
     </row>
     <row r="17" spans="1:12">
       <c r="A17" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="B17" t="s">
-        <v>392</v>
+        <v>404</v>
       </c>
       <c r="C17" t="s">
-        <v>393</v>
+        <v>405</v>
       </c>
       <c r="D17" t="s">
-        <v>394</v>
+        <v>406</v>
       </c>
       <c r="E17" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="F17" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="G17" t="s">
-        <v>395</v>
+        <v>407</v>
       </c>
       <c r="H17">
         <v>0</v>
       </c>
       <c r="I17" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="J17">
         <v>1</v>
       </c>
       <c r="K17" t="s">
-        <v>396</v>
+        <v>408</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -8831,37 +7634,37 @@
     </row>
     <row r="18" spans="1:12">
       <c r="A18" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="B18" t="s">
-        <v>397</v>
+        <v>409</v>
       </c>
       <c r="C18" t="s">
-        <v>398</v>
+        <v>410</v>
       </c>
       <c r="D18" t="s">
-        <v>399</v>
+        <v>411</v>
       </c>
       <c r="E18" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="F18" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="G18" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="H18">
         <v>0</v>
       </c>
       <c r="I18" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="J18">
         <v>1</v>
       </c>
       <c r="K18" t="s">
-        <v>396</v>
+        <v>408</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -8869,37 +7672,37 @@
     </row>
     <row r="19" spans="1:12">
       <c r="A19" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="B19" t="s">
-        <v>401</v>
+        <v>413</v>
       </c>
       <c r="C19" t="s">
-        <v>402</v>
+        <v>414</v>
       </c>
       <c r="D19" t="s">
-        <v>403</v>
+        <v>415</v>
       </c>
       <c r="E19" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="F19" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="G19" t="s">
-        <v>404</v>
+        <v>416</v>
       </c>
       <c r="H19">
         <v>0</v>
       </c>
       <c r="I19" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="J19">
         <v>1</v>
       </c>
       <c r="K19" t="s">
-        <v>396</v>
+        <v>408</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -8907,37 +7710,37 @@
     </row>
     <row r="20" spans="1:12">
       <c r="A20" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="B20" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="C20" t="s">
-        <v>406</v>
+        <v>418</v>
       </c>
       <c r="D20" t="s">
-        <v>407</v>
+        <v>419</v>
       </c>
       <c r="E20" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="F20" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="G20" t="s">
+        <v>420</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20" t="s">
+        <v>421</v>
+      </c>
+      <c r="J20">
+        <v>1</v>
+      </c>
+      <c r="K20" t="s">
         <v>408</v>
-      </c>
-      <c r="H20">
-        <v>0</v>
-      </c>
-      <c r="I20" t="s">
-        <v>409</v>
-      </c>
-      <c r="J20">
-        <v>1</v>
-      </c>
-      <c r="K20" t="s">
-        <v>396</v>
       </c>
       <c r="L20">
         <v>0</v>
@@ -8964,36 +7767,36 @@
   <sheetData>
     <row r="1" customHeight="1" spans="2:9">
       <c r="B1" s="3" t="s">
-        <v>410</v>
+        <v>422</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>411</v>
+        <v>423</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>412</v>
+        <v>424</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>413</v>
+        <v>425</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>414</v>
+        <v>426</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="2:9">
       <c r="B2" s="3" t="s">
-        <v>415</v>
+        <v>427</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>416</v>
+        <v>428</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>417</v>
+        <v>429</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>418</v>
+        <v>430</v>
       </c>
       <c r="H2" s="1">
         <v>1</v>
@@ -9007,10 +7810,10 @@
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
       <c r="D3" s="3" t="s">
-        <v>419</v>
+        <v>431</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>420</v>
+        <v>432</v>
       </c>
       <c r="H3" s="1">
         <v>2</v>
@@ -9024,10 +7827,10 @@
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
       <c r="D4" s="3" t="s">
-        <v>421</v>
+        <v>433</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>422</v>
+        <v>434</v>
       </c>
       <c r="H4" s="1">
         <v>3</v>
@@ -9041,10 +7844,10 @@
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
       <c r="D5" s="3" t="s">
-        <v>419</v>
+        <v>431</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>423</v>
+        <v>435</v>
       </c>
       <c r="H5" s="1">
         <v>4</v>
@@ -9058,10 +7861,10 @@
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
       <c r="D6" s="3" t="s">
-        <v>424</v>
+        <v>436</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>425</v>
+        <v>437</v>
       </c>
       <c r="H6" s="1">
         <v>5</v>
@@ -9075,10 +7878,10 @@
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
       <c r="D7" s="3" t="s">
-        <v>426</v>
+        <v>438</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>427</v>
+        <v>439</v>
       </c>
       <c r="H7" s="1">
         <v>6</v>
@@ -9092,10 +7895,10 @@
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
       <c r="D8" s="3" t="s">
-        <v>428</v>
+        <v>440</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>429</v>
+        <v>441</v>
       </c>
       <c r="H8" s="1">
         <v>7</v>
@@ -9109,10 +7912,10 @@
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
       <c r="D9" s="3" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>430</v>
+        <v>442</v>
       </c>
       <c r="H9" s="1">
         <v>8</v>
@@ -9126,10 +7929,10 @@
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
       <c r="D10" s="3" t="s">
-        <v>431</v>
+        <v>443</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>432</v>
+        <v>444</v>
       </c>
       <c r="H10" s="1">
         <v>9</v>
@@ -9142,13 +7945,13 @@
     <row r="11" customHeight="1" spans="2:9">
       <c r="B11" s="4"/>
       <c r="C11" s="3" t="s">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>434</v>
+        <v>446</v>
       </c>
       <c r="H11" s="1">
         <v>10</v>
@@ -9162,10 +7965,10 @@
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
       <c r="D12" s="3" t="s">
-        <v>435</v>
+        <v>447</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="H12" s="1">
         <v>11</v>
@@ -9179,10 +7982,10 @@
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
       <c r="D13" s="3" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>438</v>
+        <v>450</v>
       </c>
       <c r="H13" s="1">
         <v>12</v>
@@ -9196,10 +7999,10 @@
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
       <c r="D14" s="3" t="s">
-        <v>439</v>
+        <v>451</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>440</v>
+        <v>452</v>
       </c>
       <c r="H14" s="1">
         <v>13</v>
@@ -9212,13 +8015,13 @@
     <row r="15" customHeight="1" spans="2:9">
       <c r="B15" s="4"/>
       <c r="C15" s="3" t="s">
-        <v>441</v>
+        <v>453</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>443</v>
+        <v>455</v>
       </c>
       <c r="H15" s="1">
         <v>14</v>
@@ -9232,10 +8035,10 @@
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
       <c r="D16" s="3" t="s">
-        <v>444</v>
+        <v>456</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>445</v>
+        <v>457</v>
       </c>
       <c r="H16" s="1">
         <v>15</v>
@@ -9249,10 +8052,10 @@
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
       <c r="D17" s="3" t="s">
-        <v>446</v>
+        <v>458</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>447</v>
+        <v>459</v>
       </c>
       <c r="H17" s="1">
         <v>16</v>
@@ -9266,10 +8069,10 @@
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
       <c r="D18" s="3" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>449</v>
+        <v>461</v>
       </c>
       <c r="H18" s="1">
         <v>17</v>
@@ -9283,10 +8086,10 @@
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
       <c r="D19" s="3" t="s">
-        <v>450</v>
+        <v>462</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>451</v>
+        <v>463</v>
       </c>
       <c r="H19" s="1">
         <v>18</v>
@@ -9300,10 +8103,10 @@
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
       <c r="D20" s="3" t="s">
-        <v>450</v>
+        <v>462</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>452</v>
+        <v>464</v>
       </c>
       <c r="H20" s="1">
         <v>19</v>
@@ -9317,10 +8120,10 @@
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
       <c r="D21" s="3" t="s">
-        <v>453</v>
+        <v>465</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>454</v>
+        <v>466</v>
       </c>
       <c r="H21" s="1">
         <v>20</v>
@@ -9333,13 +8136,13 @@
     <row r="22" customHeight="1" spans="2:9">
       <c r="B22" s="4"/>
       <c r="C22" s="3" t="s">
-        <v>455</v>
+        <v>467</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>456</v>
+        <v>468</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>457</v>
+        <v>469</v>
       </c>
       <c r="H22" s="1">
         <v>21</v>
@@ -9352,13 +8155,13 @@
     <row r="23" customHeight="1" spans="2:9">
       <c r="B23" s="4"/>
       <c r="C23" s="3" t="s">
-        <v>458</v>
+        <v>470</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>459</v>
+        <v>471</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>460</v>
+        <v>472</v>
       </c>
       <c r="H23" s="1">
         <v>22</v>
@@ -9372,10 +8175,10 @@
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
       <c r="D24" s="3" t="s">
-        <v>461</v>
+        <v>473</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>462</v>
+        <v>474</v>
       </c>
       <c r="H24" s="1">
         <v>23</v>
@@ -9389,10 +8192,10 @@
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
       <c r="D25" s="3" t="s">
-        <v>463</v>
+        <v>475</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>464</v>
+        <v>476</v>
       </c>
       <c r="H25" s="1">
         <v>24</v>
@@ -9406,10 +8209,10 @@
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
       <c r="D26" s="3" t="s">
-        <v>465</v>
+        <v>477</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>466</v>
+        <v>478</v>
       </c>
       <c r="H26" s="1">
         <v>25</v>
@@ -9422,13 +8225,13 @@
     <row r="27" customHeight="1" spans="2:9">
       <c r="B27" s="4"/>
       <c r="C27" s="3" t="s">
-        <v>467</v>
+        <v>479</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>468</v>
+        <v>480</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>469</v>
+        <v>481</v>
       </c>
       <c r="H27" s="1">
         <v>26</v>
@@ -9442,10 +8245,10 @@
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
       <c r="D28" s="3" t="s">
-        <v>468</v>
+        <v>480</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>470</v>
+        <v>482</v>
       </c>
       <c r="H28" s="1">
         <v>27</v>
@@ -9458,13 +8261,13 @@
     <row r="29" customHeight="1" spans="2:9">
       <c r="B29" s="4"/>
       <c r="C29" s="3" t="s">
-        <v>471</v>
+        <v>483</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>472</v>
+        <v>484</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>473</v>
+        <v>485</v>
       </c>
       <c r="H29" s="1">
         <v>28</v>
@@ -9477,13 +8280,13 @@
     <row r="30" customHeight="1" spans="2:9">
       <c r="B30" s="4"/>
       <c r="C30" s="3" t="s">
-        <v>474</v>
+        <v>486</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>475</v>
+        <v>487</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>476</v>
+        <v>488</v>
       </c>
       <c r="H30" s="1">
         <v>29</v>
@@ -9496,13 +8299,13 @@
     <row r="31" customHeight="1" spans="2:9">
       <c r="B31" s="4"/>
       <c r="C31" s="3" t="s">
-        <v>477</v>
+        <v>489</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>475</v>
+        <v>487</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>478</v>
+        <v>490</v>
       </c>
       <c r="H31" s="1">
         <v>30</v>
@@ -9515,13 +8318,13 @@
     <row r="32" customHeight="1" spans="2:9">
       <c r="B32" s="4"/>
       <c r="C32" s="3" t="s">
-        <v>479</v>
+        <v>491</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>480</v>
+        <v>492</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>481</v>
+        <v>493</v>
       </c>
       <c r="H32" s="1">
         <v>31</v>
@@ -9535,10 +8338,10 @@
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
       <c r="D33" s="3" t="s">
-        <v>480</v>
+        <v>492</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>482</v>
+        <v>494</v>
       </c>
       <c r="H33" s="1">
         <v>32</v>
@@ -9552,10 +8355,10 @@
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
       <c r="D34" s="3" t="s">
-        <v>483</v>
+        <v>495</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>484</v>
+        <v>496</v>
       </c>
       <c r="H34" s="1">
         <v>33</v>
@@ -9568,13 +8371,13 @@
     <row r="35" customHeight="1" spans="2:9">
       <c r="B35" s="4"/>
       <c r="C35" s="5" t="s">
-        <v>485</v>
+        <v>497</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>486</v>
+        <v>498</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>487</v>
+        <v>499</v>
       </c>
       <c r="H35" s="1">
         <v>34</v>
@@ -9588,10 +8391,10 @@
       <c r="B36" s="4"/>
       <c r="C36" s="5"/>
       <c r="D36" s="6" t="s">
-        <v>488</v>
+        <v>500</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>489</v>
+        <v>501</v>
       </c>
       <c r="H36" s="1">
         <v>35</v>
@@ -9604,13 +8407,13 @@
     <row r="37" customHeight="1" spans="2:9">
       <c r="B37" s="4"/>
       <c r="C37" s="3" t="s">
-        <v>490</v>
+        <v>502</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>490</v>
+        <v>502</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>491</v>
+        <v>503</v>
       </c>
       <c r="H37" s="1">
         <v>36</v>
@@ -9623,13 +8426,13 @@
     <row r="38" customHeight="1" spans="2:9">
       <c r="B38" s="4"/>
       <c r="C38" s="3" t="s">
-        <v>492</v>
+        <v>504</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>493</v>
+        <v>505</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>494</v>
+        <v>506</v>
       </c>
       <c r="H38" s="1">
         <v>37</v>
@@ -9643,10 +8446,10 @@
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
       <c r="D39" s="3" t="s">
-        <v>495</v>
+        <v>507</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>496</v>
+        <v>508</v>
       </c>
       <c r="H39" s="1">
         <v>38</v>
@@ -9660,10 +8463,10 @@
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
       <c r="D40" s="3" t="s">
-        <v>497</v>
+        <v>509</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>498</v>
+        <v>510</v>
       </c>
       <c r="H40" s="1">
         <v>39</v>
@@ -9677,10 +8480,10 @@
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
       <c r="D41" s="3" t="s">
-        <v>499</v>
+        <v>511</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>500</v>
+        <v>512</v>
       </c>
       <c r="H41" s="1">
         <v>40</v>
@@ -9694,10 +8497,10 @@
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
       <c r="D42" s="3" t="s">
-        <v>501</v>
+        <v>513</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>502</v>
+        <v>514</v>
       </c>
       <c r="H42" s="1">
         <v>41</v>
@@ -9711,10 +8514,10 @@
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
       <c r="D43" s="3" t="s">
-        <v>503</v>
+        <v>515</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="H43" s="1">
         <v>42</v>
@@ -9727,13 +8530,13 @@
     <row r="44" customHeight="1" spans="2:9">
       <c r="B44" s="4"/>
       <c r="C44" s="3" t="s">
-        <v>505</v>
+        <v>517</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>431</v>
+        <v>443</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="H44" s="1">
         <v>43</v>
@@ -9747,10 +8550,10 @@
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
       <c r="D45" s="3" t="s">
-        <v>506</v>
+        <v>518</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="H45" s="1">
         <v>44</v>
@@ -9764,10 +8567,10 @@
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
       <c r="D46" s="3" t="s">
-        <v>508</v>
+        <v>520</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>508</v>
+        <v>520</v>
       </c>
       <c r="H46" s="1">
         <v>45</v>
@@ -9781,10 +8584,10 @@
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
       <c r="D47" s="3" t="s">
-        <v>509</v>
+        <v>521</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>510</v>
+        <v>522</v>
       </c>
       <c r="H47" s="1">
         <v>46</v>
@@ -9798,10 +8601,10 @@
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
       <c r="D48" s="3" t="s">
-        <v>511</v>
+        <v>523</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>512</v>
+        <v>524</v>
       </c>
       <c r="H48" s="1">
         <v>47</v>
@@ -9814,13 +8617,13 @@
     <row r="49" customHeight="1" spans="2:9">
       <c r="B49" s="4"/>
       <c r="C49" s="3" t="s">
-        <v>513</v>
+        <v>525</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>514</v>
+        <v>526</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>515</v>
+        <v>527</v>
       </c>
       <c r="H49" s="1">
         <v>48</v>
@@ -9834,10 +8637,10 @@
       <c r="B50" s="4"/>
       <c r="C50" s="4"/>
       <c r="D50" s="3" t="s">
-        <v>516</v>
+        <v>528</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>517</v>
+        <v>529</v>
       </c>
       <c r="H50" s="1">
         <v>49</v>
@@ -9851,10 +8654,10 @@
       <c r="B51" s="4"/>
       <c r="C51" s="4"/>
       <c r="D51" s="3" t="s">
-        <v>518</v>
+        <v>530</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>519</v>
+        <v>531</v>
       </c>
       <c r="H51" s="1">
         <v>50</v>
@@ -9867,13 +8670,13 @@
     <row r="52" customHeight="1" spans="2:9">
       <c r="B52" s="4"/>
       <c r="C52" s="3" t="s">
-        <v>520</v>
+        <v>532</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>521</v>
+        <v>533</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>522</v>
+        <v>534</v>
       </c>
       <c r="H52" s="1">
         <v>51</v>
@@ -9887,10 +8690,10 @@
       <c r="B53" s="4"/>
       <c r="C53" s="4"/>
       <c r="D53" s="3" t="s">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>523</v>
+        <v>535</v>
       </c>
       <c r="H53" s="1">
         <v>52</v>
@@ -9904,10 +8707,10 @@
       <c r="B54" s="4"/>
       <c r="C54" s="4"/>
       <c r="D54" s="3" t="s">
-        <v>524</v>
+        <v>536</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>525</v>
+        <v>537</v>
       </c>
       <c r="H54" s="1">
         <v>53</v>
@@ -9920,13 +8723,13 @@
     <row r="55" customHeight="1" spans="2:9">
       <c r="B55" s="4"/>
       <c r="C55" s="3" t="s">
-        <v>526</v>
+        <v>538</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>527</v>
+        <v>539</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>528</v>
+        <v>540</v>
       </c>
       <c r="H55" s="1">
         <v>54</v>
@@ -9940,10 +8743,10 @@
       <c r="B56" s="4"/>
       <c r="C56" s="4"/>
       <c r="D56" s="3" t="s">
-        <v>529</v>
+        <v>541</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>530</v>
+        <v>542</v>
       </c>
       <c r="H56" s="1">
         <v>55</v>
@@ -9957,10 +8760,10 @@
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
       <c r="D57" s="3" t="s">
-        <v>531</v>
+        <v>543</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>532</v>
+        <v>544</v>
       </c>
       <c r="H57" s="1">
         <v>56</v>
@@ -9974,10 +8777,10 @@
       <c r="B58" s="4"/>
       <c r="C58" s="4"/>
       <c r="D58" s="3" t="s">
-        <v>533</v>
+        <v>545</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>534</v>
+        <v>546</v>
       </c>
       <c r="H58" s="1">
         <v>57</v>
@@ -9991,10 +8794,10 @@
       <c r="B59" s="4"/>
       <c r="C59" s="4"/>
       <c r="D59" s="3" t="s">
-        <v>535</v>
+        <v>547</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>536</v>
+        <v>548</v>
       </c>
       <c r="H59" s="1">
         <v>58</v>
@@ -10008,10 +8811,10 @@
       <c r="B60" s="4"/>
       <c r="C60" s="4"/>
       <c r="D60" s="3" t="s">
-        <v>220</v>
+        <v>233</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>537</v>
+        <v>549</v>
       </c>
       <c r="H60" s="1">
         <v>59</v>
@@ -10024,13 +8827,13 @@
     <row r="61" customHeight="1" spans="2:9">
       <c r="B61" s="4"/>
       <c r="C61" s="3" t="s">
-        <v>538</v>
+        <v>550</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>539</v>
+        <v>551</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>540</v>
+        <v>552</v>
       </c>
       <c r="H61" s="1">
         <v>60</v>
@@ -10044,10 +8847,10 @@
       <c r="B62" s="4"/>
       <c r="C62" s="4"/>
       <c r="D62" s="3" t="s">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>541</v>
+        <v>553</v>
       </c>
       <c r="H62" s="1">
         <v>61</v>
@@ -10060,13 +8863,13 @@
     <row r="63" customHeight="1" spans="2:9">
       <c r="B63" s="4"/>
       <c r="C63" s="3" t="s">
-        <v>542</v>
+        <v>554</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>543</v>
+        <v>555</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>544</v>
+        <v>556</v>
       </c>
       <c r="H63" s="1">
         <v>62</v>
@@ -10080,10 +8883,10 @@
       <c r="B64" s="4"/>
       <c r="C64" s="4"/>
       <c r="D64" s="3" t="s">
-        <v>543</v>
+        <v>555</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>545</v>
+        <v>557</v>
       </c>
       <c r="H64" s="1">
         <v>63</v>
@@ -10097,10 +8900,10 @@
       <c r="B65" s="4"/>
       <c r="C65" s="4"/>
       <c r="D65" s="3" t="s">
-        <v>546</v>
+        <v>558</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>547</v>
+        <v>559</v>
       </c>
       <c r="H65" s="1">
         <v>64</v>
@@ -10114,10 +8917,10 @@
       <c r="B66" s="4"/>
       <c r="C66" s="4"/>
       <c r="D66" s="3" t="s">
-        <v>548</v>
+        <v>560</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>549</v>
+        <v>561</v>
       </c>
       <c r="H66" s="1">
         <v>65</v>
@@ -10131,10 +8934,10 @@
       <c r="B67" s="4"/>
       <c r="C67" s="4"/>
       <c r="D67" s="3" t="s">
-        <v>550</v>
+        <v>562</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>551</v>
+        <v>563</v>
       </c>
       <c r="H67" s="1">
         <v>66</v>
@@ -10147,13 +8950,13 @@
     <row r="68" customHeight="1" spans="2:9">
       <c r="B68" s="4"/>
       <c r="C68" s="3" t="s">
-        <v>552</v>
+        <v>564</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>553</v>
+        <v>565</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>554</v>
+        <v>566</v>
       </c>
       <c r="H68" s="1">
         <v>67</v>
@@ -10166,13 +8969,13 @@
     <row r="69" customHeight="1" spans="2:9">
       <c r="B69" s="4"/>
       <c r="C69" s="3" t="s">
-        <v>555</v>
+        <v>567</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>556</v>
+        <v>568</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>557</v>
+        <v>569</v>
       </c>
       <c r="H69" s="1">
         <v>68</v>
@@ -10186,10 +8989,10 @@
       <c r="B70" s="4"/>
       <c r="C70" s="4"/>
       <c r="D70" s="3" t="s">
-        <v>558</v>
+        <v>570</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>559</v>
+        <v>571</v>
       </c>
       <c r="H70" s="1">
         <v>69</v>
@@ -10203,10 +9006,10 @@
       <c r="B71" s="4"/>
       <c r="C71" s="4"/>
       <c r="D71" s="3" t="s">
-        <v>560</v>
+        <v>572</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>561</v>
+        <v>573</v>
       </c>
       <c r="H71" s="1">
         <v>70</v>
@@ -10220,10 +9023,10 @@
       <c r="B72" s="4"/>
       <c r="C72" s="4"/>
       <c r="D72" s="3" t="s">
-        <v>562</v>
+        <v>574</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>563</v>
+        <v>575</v>
       </c>
       <c r="H72" s="1">
         <v>71</v>
@@ -10237,10 +9040,10 @@
       <c r="B73" s="4"/>
       <c r="C73" s="4"/>
       <c r="D73" s="3" t="s">
-        <v>259</v>
+        <v>272</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>564</v>
+        <v>576</v>
       </c>
       <c r="H73" s="1">
         <v>72</v>
@@ -10253,13 +9056,13 @@
     <row r="74" customHeight="1" spans="2:9">
       <c r="B74" s="4"/>
       <c r="C74" s="3" t="s">
-        <v>565</v>
+        <v>577</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>566</v>
+        <v>578</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>567</v>
+        <v>579</v>
       </c>
       <c r="H74" s="1">
         <v>73</v>
@@ -10273,10 +9076,10 @@
       <c r="B75" s="4"/>
       <c r="C75" s="3"/>
       <c r="D75" s="3" t="s">
-        <v>568</v>
+        <v>580</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>569</v>
+        <v>581</v>
       </c>
       <c r="H75" s="1">
         <v>74</v>
@@ -10288,16 +9091,16 @@
     </row>
     <row r="76" customHeight="1" spans="2:9">
       <c r="B76" s="3" t="s">
-        <v>570</v>
+        <v>582</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>492</v>
+        <v>504</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>571</v>
+        <v>583</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>572</v>
+        <v>584</v>
       </c>
       <c r="H76" s="1">
         <v>75</v>
@@ -10311,10 +9114,10 @@
       <c r="B77" s="4"/>
       <c r="C77" s="4"/>
       <c r="D77" s="3" t="s">
-        <v>573</v>
+        <v>585</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>574</v>
+        <v>586</v>
       </c>
       <c r="H77" s="1">
         <v>76</v>
@@ -10328,10 +9131,10 @@
       <c r="B78" s="4"/>
       <c r="C78" s="4"/>
       <c r="D78" s="3" t="s">
-        <v>575</v>
+        <v>587</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>576</v>
+        <v>588</v>
       </c>
       <c r="H78" s="1">
         <v>77</v>
@@ -10345,10 +9148,10 @@
       <c r="B79" s="4"/>
       <c r="C79" s="4"/>
       <c r="D79" s="3" t="s">
-        <v>577</v>
+        <v>589</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>578</v>
+        <v>590</v>
       </c>
       <c r="H79" s="1">
         <v>78</v>
@@ -10362,10 +9165,10 @@
       <c r="B80" s="4"/>
       <c r="C80" s="4"/>
       <c r="D80" s="3" t="s">
-        <v>579</v>
+        <v>591</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>580</v>
+        <v>592</v>
       </c>
       <c r="H80" s="1">
         <v>79</v>
@@ -10379,10 +9182,10 @@
       <c r="B81" s="4"/>
       <c r="C81" s="4"/>
       <c r="D81" s="5" t="s">
-        <v>581</v>
+        <v>593</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>582</v>
+        <v>594</v>
       </c>
       <c r="H81" s="1">
         <v>80</v>
@@ -10396,10 +9199,10 @@
       <c r="B82" s="4"/>
       <c r="C82" s="4"/>
       <c r="D82" s="5" t="s">
-        <v>583</v>
+        <v>595</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>584</v>
+        <v>596</v>
       </c>
       <c r="H82" s="1">
         <v>81</v>
@@ -10413,10 +9216,10 @@
       <c r="B83" s="4"/>
       <c r="C83" s="4"/>
       <c r="D83" s="5" t="s">
-        <v>585</v>
+        <v>597</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>586</v>
+        <v>598</v>
       </c>
       <c r="H83" s="1">
         <v>82</v>
@@ -10430,10 +9233,10 @@
       <c r="B84" s="4"/>
       <c r="C84" s="4"/>
       <c r="D84" s="3" t="s">
-        <v>587</v>
+        <v>599</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>588</v>
+        <v>600</v>
       </c>
       <c r="H84" s="1">
         <v>83</v>
@@ -10445,16 +9248,16 @@
     </row>
     <row r="85" customHeight="1" spans="2:9">
       <c r="B85" s="3" t="s">
-        <v>589</v>
+        <v>601</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>590</v>
+        <v>602</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>591</v>
+        <v>603</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>592</v>
+        <v>604</v>
       </c>
       <c r="H85" s="1">
         <v>84</v>
@@ -10467,13 +9270,13 @@
     <row r="86" customHeight="1" spans="2:9">
       <c r="B86" s="4"/>
       <c r="C86" s="3" t="s">
-        <v>593</v>
+        <v>605</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>594</v>
+        <v>606</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>595</v>
+        <v>607</v>
       </c>
       <c r="H86" s="1">
         <v>85</v>
@@ -10487,10 +9290,10 @@
       <c r="B87" s="4"/>
       <c r="C87" s="4"/>
       <c r="D87" s="3" t="s">
-        <v>594</v>
+        <v>606</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>596</v>
+        <v>608</v>
       </c>
       <c r="H87" s="1">
         <v>86</v>
@@ -10504,10 +9307,10 @@
       <c r="B88" s="4"/>
       <c r="C88" s="4"/>
       <c r="D88" s="3" t="s">
-        <v>597</v>
+        <v>609</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>598</v>
+        <v>610</v>
       </c>
       <c r="H88" s="1">
         <v>87</v>
@@ -10521,10 +9324,10 @@
       <c r="B89" s="4"/>
       <c r="C89" s="4"/>
       <c r="D89" s="3" t="s">
-        <v>599</v>
+        <v>611</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>600</v>
+        <v>612</v>
       </c>
       <c r="H89" s="1">
         <v>88</v>
@@ -10536,13 +9339,13 @@
     </row>
     <row r="90" customHeight="1" spans="3:9">
       <c r="C90" s="3" t="s">
-        <v>601</v>
+        <v>613</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>602</v>
+        <v>614</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>603</v>
+        <v>615</v>
       </c>
       <c r="H90" s="1">
         <v>89</v>
@@ -10556,10 +9359,10 @@
       <c r="B91" s="4"/>
       <c r="C91" s="4"/>
       <c r="D91" s="3" t="s">
-        <v>604</v>
+        <v>616</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>605</v>
+        <v>617</v>
       </c>
       <c r="H91" s="1">
         <v>90</v>
@@ -10573,10 +9376,10 @@
       <c r="B92" s="4"/>
       <c r="C92" s="4"/>
       <c r="D92" s="3" t="s">
-        <v>606</v>
+        <v>618</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>607</v>
+        <v>619</v>
       </c>
       <c r="H92" s="1">
         <v>91</v>
@@ -10590,10 +9393,10 @@
       <c r="B93" s="4"/>
       <c r="C93" s="4"/>
       <c r="D93" s="3" t="s">
-        <v>608</v>
+        <v>620</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>609</v>
+        <v>621</v>
       </c>
       <c r="H93" s="1">
         <v>92</v>
@@ -10607,10 +9410,10 @@
       <c r="B94" s="4"/>
       <c r="C94" s="4"/>
       <c r="D94" s="3" t="s">
-        <v>610</v>
+        <v>622</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>611</v>
+        <v>623</v>
       </c>
       <c r="H94" s="1">
         <v>93</v>

--- a/GourmetProject/GameConfig/Datas/item.xlsx
+++ b/GourmetProject/GameConfig/Datas/item.xlsx
@@ -1322,7 +1322,7 @@
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>ItemSpecialTag</t>
         </is>
       </c>
       <c r="G3" s="7" t="inlineStr">
@@ -1397,7 +1397,11 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="F4" s="7" t="n"/>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G4" s="7" t="n">
         <v>2</v>
       </c>
@@ -1451,7 +1455,11 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="F5" s="7" t="n"/>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G5" s="7" t="n">
         <v>3</v>
       </c>
@@ -1505,7 +1513,11 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="F6" s="7" t="n"/>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G6" s="7" t="n">
         <v>2</v>
       </c>
@@ -1559,7 +1571,11 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="F7" s="7" t="n"/>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G7" s="7" t="n">
         <v>3</v>
       </c>
@@ -1613,7 +1629,11 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="F8" s="7" t="n"/>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G8" s="7" t="n">
         <v>3</v>
       </c>
@@ -1667,7 +1687,11 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="F9" s="7" t="n"/>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G9" s="7" t="n">
         <v>3</v>
       </c>
@@ -1721,7 +1745,11 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="F10" s="7" t="n"/>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G10" s="7" t="n">
         <v>1</v>
       </c>
@@ -1771,7 +1799,11 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="F11" s="7" t="n"/>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G11" s="7" t="n">
         <v>50</v>
       </c>
@@ -1825,7 +1857,11 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="F12" s="7" t="n"/>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G12" s="7" t="n">
         <v>0</v>
       </c>
@@ -1875,7 +1911,11 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="F13" s="7" t="n"/>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G13" s="7" t="n">
         <v>0</v>
       </c>
@@ -1930,7 +1970,11 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="F14" s="7" t="n"/>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G14" s="7" t="n">
         <v>15</v>
       </c>
@@ -1985,7 +2029,11 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="F15" s="7" t="n"/>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G15" s="7" t="n">
         <v>100</v>
       </c>
@@ -2036,7 +2084,11 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="F16" s="7" t="n"/>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G16" s="7" t="n">
         <v>0.2</v>
       </c>
@@ -2086,7 +2138,11 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="F17" s="7" t="n"/>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G17" s="7" t="n">
         <v>0.2</v>
       </c>
@@ -2136,7 +2192,11 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="F18" s="7" t="n"/>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G18" s="7" t="n">
         <v>0.2</v>
       </c>
@@ -2186,7 +2246,11 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="F19" s="7" t="n"/>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G19" s="7" t="n">
         <v>0.2</v>
       </c>
@@ -2236,7 +2300,11 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="F20" s="7" t="n"/>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G20" s="7" t="n">
         <v>0.2</v>
       </c>
@@ -2286,7 +2354,11 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="F21" s="7" t="n"/>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G21" s="7" t="n">
         <v>0.2</v>
       </c>
@@ -2336,7 +2408,11 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="F22" s="7" t="n"/>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G22" s="7" t="n">
         <v>30</v>
       </c>
@@ -2386,7 +2462,11 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="F23" s="7" t="n"/>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G23" s="7" t="n">
         <v>0.2</v>
       </c>
@@ -2437,7 +2517,11 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="F24" s="7" t="n"/>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G24" s="7" t="n">
         <v>0</v>
       </c>
@@ -2488,7 +2572,11 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="F25" s="7" t="n"/>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G25" s="7" t="n">
         <v>0</v>
       </c>
@@ -2542,7 +2630,11 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="F26" s="7" t="n"/>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G26" s="7" t="n">
         <v>-0.1</v>
       </c>
@@ -2592,7 +2684,11 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="F27" s="7" t="n"/>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G27" s="7" t="n">
         <v>-0.1</v>
       </c>
@@ -2642,7 +2738,11 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="F28" s="7" t="n"/>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G28" s="7" t="n">
         <v>-0.1</v>
       </c>
@@ -2693,7 +2793,11 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="F29" s="7" t="n"/>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G29" s="7" t="n">
         <v>1.1</v>
       </c>
@@ -2748,7 +2852,11 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="F30" s="7" t="n"/>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G30" s="7" t="n">
         <v>1.1</v>
       </c>
@@ -2803,7 +2911,11 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="F31" s="7" t="n"/>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G31" s="7" t="n">
         <v>0.1</v>
       </c>
@@ -2853,7 +2965,11 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="F32" s="7" t="n"/>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G32" s="7" t="n">
         <v>10</v>
       </c>
@@ -2903,7 +3019,11 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="F33" s="7" t="n"/>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G33" s="7" t="n">
         <v>0.2</v>
       </c>
@@ -2954,7 +3074,11 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="F34" s="7" t="n"/>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G34" s="7" t="n">
         <v>0</v>
       </c>
@@ -3008,7 +3132,11 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="F35" s="7" t="n"/>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G35" s="7" t="n">
         <v>0</v>
       </c>
@@ -3063,7 +3191,11 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="F36" s="7" t="n"/>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G36" s="7" t="n">
         <v>0</v>
       </c>
@@ -3113,7 +3245,11 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="F37" s="7" t="n"/>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G37" s="7" t="n">
         <v>1</v>
       </c>
@@ -3164,7 +3300,11 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="F38" s="7" t="n"/>
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G38" s="7" t="n">
         <v>0.2</v>
       </c>
@@ -3215,7 +3355,11 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="F39" s="7" t="n"/>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G39" s="7" t="n">
         <v>5</v>
       </c>
@@ -3266,7 +3410,11 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="F40" s="7" t="n"/>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G40" s="7" t="n">
         <v>5</v>
       </c>
@@ -3317,7 +3465,11 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="F41" s="7" t="n"/>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G41" s="7" t="n">
         <v>10</v>
       </c>
@@ -3368,7 +3520,11 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="F42" s="7" t="n"/>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G42" s="7" t="n">
         <v>1</v>
       </c>
@@ -3419,7 +3575,11 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="F43" s="7" t="n"/>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G43" s="7" t="n">
         <v>10</v>
       </c>
@@ -3469,7 +3629,11 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="F44" s="7" t="n"/>
+      <c r="F44" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G44" s="7" t="n">
         <v>10</v>
       </c>
@@ -3520,7 +3684,11 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="F45" s="7" t="n"/>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G45" s="7" t="n">
         <v>300</v>
       </c>
@@ -3574,7 +3742,11 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="F46" s="7" t="n"/>
+      <c r="F46" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G46" s="7" t="n">
         <v>0</v>
       </c>
@@ -3624,7 +3796,11 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="F47" s="7" t="n"/>
+      <c r="F47" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G47" s="7" t="n">
         <v>1</v>
       </c>
@@ -3674,7 +3850,11 @@
           <t>Epic</t>
         </is>
       </c>
-      <c r="F48" s="7" t="n"/>
+      <c r="F48" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G48" s="7" t="n">
         <v>1</v>
       </c>
@@ -3724,7 +3904,11 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="F49" s="7" t="n"/>
+      <c r="F49" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G49" s="7" t="n">
         <v>1</v>
       </c>
@@ -3774,7 +3958,11 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="F50" s="7" t="n"/>
+      <c r="F50" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G50" s="7" t="n">
         <v>1</v>
       </c>
@@ -3825,7 +4013,11 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="F51" s="7" t="n"/>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G51" s="7" t="n">
         <v>2</v>
       </c>
@@ -3880,7 +4072,11 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="F52" s="7" t="n"/>
+      <c r="F52" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G52" s="7" t="n">
         <v>2</v>
       </c>
@@ -3935,7 +4131,11 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="F53" s="7" t="n"/>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G53" s="7" t="n">
         <v>2</v>
       </c>
@@ -3989,7 +4189,11 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="F54" s="7" t="n"/>
+      <c r="F54" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G54" s="7" t="n">
         <v>2</v>
       </c>
@@ -4040,7 +4244,11 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="F55" s="7" t="n"/>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G55" s="7" t="n">
         <v>5</v>
       </c>
@@ -4091,7 +4299,11 @@
           <t>Epic</t>
         </is>
       </c>
-      <c r="F56" s="7" t="n"/>
+      <c r="F56" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G56" s="7" t="n">
         <v>1000</v>
       </c>
@@ -4141,7 +4353,11 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="F57" s="7" t="n"/>
+      <c r="F57" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G57" s="7" t="n">
         <v>2</v>
       </c>
@@ -4192,7 +4408,11 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="F58" s="7" t="n"/>
+      <c r="F58" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G58" s="7" t="n">
         <v>200</v>
       </c>
@@ -4243,7 +4463,11 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="F59" s="7" t="n"/>
+      <c r="F59" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G59" s="7" t="n">
         <v>2</v>
       </c>
@@ -4293,7 +4517,11 @@
           <t>Epic</t>
         </is>
       </c>
-      <c r="F60" s="7" t="n"/>
+      <c r="F60" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G60" s="7" t="n">
         <v>1</v>
       </c>
@@ -4344,7 +4572,11 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="F61" s="7" t="n"/>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G61" s="7" t="n">
         <v>1</v>
       </c>
@@ -4394,7 +4626,11 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="F62" s="7" t="n"/>
+      <c r="F62" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G62" s="7" t="n">
         <v>2</v>
       </c>
@@ -4445,7 +4681,11 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="F63" s="7" t="n"/>
+      <c r="F63" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G63" s="7" t="n">
         <v>1</v>
       </c>
@@ -4496,7 +4736,11 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="F64" s="7" t="n"/>
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G64" s="7" t="n">
         <v>4</v>
       </c>
@@ -4546,7 +4790,11 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="F65" s="7" t="n"/>
+      <c r="F65" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G65" s="7" t="n">
         <v>0.2</v>
       </c>
@@ -4596,7 +4844,11 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="F66" s="7" t="n"/>
+      <c r="F66" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G66" s="7" t="n">
         <v>0.2</v>
       </c>
@@ -4647,7 +4899,11 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="F67" s="7" t="n"/>
+      <c r="F67" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G67" s="7" t="n">
         <v>10</v>
       </c>
@@ -4697,7 +4953,11 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="F68" s="7" t="n"/>
+      <c r="F68" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G68" s="7" t="n">
         <v>0</v>
       </c>
@@ -4748,7 +5008,11 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="F69" s="7" t="n"/>
+      <c r="F69" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G69" s="7" t="n">
         <v>1</v>
       </c>
@@ -4799,7 +5063,11 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="F70" s="7" t="n"/>
+      <c r="F70" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G70" s="7" t="n">
         <v>1</v>
       </c>
@@ -4850,7 +5118,11 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="F71" s="7" t="n"/>
+      <c r="F71" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G71" s="7" t="n">
         <v>0</v>
       </c>
@@ -4905,7 +5177,11 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="F72" s="7" t="n"/>
+      <c r="F72" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G72" s="7" t="n">
         <v>0</v>
       </c>
@@ -4959,7 +5235,11 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="F73" s="7" t="n"/>
+      <c r="F73" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G73" s="7" t="n">
         <v>1</v>
       </c>
@@ -5013,7 +5293,11 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="F74" s="7" t="n"/>
+      <c r="F74" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G74" s="7" t="n">
         <v>2</v>
       </c>
@@ -5064,7 +5348,11 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="F75" s="7" t="n"/>
+      <c r="F75" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G75" s="7" t="n">
         <v>100</v>
       </c>
@@ -5601,7 +5889,11 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="F85" s="7" t="n"/>
+      <c r="F85" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G85" s="7" t="n">
         <v>1</v>
       </c>
@@ -5652,7 +5944,11 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="F86" s="7" t="n"/>
+      <c r="F86" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G86" s="7" t="n">
         <v>1.1</v>
       </c>
@@ -5708,7 +6004,11 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="F87" s="7" t="n"/>
+      <c r="F87" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G87" s="7" t="n">
         <v>1.1</v>
       </c>
@@ -5764,7 +6064,11 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="F88" s="7" t="n"/>
+      <c r="F88" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G88" s="7" t="n">
         <v>0.1</v>
       </c>
@@ -5820,7 +6124,11 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="F89" s="7" t="n"/>
+      <c r="F89" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G89" s="7" t="n">
         <v>10</v>
       </c>
@@ -5880,7 +6188,11 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="F90" s="7" t="n"/>
+      <c r="F90" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G90" s="7" t="n">
         <v>0.1</v>
       </c>
@@ -5935,7 +6247,11 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="F91" s="7" t="n"/>
+      <c r="F91" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G91" s="7" t="n">
         <v>10</v>
       </c>
@@ -5991,7 +6307,11 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="F92" s="7" t="n"/>
+      <c r="F92" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G92" s="7" t="n">
         <v>1</v>
       </c>
@@ -6047,7 +6367,11 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="F93" s="7" t="n"/>
+      <c r="F93" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G93" s="7" t="n">
         <v>10</v>
       </c>
@@ -6106,7 +6430,11 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="F94" s="7" t="n"/>
+      <c r="F94" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G94" s="7" t="n">
         <v>10</v>
       </c>
@@ -6331,7 +6659,7 @@
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>ItemSpecialTag</t>
         </is>
       </c>
       <c r="G3" s="7" t="inlineStr">
@@ -6393,7 +6721,11 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="F4" s="7" t="inlineStr"/>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
           <t>AddFlavor</t>
@@ -6447,7 +6779,11 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr"/>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
           <t>AddFlavor</t>
@@ -6501,7 +6837,11 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr"/>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
           <t>AddFlavor</t>
@@ -6555,7 +6895,11 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr"/>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
           <t>AddFlavor</t>
@@ -6609,7 +6953,11 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="F8" s="7" t="inlineStr"/>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
           <t>AddFlavor</t>
@@ -6663,7 +7011,11 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="F9" s="7" t="inlineStr"/>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
           <t>AddFlavor</t>
@@ -6717,7 +7069,11 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="F10" s="7" t="inlineStr"/>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
           <t>AddMaterial</t>
@@ -6771,7 +7127,11 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="F11" s="7" t="inlineStr"/>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
           <t>AddMaterial</t>
@@ -6825,7 +7185,11 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr"/>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
           <t>AddMaterial</t>
@@ -6879,7 +7243,11 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr"/>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
           <t>AddMaterial</t>
@@ -6933,7 +7301,11 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr"/>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
           <t>AddMaterial</t>
@@ -6987,7 +7359,11 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr"/>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
           <t>AddMaterial</t>
@@ -7041,7 +7417,11 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr"/>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
           <t>AddMaterial</t>
@@ -7095,7 +7475,11 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="F17" s="7" t="inlineStr"/>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
           <t>RerollAction</t>
@@ -7139,7 +7523,11 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="F18" s="7" t="inlineStr"/>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
           <t>ResetBossDebuff</t>
@@ -7183,7 +7571,11 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="F19" s="7" t="inlineStr"/>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
           <t>TimelineExecuteNext</t>
@@ -7227,7 +7619,11 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="F20" s="7" t="inlineStr"/>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
           <t>TimelineAddRewardNode</t>

--- a/GourmetProject/GameConfig/Datas/item.xlsx
+++ b/GourmetProject/GameConfig/Datas/item.xlsx
@@ -4,19 +4,32 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15200" activeTab="1"/>
+    <workbookView windowHeight="16760"/>
   </bookViews>
   <sheets>
     <sheet name="被动道具" sheetId="1" r:id="rId1"/>
     <sheet name="主动道具" sheetId="2" r:id="rId2"/>
     <sheet name="道具设计" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="860" uniqueCount="617">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="860" uniqueCount="618">
   <si>
     <t>##var</t>
   </si>
@@ -127,6 +140,9 @@
   </si>
   <si>
     <t>ItemQuality</t>
+  </si>
+  <si>
+    <t>ItemSpecialTag</t>
   </si>
   <si>
     <t>float</t>
@@ -1931,7 +1947,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -3102,37 +3118,37 @@
         <v>36</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>35</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Q3" t="s">
         <v>35</v>
@@ -3141,16 +3157,16 @@
     <row r="4" customFormat="1" spans="1:16">
       <c r="A4" s="1"/>
       <c r="B4" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F4" s="1"/>
       <c r="G4" s="1">
@@ -3187,16 +3203,16 @@
     <row r="5" customFormat="1" spans="1:16">
       <c r="A5" s="1"/>
       <c r="B5" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F5" s="1"/>
       <c r="G5" s="1">
@@ -3233,16 +3249,16 @@
     <row r="6" customFormat="1" spans="1:16">
       <c r="A6" s="1"/>
       <c r="B6" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>48</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>47</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="1">
@@ -3279,16 +3295,16 @@
     <row r="7" customFormat="1" spans="1:16">
       <c r="A7" s="1"/>
       <c r="B7" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F7" s="1"/>
       <c r="G7" s="1">
@@ -3324,16 +3340,16 @@
     </row>
     <row r="8" spans="2:27">
       <c r="B8" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F8" s="1"/>
       <c r="G8" s="1">
@@ -3367,7 +3383,7 @@
         <v>0</v>
       </c>
       <c r="S8" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="T8" s="1">
         <v>10</v>
@@ -3396,16 +3412,16 @@
     </row>
     <row r="9" spans="2:27">
       <c r="B9" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F9" s="1"/>
       <c r="G9" s="1">
@@ -3439,7 +3455,7 @@
         <v>0</v>
       </c>
       <c r="S9" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="T9" s="1">
         <v>20</v>
@@ -3468,16 +3484,16 @@
     </row>
     <row r="10" spans="2:27">
       <c r="B10" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F10" s="1"/>
       <c r="G10" s="1">
@@ -3511,7 +3527,7 @@
         <v>0</v>
       </c>
       <c r="S10" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="T10" s="1">
         <v>30</v>
@@ -3540,16 +3556,16 @@
     </row>
     <row r="11" spans="2:27">
       <c r="B11" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F11" s="1"/>
       <c r="G11" s="1">
@@ -3583,7 +3599,7 @@
         <v>0</v>
       </c>
       <c r="S11" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="T11" s="1">
         <v>40</v>
@@ -3612,16 +3628,16 @@
     </row>
     <row r="12" spans="2:27">
       <c r="B12" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F12" s="1"/>
       <c r="G12" s="1">
@@ -3655,7 +3671,7 @@
         <v>0</v>
       </c>
       <c r="S12" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="T12" s="1">
         <v>50</v>
@@ -3684,23 +3700,23 @@
     </row>
     <row r="13" spans="2:26">
       <c r="B13" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F13" s="1"/>
       <c r="G13" s="1">
         <v>0</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I13" s="1">
         <f t="shared" si="0"/>
@@ -3729,28 +3745,28 @@
         <v>0</v>
       </c>
       <c r="Z13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="14" ht="34" spans="2:26">
       <c r="B14" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F14" s="1"/>
       <c r="G14" s="1">
         <v>20</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I14" s="1">
         <f t="shared" si="0"/>
@@ -3779,13 +3795,13 @@
         <v>0</v>
       </c>
       <c r="T14" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V14">
         <v>300</v>
       </c>
       <c r="X14" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Z14">
         <f>COUNTIF($E$4:$E$92,T14)</f>
@@ -3794,16 +3810,16 @@
     </row>
     <row r="15" ht="34" spans="2:26">
       <c r="B15" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="1">
@@ -3837,13 +3853,13 @@
         <v>0</v>
       </c>
       <c r="T15" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="V15">
         <v>100</v>
       </c>
       <c r="X15" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Z15">
         <f>COUNTIF($E$4:$E$92,T15)</f>
@@ -3852,16 +3868,16 @@
     </row>
     <row r="16" ht="34" spans="2:26">
       <c r="B16" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F16" s="1"/>
       <c r="G16" s="1">
@@ -3895,13 +3911,13 @@
         <v>0</v>
       </c>
       <c r="T16" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="V16">
         <v>30</v>
       </c>
       <c r="X16" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Z16">
         <f>COUNTIF($E$4:$E$92,T16)</f>
@@ -3910,16 +3926,16 @@
     </row>
     <row r="17" spans="2:26">
       <c r="B17" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F17" s="1"/>
       <c r="G17" s="1">
@@ -3953,13 +3969,13 @@
         <v>0</v>
       </c>
       <c r="T17" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="V17">
         <v>10</v>
       </c>
       <c r="X17" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Z17">
         <f>COUNTIF($E$4:$E$92,T17)</f>
@@ -3969,16 +3985,16 @@
     <row r="18" customFormat="1" spans="1:16">
       <c r="A18" s="1"/>
       <c r="B18" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F18" s="1"/>
       <c r="G18" s="1">
@@ -4015,16 +4031,16 @@
     <row r="19" customFormat="1" spans="1:16">
       <c r="A19" s="1"/>
       <c r="B19" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F19" s="1"/>
       <c r="G19" s="1">
@@ -4061,16 +4077,16 @@
     <row r="20" customFormat="1" spans="1:16">
       <c r="A20" s="1"/>
       <c r="B20" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F20" s="1"/>
       <c r="G20" s="1">
@@ -4107,16 +4123,16 @@
     <row r="21" customFormat="1" spans="1:16">
       <c r="A21" s="1"/>
       <c r="B21" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F21" s="1"/>
       <c r="G21" s="1">
@@ -4153,16 +4169,16 @@
     <row r="22" customFormat="1" spans="1:16">
       <c r="A22" s="1"/>
       <c r="B22" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F22" s="1"/>
       <c r="G22" s="1">
@@ -4199,16 +4215,16 @@
     <row r="23" customFormat="1" spans="1:16">
       <c r="A23" s="1"/>
       <c r="B23" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F23" s="1"/>
       <c r="G23" s="1">
@@ -4245,16 +4261,16 @@
     <row r="24" customFormat="1" ht="34" spans="1:16">
       <c r="A24" s="1"/>
       <c r="B24" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F24" s="1"/>
       <c r="G24" s="1">
@@ -4291,23 +4307,23 @@
     <row r="25" customFormat="1" ht="34" spans="1:16">
       <c r="A25" s="1"/>
       <c r="B25" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F25" s="1"/>
       <c r="G25" s="1">
         <v>0</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I25" s="1">
         <f t="shared" si="0"/>
@@ -4339,16 +4355,16 @@
     <row r="26" customFormat="1" spans="1:16">
       <c r="A26" s="1"/>
       <c r="B26" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F26" s="1"/>
       <c r="G26" s="1">
@@ -4385,16 +4401,16 @@
     <row r="27" customFormat="1" spans="1:16">
       <c r="A27" s="1"/>
       <c r="B27" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F27" s="1"/>
       <c r="G27" s="1">
@@ -4431,16 +4447,16 @@
     <row r="28" customFormat="1" spans="1:16">
       <c r="A28" s="1"/>
       <c r="B28" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F28" s="1"/>
       <c r="G28" s="1">
@@ -4477,23 +4493,23 @@
     <row r="29" customFormat="1" ht="34" spans="1:16">
       <c r="A29" s="1"/>
       <c r="B29" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F29" s="1"/>
       <c r="G29" s="1">
         <v>1.1</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I29" s="1">
         <f t="shared" si="0"/>
@@ -4525,23 +4541,23 @@
     <row r="30" customFormat="1" ht="34" spans="1:16">
       <c r="A30" s="1"/>
       <c r="B30" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F30" s="1"/>
       <c r="G30" s="1">
         <v>1.1</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I30" s="1">
         <f t="shared" si="0"/>
@@ -4573,16 +4589,16 @@
     <row r="31" customFormat="1" ht="34" spans="1:16">
       <c r="A31" s="1"/>
       <c r="B31" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F31" s="1"/>
       <c r="G31" s="1">
@@ -4619,16 +4635,16 @@
     <row r="32" customFormat="1" spans="1:16">
       <c r="A32" s="1"/>
       <c r="B32" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F32" s="1"/>
       <c r="G32" s="1">
@@ -4665,23 +4681,23 @@
     <row r="33" customFormat="1" ht="34" spans="1:16">
       <c r="A33" s="1"/>
       <c r="B33" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F33" s="1"/>
       <c r="G33" s="1">
         <v>0</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I33" s="1">
         <f t="shared" si="0"/>
@@ -4713,23 +4729,23 @@
     <row r="34" customFormat="1" ht="34" spans="1:16">
       <c r="A34" s="1"/>
       <c r="B34" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F34" s="1"/>
       <c r="G34" s="1">
         <v>0</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I34" s="1">
         <f t="shared" si="0"/>
@@ -4761,16 +4777,16 @@
     <row r="35" customFormat="1" ht="34" spans="1:16">
       <c r="A35" s="1"/>
       <c r="B35" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F35" s="1"/>
       <c r="G35" s="1">
@@ -4807,16 +4823,16 @@
     <row r="36" customFormat="1" spans="1:16">
       <c r="A36" s="1"/>
       <c r="B36" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F36" s="1"/>
       <c r="G36" s="1">
@@ -4853,16 +4869,16 @@
     <row r="37" customFormat="1" ht="34" spans="1:16">
       <c r="A37" s="1"/>
       <c r="B37" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F37" s="1"/>
       <c r="G37" s="1">
@@ -4899,16 +4915,16 @@
     <row r="38" customFormat="1" ht="34" spans="1:16">
       <c r="A38" s="1"/>
       <c r="B38" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F38" s="1"/>
       <c r="G38" s="1">
@@ -4945,16 +4961,16 @@
     <row r="39" customFormat="1" ht="34" spans="1:16">
       <c r="A39" s="1"/>
       <c r="B39" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F39" s="1"/>
       <c r="G39" s="1">
@@ -4991,16 +5007,16 @@
     <row r="40" customFormat="1" ht="34" spans="1:16">
       <c r="A40" s="1"/>
       <c r="B40" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F40" s="1"/>
       <c r="G40" s="1">
@@ -5037,16 +5053,16 @@
     <row r="41" customFormat="1" ht="34" spans="1:16">
       <c r="A41" s="1"/>
       <c r="B41" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F41" s="1"/>
       <c r="G41" s="1">
@@ -5083,16 +5099,16 @@
     <row r="42" customFormat="1" spans="1:16">
       <c r="A42" s="1"/>
       <c r="B42" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F42" s="1"/>
       <c r="G42" s="1">
@@ -5129,23 +5145,23 @@
     <row r="43" customFormat="1" ht="34" spans="1:16">
       <c r="A43" s="1"/>
       <c r="B43" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F43" s="1"/>
       <c r="G43" s="1">
         <v>300</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I43" s="1">
         <f t="shared" si="0"/>
@@ -5177,16 +5193,16 @@
     <row r="44" customFormat="1" spans="1:16">
       <c r="A44" s="1"/>
       <c r="B44" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F44" s="1"/>
       <c r="G44" s="1">
@@ -5223,16 +5239,16 @@
     <row r="45" customFormat="1" spans="1:16">
       <c r="A45" s="1"/>
       <c r="B45" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F45" s="1"/>
       <c r="G45" s="1">
@@ -5269,16 +5285,16 @@
     <row r="46" customFormat="1" spans="1:16">
       <c r="A46" s="1"/>
       <c r="B46" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F46" s="1"/>
       <c r="G46" s="1">
@@ -5315,16 +5331,16 @@
     <row r="47" customFormat="1" ht="34" spans="1:16">
       <c r="A47" s="1"/>
       <c r="B47" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F47" s="1"/>
       <c r="G47" s="1">
@@ -5361,16 +5377,16 @@
     <row r="48" customFormat="1" ht="34" spans="1:16">
       <c r="A48" s="1"/>
       <c r="B48" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F48" s="1"/>
       <c r="G48" s="1">
@@ -5407,23 +5423,23 @@
     <row r="49" customFormat="1" ht="34" spans="1:16">
       <c r="A49" s="1"/>
       <c r="B49" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F49" s="1"/>
       <c r="G49" s="1">
         <v>2</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I49" s="1">
         <f t="shared" si="0"/>
@@ -5455,23 +5471,23 @@
     <row r="50" customFormat="1" ht="34" spans="1:16">
       <c r="A50" s="1"/>
       <c r="B50" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F50" s="1"/>
       <c r="G50" s="1">
         <v>2</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I50" s="1">
         <f t="shared" si="0"/>
@@ -5503,23 +5519,23 @@
     <row r="51" customFormat="1" ht="34" spans="1:16">
       <c r="A51" s="1"/>
       <c r="B51" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F51" s="1"/>
       <c r="G51" s="1">
         <v>2</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I51" s="1">
         <f t="shared" si="0"/>
@@ -5551,16 +5567,16 @@
     <row r="52" customFormat="1" spans="1:16">
       <c r="A52" s="1"/>
       <c r="B52" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F52" s="1"/>
       <c r="G52" s="1">
@@ -5597,16 +5613,16 @@
     <row r="53" customFormat="1" ht="34" spans="1:16">
       <c r="A53" s="1"/>
       <c r="B53" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F53" s="1"/>
       <c r="G53" s="1">
@@ -5643,16 +5659,16 @@
     <row r="54" customFormat="1" ht="34" spans="1:16">
       <c r="A54" s="1"/>
       <c r="B54" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F54" s="1"/>
       <c r="G54" s="1">
@@ -5689,16 +5705,16 @@
     <row r="55" customFormat="1" spans="1:16">
       <c r="A55" s="1"/>
       <c r="B55" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F55" s="1"/>
       <c r="G55" s="1">
@@ -5735,16 +5751,16 @@
     <row r="56" customFormat="1" ht="34" spans="1:16">
       <c r="A56" s="1"/>
       <c r="B56" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F56" s="1"/>
       <c r="G56" s="1">
@@ -5781,16 +5797,16 @@
     <row r="57" customFormat="1" ht="34" spans="1:16">
       <c r="A57" s="1"/>
       <c r="B57" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D57" s="7" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F57" s="1"/>
       <c r="G57" s="1">
@@ -5827,16 +5843,16 @@
     <row r="58" customFormat="1" spans="1:16">
       <c r="A58" s="1"/>
       <c r="B58" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F58" s="1"/>
       <c r="G58" s="1">
@@ -5873,16 +5889,16 @@
     <row r="59" customFormat="1" ht="34" spans="1:16">
       <c r="A59" s="1"/>
       <c r="B59" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F59" s="1"/>
       <c r="G59" s="1">
@@ -5919,16 +5935,16 @@
     <row r="60" customFormat="1" ht="34" spans="1:16">
       <c r="A60" s="1"/>
       <c r="B60" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F60" s="1"/>
       <c r="G60" s="1">
@@ -5965,16 +5981,16 @@
     <row r="61" customFormat="1" ht="34" spans="1:16">
       <c r="A61" s="1"/>
       <c r="B61" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D61" s="7" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F61" s="1"/>
       <c r="G61" s="1">
@@ -6011,16 +6027,16 @@
     <row r="62" customFormat="1" ht="34" spans="1:16">
       <c r="A62" s="1"/>
       <c r="B62" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F62" s="1"/>
       <c r="G62" s="1">
@@ -6057,16 +6073,16 @@
     <row r="63" customFormat="1" spans="1:16">
       <c r="A63" s="1"/>
       <c r="B63" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F63" s="1"/>
       <c r="G63" s="1">
@@ -6103,16 +6119,16 @@
     <row r="64" customFormat="1" spans="1:16">
       <c r="A64" s="1"/>
       <c r="B64" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F64" s="1"/>
       <c r="G64" s="1">
@@ -6149,16 +6165,16 @@
     <row r="65" customFormat="1" ht="34" spans="1:16">
       <c r="A65" s="1"/>
       <c r="B65" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D65" s="7" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F65" s="1"/>
       <c r="G65" s="1">
@@ -6195,16 +6211,16 @@
     <row r="66" customFormat="1" spans="1:16">
       <c r="A66" s="1"/>
       <c r="B66" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F66" s="1"/>
       <c r="G66" s="1">
@@ -6241,16 +6257,16 @@
     <row r="67" customFormat="1" ht="34" spans="1:16">
       <c r="A67" s="1"/>
       <c r="B67" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F67" s="1"/>
       <c r="G67" s="1">
@@ -6287,16 +6303,16 @@
     <row r="68" customFormat="1" ht="34" spans="1:16">
       <c r="A68" s="1"/>
       <c r="B68" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F68" s="1"/>
       <c r="G68" s="1">
@@ -6333,23 +6349,23 @@
     <row r="69" customFormat="1" ht="34" spans="1:16">
       <c r="A69" s="1"/>
       <c r="B69" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D69" s="7" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F69" s="1"/>
       <c r="G69" s="1">
         <v>0</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I69" s="1">
         <f t="shared" si="2"/>
@@ -6381,23 +6397,23 @@
     <row r="70" customFormat="1" ht="34" spans="1:16">
       <c r="A70" s="1"/>
       <c r="B70" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D70" s="7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F70" s="1"/>
       <c r="G70" s="1">
         <v>0</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="I70" s="1">
         <f t="shared" si="2"/>
@@ -6429,16 +6445,16 @@
     <row r="71" customFormat="1" spans="1:16">
       <c r="A71" s="1"/>
       <c r="B71" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F71" s="1"/>
       <c r="G71" s="1">
@@ -6475,16 +6491,16 @@
     <row r="72" customFormat="1" spans="1:16">
       <c r="A72" s="1"/>
       <c r="B72" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F72" s="1"/>
       <c r="G72" s="1">
@@ -6521,16 +6537,16 @@
     <row r="73" customFormat="1" ht="34" spans="1:16">
       <c r="A73" s="1"/>
       <c r="B73" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D73" s="7" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F73" s="1"/>
       <c r="G73" s="1">
@@ -6567,19 +6583,19 @@
     <row r="74" customFormat="1" spans="1:16">
       <c r="A74" s="1"/>
       <c r="B74" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="G74" s="1">
         <v>-0.2</v>
@@ -6615,19 +6631,19 @@
     <row r="75" customFormat="1" spans="1:16">
       <c r="A75" s="1"/>
       <c r="B75" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F75" s="1" t="s">
         <v>285</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="D75" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="E75" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F75" s="1" t="s">
-        <v>284</v>
       </c>
       <c r="G75" s="1">
         <v>0.2</v>
@@ -6663,19 +6679,19 @@
     <row r="76" customFormat="1" spans="1:16">
       <c r="A76" s="1"/>
       <c r="B76" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="G76" s="1">
         <v>0</v>
@@ -6711,19 +6727,19 @@
     <row r="77" customFormat="1" spans="1:16">
       <c r="A77" s="1"/>
       <c r="B77" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="G77" s="1">
         <v>1</v>
@@ -6759,19 +6775,19 @@
     <row r="78" customFormat="1" ht="34" spans="1:16">
       <c r="A78" s="1"/>
       <c r="B78" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D78" s="7" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="G78" s="1">
         <v>-1</v>
@@ -6807,19 +6823,19 @@
     <row r="79" customFormat="1" spans="1:16">
       <c r="A79" s="1"/>
       <c r="B79" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="G79" s="1">
         <v>0.2</v>
@@ -6855,19 +6871,19 @@
     <row r="80" customFormat="1" spans="1:16">
       <c r="A80" s="1"/>
       <c r="B80" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="G80" s="1">
         <v>0.15</v>
@@ -6903,19 +6919,19 @@
     <row r="81" customFormat="1" spans="1:16">
       <c r="A81" s="1"/>
       <c r="B81" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="G81" s="1">
         <v>0.15</v>
@@ -6951,19 +6967,19 @@
     <row r="82" customFormat="1" spans="1:16">
       <c r="A82" s="1"/>
       <c r="B82" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="G82" s="1">
         <v>0</v>
@@ -6999,16 +7015,16 @@
     <row r="83" customFormat="1" spans="1:16">
       <c r="A83" s="1"/>
       <c r="B83" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F83" s="1"/>
       <c r="G83" s="1">
@@ -7045,16 +7061,16 @@
     <row r="84" customFormat="1" ht="34" spans="1:17">
       <c r="A84" s="1"/>
       <c r="B84" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D84" s="7" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F84" s="1"/>
       <c r="G84" s="1">
@@ -7088,22 +7104,22 @@
         <v>0</v>
       </c>
       <c r="Q84" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="85" customFormat="1" ht="34" spans="1:17">
       <c r="A85" s="1"/>
       <c r="B85" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D85" s="7" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F85" s="1"/>
       <c r="G85" s="1">
@@ -7137,22 +7153,22 @@
         <v>0</v>
       </c>
       <c r="Q85" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="86" customFormat="1" ht="34" spans="1:17">
       <c r="A86" s="1"/>
       <c r="B86" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D86" s="7" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F86" s="1"/>
       <c r="G86" s="1">
@@ -7186,29 +7202,29 @@
         <v>0</v>
       </c>
       <c r="Q86" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="87" customFormat="1" ht="34" spans="1:17">
       <c r="A87" s="1"/>
       <c r="B87" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D87" s="7" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F87" s="1"/>
       <c r="G87" s="1">
         <v>10</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="I87" s="1">
         <f t="shared" si="2"/>
@@ -7237,22 +7253,22 @@
         <v>0</v>
       </c>
       <c r="Q87" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="88" customFormat="1" ht="34" spans="1:17">
       <c r="A88" s="1"/>
       <c r="B88" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D88" s="7" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F88" s="1"/>
       <c r="G88" s="1">
@@ -7286,22 +7302,22 @@
         <v>0</v>
       </c>
       <c r="Q88" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="89" customFormat="1" ht="34" spans="1:17">
       <c r="A89" s="1"/>
       <c r="B89" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D89" s="7" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F89" s="1"/>
       <c r="G89" s="1">
@@ -7335,22 +7351,22 @@
         <v>0</v>
       </c>
       <c r="Q89" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="90" customFormat="1" ht="34" spans="1:17">
       <c r="A90" s="1"/>
       <c r="B90" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D90" s="7" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F90" s="1"/>
       <c r="G90" s="1">
@@ -7384,29 +7400,29 @@
         <v>0</v>
       </c>
       <c r="Q90" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="91" customFormat="1" ht="34" spans="1:17">
       <c r="A91" s="1"/>
       <c r="B91" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D91" s="7" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F91" s="1"/>
       <c r="G91" s="1">
         <v>10</v>
       </c>
       <c r="H91" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="I91" s="1">
         <f t="shared" si="2"/>
@@ -7435,22 +7451,22 @@
         <v>0</v>
       </c>
       <c r="Q91" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="92" customFormat="1" spans="1:17">
       <c r="A92" s="1"/>
       <c r="B92" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F92" s="1"/>
       <c r="G92" s="1">
@@ -7484,7 +7500,7 @@
         <v>0</v>
       </c>
       <c r="Q92" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
   </sheetData>
@@ -7530,7 +7546,7 @@
         <v>5</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>6</v>
@@ -7542,10 +7558,10 @@
         <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L1" t="s">
         <v>16</v>
@@ -7568,7 +7584,7 @@
         <v>22</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>23</v>
@@ -7580,10 +7596,10 @@
         <v>25</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L2" t="s">
         <v>33</v>
@@ -7609,19 +7625,19 @@
         <v>35</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>35</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L3" t="s">
         <v>35</v>
@@ -7629,528 +7645,528 @@
     </row>
     <row r="4" customFormat="1" ht="34" spans="1:12">
       <c r="A4" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>354</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>353</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>350</v>
-      </c>
       <c r="F4" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="G4" s="1">
         <v>0</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="I4" s="1">
         <v>1</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="K4" s="1">
         <v>1</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="5" customFormat="1" ht="34" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="G5" s="1">
         <v>0</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="I5" s="1">
         <v>1</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="K5" s="1">
         <v>1</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="6" customFormat="1" ht="34" spans="1:12">
       <c r="A6" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="I6" s="1">
         <v>1</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="K6" s="1">
         <v>1</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="7" customFormat="1" ht="34" spans="1:12">
       <c r="A7" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="I7" s="1">
         <v>1</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="K7" s="1">
         <v>1</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="8" customFormat="1" ht="34" spans="1:12">
       <c r="A8" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="I8" s="1">
         <v>1</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="K8" s="1">
         <v>1</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="9" customFormat="1" ht="34" spans="1:12">
       <c r="A9" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="I9" s="1">
         <v>1</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="K9" s="1">
         <v>1</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="10" customFormat="1" ht="34" spans="1:12">
       <c r="A10" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="I10" s="1">
         <v>1</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="K10" s="1">
         <v>1</v>
       </c>
       <c r="L10" s="8" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="11" customFormat="1" ht="34" spans="1:12">
       <c r="A11" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="G11" s="1">
         <v>0</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="I11" s="1">
         <v>1</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="K11" s="1">
         <v>1</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="12" customFormat="1" ht="34" spans="1:12">
       <c r="A12" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="I12" s="1">
         <v>1</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="K12" s="1">
         <v>1</v>
       </c>
       <c r="L12" s="8" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="13" customFormat="1" ht="34" spans="1:12">
       <c r="A13" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="G13" s="1">
         <v>0</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="I13" s="1">
         <v>1</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="K13" s="1">
         <v>1</v>
       </c>
       <c r="L13" s="8" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="14" customFormat="1" ht="34" spans="1:12">
       <c r="A14" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="G14" s="1">
         <v>0</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="I14" s="1">
         <v>1</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="K14" s="1">
         <v>1</v>
       </c>
       <c r="L14" s="8" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="15" customFormat="1" ht="34" spans="1:12">
       <c r="A15" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="G15" s="1">
         <v>0</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="I15" s="1">
         <v>1</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="K15" s="1">
         <v>1</v>
       </c>
       <c r="L15" s="8" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="16" customFormat="1" ht="34" spans="1:12">
       <c r="A16" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="G16" s="1">
         <v>0</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="I16" s="1">
         <v>1</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="K16" s="1">
         <v>1</v>
       </c>
       <c r="L16" s="8" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="17" customFormat="1" ht="34" spans="1:11">
       <c r="A17" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="G17" s="1">
         <v>0</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="I17" s="1">
         <v>1</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="K17" s="1">
         <v>0</v>
@@ -8158,34 +8174,34 @@
     </row>
     <row r="18" customFormat="1" spans="1:11">
       <c r="A18" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="G18" s="1">
         <v>0</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="I18" s="1">
         <v>1</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="K18" s="1">
         <v>0</v>
@@ -8193,34 +8209,34 @@
     </row>
     <row r="19" customFormat="1" spans="1:11">
       <c r="A19" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="G19" s="1">
         <v>0</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="I19" s="1">
         <v>1</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="K19" s="1">
         <v>0</v>
@@ -8228,34 +8244,34 @@
     </row>
     <row r="20" customFormat="1" spans="1:11">
       <c r="A20" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="G20" s="1">
         <v>0</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="I20" s="1">
         <v>1</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="K20" s="1">
         <v>0</v>
@@ -8282,36 +8298,36 @@
   <sheetData>
     <row r="1" customHeight="1" spans="2:9">
       <c r="B1" s="3" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="2:9">
       <c r="B2" s="3" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H2" s="1">
         <v>1</v>
@@ -8325,10 +8341,10 @@
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
       <c r="D3" s="3" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H3" s="1">
         <v>2</v>
@@ -8342,10 +8358,10 @@
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
       <c r="D4" s="3" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H4" s="1">
         <v>3</v>
@@ -8359,10 +8375,10 @@
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
       <c r="D5" s="3" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H5" s="1">
         <v>4</v>
@@ -8376,10 +8392,10 @@
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
       <c r="D6" s="3" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H6" s="1">
         <v>5</v>
@@ -8393,10 +8409,10 @@
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
       <c r="D7" s="3" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H7" s="1">
         <v>6</v>
@@ -8410,10 +8426,10 @@
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
       <c r="D8" s="3" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H8" s="1">
         <v>7</v>
@@ -8427,10 +8443,10 @@
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
       <c r="D9" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H9" s="1">
         <v>8</v>
@@ -8444,10 +8460,10 @@
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
       <c r="D10" s="3" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H10" s="1">
         <v>9</v>
@@ -8460,13 +8476,13 @@
     <row r="11" customHeight="1" spans="2:9">
       <c r="B11" s="4"/>
       <c r="C11" s="3" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H11" s="1">
         <v>10</v>
@@ -8480,10 +8496,10 @@
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
       <c r="D12" s="3" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H12" s="1">
         <v>11</v>
@@ -8497,10 +8513,10 @@
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
       <c r="D13" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H13" s="1">
         <v>12</v>
@@ -8514,10 +8530,10 @@
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
       <c r="D14" s="3" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H14" s="1">
         <v>13</v>
@@ -8530,13 +8546,13 @@
     <row r="15" customHeight="1" spans="2:9">
       <c r="B15" s="4"/>
       <c r="C15" s="3" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H15" s="1">
         <v>14</v>
@@ -8550,10 +8566,10 @@
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
       <c r="D16" s="3" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H16" s="1">
         <v>15</v>
@@ -8567,10 +8583,10 @@
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
       <c r="D17" s="3" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H17" s="1">
         <v>16</v>
@@ -8584,10 +8600,10 @@
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
       <c r="D18" s="3" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H18" s="1">
         <v>17</v>
@@ -8601,10 +8617,10 @@
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
       <c r="D19" s="3" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H19" s="1">
         <v>18</v>
@@ -8618,10 +8634,10 @@
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
       <c r="D20" s="3" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H20" s="1">
         <v>19</v>
@@ -8635,10 +8651,10 @@
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
       <c r="D21" s="3" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H21" s="1">
         <v>20</v>
@@ -8651,13 +8667,13 @@
     <row r="22" customHeight="1" spans="2:9">
       <c r="B22" s="4"/>
       <c r="C22" s="3" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H22" s="1">
         <v>21</v>
@@ -8670,13 +8686,13 @@
     <row r="23" customHeight="1" spans="2:9">
       <c r="B23" s="4"/>
       <c r="C23" s="3" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H23" s="1">
         <v>22</v>
@@ -8690,10 +8706,10 @@
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
       <c r="D24" s="3" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H24" s="1">
         <v>23</v>
@@ -8707,10 +8723,10 @@
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
       <c r="D25" s="3" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H25" s="1">
         <v>24</v>
@@ -8724,10 +8740,10 @@
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
       <c r="D26" s="3" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H26" s="1">
         <v>25</v>
@@ -8740,13 +8756,13 @@
     <row r="27" customHeight="1" spans="2:9">
       <c r="B27" s="4"/>
       <c r="C27" s="3" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H27" s="1">
         <v>26</v>
@@ -8760,10 +8776,10 @@
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
       <c r="D28" s="3" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H28" s="1">
         <v>27</v>
@@ -8776,13 +8792,13 @@
     <row r="29" customHeight="1" spans="2:9">
       <c r="B29" s="4"/>
       <c r="C29" s="3" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H29" s="1">
         <v>28</v>
@@ -8795,13 +8811,13 @@
     <row r="30" customHeight="1" spans="2:9">
       <c r="B30" s="4"/>
       <c r="C30" s="3" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H30" s="1">
         <v>29</v>
@@ -8814,13 +8830,13 @@
     <row r="31" customHeight="1" spans="2:9">
       <c r="B31" s="4"/>
       <c r="C31" s="3" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H31" s="1">
         <v>30</v>
@@ -8833,13 +8849,13 @@
     <row r="32" customHeight="1" spans="2:9">
       <c r="B32" s="4"/>
       <c r="C32" s="3" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H32" s="1">
         <v>31</v>
@@ -8853,10 +8869,10 @@
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
       <c r="D33" s="3" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H33" s="1">
         <v>32</v>
@@ -8870,10 +8886,10 @@
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
       <c r="D34" s="3" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H34" s="1">
         <v>33</v>
@@ -8886,13 +8902,13 @@
     <row r="35" customHeight="1" spans="2:9">
       <c r="B35" s="4"/>
       <c r="C35" s="5" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H35" s="1">
         <v>34</v>
@@ -8906,10 +8922,10 @@
       <c r="B36" s="4"/>
       <c r="C36" s="5"/>
       <c r="D36" s="6" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H36" s="1">
         <v>35</v>
@@ -8922,13 +8938,13 @@
     <row r="37" customHeight="1" spans="2:9">
       <c r="B37" s="4"/>
       <c r="C37" s="3" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H37" s="1">
         <v>36</v>
@@ -8941,13 +8957,13 @@
     <row r="38" customHeight="1" spans="2:9">
       <c r="B38" s="4"/>
       <c r="C38" s="3" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H38" s="1">
         <v>37</v>
@@ -8961,10 +8977,10 @@
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
       <c r="D39" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H39" s="1">
         <v>38</v>
@@ -8978,10 +8994,10 @@
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
       <c r="D40" s="3" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H40" s="1">
         <v>39</v>
@@ -8995,10 +9011,10 @@
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
       <c r="D41" s="3" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H41" s="1">
         <v>40</v>
@@ -9012,10 +9028,10 @@
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
       <c r="D42" s="3" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H42" s="1">
         <v>41</v>
@@ -9029,10 +9045,10 @@
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
       <c r="D43" s="3" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H43" s="1">
         <v>42</v>
@@ -9045,13 +9061,13 @@
     <row r="44" customHeight="1" spans="2:9">
       <c r="B44" s="4"/>
       <c r="C44" s="3" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H44" s="1">
         <v>43</v>
@@ -9065,10 +9081,10 @@
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
       <c r="D45" s="3" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H45" s="1">
         <v>44</v>
@@ -9082,10 +9098,10 @@
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
       <c r="D46" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H46" s="1">
         <v>45</v>
@@ -9099,10 +9115,10 @@
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
       <c r="D47" s="3" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H47" s="1">
         <v>46</v>
@@ -9116,10 +9132,10 @@
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
       <c r="D48" s="3" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H48" s="1">
         <v>47</v>
@@ -9132,13 +9148,13 @@
     <row r="49" customHeight="1" spans="2:9">
       <c r="B49" s="4"/>
       <c r="C49" s="3" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H49" s="1">
         <v>48</v>
@@ -9152,10 +9168,10 @@
       <c r="B50" s="4"/>
       <c r="C50" s="4"/>
       <c r="D50" s="3" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H50" s="1">
         <v>49</v>
@@ -9169,10 +9185,10 @@
       <c r="B51" s="4"/>
       <c r="C51" s="4"/>
       <c r="D51" s="3" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H51" s="1">
         <v>50</v>
@@ -9185,13 +9201,13 @@
     <row r="52" customHeight="1" spans="2:9">
       <c r="B52" s="4"/>
       <c r="C52" s="3" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H52" s="1">
         <v>51</v>
@@ -9205,10 +9221,10 @@
       <c r="B53" s="4"/>
       <c r="C53" s="4"/>
       <c r="D53" s="3" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H53" s="1">
         <v>52</v>
@@ -9222,10 +9238,10 @@
       <c r="B54" s="4"/>
       <c r="C54" s="4"/>
       <c r="D54" s="3" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H54" s="1">
         <v>53</v>
@@ -9238,13 +9254,13 @@
     <row r="55" customHeight="1" spans="2:9">
       <c r="B55" s="4"/>
       <c r="C55" s="3" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H55" s="1">
         <v>54</v>
@@ -9258,10 +9274,10 @@
       <c r="B56" s="4"/>
       <c r="C56" s="4"/>
       <c r="D56" s="3" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H56" s="1">
         <v>55</v>
@@ -9275,10 +9291,10 @@
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
       <c r="D57" s="3" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H57" s="1">
         <v>56</v>
@@ -9292,10 +9308,10 @@
       <c r="B58" s="4"/>
       <c r="C58" s="4"/>
       <c r="D58" s="3" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H58" s="1">
         <v>57</v>
@@ -9309,10 +9325,10 @@
       <c r="B59" s="4"/>
       <c r="C59" s="4"/>
       <c r="D59" s="3" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H59" s="1">
         <v>58</v>
@@ -9326,10 +9342,10 @@
       <c r="B60" s="4"/>
       <c r="C60" s="4"/>
       <c r="D60" s="3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H60" s="1">
         <v>59</v>
@@ -9342,13 +9358,13 @@
     <row r="61" customHeight="1" spans="2:9">
       <c r="B61" s="4"/>
       <c r="C61" s="3" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H61" s="1">
         <v>60</v>
@@ -9362,10 +9378,10 @@
       <c r="B62" s="4"/>
       <c r="C62" s="4"/>
       <c r="D62" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H62" s="1">
         <v>61</v>
@@ -9378,13 +9394,13 @@
     <row r="63" customHeight="1" spans="2:9">
       <c r="B63" s="4"/>
       <c r="C63" s="3" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H63" s="1">
         <v>62</v>
@@ -9398,10 +9414,10 @@
       <c r="B64" s="4"/>
       <c r="C64" s="4"/>
       <c r="D64" s="3" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H64" s="1">
         <v>63</v>
@@ -9415,10 +9431,10 @@
       <c r="B65" s="4"/>
       <c r="C65" s="4"/>
       <c r="D65" s="3" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H65" s="1">
         <v>64</v>
@@ -9432,10 +9448,10 @@
       <c r="B66" s="4"/>
       <c r="C66" s="4"/>
       <c r="D66" s="3" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H66" s="1">
         <v>65</v>
@@ -9449,10 +9465,10 @@
       <c r="B67" s="4"/>
       <c r="C67" s="4"/>
       <c r="D67" s="3" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H67" s="1">
         <v>66</v>
@@ -9465,13 +9481,13 @@
     <row r="68" customHeight="1" spans="2:9">
       <c r="B68" s="4"/>
       <c r="C68" s="3" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H68" s="1">
         <v>67</v>
@@ -9484,13 +9500,13 @@
     <row r="69" customHeight="1" spans="2:9">
       <c r="B69" s="4"/>
       <c r="C69" s="3" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H69" s="1">
         <v>68</v>
@@ -9504,10 +9520,10 @@
       <c r="B70" s="4"/>
       <c r="C70" s="4"/>
       <c r="D70" s="3" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H70" s="1">
         <v>69</v>
@@ -9521,10 +9537,10 @@
       <c r="B71" s="4"/>
       <c r="C71" s="4"/>
       <c r="D71" s="3" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H71" s="1">
         <v>70</v>
@@ -9538,10 +9554,10 @@
       <c r="B72" s="4"/>
       <c r="C72" s="4"/>
       <c r="D72" s="3" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H72" s="1">
         <v>71</v>
@@ -9555,10 +9571,10 @@
       <c r="B73" s="4"/>
       <c r="C73" s="4"/>
       <c r="D73" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H73" s="1">
         <v>72</v>
@@ -9571,13 +9587,13 @@
     <row r="74" customHeight="1" spans="2:9">
       <c r="B74" s="4"/>
       <c r="C74" s="3" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H74" s="1">
         <v>73</v>
@@ -9591,10 +9607,10 @@
       <c r="B75" s="4"/>
       <c r="C75" s="3"/>
       <c r="D75" s="3" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H75" s="1">
         <v>74</v>
@@ -9606,16 +9622,16 @@
     </row>
     <row r="76" customHeight="1" spans="2:9">
       <c r="B76" s="3" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H76" s="1">
         <v>75</v>
@@ -9629,10 +9645,10 @@
       <c r="B77" s="4"/>
       <c r="C77" s="4"/>
       <c r="D77" s="3" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H77" s="1">
         <v>76</v>
@@ -9646,10 +9662,10 @@
       <c r="B78" s="4"/>
       <c r="C78" s="4"/>
       <c r="D78" s="3" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H78" s="1">
         <v>77</v>
@@ -9663,10 +9679,10 @@
       <c r="B79" s="4"/>
       <c r="C79" s="4"/>
       <c r="D79" s="3" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H79" s="1">
         <v>78</v>
@@ -9680,10 +9696,10 @@
       <c r="B80" s="4"/>
       <c r="C80" s="4"/>
       <c r="D80" s="3" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H80" s="1">
         <v>79</v>
@@ -9697,10 +9713,10 @@
       <c r="B81" s="4"/>
       <c r="C81" s="4"/>
       <c r="D81" s="5" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H81" s="1">
         <v>80</v>
@@ -9714,10 +9730,10 @@
       <c r="B82" s="4"/>
       <c r="C82" s="4"/>
       <c r="D82" s="5" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H82" s="1">
         <v>81</v>
@@ -9731,10 +9747,10 @@
       <c r="B83" s="4"/>
       <c r="C83" s="4"/>
       <c r="D83" s="5" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H83" s="1">
         <v>82</v>
@@ -9748,10 +9764,10 @@
       <c r="B84" s="4"/>
       <c r="C84" s="4"/>
       <c r="D84" s="3" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H84" s="1">
         <v>83</v>
@@ -9763,16 +9779,16 @@
     </row>
     <row r="85" customHeight="1" spans="2:9">
       <c r="B85" s="3" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H85" s="1">
         <v>84</v>
@@ -9785,13 +9801,13 @@
     <row r="86" customHeight="1" spans="2:9">
       <c r="B86" s="4"/>
       <c r="C86" s="3" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H86" s="1">
         <v>85</v>
@@ -9805,10 +9821,10 @@
       <c r="B87" s="4"/>
       <c r="C87" s="4"/>
       <c r="D87" s="3" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H87" s="1">
         <v>86</v>
@@ -9822,10 +9838,10 @@
       <c r="B88" s="4"/>
       <c r="C88" s="4"/>
       <c r="D88" s="3" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="H88" s="1">
         <v>87</v>
@@ -9839,10 +9855,10 @@
       <c r="B89" s="4"/>
       <c r="C89" s="4"/>
       <c r="D89" s="3" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="H89" s="1">
         <v>88</v>
@@ -9854,13 +9870,13 @@
     </row>
     <row r="90" customHeight="1" spans="3:9">
       <c r="C90" s="3" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="H90" s="1">
         <v>89</v>
@@ -9874,10 +9890,10 @@
       <c r="B91" s="4"/>
       <c r="C91" s="4"/>
       <c r="D91" s="3" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H91" s="1">
         <v>90</v>
@@ -9891,10 +9907,10 @@
       <c r="B92" s="4"/>
       <c r="C92" s="4"/>
       <c r="D92" s="3" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H92" s="1">
         <v>91</v>
@@ -9908,10 +9924,10 @@
       <c r="B93" s="4"/>
       <c r="C93" s="4"/>
       <c r="D93" s="3" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H93" s="1">
         <v>92</v>
@@ -9925,10 +9941,10 @@
       <c r="B94" s="4"/>
       <c r="C94" s="4"/>
       <c r="D94" s="3" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H94" s="1">
         <v>93</v>

--- a/GourmetProject/GameConfig/Datas/item.xlsx
+++ b/GourmetProject/GameConfig/Datas/item.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="860" uniqueCount="618">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="940" uniqueCount="619">
   <si>
     <t>##var</t>
   </si>
@@ -164,6 +164,9 @@
   </si>
   <si>
     <t>Uncommon</t>
+  </si>
+  <si>
+    <t>None</t>
   </si>
   <si>
     <t>item_choose_one_passive</t>
@@ -3168,7 +3171,9 @@
       <c r="E4" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F4" s="1"/>
+      <c r="F4" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="G4" s="1">
         <v>2</v>
       </c>
@@ -3203,18 +3208,20 @@
     <row r="5" customFormat="1" spans="1:16">
       <c r="A5" s="1"/>
       <c r="B5" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F5" s="1"/>
       <c r="G5" s="1">
         <v>3</v>
       </c>
@@ -3249,18 +3256,20 @@
     <row r="6" customFormat="1" spans="1:16">
       <c r="A6" s="1"/>
       <c r="B6" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F6" s="1"/>
+      <c r="F6" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="G6" s="1">
         <v>2</v>
       </c>
@@ -3295,18 +3304,20 @@
     <row r="7" customFormat="1" spans="1:16">
       <c r="A7" s="1"/>
       <c r="B7" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F7" s="1"/>
+        <v>49</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="G7" s="1">
         <v>3</v>
       </c>
@@ -3340,18 +3351,20 @@
     </row>
     <row r="8" spans="2:27">
       <c r="B8" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F8" s="1"/>
+        <v>49</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="G8" s="1">
         <v>3</v>
       </c>
@@ -3383,7 +3396,7 @@
         <v>0</v>
       </c>
       <c r="S8" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="T8" s="1">
         <v>10</v>
@@ -3412,18 +3425,20 @@
     </row>
     <row r="9" spans="2:27">
       <c r="B9" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F9" s="1"/>
+        <v>49</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="G9" s="1">
         <v>3</v>
       </c>
@@ -3455,7 +3470,7 @@
         <v>0</v>
       </c>
       <c r="S9" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="T9" s="1">
         <v>20</v>
@@ -3484,18 +3499,20 @@
     </row>
     <row r="10" spans="2:27">
       <c r="B10" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F10" s="1"/>
+        <v>49</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="G10" s="1">
         <v>1</v>
       </c>
@@ -3527,7 +3544,7 @@
         <v>0</v>
       </c>
       <c r="S10" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="T10" s="1">
         <v>30</v>
@@ -3556,18 +3573,20 @@
     </row>
     <row r="11" spans="2:27">
       <c r="B11" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="F11" s="1"/>
+        <v>71</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="G11" s="1">
         <v>50</v>
       </c>
@@ -3599,7 +3618,7 @@
         <v>0</v>
       </c>
       <c r="S11" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="T11" s="1">
         <v>40</v>
@@ -3628,18 +3647,20 @@
     </row>
     <row r="12" spans="2:27">
       <c r="B12" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="F12" s="1"/>
+        <v>71</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="G12" s="1">
         <v>0</v>
       </c>
@@ -3671,7 +3692,7 @@
         <v>0</v>
       </c>
       <c r="S12" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="T12" s="1">
         <v>50</v>
@@ -3700,23 +3721,25 @@
     </row>
     <row r="13" spans="2:26">
       <c r="B13" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F13" s="1"/>
+        <v>49</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="G13" s="1">
         <v>0</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I13" s="1">
         <f t="shared" si="0"/>
@@ -3745,28 +3768,30 @@
         <v>0</v>
       </c>
       <c r="Z13" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="14" ht="34" spans="2:26">
       <c r="B14" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F14" s="1"/>
+        <v>49</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="G14" s="1">
         <v>20</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I14" s="1">
         <f t="shared" si="0"/>
@@ -3795,13 +3820,13 @@
         <v>0</v>
       </c>
       <c r="T14" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="V14">
         <v>300</v>
       </c>
       <c r="X14" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Z14">
         <f>COUNTIF($E$4:$E$92,T14)</f>
@@ -3810,18 +3835,20 @@
     </row>
     <row r="15" ht="34" spans="2:26">
       <c r="B15" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F15" s="1"/>
+        <v>49</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="G15" s="1">
         <v>100</v>
       </c>
@@ -3853,13 +3880,13 @@
         <v>0</v>
       </c>
       <c r="T15" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="V15">
         <v>100</v>
       </c>
       <c r="X15" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Z15">
         <f>COUNTIF($E$4:$E$92,T15)</f>
@@ -3868,18 +3895,20 @@
     </row>
     <row r="16" ht="34" spans="2:26">
       <c r="B16" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F16" s="1"/>
+      <c r="F16" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="G16" s="1">
         <v>0.2</v>
       </c>
@@ -3911,13 +3940,13 @@
         <v>0</v>
       </c>
       <c r="T16" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="V16">
         <v>30</v>
       </c>
       <c r="X16" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Z16">
         <f>COUNTIF($E$4:$E$92,T16)</f>
@@ -3926,18 +3955,20 @@
     </row>
     <row r="17" spans="2:26">
       <c r="B17" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F17" s="1"/>
+      <c r="F17" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="G17" s="1">
         <v>0.2</v>
       </c>
@@ -3969,13 +4000,13 @@
         <v>0</v>
       </c>
       <c r="T17" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="V17">
         <v>10</v>
       </c>
       <c r="X17" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Z17">
         <f>COUNTIF($E$4:$E$92,T17)</f>
@@ -3985,18 +4016,20 @@
     <row r="18" customFormat="1" spans="1:16">
       <c r="A18" s="1"/>
       <c r="B18" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F18" s="1"/>
+        <v>49</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="G18" s="1">
         <v>0.2</v>
       </c>
@@ -4031,18 +4064,20 @@
     <row r="19" customFormat="1" spans="1:16">
       <c r="A19" s="1"/>
       <c r="B19" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F19" s="1"/>
+      <c r="F19" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="G19" s="1">
         <v>0.2</v>
       </c>
@@ -4077,18 +4112,20 @@
     <row r="20" customFormat="1" spans="1:16">
       <c r="A20" s="1"/>
       <c r="B20" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F20" s="1"/>
+      <c r="F20" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="G20" s="1">
         <v>0.2</v>
       </c>
@@ -4123,18 +4160,20 @@
     <row r="21" customFormat="1" spans="1:16">
       <c r="A21" s="1"/>
       <c r="B21" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F21" s="1"/>
+        <v>49</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="G21" s="1">
         <v>0.2</v>
       </c>
@@ -4169,18 +4208,20 @@
     <row r="22" customFormat="1" spans="1:16">
       <c r="A22" s="1"/>
       <c r="B22" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="F22" s="1"/>
+        <v>71</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="G22" s="1">
         <v>30</v>
       </c>
@@ -4215,18 +4256,20 @@
     <row r="23" customFormat="1" spans="1:16">
       <c r="A23" s="1"/>
       <c r="B23" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F23" s="1"/>
+        <v>49</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="G23" s="1">
         <v>0.2</v>
       </c>
@@ -4261,18 +4304,20 @@
     <row r="24" customFormat="1" ht="34" spans="1:16">
       <c r="A24" s="1"/>
       <c r="B24" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="F24" s="1"/>
+        <v>71</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="G24" s="1">
         <v>0</v>
       </c>
@@ -4307,23 +4352,25 @@
     <row r="25" customFormat="1" ht="34" spans="1:16">
       <c r="A25" s="1"/>
       <c r="B25" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F25" s="1"/>
+        <v>49</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="G25" s="1">
         <v>0</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I25" s="1">
         <f t="shared" si="0"/>
@@ -4355,18 +4402,20 @@
     <row r="26" customFormat="1" spans="1:16">
       <c r="A26" s="1"/>
       <c r="B26" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F26" s="1"/>
+        <v>49</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="G26" s="1">
         <v>-0.1</v>
       </c>
@@ -4401,18 +4450,20 @@
     <row r="27" customFormat="1" spans="1:16">
       <c r="A27" s="1"/>
       <c r="B27" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F27" s="1"/>
+      <c r="F27" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="G27" s="1">
         <v>-0.1</v>
       </c>
@@ -4447,18 +4498,20 @@
     <row r="28" customFormat="1" spans="1:16">
       <c r="A28" s="1"/>
       <c r="B28" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="F28" s="1"/>
+        <v>71</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="G28" s="1">
         <v>-0.1</v>
       </c>
@@ -4493,23 +4546,25 @@
     <row r="29" customFormat="1" ht="34" spans="1:16">
       <c r="A29" s="1"/>
       <c r="B29" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F29" s="1"/>
+      <c r="F29" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="G29" s="1">
         <v>1.1</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I29" s="1">
         <f t="shared" si="0"/>
@@ -4541,23 +4596,25 @@
     <row r="30" customFormat="1" ht="34" spans="1:16">
       <c r="A30" s="1"/>
       <c r="B30" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="F30" s="1"/>
+        <v>71</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="G30" s="1">
         <v>1.1</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I30" s="1">
         <f t="shared" si="0"/>
@@ -4589,18 +4646,20 @@
     <row r="31" customFormat="1" ht="34" spans="1:16">
       <c r="A31" s="1"/>
       <c r="B31" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F31" s="1"/>
+      <c r="F31" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="G31" s="1">
         <v>0.1</v>
       </c>
@@ -4635,18 +4694,20 @@
     <row r="32" customFormat="1" spans="1:16">
       <c r="A32" s="1"/>
       <c r="B32" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F32" s="1"/>
+      <c r="F32" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="G32" s="1">
         <v>10</v>
       </c>
@@ -4681,23 +4742,25 @@
     <row r="33" customFormat="1" ht="34" spans="1:16">
       <c r="A33" s="1"/>
       <c r="B33" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F33" s="1"/>
+      <c r="F33" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="G33" s="1">
         <v>0</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I33" s="1">
         <f t="shared" si="0"/>
@@ -4729,23 +4792,25 @@
     <row r="34" customFormat="1" ht="34" spans="1:16">
       <c r="A34" s="1"/>
       <c r="B34" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F34" s="1"/>
+      <c r="F34" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="G34" s="1">
         <v>0</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I34" s="1">
         <f t="shared" si="0"/>
@@ -4777,18 +4842,20 @@
     <row r="35" customFormat="1" ht="34" spans="1:16">
       <c r="A35" s="1"/>
       <c r="B35" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F35" s="1"/>
+      <c r="F35" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="G35" s="1">
         <v>0</v>
       </c>
@@ -4823,18 +4890,20 @@
     <row r="36" customFormat="1" spans="1:16">
       <c r="A36" s="1"/>
       <c r="B36" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F36" s="1"/>
+      <c r="F36" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="G36" s="1">
         <v>1</v>
       </c>
@@ -4869,18 +4938,20 @@
     <row r="37" customFormat="1" ht="34" spans="1:16">
       <c r="A37" s="1"/>
       <c r="B37" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="F37" s="1"/>
+        <v>71</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="G37" s="1">
         <v>0.2</v>
       </c>
@@ -4915,18 +4986,20 @@
     <row r="38" customFormat="1" ht="34" spans="1:16">
       <c r="A38" s="1"/>
       <c r="B38" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="F38" s="1"/>
+        <v>71</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="G38" s="1">
         <v>5</v>
       </c>
@@ -4961,18 +5034,20 @@
     <row r="39" customFormat="1" ht="34" spans="1:16">
       <c r="A39" s="1"/>
       <c r="B39" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F39" s="1"/>
+      <c r="F39" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="G39" s="1">
         <v>5</v>
       </c>
@@ -5007,18 +5082,20 @@
     <row r="40" customFormat="1" ht="34" spans="1:16">
       <c r="A40" s="1"/>
       <c r="B40" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F40" s="1"/>
+      <c r="F40" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="G40" s="1">
         <v>10</v>
       </c>
@@ -5053,18 +5130,20 @@
     <row r="41" customFormat="1" ht="34" spans="1:16">
       <c r="A41" s="1"/>
       <c r="B41" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F41" s="1"/>
+      <c r="F41" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="G41" s="1">
         <v>1</v>
       </c>
@@ -5099,18 +5178,20 @@
     <row r="42" customFormat="1" spans="1:16">
       <c r="A42" s="1"/>
       <c r="B42" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="F42" s="1"/>
+        <v>71</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="G42" s="1">
         <v>10</v>
       </c>
@@ -5145,23 +5226,25 @@
     <row r="43" customFormat="1" ht="34" spans="1:16">
       <c r="A43" s="1"/>
       <c r="B43" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F43" s="1"/>
+      <c r="F43" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="G43" s="1">
         <v>300</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I43" s="1">
         <f t="shared" si="0"/>
@@ -5193,18 +5276,20 @@
     <row r="44" customFormat="1" spans="1:16">
       <c r="A44" s="1"/>
       <c r="B44" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F44" s="1"/>
+      <c r="F44" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="G44" s="1">
         <v>0</v>
       </c>
@@ -5239,18 +5324,20 @@
     <row r="45" customFormat="1" spans="1:16">
       <c r="A45" s="1"/>
       <c r="B45" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F45" s="1"/>
+      <c r="F45" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="G45" s="1">
         <v>1</v>
       </c>
@@ -5285,18 +5372,20 @@
     <row r="46" customFormat="1" spans="1:16">
       <c r="A46" s="1"/>
       <c r="B46" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="F46" s="1"/>
+        <v>196</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="G46" s="1">
         <v>1</v>
       </c>
@@ -5331,18 +5420,20 @@
     <row r="47" customFormat="1" ht="34" spans="1:16">
       <c r="A47" s="1"/>
       <c r="B47" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F47" s="1"/>
+      <c r="F47" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="G47" s="1">
         <v>1</v>
       </c>
@@ -5377,18 +5468,20 @@
     <row r="48" customFormat="1" ht="34" spans="1:16">
       <c r="A48" s="1"/>
       <c r="B48" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F48" s="1"/>
+      <c r="F48" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="G48" s="1">
         <v>1</v>
       </c>
@@ -5423,23 +5516,25 @@
     <row r="49" customFormat="1" ht="34" spans="1:16">
       <c r="A49" s="1"/>
       <c r="B49" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F49" s="1"/>
+      <c r="F49" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="G49" s="1">
         <v>2</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I49" s="1">
         <f t="shared" si="0"/>
@@ -5471,23 +5566,25 @@
     <row r="50" customFormat="1" ht="34" spans="1:16">
       <c r="A50" s="1"/>
       <c r="B50" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F50" s="1"/>
+        <v>49</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="G50" s="1">
         <v>2</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I50" s="1">
         <f t="shared" si="0"/>
@@ -5519,23 +5616,25 @@
     <row r="51" customFormat="1" ht="34" spans="1:16">
       <c r="A51" s="1"/>
       <c r="B51" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F51" s="1"/>
+        <v>49</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="G51" s="1">
         <v>2</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I51" s="1">
         <f t="shared" si="0"/>
@@ -5567,18 +5666,20 @@
     <row r="52" customFormat="1" spans="1:16">
       <c r="A52" s="1"/>
       <c r="B52" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F52" s="1"/>
+      <c r="F52" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="G52" s="1">
         <v>2</v>
       </c>
@@ -5613,18 +5714,20 @@
     <row r="53" customFormat="1" ht="34" spans="1:16">
       <c r="A53" s="1"/>
       <c r="B53" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F53" s="1"/>
+      <c r="F53" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="G53" s="1">
         <v>5</v>
       </c>
@@ -5659,18 +5762,20 @@
     <row r="54" customFormat="1" ht="34" spans="1:16">
       <c r="A54" s="1"/>
       <c r="B54" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F54" s="1"/>
+      <c r="F54" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="G54" s="1">
         <v>600</v>
       </c>
@@ -5705,18 +5810,20 @@
     <row r="55" customFormat="1" spans="1:16">
       <c r="A55" s="1"/>
       <c r="B55" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F55" s="1"/>
+      <c r="F55" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="G55" s="1">
         <v>2</v>
       </c>
@@ -5751,18 +5858,20 @@
     <row r="56" customFormat="1" ht="34" spans="1:16">
       <c r="A56" s="1"/>
       <c r="B56" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F56" s="1"/>
+      <c r="F56" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="G56" s="1">
         <v>200</v>
       </c>
@@ -5797,18 +5906,20 @@
     <row r="57" customFormat="1" ht="34" spans="1:16">
       <c r="A57" s="1"/>
       <c r="B57" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D57" s="7" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F57" s="1"/>
+      <c r="F57" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="G57" s="1">
         <v>2</v>
       </c>
@@ -5843,18 +5954,20 @@
     <row r="58" customFormat="1" spans="1:16">
       <c r="A58" s="1"/>
       <c r="B58" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="F58" s="1"/>
+        <v>196</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="G58" s="1">
         <v>1</v>
       </c>
@@ -5889,18 +6002,20 @@
     <row r="59" customFormat="1" ht="34" spans="1:16">
       <c r="A59" s="1"/>
       <c r="B59" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F59" s="1"/>
+      <c r="F59" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="G59" s="1">
         <v>1</v>
       </c>
@@ -5935,18 +6050,20 @@
     <row r="60" customFormat="1" ht="34" spans="1:16">
       <c r="A60" s="1"/>
       <c r="B60" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F60" s="1"/>
+      <c r="F60" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="G60" s="1">
         <v>2</v>
       </c>
@@ -5981,18 +6098,20 @@
     <row r="61" customFormat="1" ht="34" spans="1:16">
       <c r="A61" s="1"/>
       <c r="B61" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D61" s="7" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F61" s="1"/>
+      <c r="F61" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="G61" s="1">
         <v>1</v>
       </c>
@@ -6027,18 +6146,20 @@
     <row r="62" customFormat="1" ht="34" spans="1:16">
       <c r="A62" s="1"/>
       <c r="B62" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="F62" s="1"/>
+        <v>71</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="G62" s="1">
         <v>4</v>
       </c>
@@ -6073,18 +6194,20 @@
     <row r="63" customFormat="1" spans="1:16">
       <c r="A63" s="1"/>
       <c r="B63" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="F63" s="1"/>
+        <v>71</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="G63" s="1">
         <v>0.2</v>
       </c>
@@ -6119,18 +6242,20 @@
     <row r="64" customFormat="1" spans="1:16">
       <c r="A64" s="1"/>
       <c r="B64" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F64" s="1"/>
+        <v>49</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="G64" s="1">
         <v>0.2</v>
       </c>
@@ -6165,18 +6290,20 @@
     <row r="65" customFormat="1" ht="34" spans="1:16">
       <c r="A65" s="1"/>
       <c r="B65" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D65" s="7" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F65" s="1"/>
+        <v>49</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="G65" s="1">
         <v>10</v>
       </c>
@@ -6211,18 +6338,20 @@
     <row r="66" customFormat="1" spans="1:16">
       <c r="A66" s="1"/>
       <c r="B66" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="F66" s="1"/>
+        <v>71</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="G66" s="1">
         <v>0</v>
       </c>
@@ -6257,18 +6386,20 @@
     <row r="67" customFormat="1" ht="34" spans="1:16">
       <c r="A67" s="1"/>
       <c r="B67" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F67" s="1"/>
+      <c r="F67" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="G67" s="1">
         <v>1</v>
       </c>
@@ -6303,18 +6434,20 @@
     <row r="68" customFormat="1" ht="34" spans="1:16">
       <c r="A68" s="1"/>
       <c r="B68" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="F68" s="1"/>
+        <v>71</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="G68" s="1">
         <v>1</v>
       </c>
@@ -6349,23 +6482,25 @@
     <row r="69" customFormat="1" ht="34" spans="1:16">
       <c r="A69" s="1"/>
       <c r="B69" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D69" s="7" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F69" s="1"/>
+      <c r="F69" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="G69" s="1">
         <v>0</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="I69" s="1">
         <f t="shared" si="2"/>
@@ -6397,23 +6532,25 @@
     <row r="70" customFormat="1" ht="34" spans="1:16">
       <c r="A70" s="1"/>
       <c r="B70" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D70" s="7" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E70" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F70" s="1"/>
+      <c r="F70" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="G70" s="1">
         <v>0</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="I70" s="1">
         <f t="shared" si="2"/>
@@ -6445,18 +6582,20 @@
     <row r="71" customFormat="1" spans="1:16">
       <c r="A71" s="1"/>
       <c r="B71" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F71" s="1"/>
+      <c r="F71" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="G71" s="1">
         <v>1</v>
       </c>
@@ -6491,18 +6630,20 @@
     <row r="72" customFormat="1" spans="1:16">
       <c r="A72" s="1"/>
       <c r="B72" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F72" s="1"/>
+        <v>49</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="G72" s="1">
         <v>2</v>
       </c>
@@ -6537,18 +6678,20 @@
     <row r="73" customFormat="1" ht="34" spans="1:16">
       <c r="A73" s="1"/>
       <c r="B73" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D73" s="7" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F73" s="1"/>
+      <c r="F73" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="G73" s="1">
         <v>100</v>
       </c>
@@ -6583,19 +6726,19 @@
     <row r="74" customFormat="1" spans="1:16">
       <c r="A74" s="1"/>
       <c r="B74" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="G74" s="1">
         <v>-0.2</v>
@@ -6631,19 +6774,19 @@
     <row r="75" customFormat="1" spans="1:16">
       <c r="A75" s="1"/>
       <c r="B75" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F75" s="1" t="s">
         <v>286</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="D75" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="E75" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F75" s="1" t="s">
-        <v>285</v>
       </c>
       <c r="G75" s="1">
         <v>0.2</v>
@@ -6679,19 +6822,19 @@
     <row r="76" customFormat="1" spans="1:16">
       <c r="A76" s="1"/>
       <c r="B76" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="G76" s="1">
         <v>0</v>
@@ -6727,19 +6870,19 @@
     <row r="77" customFormat="1" spans="1:16">
       <c r="A77" s="1"/>
       <c r="B77" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="G77" s="1">
         <v>1</v>
@@ -6775,19 +6918,19 @@
     <row r="78" customFormat="1" ht="34" spans="1:16">
       <c r="A78" s="1"/>
       <c r="B78" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D78" s="7" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="G78" s="1">
         <v>-1</v>
@@ -6823,19 +6966,19 @@
     <row r="79" customFormat="1" spans="1:16">
       <c r="A79" s="1"/>
       <c r="B79" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="G79" s="1">
         <v>0.2</v>
@@ -6871,19 +7014,19 @@
     <row r="80" customFormat="1" spans="1:16">
       <c r="A80" s="1"/>
       <c r="B80" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="G80" s="1">
         <v>0.15</v>
@@ -6919,19 +7062,19 @@
     <row r="81" customFormat="1" spans="1:16">
       <c r="A81" s="1"/>
       <c r="B81" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="G81" s="1">
         <v>0.15</v>
@@ -6967,19 +7110,19 @@
     <row r="82" customFormat="1" spans="1:16">
       <c r="A82" s="1"/>
       <c r="B82" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="G82" s="1">
         <v>0</v>
@@ -7015,18 +7158,20 @@
     <row r="83" customFormat="1" spans="1:16">
       <c r="A83" s="1"/>
       <c r="B83" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="F83" s="1"/>
+        <v>196</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="G83" s="1">
         <v>2</v>
       </c>
@@ -7061,18 +7206,20 @@
     <row r="84" customFormat="1" ht="34" spans="1:17">
       <c r="A84" s="1"/>
       <c r="B84" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D84" s="7" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="F84" s="1"/>
+        <v>196</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="G84" s="1">
         <v>1.2</v>
       </c>
@@ -7104,24 +7251,26 @@
         <v>0</v>
       </c>
       <c r="Q84" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="85" customFormat="1" ht="34" spans="1:17">
       <c r="A85" s="1"/>
       <c r="B85" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D85" s="7" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="F85" s="1"/>
+        <v>196</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="G85" s="1">
         <v>1.2</v>
       </c>
@@ -7153,24 +7302,26 @@
         <v>0</v>
       </c>
       <c r="Q85" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="86" customFormat="1" ht="34" spans="1:17">
       <c r="A86" s="1"/>
       <c r="B86" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D86" s="7" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E86" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F86" s="1"/>
+      <c r="F86" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="G86" s="1">
         <v>0.2</v>
       </c>
@@ -7202,29 +7353,31 @@
         <v>0</v>
       </c>
       <c r="Q86" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="87" customFormat="1" ht="34" spans="1:17">
       <c r="A87" s="1"/>
       <c r="B87" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D87" s="7" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E87" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F87" s="1"/>
+      <c r="F87" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="G87" s="1">
         <v>10</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="I87" s="1">
         <f t="shared" si="2"/>
@@ -7253,24 +7406,26 @@
         <v>0</v>
       </c>
       <c r="Q87" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="88" customFormat="1" ht="34" spans="1:17">
       <c r="A88" s="1"/>
       <c r="B88" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D88" s="7" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="F88" s="1"/>
+        <v>196</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="G88" s="1">
         <v>0.2</v>
       </c>
@@ -7302,24 +7457,26 @@
         <v>0</v>
       </c>
       <c r="Q88" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="89" customFormat="1" ht="34" spans="1:17">
       <c r="A89" s="1"/>
       <c r="B89" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D89" s="7" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E89" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F89" s="1"/>
+      <c r="F89" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="G89" s="1">
         <v>10</v>
       </c>
@@ -7351,24 +7508,26 @@
         <v>0</v>
       </c>
       <c r="Q89" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="90" customFormat="1" ht="34" spans="1:17">
       <c r="A90" s="1"/>
       <c r="B90" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D90" s="7" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="F90" s="1"/>
+        <v>71</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="G90" s="1">
         <v>1</v>
       </c>
@@ -7400,29 +7559,31 @@
         <v>0</v>
       </c>
       <c r="Q90" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="91" customFormat="1" ht="34" spans="1:17">
       <c r="A91" s="1"/>
       <c r="B91" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D91" s="7" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="E91" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F91" s="1"/>
+      <c r="F91" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="G91" s="1">
         <v>10</v>
       </c>
       <c r="H91" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="I91" s="1">
         <f t="shared" si="2"/>
@@ -7451,24 +7612,26 @@
         <v>0</v>
       </c>
       <c r="Q91" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="92" customFormat="1" spans="1:17">
       <c r="A92" s="1"/>
       <c r="B92" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E92" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F92" s="1"/>
+      <c r="F92" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="G92" s="1">
         <v>10</v>
       </c>
@@ -7500,7 +7663,7 @@
         <v>0</v>
       </c>
       <c r="Q92" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
   </sheetData>
@@ -7546,7 +7709,7 @@
         <v>5</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>6</v>
@@ -7558,10 +7721,10 @@
         <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L1" t="s">
         <v>16</v>
@@ -7584,7 +7747,7 @@
         <v>22</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>23</v>
@@ -7596,10 +7759,10 @@
         <v>25</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L2" t="s">
         <v>33</v>
@@ -7634,7 +7797,7 @@
         <v>38</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>40</v>
@@ -7645,528 +7808,528 @@
     </row>
     <row r="4" customFormat="1" ht="34" spans="1:12">
       <c r="A4" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>355</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>354</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>351</v>
-      </c>
       <c r="F4" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="G4" s="1">
         <v>0</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="I4" s="1">
         <v>1</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="K4" s="1">
         <v>1</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="5" customFormat="1" ht="34" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="G5" s="1">
         <v>0</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="I5" s="1">
         <v>1</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="K5" s="1">
         <v>1</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="6" customFormat="1" ht="34" spans="1:12">
       <c r="A6" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="I6" s="1">
         <v>1</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="K6" s="1">
         <v>1</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="7" customFormat="1" ht="34" spans="1:12">
       <c r="A7" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="I7" s="1">
         <v>1</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="K7" s="1">
         <v>1</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="8" customFormat="1" ht="34" spans="1:12">
       <c r="A8" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="I8" s="1">
         <v>1</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="K8" s="1">
         <v>1</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="9" customFormat="1" ht="34" spans="1:12">
       <c r="A9" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="I9" s="1">
         <v>1</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="K9" s="1">
         <v>1</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10" customFormat="1" ht="34" spans="1:12">
       <c r="A10" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="I10" s="1">
         <v>1</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K10" s="1">
         <v>1</v>
       </c>
       <c r="L10" s="8" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="11" customFormat="1" ht="34" spans="1:12">
       <c r="A11" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="G11" s="1">
         <v>0</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="I11" s="1">
         <v>1</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K11" s="1">
         <v>1</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="12" customFormat="1" ht="34" spans="1:12">
       <c r="A12" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="I12" s="1">
         <v>1</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K12" s="1">
         <v>1</v>
       </c>
       <c r="L12" s="8" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="13" customFormat="1" ht="34" spans="1:12">
       <c r="A13" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="G13" s="1">
         <v>0</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="I13" s="1">
         <v>1</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K13" s="1">
         <v>1</v>
       </c>
       <c r="L13" s="8" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="14" customFormat="1" ht="34" spans="1:12">
       <c r="A14" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="G14" s="1">
         <v>0</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="I14" s="1">
         <v>1</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K14" s="1">
         <v>1</v>
       </c>
       <c r="L14" s="8" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="15" customFormat="1" ht="34" spans="1:12">
       <c r="A15" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="G15" s="1">
         <v>0</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="I15" s="1">
         <v>1</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K15" s="1">
         <v>1</v>
       </c>
       <c r="L15" s="8" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="16" customFormat="1" ht="34" spans="1:12">
       <c r="A16" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="G16" s="1">
         <v>0</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="I16" s="1">
         <v>1</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K16" s="1">
         <v>1</v>
       </c>
       <c r="L16" s="8" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="17" customFormat="1" ht="34" spans="1:11">
       <c r="A17" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="G17" s="1">
         <v>0</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="I17" s="1">
         <v>1</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K17" s="1">
         <v>0</v>
@@ -8174,34 +8337,34 @@
     </row>
     <row r="18" customFormat="1" spans="1:11">
       <c r="A18" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="G18" s="1">
         <v>0</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="I18" s="1">
         <v>1</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K18" s="1">
         <v>0</v>
@@ -8209,34 +8372,34 @@
     </row>
     <row r="19" customFormat="1" spans="1:11">
       <c r="A19" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="G19" s="1">
         <v>0</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="I19" s="1">
         <v>1</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K19" s="1">
         <v>0</v>
@@ -8244,34 +8407,34 @@
     </row>
     <row r="20" customFormat="1" spans="1:11">
       <c r="A20" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="G20" s="1">
         <v>0</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="I20" s="1">
         <v>1</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K20" s="1">
         <v>0</v>
@@ -8298,36 +8461,36 @@
   <sheetData>
     <row r="1" customHeight="1" spans="2:9">
       <c r="B1" s="3" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="2:9">
       <c r="B2" s="3" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H2" s="1">
         <v>1</v>
@@ -8341,10 +8504,10 @@
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
       <c r="D3" s="3" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H3" s="1">
         <v>2</v>
@@ -8358,10 +8521,10 @@
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
       <c r="D4" s="3" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H4" s="1">
         <v>3</v>
@@ -8375,10 +8538,10 @@
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
       <c r="D5" s="3" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H5" s="1">
         <v>4</v>
@@ -8392,10 +8555,10 @@
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
       <c r="D6" s="3" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H6" s="1">
         <v>5</v>
@@ -8409,10 +8572,10 @@
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
       <c r="D7" s="3" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H7" s="1">
         <v>6</v>
@@ -8426,10 +8589,10 @@
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
       <c r="D8" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H8" s="1">
         <v>7</v>
@@ -8443,10 +8606,10 @@
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
       <c r="D9" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H9" s="1">
         <v>8</v>
@@ -8460,10 +8623,10 @@
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
       <c r="D10" s="3" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H10" s="1">
         <v>9</v>
@@ -8476,13 +8639,13 @@
     <row r="11" customHeight="1" spans="2:9">
       <c r="B11" s="4"/>
       <c r="C11" s="3" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H11" s="1">
         <v>10</v>
@@ -8496,10 +8659,10 @@
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
       <c r="D12" s="3" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H12" s="1">
         <v>11</v>
@@ -8513,10 +8676,10 @@
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
       <c r="D13" s="3" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H13" s="1">
         <v>12</v>
@@ -8530,10 +8693,10 @@
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
       <c r="D14" s="3" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H14" s="1">
         <v>13</v>
@@ -8546,13 +8709,13 @@
     <row r="15" customHeight="1" spans="2:9">
       <c r="B15" s="4"/>
       <c r="C15" s="3" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H15" s="1">
         <v>14</v>
@@ -8566,10 +8729,10 @@
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
       <c r="D16" s="3" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H16" s="1">
         <v>15</v>
@@ -8583,10 +8746,10 @@
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
       <c r="D17" s="3" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H17" s="1">
         <v>16</v>
@@ -8600,10 +8763,10 @@
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
       <c r="D18" s="3" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H18" s="1">
         <v>17</v>
@@ -8617,10 +8780,10 @@
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
       <c r="D19" s="3" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H19" s="1">
         <v>18</v>
@@ -8634,10 +8797,10 @@
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
       <c r="D20" s="3" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H20" s="1">
         <v>19</v>
@@ -8651,10 +8814,10 @@
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
       <c r="D21" s="3" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H21" s="1">
         <v>20</v>
@@ -8667,13 +8830,13 @@
     <row r="22" customHeight="1" spans="2:9">
       <c r="B22" s="4"/>
       <c r="C22" s="3" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H22" s="1">
         <v>21</v>
@@ -8686,13 +8849,13 @@
     <row r="23" customHeight="1" spans="2:9">
       <c r="B23" s="4"/>
       <c r="C23" s="3" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H23" s="1">
         <v>22</v>
@@ -8706,10 +8869,10 @@
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
       <c r="D24" s="3" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H24" s="1">
         <v>23</v>
@@ -8723,10 +8886,10 @@
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
       <c r="D25" s="3" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H25" s="1">
         <v>24</v>
@@ -8740,10 +8903,10 @@
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
       <c r="D26" s="3" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H26" s="1">
         <v>25</v>
@@ -8756,13 +8919,13 @@
     <row r="27" customHeight="1" spans="2:9">
       <c r="B27" s="4"/>
       <c r="C27" s="3" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H27" s="1">
         <v>26</v>
@@ -8776,10 +8939,10 @@
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
       <c r="D28" s="3" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H28" s="1">
         <v>27</v>
@@ -8792,13 +8955,13 @@
     <row r="29" customHeight="1" spans="2:9">
       <c r="B29" s="4"/>
       <c r="C29" s="3" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H29" s="1">
         <v>28</v>
@@ -8811,13 +8974,13 @@
     <row r="30" customHeight="1" spans="2:9">
       <c r="B30" s="4"/>
       <c r="C30" s="3" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H30" s="1">
         <v>29</v>
@@ -8830,13 +8993,13 @@
     <row r="31" customHeight="1" spans="2:9">
       <c r="B31" s="4"/>
       <c r="C31" s="3" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H31" s="1">
         <v>30</v>
@@ -8849,13 +9012,13 @@
     <row r="32" customHeight="1" spans="2:9">
       <c r="B32" s="4"/>
       <c r="C32" s="3" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H32" s="1">
         <v>31</v>
@@ -8869,10 +9032,10 @@
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
       <c r="D33" s="3" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H33" s="1">
         <v>32</v>
@@ -8886,10 +9049,10 @@
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
       <c r="D34" s="3" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H34" s="1">
         <v>33</v>
@@ -8902,13 +9065,13 @@
     <row r="35" customHeight="1" spans="2:9">
       <c r="B35" s="4"/>
       <c r="C35" s="5" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H35" s="1">
         <v>34</v>
@@ -8922,10 +9085,10 @@
       <c r="B36" s="4"/>
       <c r="C36" s="5"/>
       <c r="D36" s="6" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H36" s="1">
         <v>35</v>
@@ -8938,13 +9101,13 @@
     <row r="37" customHeight="1" spans="2:9">
       <c r="B37" s="4"/>
       <c r="C37" s="3" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H37" s="1">
         <v>36</v>
@@ -8957,13 +9120,13 @@
     <row r="38" customHeight="1" spans="2:9">
       <c r="B38" s="4"/>
       <c r="C38" s="3" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H38" s="1">
         <v>37</v>
@@ -8977,10 +9140,10 @@
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
       <c r="D39" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H39" s="1">
         <v>38</v>
@@ -8994,10 +9157,10 @@
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
       <c r="D40" s="3" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H40" s="1">
         <v>39</v>
@@ -9011,10 +9174,10 @@
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
       <c r="D41" s="3" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H41" s="1">
         <v>40</v>
@@ -9028,10 +9191,10 @@
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
       <c r="D42" s="3" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H42" s="1">
         <v>41</v>
@@ -9045,10 +9208,10 @@
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
       <c r="D43" s="3" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H43" s="1">
         <v>42</v>
@@ -9061,13 +9224,13 @@
     <row r="44" customHeight="1" spans="2:9">
       <c r="B44" s="4"/>
       <c r="C44" s="3" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H44" s="1">
         <v>43</v>
@@ -9081,10 +9244,10 @@
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
       <c r="D45" s="3" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H45" s="1">
         <v>44</v>
@@ -9098,10 +9261,10 @@
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
       <c r="D46" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H46" s="1">
         <v>45</v>
@@ -9115,10 +9278,10 @@
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
       <c r="D47" s="3" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H47" s="1">
         <v>46</v>
@@ -9132,10 +9295,10 @@
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
       <c r="D48" s="3" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H48" s="1">
         <v>47</v>
@@ -9148,13 +9311,13 @@
     <row r="49" customHeight="1" spans="2:9">
       <c r="B49" s="4"/>
       <c r="C49" s="3" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H49" s="1">
         <v>48</v>
@@ -9168,10 +9331,10 @@
       <c r="B50" s="4"/>
       <c r="C50" s="4"/>
       <c r="D50" s="3" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H50" s="1">
         <v>49</v>
@@ -9185,10 +9348,10 @@
       <c r="B51" s="4"/>
       <c r="C51" s="4"/>
       <c r="D51" s="3" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H51" s="1">
         <v>50</v>
@@ -9201,13 +9364,13 @@
     <row r="52" customHeight="1" spans="2:9">
       <c r="B52" s="4"/>
       <c r="C52" s="3" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H52" s="1">
         <v>51</v>
@@ -9221,10 +9384,10 @@
       <c r="B53" s="4"/>
       <c r="C53" s="4"/>
       <c r="D53" s="3" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H53" s="1">
         <v>52</v>
@@ -9238,10 +9401,10 @@
       <c r="B54" s="4"/>
       <c r="C54" s="4"/>
       <c r="D54" s="3" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H54" s="1">
         <v>53</v>
@@ -9254,13 +9417,13 @@
     <row r="55" customHeight="1" spans="2:9">
       <c r="B55" s="4"/>
       <c r="C55" s="3" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H55" s="1">
         <v>54</v>
@@ -9274,10 +9437,10 @@
       <c r="B56" s="4"/>
       <c r="C56" s="4"/>
       <c r="D56" s="3" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H56" s="1">
         <v>55</v>
@@ -9291,10 +9454,10 @@
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
       <c r="D57" s="3" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H57" s="1">
         <v>56</v>
@@ -9308,10 +9471,10 @@
       <c r="B58" s="4"/>
       <c r="C58" s="4"/>
       <c r="D58" s="3" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H58" s="1">
         <v>57</v>
@@ -9325,10 +9488,10 @@
       <c r="B59" s="4"/>
       <c r="C59" s="4"/>
       <c r="D59" s="3" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H59" s="1">
         <v>58</v>
@@ -9342,10 +9505,10 @@
       <c r="B60" s="4"/>
       <c r="C60" s="4"/>
       <c r="D60" s="3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H60" s="1">
         <v>59</v>
@@ -9358,13 +9521,13 @@
     <row r="61" customHeight="1" spans="2:9">
       <c r="B61" s="4"/>
       <c r="C61" s="3" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H61" s="1">
         <v>60</v>
@@ -9378,10 +9541,10 @@
       <c r="B62" s="4"/>
       <c r="C62" s="4"/>
       <c r="D62" s="3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H62" s="1">
         <v>61</v>
@@ -9394,13 +9557,13 @@
     <row r="63" customHeight="1" spans="2:9">
       <c r="B63" s="4"/>
       <c r="C63" s="3" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H63" s="1">
         <v>62</v>
@@ -9414,10 +9577,10 @@
       <c r="B64" s="4"/>
       <c r="C64" s="4"/>
       <c r="D64" s="3" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H64" s="1">
         <v>63</v>
@@ -9431,10 +9594,10 @@
       <c r="B65" s="4"/>
       <c r="C65" s="4"/>
       <c r="D65" s="3" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H65" s="1">
         <v>64</v>
@@ -9448,10 +9611,10 @@
       <c r="B66" s="4"/>
       <c r="C66" s="4"/>
       <c r="D66" s="3" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H66" s="1">
         <v>65</v>
@@ -9465,10 +9628,10 @@
       <c r="B67" s="4"/>
       <c r="C67" s="4"/>
       <c r="D67" s="3" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H67" s="1">
         <v>66</v>
@@ -9481,13 +9644,13 @@
     <row r="68" customHeight="1" spans="2:9">
       <c r="B68" s="4"/>
       <c r="C68" s="3" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H68" s="1">
         <v>67</v>
@@ -9500,13 +9663,13 @@
     <row r="69" customHeight="1" spans="2:9">
       <c r="B69" s="4"/>
       <c r="C69" s="3" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H69" s="1">
         <v>68</v>
@@ -9520,10 +9683,10 @@
       <c r="B70" s="4"/>
       <c r="C70" s="4"/>
       <c r="D70" s="3" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H70" s="1">
         <v>69</v>
@@ -9537,10 +9700,10 @@
       <c r="B71" s="4"/>
       <c r="C71" s="4"/>
       <c r="D71" s="3" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H71" s="1">
         <v>70</v>
@@ -9554,10 +9717,10 @@
       <c r="B72" s="4"/>
       <c r="C72" s="4"/>
       <c r="D72" s="3" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H72" s="1">
         <v>71</v>
@@ -9571,10 +9734,10 @@
       <c r="B73" s="4"/>
       <c r="C73" s="4"/>
       <c r="D73" s="3" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H73" s="1">
         <v>72</v>
@@ -9587,13 +9750,13 @@
     <row r="74" customHeight="1" spans="2:9">
       <c r="B74" s="4"/>
       <c r="C74" s="3" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H74" s="1">
         <v>73</v>
@@ -9607,10 +9770,10 @@
       <c r="B75" s="4"/>
       <c r="C75" s="3"/>
       <c r="D75" s="3" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H75" s="1">
         <v>74</v>
@@ -9622,16 +9785,16 @@
     </row>
     <row r="76" customHeight="1" spans="2:9">
       <c r="B76" s="3" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H76" s="1">
         <v>75</v>
@@ -9645,10 +9808,10 @@
       <c r="B77" s="4"/>
       <c r="C77" s="4"/>
       <c r="D77" s="3" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H77" s="1">
         <v>76</v>
@@ -9662,10 +9825,10 @@
       <c r="B78" s="4"/>
       <c r="C78" s="4"/>
       <c r="D78" s="3" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H78" s="1">
         <v>77</v>
@@ -9679,10 +9842,10 @@
       <c r="B79" s="4"/>
       <c r="C79" s="4"/>
       <c r="D79" s="3" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H79" s="1">
         <v>78</v>
@@ -9696,10 +9859,10 @@
       <c r="B80" s="4"/>
       <c r="C80" s="4"/>
       <c r="D80" s="3" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H80" s="1">
         <v>79</v>
@@ -9713,10 +9876,10 @@
       <c r="B81" s="4"/>
       <c r="C81" s="4"/>
       <c r="D81" s="5" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H81" s="1">
         <v>80</v>
@@ -9730,10 +9893,10 @@
       <c r="B82" s="4"/>
       <c r="C82" s="4"/>
       <c r="D82" s="5" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H82" s="1">
         <v>81</v>
@@ -9747,10 +9910,10 @@
       <c r="B83" s="4"/>
       <c r="C83" s="4"/>
       <c r="D83" s="5" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H83" s="1">
         <v>82</v>
@@ -9764,10 +9927,10 @@
       <c r="B84" s="4"/>
       <c r="C84" s="4"/>
       <c r="D84" s="3" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H84" s="1">
         <v>83</v>
@@ -9779,16 +9942,16 @@
     </row>
     <row r="85" customHeight="1" spans="2:9">
       <c r="B85" s="3" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H85" s="1">
         <v>84</v>
@@ -9801,13 +9964,13 @@
     <row r="86" customHeight="1" spans="2:9">
       <c r="B86" s="4"/>
       <c r="C86" s="3" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H86" s="1">
         <v>85</v>
@@ -9821,10 +9984,10 @@
       <c r="B87" s="4"/>
       <c r="C87" s="4"/>
       <c r="D87" s="3" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H87" s="1">
         <v>86</v>
@@ -9838,10 +10001,10 @@
       <c r="B88" s="4"/>
       <c r="C88" s="4"/>
       <c r="D88" s="3" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="H88" s="1">
         <v>87</v>
@@ -9855,10 +10018,10 @@
       <c r="B89" s="4"/>
       <c r="C89" s="4"/>
       <c r="D89" s="3" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="H89" s="1">
         <v>88</v>
@@ -9870,13 +10033,13 @@
     </row>
     <row r="90" customHeight="1" spans="3:9">
       <c r="C90" s="3" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="H90" s="1">
         <v>89</v>
@@ -9890,10 +10053,10 @@
       <c r="B91" s="4"/>
       <c r="C91" s="4"/>
       <c r="D91" s="3" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H91" s="1">
         <v>90</v>
@@ -9907,10 +10070,10 @@
       <c r="B92" s="4"/>
       <c r="C92" s="4"/>
       <c r="D92" s="3" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H92" s="1">
         <v>91</v>
@@ -9924,10 +10087,10 @@
       <c r="B93" s="4"/>
       <c r="C93" s="4"/>
       <c r="D93" s="3" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="H93" s="1">
         <v>92</v>
@@ -9941,10 +10104,10 @@
       <c r="B94" s="4"/>
       <c r="C94" s="4"/>
       <c r="D94" s="3" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H94" s="1">
         <v>93</v>

--- a/GourmetProject/GameConfig/Datas/item.xlsx
+++ b/GourmetProject/GameConfig/Datas/item.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15200"/>
+    <workbookView windowHeight="15300"/>
   </bookViews>
   <sheets>
     <sheet name="被动道具" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1005" uniqueCount="627">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="975" uniqueCount="609">
   <si>
     <t>##var</t>
   </si>
@@ -168,76 +168,22 @@
     <t>20,80</t>
   </si>
   <si>
-    <t>item_choose_one_passive</t>
-  </si>
-  <si>
-    <t>被动三选一</t>
-  </si>
-  <si>
-    <t>从3个被动道具中选择1个获得</t>
+    <t>item_grant_two_active</t>
+  </si>
+  <si>
+    <t>随机主动包</t>
+  </si>
+  <si>
+    <t>随机获得2个主动道具</t>
   </si>
   <si>
     <t>Common</t>
   </si>
   <si>
-    <t>passive_choice_3</t>
+    <t>active_grant_2</t>
   </si>
   <si>
     <t>10,80</t>
-  </si>
-  <si>
-    <t>item_grant_two_active</t>
-  </si>
-  <si>
-    <t>随机主动包</t>
-  </si>
-  <si>
-    <t>随机获得2个主动道具</t>
-  </si>
-  <si>
-    <t>active_grant_2</t>
-  </si>
-  <si>
-    <t>item_choose_one_active</t>
-  </si>
-  <si>
-    <t>主动三选一</t>
-  </si>
-  <si>
-    <t>从3个主动道具中选择1个获得</t>
-  </si>
-  <si>
-    <t>active_choice_3</t>
-  </si>
-  <si>
-    <t>item_choose_one_food</t>
-  </si>
-  <si>
-    <t>食物三选一</t>
-  </si>
-  <si>
-    <t>从3个食物中选择1个获得</t>
-  </si>
-  <si>
-    <t>dish_choice_3</t>
-  </si>
-  <si>
-    <t>0周</t>
-  </si>
-  <si>
-    <t>item_choose_one_fragment</t>
-  </si>
-  <si>
-    <t>碎片三选一</t>
-  </si>
-  <si>
-    <t>从3个餐桌格子中选择1个获得</t>
-  </si>
-  <si>
-    <t>fragment_choice_3</t>
-  </si>
-  <si>
-    <t>1周</t>
   </si>
   <si>
     <t>item_grant_recipe</t>
@@ -322,7 +268,7 @@
     <t>Boss赏金</t>
   </si>
   <si>
-    <t>下次盛宴
+    <t>完成下次盛宴
 额外+100金币</t>
   </si>
   <si>
@@ -3172,7 +3118,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AA92"/>
+  <dimension ref="A1:AA88"/>
   <sheetFormatPr defaultColWidth="9.00735294117647" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="13.0808823529412" style="1" customWidth="1"/>
@@ -3457,7 +3403,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="6" ht="16.5" customHeight="1" spans="2:18">
+    <row r="6" ht="16.5" customHeight="1" spans="2:27">
       <c r="B6" s="7" t="s">
         <v>56</v>
       </c>
@@ -3473,8 +3419,8 @@
       <c r="F6" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="H6" s="10" t="s">
-        <v>59</v>
+      <c r="G6" s="1">
+        <v>1</v>
       </c>
       <c r="I6" s="1">
         <v>300</v>
@@ -3503,8 +3449,35 @@
       <c r="R6">
         <v>45</v>
       </c>
-    </row>
-    <row r="7" ht="16.5" customHeight="1" spans="2:18">
+      <c r="S6" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="T6" s="1">
+        <v>30</v>
+      </c>
+      <c r="U6" s="1">
+        <v>31</v>
+      </c>
+      <c r="V6" s="1">
+        <v>32</v>
+      </c>
+      <c r="W6" s="1">
+        <v>33</v>
+      </c>
+      <c r="X6" s="1">
+        <v>34</v>
+      </c>
+      <c r="Y6" s="1">
+        <v>35</v>
+      </c>
+      <c r="Z6" s="1">
+        <v>36</v>
+      </c>
+      <c r="AA6" s="1">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" ht="16.5" customHeight="1" spans="2:27">
       <c r="B7" s="7" t="s">
         <v>60</v>
       </c>
@@ -3515,19 +3488,22 @@
         <v>62</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="F7" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="H7" s="10" t="s">
-        <v>63</v>
+      <c r="G7" s="1">
+        <v>50</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>64</v>
       </c>
       <c r="I7" s="1">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="K7" s="1">
         <v>0</v>
@@ -3550,31 +3526,58 @@
       <c r="R7">
         <v>45</v>
       </c>
+      <c r="S7" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="T7" s="1">
+        <v>40</v>
+      </c>
+      <c r="U7" s="1">
+        <v>41</v>
+      </c>
+      <c r="V7" s="1">
+        <v>42</v>
+      </c>
+      <c r="W7" s="1">
+        <v>43</v>
+      </c>
+      <c r="X7" s="1">
+        <v>44</v>
+      </c>
+      <c r="Y7" s="1">
+        <v>45</v>
+      </c>
+      <c r="Z7" s="1">
+        <v>46</v>
+      </c>
+      <c r="AA7" s="1">
+        <v>47</v>
+      </c>
     </row>
     <row r="8" ht="16.5" customHeight="1" spans="2:27">
       <c r="B8" s="7" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="H8" s="10" t="s">
-        <v>67</v>
+      <c r="G8" s="1">
+        <v>0</v>
       </c>
       <c r="I8" s="1">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="K8" s="1">
         <v>0</v>
@@ -3598,42 +3601,42 @@
         <v>45</v>
       </c>
       <c r="S8" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="T8" s="1">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="U8" s="1">
-        <v>11</v>
+        <v>51</v>
       </c>
       <c r="V8" s="1">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="W8" s="1">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="X8" s="1">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="Y8" s="1">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="Z8" s="1">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="AA8" s="1">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" ht="16.5" customHeight="1" spans="2:27">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="9" ht="16.5" customHeight="1" spans="2:26">
       <c r="B9" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>53</v>
@@ -3641,8 +3644,11 @@
       <c r="F9" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="H9" s="10" t="s">
-        <v>72</v>
+      <c r="G9" s="1">
+        <v>0</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>74</v>
       </c>
       <c r="I9" s="1">
         <v>300</v>
@@ -3671,43 +3677,19 @@
       <c r="R9">
         <v>45</v>
       </c>
-      <c r="S9" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="T9" s="1">
-        <v>20</v>
-      </c>
-      <c r="U9" s="1">
-        <v>21</v>
-      </c>
-      <c r="V9" s="1">
-        <v>22</v>
-      </c>
-      <c r="W9" s="1">
-        <v>23</v>
-      </c>
-      <c r="X9" s="1">
-        <v>24</v>
-      </c>
-      <c r="Y9" s="1">
-        <v>25</v>
-      </c>
-      <c r="Z9" s="1">
-        <v>26</v>
-      </c>
-      <c r="AA9" s="1">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="10" ht="16.5" customHeight="1" spans="2:27">
+      <c r="Z9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="10" ht="33.75" customHeight="1" spans="2:26">
       <c r="B10" s="7" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>78</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>53</v>
@@ -3716,7 +3698,10 @@
         <v>47</v>
       </c>
       <c r="G10" s="1">
-        <v>1</v>
+        <v>20</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>79</v>
       </c>
       <c r="I10" s="1">
         <v>300</v>
@@ -3745,61 +3730,44 @@
       <c r="R10">
         <v>45</v>
       </c>
-      <c r="S10" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="T10" s="1">
-        <v>30</v>
-      </c>
-      <c r="U10" s="1">
-        <v>31</v>
-      </c>
-      <c r="V10" s="1">
-        <v>32</v>
-      </c>
-      <c r="W10" s="1">
-        <v>33</v>
-      </c>
-      <c r="X10" s="1">
-        <v>34</v>
-      </c>
-      <c r="Y10" s="1">
-        <v>35</v>
-      </c>
-      <c r="Z10" s="1">
-        <v>36</v>
-      </c>
-      <c r="AA10" s="1">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="11" ht="16.5" customHeight="1" spans="2:27">
+      <c r="T10" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="V10">
+        <v>300</v>
+      </c>
+      <c r="X10" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z10">
+        <f>COUNTIF($E$4:$E$88,T10)</f>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" ht="33.75" customHeight="1" spans="2:26">
       <c r="B11" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>83</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>81</v>
+        <v>53</v>
       </c>
       <c r="F11" s="7" t="s">
         <v>47</v>
       </c>
       <c r="G11" s="1">
-        <v>50</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="I11" s="1">
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>83</v>
+        <v>55</v>
       </c>
       <c r="K11" s="1">
         <v>0</v>
@@ -3822,58 +3790,44 @@
       <c r="R11">
         <v>45</v>
       </c>
-      <c r="S11" s="7" t="s">
+      <c r="T11" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="T11" s="1">
-        <v>40</v>
-      </c>
-      <c r="U11" s="1">
+      <c r="V11">
+        <v>100</v>
+      </c>
+      <c r="X11" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z11">
+        <f>COUNTIF($E$4:$E$88,T11)</f>
         <v>41</v>
       </c>
-      <c r="V11" s="1">
-        <v>42</v>
-      </c>
-      <c r="W11" s="1">
-        <v>43</v>
-      </c>
-      <c r="X11" s="1">
-        <v>44</v>
-      </c>
-      <c r="Y11" s="1">
-        <v>45</v>
-      </c>
-      <c r="Z11" s="1">
-        <v>46</v>
-      </c>
-      <c r="AA11" s="1">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="12" ht="16.5" customHeight="1" spans="2:27">
+    </row>
+    <row r="12" ht="33.75" customHeight="1" spans="2:26">
       <c r="B12" s="7" t="s">
         <v>85</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" s="8" t="s">
         <v>87</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>81</v>
+        <v>46</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>47</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="I12" s="1">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>83</v>
+        <v>49</v>
       </c>
       <c r="K12" s="1">
         <v>0</v>
@@ -3896,32 +3850,18 @@
       <c r="R12">
         <v>45</v>
       </c>
-      <c r="S12" s="7" t="s">
+      <c r="T12" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="T12" s="1">
-        <v>50</v>
-      </c>
-      <c r="U12" s="1">
-        <v>51</v>
-      </c>
-      <c r="V12" s="1">
-        <v>52</v>
-      </c>
-      <c r="W12" s="1">
-        <v>53</v>
-      </c>
-      <c r="X12" s="1">
-        <v>54</v>
-      </c>
-      <c r="Y12" s="1">
-        <v>55</v>
-      </c>
-      <c r="Z12" s="1">
-        <v>56</v>
-      </c>
-      <c r="AA12" s="1">
-        <v>57</v>
+      <c r="V12">
+        <v>30</v>
+      </c>
+      <c r="X12" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z12">
+        <f>COUNTIF($E$4:$E$88,T12)</f>
+        <v>14</v>
       </c>
     </row>
     <row r="13" ht="16.5" customHeight="1" spans="2:26">
@@ -3935,22 +3875,19 @@
         <v>91</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="F13" s="7" t="s">
         <v>47</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>92</v>
+        <v>0.15</v>
       </c>
       <c r="I13" s="1">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="K13" s="1">
         <v>0</v>
@@ -3973,18 +3910,28 @@
       <c r="R13">
         <v>45</v>
       </c>
-      <c r="Z13" t="s">
+      <c r="T13" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="V13">
+        <v>10</v>
+      </c>
+      <c r="X13" s="9" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="14" ht="33.75" customHeight="1" spans="2:26">
+      <c r="Z13">
+        <f>COUNTIF($E$4:$E$88,T13)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" ht="16.5" customHeight="1" spans="2:18">
       <c r="B14" s="7" t="s">
         <v>94</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D14" s="1" t="s">
         <v>96</v>
       </c>
       <c r="E14" s="7" t="s">
@@ -3994,10 +3941,7 @@
         <v>47</v>
       </c>
       <c r="G14" s="1">
-        <v>20</v>
-      </c>
-      <c r="H14" s="7" t="s">
-        <v>97</v>
+        <v>0.2</v>
       </c>
       <c r="I14" s="1">
         <v>300</v>
@@ -4026,44 +3970,31 @@
       <c r="R14">
         <v>45</v>
       </c>
-      <c r="T14" s="9" t="s">
+    </row>
+    <row r="15" ht="16.5" customHeight="1" spans="2:18">
+      <c r="B15" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="V14">
-        <v>300</v>
-      </c>
-      <c r="X14" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="Z14">
-        <f>COUNTIF($E$4:$E$92,T14)</f>
-        <v>28</v>
-      </c>
-    </row>
-    <row r="15" ht="33.75" customHeight="1" spans="2:26">
-      <c r="B15" s="7" t="s">
+      <c r="D15" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="C15" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>101</v>
-      </c>
       <c r="E15" s="7" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="F15" s="7" t="s">
         <v>47</v>
       </c>
       <c r="G15" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="I15" s="1">
         <v>100</v>
       </c>
-      <c r="I15" s="1">
-        <v>300</v>
-      </c>
       <c r="J15" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="K15" s="1">
         <v>0</v>
@@ -4086,29 +4017,16 @@
       <c r="R15">
         <v>45</v>
       </c>
-      <c r="T15" s="9" t="s">
+    </row>
+    <row r="16" ht="16.5" customHeight="1" spans="2:18">
+      <c r="B16" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>102</v>
-      </c>
-      <c r="V15">
-        <v>100</v>
-      </c>
-      <c r="X15" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="Z15">
-        <f>COUNTIF($E$4:$E$92,T15)</f>
-        <v>41</v>
-      </c>
-    </row>
-    <row r="16" ht="33.75" customHeight="1" spans="2:26">
-      <c r="B16" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>105</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>46</v>
@@ -4117,7 +4035,7 @@
         <v>47</v>
       </c>
       <c r="G16" s="1">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="I16" s="1">
         <v>100</v>
@@ -4146,44 +4064,31 @@
       <c r="R16">
         <v>45</v>
       </c>
-      <c r="T16" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="V16">
-        <v>30</v>
-      </c>
-      <c r="X16" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="Z16">
-        <f>COUNTIF($E$4:$E$92,T16)</f>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17" ht="16.5" customHeight="1" spans="2:26">
+    </row>
+    <row r="17" ht="16.5" customHeight="1" spans="2:18">
       <c r="B17" s="7" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="F17" s="7" t="s">
         <v>47</v>
       </c>
       <c r="G17" s="1">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="I17" s="1">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="K17" s="1">
         <v>0</v>
@@ -4206,44 +4111,31 @@
       <c r="R17">
         <v>45</v>
       </c>
-      <c r="T17" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="V17">
-        <v>10</v>
-      </c>
-      <c r="X17" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="Z17">
-        <f>COUNTIF($E$4:$E$92,T17)</f>
-        <v>6</v>
-      </c>
     </row>
     <row r="18" ht="16.5" customHeight="1" spans="2:18">
       <c r="B18" s="7" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="F18" s="7" t="s">
         <v>47</v>
       </c>
       <c r="G18" s="1">
-        <v>0.2</v>
+        <v>30</v>
       </c>
       <c r="I18" s="1">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="K18" s="1">
         <v>0</v>
@@ -4269,16 +4161,16 @@
     </row>
     <row r="19" ht="16.5" customHeight="1" spans="2:18">
       <c r="B19" s="7" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="F19" s="7" t="s">
         <v>47</v>
@@ -4287,10 +4179,10 @@
         <v>0.2</v>
       </c>
       <c r="I19" s="1">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="K19" s="1">
         <v>0</v>
@@ -4314,30 +4206,30 @@
         <v>45</v>
       </c>
     </row>
-    <row r="20" ht="16.5" customHeight="1" spans="2:18">
+    <row r="20" ht="33.75" customHeight="1" spans="2:18">
       <c r="B20" s="7" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>120</v>
+        <v>113</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>114</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="F20" s="7" t="s">
         <v>47</v>
       </c>
       <c r="G20" s="1">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="I20" s="1">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="K20" s="1">
         <v>0</v>
@@ -4361,15 +4253,15 @@
         <v>45</v>
       </c>
     </row>
-    <row r="21" ht="16.5" customHeight="1" spans="2:18">
+    <row r="21" ht="33.75" customHeight="1" spans="2:18">
       <c r="B21" s="7" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>123</v>
+        <v>116</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>117</v>
       </c>
       <c r="E21" s="7" t="s">
         <v>53</v>
@@ -4378,7 +4270,10 @@
         <v>47</v>
       </c>
       <c r="G21" s="1">
-        <v>0.2</v>
+        <v>0</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>118</v>
       </c>
       <c r="I21" s="1">
         <v>300</v>
@@ -4410,28 +4305,28 @@
     </row>
     <row r="22" ht="16.5" customHeight="1" spans="2:18">
       <c r="B22" s="7" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>81</v>
+        <v>53</v>
       </c>
       <c r="F22" s="7" t="s">
         <v>47</v>
       </c>
       <c r="G22" s="1">
-        <v>30</v>
+        <v>-0.1</v>
       </c>
       <c r="I22" s="1">
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>83</v>
+        <v>55</v>
       </c>
       <c r="K22" s="1">
         <v>0</v>
@@ -4457,28 +4352,28 @@
     </row>
     <row r="23" ht="16.5" customHeight="1" spans="2:18">
       <c r="B23" s="7" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="F23" s="7" t="s">
         <v>47</v>
       </c>
       <c r="G23" s="1">
-        <v>0.2</v>
+        <v>-0.1</v>
       </c>
       <c r="I23" s="1">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="K23" s="1">
         <v>0</v>
@@ -4502,30 +4397,30 @@
         <v>45</v>
       </c>
     </row>
-    <row r="24" ht="33.75" customHeight="1" spans="2:18">
+    <row r="24" ht="16.5" customHeight="1" spans="2:18">
       <c r="B24" s="7" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>132</v>
+        <v>126</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="F24" s="7" t="s">
         <v>47</v>
       </c>
       <c r="G24" s="1">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="I24" s="1">
         <v>30</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="K24" s="1">
         <v>0</v>
@@ -4551,31 +4446,31 @@
     </row>
     <row r="25" ht="33.75" customHeight="1" spans="2:18">
       <c r="B25" s="7" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="F25" s="7" t="s">
         <v>47</v>
       </c>
       <c r="G25" s="1">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="I25" s="1">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="K25" s="1">
         <v>0</v>
@@ -4599,30 +4494,33 @@
         <v>45</v>
       </c>
     </row>
-    <row r="26" ht="16.5" customHeight="1" spans="2:18">
+    <row r="26" ht="33.75" customHeight="1" spans="2:18">
       <c r="B26" s="7" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>139</v>
+        <v>133</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>134</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="F26" s="7" t="s">
         <v>47</v>
       </c>
       <c r="G26" s="1">
-        <v>-0.1</v>
+        <v>1.1</v>
+      </c>
+      <c r="H26" s="7" t="s">
+        <v>135</v>
       </c>
       <c r="I26" s="1">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="K26" s="1">
         <v>0</v>
@@ -4646,15 +4544,15 @@
         <v>45</v>
       </c>
     </row>
-    <row r="27" ht="16.5" customHeight="1" spans="2:18">
+    <row r="27" ht="33.75" customHeight="1" spans="2:18">
       <c r="B27" s="7" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>142</v>
+        <v>137</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>138</v>
       </c>
       <c r="E27" s="7" t="s">
         <v>46</v>
@@ -4663,7 +4561,7 @@
         <v>47</v>
       </c>
       <c r="G27" s="1">
-        <v>-0.1</v>
+        <v>0.1</v>
       </c>
       <c r="I27" s="1">
         <v>100</v>
@@ -4695,28 +4593,28 @@
     </row>
     <row r="28" ht="16.5" customHeight="1" spans="2:18">
       <c r="B28" s="7" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>81</v>
+        <v>46</v>
       </c>
       <c r="F28" s="7" t="s">
         <v>47</v>
       </c>
       <c r="G28" s="1">
-        <v>-0.1</v>
+        <v>10</v>
       </c>
       <c r="I28" s="1">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>83</v>
+        <v>49</v>
       </c>
       <c r="K28" s="1">
         <v>0</v>
@@ -4742,13 +4640,13 @@
     </row>
     <row r="29" ht="33.75" customHeight="1" spans="2:18">
       <c r="B29" s="7" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="E29" s="7" t="s">
         <v>46</v>
@@ -4757,10 +4655,10 @@
         <v>47</v>
       </c>
       <c r="G29" s="1">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="I29" s="1">
         <v>100</v>
@@ -4792,31 +4690,31 @@
     </row>
     <row r="30" ht="33.75" customHeight="1" spans="2:18">
       <c r="B30" s="7" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>81</v>
+        <v>46</v>
       </c>
       <c r="F30" s="7" t="s">
         <v>47</v>
       </c>
       <c r="G30" s="1">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="H30" s="7" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="I30" s="1">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>83</v>
+        <v>49</v>
       </c>
       <c r="K30" s="1">
         <v>0</v>
@@ -4842,13 +4740,13 @@
     </row>
     <row r="31" ht="33.75" customHeight="1" spans="2:18">
       <c r="B31" s="7" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E31" s="7" t="s">
         <v>46</v>
@@ -4857,7 +4755,7 @@
         <v>47</v>
       </c>
       <c r="G31" s="1">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="I31" s="1">
         <v>100</v>
@@ -4889,13 +4787,13 @@
     </row>
     <row r="32" ht="16.5" customHeight="1" spans="2:18">
       <c r="B32" s="7" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="E32" s="7" t="s">
         <v>46</v>
@@ -4904,7 +4802,7 @@
         <v>47</v>
       </c>
       <c r="G32" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I32" s="1">
         <v>100</v>
@@ -4936,31 +4834,28 @@
     </row>
     <row r="33" ht="33.75" customHeight="1" spans="2:18">
       <c r="B33" s="7" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="F33" s="7" t="s">
         <v>47</v>
       </c>
       <c r="G33" s="1">
-        <v>0</v>
-      </c>
-      <c r="H33" s="7" t="s">
-        <v>163</v>
+        <v>0.2</v>
       </c>
       <c r="I33" s="1">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="K33" s="1">
         <v>0</v>
@@ -4986,31 +4881,28 @@
     </row>
     <row r="34" ht="33.75" customHeight="1" spans="2:18">
       <c r="B34" s="7" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="F34" s="7" t="s">
         <v>47</v>
       </c>
       <c r="G34" s="1">
-        <v>0</v>
-      </c>
-      <c r="H34" s="7" t="s">
-        <v>167</v>
+        <v>5</v>
       </c>
       <c r="I34" s="1">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="K34" s="1">
         <v>0</v>
@@ -5036,13 +4928,13 @@
     </row>
     <row r="35" ht="33.75" customHeight="1" spans="2:18">
       <c r="B35" s="7" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="E35" s="7" t="s">
         <v>46</v>
@@ -5051,7 +4943,7 @@
         <v>47</v>
       </c>
       <c r="G35" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I35" s="1">
         <v>100</v>
@@ -5081,15 +4973,15 @@
         <v>45</v>
       </c>
     </row>
-    <row r="36" ht="16.5" customHeight="1" spans="2:18">
+    <row r="36" ht="33.75" customHeight="1" spans="2:18">
       <c r="B36" s="7" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>173</v>
+        <v>166</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>167</v>
       </c>
       <c r="E36" s="7" t="s">
         <v>46</v>
@@ -5098,7 +4990,7 @@
         <v>47</v>
       </c>
       <c r="G36" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I36" s="1">
         <v>100</v>
@@ -5130,28 +5022,28 @@
     </row>
     <row r="37" ht="33.75" customHeight="1" spans="2:18">
       <c r="B37" s="7" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>81</v>
+        <v>46</v>
       </c>
       <c r="F37" s="7" t="s">
         <v>47</v>
       </c>
       <c r="G37" s="1">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I37" s="1">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>83</v>
+        <v>49</v>
       </c>
       <c r="K37" s="1">
         <v>0</v>
@@ -5175,30 +5067,30 @@
         <v>45</v>
       </c>
     </row>
-    <row r="38" ht="33.75" customHeight="1" spans="2:18">
+    <row r="38" ht="16.5" customHeight="1" spans="2:18">
       <c r="B38" s="7" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="D38" s="8" t="s">
-        <v>179</v>
+        <v>172</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>173</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="F38" s="7" t="s">
         <v>47</v>
       </c>
       <c r="G38" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I38" s="1">
         <v>30</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="K38" s="1">
         <v>0</v>
@@ -5224,13 +5116,13 @@
     </row>
     <row r="39" ht="33.75" customHeight="1" spans="2:18">
       <c r="B39" s="7" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="E39" s="7" t="s">
         <v>46</v>
@@ -5239,7 +5131,10 @@
         <v>47</v>
       </c>
       <c r="G39" s="1">
-        <v>5</v>
+        <v>300</v>
+      </c>
+      <c r="H39" s="7" t="s">
+        <v>177</v>
       </c>
       <c r="I39" s="1">
         <v>100</v>
@@ -5269,15 +5164,15 @@
         <v>45</v>
       </c>
     </row>
-    <row r="40" ht="33.75" customHeight="1" spans="2:18">
+    <row r="40" ht="16.5" customHeight="1" spans="2:18">
       <c r="B40" s="7" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="D40" s="8" t="s">
-        <v>185</v>
+        <v>179</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>180</v>
       </c>
       <c r="E40" s="7" t="s">
         <v>46</v>
@@ -5286,7 +5181,7 @@
         <v>47</v>
       </c>
       <c r="G40" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I40" s="1">
         <v>100</v>
@@ -5316,15 +5211,15 @@
         <v>45</v>
       </c>
     </row>
-    <row r="41" ht="33.75" customHeight="1" spans="2:18">
+    <row r="41" ht="16.5" customHeight="1" spans="2:18">
       <c r="B41" s="7" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="D41" s="8" t="s">
-        <v>188</v>
+        <v>182</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>183</v>
       </c>
       <c r="E41" s="7" t="s">
         <v>46</v>
@@ -5365,28 +5260,28 @@
     </row>
     <row r="42" ht="16.5" customHeight="1" spans="2:18">
       <c r="B42" s="7" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>81</v>
+        <v>187</v>
       </c>
       <c r="F42" s="7" t="s">
         <v>47</v>
       </c>
       <c r="G42" s="1">
+        <v>1</v>
+      </c>
+      <c r="I42" s="1">
         <v>10</v>
       </c>
-      <c r="I42" s="1">
-        <v>30</v>
-      </c>
       <c r="J42" s="1" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="K42" s="1">
         <v>0</v>
@@ -5412,13 +5307,13 @@
     </row>
     <row r="43" ht="33.75" customHeight="1" spans="2:18">
       <c r="B43" s="7" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="E43" s="7" t="s">
         <v>46</v>
@@ -5427,10 +5322,7 @@
         <v>47</v>
       </c>
       <c r="G43" s="1">
-        <v>300</v>
-      </c>
-      <c r="H43" s="7" t="s">
-        <v>195</v>
+        <v>1</v>
       </c>
       <c r="I43" s="1">
         <v>100</v>
@@ -5460,15 +5352,15 @@
         <v>45</v>
       </c>
     </row>
-    <row r="44" ht="16.5" customHeight="1" spans="2:18">
+    <row r="44" ht="33.75" customHeight="1" spans="2:18">
       <c r="B44" s="7" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>198</v>
+        <v>192</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>193</v>
       </c>
       <c r="E44" s="7" t="s">
         <v>46</v>
@@ -5477,7 +5369,7 @@
         <v>47</v>
       </c>
       <c r="G44" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I44" s="1">
         <v>100</v>
@@ -5507,15 +5399,15 @@
         <v>45</v>
       </c>
     </row>
-    <row r="45" ht="16.5" customHeight="1" spans="2:18">
+    <row r="45" ht="33.75" customHeight="1" spans="2:18">
       <c r="B45" s="7" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>201</v>
+        <v>195</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>196</v>
       </c>
       <c r="E45" s="7" t="s">
         <v>46</v>
@@ -5524,7 +5416,10 @@
         <v>47</v>
       </c>
       <c r="G45" s="1">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="H45" s="7" t="s">
+        <v>197</v>
       </c>
       <c r="I45" s="1">
         <v>100</v>
@@ -5554,30 +5449,33 @@
         <v>45</v>
       </c>
     </row>
-    <row r="46" ht="16.5" customHeight="1" spans="2:18">
+    <row r="46" ht="33.75" customHeight="1" spans="2:18">
       <c r="B46" s="7" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>204</v>
+        <v>199</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>200</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>205</v>
+        <v>53</v>
       </c>
       <c r="F46" s="7" t="s">
         <v>47</v>
       </c>
       <c r="G46" s="1">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="H46" s="7" t="s">
+        <v>201</v>
       </c>
       <c r="I46" s="1">
-        <v>10</v>
+        <v>300</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>111</v>
+        <v>55</v>
       </c>
       <c r="K46" s="1">
         <v>0</v>
@@ -5603,28 +5501,31 @@
     </row>
     <row r="47" ht="33.75" customHeight="1" spans="2:18">
       <c r="B47" s="7" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="F47" s="7" t="s">
         <v>47</v>
       </c>
       <c r="G47" s="1">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="H47" s="7" t="s">
+        <v>205</v>
       </c>
       <c r="I47" s="1">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="J47" s="1" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="K47" s="1">
         <v>0</v>
@@ -5648,15 +5549,15 @@
         <v>45</v>
       </c>
     </row>
-    <row r="48" ht="33.75" customHeight="1" spans="2:18">
+    <row r="48" ht="16.5" customHeight="1" spans="2:18">
       <c r="B48" s="7" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="D48" s="8" t="s">
-        <v>211</v>
+        <v>207</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>208</v>
       </c>
       <c r="E48" s="7" t="s">
         <v>46</v>
@@ -5665,7 +5566,7 @@
         <v>47</v>
       </c>
       <c r="G48" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I48" s="1">
         <v>100</v>
@@ -5697,13 +5598,13 @@
     </row>
     <row r="49" ht="33.75" customHeight="1" spans="2:18">
       <c r="B49" s="7" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="E49" s="7" t="s">
         <v>46</v>
@@ -5712,10 +5613,7 @@
         <v>47</v>
       </c>
       <c r="G49" s="1">
-        <v>2</v>
-      </c>
-      <c r="H49" s="7" t="s">
-        <v>215</v>
+        <v>5</v>
       </c>
       <c r="I49" s="1">
         <v>100</v>
@@ -5747,31 +5645,28 @@
     </row>
     <row r="50" ht="33.75" customHeight="1" spans="2:18">
       <c r="B50" s="7" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="F50" s="7" t="s">
         <v>47</v>
       </c>
       <c r="G50" s="1">
-        <v>2</v>
-      </c>
-      <c r="H50" s="7" t="s">
-        <v>219</v>
+        <v>600</v>
       </c>
       <c r="I50" s="1">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="J50" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="K50" s="1">
         <v>0</v>
@@ -5795,18 +5690,18 @@
         <v>45</v>
       </c>
     </row>
-    <row r="51" ht="33.75" customHeight="1" spans="2:18">
+    <row r="51" ht="16.5" customHeight="1" spans="2:18">
       <c r="B51" s="7" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D51" s="8" t="s">
-        <v>222</v>
+        <v>216</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>217</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="F51" s="7" t="s">
         <v>47</v>
@@ -5814,14 +5709,11 @@
       <c r="G51" s="1">
         <v>2</v>
       </c>
-      <c r="H51" s="7" t="s">
-        <v>223</v>
-      </c>
       <c r="I51" s="1">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="J51" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="K51" s="1">
         <v>0</v>
@@ -5845,15 +5737,15 @@
         <v>45</v>
       </c>
     </row>
-    <row r="52" ht="16.5" customHeight="1" spans="2:18">
+    <row r="52" ht="33.75" customHeight="1" spans="2:18">
       <c r="B52" s="7" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>226</v>
+        <v>219</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>220</v>
       </c>
       <c r="E52" s="7" t="s">
         <v>46</v>
@@ -5862,7 +5754,7 @@
         <v>47</v>
       </c>
       <c r="G52" s="1">
-        <v>2</v>
+        <v>200</v>
       </c>
       <c r="I52" s="1">
         <v>100</v>
@@ -5894,13 +5786,13 @@
     </row>
     <row r="53" ht="33.75" customHeight="1" spans="2:18">
       <c r="B53" s="7" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="E53" s="7" t="s">
         <v>46</v>
@@ -5909,7 +5801,7 @@
         <v>47</v>
       </c>
       <c r="G53" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I53" s="1">
         <v>100</v>
@@ -5939,30 +5831,30 @@
         <v>45</v>
       </c>
     </row>
-    <row r="54" ht="33.75" customHeight="1" spans="2:18">
+    <row r="54" ht="16.5" customHeight="1" spans="2:18">
       <c r="B54" s="7" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="D54" s="8" t="s">
-        <v>232</v>
+        <v>225</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>226</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>46</v>
+        <v>187</v>
       </c>
       <c r="F54" s="7" t="s">
         <v>47</v>
       </c>
       <c r="G54" s="1">
-        <v>600</v>
+        <v>1</v>
       </c>
       <c r="I54" s="1">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>49</v>
+        <v>93</v>
       </c>
       <c r="K54" s="1">
         <v>0</v>
@@ -5986,15 +5878,15 @@
         <v>45</v>
       </c>
     </row>
-    <row r="55" ht="16.5" customHeight="1" spans="2:18">
+    <row r="55" ht="33.75" customHeight="1" spans="2:18">
       <c r="B55" s="7" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>235</v>
+        <v>228</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>229</v>
       </c>
       <c r="E55" s="7" t="s">
         <v>46</v>
@@ -6003,7 +5895,7 @@
         <v>47</v>
       </c>
       <c r="G55" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I55" s="1">
         <v>100</v>
@@ -6035,13 +5927,13 @@
     </row>
     <row r="56" ht="33.75" customHeight="1" spans="2:18">
       <c r="B56" s="7" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="E56" s="7" t="s">
         <v>46</v>
@@ -6050,7 +5942,7 @@
         <v>47</v>
       </c>
       <c r="G56" s="1">
-        <v>200</v>
+        <v>2</v>
       </c>
       <c r="I56" s="1">
         <v>100</v>
@@ -6082,13 +5974,13 @@
     </row>
     <row r="57" ht="33.75" customHeight="1" spans="2:18">
       <c r="B57" s="7" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="E57" s="7" t="s">
         <v>46</v>
@@ -6097,7 +5989,7 @@
         <v>47</v>
       </c>
       <c r="G57" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I57" s="1">
         <v>100</v>
@@ -6127,30 +6019,30 @@
         <v>45</v>
       </c>
     </row>
-    <row r="58" ht="16.5" customHeight="1" spans="2:18">
+    <row r="58" ht="33.75" customHeight="1" spans="2:18">
       <c r="B58" s="7" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>244</v>
+        <v>237</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>238</v>
       </c>
       <c r="E58" s="7" t="s">
-        <v>205</v>
+        <v>63</v>
       </c>
       <c r="F58" s="7" t="s">
         <v>47</v>
       </c>
       <c r="G58" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I58" s="1">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="J58" s="1" t="s">
-        <v>111</v>
+        <v>65</v>
       </c>
       <c r="K58" s="1">
         <v>0</v>
@@ -6174,30 +6066,30 @@
         <v>45</v>
       </c>
     </row>
-    <row r="59" ht="33.75" customHeight="1" spans="2:18">
+    <row r="59" ht="16.5" customHeight="1" spans="2:18">
       <c r="B59" s="7" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="D59" s="8" t="s">
-        <v>247</v>
+        <v>240</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>241</v>
       </c>
       <c r="E59" s="7" t="s">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="F59" s="7" t="s">
         <v>47</v>
       </c>
       <c r="G59" s="1">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="I59" s="1">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="J59" s="1" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="K59" s="1">
         <v>0</v>
@@ -6221,30 +6113,30 @@
         <v>45</v>
       </c>
     </row>
-    <row r="60" ht="33.75" customHeight="1" spans="2:18">
+    <row r="60" ht="16.5" customHeight="1" spans="2:18">
       <c r="B60" s="7" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="D60" s="8" t="s">
-        <v>250</v>
+        <v>243</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>244</v>
       </c>
       <c r="E60" s="7" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="F60" s="7" t="s">
         <v>47</v>
       </c>
       <c r="G60" s="1">
-        <v>2</v>
+        <v>0.2</v>
       </c>
       <c r="I60" s="1">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="J60" s="1" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="K60" s="1">
         <v>0</v>
@@ -6270,28 +6162,28 @@
     </row>
     <row r="61" ht="33.75" customHeight="1" spans="2:18">
       <c r="B61" s="7" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="E61" s="7" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="F61" s="7" t="s">
         <v>47</v>
       </c>
       <c r="G61" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I61" s="1">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="J61" s="1" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="K61" s="1">
         <v>0</v>
@@ -6315,30 +6207,30 @@
         <v>45</v>
       </c>
     </row>
-    <row r="62" ht="33.75" customHeight="1" spans="2:18">
+    <row r="62" ht="16.5" customHeight="1" spans="2:18">
       <c r="B62" s="7" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="D62" s="8" t="s">
-        <v>256</v>
+        <v>249</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>250</v>
       </c>
       <c r="E62" s="7" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="F62" s="7" t="s">
         <v>47</v>
       </c>
       <c r="G62" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I62" s="1">
         <v>30</v>
       </c>
       <c r="J62" s="1" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="K62" s="1">
         <v>0</v>
@@ -6362,30 +6254,30 @@
         <v>45</v>
       </c>
     </row>
-    <row r="63" ht="16.5" customHeight="1" spans="2:18">
+    <row r="63" ht="33.75" customHeight="1" spans="2:18">
       <c r="B63" s="7" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>259</v>
+        <v>252</v>
+      </c>
+      <c r="D63" s="8" t="s">
+        <v>253</v>
       </c>
       <c r="E63" s="7" t="s">
-        <v>81</v>
+        <v>46</v>
       </c>
       <c r="F63" s="7" t="s">
         <v>47</v>
       </c>
       <c r="G63" s="1">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I63" s="1">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="J63" s="1" t="s">
-        <v>83</v>
+        <v>49</v>
       </c>
       <c r="K63" s="1">
         <v>0</v>
@@ -6409,30 +6301,30 @@
         <v>45</v>
       </c>
     </row>
-    <row r="64" ht="16.5" customHeight="1" spans="2:18">
+    <row r="64" ht="33.75" customHeight="1" spans="2:18">
       <c r="B64" s="7" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>262</v>
+        <v>255</v>
+      </c>
+      <c r="D64" s="8" t="s">
+        <v>256</v>
       </c>
       <c r="E64" s="7" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="F64" s="7" t="s">
         <v>47</v>
       </c>
       <c r="G64" s="1">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I64" s="1">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="J64" s="1" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="K64" s="1">
         <v>0</v>
@@ -6458,28 +6350,31 @@
     </row>
     <row r="65" ht="33.75" customHeight="1" spans="2:18">
       <c r="B65" s="7" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="D65" s="8" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="E65" s="7" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="F65" s="7" t="s">
         <v>47</v>
       </c>
       <c r="G65" s="1">
-        <v>10</v>
+        <v>0</v>
+      </c>
+      <c r="H65" s="7" t="s">
+        <v>260</v>
       </c>
       <c r="I65" s="1">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="J65" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="K65" s="1">
         <v>0</v>
@@ -6503,18 +6398,18 @@
         <v>45</v>
       </c>
     </row>
-    <row r="66" ht="16.5" customHeight="1" spans="2:18">
+    <row r="66" ht="33.75" customHeight="1" spans="2:18">
       <c r="B66" s="7" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>268</v>
+        <v>262</v>
+      </c>
+      <c r="D66" s="8" t="s">
+        <v>263</v>
       </c>
       <c r="E66" s="7" t="s">
-        <v>81</v>
+        <v>46</v>
       </c>
       <c r="F66" s="7" t="s">
         <v>47</v>
@@ -6522,11 +6417,14 @@
       <c r="G66" s="1">
         <v>0</v>
       </c>
+      <c r="H66" s="7" t="s">
+        <v>264</v>
+      </c>
       <c r="I66" s="1">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="J66" s="1" t="s">
-        <v>83</v>
+        <v>49</v>
       </c>
       <c r="K66" s="1">
         <v>0</v>
@@ -6550,15 +6448,15 @@
         <v>45</v>
       </c>
     </row>
-    <row r="67" ht="33.75" customHeight="1" spans="2:18">
+    <row r="67" ht="16.5" customHeight="1" spans="2:18">
       <c r="B67" s="7" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="D67" s="8" t="s">
-        <v>271</v>
+        <v>266</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>267</v>
       </c>
       <c r="E67" s="7" t="s">
         <v>46</v>
@@ -6597,30 +6495,30 @@
         <v>45</v>
       </c>
     </row>
-    <row r="68" ht="33.75" customHeight="1" spans="2:18">
+    <row r="68" ht="16.5" customHeight="1" spans="2:18">
       <c r="B68" s="7" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="D68" s="8" t="s">
-        <v>274</v>
+        <v>269</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>270</v>
       </c>
       <c r="E68" s="7" t="s">
-        <v>81</v>
+        <v>53</v>
       </c>
       <c r="F68" s="7" t="s">
         <v>47</v>
       </c>
       <c r="G68" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I68" s="1">
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="J68" s="1" t="s">
-        <v>83</v>
+        <v>55</v>
       </c>
       <c r="K68" s="1">
         <v>0</v>
@@ -6646,13 +6544,13 @@
     </row>
     <row r="69" ht="33.75" customHeight="1" spans="2:18">
       <c r="B69" s="7" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="D69" s="8" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="E69" s="7" t="s">
         <v>46</v>
@@ -6661,10 +6559,7 @@
         <v>47</v>
       </c>
       <c r="G69" s="1">
-        <v>0</v>
-      </c>
-      <c r="H69" s="7" t="s">
-        <v>278</v>
+        <v>100</v>
       </c>
       <c r="I69" s="1">
         <v>100</v>
@@ -6694,33 +6589,30 @@
         <v>45</v>
       </c>
     </row>
-    <row r="70" ht="33.75" customHeight="1" spans="2:18">
+    <row r="70" ht="16.5" customHeight="1" spans="2:18">
       <c r="B70" s="7" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="D70" s="8" t="s">
-        <v>281</v>
+        <v>275</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>276</v>
       </c>
       <c r="E70" s="7" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="F70" s="7" t="s">
-        <v>47</v>
+        <v>277</v>
       </c>
       <c r="G70" s="1">
-        <v>0</v>
-      </c>
-      <c r="H70" s="7" t="s">
-        <v>282</v>
+        <v>-0.2</v>
       </c>
       <c r="I70" s="1">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="J70" s="1" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="K70" s="1">
         <v>0</v>
@@ -6746,28 +6638,28 @@
     </row>
     <row r="71" ht="16.5" customHeight="1" spans="2:18">
       <c r="B71" s="7" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E71" s="7" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="F71" s="7" t="s">
-        <v>47</v>
+        <v>277</v>
       </c>
       <c r="G71" s="1">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="I71" s="1">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="J71" s="1" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="K71" s="1">
         <v>0</v>
@@ -6793,22 +6685,22 @@
     </row>
     <row r="72" ht="16.5" customHeight="1" spans="2:18">
       <c r="B72" s="7" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="E72" s="7" t="s">
         <v>53</v>
       </c>
       <c r="F72" s="7" t="s">
-        <v>47</v>
+        <v>277</v>
       </c>
       <c r="G72" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I72" s="1">
         <v>300</v>
@@ -6838,30 +6730,30 @@
         <v>45</v>
       </c>
     </row>
-    <row r="73" ht="33.75" customHeight="1" spans="2:18">
+    <row r="73" ht="16.5" customHeight="1" spans="2:18">
       <c r="B73" s="7" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="D73" s="8" t="s">
-        <v>291</v>
+        <v>285</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>286</v>
       </c>
       <c r="E73" s="7" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="F73" s="7" t="s">
-        <v>47</v>
+        <v>277</v>
       </c>
       <c r="G73" s="1">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="I73" s="1">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="J73" s="1" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="K73" s="1">
         <v>0</v>
@@ -6885,24 +6777,24 @@
         <v>45</v>
       </c>
     </row>
-    <row r="74" ht="16.5" customHeight="1" spans="2:18">
+    <row r="74" ht="33.75" customHeight="1" spans="2:18">
       <c r="B74" s="7" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="D74" s="1" t="s">
-        <v>294</v>
+        <v>288</v>
+      </c>
+      <c r="D74" s="8" t="s">
+        <v>289</v>
       </c>
       <c r="E74" s="7" t="s">
         <v>53</v>
       </c>
       <c r="F74" s="7" t="s">
-        <v>295</v>
+        <v>277</v>
       </c>
       <c r="G74" s="1">
-        <v>-0.2</v>
+        <v>-1</v>
       </c>
       <c r="I74" s="1">
         <v>300</v>
@@ -6934,19 +6826,19 @@
     </row>
     <row r="75" ht="16.5" customHeight="1" spans="2:18">
       <c r="B75" s="7" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="E75" s="7" t="s">
         <v>53</v>
       </c>
       <c r="F75" s="7" t="s">
-        <v>295</v>
+        <v>277</v>
       </c>
       <c r="G75" s="1">
         <v>0.2</v>
@@ -6981,22 +6873,22 @@
     </row>
     <row r="76" ht="16.5" customHeight="1" spans="2:18">
       <c r="B76" s="7" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="E76" s="7" t="s">
         <v>53</v>
       </c>
       <c r="F76" s="7" t="s">
-        <v>295</v>
+        <v>277</v>
       </c>
       <c r="G76" s="1">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="I76" s="1">
         <v>300</v>
@@ -7028,22 +6920,22 @@
     </row>
     <row r="77" ht="16.5" customHeight="1" spans="2:18">
       <c r="B77" s="7" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="E77" s="7" t="s">
         <v>53</v>
       </c>
       <c r="F77" s="7" t="s">
-        <v>295</v>
+        <v>277</v>
       </c>
       <c r="G77" s="1">
-        <v>1</v>
+        <v>0.15</v>
       </c>
       <c r="I77" s="1">
         <v>300</v>
@@ -7073,24 +6965,24 @@
         <v>45</v>
       </c>
     </row>
-    <row r="78" ht="33.75" customHeight="1" spans="2:18">
+    <row r="78" ht="16.5" customHeight="1" spans="2:18">
       <c r="B78" s="7" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="D78" s="8" t="s">
-        <v>307</v>
+        <v>300</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>301</v>
       </c>
       <c r="E78" s="7" t="s">
         <v>53</v>
       </c>
       <c r="F78" s="7" t="s">
-        <v>295</v>
+        <v>277</v>
       </c>
       <c r="G78" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I78" s="1">
         <v>300</v>
@@ -7122,28 +7014,28 @@
     </row>
     <row r="79" ht="16.5" customHeight="1" spans="2:18">
       <c r="B79" s="7" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="E79" s="7" t="s">
-        <v>53</v>
+        <v>187</v>
       </c>
       <c r="F79" s="7" t="s">
-        <v>295</v>
+        <v>47</v>
       </c>
       <c r="G79" s="1">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="I79" s="1">
-        <v>300</v>
+        <v>10</v>
       </c>
       <c r="J79" s="1" t="s">
-        <v>55</v>
+        <v>93</v>
       </c>
       <c r="K79" s="1">
         <v>0</v>
@@ -7167,30 +7059,30 @@
         <v>45</v>
       </c>
     </row>
-    <row r="80" ht="16.5" customHeight="1" spans="2:18">
+    <row r="80" ht="33.75" customHeight="1" spans="2:18">
       <c r="B80" s="7" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="D80" s="1" t="s">
-        <v>313</v>
+        <v>306</v>
+      </c>
+      <c r="D80" s="8" t="s">
+        <v>307</v>
       </c>
       <c r="E80" s="7" t="s">
-        <v>53</v>
+        <v>187</v>
       </c>
       <c r="F80" s="7" t="s">
-        <v>295</v>
+        <v>47</v>
       </c>
       <c r="G80" s="1">
-        <v>0.15</v>
+        <v>1.2</v>
       </c>
       <c r="I80" s="1">
-        <v>300</v>
+        <v>10</v>
       </c>
       <c r="J80" s="1" t="s">
-        <v>55</v>
+        <v>93</v>
       </c>
       <c r="K80" s="1">
         <v>0</v>
@@ -7209,35 +7101,38 @@
       </c>
       <c r="P80" s="1">
         <v>0</v>
+      </c>
+      <c r="Q80" s="7" t="s">
+        <v>308</v>
       </c>
       <c r="R80">
         <v>45</v>
       </c>
     </row>
-    <row r="81" ht="16.5" customHeight="1" spans="2:18">
+    <row r="81" ht="33.75" customHeight="1" spans="2:18">
       <c r="B81" s="7" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="D81" s="1" t="s">
-        <v>316</v>
+        <v>310</v>
+      </c>
+      <c r="D81" s="8" t="s">
+        <v>311</v>
       </c>
       <c r="E81" s="7" t="s">
-        <v>53</v>
+        <v>187</v>
       </c>
       <c r="F81" s="7" t="s">
-        <v>295</v>
+        <v>47</v>
       </c>
       <c r="G81" s="1">
-        <v>0.15</v>
+        <v>1.2</v>
       </c>
       <c r="I81" s="1">
-        <v>300</v>
+        <v>10</v>
       </c>
       <c r="J81" s="1" t="s">
-        <v>55</v>
+        <v>93</v>
       </c>
       <c r="K81" s="1">
         <v>0</v>
@@ -7256,35 +7151,38 @@
       </c>
       <c r="P81" s="1">
         <v>0</v>
+      </c>
+      <c r="Q81" s="7" t="s">
+        <v>308</v>
       </c>
       <c r="R81">
         <v>45</v>
       </c>
     </row>
-    <row r="82" ht="16.5" customHeight="1" spans="2:18">
+    <row r="82" ht="33.75" customHeight="1" spans="2:18">
       <c r="B82" s="7" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>319</v>
+        <v>313</v>
+      </c>
+      <c r="D82" s="8" t="s">
+        <v>314</v>
       </c>
       <c r="E82" s="7" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="F82" s="7" t="s">
-        <v>295</v>
+        <v>47</v>
       </c>
       <c r="G82" s="1">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="I82" s="1">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="J82" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="K82" s="1">
         <v>0</v>
@@ -7303,35 +7201,41 @@
       </c>
       <c r="P82" s="1">
         <v>0</v>
+      </c>
+      <c r="Q82" s="7" t="s">
+        <v>308</v>
       </c>
       <c r="R82">
         <v>45</v>
       </c>
     </row>
-    <row r="83" ht="16.5" customHeight="1" spans="2:18">
+    <row r="83" ht="33.75" customHeight="1" spans="2:18">
       <c r="B83" s="7" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="D83" s="1" t="s">
-        <v>322</v>
+        <v>316</v>
+      </c>
+      <c r="D83" s="8" t="s">
+        <v>317</v>
       </c>
       <c r="E83" s="7" t="s">
-        <v>205</v>
+        <v>46</v>
       </c>
       <c r="F83" s="7" t="s">
         <v>47</v>
       </c>
       <c r="G83" s="1">
-        <v>2</v>
+        <v>10</v>
+      </c>
+      <c r="H83" s="7" t="s">
+        <v>318</v>
       </c>
       <c r="I83" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="J83" s="1" t="s">
-        <v>111</v>
+        <v>49</v>
       </c>
       <c r="K83" s="1">
         <v>0</v>
@@ -7350,6 +7254,9 @@
       </c>
       <c r="P83" s="1">
         <v>0</v>
+      </c>
+      <c r="Q83" s="7" t="s">
+        <v>308</v>
       </c>
       <c r="R83">
         <v>45</v>
@@ -7357,28 +7264,28 @@
     </row>
     <row r="84" ht="33.75" customHeight="1" spans="2:18">
       <c r="B84" s="7" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="D84" s="8" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="E84" s="7" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="F84" s="7" t="s">
         <v>47</v>
       </c>
       <c r="G84" s="1">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="I84" s="1">
         <v>10</v>
       </c>
       <c r="J84" s="1" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="K84" s="1">
         <v>0</v>
@@ -7399,7 +7306,7 @@
         <v>0</v>
       </c>
       <c r="Q84" s="7" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="R84">
         <v>45</v>
@@ -7407,28 +7314,28 @@
     </row>
     <row r="85" ht="33.75" customHeight="1" spans="2:18">
       <c r="B85" s="7" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="D85" s="8" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="E85" s="7" t="s">
-        <v>205</v>
+        <v>46</v>
       </c>
       <c r="F85" s="7" t="s">
         <v>47</v>
       </c>
       <c r="G85" s="1">
-        <v>1.2</v>
+        <v>10</v>
       </c>
       <c r="I85" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="J85" s="1" t="s">
-        <v>111</v>
+        <v>49</v>
       </c>
       <c r="K85" s="1">
         <v>0</v>
@@ -7449,7 +7356,7 @@
         <v>0</v>
       </c>
       <c r="Q85" s="7" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="R85">
         <v>45</v>
@@ -7457,28 +7364,28 @@
     </row>
     <row r="86" ht="33.75" customHeight="1" spans="2:18">
       <c r="B86" s="7" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="D86" s="8" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="E86" s="7" t="s">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="F86" s="7" t="s">
         <v>47</v>
       </c>
       <c r="G86" s="1">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I86" s="1">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="J86" s="1" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="K86" s="1">
         <v>0</v>
@@ -7499,7 +7406,7 @@
         <v>0</v>
       </c>
       <c r="Q86" s="7" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="R86">
         <v>45</v>
@@ -7507,13 +7414,13 @@
     </row>
     <row r="87" ht="33.75" customHeight="1" spans="2:18">
       <c r="B87" s="7" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="D87" s="8" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="E87" s="7" t="s">
         <v>46</v>
@@ -7525,7 +7432,7 @@
         <v>10</v>
       </c>
       <c r="H87" s="7" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="I87" s="1">
         <v>100</v>
@@ -7552,36 +7459,36 @@
         <v>0</v>
       </c>
       <c r="Q87" s="7" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="R87">
         <v>45</v>
       </c>
     </row>
-    <row r="88" ht="33.75" customHeight="1" spans="2:18">
+    <row r="88" ht="16.5" customHeight="1" spans="2:18">
       <c r="B88" s="7" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="D88" s="8" t="s">
-        <v>339</v>
+        <v>334</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>335</v>
       </c>
       <c r="E88" s="7" t="s">
-        <v>205</v>
+        <v>46</v>
       </c>
       <c r="F88" s="7" t="s">
         <v>47</v>
       </c>
       <c r="G88" s="1">
-        <v>0.2</v>
+        <v>10</v>
       </c>
       <c r="I88" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="J88" s="1" t="s">
-        <v>111</v>
+        <v>49</v>
       </c>
       <c r="K88" s="1">
         <v>0</v>
@@ -7602,212 +7509,9 @@
         <v>0</v>
       </c>
       <c r="Q88" s="7" t="s">
-        <v>340</v>
+        <v>322</v>
       </c>
       <c r="R88">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="89" ht="33.75" customHeight="1" spans="2:18">
-      <c r="B89" s="7" t="s">
-        <v>341</v>
-      </c>
-      <c r="C89" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="D89" s="8" t="s">
-        <v>343</v>
-      </c>
-      <c r="E89" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="F89" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="G89" s="1">
-        <v>10</v>
-      </c>
-      <c r="I89" s="1">
-        <v>100</v>
-      </c>
-      <c r="J89" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="K89" s="1">
-        <v>0</v>
-      </c>
-      <c r="L89" s="1">
-        <v>0</v>
-      </c>
-      <c r="M89" s="1">
-        <v>0</v>
-      </c>
-      <c r="N89" s="1">
-        <v>0</v>
-      </c>
-      <c r="O89" s="1">
-        <v>0</v>
-      </c>
-      <c r="P89" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q89" s="7" t="s">
-        <v>340</v>
-      </c>
-      <c r="R89">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="90" ht="33.75" customHeight="1" spans="2:18">
-      <c r="B90" s="7" t="s">
-        <v>344</v>
-      </c>
-      <c r="C90" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="D90" s="8" t="s">
-        <v>346</v>
-      </c>
-      <c r="E90" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="F90" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="G90" s="1">
-        <v>1</v>
-      </c>
-      <c r="I90" s="1">
-        <v>30</v>
-      </c>
-      <c r="J90" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="K90" s="1">
-        <v>0</v>
-      </c>
-      <c r="L90" s="1">
-        <v>0</v>
-      </c>
-      <c r="M90" s="1">
-        <v>0</v>
-      </c>
-      <c r="N90" s="1">
-        <v>0</v>
-      </c>
-      <c r="O90" s="1">
-        <v>0</v>
-      </c>
-      <c r="P90" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q90" s="7" t="s">
-        <v>340</v>
-      </c>
-      <c r="R90">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="91" ht="33.75" customHeight="1" spans="2:18">
-      <c r="B91" s="7" t="s">
-        <v>347</v>
-      </c>
-      <c r="C91" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="D91" s="8" t="s">
-        <v>349</v>
-      </c>
-      <c r="E91" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="F91" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="G91" s="1">
-        <v>10</v>
-      </c>
-      <c r="H91" s="7" t="s">
-        <v>350</v>
-      </c>
-      <c r="I91" s="1">
-        <v>100</v>
-      </c>
-      <c r="J91" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="K91" s="1">
-        <v>0</v>
-      </c>
-      <c r="L91" s="1">
-        <v>0</v>
-      </c>
-      <c r="M91" s="1">
-        <v>0</v>
-      </c>
-      <c r="N91" s="1">
-        <v>0</v>
-      </c>
-      <c r="O91" s="1">
-        <v>0</v>
-      </c>
-      <c r="P91" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q91" s="7" t="s">
-        <v>340</v>
-      </c>
-      <c r="R91">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="92" ht="16.5" customHeight="1" spans="2:18">
-      <c r="B92" s="7" t="s">
-        <v>351</v>
-      </c>
-      <c r="C92" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="E92" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="F92" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="G92" s="1">
-        <v>10</v>
-      </c>
-      <c r="I92" s="1">
-        <v>100</v>
-      </c>
-      <c r="J92" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="K92" s="1">
-        <v>0</v>
-      </c>
-      <c r="L92" s="1">
-        <v>0</v>
-      </c>
-      <c r="M92" s="1">
-        <v>0</v>
-      </c>
-      <c r="N92" s="1">
-        <v>0</v>
-      </c>
-      <c r="O92" s="1">
-        <v>0</v>
-      </c>
-      <c r="P92" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q92" s="7" t="s">
-        <v>340</v>
-      </c>
-      <c r="R92">
         <v>45</v>
       </c>
     </row>
@@ -7855,7 +7559,7 @@
         <v>5</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>354</v>
+        <v>336</v>
       </c>
       <c r="G1" s="7" t="s">
         <v>6</v>
@@ -7867,10 +7571,10 @@
         <v>8</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>355</v>
+        <v>337</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>356</v>
+        <v>338</v>
       </c>
       <c r="L1" s="9" t="s">
         <v>16</v>
@@ -7896,7 +7600,7 @@
         <v>23</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>357</v>
+        <v>339</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>24</v>
@@ -7908,10 +7612,10 @@
         <v>26</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>358</v>
+        <v>340</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>359</v>
+        <v>341</v>
       </c>
       <c r="L2" t="s">
         <v>34</v>
@@ -7949,7 +7653,7 @@
         <v>40</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>360</v>
+        <v>342</v>
       </c>
       <c r="K3" s="7" t="s">
         <v>42</v>
@@ -7963,34 +7667,34 @@
     </row>
     <row r="4" ht="33.75" customHeight="1" spans="2:13">
       <c r="B4" s="7" t="s">
-        <v>361</v>
+        <v>343</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>363</v>
+        <v>345</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>364</v>
+        <v>346</v>
       </c>
       <c r="G4" s="1">
         <v>0</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>365</v>
+        <v>347</v>
       </c>
       <c r="I4" s="1">
         <v>1</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>366</v>
+        <v>348</v>
       </c>
       <c r="K4" s="1">
         <v>1</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>365</v>
+        <v>347</v>
       </c>
       <c r="M4">
         <v>35</v>
@@ -7998,34 +7702,34 @@
     </row>
     <row r="5" ht="33.75" customHeight="1" spans="2:13">
       <c r="B5" s="7" t="s">
-        <v>367</v>
+        <v>349</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>368</v>
+        <v>350</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>369</v>
+        <v>351</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>364</v>
+        <v>346</v>
       </c>
       <c r="G5" s="1">
         <v>0</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>370</v>
+        <v>352</v>
       </c>
       <c r="I5" s="1">
         <v>1</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>366</v>
+        <v>348</v>
       </c>
       <c r="K5" s="1">
         <v>1</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>370</v>
+        <v>352</v>
       </c>
       <c r="M5">
         <v>35</v>
@@ -8033,34 +7737,34 @@
     </row>
     <row r="6" ht="33.75" customHeight="1" spans="2:13">
       <c r="B6" s="7" t="s">
-        <v>371</v>
+        <v>353</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>372</v>
+        <v>354</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>373</v>
+        <v>355</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>364</v>
+        <v>346</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>374</v>
+        <v>356</v>
       </c>
       <c r="I6" s="1">
         <v>1</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>366</v>
+        <v>348</v>
       </c>
       <c r="K6" s="1">
         <v>1</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>374</v>
+        <v>356</v>
       </c>
       <c r="M6">
         <v>35</v>
@@ -8068,34 +7772,34 @@
     </row>
     <row r="7" ht="33.75" customHeight="1" spans="2:13">
       <c r="B7" s="7" t="s">
-        <v>375</v>
+        <v>357</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>376</v>
+        <v>358</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>377</v>
+        <v>359</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>364</v>
+        <v>346</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>378</v>
+        <v>360</v>
       </c>
       <c r="I7" s="1">
         <v>1</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>366</v>
+        <v>348</v>
       </c>
       <c r="K7" s="1">
         <v>1</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>378</v>
+        <v>360</v>
       </c>
       <c r="M7">
         <v>35</v>
@@ -8103,34 +7807,34 @@
     </row>
     <row r="8" ht="33.75" customHeight="1" spans="2:13">
       <c r="B8" s="7" t="s">
-        <v>379</v>
+        <v>361</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>380</v>
+        <v>362</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>381</v>
+        <v>363</v>
       </c>
       <c r="F8" s="7" t="s">
+        <v>346</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0</v>
+      </c>
+      <c r="H8" s="7" t="s">
         <v>364</v>
-      </c>
-      <c r="G8" s="1">
-        <v>0</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>382</v>
       </c>
       <c r="I8" s="1">
         <v>1</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>366</v>
+        <v>348</v>
       </c>
       <c r="K8" s="1">
         <v>1</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>382</v>
+        <v>364</v>
       </c>
       <c r="M8">
         <v>35</v>
@@ -8138,34 +7842,34 @@
     </row>
     <row r="9" ht="33.75" customHeight="1" spans="2:13">
       <c r="B9" s="7" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>384</v>
+        <v>366</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>385</v>
+        <v>367</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>364</v>
+        <v>346</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>386</v>
+        <v>368</v>
       </c>
       <c r="I9" s="1">
         <v>1</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>366</v>
+        <v>348</v>
       </c>
       <c r="K9" s="1">
         <v>1</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>386</v>
+        <v>368</v>
       </c>
       <c r="M9">
         <v>35</v>
@@ -8173,34 +7877,34 @@
     </row>
     <row r="10" ht="33.75" customHeight="1" spans="2:13">
       <c r="B10" s="7" t="s">
-        <v>387</v>
+        <v>369</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>388</v>
+        <v>370</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>389</v>
+        <v>371</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>390</v>
+        <v>372</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>391</v>
+        <v>373</v>
       </c>
       <c r="I10" s="1">
         <v>1</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>392</v>
+        <v>374</v>
       </c>
       <c r="K10" s="1">
         <v>1</v>
       </c>
       <c r="L10" s="7" t="s">
-        <v>391</v>
+        <v>373</v>
       </c>
       <c r="M10">
         <v>35</v>
@@ -8208,34 +7912,34 @@
     </row>
     <row r="11" ht="33.75" customHeight="1" spans="2:13">
       <c r="B11" s="7" t="s">
-        <v>393</v>
+        <v>375</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>394</v>
+        <v>376</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>395</v>
+        <v>377</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>390</v>
+        <v>372</v>
       </c>
       <c r="G11" s="1">
         <v>0</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>396</v>
+        <v>378</v>
       </c>
       <c r="I11" s="1">
         <v>1</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>392</v>
+        <v>374</v>
       </c>
       <c r="K11" s="1">
         <v>1</v>
       </c>
       <c r="L11" s="7" t="s">
-        <v>396</v>
+        <v>378</v>
       </c>
       <c r="M11">
         <v>35</v>
@@ -8243,34 +7947,34 @@
     </row>
     <row r="12" ht="33.75" customHeight="1" spans="2:13">
       <c r="B12" s="7" t="s">
-        <v>397</v>
+        <v>379</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>398</v>
+        <v>380</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>399</v>
+        <v>381</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>390</v>
+        <v>372</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>400</v>
+        <v>382</v>
       </c>
       <c r="I12" s="1">
         <v>1</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>392</v>
+        <v>374</v>
       </c>
       <c r="K12" s="1">
         <v>1</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>400</v>
+        <v>382</v>
       </c>
       <c r="M12">
         <v>35</v>
@@ -8278,34 +7982,34 @@
     </row>
     <row r="13" ht="33.75" customHeight="1" spans="2:13">
       <c r="B13" s="7" t="s">
-        <v>401</v>
+        <v>383</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>402</v>
+        <v>384</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>403</v>
+        <v>385</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>390</v>
+        <v>372</v>
       </c>
       <c r="G13" s="1">
         <v>0</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>404</v>
+        <v>386</v>
       </c>
       <c r="I13" s="1">
         <v>1</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>392</v>
+        <v>374</v>
       </c>
       <c r="K13" s="1">
         <v>1</v>
       </c>
       <c r="L13" s="7" t="s">
-        <v>404</v>
+        <v>386</v>
       </c>
       <c r="M13">
         <v>35</v>
@@ -8313,34 +8017,34 @@
     </row>
     <row r="14" ht="33.75" customHeight="1" spans="2:13">
       <c r="B14" s="7" t="s">
-        <v>405</v>
+        <v>387</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>406</v>
+        <v>388</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>407</v>
+        <v>389</v>
       </c>
       <c r="F14" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="G14" s="1">
+        <v>0</v>
+      </c>
+      <c r="H14" s="7" t="s">
         <v>390</v>
-      </c>
-      <c r="G14" s="1">
-        <v>0</v>
-      </c>
-      <c r="H14" s="7" t="s">
-        <v>408</v>
       </c>
       <c r="I14" s="1">
         <v>1</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>392</v>
+        <v>374</v>
       </c>
       <c r="K14" s="1">
         <v>1</v>
       </c>
       <c r="L14" s="7" t="s">
-        <v>408</v>
+        <v>390</v>
       </c>
       <c r="M14">
         <v>35</v>
@@ -8348,34 +8052,34 @@
     </row>
     <row r="15" ht="33.75" customHeight="1" spans="2:13">
       <c r="B15" s="7" t="s">
-        <v>409</v>
+        <v>391</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>410</v>
+        <v>392</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>411</v>
+        <v>393</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>390</v>
+        <v>372</v>
       </c>
       <c r="G15" s="1">
         <v>0</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>412</v>
+        <v>394</v>
       </c>
       <c r="I15" s="1">
         <v>1</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>392</v>
+        <v>374</v>
       </c>
       <c r="K15" s="1">
         <v>1</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>412</v>
+        <v>394</v>
       </c>
       <c r="M15">
         <v>35</v>
@@ -8383,34 +8087,34 @@
     </row>
     <row r="16" ht="33.75" customHeight="1" spans="2:13">
       <c r="B16" s="7" t="s">
-        <v>413</v>
+        <v>395</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>414</v>
+        <v>396</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>415</v>
+        <v>397</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>390</v>
+        <v>372</v>
       </c>
       <c r="G16" s="1">
         <v>0</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>416</v>
+        <v>398</v>
       </c>
       <c r="I16" s="1">
         <v>1</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>392</v>
+        <v>374</v>
       </c>
       <c r="K16" s="1">
         <v>1</v>
       </c>
       <c r="L16" s="7" t="s">
-        <v>416</v>
+        <v>398</v>
       </c>
       <c r="M16">
         <v>35</v>
@@ -8418,16 +8122,16 @@
     </row>
     <row r="17" ht="33.75" customHeight="1" spans="2:13">
       <c r="B17" s="7" t="s">
-        <v>417</v>
+        <v>399</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>418</v>
+        <v>400</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>419</v>
+        <v>401</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>420</v>
+        <v>402</v>
       </c>
       <c r="G17" s="1">
         <v>0</v>
@@ -8436,7 +8140,7 @@
         <v>1</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>421</v>
+        <v>403</v>
       </c>
       <c r="K17" s="1">
         <v>0</v>
@@ -8447,16 +8151,16 @@
     </row>
     <row r="18" ht="16.5" customHeight="1" spans="2:13">
       <c r="B18" s="7" t="s">
-        <v>422</v>
+        <v>404</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>423</v>
+        <v>405</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>424</v>
+        <v>406</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>425</v>
+        <v>407</v>
       </c>
       <c r="G18" s="1">
         <v>0</v>
@@ -8465,7 +8169,7 @@
         <v>1</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>421</v>
+        <v>403</v>
       </c>
       <c r="K18" s="1">
         <v>0</v>
@@ -8476,16 +8180,16 @@
     </row>
     <row r="19" ht="16.5" customHeight="1" spans="2:13">
       <c r="B19" s="7" t="s">
-        <v>426</v>
+        <v>408</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>427</v>
+        <v>409</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>428</v>
+        <v>410</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>429</v>
+        <v>411</v>
       </c>
       <c r="G19" s="1">
         <v>0</v>
@@ -8494,7 +8198,7 @@
         <v>1</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>421</v>
+        <v>403</v>
       </c>
       <c r="K19" s="1">
         <v>0</v>
@@ -8505,28 +8209,28 @@
     </row>
     <row r="20" ht="16.5" customHeight="1" spans="2:13">
       <c r="B20" s="7" t="s">
-        <v>430</v>
+        <v>412</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>431</v>
+        <v>413</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>432</v>
+        <v>414</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>433</v>
+        <v>415</v>
       </c>
       <c r="G20" s="1">
         <v>0</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>434</v>
+        <v>416</v>
       </c>
       <c r="I20" s="1">
         <v>1</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>421</v>
+        <v>403</v>
       </c>
       <c r="K20" s="1">
         <v>0</v>
@@ -8557,36 +8261,36 @@
   <sheetData>
     <row r="1" customHeight="1" spans="2:9">
       <c r="B1" s="3" t="s">
-        <v>435</v>
+        <v>417</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>436</v>
+        <v>418</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>437</v>
+        <v>419</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>438</v>
+        <v>420</v>
       </c>
       <c r="H1" s="7" t="s">
         <v>1</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>439</v>
+        <v>421</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="2:9">
       <c r="B2" s="3" t="s">
-        <v>440</v>
+        <v>422</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>441</v>
+        <v>423</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>442</v>
+        <v>424</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>443</v>
+        <v>425</v>
       </c>
       <c r="H2" s="1">
         <v>1</v>
@@ -8600,10 +8304,10 @@
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
       <c r="D3" s="3" t="s">
-        <v>444</v>
+        <v>426</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>445</v>
+        <v>427</v>
       </c>
       <c r="H3" s="1">
         <v>2</v>
@@ -8617,10 +8321,10 @@
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
       <c r="D4" s="3" t="s">
-        <v>446</v>
+        <v>428</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>447</v>
+        <v>429</v>
       </c>
       <c r="H4" s="1">
         <v>3</v>
@@ -8634,10 +8338,10 @@
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
       <c r="D5" s="3" t="s">
-        <v>444</v>
+        <v>426</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>448</v>
+        <v>430</v>
       </c>
       <c r="H5" s="1">
         <v>4</v>
@@ -8651,10 +8355,10 @@
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
       <c r="D6" s="3" t="s">
-        <v>449</v>
+        <v>431</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>450</v>
+        <v>432</v>
       </c>
       <c r="H6" s="1">
         <v>5</v>
@@ -8668,10 +8372,10 @@
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
       <c r="D7" s="3" t="s">
-        <v>451</v>
+        <v>433</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>452</v>
+        <v>434</v>
       </c>
       <c r="H7" s="1">
         <v>6</v>
@@ -8685,10 +8389,10 @@
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
       <c r="D8" s="3" t="s">
-        <v>453</v>
+        <v>435</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>454</v>
+        <v>436</v>
       </c>
       <c r="H8" s="1">
         <v>7</v>
@@ -8702,10 +8406,10 @@
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
       <c r="D9" s="3" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>455</v>
+        <v>437</v>
       </c>
       <c r="H9" s="1">
         <v>8</v>
@@ -8719,10 +8423,10 @@
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
       <c r="D10" s="3" t="s">
-        <v>456</v>
+        <v>438</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="H10" s="1">
         <v>9</v>
@@ -8735,13 +8439,13 @@
     <row r="11" customHeight="1" spans="2:9">
       <c r="B11" s="4"/>
       <c r="C11" s="3" t="s">
-        <v>457</v>
+        <v>439</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>458</v>
+        <v>440</v>
       </c>
       <c r="H11" s="1">
         <v>10</v>
@@ -8755,10 +8459,10 @@
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
       <c r="D12" s="3" t="s">
-        <v>459</v>
+        <v>441</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>460</v>
+        <v>442</v>
       </c>
       <c r="H12" s="1">
         <v>11</v>
@@ -8772,10 +8476,10 @@
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
       <c r="D13" s="5" t="s">
-        <v>461</v>
+        <v>443</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>462</v>
+        <v>444</v>
       </c>
       <c r="H13" s="1">
         <v>12</v>
@@ -8789,10 +8493,10 @@
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
       <c r="D14" s="3" t="s">
-        <v>463</v>
+        <v>445</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>464</v>
+        <v>446</v>
       </c>
       <c r="H14" s="1">
         <v>13</v>
@@ -8805,13 +8509,13 @@
     <row r="15" customHeight="1" spans="2:9">
       <c r="B15" s="4"/>
       <c r="C15" s="3" t="s">
-        <v>465</v>
+        <v>447</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>466</v>
+        <v>448</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>467</v>
+        <v>449</v>
       </c>
       <c r="H15" s="1">
         <v>14</v>
@@ -8825,10 +8529,10 @@
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
       <c r="D16" s="3" t="s">
-        <v>468</v>
+        <v>450</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>469</v>
+        <v>451</v>
       </c>
       <c r="H16" s="1">
         <v>15</v>
@@ -8842,10 +8546,10 @@
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
       <c r="D17" s="3" t="s">
-        <v>470</v>
+        <v>452</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>471</v>
+        <v>453</v>
       </c>
       <c r="H17" s="1">
         <v>16</v>
@@ -8859,10 +8563,10 @@
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
       <c r="D18" s="3" t="s">
-        <v>472</v>
+        <v>454</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>473</v>
+        <v>455</v>
       </c>
       <c r="H18" s="1">
         <v>17</v>
@@ -8876,10 +8580,10 @@
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
       <c r="D19" s="3" t="s">
-        <v>474</v>
+        <v>456</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>475</v>
+        <v>457</v>
       </c>
       <c r="H19" s="1">
         <v>18</v>
@@ -8893,10 +8597,10 @@
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
       <c r="D20" s="3" t="s">
-        <v>474</v>
+        <v>456</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="H20" s="1">
         <v>19</v>
@@ -8910,10 +8614,10 @@
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
       <c r="D21" s="3" t="s">
-        <v>476</v>
+        <v>458</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>477</v>
+        <v>459</v>
       </c>
       <c r="H21" s="1">
         <v>20</v>
@@ -8926,13 +8630,13 @@
     <row r="22" customHeight="1" spans="2:9">
       <c r="B22" s="4"/>
       <c r="C22" s="3" t="s">
-        <v>478</v>
+        <v>460</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>479</v>
+        <v>461</v>
       </c>
       <c r="H22" s="1">
         <v>21</v>
@@ -8945,13 +8649,13 @@
     <row r="23" customHeight="1" spans="2:9">
       <c r="B23" s="4"/>
       <c r="C23" s="3" t="s">
-        <v>480</v>
+        <v>462</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>481</v>
+        <v>463</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>482</v>
+        <v>464</v>
       </c>
       <c r="H23" s="1">
         <v>22</v>
@@ -8965,10 +8669,10 @@
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
       <c r="D24" s="3" t="s">
-        <v>483</v>
+        <v>465</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>484</v>
+        <v>466</v>
       </c>
       <c r="H24" s="1">
         <v>23</v>
@@ -8982,10 +8686,10 @@
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
       <c r="D25" s="3" t="s">
-        <v>485</v>
+        <v>467</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>486</v>
+        <v>468</v>
       </c>
       <c r="H25" s="1">
         <v>24</v>
@@ -8999,10 +8703,10 @@
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
       <c r="D26" s="3" t="s">
-        <v>487</v>
+        <v>469</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>145</v>
+        <v>127</v>
       </c>
       <c r="H26" s="1">
         <v>25</v>
@@ -9015,13 +8719,13 @@
     <row r="27" customHeight="1" spans="2:9">
       <c r="B27" s="4"/>
       <c r="C27" s="3" t="s">
-        <v>488</v>
+        <v>470</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>489</v>
+        <v>471</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>490</v>
+        <v>472</v>
       </c>
       <c r="H27" s="1">
         <v>26</v>
@@ -9035,10 +8739,10 @@
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
       <c r="D28" s="3" t="s">
-        <v>489</v>
+        <v>471</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>491</v>
+        <v>473</v>
       </c>
       <c r="H28" s="1">
         <v>27</v>
@@ -9051,13 +8755,13 @@
     <row r="29" customHeight="1" spans="2:9">
       <c r="B29" s="4"/>
       <c r="C29" s="3" t="s">
-        <v>492</v>
+        <v>474</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>493</v>
+        <v>475</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>494</v>
+        <v>476</v>
       </c>
       <c r="H29" s="1">
         <v>28</v>
@@ -9070,13 +8774,13 @@
     <row r="30" customHeight="1" spans="2:9">
       <c r="B30" s="4"/>
       <c r="C30" s="3" t="s">
-        <v>495</v>
+        <v>477</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>496</v>
+        <v>478</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>497</v>
+        <v>479</v>
       </c>
       <c r="H30" s="1">
         <v>29</v>
@@ -9089,13 +8793,13 @@
     <row r="31" customHeight="1" spans="2:9">
       <c r="B31" s="4"/>
       <c r="C31" s="3" t="s">
-        <v>498</v>
+        <v>480</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>496</v>
+        <v>478</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>499</v>
+        <v>481</v>
       </c>
       <c r="H31" s="1">
         <v>30</v>
@@ -9108,13 +8812,13 @@
     <row r="32" customHeight="1" spans="2:9">
       <c r="B32" s="4"/>
       <c r="C32" s="3" t="s">
-        <v>500</v>
+        <v>482</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>501</v>
+        <v>483</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>502</v>
+        <v>484</v>
       </c>
       <c r="H32" s="1">
         <v>31</v>
@@ -9128,10 +8832,10 @@
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
       <c r="D33" s="3" t="s">
-        <v>501</v>
+        <v>483</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>503</v>
+        <v>485</v>
       </c>
       <c r="H33" s="1">
         <v>32</v>
@@ -9145,10 +8849,10 @@
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
       <c r="D34" s="3" t="s">
-        <v>504</v>
+        <v>486</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>505</v>
+        <v>487</v>
       </c>
       <c r="H34" s="1">
         <v>33</v>
@@ -9161,13 +8865,13 @@
     <row r="35" customHeight="1" spans="2:9">
       <c r="B35" s="4"/>
       <c r="C35" s="3" t="s">
-        <v>506</v>
+        <v>488</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>507</v>
+        <v>489</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>173</v>
+        <v>155</v>
       </c>
       <c r="H35" s="1">
         <v>34</v>
@@ -9181,10 +8885,10 @@
       <c r="B36" s="4"/>
       <c r="C36" s="3"/>
       <c r="D36" s="6" t="s">
-        <v>508</v>
+        <v>490</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>509</v>
+        <v>491</v>
       </c>
       <c r="H36" s="1">
         <v>35</v>
@@ -9197,13 +8901,13 @@
     <row r="37" customHeight="1" spans="2:9">
       <c r="B37" s="4"/>
       <c r="C37" s="3" t="s">
-        <v>510</v>
+        <v>492</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>510</v>
+        <v>492</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>511</v>
+        <v>493</v>
       </c>
       <c r="H37" s="1">
         <v>36</v>
@@ -9216,13 +8920,13 @@
     <row r="38" customHeight="1" spans="2:9">
       <c r="B38" s="4"/>
       <c r="C38" s="3" t="s">
-        <v>512</v>
+        <v>494</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>513</v>
+        <v>495</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>514</v>
+        <v>496</v>
       </c>
       <c r="H38" s="1">
         <v>37</v>
@@ -9236,10 +8940,10 @@
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
       <c r="D39" s="3" t="s">
-        <v>515</v>
+        <v>497</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>516</v>
+        <v>498</v>
       </c>
       <c r="H39" s="1">
         <v>38</v>
@@ -9253,10 +8957,10 @@
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
       <c r="D40" s="3" t="s">
-        <v>517</v>
+        <v>499</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>518</v>
+        <v>500</v>
       </c>
       <c r="H40" s="1">
         <v>39</v>
@@ -9270,10 +8974,10 @@
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
       <c r="D41" s="3" t="s">
-        <v>519</v>
+        <v>501</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>520</v>
+        <v>502</v>
       </c>
       <c r="H41" s="1">
         <v>40</v>
@@ -9287,10 +8991,10 @@
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
       <c r="D42" s="3" t="s">
-        <v>521</v>
+        <v>503</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>522</v>
+        <v>504</v>
       </c>
       <c r="H42" s="1">
         <v>41</v>
@@ -9304,10 +9008,10 @@
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
       <c r="D43" s="3" t="s">
-        <v>523</v>
+        <v>505</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>524</v>
+        <v>506</v>
       </c>
       <c r="H43" s="1">
         <v>42</v>
@@ -9320,13 +9024,13 @@
     <row r="44" customHeight="1" spans="2:9">
       <c r="B44" s="4"/>
       <c r="C44" s="3" t="s">
-        <v>525</v>
+        <v>507</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>456</v>
+        <v>438</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>526</v>
+        <v>508</v>
       </c>
       <c r="H44" s="1">
         <v>43</v>
@@ -9340,10 +9044,10 @@
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
       <c r="D45" s="3" t="s">
-        <v>527</v>
+        <v>509</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>528</v>
+        <v>510</v>
       </c>
       <c r="H45" s="1">
         <v>44</v>
@@ -9357,10 +9061,10 @@
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
       <c r="D46" s="3" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
       <c r="H46" s="1">
         <v>45</v>
@@ -9374,10 +9078,10 @@
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
       <c r="D47" s="3" t="s">
-        <v>529</v>
+        <v>511</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>530</v>
+        <v>512</v>
       </c>
       <c r="H47" s="1">
         <v>46</v>
@@ -9391,10 +9095,10 @@
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
       <c r="D48" s="3" t="s">
-        <v>531</v>
+        <v>513</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>532</v>
+        <v>514</v>
       </c>
       <c r="H48" s="1">
         <v>47</v>
@@ -9407,13 +9111,13 @@
     <row r="49" customHeight="1" spans="2:9">
       <c r="B49" s="4"/>
       <c r="C49" s="3" t="s">
-        <v>533</v>
+        <v>515</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>534</v>
+        <v>516</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>535</v>
+        <v>517</v>
       </c>
       <c r="H49" s="1">
         <v>48</v>
@@ -9427,10 +9131,10 @@
       <c r="B50" s="4"/>
       <c r="C50" s="4"/>
       <c r="D50" s="3" t="s">
-        <v>536</v>
+        <v>518</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>537</v>
+        <v>519</v>
       </c>
       <c r="H50" s="1">
         <v>49</v>
@@ -9444,10 +9148,10 @@
       <c r="B51" s="4"/>
       <c r="C51" s="4"/>
       <c r="D51" s="3" t="s">
-        <v>538</v>
+        <v>520</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>539</v>
+        <v>521</v>
       </c>
       <c r="H51" s="1">
         <v>50</v>
@@ -9460,13 +9164,13 @@
     <row r="52" customHeight="1" spans="2:9">
       <c r="B52" s="4"/>
       <c r="C52" s="3" t="s">
-        <v>540</v>
+        <v>522</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>541</v>
+        <v>523</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>542</v>
+        <v>524</v>
       </c>
       <c r="H52" s="1">
         <v>51</v>
@@ -9480,10 +9184,10 @@
       <c r="B53" s="4"/>
       <c r="C53" s="4"/>
       <c r="D53" s="3" t="s">
-        <v>457</v>
+        <v>439</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>543</v>
+        <v>525</v>
       </c>
       <c r="H53" s="1">
         <v>52</v>
@@ -9497,10 +9201,10 @@
       <c r="B54" s="4"/>
       <c r="C54" s="4"/>
       <c r="D54" s="3" t="s">
-        <v>544</v>
+        <v>526</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>545</v>
+        <v>527</v>
       </c>
       <c r="H54" s="1">
         <v>53</v>
@@ -9513,13 +9217,13 @@
     <row r="55" customHeight="1" spans="2:9">
       <c r="B55" s="4"/>
       <c r="C55" s="3" t="s">
-        <v>546</v>
+        <v>528</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>547</v>
+        <v>529</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>548</v>
+        <v>530</v>
       </c>
       <c r="H55" s="1">
         <v>54</v>
@@ -9533,10 +9237,10 @@
       <c r="B56" s="4"/>
       <c r="C56" s="4"/>
       <c r="D56" s="3" t="s">
-        <v>549</v>
+        <v>531</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>550</v>
+        <v>532</v>
       </c>
       <c r="H56" s="1">
         <v>55</v>
@@ -9550,10 +9254,10 @@
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
       <c r="D57" s="3" t="s">
-        <v>551</v>
+        <v>533</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>552</v>
+        <v>534</v>
       </c>
       <c r="H57" s="1">
         <v>56</v>
@@ -9567,10 +9271,10 @@
       <c r="B58" s="4"/>
       <c r="C58" s="4"/>
       <c r="D58" s="3" t="s">
-        <v>553</v>
+        <v>535</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>554</v>
+        <v>536</v>
       </c>
       <c r="H58" s="1">
         <v>57</v>
@@ -9584,10 +9288,10 @@
       <c r="B59" s="4"/>
       <c r="C59" s="4"/>
       <c r="D59" s="3" t="s">
-        <v>555</v>
+        <v>537</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>556</v>
+        <v>538</v>
       </c>
       <c r="H59" s="1">
         <v>58</v>
@@ -9601,10 +9305,10 @@
       <c r="B60" s="4"/>
       <c r="C60" s="4"/>
       <c r="D60" s="3" t="s">
-        <v>246</v>
+        <v>228</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>557</v>
+        <v>539</v>
       </c>
       <c r="H60" s="1">
         <v>59</v>
@@ -9617,13 +9321,13 @@
     <row r="61" customHeight="1" spans="2:9">
       <c r="B61" s="4"/>
       <c r="C61" s="3" t="s">
-        <v>558</v>
+        <v>540</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>559</v>
+        <v>541</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>560</v>
+        <v>542</v>
       </c>
       <c r="H61" s="1">
         <v>60</v>
@@ -9637,10 +9341,10 @@
       <c r="B62" s="4"/>
       <c r="C62" s="4"/>
       <c r="D62" s="3" t="s">
-        <v>252</v>
+        <v>234</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>561</v>
+        <v>543</v>
       </c>
       <c r="H62" s="1">
         <v>61</v>
@@ -9653,13 +9357,13 @@
     <row r="63" customHeight="1" spans="2:9">
       <c r="B63" s="4"/>
       <c r="C63" s="3" t="s">
-        <v>562</v>
+        <v>544</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>563</v>
+        <v>545</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>564</v>
+        <v>546</v>
       </c>
       <c r="H63" s="1">
         <v>62</v>
@@ -9673,10 +9377,10 @@
       <c r="B64" s="4"/>
       <c r="C64" s="4"/>
       <c r="D64" s="3" t="s">
-        <v>563</v>
+        <v>545</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>565</v>
+        <v>547</v>
       </c>
       <c r="H64" s="1">
         <v>63</v>
@@ -9690,10 +9394,10 @@
       <c r="B65" s="4"/>
       <c r="C65" s="4"/>
       <c r="D65" s="3" t="s">
-        <v>566</v>
+        <v>548</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>567</v>
+        <v>549</v>
       </c>
       <c r="H65" s="1">
         <v>64</v>
@@ -9707,10 +9411,10 @@
       <c r="B66" s="4"/>
       <c r="C66" s="4"/>
       <c r="D66" s="3" t="s">
-        <v>568</v>
+        <v>550</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>569</v>
+        <v>551</v>
       </c>
       <c r="H66" s="1">
         <v>65</v>
@@ -9724,10 +9428,10 @@
       <c r="B67" s="4"/>
       <c r="C67" s="4"/>
       <c r="D67" s="3" t="s">
-        <v>570</v>
+        <v>552</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>571</v>
+        <v>553</v>
       </c>
       <c r="H67" s="1">
         <v>66</v>
@@ -9740,13 +9444,13 @@
     <row r="68" customHeight="1" spans="2:9">
       <c r="B68" s="4"/>
       <c r="C68" s="3" t="s">
-        <v>572</v>
+        <v>554</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>573</v>
+        <v>555</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>268</v>
+        <v>250</v>
       </c>
       <c r="H68" s="1">
         <v>67</v>
@@ -9759,13 +9463,13 @@
     <row r="69" customHeight="1" spans="2:9">
       <c r="B69" s="4"/>
       <c r="C69" s="3" t="s">
-        <v>574</v>
+        <v>556</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>575</v>
+        <v>557</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>576</v>
+        <v>558</v>
       </c>
       <c r="H69" s="1">
         <v>68</v>
@@ -9779,10 +9483,10 @@
       <c r="B70" s="4"/>
       <c r="C70" s="4"/>
       <c r="D70" s="3" t="s">
-        <v>577</v>
+        <v>559</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>578</v>
+        <v>560</v>
       </c>
       <c r="H70" s="1">
         <v>69</v>
@@ -9796,10 +9500,10 @@
       <c r="B71" s="4"/>
       <c r="C71" s="4"/>
       <c r="D71" s="3" t="s">
-        <v>579</v>
+        <v>561</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>580</v>
+        <v>562</v>
       </c>
       <c r="H71" s="1">
         <v>70</v>
@@ -9813,10 +9517,10 @@
       <c r="B72" s="4"/>
       <c r="C72" s="4"/>
       <c r="D72" s="3" t="s">
-        <v>581</v>
+        <v>563</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>582</v>
+        <v>564</v>
       </c>
       <c r="H72" s="1">
         <v>71</v>
@@ -9830,10 +9534,10 @@
       <c r="B73" s="4"/>
       <c r="C73" s="4"/>
       <c r="D73" s="3" t="s">
-        <v>284</v>
+        <v>266</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>583</v>
+        <v>565</v>
       </c>
       <c r="H73" s="1">
         <v>72</v>
@@ -9846,13 +9550,13 @@
     <row r="74" customHeight="1" spans="2:9">
       <c r="B74" s="4"/>
       <c r="C74" s="3" t="s">
-        <v>584</v>
+        <v>566</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>585</v>
+        <v>567</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>288</v>
+        <v>270</v>
       </c>
       <c r="H74" s="1">
         <v>73</v>
@@ -9866,10 +9570,10 @@
       <c r="B75" s="4"/>
       <c r="C75" s="3"/>
       <c r="D75" s="3" t="s">
-        <v>586</v>
+        <v>568</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>587</v>
+        <v>569</v>
       </c>
       <c r="H75" s="1">
         <v>74</v>
@@ -9881,16 +9585,16 @@
     </row>
     <row r="76" customHeight="1" spans="2:9">
       <c r="B76" s="3" t="s">
-        <v>588</v>
+        <v>570</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>512</v>
+        <v>494</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>589</v>
+        <v>571</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>590</v>
+        <v>572</v>
       </c>
       <c r="H76" s="1">
         <v>75</v>
@@ -9904,10 +9608,10 @@
       <c r="B77" s="4"/>
       <c r="C77" s="4"/>
       <c r="D77" s="3" t="s">
-        <v>591</v>
+        <v>573</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>592</v>
+        <v>574</v>
       </c>
       <c r="H77" s="1">
         <v>76</v>
@@ -9921,10 +9625,10 @@
       <c r="B78" s="4"/>
       <c r="C78" s="4"/>
       <c r="D78" s="3" t="s">
-        <v>593</v>
+        <v>575</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>301</v>
+        <v>283</v>
       </c>
       <c r="H78" s="1">
         <v>77</v>
@@ -9938,10 +9642,10 @@
       <c r="B79" s="4"/>
       <c r="C79" s="4"/>
       <c r="D79" s="3" t="s">
-        <v>594</v>
+        <v>576</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>304</v>
+        <v>286</v>
       </c>
       <c r="H79" s="1">
         <v>78</v>
@@ -9955,10 +9659,10 @@
       <c r="B80" s="4"/>
       <c r="C80" s="4"/>
       <c r="D80" s="3" t="s">
-        <v>595</v>
+        <v>577</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>596</v>
+        <v>578</v>
       </c>
       <c r="H80" s="1">
         <v>79</v>
@@ -9972,10 +9676,10 @@
       <c r="B81" s="4"/>
       <c r="C81" s="4"/>
       <c r="D81" s="3" t="s">
-        <v>597</v>
+        <v>579</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>598</v>
+        <v>580</v>
       </c>
       <c r="H81" s="1">
         <v>80</v>
@@ -9989,10 +9693,10 @@
       <c r="B82" s="4"/>
       <c r="C82" s="4"/>
       <c r="D82" s="3" t="s">
-        <v>599</v>
+        <v>581</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>600</v>
+        <v>582</v>
       </c>
       <c r="H82" s="1">
         <v>81</v>
@@ -10006,10 +9710,10 @@
       <c r="B83" s="4"/>
       <c r="C83" s="4"/>
       <c r="D83" s="3" t="s">
-        <v>601</v>
+        <v>583</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>602</v>
+        <v>584</v>
       </c>
       <c r="H83" s="1">
         <v>82</v>
@@ -10023,10 +9727,10 @@
       <c r="B84" s="4"/>
       <c r="C84" s="4"/>
       <c r="D84" s="3" t="s">
-        <v>603</v>
+        <v>585</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>604</v>
+        <v>586</v>
       </c>
       <c r="H84" s="1">
         <v>83</v>
@@ -10038,16 +9742,16 @@
     </row>
     <row r="85" customHeight="1" spans="2:9">
       <c r="B85" s="3" t="s">
-        <v>605</v>
+        <v>587</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>606</v>
+        <v>588</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>607</v>
+        <v>589</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>608</v>
+        <v>590</v>
       </c>
       <c r="H85" s="1">
         <v>84</v>
@@ -10060,13 +9764,13 @@
     <row r="86" customHeight="1" spans="2:9">
       <c r="B86" s="4"/>
       <c r="C86" s="3" t="s">
-        <v>609</v>
+        <v>591</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>610</v>
+        <v>592</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>611</v>
+        <v>593</v>
       </c>
       <c r="H86" s="1">
         <v>85</v>
@@ -10080,10 +9784,10 @@
       <c r="B87" s="4"/>
       <c r="C87" s="4"/>
       <c r="D87" s="3" t="s">
-        <v>610</v>
+        <v>592</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>612</v>
+        <v>594</v>
       </c>
       <c r="H87" s="1">
         <v>86</v>
@@ -10097,10 +9801,10 @@
       <c r="B88" s="4"/>
       <c r="C88" s="4"/>
       <c r="D88" s="3" t="s">
-        <v>613</v>
+        <v>595</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>614</v>
+        <v>596</v>
       </c>
       <c r="H88" s="1">
         <v>87</v>
@@ -10114,10 +9818,10 @@
       <c r="B89" s="4"/>
       <c r="C89" s="4"/>
       <c r="D89" s="3" t="s">
-        <v>615</v>
+        <v>597</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>616</v>
+        <v>598</v>
       </c>
       <c r="H89" s="1">
         <v>88</v>
@@ -10129,13 +9833,13 @@
     </row>
     <row r="90" customHeight="1" spans="3:9">
       <c r="C90" s="3" t="s">
-        <v>617</v>
+        <v>599</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>618</v>
+        <v>600</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>619</v>
+        <v>601</v>
       </c>
       <c r="H90" s="1">
         <v>89</v>
@@ -10149,10 +9853,10 @@
       <c r="B91" s="4"/>
       <c r="C91" s="4"/>
       <c r="D91" s="3" t="s">
-        <v>620</v>
+        <v>602</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>621</v>
+        <v>603</v>
       </c>
       <c r="H91" s="1">
         <v>90</v>
@@ -10166,10 +9870,10 @@
       <c r="B92" s="4"/>
       <c r="C92" s="4"/>
       <c r="D92" s="3" t="s">
-        <v>622</v>
+        <v>604</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>623</v>
+        <v>605</v>
       </c>
       <c r="H92" s="1">
         <v>91</v>
@@ -10183,10 +9887,10 @@
       <c r="B93" s="4"/>
       <c r="C93" s="4"/>
       <c r="D93" s="3" t="s">
-        <v>624</v>
+        <v>606</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>625</v>
+        <v>607</v>
       </c>
       <c r="H93" s="1">
         <v>92</v>
@@ -10200,10 +9904,10 @@
       <c r="B94" s="4"/>
       <c r="C94" s="4"/>
       <c r="D94" s="3" t="s">
-        <v>626</v>
+        <v>608</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>353</v>
+        <v>335</v>
       </c>
       <c r="H94" s="1">
         <v>93</v>

--- a/GourmetProject/GameConfig/Datas/item.xlsx
+++ b/GourmetProject/GameConfig/Datas/item.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15300"/>
+    <workbookView windowHeight="15200"/>
   </bookViews>
   <sheets>
     <sheet name="被动道具" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="975" uniqueCount="609">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="963" uniqueCount="603">
   <si>
     <t>##var</t>
   </si>
@@ -413,7 +413,8 @@
     <t>精致料理</t>
   </si>
   <si>
-    <t>结算时食物数量&lt;=10
+    <t>结算开始
+若食物数量&lt;=10
 所有美食倍率×1.2</t>
   </si>
   <si>
@@ -426,21 +427,12 @@
     <t>丰盛大餐</t>
   </si>
   <si>
-    <t>结算时食物数量&gt;=10
+    <t>结算开始
+若食物数量&gt;=10
 所有美食倍率×1.2</t>
   </si>
   <si>
     <t>gte:10</t>
-  </si>
-  <si>
-    <t>item_per_dish_mult</t>
-  </si>
-  <si>
-    <t>流水席</t>
-  </si>
-  <si>
-    <t>结算时每结算1个食物
-所有食物倍率+0.2</t>
   </si>
   <si>
     <t>item_perma_flat_all</t>
@@ -484,7 +476,7 @@
     <t>免费调整</t>
   </si>
   <si>
-    <t>每局第1次上菜后
+    <t>每局第1次上菜时
 可不消耗修正次数移动</t>
   </si>
   <si>
@@ -503,18 +495,9 @@
     <t>节俭加成</t>
   </si>
   <si>
-    <t>每1个未使用的调整次数
+    <t>结算开始
+每个未使用的调整次数
 使所有食物倍率+0.1</t>
-  </si>
-  <si>
-    <t>item_food_convert</t>
-  </si>
-  <si>
-    <t>点石成金</t>
-  </si>
-  <si>
-    <t>将5个随机食物
-变为至少同品质的食物</t>
   </si>
   <si>
     <t>item_adjust_to_gold</t>
@@ -3118,7 +3101,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AA88"/>
+  <dimension ref="A1:AA86"/>
   <sheetFormatPr defaultColWidth="9.00735294117647" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="13.0808823529412" style="1" customWidth="1"/>
@@ -3141,64 +3124,64 @@
     <col min="20" max="20" width="11.7720588235294" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" customHeight="1" spans="1:18">
-      <c r="A1" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="7" t="s">
+    <row r="1" customFormat="1" ht="16.5" customHeight="1" spans="1:18">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="7" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="7" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="7" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="9" t="s">
+      <c r="Q1" t="s">
         <v>16</v>
       </c>
       <c r="R1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2" ht="16.5" customHeight="1" spans="1:18">
-      <c r="A2" s="7" t="s">
+    <row r="2" customFormat="1" ht="16.5" customHeight="1" spans="1:18">
+      <c r="A2" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -3253,64 +3236,65 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" ht="16.5" customHeight="1" spans="1:18">
-      <c r="A3" s="7" t="s">
+    <row r="3" customFormat="1" ht="16.5" customHeight="1" spans="1:18">
+      <c r="A3" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="I3" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J3" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="K3" s="7" t="s">
+      <c r="K3" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="L3" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="M3" s="7" t="s">
+      <c r="M3" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="N3" s="7" t="s">
+      <c r="N3" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="O3" s="7" t="s">
+      <c r="O3" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="P3" s="7" t="s">
+      <c r="P3" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="Q3" s="9" t="s">
+      <c r="Q3" t="s">
         <v>37</v>
       </c>
       <c r="R3" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="4" ht="16.5" customHeight="1" spans="2:18">
-      <c r="B4" s="7" t="s">
+    <row r="4" customFormat="1" ht="16.5" customHeight="1" spans="1:18">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1" t="s">
         <v>43</v>
       </c>
       <c r="C4" s="1" t="s">
@@ -3319,13 +3303,14 @@
       <c r="D4" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="G4" s="1"/>
+      <c r="H4" s="1" t="s">
         <v>48</v>
       </c>
       <c r="I4" s="1">
@@ -3352,12 +3337,14 @@
       <c r="P4" s="1">
         <v>0</v>
       </c>
+      <c r="Q4"/>
       <c r="R4">
         <v>45</v>
       </c>
     </row>
-    <row r="5" ht="16.5" customHeight="1" spans="2:18">
-      <c r="B5" s="7" t="s">
+    <row r="5" customFormat="1" ht="16.5" customHeight="1" spans="1:18">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1" t="s">
         <v>50</v>
       </c>
       <c r="C5" s="1" t="s">
@@ -3366,12 +3353,13 @@
       <c r="D5" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="1" t="s">
         <v>47</v>
       </c>
+      <c r="G5" s="1"/>
       <c r="H5" s="10" t="s">
         <v>54</v>
       </c>
@@ -3399,12 +3387,13 @@
       <c r="P5" s="1">
         <v>0</v>
       </c>
+      <c r="Q5"/>
       <c r="R5">
         <v>45</v>
       </c>
     </row>
     <row r="6" ht="16.5" customHeight="1" spans="2:27">
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="1" t="s">
         <v>56</v>
       </c>
       <c r="C6" s="1" t="s">
@@ -3413,15 +3402,16 @@
       <c r="D6" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G6" s="1">
         <v>1</v>
       </c>
+      <c r="H6" s="1"/>
       <c r="I6" s="1">
         <v>300</v>
       </c>
@@ -3449,7 +3439,7 @@
       <c r="R6">
         <v>45</v>
       </c>
-      <c r="S6" s="7" t="s">
+      <c r="S6" s="1" t="s">
         <v>59</v>
       </c>
       <c r="T6" s="1">
@@ -3478,7 +3468,7 @@
       </c>
     </row>
     <row r="7" ht="16.5" customHeight="1" spans="2:27">
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="1" t="s">
         <v>60</v>
       </c>
       <c r="C7" s="1" t="s">
@@ -3487,16 +3477,16 @@
       <c r="D7" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G7" s="1">
         <v>50</v>
       </c>
-      <c r="H7" s="7" t="s">
+      <c r="H7" s="1" t="s">
         <v>64</v>
       </c>
       <c r="I7" s="1">
@@ -3526,7 +3516,7 @@
       <c r="R7">
         <v>45</v>
       </c>
-      <c r="S7" s="7" t="s">
+      <c r="S7" s="1" t="s">
         <v>66</v>
       </c>
       <c r="T7" s="1">
@@ -3555,7 +3545,7 @@
       </c>
     </row>
     <row r="8" ht="16.5" customHeight="1" spans="2:27">
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="1" t="s">
         <v>67</v>
       </c>
       <c r="C8" s="1" t="s">
@@ -3564,15 +3554,16 @@
       <c r="D8" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
       </c>
+      <c r="H8" s="1"/>
       <c r="I8" s="1">
         <v>30</v>
       </c>
@@ -3600,7 +3591,7 @@
       <c r="R8">
         <v>45</v>
       </c>
-      <c r="S8" s="7" t="s">
+      <c r="S8" s="1" t="s">
         <v>70</v>
       </c>
       <c r="T8" s="1">
@@ -3629,7 +3620,7 @@
       </c>
     </row>
     <row r="9" ht="16.5" customHeight="1" spans="2:26">
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="1" t="s">
         <v>71</v>
       </c>
       <c r="C9" s="1" t="s">
@@ -3638,16 +3629,16 @@
       <c r="D9" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
       </c>
-      <c r="H9" s="7" t="s">
+      <c r="H9" s="1" t="s">
         <v>74</v>
       </c>
       <c r="I9" s="1">
@@ -3682,7 +3673,7 @@
       </c>
     </row>
     <row r="10" ht="33.75" customHeight="1" spans="2:26">
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="1" t="s">
         <v>76</v>
       </c>
       <c r="C10" s="1" t="s">
@@ -3691,16 +3682,16 @@
       <c r="D10" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G10" s="1">
         <v>20</v>
       </c>
-      <c r="H10" s="7" t="s">
+      <c r="H10" s="1" t="s">
         <v>79</v>
       </c>
       <c r="I10" s="1">
@@ -3730,39 +3721,40 @@
       <c r="R10">
         <v>45</v>
       </c>
-      <c r="T10" s="9" t="s">
+      <c r="T10" t="s">
         <v>80</v>
       </c>
       <c r="V10">
         <v>300</v>
       </c>
-      <c r="X10" s="9" t="s">
+      <c r="X10" t="s">
         <v>55</v>
       </c>
       <c r="Z10">
-        <f>COUNTIF($E$4:$E$88,T10)</f>
+        <f>COUNTIF($E$4:$E$86,T10)</f>
         <v>24</v>
       </c>
     </row>
     <row r="11" ht="33.75" customHeight="1" spans="2:26">
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G11" s="1">
         <v>100</v>
       </c>
+      <c r="H11" s="1"/>
       <c r="I11" s="1">
         <v>300</v>
       </c>
@@ -3790,22 +3782,22 @@
       <c r="R11">
         <v>45</v>
       </c>
-      <c r="T11" s="9" t="s">
+      <c r="T11" t="s">
         <v>84</v>
       </c>
       <c r="V11">
         <v>100</v>
       </c>
-      <c r="X11" s="9" t="s">
+      <c r="X11" t="s">
         <v>49</v>
       </c>
       <c r="Z11">
-        <f>COUNTIF($E$4:$E$88,T11)</f>
-        <v>41</v>
+        <f>COUNTIF($E$4:$E$86,T11)</f>
+        <v>40</v>
       </c>
     </row>
     <row r="12" ht="33.75" customHeight="1" spans="2:26">
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="1" t="s">
         <v>85</v>
       </c>
       <c r="C12" s="1" t="s">
@@ -3814,15 +3806,16 @@
       <c r="D12" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="E12" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G12" s="1">
         <v>0.2</v>
       </c>
+      <c r="H12" s="1"/>
       <c r="I12" s="1">
         <v>100</v>
       </c>
@@ -3850,22 +3843,22 @@
       <c r="R12">
         <v>45</v>
       </c>
-      <c r="T12" s="9" t="s">
+      <c r="T12" t="s">
         <v>88</v>
       </c>
       <c r="V12">
         <v>30</v>
       </c>
-      <c r="X12" s="9" t="s">
+      <c r="X12" t="s">
         <v>65</v>
       </c>
       <c r="Z12">
-        <f>COUNTIF($E$4:$E$88,T12)</f>
-        <v>14</v>
+        <f>COUNTIF($E$4:$E$86,T12)</f>
+        <v>13</v>
       </c>
     </row>
     <row r="13" ht="16.5" customHeight="1" spans="2:26">
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="1" t="s">
         <v>89</v>
       </c>
       <c r="C13" s="1" t="s">
@@ -3874,15 +3867,16 @@
       <c r="D13" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E13" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="F13" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G13" s="1">
         <v>0.15</v>
       </c>
+      <c r="H13" s="1"/>
       <c r="I13" s="1">
         <v>100</v>
       </c>
@@ -3910,22 +3904,23 @@
       <c r="R13">
         <v>45</v>
       </c>
-      <c r="T13" s="9" t="s">
+      <c r="T13" t="s">
         <v>92</v>
       </c>
       <c r="V13">
         <v>10</v>
       </c>
-      <c r="X13" s="9" t="s">
+      <c r="X13" t="s">
         <v>93</v>
       </c>
       <c r="Z13">
-        <f>COUNTIF($E$4:$E$88,T13)</f>
+        <f>COUNTIF($E$4:$E$86,T13)</f>
         <v>6</v>
       </c>
     </row>
-    <row r="14" ht="16.5" customHeight="1" spans="2:18">
-      <c r="B14" s="7" t="s">
+    <row r="14" customFormat="1" ht="16.5" customHeight="1" spans="1:18">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1" t="s">
         <v>94</v>
       </c>
       <c r="C14" s="1" t="s">
@@ -3934,15 +3929,16 @@
       <c r="D14" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="E14" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="F14" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G14" s="1">
         <v>0.2</v>
       </c>
+      <c r="H14" s="1"/>
       <c r="I14" s="1">
         <v>300</v>
       </c>
@@ -3967,12 +3963,14 @@
       <c r="P14" s="1">
         <v>0</v>
       </c>
+      <c r="Q14"/>
       <c r="R14">
         <v>45</v>
       </c>
     </row>
-    <row r="15" ht="16.5" customHeight="1" spans="2:18">
-      <c r="B15" s="7" t="s">
+    <row r="15" customFormat="1" ht="16.5" customHeight="1" spans="1:18">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1" t="s">
         <v>97</v>
       </c>
       <c r="C15" s="1" t="s">
@@ -3981,15 +3979,16 @@
       <c r="D15" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="E15" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F15" s="7" t="s">
+      <c r="F15" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G15" s="1">
         <v>0.15</v>
       </c>
+      <c r="H15" s="1"/>
       <c r="I15" s="1">
         <v>100</v>
       </c>
@@ -4014,12 +4013,14 @@
       <c r="P15" s="1">
         <v>0</v>
       </c>
+      <c r="Q15"/>
       <c r="R15">
         <v>45</v>
       </c>
     </row>
-    <row r="16" ht="16.5" customHeight="1" spans="2:18">
-      <c r="B16" s="7" t="s">
+    <row r="16" customFormat="1" ht="16.5" customHeight="1" spans="1:18">
+      <c r="A16" s="1"/>
+      <c r="B16" s="1" t="s">
         <v>100</v>
       </c>
       <c r="C16" s="1" t="s">
@@ -4028,15 +4029,16 @@
       <c r="D16" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="E16" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F16" s="7" t="s">
+      <c r="F16" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G16" s="1">
         <v>0.15</v>
       </c>
+      <c r="H16" s="1"/>
       <c r="I16" s="1">
         <v>100</v>
       </c>
@@ -4061,12 +4063,14 @@
       <c r="P16" s="1">
         <v>0</v>
       </c>
+      <c r="Q16"/>
       <c r="R16">
         <v>45</v>
       </c>
     </row>
-    <row r="17" ht="16.5" customHeight="1" spans="2:18">
-      <c r="B17" s="7" t="s">
+    <row r="17" customFormat="1" ht="16.5" customHeight="1" spans="1:18">
+      <c r="A17" s="1"/>
+      <c r="B17" s="1" t="s">
         <v>103</v>
       </c>
       <c r="C17" s="1" t="s">
@@ -4075,15 +4079,16 @@
       <c r="D17" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="E17" s="7" t="s">
+      <c r="E17" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="F17" s="7" t="s">
+      <c r="F17" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G17" s="1">
         <v>0.3</v>
       </c>
+      <c r="H17" s="1"/>
       <c r="I17" s="1">
         <v>300</v>
       </c>
@@ -4108,12 +4113,14 @@
       <c r="P17" s="1">
         <v>0</v>
       </c>
+      <c r="Q17"/>
       <c r="R17">
         <v>45</v>
       </c>
     </row>
-    <row r="18" ht="16.5" customHeight="1" spans="2:18">
-      <c r="B18" s="7" t="s">
+    <row r="18" customFormat="1" ht="16.5" customHeight="1" spans="1:18">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1" t="s">
         <v>106</v>
       </c>
       <c r="C18" s="1" t="s">
@@ -4122,15 +4129,16 @@
       <c r="D18" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="E18" s="7" t="s">
+      <c r="E18" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="F18" s="7" t="s">
+      <c r="F18" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G18" s="1">
         <v>30</v>
       </c>
+      <c r="H18" s="1"/>
       <c r="I18" s="1">
         <v>30</v>
       </c>
@@ -4155,12 +4163,14 @@
       <c r="P18" s="1">
         <v>0</v>
       </c>
+      <c r="Q18"/>
       <c r="R18">
         <v>45</v>
       </c>
     </row>
-    <row r="19" ht="16.5" customHeight="1" spans="2:18">
-      <c r="B19" s="7" t="s">
+    <row r="19" customFormat="1" ht="16.5" customHeight="1" spans="1:18">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1" t="s">
         <v>109</v>
       </c>
       <c r="C19" s="1" t="s">
@@ -4169,15 +4179,16 @@
       <c r="D19" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="E19" s="7" t="s">
+      <c r="E19" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="F19" s="7" t="s">
+      <c r="F19" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G19" s="1">
         <v>0.2</v>
       </c>
+      <c r="H19" s="1"/>
       <c r="I19" s="1">
         <v>300</v>
       </c>
@@ -4202,12 +4213,14 @@
       <c r="P19" s="1">
         <v>0</v>
       </c>
+      <c r="Q19"/>
       <c r="R19">
         <v>45</v>
       </c>
     </row>
-    <row r="20" ht="33.75" customHeight="1" spans="2:18">
-      <c r="B20" s="7" t="s">
+    <row r="20" customFormat="1" ht="33.75" customHeight="1" spans="1:18">
+      <c r="A20" s="1"/>
+      <c r="B20" s="1" t="s">
         <v>112</v>
       </c>
       <c r="C20" s="1" t="s">
@@ -4216,15 +4229,16 @@
       <c r="D20" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="E20" s="7" t="s">
+      <c r="E20" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="F20" s="7" t="s">
+      <c r="F20" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G20" s="1">
         <v>0</v>
       </c>
+      <c r="H20" s="1"/>
       <c r="I20" s="1">
         <v>30</v>
       </c>
@@ -4249,12 +4263,14 @@
       <c r="P20" s="1">
         <v>0</v>
       </c>
+      <c r="Q20"/>
       <c r="R20">
         <v>45</v>
       </c>
     </row>
-    <row r="21" ht="33.75" customHeight="1" spans="2:18">
-      <c r="B21" s="7" t="s">
+    <row r="21" customFormat="1" ht="33.75" customHeight="1" spans="1:18">
+      <c r="A21" s="1"/>
+      <c r="B21" s="1" t="s">
         <v>115</v>
       </c>
       <c r="C21" s="1" t="s">
@@ -4263,16 +4279,16 @@
       <c r="D21" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="E21" s="7" t="s">
+      <c r="E21" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="F21" s="7" t="s">
+      <c r="F21" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G21" s="1">
         <v>0</v>
       </c>
-      <c r="H21" s="7" t="s">
+      <c r="H21" s="1" t="s">
         <v>118</v>
       </c>
       <c r="I21" s="1">
@@ -4299,12 +4315,14 @@
       <c r="P21" s="1">
         <v>0</v>
       </c>
+      <c r="Q21"/>
       <c r="R21">
         <v>45</v>
       </c>
     </row>
-    <row r="22" ht="16.5" customHeight="1" spans="2:18">
-      <c r="B22" s="7" t="s">
+    <row r="22" customFormat="1" ht="16.5" customHeight="1" spans="1:18">
+      <c r="A22" s="1"/>
+      <c r="B22" s="1" t="s">
         <v>119</v>
       </c>
       <c r="C22" s="1" t="s">
@@ -4313,15 +4331,16 @@
       <c r="D22" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="E22" s="7" t="s">
+      <c r="E22" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="F22" s="7" t="s">
+      <c r="F22" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G22" s="1">
         <v>-0.1</v>
       </c>
+      <c r="H22" s="1"/>
       <c r="I22" s="1">
         <v>300</v>
       </c>
@@ -4346,12 +4365,14 @@
       <c r="P22" s="1">
         <v>0</v>
       </c>
+      <c r="Q22"/>
       <c r="R22">
         <v>45</v>
       </c>
     </row>
-    <row r="23" ht="16.5" customHeight="1" spans="2:18">
-      <c r="B23" s="7" t="s">
+    <row r="23" customFormat="1" ht="16.5" customHeight="1" spans="1:18">
+      <c r="A23" s="1"/>
+      <c r="B23" s="1" t="s">
         <v>122</v>
       </c>
       <c r="C23" s="1" t="s">
@@ -4360,15 +4381,16 @@
       <c r="D23" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="E23" s="7" t="s">
+      <c r="E23" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F23" s="7" t="s">
+      <c r="F23" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G23" s="1">
         <v>-0.1</v>
       </c>
+      <c r="H23" s="1"/>
       <c r="I23" s="1">
         <v>100</v>
       </c>
@@ -4393,12 +4415,14 @@
       <c r="P23" s="1">
         <v>0</v>
       </c>
+      <c r="Q23"/>
       <c r="R23">
         <v>45</v>
       </c>
     </row>
-    <row r="24" ht="16.5" customHeight="1" spans="2:18">
-      <c r="B24" s="7" t="s">
+    <row r="24" customFormat="1" ht="16.5" customHeight="1" spans="1:18">
+      <c r="A24" s="1"/>
+      <c r="B24" s="1" t="s">
         <v>125</v>
       </c>
       <c r="C24" s="1" t="s">
@@ -4407,15 +4431,16 @@
       <c r="D24" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="E24" s="7" t="s">
+      <c r="E24" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="F24" s="7" t="s">
+      <c r="F24" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G24" s="1">
         <v>-0.1</v>
       </c>
+      <c r="H24" s="1"/>
       <c r="I24" s="1">
         <v>30</v>
       </c>
@@ -4440,12 +4465,14 @@
       <c r="P24" s="1">
         <v>0</v>
       </c>
+      <c r="Q24"/>
       <c r="R24">
         <v>45</v>
       </c>
     </row>
-    <row r="25" ht="33.75" customHeight="1" spans="2:18">
-      <c r="B25" s="7" t="s">
+    <row r="25" customFormat="1" ht="51" spans="1:18">
+      <c r="A25" s="1"/>
+      <c r="B25" s="1" t="s">
         <v>128</v>
       </c>
       <c r="C25" s="1" t="s">
@@ -4454,16 +4481,16 @@
       <c r="D25" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="E25" s="7" t="s">
+      <c r="E25" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F25" s="7" t="s">
+      <c r="F25" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G25" s="1">
         <v>1.1</v>
       </c>
-      <c r="H25" s="7" t="s">
+      <c r="H25" s="1" t="s">
         <v>131</v>
       </c>
       <c r="I25" s="1">
@@ -4490,12 +4517,14 @@
       <c r="P25" s="1">
         <v>0</v>
       </c>
+      <c r="Q25"/>
       <c r="R25">
         <v>45</v>
       </c>
     </row>
-    <row r="26" ht="33.75" customHeight="1" spans="2:18">
-      <c r="B26" s="7" t="s">
+    <row r="26" customFormat="1" ht="51" spans="1:18">
+      <c r="A26" s="1"/>
+      <c r="B26" s="1" t="s">
         <v>132</v>
       </c>
       <c r="C26" s="1" t="s">
@@ -4504,16 +4533,16 @@
       <c r="D26" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="E26" s="7" t="s">
+      <c r="E26" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="F26" s="7" t="s">
+      <c r="F26" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G26" s="1">
         <v>1.1</v>
       </c>
-      <c r="H26" s="7" t="s">
+      <c r="H26" s="1" t="s">
         <v>135</v>
       </c>
       <c r="I26" s="1">
@@ -4540,29 +4569,32 @@
       <c r="P26" s="1">
         <v>0</v>
       </c>
+      <c r="Q26"/>
       <c r="R26">
         <v>45</v>
       </c>
     </row>
-    <row r="27" ht="33.75" customHeight="1" spans="2:18">
-      <c r="B27" s="7" t="s">
+    <row r="27" customFormat="1" ht="16.5" customHeight="1" spans="1:18">
+      <c r="A27" s="1"/>
+      <c r="B27" s="1" t="s">
         <v>136</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="D27" s="8" t="s">
+      <c r="D27" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="E27" s="7" t="s">
+      <c r="E27" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F27" s="7" t="s">
+      <c r="F27" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G27" s="1">
-        <v>0.1</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="H27" s="1"/>
       <c r="I27" s="1">
         <v>100</v>
       </c>
@@ -4587,28 +4619,33 @@
       <c r="P27" s="1">
         <v>0</v>
       </c>
+      <c r="Q27"/>
       <c r="R27">
         <v>45</v>
       </c>
     </row>
-    <row r="28" ht="16.5" customHeight="1" spans="2:18">
-      <c r="B28" s="7" t="s">
+    <row r="28" customFormat="1" ht="33.75" customHeight="1" spans="1:18">
+      <c r="A28" s="1"/>
+      <c r="B28" s="1" t="s">
         <v>139</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="D28" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="E28" s="7" t="s">
+      <c r="E28" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F28" s="7" t="s">
+      <c r="F28" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G28" s="1">
-        <v>10</v>
+        <v>0</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>142</v>
       </c>
       <c r="I28" s="1">
         <v>100</v>
@@ -4634,31 +4671,33 @@
       <c r="P28" s="1">
         <v>0</v>
       </c>
+      <c r="Q28"/>
       <c r="R28">
         <v>45</v>
       </c>
     </row>
-    <row r="29" ht="33.75" customHeight="1" spans="2:18">
-      <c r="B29" s="7" t="s">
-        <v>142</v>
+    <row r="29" customFormat="1" ht="33.75" customHeight="1" spans="1:18">
+      <c r="A29" s="1"/>
+      <c r="B29" s="1" t="s">
+        <v>143</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="E29" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="E29" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F29" s="7" t="s">
+      <c r="F29" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G29" s="1">
         <v>0</v>
       </c>
-      <c r="H29" s="7" t="s">
-        <v>145</v>
+      <c r="H29" s="1" t="s">
+        <v>146</v>
       </c>
       <c r="I29" s="1">
         <v>100</v>
@@ -4684,32 +4723,32 @@
       <c r="P29" s="1">
         <v>0</v>
       </c>
+      <c r="Q29"/>
       <c r="R29">
         <v>45</v>
       </c>
     </row>
-    <row r="30" ht="33.75" customHeight="1" spans="2:18">
-      <c r="B30" s="7" t="s">
-        <v>146</v>
+    <row r="30" customFormat="1" ht="33.75" customHeight="1" spans="1:18">
+      <c r="A30" s="1"/>
+      <c r="B30" s="1" t="s">
+        <v>147</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="E30" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E30" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F30" s="7" t="s">
+      <c r="F30" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G30" s="1">
         <v>0</v>
       </c>
-      <c r="H30" s="7" t="s">
-        <v>149</v>
-      </c>
+      <c r="H30" s="1"/>
       <c r="I30" s="1">
         <v>100</v>
       </c>
@@ -4734,29 +4773,32 @@
       <c r="P30" s="1">
         <v>0</v>
       </c>
+      <c r="Q30"/>
       <c r="R30">
         <v>45</v>
       </c>
     </row>
-    <row r="31" ht="33.75" customHeight="1" spans="2:18">
-      <c r="B31" s="7" t="s">
+    <row r="31" customFormat="1" ht="16.5" customHeight="1" spans="1:18">
+      <c r="A31" s="1"/>
+      <c r="B31" s="1" t="s">
         <v>150</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="D31" s="8" t="s">
+      <c r="D31" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="E31" s="7" t="s">
+      <c r="E31" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F31" s="7" t="s">
+      <c r="F31" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G31" s="1">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H31" s="1"/>
       <c r="I31" s="1">
         <v>100</v>
       </c>
@@ -4781,34 +4823,37 @@
       <c r="P31" s="1">
         <v>0</v>
       </c>
+      <c r="Q31"/>
       <c r="R31">
         <v>45</v>
       </c>
     </row>
-    <row r="32" ht="16.5" customHeight="1" spans="2:18">
-      <c r="B32" s="7" t="s">
+    <row r="32" customFormat="1" ht="51" spans="1:18">
+      <c r="A32" s="1"/>
+      <c r="B32" s="1" t="s">
         <v>153</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="D32" s="1" t="s">
+      <c r="D32" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="E32" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="F32" s="7" t="s">
+      <c r="E32" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F32" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G32" s="1">
-        <v>1</v>
-      </c>
+        <v>0.2</v>
+      </c>
+      <c r="H32" s="1"/>
       <c r="I32" s="1">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="K32" s="1">
         <v>0</v>
@@ -4828,12 +4873,14 @@
       <c r="P32" s="1">
         <v>0</v>
       </c>
+      <c r="Q32"/>
       <c r="R32">
         <v>45</v>
       </c>
     </row>
-    <row r="33" ht="33.75" customHeight="1" spans="2:18">
-      <c r="B33" s="7" t="s">
+    <row r="33" customFormat="1" ht="33.75" customHeight="1" spans="1:18">
+      <c r="A33" s="1"/>
+      <c r="B33" s="1" t="s">
         <v>156</v>
       </c>
       <c r="C33" s="1" t="s">
@@ -4842,20 +4889,21 @@
       <c r="D33" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="E33" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="F33" s="7" t="s">
+      <c r="E33" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F33" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G33" s="1">
-        <v>0.2</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="H33" s="1"/>
       <c r="I33" s="1">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="K33" s="1">
         <v>0</v>
@@ -4875,12 +4923,14 @@
       <c r="P33" s="1">
         <v>0</v>
       </c>
+      <c r="Q33"/>
       <c r="R33">
         <v>45</v>
       </c>
     </row>
-    <row r="34" ht="33.75" customHeight="1" spans="2:18">
-      <c r="B34" s="7" t="s">
+    <row r="34" customFormat="1" ht="33.75" customHeight="1" spans="1:18">
+      <c r="A34" s="1"/>
+      <c r="B34" s="1" t="s">
         <v>159</v>
       </c>
       <c r="C34" s="1" t="s">
@@ -4889,20 +4939,21 @@
       <c r="D34" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="E34" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="F34" s="7" t="s">
+      <c r="E34" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F34" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G34" s="1">
-        <v>5</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="H34" s="1"/>
       <c r="I34" s="1">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="K34" s="1">
         <v>0</v>
@@ -4922,12 +4973,14 @@
       <c r="P34" s="1">
         <v>0</v>
       </c>
+      <c r="Q34"/>
       <c r="R34">
         <v>45</v>
       </c>
     </row>
-    <row r="35" ht="33.75" customHeight="1" spans="2:18">
-      <c r="B35" s="7" t="s">
+    <row r="35" customFormat="1" ht="33.75" customHeight="1" spans="1:18">
+      <c r="A35" s="1"/>
+      <c r="B35" s="1" t="s">
         <v>162</v>
       </c>
       <c r="C35" s="1" t="s">
@@ -4936,15 +4989,16 @@
       <c r="D35" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="E35" s="7" t="s">
+      <c r="E35" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F35" s="7" t="s">
+      <c r="F35" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G35" s="1">
-        <v>5</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H35" s="1"/>
       <c r="I35" s="1">
         <v>100</v>
       </c>
@@ -4969,34 +5023,37 @@
       <c r="P35" s="1">
         <v>0</v>
       </c>
+      <c r="Q35"/>
       <c r="R35">
         <v>45</v>
       </c>
     </row>
-    <row r="36" ht="33.75" customHeight="1" spans="2:18">
-      <c r="B36" s="7" t="s">
+    <row r="36" customFormat="1" ht="16.5" customHeight="1" spans="1:18">
+      <c r="A36" s="1"/>
+      <c r="B36" s="1" t="s">
         <v>165</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D36" s="8" t="s">
+      <c r="D36" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="E36" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="F36" s="7" t="s">
+      <c r="E36" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F36" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G36" s="1">
         <v>10</v>
       </c>
+      <c r="H36" s="1"/>
       <c r="I36" s="1">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="K36" s="1">
         <v>0</v>
@@ -5016,12 +5073,14 @@
       <c r="P36" s="1">
         <v>0</v>
       </c>
+      <c r="Q36"/>
       <c r="R36">
         <v>45</v>
       </c>
     </row>
-    <row r="37" ht="33.75" customHeight="1" spans="2:18">
-      <c r="B37" s="7" t="s">
+    <row r="37" customFormat="1" ht="33.75" customHeight="1" spans="1:18">
+      <c r="A37" s="1"/>
+      <c r="B37" s="1" t="s">
         <v>168</v>
       </c>
       <c r="C37" s="1" t="s">
@@ -5030,14 +5089,17 @@
       <c r="D37" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="E37" s="7" t="s">
+      <c r="E37" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F37" s="7" t="s">
+      <c r="F37" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G37" s="1">
-        <v>1</v>
+        <v>300</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>171</v>
       </c>
       <c r="I37" s="1">
         <v>100</v>
@@ -5063,34 +5125,37 @@
       <c r="P37" s="1">
         <v>0</v>
       </c>
+      <c r="Q37"/>
       <c r="R37">
         <v>45</v>
       </c>
     </row>
-    <row r="38" ht="16.5" customHeight="1" spans="2:18">
-      <c r="B38" s="7" t="s">
-        <v>171</v>
+    <row r="38" customFormat="1" ht="16.5" customHeight="1" spans="1:18">
+      <c r="A38" s="1"/>
+      <c r="B38" s="1" t="s">
+        <v>172</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="E38" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="F38" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F38" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G38" s="1">
-        <v>10</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H38" s="1"/>
       <c r="I38" s="1">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="K38" s="1">
         <v>0</v>
@@ -5110,32 +5175,32 @@
       <c r="P38" s="1">
         <v>0</v>
       </c>
+      <c r="Q38"/>
       <c r="R38">
         <v>45</v>
       </c>
     </row>
-    <row r="39" ht="33.75" customHeight="1" spans="2:18">
-      <c r="B39" s="7" t="s">
-        <v>174</v>
+    <row r="39" customFormat="1" ht="16.5" customHeight="1" spans="1:18">
+      <c r="A39" s="1"/>
+      <c r="B39" s="1" t="s">
+        <v>175</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="D39" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="E39" s="7" t="s">
+      <c r="D39" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E39" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F39" s="7" t="s">
+      <c r="F39" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G39" s="1">
-        <v>300</v>
-      </c>
-      <c r="H39" s="7" t="s">
-        <v>177</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H39" s="1"/>
       <c r="I39" s="1">
         <v>100</v>
       </c>
@@ -5160,12 +5225,14 @@
       <c r="P39" s="1">
         <v>0</v>
       </c>
+      <c r="Q39"/>
       <c r="R39">
         <v>45</v>
       </c>
     </row>
-    <row r="40" ht="16.5" customHeight="1" spans="2:18">
-      <c r="B40" s="7" t="s">
+    <row r="40" customFormat="1" ht="16.5" customHeight="1" spans="1:18">
+      <c r="A40" s="1"/>
+      <c r="B40" s="1" t="s">
         <v>178</v>
       </c>
       <c r="C40" s="1" t="s">
@@ -5174,20 +5241,21 @@
       <c r="D40" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="E40" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="F40" s="7" t="s">
+      <c r="E40" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="F40" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G40" s="1">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H40" s="1"/>
       <c r="I40" s="1">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>49</v>
+        <v>93</v>
       </c>
       <c r="K40" s="1">
         <v>0</v>
@@ -5207,29 +5275,32 @@
       <c r="P40" s="1">
         <v>0</v>
       </c>
+      <c r="Q40"/>
       <c r="R40">
         <v>45</v>
       </c>
     </row>
-    <row r="41" ht="16.5" customHeight="1" spans="2:18">
-      <c r="B41" s="7" t="s">
-        <v>181</v>
+    <row r="41" customFormat="1" ht="33.75" customHeight="1" spans="1:18">
+      <c r="A41" s="1"/>
+      <c r="B41" s="1" t="s">
+        <v>182</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="D41" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="E41" s="7" t="s">
+      <c r="D41" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="E41" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F41" s="7" t="s">
+      <c r="F41" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G41" s="1">
         <v>1</v>
       </c>
+      <c r="H41" s="1"/>
       <c r="I41" s="1">
         <v>100</v>
       </c>
@@ -5254,34 +5325,37 @@
       <c r="P41" s="1">
         <v>0</v>
       </c>
+      <c r="Q41"/>
       <c r="R41">
         <v>45</v>
       </c>
     </row>
-    <row r="42" ht="16.5" customHeight="1" spans="2:18">
-      <c r="B42" s="7" t="s">
-        <v>184</v>
+    <row r="42" customFormat="1" ht="33.75" customHeight="1" spans="1:18">
+      <c r="A42" s="1"/>
+      <c r="B42" s="1" t="s">
+        <v>185</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="D42" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="E42" s="7" t="s">
+      <c r="D42" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="F42" s="7" t="s">
+      <c r="E42" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F42" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G42" s="1">
         <v>1</v>
       </c>
+      <c r="H42" s="1"/>
       <c r="I42" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>93</v>
+        <v>49</v>
       </c>
       <c r="K42" s="1">
         <v>0</v>
@@ -5301,12 +5375,14 @@
       <c r="P42" s="1">
         <v>0</v>
       </c>
+      <c r="Q42"/>
       <c r="R42">
         <v>45</v>
       </c>
     </row>
-    <row r="43" ht="33.75" customHeight="1" spans="2:18">
-      <c r="B43" s="7" t="s">
+    <row r="43" customFormat="1" ht="33.75" customHeight="1" spans="1:18">
+      <c r="A43" s="1"/>
+      <c r="B43" s="1" t="s">
         <v>188</v>
       </c>
       <c r="C43" s="1" t="s">
@@ -5315,14 +5391,17 @@
       <c r="D43" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="E43" s="7" t="s">
+      <c r="E43" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F43" s="7" t="s">
+      <c r="F43" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G43" s="1">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>191</v>
       </c>
       <c r="I43" s="1">
         <v>100</v>
@@ -5348,34 +5427,39 @@
       <c r="P43" s="1">
         <v>0</v>
       </c>
+      <c r="Q43"/>
       <c r="R43">
         <v>45</v>
       </c>
     </row>
-    <row r="44" ht="33.75" customHeight="1" spans="2:18">
-      <c r="B44" s="7" t="s">
-        <v>191</v>
+    <row r="44" customFormat="1" ht="33.75" customHeight="1" spans="1:18">
+      <c r="A44" s="1"/>
+      <c r="B44" s="1" t="s">
+        <v>192</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>193</v>
-      </c>
-      <c r="E44" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="F44" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F44" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G44" s="1">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>195</v>
       </c>
       <c r="I44" s="1">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="K44" s="1">
         <v>0</v>
@@ -5395,37 +5479,39 @@
       <c r="P44" s="1">
         <v>0</v>
       </c>
+      <c r="Q44"/>
       <c r="R44">
         <v>45</v>
       </c>
     </row>
-    <row r="45" ht="33.75" customHeight="1" spans="2:18">
-      <c r="B45" s="7" t="s">
-        <v>194</v>
+    <row r="45" customFormat="1" ht="33.75" customHeight="1" spans="1:18">
+      <c r="A45" s="1"/>
+      <c r="B45" s="1" t="s">
+        <v>196</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>196</v>
-      </c>
-      <c r="E45" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="F45" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F45" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G45" s="1">
         <v>2</v>
       </c>
-      <c r="H45" s="7" t="s">
-        <v>197</v>
+      <c r="H45" s="1" t="s">
+        <v>199</v>
       </c>
       <c r="I45" s="1">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="K45" s="1">
         <v>0</v>
@@ -5445,37 +5531,37 @@
       <c r="P45" s="1">
         <v>0</v>
       </c>
+      <c r="Q45"/>
       <c r="R45">
         <v>45</v>
       </c>
     </row>
-    <row r="46" ht="33.75" customHeight="1" spans="2:18">
-      <c r="B46" s="7" t="s">
-        <v>198</v>
+    <row r="46" customFormat="1" ht="16.5" customHeight="1" spans="1:18">
+      <c r="A46" s="1"/>
+      <c r="B46" s="1" t="s">
+        <v>200</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="D46" s="8" t="s">
-        <v>200</v>
-      </c>
-      <c r="E46" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="F46" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F46" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G46" s="1">
         <v>2</v>
       </c>
-      <c r="H46" s="7" t="s">
-        <v>201</v>
-      </c>
+      <c r="H46" s="1"/>
       <c r="I46" s="1">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="K46" s="1">
         <v>0</v>
@@ -5495,37 +5581,37 @@
       <c r="P46" s="1">
         <v>0</v>
       </c>
+      <c r="Q46"/>
       <c r="R46">
         <v>45</v>
       </c>
     </row>
-    <row r="47" ht="33.75" customHeight="1" spans="2:18">
-      <c r="B47" s="7" t="s">
-        <v>202</v>
+    <row r="47" customFormat="1" ht="33.75" customHeight="1" spans="1:18">
+      <c r="A47" s="1"/>
+      <c r="B47" s="1" t="s">
+        <v>203</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>204</v>
-      </c>
-      <c r="E47" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="F47" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F47" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G47" s="1">
-        <v>2</v>
-      </c>
-      <c r="H47" s="7" t="s">
-        <v>205</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="H47" s="1"/>
       <c r="I47" s="1">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="J47" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="K47" s="1">
         <v>0</v>
@@ -5545,29 +5631,32 @@
       <c r="P47" s="1">
         <v>0</v>
       </c>
+      <c r="Q47"/>
       <c r="R47">
         <v>45</v>
       </c>
     </row>
-    <row r="48" ht="16.5" customHeight="1" spans="2:18">
-      <c r="B48" s="7" t="s">
+    <row r="48" customFormat="1" ht="33.75" customHeight="1" spans="1:18">
+      <c r="A48" s="1"/>
+      <c r="B48" s="1" t="s">
         <v>206</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="D48" s="1" t="s">
+      <c r="D48" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="E48" s="7" t="s">
+      <c r="E48" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F48" s="7" t="s">
+      <c r="F48" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G48" s="1">
-        <v>2</v>
-      </c>
+        <v>600</v>
+      </c>
+      <c r="H48" s="1"/>
       <c r="I48" s="1">
         <v>100</v>
       </c>
@@ -5592,29 +5681,32 @@
       <c r="P48" s="1">
         <v>0</v>
       </c>
+      <c r="Q48"/>
       <c r="R48">
         <v>45</v>
       </c>
     </row>
-    <row r="49" ht="33.75" customHeight="1" spans="2:18">
-      <c r="B49" s="7" t="s">
+    <row r="49" customFormat="1" ht="16.5" customHeight="1" spans="1:18">
+      <c r="A49" s="1"/>
+      <c r="B49" s="1" t="s">
         <v>209</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="D49" s="8" t="s">
+      <c r="D49" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="E49" s="7" t="s">
+      <c r="E49" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F49" s="7" t="s">
+      <c r="F49" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G49" s="1">
-        <v>5</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="H49" s="1"/>
       <c r="I49" s="1">
         <v>100</v>
       </c>
@@ -5639,12 +5731,14 @@
       <c r="P49" s="1">
         <v>0</v>
       </c>
+      <c r="Q49"/>
       <c r="R49">
         <v>45</v>
       </c>
     </row>
-    <row r="50" ht="33.75" customHeight="1" spans="2:18">
-      <c r="B50" s="7" t="s">
+    <row r="50" customFormat="1" ht="33.75" customHeight="1" spans="1:18">
+      <c r="A50" s="1"/>
+      <c r="B50" s="1" t="s">
         <v>212</v>
       </c>
       <c r="C50" s="1" t="s">
@@ -5653,15 +5747,16 @@
       <c r="D50" s="8" t="s">
         <v>214</v>
       </c>
-      <c r="E50" s="7" t="s">
+      <c r="E50" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F50" s="7" t="s">
+      <c r="F50" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G50" s="1">
-        <v>600</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="H50" s="1"/>
       <c r="I50" s="1">
         <v>100</v>
       </c>
@@ -5686,29 +5781,32 @@
       <c r="P50" s="1">
         <v>0</v>
       </c>
+      <c r="Q50"/>
       <c r="R50">
         <v>45</v>
       </c>
     </row>
-    <row r="51" ht="16.5" customHeight="1" spans="2:18">
-      <c r="B51" s="7" t="s">
+    <row r="51" customFormat="1" ht="33.75" customHeight="1" spans="1:18">
+      <c r="A51" s="1"/>
+      <c r="B51" s="1" t="s">
         <v>215</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="D51" s="1" t="s">
+      <c r="D51" s="8" t="s">
         <v>217</v>
       </c>
-      <c r="E51" s="7" t="s">
+      <c r="E51" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F51" s="7" t="s">
+      <c r="F51" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G51" s="1">
         <v>2</v>
       </c>
+      <c r="H51" s="1"/>
       <c r="I51" s="1">
         <v>100</v>
       </c>
@@ -5733,34 +5831,37 @@
       <c r="P51" s="1">
         <v>0</v>
       </c>
+      <c r="Q51"/>
       <c r="R51">
         <v>45</v>
       </c>
     </row>
-    <row r="52" ht="33.75" customHeight="1" spans="2:18">
-      <c r="B52" s="7" t="s">
+    <row r="52" customFormat="1" ht="16.5" customHeight="1" spans="1:18">
+      <c r="A52" s="1"/>
+      <c r="B52" s="1" t="s">
         <v>218</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="D52" s="8" t="s">
+      <c r="D52" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="E52" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="F52" s="7" t="s">
+      <c r="E52" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="F52" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G52" s="1">
-        <v>200</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H52" s="1"/>
       <c r="I52" s="1">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="J52" s="1" t="s">
-        <v>49</v>
+        <v>93</v>
       </c>
       <c r="K52" s="1">
         <v>0</v>
@@ -5780,12 +5881,14 @@
       <c r="P52" s="1">
         <v>0</v>
       </c>
+      <c r="Q52"/>
       <c r="R52">
         <v>45</v>
       </c>
     </row>
-    <row r="53" ht="33.75" customHeight="1" spans="2:18">
-      <c r="B53" s="7" t="s">
+    <row r="53" customFormat="1" ht="33.75" customHeight="1" spans="1:18">
+      <c r="A53" s="1"/>
+      <c r="B53" s="1" t="s">
         <v>221</v>
       </c>
       <c r="C53" s="1" t="s">
@@ -5794,15 +5897,16 @@
       <c r="D53" s="8" t="s">
         <v>223</v>
       </c>
-      <c r="E53" s="7" t="s">
+      <c r="E53" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F53" s="7" t="s">
+      <c r="F53" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G53" s="1">
-        <v>2</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H53" s="1"/>
       <c r="I53" s="1">
         <v>100</v>
       </c>
@@ -5827,34 +5931,37 @@
       <c r="P53" s="1">
         <v>0</v>
       </c>
+      <c r="Q53"/>
       <c r="R53">
         <v>45</v>
       </c>
     </row>
-    <row r="54" ht="16.5" customHeight="1" spans="2:18">
-      <c r="B54" s="7" t="s">
+    <row r="54" customFormat="1" ht="33.75" customHeight="1" spans="1:18">
+      <c r="A54" s="1"/>
+      <c r="B54" s="1" t="s">
         <v>224</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="D54" s="1" t="s">
+      <c r="D54" s="8" t="s">
         <v>226</v>
       </c>
-      <c r="E54" s="7" t="s">
-        <v>187</v>
-      </c>
-      <c r="F54" s="7" t="s">
+      <c r="E54" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G54" s="1">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="H54" s="1"/>
       <c r="I54" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>93</v>
+        <v>49</v>
       </c>
       <c r="K54" s="1">
         <v>0</v>
@@ -5874,12 +5981,14 @@
       <c r="P54" s="1">
         <v>0</v>
       </c>
+      <c r="Q54"/>
       <c r="R54">
         <v>45</v>
       </c>
     </row>
-    <row r="55" ht="33.75" customHeight="1" spans="2:18">
-      <c r="B55" s="7" t="s">
+    <row r="55" customFormat="1" ht="33.75" customHeight="1" spans="1:18">
+      <c r="A55" s="1"/>
+      <c r="B55" s="1" t="s">
         <v>227</v>
       </c>
       <c r="C55" s="1" t="s">
@@ -5888,15 +5997,16 @@
       <c r="D55" s="8" t="s">
         <v>229</v>
       </c>
-      <c r="E55" s="7" t="s">
+      <c r="E55" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F55" s="7" t="s">
+      <c r="F55" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G55" s="1">
         <v>1</v>
       </c>
+      <c r="H55" s="1"/>
       <c r="I55" s="1">
         <v>100</v>
       </c>
@@ -5921,12 +6031,14 @@
       <c r="P55" s="1">
         <v>0</v>
       </c>
+      <c r="Q55"/>
       <c r="R55">
         <v>45</v>
       </c>
     </row>
-    <row r="56" ht="33.75" customHeight="1" spans="2:18">
-      <c r="B56" s="7" t="s">
+    <row r="56" customFormat="1" ht="33.75" customHeight="1" spans="1:18">
+      <c r="A56" s="1"/>
+      <c r="B56" s="1" t="s">
         <v>230</v>
       </c>
       <c r="C56" s="1" t="s">
@@ -5935,20 +6047,21 @@
       <c r="D56" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="E56" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="F56" s="7" t="s">
+      <c r="E56" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F56" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G56" s="1">
-        <v>2</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="H56" s="1"/>
       <c r="I56" s="1">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="J56" s="1" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="K56" s="1">
         <v>0</v>
@@ -5968,34 +6081,37 @@
       <c r="P56" s="1">
         <v>0</v>
       </c>
+      <c r="Q56"/>
       <c r="R56">
         <v>45</v>
       </c>
     </row>
-    <row r="57" ht="33.75" customHeight="1" spans="2:18">
-      <c r="B57" s="7" t="s">
+    <row r="57" customFormat="1" ht="16.5" customHeight="1" spans="1:18">
+      <c r="A57" s="1"/>
+      <c r="B57" s="1" t="s">
         <v>233</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="D57" s="8" t="s">
+      <c r="D57" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="E57" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="F57" s="7" t="s">
+      <c r="E57" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F57" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G57" s="1">
-        <v>1</v>
-      </c>
+        <v>0.2</v>
+      </c>
+      <c r="H57" s="1"/>
       <c r="I57" s="1">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="J57" s="1" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="K57" s="1">
         <v>0</v>
@@ -6015,34 +6131,37 @@
       <c r="P57" s="1">
         <v>0</v>
       </c>
+      <c r="Q57"/>
       <c r="R57">
         <v>45</v>
       </c>
     </row>
-    <row r="58" ht="33.75" customHeight="1" spans="2:18">
-      <c r="B58" s="7" t="s">
+    <row r="58" customFormat="1" ht="16.5" customHeight="1" spans="1:18">
+      <c r="A58" s="1"/>
+      <c r="B58" s="1" t="s">
         <v>236</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="D58" s="8" t="s">
+      <c r="D58" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="E58" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="F58" s="7" t="s">
+      <c r="E58" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F58" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G58" s="1">
-        <v>4</v>
-      </c>
+        <v>0.2</v>
+      </c>
+      <c r="H58" s="1"/>
       <c r="I58" s="1">
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="J58" s="1" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="K58" s="1">
         <v>0</v>
@@ -6062,34 +6181,37 @@
       <c r="P58" s="1">
         <v>0</v>
       </c>
+      <c r="Q58"/>
       <c r="R58">
         <v>45</v>
       </c>
     </row>
-    <row r="59" ht="16.5" customHeight="1" spans="2:18">
-      <c r="B59" s="7" t="s">
+    <row r="59" customFormat="1" ht="33.75" customHeight="1" spans="1:18">
+      <c r="A59" s="1"/>
+      <c r="B59" s="1" t="s">
         <v>239</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="D59" s="1" t="s">
+      <c r="D59" s="8" t="s">
         <v>241</v>
       </c>
-      <c r="E59" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="F59" s="7" t="s">
+      <c r="E59" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F59" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G59" s="1">
-        <v>0.2</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="H59" s="1"/>
       <c r="I59" s="1">
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="J59" s="1" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="K59" s="1">
         <v>0</v>
@@ -6109,12 +6231,14 @@
       <c r="P59" s="1">
         <v>0</v>
       </c>
+      <c r="Q59"/>
       <c r="R59">
         <v>45</v>
       </c>
     </row>
-    <row r="60" ht="16.5" customHeight="1" spans="2:18">
-      <c r="B60" s="7" t="s">
+    <row r="60" customFormat="1" ht="16.5" customHeight="1" spans="1:18">
+      <c r="A60" s="1"/>
+      <c r="B60" s="1" t="s">
         <v>242</v>
       </c>
       <c r="C60" s="1" t="s">
@@ -6123,20 +6247,21 @@
       <c r="D60" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="E60" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="F60" s="7" t="s">
+      <c r="E60" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F60" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G60" s="1">
-        <v>0.2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H60" s="1"/>
       <c r="I60" s="1">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="J60" s="1" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="K60" s="1">
         <v>0</v>
@@ -6156,12 +6281,14 @@
       <c r="P60" s="1">
         <v>0</v>
       </c>
+      <c r="Q60"/>
       <c r="R60">
         <v>45</v>
       </c>
     </row>
-    <row r="61" ht="33.75" customHeight="1" spans="2:18">
-      <c r="B61" s="7" t="s">
+    <row r="61" customFormat="1" ht="33.75" customHeight="1" spans="1:18">
+      <c r="A61" s="1"/>
+      <c r="B61" s="1" t="s">
         <v>245</v>
       </c>
       <c r="C61" s="1" t="s">
@@ -6170,20 +6297,21 @@
       <c r="D61" s="8" t="s">
         <v>247</v>
       </c>
-      <c r="E61" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="F61" s="7" t="s">
+      <c r="E61" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F61" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G61" s="1">
-        <v>10</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H61" s="1"/>
       <c r="I61" s="1">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="J61" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="K61" s="1">
         <v>0</v>
@@ -6203,29 +6331,32 @@
       <c r="P61" s="1">
         <v>0</v>
       </c>
+      <c r="Q61"/>
       <c r="R61">
         <v>45</v>
       </c>
     </row>
-    <row r="62" ht="16.5" customHeight="1" spans="2:18">
-      <c r="B62" s="7" t="s">
+    <row r="62" customFormat="1" ht="33.75" customHeight="1" spans="1:18">
+      <c r="A62" s="1"/>
+      <c r="B62" s="1" t="s">
         <v>248</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="D62" s="1" t="s">
+      <c r="D62" s="8" t="s">
         <v>250</v>
       </c>
-      <c r="E62" s="7" t="s">
+      <c r="E62" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="F62" s="7" t="s">
+      <c r="F62" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G62" s="1">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H62" s="1"/>
       <c r="I62" s="1">
         <v>30</v>
       </c>
@@ -6250,12 +6381,14 @@
       <c r="P62" s="1">
         <v>0</v>
       </c>
+      <c r="Q62"/>
       <c r="R62">
         <v>45</v>
       </c>
     </row>
-    <row r="63" ht="33.75" customHeight="1" spans="2:18">
-      <c r="B63" s="7" t="s">
+    <row r="63" customFormat="1" ht="33.75" customHeight="1" spans="1:18">
+      <c r="A63" s="1"/>
+      <c r="B63" s="1" t="s">
         <v>251</v>
       </c>
       <c r="C63" s="1" t="s">
@@ -6264,14 +6397,17 @@
       <c r="D63" s="8" t="s">
         <v>253</v>
       </c>
-      <c r="E63" s="7" t="s">
+      <c r="E63" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F63" s="7" t="s">
+      <c r="F63" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G63" s="1">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>254</v>
       </c>
       <c r="I63" s="1">
         <v>100</v>
@@ -6297,34 +6433,39 @@
       <c r="P63" s="1">
         <v>0</v>
       </c>
+      <c r="Q63"/>
       <c r="R63">
         <v>45</v>
       </c>
     </row>
-    <row r="64" ht="33.75" customHeight="1" spans="2:18">
-      <c r="B64" s="7" t="s">
-        <v>254</v>
+    <row r="64" customFormat="1" ht="33.75" customHeight="1" spans="1:18">
+      <c r="A64" s="1"/>
+      <c r="B64" s="1" t="s">
+        <v>255</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D64" s="8" t="s">
-        <v>256</v>
-      </c>
-      <c r="E64" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="F64" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F64" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G64" s="1">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="H64" s="1" t="s">
+        <v>258</v>
       </c>
       <c r="I64" s="1">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="J64" s="1" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="K64" s="1">
         <v>0</v>
@@ -6344,32 +6485,32 @@
       <c r="P64" s="1">
         <v>0</v>
       </c>
+      <c r="Q64"/>
       <c r="R64">
         <v>45</v>
       </c>
     </row>
-    <row r="65" ht="33.75" customHeight="1" spans="2:18">
-      <c r="B65" s="7" t="s">
-        <v>257</v>
+    <row r="65" customFormat="1" ht="16.5" customHeight="1" spans="1:18">
+      <c r="A65" s="1"/>
+      <c r="B65" s="1" t="s">
+        <v>259</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="D65" s="8" t="s">
-        <v>259</v>
-      </c>
-      <c r="E65" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="E65" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F65" s="7" t="s">
+      <c r="F65" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G65" s="1">
-        <v>0</v>
-      </c>
-      <c r="H65" s="7" t="s">
-        <v>260</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H65" s="1"/>
       <c r="I65" s="1">
         <v>100</v>
       </c>
@@ -6394,37 +6535,37 @@
       <c r="P65" s="1">
         <v>0</v>
       </c>
+      <c r="Q65"/>
       <c r="R65">
         <v>45</v>
       </c>
     </row>
-    <row r="66" ht="33.75" customHeight="1" spans="2:18">
-      <c r="B66" s="7" t="s">
-        <v>261</v>
+    <row r="66" customFormat="1" ht="16.5" customHeight="1" spans="1:18">
+      <c r="A66" s="1"/>
+      <c r="B66" s="1" t="s">
+        <v>262</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="D66" s="8" t="s">
         <v>263</v>
       </c>
-      <c r="E66" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="F66" s="7" t="s">
+      <c r="D66" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F66" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G66" s="1">
-        <v>0</v>
-      </c>
-      <c r="H66" s="7" t="s">
-        <v>264</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="H66" s="1"/>
       <c r="I66" s="1">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="J66" s="1" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="K66" s="1">
         <v>0</v>
@@ -6444,29 +6585,32 @@
       <c r="P66" s="1">
         <v>0</v>
       </c>
+      <c r="Q66"/>
       <c r="R66">
         <v>45</v>
       </c>
     </row>
-    <row r="67" ht="16.5" customHeight="1" spans="2:18">
-      <c r="B67" s="7" t="s">
+    <row r="67" customFormat="1" ht="33.75" customHeight="1" spans="1:18">
+      <c r="A67" s="1"/>
+      <c r="B67" s="1" t="s">
         <v>265</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="D67" s="1" t="s">
+      <c r="D67" s="8" t="s">
         <v>267</v>
       </c>
-      <c r="E67" s="7" t="s">
+      <c r="E67" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F67" s="7" t="s">
+      <c r="F67" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G67" s="1">
-        <v>1</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="H67" s="1"/>
       <c r="I67" s="1">
         <v>100</v>
       </c>
@@ -6491,12 +6635,14 @@
       <c r="P67" s="1">
         <v>0</v>
       </c>
+      <c r="Q67"/>
       <c r="R67">
         <v>45</v>
       </c>
     </row>
-    <row r="68" ht="16.5" customHeight="1" spans="2:18">
-      <c r="B68" s="7" t="s">
+    <row r="68" customFormat="1" ht="16.5" customHeight="1" spans="1:18">
+      <c r="A68" s="1"/>
+      <c r="B68" s="1" t="s">
         <v>268</v>
       </c>
       <c r="C68" s="1" t="s">
@@ -6505,15 +6651,16 @@
       <c r="D68" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="E68" s="7" t="s">
+      <c r="E68" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="F68" s="7" t="s">
-        <v>47</v>
+      <c r="F68" s="1" t="s">
+        <v>271</v>
       </c>
       <c r="G68" s="1">
-        <v>2</v>
-      </c>
+        <v>-0.2</v>
+      </c>
+      <c r="H68" s="1"/>
       <c r="I68" s="1">
         <v>300</v>
       </c>
@@ -6538,34 +6685,37 @@
       <c r="P68" s="1">
         <v>0</v>
       </c>
+      <c r="Q68"/>
       <c r="R68">
         <v>45</v>
       </c>
     </row>
-    <row r="69" ht="33.75" customHeight="1" spans="2:18">
-      <c r="B69" s="7" t="s">
+    <row r="69" customFormat="1" ht="16.5" customHeight="1" spans="1:18">
+      <c r="A69" s="1"/>
+      <c r="B69" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F69" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="C69" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="D69" s="8" t="s">
-        <v>273</v>
-      </c>
-      <c r="E69" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="F69" s="7" t="s">
-        <v>47</v>
-      </c>
       <c r="G69" s="1">
-        <v>100</v>
-      </c>
+        <v>0.2</v>
+      </c>
+      <c r="H69" s="1"/>
       <c r="I69" s="1">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="J69" s="1" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="K69" s="1">
         <v>0</v>
@@ -6585,29 +6735,32 @@
       <c r="P69" s="1">
         <v>0</v>
       </c>
+      <c r="Q69"/>
       <c r="R69">
         <v>45</v>
       </c>
     </row>
-    <row r="70" ht="16.5" customHeight="1" spans="2:18">
-      <c r="B70" s="7" t="s">
-        <v>274</v>
+    <row r="70" customFormat="1" ht="16.5" customHeight="1" spans="1:18">
+      <c r="A70" s="1"/>
+      <c r="B70" s="1" t="s">
+        <v>275</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="E70" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="E70" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="F70" s="7" t="s">
-        <v>277</v>
+      <c r="F70" s="1" t="s">
+        <v>271</v>
       </c>
       <c r="G70" s="1">
-        <v>-0.2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H70" s="1"/>
       <c r="I70" s="1">
         <v>300</v>
       </c>
@@ -6632,12 +6785,14 @@
       <c r="P70" s="1">
         <v>0</v>
       </c>
+      <c r="Q70"/>
       <c r="R70">
         <v>45</v>
       </c>
     </row>
-    <row r="71" ht="16.5" customHeight="1" spans="2:18">
-      <c r="B71" s="7" t="s">
+    <row r="71" customFormat="1" ht="16.5" customHeight="1" spans="1:18">
+      <c r="A71" s="1"/>
+      <c r="B71" s="1" t="s">
         <v>278</v>
       </c>
       <c r="C71" s="1" t="s">
@@ -6646,15 +6801,16 @@
       <c r="D71" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="E71" s="7" t="s">
+      <c r="E71" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="F71" s="7" t="s">
-        <v>277</v>
+      <c r="F71" s="1" t="s">
+        <v>271</v>
       </c>
       <c r="G71" s="1">
-        <v>0.2</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H71" s="1"/>
       <c r="I71" s="1">
         <v>300</v>
       </c>
@@ -6679,29 +6835,32 @@
       <c r="P71" s="1">
         <v>0</v>
       </c>
+      <c r="Q71"/>
       <c r="R71">
         <v>45</v>
       </c>
     </row>
-    <row r="72" ht="16.5" customHeight="1" spans="2:18">
-      <c r="B72" s="7" t="s">
+    <row r="72" customFormat="1" ht="33.75" customHeight="1" spans="1:18">
+      <c r="A72" s="1"/>
+      <c r="B72" s="1" t="s">
         <v>281</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="D72" s="1" t="s">
+      <c r="D72" s="8" t="s">
         <v>283</v>
       </c>
-      <c r="E72" s="7" t="s">
+      <c r="E72" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="F72" s="7" t="s">
-        <v>277</v>
+      <c r="F72" s="1" t="s">
+        <v>271</v>
       </c>
       <c r="G72" s="1">
-        <v>0</v>
-      </c>
+        <v>-1</v>
+      </c>
+      <c r="H72" s="1"/>
       <c r="I72" s="1">
         <v>300</v>
       </c>
@@ -6726,12 +6885,14 @@
       <c r="P72" s="1">
         <v>0</v>
       </c>
+      <c r="Q72"/>
       <c r="R72">
         <v>45</v>
       </c>
     </row>
-    <row r="73" ht="16.5" customHeight="1" spans="2:18">
-      <c r="B73" s="7" t="s">
+    <row r="73" customFormat="1" ht="16.5" customHeight="1" spans="1:18">
+      <c r="A73" s="1"/>
+      <c r="B73" s="1" t="s">
         <v>284</v>
       </c>
       <c r="C73" s="1" t="s">
@@ -6740,15 +6901,16 @@
       <c r="D73" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="E73" s="7" t="s">
+      <c r="E73" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="F73" s="7" t="s">
-        <v>277</v>
+      <c r="F73" s="1" t="s">
+        <v>271</v>
       </c>
       <c r="G73" s="1">
-        <v>1</v>
-      </c>
+        <v>0.2</v>
+      </c>
+      <c r="H73" s="1"/>
       <c r="I73" s="1">
         <v>300</v>
       </c>
@@ -6773,29 +6935,32 @@
       <c r="P73" s="1">
         <v>0</v>
       </c>
+      <c r="Q73"/>
       <c r="R73">
         <v>45</v>
       </c>
     </row>
-    <row r="74" ht="33.75" customHeight="1" spans="2:18">
-      <c r="B74" s="7" t="s">
+    <row r="74" customFormat="1" ht="16.5" customHeight="1" spans="1:18">
+      <c r="A74" s="1"/>
+      <c r="B74" s="1" t="s">
         <v>287</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="D74" s="8" t="s">
+      <c r="D74" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="E74" s="7" t="s">
+      <c r="E74" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="F74" s="7" t="s">
-        <v>277</v>
+      <c r="F74" s="1" t="s">
+        <v>271</v>
       </c>
       <c r="G74" s="1">
-        <v>-1</v>
-      </c>
+        <v>0.15</v>
+      </c>
+      <c r="H74" s="1"/>
       <c r="I74" s="1">
         <v>300</v>
       </c>
@@ -6820,12 +6985,14 @@
       <c r="P74" s="1">
         <v>0</v>
       </c>
+      <c r="Q74"/>
       <c r="R74">
         <v>45</v>
       </c>
     </row>
-    <row r="75" ht="16.5" customHeight="1" spans="2:18">
-      <c r="B75" s="7" t="s">
+    <row r="75" customFormat="1" ht="16.5" customHeight="1" spans="1:18">
+      <c r="A75" s="1"/>
+      <c r="B75" s="1" t="s">
         <v>290</v>
       </c>
       <c r="C75" s="1" t="s">
@@ -6834,15 +7001,16 @@
       <c r="D75" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="E75" s="7" t="s">
+      <c r="E75" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="F75" s="7" t="s">
-        <v>277</v>
+      <c r="F75" s="1" t="s">
+        <v>271</v>
       </c>
       <c r="G75" s="1">
-        <v>0.2</v>
-      </c>
+        <v>0.15</v>
+      </c>
+      <c r="H75" s="1"/>
       <c r="I75" s="1">
         <v>300</v>
       </c>
@@ -6867,12 +7035,14 @@
       <c r="P75" s="1">
         <v>0</v>
       </c>
+      <c r="Q75"/>
       <c r="R75">
         <v>45</v>
       </c>
     </row>
-    <row r="76" ht="16.5" customHeight="1" spans="2:18">
-      <c r="B76" s="7" t="s">
+    <row r="76" customFormat="1" ht="16.5" customHeight="1" spans="1:18">
+      <c r="A76" s="1"/>
+      <c r="B76" s="1" t="s">
         <v>293</v>
       </c>
       <c r="C76" s="1" t="s">
@@ -6881,15 +7051,16 @@
       <c r="D76" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="E76" s="7" t="s">
+      <c r="E76" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="F76" s="7" t="s">
-        <v>277</v>
+      <c r="F76" s="1" t="s">
+        <v>271</v>
       </c>
       <c r="G76" s="1">
-        <v>0.15</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H76" s="1"/>
       <c r="I76" s="1">
         <v>300</v>
       </c>
@@ -6914,12 +7085,14 @@
       <c r="P76" s="1">
         <v>0</v>
       </c>
+      <c r="Q76"/>
       <c r="R76">
         <v>45</v>
       </c>
     </row>
-    <row r="77" ht="16.5" customHeight="1" spans="2:18">
-      <c r="B77" s="7" t="s">
+    <row r="77" customFormat="1" ht="16.5" customHeight="1" spans="1:18">
+      <c r="A77" s="1"/>
+      <c r="B77" s="1" t="s">
         <v>296</v>
       </c>
       <c r="C77" s="1" t="s">
@@ -6928,20 +7101,21 @@
       <c r="D77" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="E77" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="F77" s="7" t="s">
-        <v>277</v>
+      <c r="E77" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="G77" s="1">
-        <v>0.15</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="H77" s="1"/>
       <c r="I77" s="1">
-        <v>300</v>
+        <v>10</v>
       </c>
       <c r="J77" s="1" t="s">
-        <v>55</v>
+        <v>93</v>
       </c>
       <c r="K77" s="1">
         <v>0</v>
@@ -6961,34 +7135,37 @@
       <c r="P77" s="1">
         <v>0</v>
       </c>
+      <c r="Q77"/>
       <c r="R77">
         <v>45</v>
       </c>
     </row>
-    <row r="78" ht="16.5" customHeight="1" spans="2:18">
-      <c r="B78" s="7" t="s">
+    <row r="78" customFormat="1" ht="33.75" customHeight="1" spans="1:18">
+      <c r="A78" s="1"/>
+      <c r="B78" s="1" t="s">
         <v>299</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="D78" s="1" t="s">
+      <c r="D78" s="8" t="s">
         <v>301</v>
       </c>
-      <c r="E78" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="F78" s="7" t="s">
-        <v>277</v>
+      <c r="E78" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="G78" s="1">
-        <v>0</v>
-      </c>
+        <v>1.2</v>
+      </c>
+      <c r="H78" s="1"/>
       <c r="I78" s="1">
-        <v>300</v>
+        <v>10</v>
       </c>
       <c r="J78" s="1" t="s">
-        <v>55</v>
+        <v>93</v>
       </c>
       <c r="K78" s="1">
         <v>0</v>
@@ -7007,30 +7184,35 @@
       </c>
       <c r="P78" s="1">
         <v>0</v>
+      </c>
+      <c r="Q78" s="1" t="s">
+        <v>302</v>
       </c>
       <c r="R78">
         <v>45</v>
       </c>
     </row>
-    <row r="79" ht="16.5" customHeight="1" spans="2:18">
-      <c r="B79" s="7" t="s">
-        <v>302</v>
+    <row r="79" customFormat="1" ht="33.75" customHeight="1" spans="1:18">
+      <c r="A79" s="1"/>
+      <c r="B79" s="1" t="s">
+        <v>303</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="D79" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="E79" s="7" t="s">
-        <v>187</v>
-      </c>
-      <c r="F79" s="7" t="s">
+      <c r="D79" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="F79" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G79" s="1">
-        <v>2</v>
-      </c>
+        <v>1.2</v>
+      </c>
+      <c r="H79" s="1"/>
       <c r="I79" s="1">
         <v>10</v>
       </c>
@@ -7055,34 +7237,39 @@
       <c r="P79" s="1">
         <v>0</v>
       </c>
+      <c r="Q79" s="1" t="s">
+        <v>302</v>
+      </c>
       <c r="R79">
         <v>45</v>
       </c>
     </row>
-    <row r="80" ht="33.75" customHeight="1" spans="2:18">
-      <c r="B80" s="7" t="s">
-        <v>305</v>
+    <row r="80" customFormat="1" ht="33.75" customHeight="1" spans="1:18">
+      <c r="A80" s="1"/>
+      <c r="B80" s="1" t="s">
+        <v>306</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D80" s="8" t="s">
-        <v>307</v>
-      </c>
-      <c r="E80" s="7" t="s">
-        <v>187</v>
-      </c>
-      <c r="F80" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F80" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G80" s="1">
-        <v>1.2</v>
-      </c>
+        <v>0.2</v>
+      </c>
+      <c r="H80" s="1"/>
       <c r="I80" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="J80" s="1" t="s">
-        <v>93</v>
+        <v>49</v>
       </c>
       <c r="K80" s="1">
         <v>0</v>
@@ -7102,15 +7289,16 @@
       <c r="P80" s="1">
         <v>0</v>
       </c>
-      <c r="Q80" s="7" t="s">
-        <v>308</v>
+      <c r="Q80" s="1" t="s">
+        <v>302</v>
       </c>
       <c r="R80">
         <v>45</v>
       </c>
     </row>
-    <row r="81" ht="33.75" customHeight="1" spans="2:18">
-      <c r="B81" s="7" t="s">
+    <row r="81" customFormat="1" ht="33.75" customHeight="1" spans="1:18">
+      <c r="A81" s="1"/>
+      <c r="B81" s="1" t="s">
         <v>309</v>
       </c>
       <c r="C81" s="1" t="s">
@@ -7119,20 +7307,23 @@
       <c r="D81" s="8" t="s">
         <v>311</v>
       </c>
-      <c r="E81" s="7" t="s">
-        <v>187</v>
-      </c>
-      <c r="F81" s="7" t="s">
+      <c r="E81" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F81" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G81" s="1">
-        <v>1.2</v>
+        <v>10</v>
+      </c>
+      <c r="H81" s="1" t="s">
+        <v>312</v>
       </c>
       <c r="I81" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="J81" s="1" t="s">
-        <v>93</v>
+        <v>49</v>
       </c>
       <c r="K81" s="1">
         <v>0</v>
@@ -7152,37 +7343,39 @@
       <c r="P81" s="1">
         <v>0</v>
       </c>
-      <c r="Q81" s="7" t="s">
-        <v>308</v>
+      <c r="Q81" s="1" t="s">
+        <v>302</v>
       </c>
       <c r="R81">
         <v>45</v>
       </c>
     </row>
-    <row r="82" ht="33.75" customHeight="1" spans="2:18">
-      <c r="B82" s="7" t="s">
-        <v>312</v>
+    <row r="82" customFormat="1" ht="33.75" customHeight="1" spans="1:18">
+      <c r="A82" s="1"/>
+      <c r="B82" s="1" t="s">
+        <v>313</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D82" s="8" t="s">
-        <v>314</v>
-      </c>
-      <c r="E82" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="F82" s="7" t="s">
+        <v>315</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="F82" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G82" s="1">
         <v>0.2</v>
       </c>
+      <c r="H82" s="1"/>
       <c r="I82" s="1">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="J82" s="1" t="s">
-        <v>49</v>
+        <v>93</v>
       </c>
       <c r="K82" s="1">
         <v>0</v>
@@ -7202,35 +7395,34 @@
       <c r="P82" s="1">
         <v>0</v>
       </c>
-      <c r="Q82" s="7" t="s">
-        <v>308</v>
+      <c r="Q82" s="1" t="s">
+        <v>316</v>
       </c>
       <c r="R82">
         <v>45</v>
       </c>
     </row>
-    <row r="83" ht="33.75" customHeight="1" spans="2:18">
-      <c r="B83" s="7" t="s">
-        <v>315</v>
+    <row r="83" customFormat="1" ht="33.75" customHeight="1" spans="1:18">
+      <c r="A83" s="1"/>
+      <c r="B83" s="1" t="s">
+        <v>317</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="D83" s="8" t="s">
-        <v>317</v>
-      </c>
-      <c r="E83" s="7" t="s">
+        <v>319</v>
+      </c>
+      <c r="E83" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F83" s="7" t="s">
+      <c r="F83" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G83" s="1">
         <v>10</v>
       </c>
-      <c r="H83" s="7" t="s">
-        <v>318</v>
-      </c>
+      <c r="H83" s="1"/>
       <c r="I83" s="1">
         <v>100</v>
       </c>
@@ -7255,37 +7447,39 @@
       <c r="P83" s="1">
         <v>0</v>
       </c>
-      <c r="Q83" s="7" t="s">
-        <v>308</v>
+      <c r="Q83" s="1" t="s">
+        <v>316</v>
       </c>
       <c r="R83">
         <v>45</v>
       </c>
     </row>
-    <row r="84" ht="33.75" customHeight="1" spans="2:18">
-      <c r="B84" s="7" t="s">
-        <v>319</v>
+    <row r="84" customFormat="1" ht="33.75" customHeight="1" spans="1:18">
+      <c r="A84" s="1"/>
+      <c r="B84" s="1" t="s">
+        <v>320</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D84" s="8" t="s">
-        <v>321</v>
-      </c>
-      <c r="E84" s="7" t="s">
-        <v>187</v>
-      </c>
-      <c r="F84" s="7" t="s">
+        <v>322</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F84" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G84" s="1">
-        <v>0.2</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H84" s="1"/>
       <c r="I84" s="1">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="J84" s="1" t="s">
-        <v>93</v>
+        <v>65</v>
       </c>
       <c r="K84" s="1">
         <v>0</v>
@@ -7305,15 +7499,16 @@
       <c r="P84" s="1">
         <v>0</v>
       </c>
-      <c r="Q84" s="7" t="s">
-        <v>322</v>
+      <c r="Q84" s="1" t="s">
+        <v>316</v>
       </c>
       <c r="R84">
         <v>45</v>
       </c>
     </row>
-    <row r="85" ht="33.75" customHeight="1" spans="2:18">
-      <c r="B85" s="7" t="s">
+    <row r="85" customFormat="1" ht="33.75" customHeight="1" spans="1:18">
+      <c r="A85" s="1"/>
+      <c r="B85" s="1" t="s">
         <v>323</v>
       </c>
       <c r="C85" s="1" t="s">
@@ -7322,15 +7517,18 @@
       <c r="D85" s="8" t="s">
         <v>325</v>
       </c>
-      <c r="E85" s="7" t="s">
+      <c r="E85" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F85" s="7" t="s">
+      <c r="F85" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G85" s="1">
         <v>10</v>
       </c>
+      <c r="H85" s="1" t="s">
+        <v>326</v>
+      </c>
       <c r="I85" s="1">
         <v>100</v>
       </c>
@@ -7355,37 +7553,39 @@
       <c r="P85" s="1">
         <v>0</v>
       </c>
-      <c r="Q85" s="7" t="s">
-        <v>322</v>
+      <c r="Q85" s="1" t="s">
+        <v>316</v>
       </c>
       <c r="R85">
         <v>45</v>
       </c>
     </row>
-    <row r="86" ht="33.75" customHeight="1" spans="2:18">
-      <c r="B86" s="7" t="s">
-        <v>326</v>
+    <row r="86" customFormat="1" ht="16.5" customHeight="1" spans="1:18">
+      <c r="A86" s="1"/>
+      <c r="B86" s="1" t="s">
+        <v>327</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="D86" s="8" t="s">
         <v>328</v>
       </c>
-      <c r="E86" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="F86" s="7" t="s">
+      <c r="D86" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F86" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G86" s="1">
-        <v>1</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="H86" s="1"/>
       <c r="I86" s="1">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="J86" s="1" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="K86" s="1">
         <v>0</v>
@@ -7405,113 +7605,10 @@
       <c r="P86" s="1">
         <v>0</v>
       </c>
-      <c r="Q86" s="7" t="s">
-        <v>322</v>
+      <c r="Q86" s="1" t="s">
+        <v>316</v>
       </c>
       <c r="R86">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="87" ht="33.75" customHeight="1" spans="2:18">
-      <c r="B87" s="7" t="s">
-        <v>329</v>
-      </c>
-      <c r="C87" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="D87" s="8" t="s">
-        <v>331</v>
-      </c>
-      <c r="E87" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="F87" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="G87" s="1">
-        <v>10</v>
-      </c>
-      <c r="H87" s="7" t="s">
-        <v>332</v>
-      </c>
-      <c r="I87" s="1">
-        <v>100</v>
-      </c>
-      <c r="J87" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="K87" s="1">
-        <v>0</v>
-      </c>
-      <c r="L87" s="1">
-        <v>0</v>
-      </c>
-      <c r="M87" s="1">
-        <v>0</v>
-      </c>
-      <c r="N87" s="1">
-        <v>0</v>
-      </c>
-      <c r="O87" s="1">
-        <v>0</v>
-      </c>
-      <c r="P87" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q87" s="7" t="s">
-        <v>322</v>
-      </c>
-      <c r="R87">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="88" ht="16.5" customHeight="1" spans="2:18">
-      <c r="B88" s="7" t="s">
-        <v>333</v>
-      </c>
-      <c r="C88" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="D88" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="E88" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="F88" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="G88" s="1">
-        <v>10</v>
-      </c>
-      <c r="I88" s="1">
-        <v>100</v>
-      </c>
-      <c r="J88" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="K88" s="1">
-        <v>0</v>
-      </c>
-      <c r="L88" s="1">
-        <v>0</v>
-      </c>
-      <c r="M88" s="1">
-        <v>0</v>
-      </c>
-      <c r="N88" s="1">
-        <v>0</v>
-      </c>
-      <c r="O88" s="1">
-        <v>0</v>
-      </c>
-      <c r="P88" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q88" s="7" t="s">
-        <v>322</v>
-      </c>
-      <c r="R88">
         <v>45</v>
       </c>
     </row>
@@ -7559,7 +7656,7 @@
         <v>5</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="G1" s="7" t="s">
         <v>6</v>
@@ -7571,10 +7668,10 @@
         <v>8</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="L1" s="9" t="s">
         <v>16</v>
@@ -7600,7 +7697,7 @@
         <v>23</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>24</v>
@@ -7612,10 +7709,10 @@
         <v>26</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="L2" t="s">
         <v>34</v>
@@ -7653,7 +7750,7 @@
         <v>40</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="K3" s="7" t="s">
         <v>42</v>
@@ -7667,34 +7764,34 @@
     </row>
     <row r="4" ht="33.75" customHeight="1" spans="2:13">
       <c r="B4" s="7" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="G4" s="1">
         <v>0</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="I4" s="1">
         <v>1</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="K4" s="1">
         <v>1</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="M4">
         <v>35</v>
@@ -7702,34 +7799,34 @@
     </row>
     <row r="5" ht="33.75" customHeight="1" spans="2:13">
       <c r="B5" s="7" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="F5" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0</v>
+      </c>
+      <c r="H5" s="7" t="s">
         <v>346</v>
-      </c>
-      <c r="G5" s="1">
-        <v>0</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>352</v>
       </c>
       <c r="I5" s="1">
         <v>1</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="K5" s="1">
         <v>1</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="M5">
         <v>35</v>
@@ -7737,34 +7834,34 @@
     </row>
     <row r="6" ht="33.75" customHeight="1" spans="2:13">
       <c r="B6" s="7" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="I6" s="1">
         <v>1</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="K6" s="1">
         <v>1</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="M6">
         <v>35</v>
@@ -7772,34 +7869,34 @@
     </row>
     <row r="7" ht="33.75" customHeight="1" spans="2:13">
       <c r="B7" s="7" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="I7" s="1">
         <v>1</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="K7" s="1">
         <v>1</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="M7">
         <v>35</v>
@@ -7807,34 +7904,34 @@
     </row>
     <row r="8" ht="33.75" customHeight="1" spans="2:13">
       <c r="B8" s="7" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="I8" s="1">
         <v>1</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="K8" s="1">
         <v>1</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="M8">
         <v>35</v>
@@ -7842,34 +7939,34 @@
     </row>
     <row r="9" ht="33.75" customHeight="1" spans="2:13">
       <c r="B9" s="7" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="I9" s="1">
         <v>1</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="K9" s="1">
         <v>1</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="M9">
         <v>35</v>
@@ -7877,34 +7974,34 @@
     </row>
     <row r="10" ht="33.75" customHeight="1" spans="2:13">
       <c r="B10" s="7" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="I10" s="1">
         <v>1</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="K10" s="1">
         <v>1</v>
       </c>
       <c r="L10" s="7" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="M10">
         <v>35</v>
@@ -7912,34 +8009,34 @@
     </row>
     <row r="11" ht="33.75" customHeight="1" spans="2:13">
       <c r="B11" s="7" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="F11" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="G11" s="1">
+        <v>0</v>
+      </c>
+      <c r="H11" s="7" t="s">
         <v>372</v>
-      </c>
-      <c r="G11" s="1">
-        <v>0</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>378</v>
       </c>
       <c r="I11" s="1">
         <v>1</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="K11" s="1">
         <v>1</v>
       </c>
       <c r="L11" s="7" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="M11">
         <v>35</v>
@@ -7947,34 +8044,34 @@
     </row>
     <row r="12" ht="33.75" customHeight="1" spans="2:13">
       <c r="B12" s="7" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="I12" s="1">
         <v>1</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="K12" s="1">
         <v>1</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="M12">
         <v>35</v>
@@ -7982,34 +8079,34 @@
     </row>
     <row r="13" ht="33.75" customHeight="1" spans="2:13">
       <c r="B13" s="7" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="G13" s="1">
         <v>0</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="I13" s="1">
         <v>1</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="K13" s="1">
         <v>1</v>
       </c>
       <c r="L13" s="7" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="M13">
         <v>35</v>
@@ -8017,34 +8114,34 @@
     </row>
     <row r="14" ht="33.75" customHeight="1" spans="2:13">
       <c r="B14" s="7" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="G14" s="1">
         <v>0</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="I14" s="1">
         <v>1</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="K14" s="1">
         <v>1</v>
       </c>
       <c r="L14" s="7" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="M14">
         <v>35</v>
@@ -8052,34 +8149,34 @@
     </row>
     <row r="15" ht="33.75" customHeight="1" spans="2:13">
       <c r="B15" s="7" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="G15" s="1">
         <v>0</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="I15" s="1">
         <v>1</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="K15" s="1">
         <v>1</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="M15">
         <v>35</v>
@@ -8087,34 +8184,34 @@
     </row>
     <row r="16" ht="33.75" customHeight="1" spans="2:13">
       <c r="B16" s="7" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="G16" s="1">
         <v>0</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="I16" s="1">
         <v>1</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="K16" s="1">
         <v>1</v>
       </c>
       <c r="L16" s="7" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="M16">
         <v>35</v>
@@ -8122,16 +8219,16 @@
     </row>
     <row r="17" ht="33.75" customHeight="1" spans="2:13">
       <c r="B17" s="7" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="G17" s="1">
         <v>0</v>
@@ -8140,7 +8237,7 @@
         <v>1</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="K17" s="1">
         <v>0</v>
@@ -8151,16 +8248,16 @@
     </row>
     <row r="18" ht="16.5" customHeight="1" spans="2:13">
       <c r="B18" s="7" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="G18" s="1">
         <v>0</v>
@@ -8169,7 +8266,7 @@
         <v>1</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="K18" s="1">
         <v>0</v>
@@ -8180,16 +8277,16 @@
     </row>
     <row r="19" ht="16.5" customHeight="1" spans="2:13">
       <c r="B19" s="7" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="G19" s="1">
         <v>0</v>
@@ -8198,7 +8295,7 @@
         <v>1</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="K19" s="1">
         <v>0</v>
@@ -8209,28 +8306,28 @@
     </row>
     <row r="20" ht="16.5" customHeight="1" spans="2:13">
       <c r="B20" s="7" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="G20" s="1">
         <v>0</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="I20" s="1">
         <v>1</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="K20" s="1">
         <v>0</v>
@@ -8261,36 +8358,36 @@
   <sheetData>
     <row r="1" customHeight="1" spans="2:9">
       <c r="B1" s="3" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="H1" s="7" t="s">
         <v>1</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="2:9">
       <c r="B2" s="3" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="H2" s="1">
         <v>1</v>
@@ -8304,10 +8401,10 @@
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
       <c r="D3" s="3" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="H3" s="1">
         <v>2</v>
@@ -8321,10 +8418,10 @@
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
       <c r="D4" s="3" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="H4" s="1">
         <v>3</v>
@@ -8338,10 +8435,10 @@
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
       <c r="D5" s="3" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="H5" s="1">
         <v>4</v>
@@ -8355,10 +8452,10 @@
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
       <c r="D6" s="3" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="H6" s="1">
         <v>5</v>
@@ -8372,10 +8469,10 @@
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
       <c r="D7" s="3" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="H7" s="1">
         <v>6</v>
@@ -8389,10 +8486,10 @@
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
       <c r="D8" s="3" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="H8" s="1">
         <v>7</v>
@@ -8409,7 +8506,7 @@
         <v>61</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="H9" s="1">
         <v>8</v>
@@ -8423,7 +8520,7 @@
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
       <c r="D10" s="3" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>69</v>
@@ -8439,13 +8536,13 @@
     <row r="11" customHeight="1" spans="2:9">
       <c r="B11" s="4"/>
       <c r="C11" s="3" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>72</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="H11" s="1">
         <v>10</v>
@@ -8459,10 +8556,10 @@
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
       <c r="D12" s="3" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="H12" s="1">
         <v>11</v>
@@ -8476,10 +8573,10 @@
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
       <c r="D13" s="5" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="H13" s="1">
         <v>12</v>
@@ -8493,10 +8590,10 @@
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
       <c r="D14" s="3" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="H14" s="1">
         <v>13</v>
@@ -8509,13 +8606,13 @@
     <row r="15" customHeight="1" spans="2:9">
       <c r="B15" s="4"/>
       <c r="C15" s="3" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="H15" s="1">
         <v>14</v>
@@ -8529,10 +8626,10 @@
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
       <c r="D16" s="3" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="H16" s="1">
         <v>15</v>
@@ -8546,10 +8643,10 @@
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
       <c r="D17" s="3" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="H17" s="1">
         <v>16</v>
@@ -8563,10 +8660,10 @@
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
       <c r="D18" s="3" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="H18" s="1">
         <v>17</v>
@@ -8580,10 +8677,10 @@
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
       <c r="D19" s="3" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="H19" s="1">
         <v>18</v>
@@ -8597,7 +8694,7 @@
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
       <c r="D20" s="3" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>108</v>
@@ -8614,10 +8711,10 @@
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
       <c r="D21" s="3" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="H21" s="1">
         <v>20</v>
@@ -8630,13 +8727,13 @@
     <row r="22" customHeight="1" spans="2:9">
       <c r="B22" s="4"/>
       <c r="C22" s="3" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>113</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="H22" s="1">
         <v>21</v>
@@ -8649,13 +8746,13 @@
     <row r="23" customHeight="1" spans="2:9">
       <c r="B23" s="4"/>
       <c r="C23" s="3" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="H23" s="1">
         <v>22</v>
@@ -8669,10 +8766,10 @@
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
       <c r="D24" s="3" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="H24" s="1">
         <v>23</v>
@@ -8686,10 +8783,10 @@
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
       <c r="D25" s="3" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="H25" s="1">
         <v>24</v>
@@ -8703,7 +8800,7 @@
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
       <c r="D26" s="3" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>127</v>
@@ -8719,13 +8816,13 @@
     <row r="27" customHeight="1" spans="2:9">
       <c r="B27" s="4"/>
       <c r="C27" s="3" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="H27" s="1">
         <v>26</v>
@@ -8739,10 +8836,10 @@
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
       <c r="D28" s="3" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="H28" s="1">
         <v>27</v>
@@ -8755,13 +8852,13 @@
     <row r="29" customHeight="1" spans="2:9">
       <c r="B29" s="4"/>
       <c r="C29" s="3" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="H29" s="1">
         <v>28</v>
@@ -8774,13 +8871,13 @@
     <row r="30" customHeight="1" spans="2:9">
       <c r="B30" s="4"/>
       <c r="C30" s="3" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="H30" s="1">
         <v>29</v>
@@ -8793,13 +8890,13 @@
     <row r="31" customHeight="1" spans="2:9">
       <c r="B31" s="4"/>
       <c r="C31" s="3" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="H31" s="1">
         <v>30</v>
@@ -8812,13 +8909,13 @@
     <row r="32" customHeight="1" spans="2:9">
       <c r="B32" s="4"/>
       <c r="C32" s="3" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="H32" s="1">
         <v>31</v>
@@ -8832,10 +8929,10 @@
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
       <c r="D33" s="3" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="H33" s="1">
         <v>32</v>
@@ -8849,10 +8946,10 @@
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
       <c r="D34" s="3" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="H34" s="1">
         <v>33</v>
@@ -8865,13 +8962,13 @@
     <row r="35" customHeight="1" spans="2:9">
       <c r="B35" s="4"/>
       <c r="C35" s="3" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="H35" s="1">
         <v>34</v>
@@ -8885,10 +8982,10 @@
       <c r="B36" s="4"/>
       <c r="C36" s="3"/>
       <c r="D36" s="6" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="H36" s="1">
         <v>35</v>
@@ -8901,13 +8998,13 @@
     <row r="37" customHeight="1" spans="2:9">
       <c r="B37" s="4"/>
       <c r="C37" s="3" t="s">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="H37" s="1">
         <v>36</v>
@@ -8920,13 +9017,13 @@
     <row r="38" customHeight="1" spans="2:9">
       <c r="B38" s="4"/>
       <c r="C38" s="3" t="s">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="H38" s="1">
         <v>37</v>
@@ -8940,10 +9037,10 @@
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
       <c r="D39" s="3" t="s">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="H39" s="1">
         <v>38</v>
@@ -8957,10 +9054,10 @@
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
       <c r="D40" s="3" t="s">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="H40" s="1">
         <v>39</v>
@@ -8974,10 +9071,10 @@
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
       <c r="D41" s="3" t="s">
-        <v>501</v>
+        <v>495</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="H41" s="1">
         <v>40</v>
@@ -8991,10 +9088,10 @@
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
       <c r="D42" s="3" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="H42" s="1">
         <v>41</v>
@@ -9008,10 +9105,10 @@
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
       <c r="D43" s="3" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="H43" s="1">
         <v>42</v>
@@ -9024,13 +9121,13 @@
     <row r="44" customHeight="1" spans="2:9">
       <c r="B44" s="4"/>
       <c r="C44" s="3" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="H44" s="1">
         <v>43</v>
@@ -9044,10 +9141,10 @@
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
       <c r="D45" s="3" t="s">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="H45" s="1">
         <v>44</v>
@@ -9061,10 +9158,10 @@
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
       <c r="D46" s="3" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="H46" s="1">
         <v>45</v>
@@ -9078,10 +9175,10 @@
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
       <c r="D47" s="3" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>512</v>
+        <v>506</v>
       </c>
       <c r="H47" s="1">
         <v>46</v>
@@ -9095,10 +9192,10 @@
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
       <c r="D48" s="3" t="s">
-        <v>513</v>
+        <v>507</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="H48" s="1">
         <v>47</v>
@@ -9111,13 +9208,13 @@
     <row r="49" customHeight="1" spans="2:9">
       <c r="B49" s="4"/>
       <c r="C49" s="3" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="H49" s="1">
         <v>48</v>
@@ -9131,10 +9228,10 @@
       <c r="B50" s="4"/>
       <c r="C50" s="4"/>
       <c r="D50" s="3" t="s">
-        <v>518</v>
+        <v>512</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>519</v>
+        <v>513</v>
       </c>
       <c r="H50" s="1">
         <v>49</v>
@@ -9148,10 +9245,10 @@
       <c r="B51" s="4"/>
       <c r="C51" s="4"/>
       <c r="D51" s="3" t="s">
-        <v>520</v>
+        <v>514</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>521</v>
+        <v>515</v>
       </c>
       <c r="H51" s="1">
         <v>50</v>
@@ -9164,13 +9261,13 @@
     <row r="52" customHeight="1" spans="2:9">
       <c r="B52" s="4"/>
       <c r="C52" s="3" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="H52" s="1">
         <v>51</v>
@@ -9184,10 +9281,10 @@
       <c r="B53" s="4"/>
       <c r="C53" s="4"/>
       <c r="D53" s="3" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="H53" s="1">
         <v>52</v>
@@ -9201,10 +9298,10 @@
       <c r="B54" s="4"/>
       <c r="C54" s="4"/>
       <c r="D54" s="3" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="H54" s="1">
         <v>53</v>
@@ -9217,13 +9314,13 @@
     <row r="55" customHeight="1" spans="2:9">
       <c r="B55" s="4"/>
       <c r="C55" s="3" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="H55" s="1">
         <v>54</v>
@@ -9237,10 +9334,10 @@
       <c r="B56" s="4"/>
       <c r="C56" s="4"/>
       <c r="D56" s="3" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="H56" s="1">
         <v>55</v>
@@ -9254,10 +9351,10 @@
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
       <c r="D57" s="3" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="H57" s="1">
         <v>56</v>
@@ -9271,10 +9368,10 @@
       <c r="B58" s="4"/>
       <c r="C58" s="4"/>
       <c r="D58" s="3" t="s">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="H58" s="1">
         <v>57</v>
@@ -9288,10 +9385,10 @@
       <c r="B59" s="4"/>
       <c r="C59" s="4"/>
       <c r="D59" s="3" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="H59" s="1">
         <v>58</v>
@@ -9305,10 +9402,10 @@
       <c r="B60" s="4"/>
       <c r="C60" s="4"/>
       <c r="D60" s="3" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>539</v>
+        <v>533</v>
       </c>
       <c r="H60" s="1">
         <v>59</v>
@@ -9321,13 +9418,13 @@
     <row r="61" customHeight="1" spans="2:9">
       <c r="B61" s="4"/>
       <c r="C61" s="3" t="s">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="H61" s="1">
         <v>60</v>
@@ -9341,10 +9438,10 @@
       <c r="B62" s="4"/>
       <c r="C62" s="4"/>
       <c r="D62" s="3" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="H62" s="1">
         <v>61</v>
@@ -9357,13 +9454,13 @@
     <row r="63" customHeight="1" spans="2:9">
       <c r="B63" s="4"/>
       <c r="C63" s="3" t="s">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="H63" s="1">
         <v>62</v>
@@ -9377,10 +9474,10 @@
       <c r="B64" s="4"/>
       <c r="C64" s="4"/>
       <c r="D64" s="3" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="H64" s="1">
         <v>63</v>
@@ -9394,10 +9491,10 @@
       <c r="B65" s="4"/>
       <c r="C65" s="4"/>
       <c r="D65" s="3" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="H65" s="1">
         <v>64</v>
@@ -9411,10 +9508,10 @@
       <c r="B66" s="4"/>
       <c r="C66" s="4"/>
       <c r="D66" s="3" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="H66" s="1">
         <v>65</v>
@@ -9428,10 +9525,10 @@
       <c r="B67" s="4"/>
       <c r="C67" s="4"/>
       <c r="D67" s="3" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>553</v>
+        <v>547</v>
       </c>
       <c r="H67" s="1">
         <v>66</v>
@@ -9444,13 +9541,13 @@
     <row r="68" customHeight="1" spans="2:9">
       <c r="B68" s="4"/>
       <c r="C68" s="3" t="s">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="H68" s="1">
         <v>67</v>
@@ -9463,13 +9560,13 @@
     <row r="69" customHeight="1" spans="2:9">
       <c r="B69" s="4"/>
       <c r="C69" s="3" t="s">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>557</v>
+        <v>551</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>558</v>
+        <v>552</v>
       </c>
       <c r="H69" s="1">
         <v>68</v>
@@ -9483,10 +9580,10 @@
       <c r="B70" s="4"/>
       <c r="C70" s="4"/>
       <c r="D70" s="3" t="s">
-        <v>559</v>
+        <v>553</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="H70" s="1">
         <v>69</v>
@@ -9500,10 +9597,10 @@
       <c r="B71" s="4"/>
       <c r="C71" s="4"/>
       <c r="D71" s="3" t="s">
-        <v>561</v>
+        <v>555</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>562</v>
+        <v>556</v>
       </c>
       <c r="H71" s="1">
         <v>70</v>
@@ -9517,10 +9614,10 @@
       <c r="B72" s="4"/>
       <c r="C72" s="4"/>
       <c r="D72" s="3" t="s">
-        <v>563</v>
+        <v>557</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>564</v>
+        <v>558</v>
       </c>
       <c r="H72" s="1">
         <v>71</v>
@@ -9534,10 +9631,10 @@
       <c r="B73" s="4"/>
       <c r="C73" s="4"/>
       <c r="D73" s="3" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>565</v>
+        <v>559</v>
       </c>
       <c r="H73" s="1">
         <v>72</v>
@@ -9550,13 +9647,13 @@
     <row r="74" customHeight="1" spans="2:9">
       <c r="B74" s="4"/>
       <c r="C74" s="3" t="s">
-        <v>566</v>
+        <v>560</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>567</v>
+        <v>561</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="H74" s="1">
         <v>73</v>
@@ -9570,10 +9667,10 @@
       <c r="B75" s="4"/>
       <c r="C75" s="3"/>
       <c r="D75" s="3" t="s">
-        <v>568</v>
+        <v>562</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>569</v>
+        <v>563</v>
       </c>
       <c r="H75" s="1">
         <v>74</v>
@@ -9585,16 +9682,16 @@
     </row>
     <row r="76" customHeight="1" spans="2:9">
       <c r="B76" s="3" t="s">
-        <v>570</v>
+        <v>564</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>572</v>
+        <v>566</v>
       </c>
       <c r="H76" s="1">
         <v>75</v>
@@ -9608,10 +9705,10 @@
       <c r="B77" s="4"/>
       <c r="C77" s="4"/>
       <c r="D77" s="3" t="s">
-        <v>573</v>
+        <v>567</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>574</v>
+        <v>568</v>
       </c>
       <c r="H77" s="1">
         <v>76</v>
@@ -9625,10 +9722,10 @@
       <c r="B78" s="4"/>
       <c r="C78" s="4"/>
       <c r="D78" s="3" t="s">
-        <v>575</v>
+        <v>569</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="H78" s="1">
         <v>77</v>
@@ -9642,10 +9739,10 @@
       <c r="B79" s="4"/>
       <c r="C79" s="4"/>
       <c r="D79" s="3" t="s">
-        <v>576</v>
+        <v>570</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="H79" s="1">
         <v>78</v>
@@ -9659,10 +9756,10 @@
       <c r="B80" s="4"/>
       <c r="C80" s="4"/>
       <c r="D80" s="3" t="s">
-        <v>577</v>
+        <v>571</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>578</v>
+        <v>572</v>
       </c>
       <c r="H80" s="1">
         <v>79</v>
@@ -9676,10 +9773,10 @@
       <c r="B81" s="4"/>
       <c r="C81" s="4"/>
       <c r="D81" s="3" t="s">
-        <v>579</v>
+        <v>573</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>580</v>
+        <v>574</v>
       </c>
       <c r="H81" s="1">
         <v>80</v>
@@ -9693,10 +9790,10 @@
       <c r="B82" s="4"/>
       <c r="C82" s="4"/>
       <c r="D82" s="3" t="s">
-        <v>581</v>
+        <v>575</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>582</v>
+        <v>576</v>
       </c>
       <c r="H82" s="1">
         <v>81</v>
@@ -9710,10 +9807,10 @@
       <c r="B83" s="4"/>
       <c r="C83" s="4"/>
       <c r="D83" s="3" t="s">
-        <v>583</v>
+        <v>577</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>584</v>
+        <v>578</v>
       </c>
       <c r="H83" s="1">
         <v>82</v>
@@ -9727,10 +9824,10 @@
       <c r="B84" s="4"/>
       <c r="C84" s="4"/>
       <c r="D84" s="3" t="s">
-        <v>585</v>
+        <v>579</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>586</v>
+        <v>580</v>
       </c>
       <c r="H84" s="1">
         <v>83</v>
@@ -9742,16 +9839,16 @@
     </row>
     <row r="85" customHeight="1" spans="2:9">
       <c r="B85" s="3" t="s">
-        <v>587</v>
+        <v>581</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>588</v>
+        <v>582</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>589</v>
+        <v>583</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
       <c r="H85" s="1">
         <v>84</v>
@@ -9764,13 +9861,13 @@
     <row r="86" customHeight="1" spans="2:9">
       <c r="B86" s="4"/>
       <c r="C86" s="3" t="s">
-        <v>591</v>
+        <v>585</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>593</v>
+        <v>587</v>
       </c>
       <c r="H86" s="1">
         <v>85</v>
@@ -9784,10 +9881,10 @@
       <c r="B87" s="4"/>
       <c r="C87" s="4"/>
       <c r="D87" s="3" t="s">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
       <c r="H87" s="1">
         <v>86</v>
@@ -9801,10 +9898,10 @@
       <c r="B88" s="4"/>
       <c r="C88" s="4"/>
       <c r="D88" s="3" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>596</v>
+        <v>590</v>
       </c>
       <c r="H88" s="1">
         <v>87</v>
@@ -9818,10 +9915,10 @@
       <c r="B89" s="4"/>
       <c r="C89" s="4"/>
       <c r="D89" s="3" t="s">
-        <v>597</v>
+        <v>591</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>598</v>
+        <v>592</v>
       </c>
       <c r="H89" s="1">
         <v>88</v>
@@ -9833,13 +9930,13 @@
     </row>
     <row r="90" customHeight="1" spans="3:9">
       <c r="C90" s="3" t="s">
-        <v>599</v>
+        <v>593</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>600</v>
+        <v>594</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>601</v>
+        <v>595</v>
       </c>
       <c r="H90" s="1">
         <v>89</v>
@@ -9853,10 +9950,10 @@
       <c r="B91" s="4"/>
       <c r="C91" s="4"/>
       <c r="D91" s="3" t="s">
-        <v>602</v>
+        <v>596</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>603</v>
+        <v>597</v>
       </c>
       <c r="H91" s="1">
         <v>90</v>
@@ -9870,10 +9967,10 @@
       <c r="B92" s="4"/>
       <c r="C92" s="4"/>
       <c r="D92" s="3" t="s">
-        <v>604</v>
+        <v>598</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>605</v>
+        <v>599</v>
       </c>
       <c r="H92" s="1">
         <v>91</v>
@@ -9887,10 +9984,10 @@
       <c r="B93" s="4"/>
       <c r="C93" s="4"/>
       <c r="D93" s="3" t="s">
-        <v>606</v>
+        <v>600</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>607</v>
+        <v>601</v>
       </c>
       <c r="H93" s="1">
         <v>92</v>
@@ -9904,10 +10001,10 @@
       <c r="B94" s="4"/>
       <c r="C94" s="4"/>
       <c r="D94" s="3" t="s">
-        <v>608</v>
+        <v>602</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="H94" s="1">
         <v>93</v>

--- a/GourmetProject/GameConfig/Datas/item.xlsx
+++ b/GourmetProject/GameConfig/Datas/item.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15200"/>
+    <workbookView windowHeight="15280"/>
   </bookViews>
   <sheets>
     <sheet name="被动道具" sheetId="1" r:id="rId1"/>
@@ -441,7 +441,7 @@
     <t>增鲜剂</t>
   </si>
   <si>
-    <t>所有食物分数永久+20</t>
+    <t>所有食物分数永久+10</t>
   </si>
   <si>
     <t>item_stargaze_every5</t>
@@ -3337,7 +3337,6 @@
       <c r="P4" s="1">
         <v>0</v>
       </c>
-      <c r="Q4"/>
       <c r="R4">
         <v>45</v>
       </c>
@@ -3387,7 +3386,6 @@
       <c r="P5" s="1">
         <v>0</v>
       </c>
-      <c r="Q5"/>
       <c r="R5">
         <v>45</v>
       </c>
@@ -3411,7 +3409,6 @@
       <c r="G6" s="1">
         <v>1</v>
       </c>
-      <c r="H6" s="1"/>
       <c r="I6" s="1">
         <v>300</v>
       </c>
@@ -3563,7 +3560,6 @@
       <c r="G8" s="1">
         <v>0</v>
       </c>
-      <c r="H8" s="1"/>
       <c r="I8" s="1">
         <v>30</v>
       </c>
@@ -3754,7 +3750,6 @@
       <c r="G11" s="1">
         <v>100</v>
       </c>
-      <c r="H11" s="1"/>
       <c r="I11" s="1">
         <v>300</v>
       </c>
@@ -3815,7 +3810,6 @@
       <c r="G12" s="1">
         <v>0.2</v>
       </c>
-      <c r="H12" s="1"/>
       <c r="I12" s="1">
         <v>100</v>
       </c>
@@ -3876,7 +3870,6 @@
       <c r="G13" s="1">
         <v>0.15</v>
       </c>
-      <c r="H13" s="1"/>
       <c r="I13" s="1">
         <v>100</v>
       </c>
@@ -3963,7 +3956,6 @@
       <c r="P14" s="1">
         <v>0</v>
       </c>
-      <c r="Q14"/>
       <c r="R14">
         <v>45</v>
       </c>
@@ -4013,7 +4005,6 @@
       <c r="P15" s="1">
         <v>0</v>
       </c>
-      <c r="Q15"/>
       <c r="R15">
         <v>45</v>
       </c>
@@ -4063,7 +4054,6 @@
       <c r="P16" s="1">
         <v>0</v>
       </c>
-      <c r="Q16"/>
       <c r="R16">
         <v>45</v>
       </c>
@@ -4113,7 +4103,6 @@
       <c r="P17" s="1">
         <v>0</v>
       </c>
-      <c r="Q17"/>
       <c r="R17">
         <v>45</v>
       </c>
@@ -4163,7 +4152,6 @@
       <c r="P18" s="1">
         <v>0</v>
       </c>
-      <c r="Q18"/>
       <c r="R18">
         <v>45</v>
       </c>
@@ -4213,7 +4201,6 @@
       <c r="P19" s="1">
         <v>0</v>
       </c>
-      <c r="Q19"/>
       <c r="R19">
         <v>45</v>
       </c>
@@ -4263,7 +4250,6 @@
       <c r="P20" s="1">
         <v>0</v>
       </c>
-      <c r="Q20"/>
       <c r="R20">
         <v>45</v>
       </c>
@@ -4315,7 +4301,6 @@
       <c r="P21" s="1">
         <v>0</v>
       </c>
-      <c r="Q21"/>
       <c r="R21">
         <v>45</v>
       </c>
@@ -4365,7 +4350,6 @@
       <c r="P22" s="1">
         <v>0</v>
       </c>
-      <c r="Q22"/>
       <c r="R22">
         <v>45</v>
       </c>
@@ -4415,7 +4399,6 @@
       <c r="P23" s="1">
         <v>0</v>
       </c>
-      <c r="Q23"/>
       <c r="R23">
         <v>45</v>
       </c>
@@ -4465,7 +4448,6 @@
       <c r="P24" s="1">
         <v>0</v>
       </c>
-      <c r="Q24"/>
       <c r="R24">
         <v>45</v>
       </c>
@@ -4517,7 +4499,6 @@
       <c r="P25" s="1">
         <v>0</v>
       </c>
-      <c r="Q25"/>
       <c r="R25">
         <v>45</v>
       </c>
@@ -4569,7 +4550,6 @@
       <c r="P26" s="1">
         <v>0</v>
       </c>
-      <c r="Q26"/>
       <c r="R26">
         <v>45</v>
       </c>
@@ -4619,7 +4599,6 @@
       <c r="P27" s="1">
         <v>0</v>
       </c>
-      <c r="Q27"/>
       <c r="R27">
         <v>45</v>
       </c>
@@ -4671,7 +4650,6 @@
       <c r="P28" s="1">
         <v>0</v>
       </c>
-      <c r="Q28"/>
       <c r="R28">
         <v>45</v>
       </c>
@@ -4723,7 +4701,6 @@
       <c r="P29" s="1">
         <v>0</v>
       </c>
-      <c r="Q29"/>
       <c r="R29">
         <v>45</v>
       </c>
@@ -4773,7 +4750,6 @@
       <c r="P30" s="1">
         <v>0</v>
       </c>
-      <c r="Q30"/>
       <c r="R30">
         <v>45</v>
       </c>
@@ -4823,7 +4799,6 @@
       <c r="P31" s="1">
         <v>0</v>
       </c>
-      <c r="Q31"/>
       <c r="R31">
         <v>45</v>
       </c>
@@ -4846,7 +4821,7 @@
         <v>47</v>
       </c>
       <c r="G32" s="1">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="H32" s="1"/>
       <c r="I32" s="1">
@@ -4873,7 +4848,6 @@
       <c r="P32" s="1">
         <v>0</v>
       </c>
-      <c r="Q32"/>
       <c r="R32">
         <v>45</v>
       </c>
@@ -4923,7 +4897,6 @@
       <c r="P33" s="1">
         <v>0</v>
       </c>
-      <c r="Q33"/>
       <c r="R33">
         <v>45</v>
       </c>
@@ -4973,7 +4946,6 @@
       <c r="P34" s="1">
         <v>0</v>
       </c>
-      <c r="Q34"/>
       <c r="R34">
         <v>45</v>
       </c>
@@ -5023,7 +4995,6 @@
       <c r="P35" s="1">
         <v>0</v>
       </c>
-      <c r="Q35"/>
       <c r="R35">
         <v>45</v>
       </c>
@@ -5073,7 +5044,6 @@
       <c r="P36" s="1">
         <v>0</v>
       </c>
-      <c r="Q36"/>
       <c r="R36">
         <v>45</v>
       </c>
@@ -5125,7 +5095,6 @@
       <c r="P37" s="1">
         <v>0</v>
       </c>
-      <c r="Q37"/>
       <c r="R37">
         <v>45</v>
       </c>
@@ -5175,7 +5144,6 @@
       <c r="P38" s="1">
         <v>0</v>
       </c>
-      <c r="Q38"/>
       <c r="R38">
         <v>45</v>
       </c>
@@ -5225,7 +5193,6 @@
       <c r="P39" s="1">
         <v>0</v>
       </c>
-      <c r="Q39"/>
       <c r="R39">
         <v>45</v>
       </c>
@@ -5275,7 +5242,6 @@
       <c r="P40" s="1">
         <v>0</v>
       </c>
-      <c r="Q40"/>
       <c r="R40">
         <v>45</v>
       </c>
@@ -5325,7 +5291,6 @@
       <c r="P41" s="1">
         <v>0</v>
       </c>
-      <c r="Q41"/>
       <c r="R41">
         <v>45</v>
       </c>
@@ -5375,7 +5340,6 @@
       <c r="P42" s="1">
         <v>0</v>
       </c>
-      <c r="Q42"/>
       <c r="R42">
         <v>45</v>
       </c>
@@ -5398,7 +5362,7 @@
         <v>47</v>
       </c>
       <c r="G43" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H43" s="1" t="s">
         <v>191</v>
@@ -5427,7 +5391,6 @@
       <c r="P43" s="1">
         <v>0</v>
       </c>
-      <c r="Q43"/>
       <c r="R43">
         <v>45</v>
       </c>
@@ -5479,7 +5442,6 @@
       <c r="P44" s="1">
         <v>0</v>
       </c>
-      <c r="Q44"/>
       <c r="R44">
         <v>45</v>
       </c>
@@ -5531,7 +5493,6 @@
       <c r="P45" s="1">
         <v>0</v>
       </c>
-      <c r="Q45"/>
       <c r="R45">
         <v>45</v>
       </c>
@@ -5581,7 +5542,6 @@
       <c r="P46" s="1">
         <v>0</v>
       </c>
-      <c r="Q46"/>
       <c r="R46">
         <v>45</v>
       </c>
@@ -5631,7 +5591,6 @@
       <c r="P47" s="1">
         <v>0</v>
       </c>
-      <c r="Q47"/>
       <c r="R47">
         <v>45</v>
       </c>
@@ -5681,7 +5640,6 @@
       <c r="P48" s="1">
         <v>0</v>
       </c>
-      <c r="Q48"/>
       <c r="R48">
         <v>45</v>
       </c>
@@ -5731,7 +5689,6 @@
       <c r="P49" s="1">
         <v>0</v>
       </c>
-      <c r="Q49"/>
       <c r="R49">
         <v>45</v>
       </c>
@@ -5781,7 +5738,6 @@
       <c r="P50" s="1">
         <v>0</v>
       </c>
-      <c r="Q50"/>
       <c r="R50">
         <v>45</v>
       </c>
@@ -5831,7 +5787,6 @@
       <c r="P51" s="1">
         <v>0</v>
       </c>
-      <c r="Q51"/>
       <c r="R51">
         <v>45</v>
       </c>
@@ -5881,7 +5836,6 @@
       <c r="P52" s="1">
         <v>0</v>
       </c>
-      <c r="Q52"/>
       <c r="R52">
         <v>45</v>
       </c>
@@ -5931,7 +5885,6 @@
       <c r="P53" s="1">
         <v>0</v>
       </c>
-      <c r="Q53"/>
       <c r="R53">
         <v>45</v>
       </c>
@@ -5981,7 +5934,6 @@
       <c r="P54" s="1">
         <v>0</v>
       </c>
-      <c r="Q54"/>
       <c r="R54">
         <v>45</v>
       </c>
@@ -6031,7 +5983,6 @@
       <c r="P55" s="1">
         <v>0</v>
       </c>
-      <c r="Q55"/>
       <c r="R55">
         <v>45</v>
       </c>
@@ -6081,7 +6032,6 @@
       <c r="P56" s="1">
         <v>0</v>
       </c>
-      <c r="Q56"/>
       <c r="R56">
         <v>45</v>
       </c>
@@ -6131,7 +6081,6 @@
       <c r="P57" s="1">
         <v>0</v>
       </c>
-      <c r="Q57"/>
       <c r="R57">
         <v>45</v>
       </c>
@@ -6181,7 +6130,6 @@
       <c r="P58" s="1">
         <v>0</v>
       </c>
-      <c r="Q58"/>
       <c r="R58">
         <v>45</v>
       </c>
@@ -6231,7 +6179,6 @@
       <c r="P59" s="1">
         <v>0</v>
       </c>
-      <c r="Q59"/>
       <c r="R59">
         <v>45</v>
       </c>
@@ -6281,7 +6228,6 @@
       <c r="P60" s="1">
         <v>0</v>
       </c>
-      <c r="Q60"/>
       <c r="R60">
         <v>45</v>
       </c>
@@ -6331,7 +6277,6 @@
       <c r="P61" s="1">
         <v>0</v>
       </c>
-      <c r="Q61"/>
       <c r="R61">
         <v>45</v>
       </c>
@@ -6381,7 +6326,6 @@
       <c r="P62" s="1">
         <v>0</v>
       </c>
-      <c r="Q62"/>
       <c r="R62">
         <v>45</v>
       </c>
@@ -6433,7 +6377,6 @@
       <c r="P63" s="1">
         <v>0</v>
       </c>
-      <c r="Q63"/>
       <c r="R63">
         <v>45</v>
       </c>
@@ -6485,7 +6428,6 @@
       <c r="P64" s="1">
         <v>0</v>
       </c>
-      <c r="Q64"/>
       <c r="R64">
         <v>45</v>
       </c>
@@ -6535,7 +6477,6 @@
       <c r="P65" s="1">
         <v>0</v>
       </c>
-      <c r="Q65"/>
       <c r="R65">
         <v>45</v>
       </c>
@@ -6585,7 +6526,6 @@
       <c r="P66" s="1">
         <v>0</v>
       </c>
-      <c r="Q66"/>
       <c r="R66">
         <v>45</v>
       </c>
@@ -6635,7 +6575,6 @@
       <c r="P67" s="1">
         <v>0</v>
       </c>
-      <c r="Q67"/>
       <c r="R67">
         <v>45</v>
       </c>
@@ -6685,7 +6624,6 @@
       <c r="P68" s="1">
         <v>0</v>
       </c>
-      <c r="Q68"/>
       <c r="R68">
         <v>45</v>
       </c>
@@ -6735,7 +6673,6 @@
       <c r="P69" s="1">
         <v>0</v>
       </c>
-      <c r="Q69"/>
       <c r="R69">
         <v>45</v>
       </c>
@@ -6785,7 +6722,6 @@
       <c r="P70" s="1">
         <v>0</v>
       </c>
-      <c r="Q70"/>
       <c r="R70">
         <v>45</v>
       </c>
@@ -6835,7 +6771,6 @@
       <c r="P71" s="1">
         <v>0</v>
       </c>
-      <c r="Q71"/>
       <c r="R71">
         <v>45</v>
       </c>
@@ -6885,7 +6820,6 @@
       <c r="P72" s="1">
         <v>0</v>
       </c>
-      <c r="Q72"/>
       <c r="R72">
         <v>45</v>
       </c>
@@ -6935,7 +6869,6 @@
       <c r="P73" s="1">
         <v>0</v>
       </c>
-      <c r="Q73"/>
       <c r="R73">
         <v>45</v>
       </c>
@@ -6985,7 +6918,6 @@
       <c r="P74" s="1">
         <v>0</v>
       </c>
-      <c r="Q74"/>
       <c r="R74">
         <v>45</v>
       </c>
@@ -7035,7 +6967,6 @@
       <c r="P75" s="1">
         <v>0</v>
       </c>
-      <c r="Q75"/>
       <c r="R75">
         <v>45</v>
       </c>
@@ -7085,7 +7016,6 @@
       <c r="P76" s="1">
         <v>0</v>
       </c>
-      <c r="Q76"/>
       <c r="R76">
         <v>45</v>
       </c>
@@ -7135,7 +7065,6 @@
       <c r="P77" s="1">
         <v>0</v>
       </c>
-      <c r="Q77"/>
       <c r="R77">
         <v>45</v>
       </c>

--- a/GourmetProject/GameConfig/Datas/item.xlsx
+++ b/GourmetProject/GameConfig/Datas/item.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15280"/>
+    <workbookView windowWidth="27240" windowHeight="15240"/>
   </bookViews>
   <sheets>
     <sheet name="被动道具" sheetId="1" r:id="rId1"/>
@@ -126,6 +126,9 @@
     <t>商店基础价格</t>
   </si>
   <si>
+    <t>2周</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -147,6 +150,9 @@
     <t>int</t>
   </si>
   <si>
+    <t>3周</t>
+  </si>
+  <si>
     <t>item_grant_two_passive</t>
   </si>
   <si>
@@ -168,6 +174,9 @@
     <t>20,80</t>
   </si>
   <si>
+    <t>4周</t>
+  </si>
+  <si>
     <t>item_grant_two_active</t>
   </si>
   <si>
@@ -195,9 +204,6 @@
     <t>获得1个菜谱</t>
   </si>
   <si>
-    <t>2周</t>
-  </si>
-  <si>
     <t>item_family_pack</t>
   </si>
   <si>
@@ -216,9 +222,6 @@
     <t>30,80</t>
   </si>
   <si>
-    <t>3周</t>
-  </si>
-  <si>
     <t>item_randomize_items</t>
   </si>
   <si>
@@ -226,9 +229,6 @@
   </si>
   <si>
     <t>所有道具替换为随机道具</t>
-  </si>
-  <si>
-    <t>4周</t>
   </si>
   <si>
     <t>item_gold_random</t>
@@ -3101,7 +3101,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AA86"/>
+  <dimension ref="A1:AC86"/>
   <sheetFormatPr defaultColWidth="9.00735294117647" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="13.0808823529412" style="1" customWidth="1"/>
@@ -3111,7 +3111,7 @@
     <col min="5" max="5" width="12.8382352941176" style="1" customWidth="1"/>
     <col min="6" max="6" width="15.1617647058824" style="1" customWidth="1"/>
     <col min="7" max="7" width="11.9191176470588" style="1" customWidth="1"/>
-    <col min="8" max="8" width="13.7720588235294" style="1" customWidth="1"/>
+    <col min="8" max="8" width="25.5294117647059" style="1" customWidth="1"/>
     <col min="9" max="9" width="15.1617647058824" style="1" customWidth="1"/>
     <col min="10" max="10" width="36" style="1" customWidth="1"/>
     <col min="11" max="11" width="25.0808823529412" style="1" customWidth="1"/>
@@ -3180,7 +3180,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" customFormat="1" ht="16.5" customHeight="1" spans="1:18">
+    <row r="2" customFormat="1" ht="16.5" customHeight="1" spans="1:29">
       <c r="A2" s="1" t="s">
         <v>18</v>
       </c>
@@ -3235,89 +3235,143 @@
       <c r="R2" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="3" customFormat="1" ht="16.5" customHeight="1" spans="1:18">
+      <c r="U2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="V2" s="1">
+        <v>30</v>
+      </c>
+      <c r="W2" s="1">
+        <v>31</v>
+      </c>
+      <c r="X2" s="1">
+        <v>32</v>
+      </c>
+      <c r="Y2" s="1">
+        <v>33</v>
+      </c>
+      <c r="Z2" s="1">
+        <v>34</v>
+      </c>
+      <c r="AA2" s="1">
+        <v>35</v>
+      </c>
+      <c r="AB2" s="1">
+        <v>36</v>
+      </c>
+      <c r="AC2" s="1">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" customFormat="1" ht="16.5" customHeight="1" spans="1:29">
       <c r="A3" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="G3" s="1" t="s">
+      <c r="I3" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>38</v>
+      </c>
+      <c r="R3" t="s">
+        <v>43</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="V3" s="1">
         <v>40</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="J3" s="1" t="s">
+      <c r="W3" s="1">
         <v>41</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="X3" s="1">
         <v>42</v>
       </c>
-      <c r="L3" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>37</v>
-      </c>
-      <c r="R3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="4" customFormat="1" ht="16.5" customHeight="1" spans="1:18">
+      <c r="Y3" s="1">
+        <v>43</v>
+      </c>
+      <c r="Z3" s="1">
+        <v>44</v>
+      </c>
+      <c r="AA3" s="1">
+        <v>45</v>
+      </c>
+      <c r="AB3" s="1">
+        <v>46</v>
+      </c>
+      <c r="AC3" s="1">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" ht="16.5" customHeight="1" spans="1:29">
       <c r="A4" s="1"/>
       <c r="B4" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G4" s="1"/>
       <c r="H4" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I4" s="1">
         <v>100</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K4" s="1">
         <v>0</v>
@@ -3338,35 +3392,63 @@
         <v>0</v>
       </c>
       <c r="R4">
-        <v>45</v>
+        <f>VLOOKUP(E4,$T$10:$AB$13,9,FALSE)</f>
+        <v>80</v>
+      </c>
+      <c r="U4" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="V4" s="1">
+        <v>50</v>
+      </c>
+      <c r="W4" s="1">
+        <v>51</v>
+      </c>
+      <c r="X4" s="1">
+        <v>52</v>
+      </c>
+      <c r="Y4" s="1">
+        <v>53</v>
+      </c>
+      <c r="Z4" s="1">
+        <v>54</v>
+      </c>
+      <c r="AA4" s="1">
+        <v>55</v>
+      </c>
+      <c r="AB4" s="1">
+        <v>56</v>
+      </c>
+      <c r="AC4" s="1">
+        <v>57</v>
       </c>
     </row>
     <row r="5" customFormat="1" ht="16.5" customHeight="1" spans="1:18">
       <c r="A5" s="1"/>
       <c r="B5" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G5" s="1"/>
       <c r="H5" s="10" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="I5" s="1">
         <v>300</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K5" s="1">
         <v>0</v>
@@ -3387,24 +3469,25 @@
         <v>0</v>
       </c>
       <c r="R5">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="6" ht="16.5" customHeight="1" spans="2:27">
+        <f t="shared" ref="R5:R36" si="0">VLOOKUP(E5,$T$10:$AB$13,9,FALSE)</f>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" ht="16.5" customHeight="1" spans="2:18">
       <c r="B6" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>53</v>
-      </c>
       <c r="F6" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G6" s="1">
         <v>1</v>
@@ -3413,7 +3496,7 @@
         <v>300</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K6" s="1">
         <v>0</v>
@@ -3434,128 +3517,76 @@
         <v>0</v>
       </c>
       <c r="R6">
-        <v>45</v>
-      </c>
-      <c r="S6" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="T6" s="1">
-        <v>30</v>
-      </c>
-      <c r="U6" s="1">
-        <v>31</v>
-      </c>
-      <c r="V6" s="1">
-        <v>32</v>
-      </c>
-      <c r="W6" s="1">
-        <v>33</v>
-      </c>
-      <c r="X6" s="1">
-        <v>34</v>
-      </c>
-      <c r="Y6" s="1">
-        <v>35</v>
-      </c>
-      <c r="Z6" s="1">
-        <v>36</v>
-      </c>
-      <c r="AA6" s="1">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" ht="16.5" customHeight="1" spans="2:27">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" ht="16.5" customHeight="1" spans="2:18">
       <c r="B7" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G7" s="1">
         <v>50</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I7" s="1">
         <v>30</v>
       </c>
       <c r="J7" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="K7" s="1">
+        <v>0</v>
+      </c>
+      <c r="L7" s="1">
+        <v>0</v>
+      </c>
+      <c r="M7" s="1">
+        <v>0</v>
+      </c>
+      <c r="N7" s="1">
+        <v>0</v>
+      </c>
+      <c r="O7" s="1">
+        <v>0</v>
+      </c>
+      <c r="P7" s="1">
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="0"/>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="8" ht="16.5" customHeight="1" spans="2:18">
+      <c r="B8" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="K7" s="1">
-        <v>0</v>
-      </c>
-      <c r="L7" s="1">
-        <v>0</v>
-      </c>
-      <c r="M7" s="1">
-        <v>0</v>
-      </c>
-      <c r="N7" s="1">
-        <v>0</v>
-      </c>
-      <c r="O7" s="1">
-        <v>0</v>
-      </c>
-      <c r="P7" s="1">
-        <v>0</v>
-      </c>
-      <c r="R7">
-        <v>45</v>
-      </c>
-      <c r="S7" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="T7" s="1">
-        <v>40</v>
-      </c>
-      <c r="U7" s="1">
-        <v>41</v>
-      </c>
-      <c r="V7" s="1">
-        <v>42</v>
-      </c>
-      <c r="W7" s="1">
-        <v>43</v>
-      </c>
-      <c r="X7" s="1">
-        <v>44</v>
-      </c>
-      <c r="Y7" s="1">
-        <v>45</v>
-      </c>
-      <c r="Z7" s="1">
-        <v>46</v>
-      </c>
-      <c r="AA7" s="1">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="8" ht="16.5" customHeight="1" spans="2:27">
-      <c r="B8" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>63</v>
-      </c>
       <c r="F8" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
@@ -3564,7 +3595,7 @@
         <v>30</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K8" s="1">
         <v>0</v>
@@ -3585,34 +3616,8 @@
         <v>0</v>
       </c>
       <c r="R8">
-        <v>45</v>
-      </c>
-      <c r="S8" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="T8" s="1">
-        <v>50</v>
-      </c>
-      <c r="U8" s="1">
-        <v>51</v>
-      </c>
-      <c r="V8" s="1">
-        <v>52</v>
-      </c>
-      <c r="W8" s="1">
-        <v>53</v>
-      </c>
-      <c r="X8" s="1">
-        <v>54</v>
-      </c>
-      <c r="Y8" s="1">
-        <v>55</v>
-      </c>
-      <c r="Z8" s="1">
-        <v>56</v>
-      </c>
-      <c r="AA8" s="1">
-        <v>57</v>
+        <f t="shared" si="0"/>
+        <v>120</v>
       </c>
     </row>
     <row r="9" ht="16.5" customHeight="1" spans="2:26">
@@ -3626,10 +3631,10 @@
         <v>73</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
@@ -3641,7 +3646,7 @@
         <v>300</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K9" s="1">
         <v>0</v>
@@ -3662,13 +3667,14 @@
         <v>0</v>
       </c>
       <c r="R9">
-        <v>45</v>
+        <f t="shared" si="0"/>
+        <v>50</v>
       </c>
       <c r="Z9" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="10" ht="33.75" customHeight="1" spans="2:26">
+    <row r="10" ht="33.75" customHeight="1" spans="2:28">
       <c r="B10" s="1" t="s">
         <v>76</v>
       </c>
@@ -3679,10 +3685,10 @@
         <v>78</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G10" s="1">
         <v>20</v>
@@ -3694,7 +3700,7 @@
         <v>300</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K10" s="1">
         <v>0</v>
@@ -3715,7 +3721,8 @@
         <v>0</v>
       </c>
       <c r="R10">
-        <v>45</v>
+        <f t="shared" si="0"/>
+        <v>50</v>
       </c>
       <c r="T10" t="s">
         <v>80</v>
@@ -3724,14 +3731,17 @@
         <v>300</v>
       </c>
       <c r="X10" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="Z10">
         <f>COUNTIF($E$4:$E$86,T10)</f>
         <v>24</v>
       </c>
-    </row>
-    <row r="11" ht="33.75" customHeight="1" spans="2:26">
+      <c r="AB10">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" ht="33.75" customHeight="1" spans="2:28">
       <c r="B11" s="1" t="s">
         <v>81</v>
       </c>
@@ -3742,10 +3752,10 @@
         <v>83</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G11" s="1">
         <v>100</v>
@@ -3754,7 +3764,7 @@
         <v>300</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K11" s="1">
         <v>0</v>
@@ -3775,7 +3785,8 @@
         <v>0</v>
       </c>
       <c r="R11">
-        <v>45</v>
+        <f t="shared" si="0"/>
+        <v>50</v>
       </c>
       <c r="T11" t="s">
         <v>84</v>
@@ -3784,14 +3795,17 @@
         <v>100</v>
       </c>
       <c r="X11" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Z11">
         <f>COUNTIF($E$4:$E$86,T11)</f>
         <v>40</v>
       </c>
-    </row>
-    <row r="12" ht="33.75" customHeight="1" spans="2:26">
+      <c r="AB11">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="12" ht="33.75" customHeight="1" spans="2:28">
       <c r="B12" s="1" t="s">
         <v>85</v>
       </c>
@@ -3802,10 +3816,10 @@
         <v>87</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G12" s="1">
         <v>0.2</v>
@@ -3814,7 +3828,7 @@
         <v>100</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K12" s="1">
         <v>0</v>
@@ -3835,7 +3849,8 @@
         <v>0</v>
       </c>
       <c r="R12">
-        <v>45</v>
+        <f t="shared" si="0"/>
+        <v>80</v>
       </c>
       <c r="T12" t="s">
         <v>88</v>
@@ -3844,14 +3859,17 @@
         <v>30</v>
       </c>
       <c r="X12" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Z12">
         <f>COUNTIF($E$4:$E$86,T12)</f>
         <v>13</v>
       </c>
-    </row>
-    <row r="13" ht="16.5" customHeight="1" spans="2:26">
+      <c r="AB12">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="13" ht="16.5" customHeight="1" spans="2:28">
       <c r="B13" s="1" t="s">
         <v>89</v>
       </c>
@@ -3862,10 +3880,10 @@
         <v>91</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G13" s="1">
         <v>0.15</v>
@@ -3874,7 +3892,7 @@
         <v>100</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K13" s="1">
         <v>0</v>
@@ -3895,7 +3913,8 @@
         <v>0</v>
       </c>
       <c r="R13">
-        <v>45</v>
+        <f t="shared" si="0"/>
+        <v>80</v>
       </c>
       <c r="T13" t="s">
         <v>92</v>
@@ -3909,6 +3928,9 @@
       <c r="Z13">
         <f>COUNTIF($E$4:$E$86,T13)</f>
         <v>6</v>
+      </c>
+      <c r="AB13">
+        <v>200</v>
       </c>
     </row>
     <row r="14" customFormat="1" ht="16.5" customHeight="1" spans="1:18">
@@ -3923,10 +3945,10 @@
         <v>96</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G14" s="1">
         <v>0.2</v>
@@ -3936,7 +3958,7 @@
         <v>300</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K14" s="1">
         <v>0</v>
@@ -3957,7 +3979,8 @@
         <v>0</v>
       </c>
       <c r="R14">
-        <v>45</v>
+        <f t="shared" si="0"/>
+        <v>50</v>
       </c>
     </row>
     <row r="15" customFormat="1" ht="16.5" customHeight="1" spans="1:18">
@@ -3972,10 +3995,10 @@
         <v>99</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G15" s="1">
         <v>0.15</v>
@@ -3985,7 +4008,7 @@
         <v>100</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K15" s="1">
         <v>0</v>
@@ -4006,7 +4029,8 @@
         <v>0</v>
       </c>
       <c r="R15">
-        <v>45</v>
+        <f t="shared" si="0"/>
+        <v>80</v>
       </c>
     </row>
     <row r="16" customFormat="1" ht="16.5" customHeight="1" spans="1:18">
@@ -4021,10 +4045,10 @@
         <v>102</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G16" s="1">
         <v>0.15</v>
@@ -4034,7 +4058,7 @@
         <v>100</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K16" s="1">
         <v>0</v>
@@ -4055,7 +4079,8 @@
         <v>0</v>
       </c>
       <c r="R16">
-        <v>45</v>
+        <f t="shared" si="0"/>
+        <v>80</v>
       </c>
     </row>
     <row r="17" customFormat="1" ht="16.5" customHeight="1" spans="1:18">
@@ -4070,10 +4095,10 @@
         <v>105</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G17" s="1">
         <v>0.3</v>
@@ -4083,7 +4108,7 @@
         <v>300</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K17" s="1">
         <v>0</v>
@@ -4104,7 +4129,8 @@
         <v>0</v>
       </c>
       <c r="R17">
-        <v>45</v>
+        <f t="shared" si="0"/>
+        <v>50</v>
       </c>
     </row>
     <row r="18" customFormat="1" ht="16.5" customHeight="1" spans="1:18">
@@ -4119,10 +4145,10 @@
         <v>108</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G18" s="1">
         <v>30</v>
@@ -4132,7 +4158,7 @@
         <v>30</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K18" s="1">
         <v>0</v>
@@ -4153,7 +4179,8 @@
         <v>0</v>
       </c>
       <c r="R18">
-        <v>45</v>
+        <f t="shared" si="0"/>
+        <v>120</v>
       </c>
     </row>
     <row r="19" customFormat="1" ht="16.5" customHeight="1" spans="1:18">
@@ -4168,10 +4195,10 @@
         <v>111</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G19" s="1">
         <v>0.2</v>
@@ -4181,7 +4208,7 @@
         <v>300</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K19" s="1">
         <v>0</v>
@@ -4202,7 +4229,8 @@
         <v>0</v>
       </c>
       <c r="R19">
-        <v>45</v>
+        <f t="shared" si="0"/>
+        <v>50</v>
       </c>
     </row>
     <row r="20" customFormat="1" ht="33.75" customHeight="1" spans="1:18">
@@ -4217,10 +4245,10 @@
         <v>114</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G20" s="1">
         <v>0</v>
@@ -4230,7 +4258,7 @@
         <v>30</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K20" s="1">
         <v>0</v>
@@ -4251,7 +4279,8 @@
         <v>0</v>
       </c>
       <c r="R20">
-        <v>45</v>
+        <f t="shared" si="0"/>
+        <v>120</v>
       </c>
     </row>
     <row r="21" customFormat="1" ht="33.75" customHeight="1" spans="1:18">
@@ -4266,10 +4295,10 @@
         <v>117</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G21" s="1">
         <v>0</v>
@@ -4281,7 +4310,7 @@
         <v>300</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K21" s="1">
         <v>0</v>
@@ -4302,7 +4331,8 @@
         <v>0</v>
       </c>
       <c r="R21">
-        <v>45</v>
+        <f t="shared" si="0"/>
+        <v>50</v>
       </c>
     </row>
     <row r="22" customFormat="1" ht="16.5" customHeight="1" spans="1:18">
@@ -4317,10 +4347,10 @@
         <v>121</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G22" s="1">
         <v>-0.1</v>
@@ -4330,7 +4360,7 @@
         <v>300</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K22" s="1">
         <v>0</v>
@@ -4351,7 +4381,8 @@
         <v>0</v>
       </c>
       <c r="R22">
-        <v>45</v>
+        <f t="shared" si="0"/>
+        <v>50</v>
       </c>
     </row>
     <row r="23" customFormat="1" ht="16.5" customHeight="1" spans="1:18">
@@ -4366,10 +4397,10 @@
         <v>124</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G23" s="1">
         <v>-0.1</v>
@@ -4379,7 +4410,7 @@
         <v>100</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K23" s="1">
         <v>0</v>
@@ -4400,7 +4431,8 @@
         <v>0</v>
       </c>
       <c r="R23">
-        <v>45</v>
+        <f t="shared" si="0"/>
+        <v>80</v>
       </c>
     </row>
     <row r="24" customFormat="1" ht="16.5" customHeight="1" spans="1:18">
@@ -4415,10 +4447,10 @@
         <v>127</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G24" s="1">
         <v>-0.1</v>
@@ -4428,7 +4460,7 @@
         <v>30</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K24" s="1">
         <v>0</v>
@@ -4449,7 +4481,8 @@
         <v>0</v>
       </c>
       <c r="R24">
-        <v>45</v>
+        <f t="shared" si="0"/>
+        <v>120</v>
       </c>
     </row>
     <row r="25" customFormat="1" ht="51" spans="1:18">
@@ -4464,10 +4497,10 @@
         <v>130</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G25" s="1">
         <v>1.1</v>
@@ -4479,7 +4512,7 @@
         <v>100</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K25" s="1">
         <v>0</v>
@@ -4500,7 +4533,8 @@
         <v>0</v>
       </c>
       <c r="R25">
-        <v>45</v>
+        <f t="shared" si="0"/>
+        <v>80</v>
       </c>
     </row>
     <row r="26" customFormat="1" ht="51" spans="1:18">
@@ -4515,10 +4549,10 @@
         <v>134</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G26" s="1">
         <v>1.1</v>
@@ -4530,7 +4564,7 @@
         <v>30</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K26" s="1">
         <v>0</v>
@@ -4551,7 +4585,8 @@
         <v>0</v>
       </c>
       <c r="R26">
-        <v>45</v>
+        <f t="shared" si="0"/>
+        <v>120</v>
       </c>
     </row>
     <row r="27" customFormat="1" ht="16.5" customHeight="1" spans="1:18">
@@ -4566,10 +4601,10 @@
         <v>138</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G27" s="1">
         <v>10</v>
@@ -4579,7 +4614,7 @@
         <v>100</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K27" s="1">
         <v>0</v>
@@ -4600,7 +4635,8 @@
         <v>0</v>
       </c>
       <c r="R27">
-        <v>45</v>
+        <f t="shared" si="0"/>
+        <v>80</v>
       </c>
     </row>
     <row r="28" customFormat="1" ht="33.75" customHeight="1" spans="1:18">
@@ -4615,10 +4651,10 @@
         <v>141</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G28" s="1">
         <v>0</v>
@@ -4630,7 +4666,7 @@
         <v>100</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K28" s="1">
         <v>0</v>
@@ -4651,7 +4687,8 @@
         <v>0</v>
       </c>
       <c r="R28">
-        <v>45</v>
+        <f t="shared" si="0"/>
+        <v>80</v>
       </c>
     </row>
     <row r="29" customFormat="1" ht="33.75" customHeight="1" spans="1:18">
@@ -4666,10 +4703,10 @@
         <v>145</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G29" s="1">
         <v>0</v>
@@ -4681,7 +4718,7 @@
         <v>100</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K29" s="1">
         <v>0</v>
@@ -4702,7 +4739,8 @@
         <v>0</v>
       </c>
       <c r="R29">
-        <v>45</v>
+        <f t="shared" si="0"/>
+        <v>80</v>
       </c>
     </row>
     <row r="30" customFormat="1" ht="33.75" customHeight="1" spans="1:18">
@@ -4717,10 +4755,10 @@
         <v>149</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G30" s="1">
         <v>0</v>
@@ -4730,7 +4768,7 @@
         <v>100</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K30" s="1">
         <v>0</v>
@@ -4751,7 +4789,8 @@
         <v>0</v>
       </c>
       <c r="R30">
-        <v>45</v>
+        <f t="shared" si="0"/>
+        <v>80</v>
       </c>
     </row>
     <row r="31" customFormat="1" ht="16.5" customHeight="1" spans="1:18">
@@ -4766,10 +4805,10 @@
         <v>152</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G31" s="1">
         <v>1</v>
@@ -4779,7 +4818,7 @@
         <v>100</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K31" s="1">
         <v>0</v>
@@ -4800,7 +4839,8 @@
         <v>0</v>
       </c>
       <c r="R31">
-        <v>45</v>
+        <f t="shared" si="0"/>
+        <v>80</v>
       </c>
     </row>
     <row r="32" customFormat="1" ht="51" spans="1:18">
@@ -4815,10 +4855,10 @@
         <v>155</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G32" s="1">
         <v>0.1</v>
@@ -4828,7 +4868,7 @@
         <v>30</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K32" s="1">
         <v>0</v>
@@ -4849,7 +4889,8 @@
         <v>0</v>
       </c>
       <c r="R32">
-        <v>45</v>
+        <f t="shared" si="0"/>
+        <v>120</v>
       </c>
     </row>
     <row r="33" customFormat="1" ht="33.75" customHeight="1" spans="1:18">
@@ -4864,10 +4905,10 @@
         <v>158</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G33" s="1">
         <v>5</v>
@@ -4877,7 +4918,7 @@
         <v>100</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K33" s="1">
         <v>0</v>
@@ -4898,7 +4939,8 @@
         <v>0</v>
       </c>
       <c r="R33">
-        <v>45</v>
+        <f t="shared" si="0"/>
+        <v>80</v>
       </c>
     </row>
     <row r="34" customFormat="1" ht="33.75" customHeight="1" spans="1:18">
@@ -4913,10 +4955,10 @@
         <v>161</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G34" s="1">
         <v>10</v>
@@ -4926,7 +4968,7 @@
         <v>100</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K34" s="1">
         <v>0</v>
@@ -4947,7 +4989,8 @@
         <v>0</v>
       </c>
       <c r="R34">
-        <v>45</v>
+        <f t="shared" si="0"/>
+        <v>80</v>
       </c>
     </row>
     <row r="35" customFormat="1" ht="33.75" customHeight="1" spans="1:18">
@@ -4962,10 +5005,10 @@
         <v>164</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G35" s="1">
         <v>1</v>
@@ -4975,7 +5018,7 @@
         <v>100</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K35" s="1">
         <v>0</v>
@@ -4996,7 +5039,8 @@
         <v>0</v>
       </c>
       <c r="R35">
-        <v>45</v>
+        <f t="shared" si="0"/>
+        <v>80</v>
       </c>
     </row>
     <row r="36" customFormat="1" ht="16.5" customHeight="1" spans="1:18">
@@ -5011,10 +5055,10 @@
         <v>167</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G36" s="1">
         <v>10</v>
@@ -5024,7 +5068,7 @@
         <v>30</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K36" s="1">
         <v>0</v>
@@ -5045,7 +5089,8 @@
         <v>0</v>
       </c>
       <c r="R36">
-        <v>45</v>
+        <f t="shared" si="0"/>
+        <v>120</v>
       </c>
     </row>
     <row r="37" customFormat="1" ht="33.75" customHeight="1" spans="1:18">
@@ -5060,10 +5105,10 @@
         <v>170</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G37" s="1">
         <v>300</v>
@@ -5075,7 +5120,7 @@
         <v>100</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K37" s="1">
         <v>0</v>
@@ -5096,7 +5141,8 @@
         <v>0</v>
       </c>
       <c r="R37">
-        <v>45</v>
+        <f t="shared" ref="R37:R68" si="1">VLOOKUP(E37,$T$10:$AB$13,9,FALSE)</f>
+        <v>80</v>
       </c>
     </row>
     <row r="38" customFormat="1" ht="16.5" customHeight="1" spans="1:18">
@@ -5111,10 +5157,10 @@
         <v>174</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G38" s="1">
         <v>0</v>
@@ -5124,7 +5170,7 @@
         <v>100</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K38" s="1">
         <v>0</v>
@@ -5145,7 +5191,8 @@
         <v>0</v>
       </c>
       <c r="R38">
-        <v>45</v>
+        <f t="shared" si="1"/>
+        <v>80</v>
       </c>
     </row>
     <row r="39" customFormat="1" ht="16.5" customHeight="1" spans="1:18">
@@ -5160,10 +5207,10 @@
         <v>177</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G39" s="1">
         <v>1</v>
@@ -5173,7 +5220,7 @@
         <v>100</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K39" s="1">
         <v>0</v>
@@ -5194,7 +5241,8 @@
         <v>0</v>
       </c>
       <c r="R39">
-        <v>45</v>
+        <f t="shared" si="1"/>
+        <v>80</v>
       </c>
     </row>
     <row r="40" customFormat="1" ht="16.5" customHeight="1" spans="1:18">
@@ -5212,7 +5260,7 @@
         <v>181</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G40" s="1">
         <v>1</v>
@@ -5243,7 +5291,8 @@
         <v>0</v>
       </c>
       <c r="R40">
-        <v>45</v>
+        <f t="shared" si="1"/>
+        <v>200</v>
       </c>
     </row>
     <row r="41" customFormat="1" ht="33.75" customHeight="1" spans="1:18">
@@ -5258,10 +5307,10 @@
         <v>184</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G41" s="1">
         <v>1</v>
@@ -5271,7 +5320,7 @@
         <v>100</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K41" s="1">
         <v>0</v>
@@ -5292,7 +5341,8 @@
         <v>0</v>
       </c>
       <c r="R41">
-        <v>45</v>
+        <f t="shared" si="1"/>
+        <v>80</v>
       </c>
     </row>
     <row r="42" customFormat="1" ht="33.75" customHeight="1" spans="1:18">
@@ -5307,10 +5357,10 @@
         <v>187</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G42" s="1">
         <v>1</v>
@@ -5320,7 +5370,7 @@
         <v>100</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K42" s="1">
         <v>0</v>
@@ -5341,7 +5391,8 @@
         <v>0</v>
       </c>
       <c r="R42">
-        <v>45</v>
+        <f t="shared" si="1"/>
+        <v>80</v>
       </c>
     </row>
     <row r="43" customFormat="1" ht="33.75" customHeight="1" spans="1:18">
@@ -5356,10 +5407,10 @@
         <v>190</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G43" s="1">
         <v>1</v>
@@ -5371,7 +5422,7 @@
         <v>100</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K43" s="1">
         <v>0</v>
@@ -5392,7 +5443,8 @@
         <v>0</v>
       </c>
       <c r="R43">
-        <v>45</v>
+        <f t="shared" si="1"/>
+        <v>80</v>
       </c>
     </row>
     <row r="44" customFormat="1" ht="33.75" customHeight="1" spans="1:18">
@@ -5407,10 +5459,10 @@
         <v>194</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G44" s="1">
         <v>2</v>
@@ -5422,7 +5474,7 @@
         <v>300</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K44" s="1">
         <v>0</v>
@@ -5443,7 +5495,8 @@
         <v>0</v>
       </c>
       <c r="R44">
-        <v>45</v>
+        <f t="shared" si="1"/>
+        <v>50</v>
       </c>
     </row>
     <row r="45" customFormat="1" ht="33.75" customHeight="1" spans="1:18">
@@ -5458,10 +5511,10 @@
         <v>198</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G45" s="1">
         <v>2</v>
@@ -5473,7 +5526,7 @@
         <v>300</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K45" s="1">
         <v>0</v>
@@ -5494,7 +5547,8 @@
         <v>0</v>
       </c>
       <c r="R45">
-        <v>45</v>
+        <f t="shared" si="1"/>
+        <v>50</v>
       </c>
     </row>
     <row r="46" customFormat="1" ht="16.5" customHeight="1" spans="1:18">
@@ -5509,10 +5563,10 @@
         <v>202</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G46" s="1">
         <v>2</v>
@@ -5522,7 +5576,7 @@
         <v>100</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K46" s="1">
         <v>0</v>
@@ -5543,7 +5597,8 @@
         <v>0</v>
       </c>
       <c r="R46">
-        <v>45</v>
+        <f t="shared" si="1"/>
+        <v>80</v>
       </c>
     </row>
     <row r="47" customFormat="1" ht="33.75" customHeight="1" spans="1:18">
@@ -5558,10 +5613,10 @@
         <v>205</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G47" s="1">
         <v>5</v>
@@ -5571,7 +5626,7 @@
         <v>100</v>
       </c>
       <c r="J47" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K47" s="1">
         <v>0</v>
@@ -5592,7 +5647,8 @@
         <v>0</v>
       </c>
       <c r="R47">
-        <v>45</v>
+        <f t="shared" si="1"/>
+        <v>80</v>
       </c>
     </row>
     <row r="48" customFormat="1" ht="33.75" customHeight="1" spans="1:18">
@@ -5607,10 +5663,10 @@
         <v>208</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G48" s="1">
         <v>600</v>
@@ -5620,7 +5676,7 @@
         <v>100</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K48" s="1">
         <v>0</v>
@@ -5641,7 +5697,8 @@
         <v>0</v>
       </c>
       <c r="R48">
-        <v>45</v>
+        <f t="shared" si="1"/>
+        <v>80</v>
       </c>
     </row>
     <row r="49" customFormat="1" ht="16.5" customHeight="1" spans="1:18">
@@ -5656,10 +5713,10 @@
         <v>211</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G49" s="1">
         <v>2</v>
@@ -5669,7 +5726,7 @@
         <v>100</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K49" s="1">
         <v>0</v>
@@ -5690,7 +5747,8 @@
         <v>0</v>
       </c>
       <c r="R49">
-        <v>45</v>
+        <f t="shared" si="1"/>
+        <v>80</v>
       </c>
     </row>
     <row r="50" customFormat="1" ht="33.75" customHeight="1" spans="1:18">
@@ -5705,10 +5763,10 @@
         <v>214</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G50" s="1">
         <v>200</v>
@@ -5718,7 +5776,7 @@
         <v>100</v>
       </c>
       <c r="J50" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K50" s="1">
         <v>0</v>
@@ -5739,7 +5797,8 @@
         <v>0</v>
       </c>
       <c r="R50">
-        <v>45</v>
+        <f t="shared" si="1"/>
+        <v>80</v>
       </c>
     </row>
     <row r="51" customFormat="1" ht="33.75" customHeight="1" spans="1:18">
@@ -5754,10 +5813,10 @@
         <v>217</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G51" s="1">
         <v>2</v>
@@ -5767,7 +5826,7 @@
         <v>100</v>
       </c>
       <c r="J51" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K51" s="1">
         <v>0</v>
@@ -5788,7 +5847,8 @@
         <v>0</v>
       </c>
       <c r="R51">
-        <v>45</v>
+        <f t="shared" si="1"/>
+        <v>80</v>
       </c>
     </row>
     <row r="52" customFormat="1" ht="16.5" customHeight="1" spans="1:18">
@@ -5806,7 +5866,7 @@
         <v>181</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G52" s="1">
         <v>1</v>
@@ -5837,7 +5897,8 @@
         <v>0</v>
       </c>
       <c r="R52">
-        <v>45</v>
+        <f t="shared" si="1"/>
+        <v>200</v>
       </c>
     </row>
     <row r="53" customFormat="1" ht="33.75" customHeight="1" spans="1:18">
@@ -5852,10 +5913,10 @@
         <v>223</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G53" s="1">
         <v>1</v>
@@ -5865,7 +5926,7 @@
         <v>100</v>
       </c>
       <c r="J53" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K53" s="1">
         <v>0</v>
@@ -5886,7 +5947,8 @@
         <v>0</v>
       </c>
       <c r="R53">
-        <v>45</v>
+        <f t="shared" si="1"/>
+        <v>80</v>
       </c>
     </row>
     <row r="54" customFormat="1" ht="33.75" customHeight="1" spans="1:18">
@@ -5901,10 +5963,10 @@
         <v>226</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G54" s="1">
         <v>2</v>
@@ -5914,7 +5976,7 @@
         <v>100</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K54" s="1">
         <v>0</v>
@@ -5935,7 +5997,8 @@
         <v>0</v>
       </c>
       <c r="R54">
-        <v>45</v>
+        <f t="shared" si="1"/>
+        <v>80</v>
       </c>
     </row>
     <row r="55" customFormat="1" ht="33.75" customHeight="1" spans="1:18">
@@ -5950,10 +6013,10 @@
         <v>229</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G55" s="1">
         <v>1</v>
@@ -5963,7 +6026,7 @@
         <v>100</v>
       </c>
       <c r="J55" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K55" s="1">
         <v>0</v>
@@ -5984,7 +6047,8 @@
         <v>0</v>
       </c>
       <c r="R55">
-        <v>45</v>
+        <f t="shared" si="1"/>
+        <v>80</v>
       </c>
     </row>
     <row r="56" customFormat="1" ht="33.75" customHeight="1" spans="1:18">
@@ -5999,10 +6063,10 @@
         <v>232</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G56" s="1">
         <v>4</v>
@@ -6012,7 +6076,7 @@
         <v>30</v>
       </c>
       <c r="J56" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K56" s="1">
         <v>0</v>
@@ -6033,7 +6097,8 @@
         <v>0</v>
       </c>
       <c r="R56">
-        <v>45</v>
+        <f t="shared" si="1"/>
+        <v>120</v>
       </c>
     </row>
     <row r="57" customFormat="1" ht="16.5" customHeight="1" spans="1:18">
@@ -6048,10 +6113,10 @@
         <v>235</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G57" s="1">
         <v>0.2</v>
@@ -6061,7 +6126,7 @@
         <v>30</v>
       </c>
       <c r="J57" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K57" s="1">
         <v>0</v>
@@ -6082,7 +6147,8 @@
         <v>0</v>
       </c>
       <c r="R57">
-        <v>45</v>
+        <f t="shared" si="1"/>
+        <v>120</v>
       </c>
     </row>
     <row r="58" customFormat="1" ht="16.5" customHeight="1" spans="1:18">
@@ -6097,10 +6163,10 @@
         <v>238</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G58" s="1">
         <v>0.2</v>
@@ -6110,7 +6176,7 @@
         <v>300</v>
       </c>
       <c r="J58" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K58" s="1">
         <v>0</v>
@@ -6131,7 +6197,8 @@
         <v>0</v>
       </c>
       <c r="R58">
-        <v>45</v>
+        <f t="shared" si="1"/>
+        <v>50</v>
       </c>
     </row>
     <row r="59" customFormat="1" ht="33.75" customHeight="1" spans="1:18">
@@ -6146,10 +6213,10 @@
         <v>241</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G59" s="1">
         <v>10</v>
@@ -6159,7 +6226,7 @@
         <v>300</v>
       </c>
       <c r="J59" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K59" s="1">
         <v>0</v>
@@ -6180,7 +6247,8 @@
         <v>0</v>
       </c>
       <c r="R59">
-        <v>45</v>
+        <f t="shared" si="1"/>
+        <v>50</v>
       </c>
     </row>
     <row r="60" customFormat="1" ht="16.5" customHeight="1" spans="1:18">
@@ -6195,10 +6263,10 @@
         <v>244</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G60" s="1">
         <v>0</v>
@@ -6208,7 +6276,7 @@
         <v>30</v>
       </c>
       <c r="J60" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K60" s="1">
         <v>0</v>
@@ -6229,7 +6297,8 @@
         <v>0</v>
       </c>
       <c r="R60">
-        <v>45</v>
+        <f t="shared" si="1"/>
+        <v>120</v>
       </c>
     </row>
     <row r="61" customFormat="1" ht="33.75" customHeight="1" spans="1:18">
@@ -6244,10 +6313,10 @@
         <v>247</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G61" s="1">
         <v>1</v>
@@ -6257,7 +6326,7 @@
         <v>100</v>
       </c>
       <c r="J61" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K61" s="1">
         <v>0</v>
@@ -6278,7 +6347,8 @@
         <v>0</v>
       </c>
       <c r="R61">
-        <v>45</v>
+        <f t="shared" si="1"/>
+        <v>80</v>
       </c>
     </row>
     <row r="62" customFormat="1" ht="33.75" customHeight="1" spans="1:18">
@@ -6293,10 +6363,10 @@
         <v>250</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G62" s="1">
         <v>1</v>
@@ -6306,7 +6376,7 @@
         <v>30</v>
       </c>
       <c r="J62" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K62" s="1">
         <v>0</v>
@@ -6327,7 +6397,8 @@
         <v>0</v>
       </c>
       <c r="R62">
-        <v>45</v>
+        <f t="shared" si="1"/>
+        <v>120</v>
       </c>
     </row>
     <row r="63" customFormat="1" ht="33.75" customHeight="1" spans="1:18">
@@ -6342,10 +6413,10 @@
         <v>253</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G63" s="1">
         <v>0</v>
@@ -6357,7 +6428,7 @@
         <v>100</v>
       </c>
       <c r="J63" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K63" s="1">
         <v>0</v>
@@ -6378,7 +6449,8 @@
         <v>0</v>
       </c>
       <c r="R63">
-        <v>45</v>
+        <f t="shared" si="1"/>
+        <v>80</v>
       </c>
     </row>
     <row r="64" customFormat="1" ht="33.75" customHeight="1" spans="1:18">
@@ -6393,10 +6465,10 @@
         <v>257</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G64" s="1">
         <v>0</v>
@@ -6408,7 +6480,7 @@
         <v>100</v>
       </c>
       <c r="J64" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K64" s="1">
         <v>0</v>
@@ -6429,7 +6501,8 @@
         <v>0</v>
       </c>
       <c r="R64">
-        <v>45</v>
+        <f t="shared" si="1"/>
+        <v>80</v>
       </c>
     </row>
     <row r="65" customFormat="1" ht="16.5" customHeight="1" spans="1:18">
@@ -6444,10 +6517,10 @@
         <v>261</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G65" s="1">
         <v>1</v>
@@ -6457,7 +6530,7 @@
         <v>100</v>
       </c>
       <c r="J65" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K65" s="1">
         <v>0</v>
@@ -6478,7 +6551,8 @@
         <v>0</v>
       </c>
       <c r="R65">
-        <v>45</v>
+        <f t="shared" si="1"/>
+        <v>80</v>
       </c>
     </row>
     <row r="66" customFormat="1" ht="16.5" customHeight="1" spans="1:18">
@@ -6493,10 +6567,10 @@
         <v>264</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G66" s="1">
         <v>2</v>
@@ -6506,7 +6580,7 @@
         <v>300</v>
       </c>
       <c r="J66" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K66" s="1">
         <v>0</v>
@@ -6527,7 +6601,8 @@
         <v>0</v>
       </c>
       <c r="R66">
-        <v>45</v>
+        <f t="shared" si="1"/>
+        <v>50</v>
       </c>
     </row>
     <row r="67" customFormat="1" ht="33.75" customHeight="1" spans="1:18">
@@ -6542,10 +6617,10 @@
         <v>267</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G67" s="1">
         <v>100</v>
@@ -6555,7 +6630,7 @@
         <v>100</v>
       </c>
       <c r="J67" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K67" s="1">
         <v>0</v>
@@ -6576,7 +6651,8 @@
         <v>0</v>
       </c>
       <c r="R67">
-        <v>45</v>
+        <f t="shared" si="1"/>
+        <v>80</v>
       </c>
     </row>
     <row r="68" customFormat="1" ht="16.5" customHeight="1" spans="1:18">
@@ -6591,7 +6667,7 @@
         <v>270</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>271</v>
@@ -6604,7 +6680,7 @@
         <v>300</v>
       </c>
       <c r="J68" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K68" s="1">
         <v>0</v>
@@ -6625,7 +6701,8 @@
         <v>0</v>
       </c>
       <c r="R68">
-        <v>45</v>
+        <f t="shared" si="1"/>
+        <v>50</v>
       </c>
     </row>
     <row r="69" customFormat="1" ht="16.5" customHeight="1" spans="1:18">
@@ -6640,7 +6717,7 @@
         <v>274</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>271</v>
@@ -6653,7 +6730,7 @@
         <v>300</v>
       </c>
       <c r="J69" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K69" s="1">
         <v>0</v>
@@ -6674,7 +6751,8 @@
         <v>0</v>
       </c>
       <c r="R69">
-        <v>45</v>
+        <f t="shared" ref="R69:R86" si="2">VLOOKUP(E69,$T$10:$AB$13,9,FALSE)</f>
+        <v>50</v>
       </c>
     </row>
     <row r="70" customFormat="1" ht="16.5" customHeight="1" spans="1:18">
@@ -6689,7 +6767,7 @@
         <v>277</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>271</v>
@@ -6702,7 +6780,7 @@
         <v>300</v>
       </c>
       <c r="J70" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K70" s="1">
         <v>0</v>
@@ -6723,7 +6801,8 @@
         <v>0</v>
       </c>
       <c r="R70">
-        <v>45</v>
+        <f t="shared" si="2"/>
+        <v>50</v>
       </c>
     </row>
     <row r="71" customFormat="1" ht="16.5" customHeight="1" spans="1:18">
@@ -6738,7 +6817,7 @@
         <v>280</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>271</v>
@@ -6751,7 +6830,7 @@
         <v>300</v>
       </c>
       <c r="J71" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K71" s="1">
         <v>0</v>
@@ -6772,7 +6851,8 @@
         <v>0</v>
       </c>
       <c r="R71">
-        <v>45</v>
+        <f t="shared" si="2"/>
+        <v>50</v>
       </c>
     </row>
     <row r="72" customFormat="1" ht="33.75" customHeight="1" spans="1:18">
@@ -6787,7 +6867,7 @@
         <v>283</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>271</v>
@@ -6800,7 +6880,7 @@
         <v>300</v>
       </c>
       <c r="J72" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K72" s="1">
         <v>0</v>
@@ -6821,7 +6901,8 @@
         <v>0</v>
       </c>
       <c r="R72">
-        <v>45</v>
+        <f t="shared" si="2"/>
+        <v>50</v>
       </c>
     </row>
     <row r="73" customFormat="1" ht="16.5" customHeight="1" spans="1:18">
@@ -6836,7 +6917,7 @@
         <v>286</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>271</v>
@@ -6849,7 +6930,7 @@
         <v>300</v>
       </c>
       <c r="J73" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K73" s="1">
         <v>0</v>
@@ -6870,7 +6951,8 @@
         <v>0</v>
       </c>
       <c r="R73">
-        <v>45</v>
+        <f t="shared" si="2"/>
+        <v>50</v>
       </c>
     </row>
     <row r="74" customFormat="1" ht="16.5" customHeight="1" spans="1:18">
@@ -6885,7 +6967,7 @@
         <v>289</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>271</v>
@@ -6898,7 +6980,7 @@
         <v>300</v>
       </c>
       <c r="J74" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K74" s="1">
         <v>0</v>
@@ -6919,7 +7001,8 @@
         <v>0</v>
       </c>
       <c r="R74">
-        <v>45</v>
+        <f t="shared" si="2"/>
+        <v>50</v>
       </c>
     </row>
     <row r="75" customFormat="1" ht="16.5" customHeight="1" spans="1:18">
@@ -6934,7 +7017,7 @@
         <v>292</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>271</v>
@@ -6947,7 +7030,7 @@
         <v>300</v>
       </c>
       <c r="J75" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K75" s="1">
         <v>0</v>
@@ -6968,7 +7051,8 @@
         <v>0</v>
       </c>
       <c r="R75">
-        <v>45</v>
+        <f t="shared" si="2"/>
+        <v>50</v>
       </c>
     </row>
     <row r="76" customFormat="1" ht="16.5" customHeight="1" spans="1:18">
@@ -6983,7 +7067,7 @@
         <v>295</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>271</v>
@@ -6996,7 +7080,7 @@
         <v>300</v>
       </c>
       <c r="J76" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K76" s="1">
         <v>0</v>
@@ -7017,7 +7101,8 @@
         <v>0</v>
       </c>
       <c r="R76">
-        <v>45</v>
+        <f t="shared" si="2"/>
+        <v>50</v>
       </c>
     </row>
     <row r="77" customFormat="1" ht="16.5" customHeight="1" spans="1:18">
@@ -7035,7 +7120,7 @@
         <v>181</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G77" s="1">
         <v>2</v>
@@ -7066,7 +7151,8 @@
         <v>0</v>
       </c>
       <c r="R77">
-        <v>45</v>
+        <f t="shared" si="2"/>
+        <v>200</v>
       </c>
     </row>
     <row r="78" customFormat="1" ht="33.75" customHeight="1" spans="1:18">
@@ -7084,7 +7170,7 @@
         <v>181</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G78" s="1">
         <v>1.2</v>
@@ -7118,7 +7204,8 @@
         <v>302</v>
       </c>
       <c r="R78">
-        <v>45</v>
+        <f t="shared" si="2"/>
+        <v>200</v>
       </c>
     </row>
     <row r="79" customFormat="1" ht="33.75" customHeight="1" spans="1:18">
@@ -7136,7 +7223,7 @@
         <v>181</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G79" s="1">
         <v>1.2</v>
@@ -7170,7 +7257,8 @@
         <v>302</v>
       </c>
       <c r="R79">
-        <v>45</v>
+        <f t="shared" si="2"/>
+        <v>200</v>
       </c>
     </row>
     <row r="80" customFormat="1" ht="33.75" customHeight="1" spans="1:18">
@@ -7185,10 +7273,10 @@
         <v>308</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G80" s="1">
         <v>0.2</v>
@@ -7198,7 +7286,7 @@
         <v>100</v>
       </c>
       <c r="J80" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K80" s="1">
         <v>0</v>
@@ -7222,7 +7310,8 @@
         <v>302</v>
       </c>
       <c r="R80">
-        <v>45</v>
+        <f t="shared" si="2"/>
+        <v>80</v>
       </c>
     </row>
     <row r="81" customFormat="1" ht="33.75" customHeight="1" spans="1:18">
@@ -7237,10 +7326,10 @@
         <v>311</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G81" s="1">
         <v>10</v>
@@ -7252,7 +7341,7 @@
         <v>100</v>
       </c>
       <c r="J81" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K81" s="1">
         <v>0</v>
@@ -7276,7 +7365,8 @@
         <v>302</v>
       </c>
       <c r="R81">
-        <v>45</v>
+        <f t="shared" si="2"/>
+        <v>80</v>
       </c>
     </row>
     <row r="82" customFormat="1" ht="33.75" customHeight="1" spans="1:18">
@@ -7294,7 +7384,7 @@
         <v>181</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G82" s="1">
         <v>0.2</v>
@@ -7328,7 +7418,8 @@
         <v>316</v>
       </c>
       <c r="R82">
-        <v>45</v>
+        <f t="shared" si="2"/>
+        <v>200</v>
       </c>
     </row>
     <row r="83" customFormat="1" ht="33.75" customHeight="1" spans="1:18">
@@ -7343,10 +7434,10 @@
         <v>319</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G83" s="1">
         <v>10</v>
@@ -7356,7 +7447,7 @@
         <v>100</v>
       </c>
       <c r="J83" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K83" s="1">
         <v>0</v>
@@ -7380,7 +7471,8 @@
         <v>316</v>
       </c>
       <c r="R83">
-        <v>45</v>
+        <f t="shared" si="2"/>
+        <v>80</v>
       </c>
     </row>
     <row r="84" customFormat="1" ht="33.75" customHeight="1" spans="1:18">
@@ -7395,10 +7487,10 @@
         <v>322</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G84" s="1">
         <v>1</v>
@@ -7408,7 +7500,7 @@
         <v>30</v>
       </c>
       <c r="J84" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K84" s="1">
         <v>0</v>
@@ -7432,7 +7524,8 @@
         <v>316</v>
       </c>
       <c r="R84">
-        <v>45</v>
+        <f t="shared" si="2"/>
+        <v>120</v>
       </c>
     </row>
     <row r="85" customFormat="1" ht="33.75" customHeight="1" spans="1:18">
@@ -7447,10 +7540,10 @@
         <v>325</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G85" s="1">
         <v>10</v>
@@ -7462,7 +7555,7 @@
         <v>100</v>
       </c>
       <c r="J85" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K85" s="1">
         <v>0</v>
@@ -7486,7 +7579,8 @@
         <v>316</v>
       </c>
       <c r="R85">
-        <v>45</v>
+        <f t="shared" si="2"/>
+        <v>80</v>
       </c>
     </row>
     <row r="86" customFormat="1" ht="16.5" customHeight="1" spans="1:18">
@@ -7501,10 +7595,10 @@
         <v>329</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G86" s="1">
         <v>10</v>
@@ -7514,7 +7608,7 @@
         <v>100</v>
       </c>
       <c r="J86" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K86" s="1">
         <v>0</v>
@@ -7538,7 +7632,8 @@
         <v>316</v>
       </c>
       <c r="R86">
-        <v>45</v>
+        <f t="shared" si="2"/>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -7652,43 +7747,43 @@
     </row>
     <row r="3" ht="16.5" customHeight="1" spans="1:13">
       <c r="A3" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J3" s="7" t="s">
         <v>336</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" ht="33.75" customHeight="1" spans="2:13">
@@ -8432,7 +8527,7 @@
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
       <c r="D9" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>431</v>
@@ -8452,7 +8547,7 @@
         <v>432</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H10" s="1">
         <v>9</v>

--- a/GourmetProject/GameConfig/Datas/item.xlsx
+++ b/GourmetProject/GameConfig/Datas/item.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="被动道具" sheetId="1" r:id="R0e59fa5c040845ea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主动道具" sheetId="2" r:id="R5a17a7dd50b54da9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="道具设计" sheetId="3" r:id="R2725ff8739254b57"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="被动道具" sheetId="1" r:id="Rfc2a5b19df394865"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主动道具" sheetId="2" r:id="R3fd8ff8f6f154e9c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="道具设计" sheetId="3" r:id="R63500342532b42d4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2158,7 +2158,7 @@
       </x:c>
       <x:c r="Z11" t="n">
         <x:f>COUNTIF($E$4:$E$86,T11)</x:f>
-        <x:v>40</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="AB11">
         <x:v>80</x:v>
@@ -2225,7 +2225,7 @@
       </x:c>
       <x:c r="Z12" t="n">
         <x:f>COUNTIF($E$4:$E$86,T12)</x:f>
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="AB12">
         <x:v>120</x:v>
@@ -3033,14 +3033,14 @@
     <x:row r="28" ht="33.75" customHeight="1">
       <x:c r="A28" s="1"/>
       <x:c r="B28" s="1" t="str">
-        <x:v>item_free_move_first</x:v>
+        <x:v>item_gold_on_shop</x:v>
       </x:c>
       <x:c r="C28" s="1" t="str">
-        <x:v>免费调整</x:v>
+        <x:v>商会返利</x:v>
       </x:c>
       <x:c r="D28" s="8" t="str">
-        <x:v>每局第1次上菜时
-可不消耗修正次数移动</x:v>
+        <x:v>进入商店时
+获得10金币</x:v>
       </x:c>
       <x:c r="E28" s="1" t="str">
         <x:v>Uncommon</x:v>
@@ -3049,7 +3049,7 @@
         <x:v>None</x:v>
       </x:c>
       <x:c r="G28" s="1" t="n">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H28" s="1"/>
       <x:c r="I28" s="1" t="n">
@@ -3085,13 +3085,14 @@
     <x:row r="29" ht="33.75" customHeight="1">
       <x:c r="A29" s="1"/>
       <x:c r="B29" s="1" t="str">
-        <x:v>item_adjust_plus1</x:v>
+        <x:v>item_extra_interest</x:v>
       </x:c>
       <x:c r="C29" s="1" t="str">
-        <x:v>熟练的手</x:v>
+        <x:v>复利账户</x:v>
       </x:c>
       <x:c r="D29" s="8" t="str">
-        <x:v>调整次数+1</x:v>
+        <x:v>每周结束时
+额外执行1次利息结算</x:v>
       </x:c>
       <x:c r="E29" s="1" t="str">
         <x:v>Uncommon</x:v>
@@ -3136,15 +3137,13 @@
     <x:row r="30" ht="33.75" customHeight="1">
       <x:c r="A30" s="1"/>
       <x:c r="B30" s="1" t="str">
-        <x:v>item_adjust_to_mult</x:v>
+        <x:v>item_interest_cap</x:v>
       </x:c>
       <x:c r="C30" s="1" t="str">
-        <x:v>节俭加成</x:v>
+        <x:v>高息账户</x:v>
       </x:c>
       <x:c r="D30" s="8" t="str">
-        <x:v>结算开始
-每个未使用的调整次数
-使所有食物倍率+0.1</x:v>
+        <x:v>利息上限扩展到40金币</x:v>
       </x:c>
       <x:c r="E30" s="1" t="str">
         <x:v>Rare</x:v>
@@ -3153,7 +3152,7 @@
         <x:v>None</x:v>
       </x:c>
       <x:c r="G30" s="1" t="n">
-        <x:v>0.1</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H30" s="1"/>
       <x:c r="I30" s="1" t="n">
@@ -3189,14 +3188,14 @@
     <x:row r="31" ht="16.5" customHeight="1">
       <x:c r="A31" s="1"/>
       <x:c r="B31" s="1" t="str">
-        <x:v>item_adjust_to_gold</x:v>
+        <x:v>item_loan</x:v>
       </x:c>
       <x:c r="C31" s="1" t="str">
-        <x:v>变卖技巧</x:v>
+        <x:v>高利贷</x:v>
       </x:c>
       <x:c r="D31" s="1" t="str">
-        <x:v>每个未使用的调整次数
-获得5金币</x:v>
+        <x:v>临时获得200金币
+下一周开始失去400金币</x:v>
       </x:c>
       <x:c r="E31" s="1" t="str">
         <x:v>Uncommon</x:v>
@@ -3205,9 +3204,11 @@
         <x:v>None</x:v>
       </x:c>
       <x:c r="G31" s="1" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H31" s="1"/>
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="H31" s="1" t="str">
+        <x:v>repay:600</x:v>
+      </x:c>
       <x:c r="I31" s="1" t="n">
         <x:v>100</x:v>
       </x:c>
@@ -3241,14 +3242,13 @@
     <x:row r="32" ht="51">
       <x:c r="A32" s="1"/>
       <x:c r="B32" s="1" t="str">
-        <x:v>item_gold_on_shop</x:v>
+        <x:v>item_timeline_random</x:v>
       </x:c>
       <x:c r="C32" s="1" t="str">
-        <x:v>商会返利</x:v>
+        <x:v>命运骰子</x:v>
       </x:c>
       <x:c r="D32" s="8" t="str">
-        <x:v>进入商店时
-获得10金币</x:v>
+        <x:v>打乱时间轴的节点事件</x:v>
       </x:c>
       <x:c r="E32" s="1" t="str">
         <x:v>Uncommon</x:v>
@@ -3257,7 +3257,7 @@
         <x:v>None</x:v>
       </x:c>
       <x:c r="G32" s="1" t="n">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H32" s="1"/>
       <x:c r="I32" s="1" t="n">
@@ -3293,14 +3293,13 @@
     <x:row r="33" ht="33.75" customHeight="1">
       <x:c r="A33" s="1"/>
       <x:c r="B33" s="1" t="str">
-        <x:v>item_extra_interest</x:v>
+        <x:v>item_extra_day</x:v>
       </x:c>
       <x:c r="C33" s="1" t="str">
-        <x:v>复利账户</x:v>
+        <x:v>加班一天</x:v>
       </x:c>
       <x:c r="D33" s="8" t="str">
-        <x:v>每周结束时
-额外执行1次利息结算</x:v>
+        <x:v>盛宴延后一天</x:v>
       </x:c>
       <x:c r="E33" s="1" t="str">
         <x:v>Uncommon</x:v>
@@ -3345,29 +3344,29 @@
     <x:row r="34" ht="33.75" customHeight="1">
       <x:c r="A34" s="1"/>
       <x:c r="B34" s="1" t="str">
-        <x:v>item_interest_cap</x:v>
+        <x:v>item_week_minus</x:v>
       </x:c>
       <x:c r="C34" s="1" t="str">
-        <x:v>高息账户</x:v>
+        <x:v>时光倒流</x:v>
       </x:c>
       <x:c r="D34" s="8" t="str">
-        <x:v>利息上限扩展到40金币</x:v>
+        <x:v>周数-1</x:v>
       </x:c>
       <x:c r="E34" s="1" t="str">
-        <x:v>Rare</x:v>
+        <x:v>Epic</x:v>
       </x:c>
       <x:c r="F34" s="1" t="str">
         <x:v>None</x:v>
       </x:c>
       <x:c r="G34" s="1" t="n">
-        <x:v>10</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H34" s="1"/>
       <x:c r="I34" s="1" t="n">
-        <x:v>30</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="J34" s="1" t="str">
-        <x:v>30,80</x:v>
+        <x:v>40,80</x:v>
       </x:c>
       <x:c r="K34" s="1" t="n">
         <x:v>0</x:v>
@@ -3390,20 +3389,20 @@
       <x:c r="Q34"/>
       <x:c r="R34" t="n">
         <x:f t="shared" si="0"/>
-        <x:v>120</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="33.75" customHeight="1">
       <x:c r="A35" s="1"/>
       <x:c r="B35" s="1" t="str">
-        <x:v>item_loan</x:v>
+        <x:v>item_add_reward_node</x:v>
       </x:c>
       <x:c r="C35" s="1" t="str">
-        <x:v>高利贷</x:v>
+        <x:v>额外奖励</x:v>
       </x:c>
       <x:c r="D35" s="8" t="str">
-        <x:v>临时获得200金币
-下一周开始失去400金币</x:v>
+        <x:v>增加一个奖励节点到
+未来时间轴上</x:v>
       </x:c>
       <x:c r="E35" s="1" t="str">
         <x:v>Uncommon</x:v>
@@ -3412,11 +3411,9 @@
         <x:v>None</x:v>
       </x:c>
       <x:c r="G35" s="1" t="n">
-        <x:v>300</x:v>
-      </x:c>
-      <x:c r="H35" s="1" t="str">
-        <x:v>repay:600</x:v>
-      </x:c>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H35" s="1"/>
       <x:c r="I35" s="1" t="n">
         <x:v>100</x:v>
       </x:c>
@@ -3450,13 +3447,14 @@
     <x:row r="36" ht="16.5" customHeight="1">
       <x:c r="A36" s="1"/>
       <x:c r="B36" s="1" t="str">
-        <x:v>item_timeline_random</x:v>
+        <x:v>item_add_interest_node</x:v>
       </x:c>
       <x:c r="C36" s="1" t="str">
-        <x:v>命运骰子</x:v>
+        <x:v>额外利息节点</x:v>
       </x:c>
       <x:c r="D36" s="1" t="str">
-        <x:v>打乱时间轴的节点事件</x:v>
+        <x:v>增加一个利息节点
+到未来时间轴上</x:v>
       </x:c>
       <x:c r="E36" s="1" t="str">
         <x:v>Uncommon</x:v>
@@ -3465,7 +3463,7 @@
         <x:v>None</x:v>
       </x:c>
       <x:c r="G36" s="1" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H36" s="1"/>
       <x:c r="I36" s="1" t="n">
@@ -3501,13 +3499,14 @@
     <x:row r="37" ht="33.75" customHeight="1">
       <x:c r="A37" s="1"/>
       <x:c r="B37" s="1" t="str">
-        <x:v>item_extra_day</x:v>
+        <x:v>item_every3_next_mult</x:v>
       </x:c>
       <x:c r="C37" s="1" t="str">
-        <x:v>加班一天</x:v>
+        <x:v>节奏大师</x:v>
       </x:c>
       <x:c r="D37" s="8" t="str">
-        <x:v>盛宴延后一天</x:v>
+        <x:v>每上3个食物后
+下个食物倍率+1</x:v>
       </x:c>
       <x:c r="E37" s="1" t="str">
         <x:v>Uncommon</x:v>
@@ -3518,7 +3517,9 @@
       <x:c r="G37" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H37" s="1"/>
+      <x:c r="H37" s="1" t="str">
+        <x:v>every:3</x:v>
+      </x:c>
       <x:c r="I37" s="1" t="n">
         <x:v>100</x:v>
       </x:c>
@@ -3552,29 +3553,32 @@
     <x:row r="38" ht="16.5" customHeight="1">
       <x:c r="A38" s="1"/>
       <x:c r="B38" s="1" t="str">
-        <x:v>item_week_minus</x:v>
+        <x:v>item_first_+2</x:v>
       </x:c>
       <x:c r="C38" s="1" t="str">
-        <x:v>时光倒流</x:v>
+        <x:v>开门红</x:v>
       </x:c>
       <x:c r="D38" s="1" t="str">
-        <x:v>周数-1</x:v>
+        <x:v>首个上的食物
+倍率+2</x:v>
       </x:c>
       <x:c r="E38" s="1" t="str">
-        <x:v>Epic</x:v>
+        <x:v>Common</x:v>
       </x:c>
       <x:c r="F38" s="1" t="str">
         <x:v>None</x:v>
       </x:c>
       <x:c r="G38" s="1" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H38" s="1"/>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H38" s="1" t="str">
+        <x:v>index:1</x:v>
+      </x:c>
       <x:c r="I38" s="1" t="n">
-        <x:v>10</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="J38" s="1" t="str">
-        <x:v>40,80</x:v>
+        <x:v>10,80</x:v>
       </x:c>
       <x:c r="K38" s="1" t="n">
         <x:v>0</x:v>
@@ -3597,36 +3601,38 @@
       <x:c r="Q38"/>
       <x:c r="R38" t="n">
         <x:f t="shared" si="1"/>
-        <x:v>200</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="16.5" customHeight="1">
       <x:c r="A39" s="1"/>
       <x:c r="B39" s="1" t="str">
-        <x:v>item_add_reward_node</x:v>
+        <x:v>item_last_+2</x:v>
       </x:c>
       <x:c r="C39" s="1" t="str">
-        <x:v>额外奖励</x:v>
+        <x:v>压轴好戏</x:v>
       </x:c>
       <x:c r="D39" s="1" t="str">
-        <x:v>增加一个奖励节点到
-未来时间轴上</x:v>
+        <x:v>最后上的食物
+倍率+2</x:v>
       </x:c>
       <x:c r="E39" s="1" t="str">
-        <x:v>Uncommon</x:v>
+        <x:v>Common</x:v>
       </x:c>
       <x:c r="F39" s="1" t="str">
         <x:v>None</x:v>
       </x:c>
       <x:c r="G39" s="1" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H39" s="1"/>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H39" s="1" t="str">
+        <x:v>index:-1</x:v>
+      </x:c>
       <x:c r="I39" s="1" t="n">
-        <x:v>100</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="J39" s="1" t="str">
-        <x:v>20,80</x:v>
+        <x:v>10,80</x:v>
       </x:c>
       <x:c r="K39" s="1" t="n">
         <x:v>0</x:v>
@@ -3649,20 +3655,19 @@
       <x:c r="Q39"/>
       <x:c r="R39" t="n">
         <x:f t="shared" si="1"/>
-        <x:v>80</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="16.5" customHeight="1">
       <x:c r="A40" s="1"/>
       <x:c r="B40" s="1" t="str">
-        <x:v>item_add_interest_node</x:v>
+        <x:v>item_extra_active_slots</x:v>
       </x:c>
       <x:c r="C40" s="1" t="str">
-        <x:v>额外利息节点</x:v>
+        <x:v>工具箱</x:v>
       </x:c>
       <x:c r="D40" s="1" t="str">
-        <x:v>增加一个利息节点
-到未来时间轴上</x:v>
+        <x:v>增加2个主动道具栏</x:v>
       </x:c>
       <x:c r="E40" s="1" t="str">
         <x:v>Uncommon</x:v>
@@ -3671,7 +3676,7 @@
         <x:v>None</x:v>
       </x:c>
       <x:c r="G40" s="1" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H40" s="1"/>
       <x:c r="I40" s="1" t="n">
@@ -3707,14 +3712,14 @@
     <x:row r="41" ht="33.75" customHeight="1">
       <x:c r="A41" s="1"/>
       <x:c r="B41" s="1" t="str">
-        <x:v>item_every3_next_mult</x:v>
+        <x:v>item_gold_on_active</x:v>
       </x:c>
       <x:c r="C41" s="1" t="str">
-        <x:v>节奏大师</x:v>
+        <x:v>以用换钱</x:v>
       </x:c>
       <x:c r="D41" s="8" t="str">
-        <x:v>每上3个食物后
-下个食物倍率+1</x:v>
+        <x:v>使用主动道具时
+获得5金币</x:v>
       </x:c>
       <x:c r="E41" s="1" t="str">
         <x:v>Uncommon</x:v>
@@ -3723,11 +3728,9 @@
         <x:v>None</x:v>
       </x:c>
       <x:c r="G41" s="1" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H41" s="1" t="str">
-        <x:v>every:3</x:v>
-      </x:c>
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H41" s="1"/>
       <x:c r="I41" s="1" t="n">
         <x:v>100</x:v>
       </x:c>
@@ -3761,32 +3764,30 @@
     <x:row r="42" ht="33.75" customHeight="1">
       <x:c r="A42" s="1"/>
       <x:c r="B42" s="1" t="str">
-        <x:v>item_first_+2</x:v>
+        <x:v>item_block_active</x:v>
       </x:c>
       <x:c r="C42" s="1" t="str">
-        <x:v>开门红</x:v>
+        <x:v>极简主义</x:v>
       </x:c>
       <x:c r="D42" s="8" t="str">
-        <x:v>首个上的食物
-倍率+2</x:v>
+        <x:v>无法再获得主动道具
+立即获得600金币</x:v>
       </x:c>
       <x:c r="E42" s="1" t="str">
-        <x:v>Common</x:v>
+        <x:v>Uncommon</x:v>
       </x:c>
       <x:c r="F42" s="1" t="str">
         <x:v>None</x:v>
       </x:c>
       <x:c r="G42" s="1" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H42" s="1" t="str">
-        <x:v>index:1</x:v>
-      </x:c>
+        <x:v>600</x:v>
+      </x:c>
+      <x:c r="H42" s="1"/>
       <x:c r="I42" s="1" t="n">
-        <x:v>300</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="J42" s="1" t="str">
-        <x:v>10,80</x:v>
+        <x:v>20,80</x:v>
       </x:c>
       <x:c r="K42" s="1" t="n">
         <x:v>0</x:v>
@@ -3809,23 +3810,22 @@
       <x:c r="Q42"/>
       <x:c r="R42" t="n">
         <x:f t="shared" si="1"/>
-        <x:v>50</x:v>
+        <x:v>80</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="33.75" customHeight="1">
       <x:c r="A43" s="1"/>
       <x:c r="B43" s="1" t="str">
-        <x:v>item_last_+2</x:v>
+        <x:v>item_flavor_enhance</x:v>
       </x:c>
       <x:c r="C43" s="1" t="str">
-        <x:v>压轴好戏</x:v>
+        <x:v>风味喷雾</x:v>
       </x:c>
       <x:c r="D43" s="8" t="str">
-        <x:v>最后上的食物
-倍率+2</x:v>
+        <x:v>为2个食物添加随机风味</x:v>
       </x:c>
       <x:c r="E43" s="1" t="str">
-        <x:v>Common</x:v>
+        <x:v>Uncommon</x:v>
       </x:c>
       <x:c r="F43" s="1" t="str">
         <x:v>None</x:v>
@@ -3833,14 +3833,12 @@
       <x:c r="G43" s="1" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="H43" s="1" t="str">
-        <x:v>index:-1</x:v>
-      </x:c>
+      <x:c r="H43" s="1"/>
       <x:c r="I43" s="1" t="n">
-        <x:v>300</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="J43" s="1" t="str">
-        <x:v>10,80</x:v>
+        <x:v>20,80</x:v>
       </x:c>
       <x:c r="K43" s="1" t="n">
         <x:v>0</x:v>
@@ -3863,19 +3861,20 @@
       <x:c r="Q43"/>
       <x:c r="R43" t="n">
         <x:f t="shared" si="1"/>
-        <x:v>50</x:v>
+        <x:v>80</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="33.75" customHeight="1">
       <x:c r="A44" s="1"/>
       <x:c r="B44" s="1" t="str">
-        <x:v>item_extra_active_slots</x:v>
+        <x:v>item_flavor_remove_gold</x:v>
       </x:c>
       <x:c r="C44" s="1" t="str">
-        <x:v>工具箱</x:v>
+        <x:v>风味回收</x:v>
       </x:c>
       <x:c r="D44" s="8" t="str">
-        <x:v>增加2个主动道具栏</x:v>
+        <x:v>移除1个食物的风味
+获得200金币</x:v>
       </x:c>
       <x:c r="E44" s="1" t="str">
         <x:v>Uncommon</x:v>
@@ -3884,7 +3883,7 @@
         <x:v>None</x:v>
       </x:c>
       <x:c r="G44" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="H44" s="1"/>
       <x:c r="I44" s="1" t="n">
@@ -3920,14 +3919,14 @@
     <x:row r="45" ht="33.75" customHeight="1">
       <x:c r="A45" s="1"/>
       <x:c r="B45" s="1" t="str">
-        <x:v>item_gold_on_active</x:v>
+        <x:v>item_flavor_remove_double</x:v>
       </x:c>
       <x:c r="C45" s="1" t="str">
-        <x:v>以用换钱</x:v>
+        <x:v>风味浓缩</x:v>
       </x:c>
       <x:c r="D45" s="8" t="str">
-        <x:v>使用主动道具时
-获得5金币</x:v>
+        <x:v>移除1个食物的风味
+其分数翻倍</x:v>
       </x:c>
       <x:c r="E45" s="1" t="str">
         <x:v>Uncommon</x:v>
@@ -3936,7 +3935,7 @@
         <x:v>None</x:v>
       </x:c>
       <x:c r="G45" s="1" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H45" s="1"/>
       <x:c r="I45" s="1" t="n">
@@ -3972,30 +3971,29 @@
     <x:row r="46" ht="16.5" customHeight="1">
       <x:c r="A46" s="1"/>
       <x:c r="B46" s="1" t="str">
-        <x:v>item_block_active</x:v>
+        <x:v>item_flavor_double_slot</x:v>
       </x:c>
       <x:c r="C46" s="1" t="str">
-        <x:v>极简主义</x:v>
+        <x:v>双重风味</x:v>
       </x:c>
       <x:c r="D46" s="1" t="str">
-        <x:v>无法再获得主动道具
-立即获得600金币</x:v>
+        <x:v>食物风味上限变为2</x:v>
       </x:c>
       <x:c r="E46" s="1" t="str">
-        <x:v>Uncommon</x:v>
+        <x:v>Epic</x:v>
       </x:c>
       <x:c r="F46" s="1" t="str">
         <x:v>None</x:v>
       </x:c>
       <x:c r="G46" s="1" t="n">
-        <x:v>600</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H46" s="1"/>
       <x:c r="I46" s="1" t="n">
-        <x:v>100</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="J46" s="1" t="str">
-        <x:v>20,80</x:v>
+        <x:v>40,80</x:v>
       </x:c>
       <x:c r="K46" s="1" t="n">
         <x:v>0</x:v>
@@ -4018,19 +4016,20 @@
       <x:c r="Q46"/>
       <x:c r="R46" t="n">
         <x:f t="shared" si="1"/>
-        <x:v>80</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="33.75" customHeight="1">
       <x:c r="A47" s="1"/>
       <x:c r="B47" s="1" t="str">
-        <x:v>item_flavor_enhance</x:v>
+        <x:v>item_flavor_contagion</x:v>
       </x:c>
       <x:c r="C47" s="1" t="str">
-        <x:v>风味喷雾</x:v>
+        <x:v>风味传染</x:v>
       </x:c>
       <x:c r="D47" s="8" t="str">
-        <x:v>为2个食物添加随机风味</x:v>
+        <x:v>使1个食物
+拥有菜谱中另1个食物的风味</x:v>
       </x:c>
       <x:c r="E47" s="1" t="str">
         <x:v>Uncommon</x:v>
@@ -4039,7 +4038,7 @@
         <x:v>None</x:v>
       </x:c>
       <x:c r="G47" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H47" s="1"/>
       <x:c r="I47" s="1" t="n">
@@ -4075,14 +4074,14 @@
     <x:row r="48" ht="33.75" customHeight="1">
       <x:c r="A48" s="1"/>
       <x:c r="B48" s="1" t="str">
-        <x:v>item_flavor_remove_gold</x:v>
+        <x:v>item_celltag_enhance</x:v>
       </x:c>
       <x:c r="C48" s="1" t="str">
-        <x:v>风味回收</x:v>
+        <x:v>标签强化</x:v>
       </x:c>
       <x:c r="D48" s="8" t="str">
-        <x:v>移除1个食物的风味
-获得200金币</x:v>
+        <x:v>为2个餐桌格子
+强化随机材质</x:v>
       </x:c>
       <x:c r="E48" s="1" t="str">
         <x:v>Uncommon</x:v>
@@ -4091,7 +4090,7 @@
         <x:v>None</x:v>
       </x:c>
       <x:c r="G48" s="1" t="n">
-        <x:v>200</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H48" s="1"/>
       <x:c r="I48" s="1" t="n">
@@ -4127,14 +4126,14 @@
     <x:row r="49" ht="16.5" customHeight="1">
       <x:c r="A49" s="1"/>
       <x:c r="B49" s="1" t="str">
-        <x:v>item_flavor_remove_double</x:v>
+        <x:v>item_celltag_contagion</x:v>
       </x:c>
       <x:c r="C49" s="1" t="str">
-        <x:v>风味浓缩</x:v>
+        <x:v>标签传染</x:v>
       </x:c>
       <x:c r="D49" s="1" t="str">
-        <x:v>移除1个食物的风味
-其分数翻倍</x:v>
+        <x:v>使1个格子
+拥有另1个格子的材质</x:v>
       </x:c>
       <x:c r="E49" s="1" t="str">
         <x:v>Uncommon</x:v>
@@ -4143,7 +4142,7 @@
         <x:v>None</x:v>
       </x:c>
       <x:c r="G49" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H49" s="1"/>
       <x:c r="I49" s="1" t="n">
@@ -4179,29 +4178,30 @@
     <x:row r="50" ht="33.75" customHeight="1">
       <x:c r="A50" s="1"/>
       <x:c r="B50" s="1" t="str">
-        <x:v>item_flavor_double_slot</x:v>
+        <x:v>item_lucky_guarantee</x:v>
       </x:c>
       <x:c r="C50" s="1" t="str">
-        <x:v>双重风味</x:v>
+        <x:v>好运连连</x:v>
       </x:c>
       <x:c r="D50" s="8" t="str">
-        <x:v>食物风味上限变为2</x:v>
+        <x:v>经历4个事件后
+下个事件一定为奖励</x:v>
       </x:c>
       <x:c r="E50" s="1" t="str">
-        <x:v>Epic</x:v>
+        <x:v>Rare</x:v>
       </x:c>
       <x:c r="F50" s="1" t="str">
         <x:v>None</x:v>
       </x:c>
       <x:c r="G50" s="1" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H50" s="1"/>
       <x:c r="I50" s="1" t="n">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="J50" s="1" t="str">
-        <x:v>40,80</x:v>
+        <x:v>30,80</x:v>
       </x:c>
       <x:c r="K50" s="1" t="n">
         <x:v>0</x:v>
@@ -4224,36 +4224,35 @@
       <x:c r="Q50"/>
       <x:c r="R50" t="n">
         <x:f t="shared" si="1"/>
-        <x:v>200</x:v>
+        <x:v>120</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="33.75" customHeight="1">
       <x:c r="A51" s="1"/>
       <x:c r="B51" s="1" t="str">
-        <x:v>item_flavor_contagion</x:v>
+        <x:v>item_lucky_chance</x:v>
       </x:c>
       <x:c r="C51" s="1" t="str">
-        <x:v>风味传染</x:v>
+        <x:v>幸运符</x:v>
       </x:c>
       <x:c r="D51" s="8" t="str">
-        <x:v>使1个食物
-拥有菜谱中另1个食物的风味</x:v>
+        <x:v>更容易在事件中遇到奖励</x:v>
       </x:c>
       <x:c r="E51" s="1" t="str">
-        <x:v>Uncommon</x:v>
+        <x:v>Rare</x:v>
       </x:c>
       <x:c r="F51" s="1" t="str">
         <x:v>None</x:v>
       </x:c>
       <x:c r="G51" s="1" t="n">
-        <x:v>1</x:v>
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="H51" s="1"/>
       <x:c r="I51" s="1" t="n">
-        <x:v>100</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="J51" s="1" t="str">
-        <x:v>20,80</x:v>
+        <x:v>30,80</x:v>
       </x:c>
       <x:c r="K51" s="1" t="n">
         <x:v>0</x:v>
@@ -4276,36 +4275,35 @@
       <x:c r="Q51"/>
       <x:c r="R51" t="n">
         <x:f t="shared" si="1"/>
-        <x:v>80</x:v>
+        <x:v>120</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="16.5" customHeight="1">
       <x:c r="A52" s="1"/>
       <x:c r="B52" s="1" t="str">
-        <x:v>item_celltag_enhance</x:v>
+        <x:v>item_more_events</x:v>
       </x:c>
       <x:c r="C52" s="1" t="str">
-        <x:v>标签强化</x:v>
+        <x:v>热闹街区</x:v>
       </x:c>
       <x:c r="D52" s="1" t="str">
-        <x:v>为2个餐桌格子
-强化随机材质</x:v>
+        <x:v>更容易遇到事件</x:v>
       </x:c>
       <x:c r="E52" s="1" t="str">
-        <x:v>Uncommon</x:v>
+        <x:v>Common</x:v>
       </x:c>
       <x:c r="F52" s="1" t="str">
         <x:v>None</x:v>
       </x:c>
       <x:c r="G52" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="H52" s="1"/>
       <x:c r="I52" s="1" t="n">
-        <x:v>100</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="J52" s="1" t="str">
-        <x:v>20,80</x:v>
+        <x:v>10,80</x:v>
       </x:c>
       <x:c r="K52" s="1" t="n">
         <x:v>0</x:v>
@@ -4328,36 +4326,36 @@
       <x:c r="Q52"/>
       <x:c r="R52" t="n">
         <x:f t="shared" si="1"/>
-        <x:v>80</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="33.75" customHeight="1">
       <x:c r="A53" s="1"/>
       <x:c r="B53" s="1" t="str">
-        <x:v>item_celltag_contagion</x:v>
+        <x:v>item_gold_on_event</x:v>
       </x:c>
       <x:c r="C53" s="1" t="str">
-        <x:v>标签传染</x:v>
+        <x:v>事件红包</x:v>
       </x:c>
       <x:c r="D53" s="8" t="str">
-        <x:v>使1个格子
-拥有另1个格子的材质</x:v>
+        <x:v>经历1个事件
+获得10金币</x:v>
       </x:c>
       <x:c r="E53" s="1" t="str">
-        <x:v>Uncommon</x:v>
+        <x:v>Common</x:v>
       </x:c>
       <x:c r="F53" s="1" t="str">
         <x:v>None</x:v>
       </x:c>
       <x:c r="G53" s="1" t="n">
-        <x:v>1</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H53" s="1"/>
       <x:c r="I53" s="1" t="n">
-        <x:v>100</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="J53" s="1" t="str">
-        <x:v>20,80</x:v>
+        <x:v>10,80</x:v>
       </x:c>
       <x:c r="K53" s="1" t="n">
         <x:v>0</x:v>
@@ -4380,20 +4378,19 @@
       <x:c r="Q53"/>
       <x:c r="R53" t="n">
         <x:f t="shared" si="1"/>
-        <x:v>80</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="33.75" customHeight="1">
       <x:c r="A54" s="1"/>
       <x:c r="B54" s="1" t="str">
-        <x:v>item_lucky_guarantee</x:v>
+        <x:v>item_shop_restock</x:v>
       </x:c>
       <x:c r="C54" s="1" t="str">
-        <x:v>好运连连</x:v>
+        <x:v>自动补货</x:v>
       </x:c>
       <x:c r="D54" s="8" t="str">
-        <x:v>经历4个事件后
-下个事件一定为奖励</x:v>
+        <x:v>商店会自动补货</x:v>
       </x:c>
       <x:c r="E54" s="1" t="str">
         <x:v>Rare</x:v>
@@ -4402,7 +4399,7 @@
         <x:v>None</x:v>
       </x:c>
       <x:c r="G54" s="1" t="n">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H54" s="1"/>
       <x:c r="I54" s="1" t="n">
@@ -4438,29 +4435,30 @@
     <x:row r="55" ht="33.75" customHeight="1">
       <x:c r="A55" s="1"/>
       <x:c r="B55" s="1" t="str">
-        <x:v>item_lucky_chance</x:v>
+        <x:v>item_choice_count_plus1</x:v>
       </x:c>
       <x:c r="C55" s="1" t="str">
-        <x:v>幸运符</x:v>
+        <x:v>琳琅满目</x:v>
       </x:c>
       <x:c r="D55" s="8" t="str">
-        <x:v>更容易在事件中遇到奖励</x:v>
+        <x:v>选择食物时
+可选数量+1</x:v>
       </x:c>
       <x:c r="E55" s="1" t="str">
-        <x:v>Rare</x:v>
+        <x:v>Uncommon</x:v>
       </x:c>
       <x:c r="F55" s="1" t="str">
         <x:v>None</x:v>
       </x:c>
       <x:c r="G55" s="1" t="n">
-        <x:v>0.2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H55" s="1"/>
       <x:c r="I55" s="1" t="n">
-        <x:v>30</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="J55" s="1" t="str">
-        <x:v>30,80</x:v>
+        <x:v>20,80</x:v>
       </x:c>
       <x:c r="K55" s="1" t="n">
         <x:v>0</x:v>
@@ -4483,35 +4481,36 @@
       <x:c r="Q55"/>
       <x:c r="R55" t="n">
         <x:f t="shared" si="1"/>
-        <x:v>120</x:v>
+        <x:v>80</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="33.75" customHeight="1">
       <x:c r="A56" s="1"/>
       <x:c r="B56" s="1" t="str">
-        <x:v>item_more_events</x:v>
+        <x:v>item_choice_times_plus1</x:v>
       </x:c>
       <x:c r="C56" s="1" t="str">
-        <x:v>热闹街区</x:v>
+        <x:v>细嚼慢咽</x:v>
       </x:c>
       <x:c r="D56" s="8" t="str">
-        <x:v>更容易遇到事件</x:v>
+        <x:v>选择食物时
+可选次数+1，可选数量-1</x:v>
       </x:c>
       <x:c r="E56" s="1" t="str">
-        <x:v>Common</x:v>
+        <x:v>Rare</x:v>
       </x:c>
       <x:c r="F56" s="1" t="str">
         <x:v>None</x:v>
       </x:c>
       <x:c r="G56" s="1" t="n">
-        <x:v>0.2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H56" s="1"/>
       <x:c r="I56" s="1" t="n">
-        <x:v>300</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="J56" s="1" t="str">
-        <x:v>10,80</x:v>
+        <x:v>30,80</x:v>
       </x:c>
       <x:c r="K56" s="1" t="n">
         <x:v>0</x:v>
@@ -4534,36 +4533,38 @@
       <x:c r="Q56"/>
       <x:c r="R56" t="n">
         <x:f t="shared" si="1"/>
-        <x:v>50</x:v>
+        <x:v>120</x:v>
       </x:c>
     </x:row>
     <x:row r="57" ht="16.5" customHeight="1">
       <x:c r="A57" s="1"/>
       <x:c r="B57" s="1" t="str">
-        <x:v>item_gold_on_event</x:v>
+        <x:v>item_extra_food_choice</x:v>
       </x:c>
       <x:c r="C57" s="1" t="str">
-        <x:v>事件红包</x:v>
+        <x:v>加餐</x:v>
       </x:c>
       <x:c r="D57" s="1" t="str">
-        <x:v>经历1个事件
-获得10金币</x:v>
+        <x:v>每6次普通美食
+额外获得3选一美食</x:v>
       </x:c>
       <x:c r="E57" s="1" t="str">
-        <x:v>Common</x:v>
+        <x:v>Uncommon</x:v>
       </x:c>
       <x:c r="F57" s="1" t="str">
         <x:v>None</x:v>
       </x:c>
       <x:c r="G57" s="1" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="H57" s="1"/>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H57" s="1" t="str">
+        <x:v>every:6</x:v>
+      </x:c>
       <x:c r="I57" s="1" t="n">
-        <x:v>300</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="J57" s="1" t="str">
-        <x:v>10,80</x:v>
+        <x:v>20,80</x:v>
       </x:c>
       <x:c r="K57" s="1" t="n">
         <x:v>0</x:v>
@@ -4586,22 +4587,23 @@
       <x:c r="Q57"/>
       <x:c r="R57" t="n">
         <x:f t="shared" si="1"/>
-        <x:v>50</x:v>
+        <x:v>80</x:v>
       </x:c>
     </x:row>
     <x:row r="58" ht="16.5" customHeight="1">
       <x:c r="A58" s="1"/>
       <x:c r="B58" s="1" t="str">
-        <x:v>item_shop_restock</x:v>
+        <x:v>item_extra_item_choice</x:v>
       </x:c>
       <x:c r="C58" s="1" t="str">
-        <x:v>自动补货</x:v>
+        <x:v>加料</x:v>
       </x:c>
       <x:c r="D58" s="1" t="str">
-        <x:v>商店会自动补货</x:v>
+        <x:v>每4次超级美食
+额外获得多选一道具</x:v>
       </x:c>
       <x:c r="E58" s="1" t="str">
-        <x:v>Rare</x:v>
+        <x:v>Uncommon</x:v>
       </x:c>
       <x:c r="F58" s="1" t="str">
         <x:v>None</x:v>
@@ -4609,12 +4611,14 @@
       <x:c r="G58" s="1" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H58" s="1"/>
+      <x:c r="H58" s="1" t="str">
+        <x:v>every:4</x:v>
+      </x:c>
       <x:c r="I58" s="1" t="n">
-        <x:v>30</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="J58" s="1" t="str">
-        <x:v>30,80</x:v>
+        <x:v>20,80</x:v>
       </x:c>
       <x:c r="K58" s="1" t="n">
         <x:v>0</x:v>
@@ -4637,20 +4641,19 @@
       <x:c r="Q58"/>
       <x:c r="R58" t="n">
         <x:f t="shared" si="1"/>
-        <x:v>120</x:v>
+        <x:v>80</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="33.75" customHeight="1">
       <x:c r="A59" s="1"/>
       <x:c r="B59" s="1" t="str">
-        <x:v>item_choice_count_plus1</x:v>
+        <x:v>item_copy_food</x:v>
       </x:c>
       <x:c r="C59" s="1" t="str">
-        <x:v>琳琅满目</x:v>
+        <x:v>复制美食</x:v>
       </x:c>
       <x:c r="D59" s="8" t="str">
-        <x:v>选择食物时
-可选数量+1</x:v>
+        <x:v>随机复制一个食物</x:v>
       </x:c>
       <x:c r="E59" s="1" t="str">
         <x:v>Uncommon</x:v>
@@ -4695,30 +4698,29 @@
     <x:row r="60" ht="16.5" customHeight="1">
       <x:c r="A60" s="1"/>
       <x:c r="B60" s="1" t="str">
-        <x:v>item_choice_times_plus1</x:v>
+        <x:v>item_discard_negative</x:v>
       </x:c>
       <x:c r="C60" s="1" t="str">
-        <x:v>细嚼慢咽</x:v>
+        <x:v>断舍离</x:v>
       </x:c>
       <x:c r="D60" s="1" t="str">
-        <x:v>选择食物时
-可选次数+1，可选数量-1</x:v>
+        <x:v>丢弃两个负面道具</x:v>
       </x:c>
       <x:c r="E60" s="1" t="str">
-        <x:v>Rare</x:v>
+        <x:v>Common</x:v>
       </x:c>
       <x:c r="F60" s="1" t="str">
         <x:v>None</x:v>
       </x:c>
       <x:c r="G60" s="1" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H60" s="1"/>
       <x:c r="I60" s="1" t="n">
-        <x:v>30</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="J60" s="1" t="str">
-        <x:v>30,80</x:v>
+        <x:v>10,80</x:v>
       </x:c>
       <x:c r="K60" s="1" t="n">
         <x:v>0</x:v>
@@ -4741,20 +4743,20 @@
       <x:c r="Q60"/>
       <x:c r="R60" t="n">
         <x:f t="shared" si="1"/>
-        <x:v>120</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="61" ht="33.75" customHeight="1">
       <x:c r="A61" s="1"/>
       <x:c r="B61" s="1" t="str">
-        <x:v>item_extra_food_choice</x:v>
+        <x:v>item_discard_negative_gold</x:v>
       </x:c>
       <x:c r="C61" s="1" t="str">
-        <x:v>加餐</x:v>
+        <x:v>变废为宝</x:v>
       </x:c>
       <x:c r="D61" s="8" t="str">
-        <x:v>每6次普通美食
-额外获得3选一美食</x:v>
+        <x:v>丢弃所有负面道具
+每丢弃一个获得100金币</x:v>
       </x:c>
       <x:c r="E61" s="1" t="str">
         <x:v>Uncommon</x:v>
@@ -4763,11 +4765,9 @@
         <x:v>None</x:v>
       </x:c>
       <x:c r="G61" s="1" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H61" s="1" t="str">
-        <x:v>every:6</x:v>
-      </x:c>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H61" s="1"/>
       <x:c r="I61" s="1" t="n">
         <x:v>100</x:v>
       </x:c>
@@ -4801,32 +4801,29 @@
     <x:row r="62" ht="33.75" customHeight="1">
       <x:c r="A62" s="1"/>
       <x:c r="B62" s="1" t="str">
-        <x:v>item_extra_item_choice</x:v>
+        <x:v>item_gold_meal_penalty</x:v>
       </x:c>
       <x:c r="C62" s="1" t="str">
-        <x:v>加料</x:v>
+        <x:v>克扣工钱</x:v>
       </x:c>
       <x:c r="D62" s="8" t="str">
-        <x:v>每4次超级美食
-额外获得多选一道具</x:v>
+        <x:v>美食获得的金币-20%</x:v>
       </x:c>
       <x:c r="E62" s="1" t="str">
-        <x:v>Uncommon</x:v>
+        <x:v>Common</x:v>
       </x:c>
       <x:c r="F62" s="1" t="str">
-        <x:v>None</x:v>
+        <x:v>Negative</x:v>
       </x:c>
       <x:c r="G62" s="1" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H62" s="1" t="str">
-        <x:v>every:4</x:v>
-      </x:c>
+        <x:v>-0.2</x:v>
+      </x:c>
+      <x:c r="H62" s="1"/>
       <x:c r="I62" s="1" t="n">
-        <x:v>100</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="J62" s="1" t="str">
-        <x:v>20,80</x:v>
+        <x:v>10,80</x:v>
       </x:c>
       <x:c r="K62" s="1" t="n">
         <x:v>0</x:v>
@@ -4849,35 +4846,35 @@
       <x:c r="Q62"/>
       <x:c r="R62" t="n">
         <x:f t="shared" si="1"/>
-        <x:v>80</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="63" ht="33.75" customHeight="1">
       <x:c r="A63" s="1"/>
       <x:c r="B63" s="1" t="str">
-        <x:v>item_copy_food</x:v>
+        <x:v>item_shop_price_up</x:v>
       </x:c>
       <x:c r="C63" s="1" t="str">
-        <x:v>复制美食</x:v>
+        <x:v>涨价</x:v>
       </x:c>
       <x:c r="D63" s="8" t="str">
-        <x:v>随机复制一个食物</x:v>
+        <x:v>商店的价格+20%</x:v>
       </x:c>
       <x:c r="E63" s="1" t="str">
-        <x:v>Uncommon</x:v>
+        <x:v>Common</x:v>
       </x:c>
       <x:c r="F63" s="1" t="str">
-        <x:v>None</x:v>
+        <x:v>Negative</x:v>
       </x:c>
       <x:c r="G63" s="1" t="n">
-        <x:v>1</x:v>
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="H63" s="1"/>
       <x:c r="I63" s="1" t="n">
-        <x:v>100</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="J63" s="1" t="str">
-        <x:v>20,80</x:v>
+        <x:v>10,80</x:v>
       </x:c>
       <x:c r="K63" s="1" t="n">
         <x:v>0</x:v>
@@ -4900,28 +4897,28 @@
       <x:c r="Q63"/>
       <x:c r="R63" t="n">
         <x:f t="shared" si="1"/>
-        <x:v>80</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="64" ht="33.75" customHeight="1">
       <x:c r="A64" s="1"/>
       <x:c r="B64" s="1" t="str">
-        <x:v>item_discard_negative</x:v>
+        <x:v>item_no_remove</x:v>
       </x:c>
       <x:c r="C64" s="1" t="str">
-        <x:v>断舍离</x:v>
+        <x:v>囤积癖</x:v>
       </x:c>
       <x:c r="D64" s="8" t="str">
-        <x:v>丢弃两个负面道具</x:v>
+        <x:v>无法再删除食物</x:v>
       </x:c>
       <x:c r="E64" s="1" t="str">
         <x:v>Common</x:v>
       </x:c>
       <x:c r="F64" s="1" t="str">
-        <x:v>None</x:v>
+        <x:v>Negative</x:v>
       </x:c>
       <x:c r="G64" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H64" s="1"/>
       <x:c r="I64" s="1" t="n">
@@ -4957,30 +4954,29 @@
     <x:row r="65" ht="16.5" customHeight="1">
       <x:c r="A65" s="1"/>
       <x:c r="B65" s="1" t="str">
-        <x:v>item_discard_negative_gold</x:v>
+        <x:v>item_skip_node</x:v>
       </x:c>
       <x:c r="C65" s="1" t="str">
-        <x:v>变废为宝</x:v>
+        <x:v>停业整顿</x:v>
       </x:c>
       <x:c r="D65" s="1" t="str">
-        <x:v>丢弃所有负面道具
-每丢弃一个获得100金币</x:v>
+        <x:v>跳过下一个商店或利息节点</x:v>
       </x:c>
       <x:c r="E65" s="1" t="str">
-        <x:v>Uncommon</x:v>
+        <x:v>Common</x:v>
       </x:c>
       <x:c r="F65" s="1" t="str">
-        <x:v>None</x:v>
+        <x:v>Negative</x:v>
       </x:c>
       <x:c r="G65" s="1" t="n">
-        <x:v>100</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H65" s="1"/>
       <x:c r="I65" s="1" t="n">
-        <x:v>100</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="J65" s="1" t="str">
-        <x:v>20,80</x:v>
+        <x:v>10,80</x:v>
       </x:c>
       <x:c r="K65" s="1" t="n">
         <x:v>0</x:v>
@@ -5003,19 +4999,20 @@
       <x:c r="Q65"/>
       <x:c r="R65" t="n">
         <x:f t="shared" si="1"/>
-        <x:v>80</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="66" ht="16.5" customHeight="1">
       <x:c r="A66" s="1"/>
       <x:c r="B66" s="1" t="str">
-        <x:v>item_gold_meal_penalty</x:v>
+        <x:v>item_choice_minus1</x:v>
       </x:c>
       <x:c r="C66" s="1" t="str">
-        <x:v>克扣工钱</x:v>
+        <x:v>选择困难</x:v>
       </x:c>
       <x:c r="D66" s="1" t="str">
-        <x:v>美食获得的金币-20%</x:v>
+        <x:v>多选一食物时
+可选数量-1</x:v>
       </x:c>
       <x:c r="E66" s="1" t="str">
         <x:v>Common</x:v>
@@ -5024,7 +5021,7 @@
         <x:v>Negative</x:v>
       </x:c>
       <x:c r="G66" s="1" t="n">
-        <x:v>-0.2</x:v>
+        <x:v>-1</x:v>
       </x:c>
       <x:c r="H66" s="1"/>
       <x:c r="I66" s="1" t="n">
@@ -5060,13 +5057,13 @@
     <x:row r="67" ht="33.75" customHeight="1">
       <x:c r="A67" s="1"/>
       <x:c r="B67" s="1" t="str">
-        <x:v>item_shop_price_up</x:v>
+        <x:v>item_req_normal_up</x:v>
       </x:c>
       <x:c r="C67" s="1" t="str">
-        <x:v>涨价</x:v>
+        <x:v>家常加码</x:v>
       </x:c>
       <x:c r="D67" s="8" t="str">
-        <x:v>商店的价格+20%</x:v>
+        <x:v>普通美食要求分数+20%</x:v>
       </x:c>
       <x:c r="E67" s="1" t="str">
         <x:v>Common</x:v>
@@ -5111,13 +5108,13 @@
     <x:row r="68" ht="16.5" customHeight="1">
       <x:c r="A68" s="1"/>
       <x:c r="B68" s="1" t="str">
-        <x:v>item_no_remove</x:v>
+        <x:v>item_req_super_up</x:v>
       </x:c>
       <x:c r="C68" s="1" t="str">
-        <x:v>囤积癖</x:v>
+        <x:v>超级加码</x:v>
       </x:c>
       <x:c r="D68" s="1" t="str">
-        <x:v>无法再删除食物</x:v>
+        <x:v>超级美食要求分数+15%</x:v>
       </x:c>
       <x:c r="E68" s="1" t="str">
         <x:v>Common</x:v>
@@ -5126,7 +5123,7 @@
         <x:v>Negative</x:v>
       </x:c>
       <x:c r="G68" s="1" t="n">
-        <x:v>0</x:v>
+        <x:v>0.15</x:v>
       </x:c>
       <x:c r="H68" s="1"/>
       <x:c r="I68" s="1" t="n">
@@ -5162,13 +5159,13 @@
     <x:row r="69" ht="16.5" customHeight="1">
       <x:c r="A69" s="1"/>
       <x:c r="B69" s="1" t="str">
-        <x:v>item_skip_node</x:v>
+        <x:v>item_req_feast_up</x:v>
       </x:c>
       <x:c r="C69" s="1" t="str">
-        <x:v>停业整顿</x:v>
+        <x:v>盛宴加码</x:v>
       </x:c>
       <x:c r="D69" s="1" t="str">
-        <x:v>跳过下一个商店或利息节点</x:v>
+        <x:v>盛宴美食要求分数+15%</x:v>
       </x:c>
       <x:c r="E69" s="1" t="str">
         <x:v>Common</x:v>
@@ -5177,7 +5174,7 @@
         <x:v>Negative</x:v>
       </x:c>
       <x:c r="G69" s="1" t="n">
-        <x:v>1</x:v>
+        <x:v>0.15</x:v>
       </x:c>
       <x:c r="H69" s="1"/>
       <x:c r="I69" s="1" t="n">
@@ -5213,14 +5210,13 @@
     <x:row r="70" ht="16.5" customHeight="1">
       <x:c r="A70" s="1"/>
       <x:c r="B70" s="1" t="str">
-        <x:v>item_choice_minus1</x:v>
+        <x:v>item_gold_week_clear</x:v>
       </x:c>
       <x:c r="C70" s="1" t="str">
-        <x:v>选择困难</x:v>
+        <x:v>月光族</x:v>
       </x:c>
       <x:c r="D70" s="1" t="str">
-        <x:v>多选一食物时
-可选数量-1</x:v>
+        <x:v>本周结束时金币清空</x:v>
       </x:c>
       <x:c r="E70" s="1" t="str">
         <x:v>Common</x:v>
@@ -5229,7 +5225,7 @@
         <x:v>Negative</x:v>
       </x:c>
       <x:c r="G70" s="1" t="n">
-        <x:v>-1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H70" s="1"/>
       <x:c r="I70" s="1" t="n">
@@ -5265,29 +5261,29 @@
     <x:row r="71" ht="16.5" customHeight="1">
       <x:c r="A71" s="1"/>
       <x:c r="B71" s="1" t="str">
-        <x:v>item_req_normal_up</x:v>
+        <x:v>item_count_as_all</x:v>
       </x:c>
       <x:c r="C71" s="1" t="str">
-        <x:v>家常加码</x:v>
+        <x:v>小份主义</x:v>
       </x:c>
       <x:c r="D71" s="1" t="str">
-        <x:v>普通美食要求分数+20%</x:v>
+        <x:v>所有食物额外被视为2个食物</x:v>
       </x:c>
       <x:c r="E71" s="1" t="str">
-        <x:v>Common</x:v>
+        <x:v>Epic</x:v>
       </x:c>
       <x:c r="F71" s="1" t="str">
-        <x:v>Negative</x:v>
+        <x:v>None</x:v>
       </x:c>
       <x:c r="G71" s="1" t="n">
-        <x:v>0.2</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H71" s="1"/>
       <x:c r="I71" s="1" t="n">
-        <x:v>300</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="J71" s="1" t="str">
-        <x:v>10,80</x:v>
+        <x:v>40,80</x:v>
       </x:c>
       <x:c r="K71" s="1" t="n">
         <x:v>0</x:v>
@@ -5310,35 +5306,36 @@
       <x:c r="Q71"/>
       <x:c r="R71" t="n">
         <x:f t="shared" si="2"/>
-        <x:v>50</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="72" ht="33.75" customHeight="1">
       <x:c r="A72" s="1"/>
       <x:c r="B72" s="1" t="str">
-        <x:v>item_req_super_up</x:v>
+        <x:v>item_transfer_target_mult</x:v>
       </x:c>
       <x:c r="C72" s="1" t="str">
-        <x:v>超级加码</x:v>
+        <x:v>传递受益</x:v>
       </x:c>
       <x:c r="D72" s="8" t="str">
-        <x:v>超级美食要求分数+15%</x:v>
+        <x:v>甜蜜传递时
+被传递方倍率×1.2</x:v>
       </x:c>
       <x:c r="E72" s="1" t="str">
-        <x:v>Common</x:v>
+        <x:v>Epic</x:v>
       </x:c>
       <x:c r="F72" s="1" t="str">
-        <x:v>Negative</x:v>
+        <x:v>None</x:v>
       </x:c>
       <x:c r="G72" s="1" t="n">
-        <x:v>0.15</x:v>
+        <x:v>1.2</x:v>
       </x:c>
       <x:c r="H72" s="1"/>
       <x:c r="I72" s="1" t="n">
-        <x:v>300</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="J72" s="1" t="str">
-        <x:v>10,80</x:v>
+        <x:v>40,80</x:v>
       </x:c>
       <x:c r="K72" s="1" t="n">
         <x:v>0</x:v>
@@ -5358,38 +5355,41 @@
       <x:c r="P72" s="1" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="Q72"/>
+      <x:c r="Q72" t="str">
+        <x:v>term_sweet_transfer</x:v>
+      </x:c>
       <x:c r="R72" t="n">
         <x:f t="shared" si="2"/>
-        <x:v>50</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="73" ht="16.5" customHeight="1">
       <x:c r="A73" s="1"/>
       <x:c r="B73" s="1" t="str">
-        <x:v>item_req_feast_up</x:v>
+        <x:v>item_transfer_source_mult</x:v>
       </x:c>
       <x:c r="C73" s="1" t="str">
-        <x:v>盛宴加码</x:v>
+        <x:v>传递奉献</x:v>
       </x:c>
       <x:c r="D73" s="1" t="str">
-        <x:v>盛宴美食要求分数+15%</x:v>
+        <x:v>甜蜜传递时
+传递方倍率×1.2</x:v>
       </x:c>
       <x:c r="E73" s="1" t="str">
-        <x:v>Common</x:v>
+        <x:v>Epic</x:v>
       </x:c>
       <x:c r="F73" s="1" t="str">
-        <x:v>Negative</x:v>
+        <x:v>None</x:v>
       </x:c>
       <x:c r="G73" s="1" t="n">
-        <x:v>0.15</x:v>
+        <x:v>1.2</x:v>
       </x:c>
       <x:c r="H73" s="1"/>
       <x:c r="I73" s="1" t="n">
-        <x:v>300</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="J73" s="1" t="str">
-        <x:v>10,80</x:v>
+        <x:v>40,80</x:v>
       </x:c>
       <x:c r="K73" s="1" t="n">
         <x:v>0</x:v>
@@ -5409,38 +5409,41 @@
       <x:c r="P73" s="1" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="Q73"/>
+      <x:c r="Q73" t="str">
+        <x:v>term_sweet_transfer</x:v>
+      </x:c>
       <x:c r="R73" t="n">
         <x:f t="shared" si="2"/>
-        <x:v>50</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="74" ht="16.5" customHeight="1">
       <x:c r="A74" s="1"/>
       <x:c r="B74" s="1" t="str">
-        <x:v>item_gold_week_clear</x:v>
+        <x:v>item_skill_count_mult</x:v>
       </x:c>
       <x:c r="C74" s="1" t="str">
-        <x:v>月光族</x:v>
+        <x:v>技法大师</x:v>
       </x:c>
       <x:c r="D74" s="1" t="str">
-        <x:v>本周结束时金币清空</x:v>
+        <x:v>结算时每有1个技能
+倍率+0.2</x:v>
       </x:c>
       <x:c r="E74" s="1" t="str">
-        <x:v>Common</x:v>
+        <x:v>Uncommon</x:v>
       </x:c>
       <x:c r="F74" s="1" t="str">
-        <x:v>Negative</x:v>
+        <x:v>None</x:v>
       </x:c>
       <x:c r="G74" s="1" t="n">
-        <x:v>0</x:v>
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="H74" s="1"/>
       <x:c r="I74" s="1" t="n">
-        <x:v>300</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="J74" s="1" t="str">
-        <x:v>10,80</x:v>
+        <x:v>20,80</x:v>
       </x:c>
       <x:c r="K74" s="1" t="n">
         <x:v>0</x:v>
@@ -5460,38 +5463,43 @@
       <x:c r="P74" s="1" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="Q74"/>
+      <x:c r="Q74" t="str">
+        <x:v>term_sweet_transfer</x:v>
+      </x:c>
       <x:c r="R74" t="n">
         <x:f t="shared" si="2"/>
-        <x:v>50</x:v>
+        <x:v>80</x:v>
       </x:c>
     </x:row>
     <x:row r="75" ht="16.5" customHeight="1">
       <x:c r="A75" s="1"/>
       <x:c r="B75" s="1" t="str">
-        <x:v>item_count_as_all</x:v>
+        <x:v>item_gold_on_transfer</x:v>
       </x:c>
       <x:c r="C75" s="1" t="str">
-        <x:v>小份主义</x:v>
+        <x:v>传递分红</x:v>
       </x:c>
       <x:c r="D75" s="1" t="str">
-        <x:v>所有食物额外被视为2个食物</x:v>
+        <x:v>甜蜜传递10次后
++10金币</x:v>
       </x:c>
       <x:c r="E75" s="1" t="str">
-        <x:v>Epic</x:v>
+        <x:v>Uncommon</x:v>
       </x:c>
       <x:c r="F75" s="1" t="str">
         <x:v>None</x:v>
       </x:c>
       <x:c r="G75" s="1" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H75" s="1"/>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H75" s="1" t="str">
+        <x:v>count:10</x:v>
+      </x:c>
       <x:c r="I75" s="1" t="n">
-        <x:v>10</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="J75" s="1" t="str">
-        <x:v>40,80</x:v>
+        <x:v>20,80</x:v>
       </x:c>
       <x:c r="K75" s="1" t="n">
         <x:v>0</x:v>
@@ -5511,23 +5519,25 @@
       <x:c r="P75" s="1" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="Q75"/>
+      <x:c r="Q75" t="str">
+        <x:v>term_sweet_transfer</x:v>
+      </x:c>
       <x:c r="R75" t="n">
         <x:f t="shared" si="2"/>
-        <x:v>200</x:v>
+        <x:v>80</x:v>
       </x:c>
     </x:row>
     <x:row r="76" ht="16.5" customHeight="1">
       <x:c r="A76" s="1"/>
       <x:c r="B76" s="1" t="str">
-        <x:v>item_transfer_target_mult</x:v>
+        <x:v>item_cake_retain</x:v>
       </x:c>
       <x:c r="C76" s="1" t="str">
-        <x:v>传递受益</x:v>
+        <x:v>蛋糕保鲜</x:v>
       </x:c>
       <x:c r="D76" s="1" t="str">
-        <x:v>甜蜜传递时
-被传递方倍率×1.2</x:v>
+        <x:v>保留20%的蛋糕层数
+至下一次美食</x:v>
       </x:c>
       <x:c r="E76" s="1" t="str">
         <x:v>Epic</x:v>
@@ -5536,7 +5546,7 @@
         <x:v>None</x:v>
       </x:c>
       <x:c r="G76" s="1" t="n">
-        <x:v>1.2</x:v>
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="H76" s="1"/>
       <x:c r="I76" s="1" t="n">
@@ -5564,7 +5574,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q76" t="str">
-        <x:v>term_sweet_transfer</x:v>
+        <x:v>clb</x:v>
       </x:c>
       <x:c r="R76" t="n">
         <x:f t="shared" si="2"/>
@@ -5574,30 +5584,30 @@
     <x:row r="77" ht="16.5" customHeight="1">
       <x:c r="A77" s="1"/>
       <x:c r="B77" s="1" t="str">
-        <x:v>item_transfer_source_mult</x:v>
+        <x:v>item_cake_init_bonus</x:v>
       </x:c>
       <x:c r="C77" s="1" t="str">
-        <x:v>传递奉献</x:v>
+        <x:v>蛋糕打底</x:v>
       </x:c>
       <x:c r="D77" s="1" t="str">
-        <x:v>甜蜜传递时
-传递方倍率×1.2</x:v>
+        <x:v>蛋糕层数
+初始额外获得10层</x:v>
       </x:c>
       <x:c r="E77" s="1" t="str">
-        <x:v>Epic</x:v>
+        <x:v>Uncommon</x:v>
       </x:c>
       <x:c r="F77" s="1" t="str">
         <x:v>None</x:v>
       </x:c>
       <x:c r="G77" s="1" t="n">
-        <x:v>1.2</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H77" s="1"/>
       <x:c r="I77" s="1" t="n">
-        <x:v>10</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="J77" s="1" t="str">
-        <x:v>40,80</x:v>
+        <x:v>20,80</x:v>
       </x:c>
       <x:c r="K77" s="1" t="n">
         <x:v>0</x:v>
@@ -5618,40 +5628,40 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q77" t="str">
-        <x:v>term_sweet_transfer</x:v>
+        <x:v>clb</x:v>
       </x:c>
       <x:c r="R77" t="n">
         <x:f t="shared" si="2"/>
-        <x:v>200</x:v>
+        <x:v>80</x:v>
       </x:c>
     </x:row>
     <x:row r="78" ht="33.75" customHeight="1">
       <x:c r="A78" s="1"/>
       <x:c r="B78" s="1" t="str">
-        <x:v>item_skill_count_mult</x:v>
+        <x:v>item_cake_accel</x:v>
       </x:c>
       <x:c r="C78" s="1" t="str">
-        <x:v>技法大师</x:v>
+        <x:v>蛋糕膨胀</x:v>
       </x:c>
       <x:c r="D78" s="8" t="str">
-        <x:v>结算时每有1个技能
-倍率+0.2</x:v>
+        <x:v>蛋糕层数增加时
+额外加1层</x:v>
       </x:c>
       <x:c r="E78" s="1" t="str">
-        <x:v>Uncommon</x:v>
+        <x:v>Rare</x:v>
       </x:c>
       <x:c r="F78" s="1" t="str">
         <x:v>None</x:v>
       </x:c>
       <x:c r="G78" s="1" t="n">
-        <x:v>0.2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H78" s="1"/>
       <x:c r="I78" s="1" t="n">
-        <x:v>100</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="J78" s="1" t="str">
-        <x:v>20,80</x:v>
+        <x:v>30,80</x:v>
       </x:c>
       <x:c r="K78" s="1" t="n">
         <x:v>0</x:v>
@@ -5672,24 +5682,24 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q78" s="1" t="str">
-        <x:v>term_sweet_transfer</x:v>
+        <x:v>clb</x:v>
       </x:c>
       <x:c r="R78" t="n">
         <x:f t="shared" si="2"/>
-        <x:v>80</x:v>
+        <x:v>120</x:v>
       </x:c>
     </x:row>
     <x:row r="79" ht="33.75" customHeight="1">
       <x:c r="A79" s="1"/>
       <x:c r="B79" s="1" t="str">
-        <x:v>item_gold_on_transfer</x:v>
+        <x:v>item_cake_to_gold</x:v>
       </x:c>
       <x:c r="C79" s="1" t="str">
-        <x:v>传递分红</x:v>
+        <x:v>蛋糕变现</x:v>
       </x:c>
       <x:c r="D79" s="8" t="str">
-        <x:v>甜蜜传递10次后
-+10金币</x:v>
+        <x:v>蛋糕层数大于100层时
+获得10金币</x:v>
       </x:c>
       <x:c r="E79" s="1" t="str">
         <x:v>Uncommon</x:v>
@@ -5701,7 +5711,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="H79" s="1" t="str">
-        <x:v>count:10</x:v>
+        <x:v>threshold:100</x:v>
       </x:c>
       <x:c r="I79" s="1" t="n">
         <x:v>100</x:v>
@@ -5728,7 +5738,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q79" s="1" t="str">
-        <x:v>term_sweet_transfer</x:v>
+        <x:v>clb</x:v>
       </x:c>
       <x:c r="R79" t="n">
         <x:f t="shared" si="2"/>
@@ -5738,30 +5748,29 @@
     <x:row r="80" ht="33.75" customHeight="1">
       <x:c r="A80" s="1"/>
       <x:c r="B80" s="1" t="str">
-        <x:v>item_cake_retain</x:v>
+        <x:v>item_cake_req_minus</x:v>
       </x:c>
       <x:c r="C80" s="1" t="str">
-        <x:v>蛋糕保鲜</x:v>
+        <x:v>蛋糕捷径</x:v>
       </x:c>
       <x:c r="D80" s="8" t="str">
-        <x:v>保留20%的蛋糕层数
-至下一次美食</x:v>
+        <x:v>蛋糕效果需求的层数-10</x:v>
       </x:c>
       <x:c r="E80" s="1" t="str">
-        <x:v>Epic</x:v>
+        <x:v>Uncommon</x:v>
       </x:c>
       <x:c r="F80" s="1" t="str">
         <x:v>None</x:v>
       </x:c>
       <x:c r="G80" s="1" t="n">
-        <x:v>0.2</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H80" s="1"/>
       <x:c r="I80" s="1" t="n">
-        <x:v>10</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="J80" s="1" t="str">
-        <x:v>40,80</x:v>
+        <x:v>20,80</x:v>
       </x:c>
       <x:c r="K80" s="1" t="n">
         <x:v>0</x:v>
@@ -5786,224 +5795,95 @@
       </x:c>
       <x:c r="R80" t="n">
         <x:f t="shared" si="2"/>
-        <x:v>200</x:v>
+        <x:v>80</x:v>
       </x:c>
     </x:row>
     <x:row r="81" ht="33.75" customHeight="1">
       <x:c r="A81" s="1"/>
-      <x:c r="B81" s="1" t="str">
-        <x:v>item_cake_init_bonus</x:v>
-      </x:c>
-      <x:c r="C81" s="1" t="str">
-        <x:v>蛋糕打底</x:v>
-      </x:c>
-      <x:c r="D81" s="8" t="str">
-        <x:v>蛋糕层数
-初始额外获得10层</x:v>
-      </x:c>
-      <x:c r="E81" s="1" t="str">
-        <x:v>Uncommon</x:v>
-      </x:c>
-      <x:c r="F81" s="1" t="str">
-        <x:v>None</x:v>
-      </x:c>
-      <x:c r="G81" s="1" t="n">
-        <x:v>10</x:v>
-      </x:c>
+      <x:c r="B81" s="1"/>
+      <x:c r="C81" s="1"/>
+      <x:c r="D81" s="8"/>
+      <x:c r="E81" s="1"/>
+      <x:c r="F81" s="1"/>
+      <x:c r="G81" s="1"/>
       <x:c r="H81" s="1"/>
-      <x:c r="I81" s="1" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="J81" s="1" t="str">
-        <x:v>20,80</x:v>
-      </x:c>
-      <x:c r="K81" s="1" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L81" s="1" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M81" s="1" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N81" s="1" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O81" s="1" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P81" s="1" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q81" s="1" t="str">
-        <x:v>clb</x:v>
-      </x:c>
-      <x:c r="R81" t="n">
+      <x:c r="I81" s="1"/>
+      <x:c r="J81" s="1"/>
+      <x:c r="K81" s="1"/>
+      <x:c r="L81" s="1"/>
+      <x:c r="M81" s="1"/>
+      <x:c r="N81" s="1"/>
+      <x:c r="O81" s="1"/>
+      <x:c r="P81" s="1"/>
+      <x:c r="Q81" s="1"/>
+      <x:c r="R81">
         <x:f t="shared" si="2"/>
-        <x:v>80</x:v>
       </x:c>
     </x:row>
     <x:row r="82" ht="33.75" customHeight="1">
       <x:c r="A82" s="1"/>
-      <x:c r="B82" s="1" t="str">
-        <x:v>item_cake_accel</x:v>
-      </x:c>
-      <x:c r="C82" s="1" t="str">
-        <x:v>蛋糕膨胀</x:v>
-      </x:c>
-      <x:c r="D82" s="8" t="str">
-        <x:v>蛋糕层数增加时
-额外加1层</x:v>
-      </x:c>
-      <x:c r="E82" s="1" t="str">
-        <x:v>Rare</x:v>
-      </x:c>
-      <x:c r="F82" s="1" t="str">
-        <x:v>None</x:v>
-      </x:c>
-      <x:c r="G82" s="1" t="n">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="B82" s="1"/>
+      <x:c r="C82" s="1"/>
+      <x:c r="D82" s="8"/>
+      <x:c r="E82" s="1"/>
+      <x:c r="F82" s="1"/>
+      <x:c r="G82" s="1"/>
       <x:c r="H82" s="1"/>
-      <x:c r="I82" s="1" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="J82" s="1" t="str">
-        <x:v>30,80</x:v>
-      </x:c>
-      <x:c r="K82" s="1" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L82" s="1" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M82" s="1" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N82" s="1" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O82" s="1" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P82" s="1" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q82" s="1" t="str">
-        <x:v>clb</x:v>
-      </x:c>
-      <x:c r="R82" t="n">
+      <x:c r="I82" s="1"/>
+      <x:c r="J82" s="1"/>
+      <x:c r="K82" s="1"/>
+      <x:c r="L82" s="1"/>
+      <x:c r="M82" s="1"/>
+      <x:c r="N82" s="1"/>
+      <x:c r="O82" s="1"/>
+      <x:c r="P82" s="1"/>
+      <x:c r="Q82" s="1"/>
+      <x:c r="R82">
         <x:f t="shared" si="2"/>
-        <x:v>120</x:v>
       </x:c>
     </x:row>
     <x:row r="83" ht="33.75" customHeight="1">
       <x:c r="A83" s="1"/>
-      <x:c r="B83" s="1" t="str">
-        <x:v>item_cake_to_gold</x:v>
-      </x:c>
-      <x:c r="C83" s="1" t="str">
-        <x:v>蛋糕变现</x:v>
-      </x:c>
-      <x:c r="D83" s="8" t="str">
-        <x:v>蛋糕层数大于100层时
-获得10金币</x:v>
-      </x:c>
-      <x:c r="E83" s="1" t="str">
-        <x:v>Uncommon</x:v>
-      </x:c>
-      <x:c r="F83" s="1" t="str">
-        <x:v>None</x:v>
-      </x:c>
-      <x:c r="G83" s="1" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="H83" s="1" t="str">
-        <x:v>threshold:100</x:v>
-      </x:c>
-      <x:c r="I83" s="1" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="J83" s="1" t="str">
-        <x:v>20,80</x:v>
-      </x:c>
-      <x:c r="K83" s="1" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L83" s="1" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M83" s="1" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N83" s="1" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O83" s="1" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P83" s="1" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q83" s="1" t="str">
-        <x:v>clb</x:v>
-      </x:c>
-      <x:c r="R83" t="n">
+      <x:c r="B83" s="1"/>
+      <x:c r="C83" s="1"/>
+      <x:c r="D83" s="8"/>
+      <x:c r="E83" s="1"/>
+      <x:c r="F83" s="1"/>
+      <x:c r="G83" s="1"/>
+      <x:c r="H83" s="1"/>
+      <x:c r="I83" s="1"/>
+      <x:c r="J83" s="1"/>
+      <x:c r="K83" s="1"/>
+      <x:c r="L83" s="1"/>
+      <x:c r="M83" s="1"/>
+      <x:c r="N83" s="1"/>
+      <x:c r="O83" s="1"/>
+      <x:c r="P83" s="1"/>
+      <x:c r="Q83" s="1"/>
+      <x:c r="R83">
         <x:f t="shared" si="2"/>
-        <x:v>80</x:v>
       </x:c>
     </x:row>
     <x:row r="84" ht="33.75" customHeight="1">
       <x:c r="A84" s="1"/>
-      <x:c r="B84" s="1" t="str">
-        <x:v>item_cake_req_minus</x:v>
-      </x:c>
-      <x:c r="C84" s="1" t="str">
-        <x:v>蛋糕捷径</x:v>
-      </x:c>
-      <x:c r="D84" s="8" t="str">
-        <x:v>蛋糕效果需求的层数-10</x:v>
-      </x:c>
-      <x:c r="E84" s="1" t="str">
-        <x:v>Uncommon</x:v>
-      </x:c>
-      <x:c r="F84" s="1" t="str">
-        <x:v>None</x:v>
-      </x:c>
-      <x:c r="G84" s="1" t="n">
-        <x:v>10</x:v>
-      </x:c>
+      <x:c r="B84" s="1"/>
+      <x:c r="C84" s="1"/>
+      <x:c r="D84" s="8"/>
+      <x:c r="E84" s="1"/>
+      <x:c r="F84" s="1"/>
+      <x:c r="G84" s="1"/>
       <x:c r="H84" s="1"/>
-      <x:c r="I84" s="1" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="J84" s="1" t="str">
-        <x:v>20,80</x:v>
-      </x:c>
-      <x:c r="K84" s="1" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L84" s="1" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M84" s="1" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N84" s="1" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O84" s="1" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P84" s="1" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q84" s="1" t="str">
-        <x:v>clb</x:v>
-      </x:c>
-      <x:c r="R84" t="n">
+      <x:c r="I84" s="1"/>
+      <x:c r="J84" s="1"/>
+      <x:c r="K84" s="1"/>
+      <x:c r="L84" s="1"/>
+      <x:c r="M84" s="1"/>
+      <x:c r="N84" s="1"/>
+      <x:c r="O84" s="1"/>
+      <x:c r="P84" s="1"/>
+      <x:c r="Q84" s="1"/>
+      <x:c r="R84">
         <x:f t="shared" si="2"/>
-        <x:v>80</x:v>
       </x:c>
     </x:row>
     <x:row r="85" ht="33.75" customHeight="1">
@@ -7340,1075 +7220,1045 @@
     </x:row>
     <x:row r="32" customHeight="1">
       <x:c r="B32" s="4"/>
-      <x:c r="C32" s="3"/>
+      <x:c r="C32" s="3" t="str">
+        <x:v>食物转换</x:v>
+      </x:c>
       <x:c r="D32" s="3" t="str">
-        <x:v>移动</x:v>
+        <x:v>食物转换</x:v>
       </x:c>
       <x:c r="E32" s="3" t="str">
-        <x:v>每局第一次上菜后，可以不消耗修正次数移动</x:v>
+        <x:v>随机将5个食物，变为至少同品质的食物</x:v>
       </x:c>
       <x:c r="H32" s="1" t="n">
         <x:v>31</x:v>
       </x:c>
       <x:c r="I32" s="2" t="str">
         <x:f t="shared" si="0"/>
-        <x:v>每局第一次上菜后，可以不消耗修正次数移动</x:v>
+        <x:v>随机将5个食物，变为至少同品质的食物</x:v>
       </x:c>
     </x:row>
     <x:row r="33" customHeight="1">
       <x:c r="B33" s="4"/>
-      <x:c r="C33" s="4" t="str">
-        <x:v>调整</x:v>
-      </x:c>
+      <x:c r="C33" s="4"/>
       <x:c r="D33" s="3" t="str">
-        <x:v>调整次数增加</x:v>
+        <x:v>商店给钱</x:v>
       </x:c>
       <x:c r="E33" s="3" t="str">
-        <x:v>调整次数+1</x:v>
+        <x:v>进入商店时，获得10金币</x:v>
       </x:c>
       <x:c r="H33" s="1" t="n">
         <x:v>32</x:v>
       </x:c>
       <x:c r="I33" s="2" t="str">
         <x:f t="shared" si="0"/>
-        <x:v>调整次数+1</x:v>
+        <x:v>进入商店时，获得10金币</x:v>
       </x:c>
     </x:row>
     <x:row r="34" customHeight="1">
       <x:c r="B34" s="4"/>
       <x:c r="C34" s="4"/>
       <x:c r="D34" s="3" t="str">
-        <x:v>调整加倍率</x:v>
+        <x:v>利息</x:v>
       </x:c>
       <x:c r="E34" s="3" t="str">
-        <x:v>每1个未使用的调整次数，使倍率+0.2</x:v>
+        <x:v>每周结束，额外执行一次利息</x:v>
       </x:c>
       <x:c r="H34" s="1" t="n">
         <x:v>33</x:v>
       </x:c>
       <x:c r="I34" s="2" t="str">
         <x:f t="shared" si="0"/>
-        <x:v>每1个未使用的调整次数，使倍率+0.2</x:v>
+        <x:v>每周结束，额外执行一次利息</x:v>
       </x:c>
     </x:row>
     <x:row r="35" customHeight="1">
       <x:c r="B35" s="4"/>
-      <x:c r="C35" s="3" t="str">
-        <x:v>食物转换</x:v>
-      </x:c>
+      <x:c r="C35" s="3"/>
       <x:c r="D35" s="3" t="str">
-        <x:v>食物转换</x:v>
+        <x:v>保底钱</x:v>
       </x:c>
       <x:c r="E35" s="3" t="str">
-        <x:v>随机将5个食物，变为至少同品质的食物</x:v>
+        <x:v>回合结束金币小于10时，获得10金币</x:v>
       </x:c>
       <x:c r="H35" s="1" t="n">
         <x:v>34</x:v>
       </x:c>
       <x:c r="I35" s="2" t="str">
         <x:f t="shared" si="0"/>
-        <x:v>随机将5个食物，变为至少同品质的食物</x:v>
+        <x:v>回合结束金币小于10时，获得10金币</x:v>
       </x:c>
     </x:row>
     <x:row r="36" customHeight="1">
       <x:c r="B36" s="4"/>
-      <x:c r="C36" s="3" t="str">
-        <x:v>运营</x:v>
-      </x:c>
+      <x:c r="C36" s="3"/>
       <x:c r="D36" s="6" t="str">
-        <x:v>调整次数换钱</x:v>
+        <x:v>利息上限</x:v>
       </x:c>
       <x:c r="E36" s="3" t="str">
-        <x:v>每个未使用的调整次数，获得1金币</x:v>
+        <x:v>利息上限扩展到10金币</x:v>
       </x:c>
       <x:c r="H36" s="1" t="n">
         <x:v>35</x:v>
       </x:c>
       <x:c r="I36" s="2" t="str">
         <x:f t="shared" si="0"/>
-        <x:v>每个未使用的调整次数，获得1金币</x:v>
+        <x:v>利息上限扩展到10金币</x:v>
       </x:c>
     </x:row>
     <x:row r="37" customHeight="1">
       <x:c r="B37" s="4"/>
       <x:c r="C37" s="3"/>
       <x:c r="D37" s="3" t="str">
-        <x:v>商店给钱</x:v>
+        <x:v>贷款</x:v>
       </x:c>
       <x:c r="E37" s="3" t="str">
-        <x:v>进入商店时，获得10金币</x:v>
+        <x:v>临时获得300金币，下一周失去600金币</x:v>
       </x:c>
       <x:c r="H37" s="1" t="n">
         <x:v>36</x:v>
       </x:c>
       <x:c r="I37" s="2" t="str">
         <x:f t="shared" si="0"/>
-        <x:v>进入商店时，获得10金币</x:v>
+        <x:v>临时获得300金币，下一周失去600金币</x:v>
       </x:c>
     </x:row>
     <x:row r="38" customHeight="1">
       <x:c r="B38" s="4"/>
-      <x:c r="C38" s="3"/>
+      <x:c r="C38" s="3" t="str">
+        <x:v>时间轴</x:v>
+      </x:c>
       <x:c r="D38" s="3" t="str">
-        <x:v>利息</x:v>
+        <x:v>随机</x:v>
       </x:c>
       <x:c r="E38" s="3" t="str">
-        <x:v>每周结束，额外执行一次利息</x:v>
+        <x:v>随机化时间轴的节点事件。</x:v>
       </x:c>
       <x:c r="H38" s="1" t="n">
         <x:v>37</x:v>
       </x:c>
       <x:c r="I38" s="2" t="str">
         <x:f t="shared" si="0"/>
-        <x:v>每周结束，额外执行一次利息</x:v>
+        <x:v>随机化时间轴的节点事件。</x:v>
       </x:c>
     </x:row>
     <x:row r="39" customHeight="1">
       <x:c r="B39" s="4"/>
       <x:c r="C39" s="4"/>
       <x:c r="D39" s="3" t="str">
-        <x:v>保底钱</x:v>
+        <x:v>增加第八天</x:v>
       </x:c>
       <x:c r="E39" s="3" t="str">
-        <x:v>回合结束金币小于10时，获得10金币</x:v>
+        <x:v>延后所有Boss一天</x:v>
       </x:c>
       <x:c r="H39" s="1" t="n">
         <x:v>38</x:v>
       </x:c>
       <x:c r="I39" s="2" t="str">
         <x:f t="shared" si="0"/>
-        <x:v>回合结束金币小于10时，获得10金币</x:v>
+        <x:v>延后所有Boss一天</x:v>
       </x:c>
     </x:row>
     <x:row r="40" customHeight="1">
       <x:c r="B40" s="4"/>
       <x:c r="C40" s="4"/>
       <x:c r="D40" s="3" t="str">
-        <x:v>利息上限</x:v>
+        <x:v>周数-1</x:v>
       </x:c>
       <x:c r="E40" s="3" t="str">
-        <x:v>利息上限扩展到10金币</x:v>
+        <x:v>周数-1</x:v>
       </x:c>
       <x:c r="H40" s="1" t="n">
         <x:v>39</x:v>
       </x:c>
       <x:c r="I40" s="2" t="str">
         <x:f t="shared" si="0"/>
-        <x:v>利息上限扩展到10金币</x:v>
+        <x:v>周数-1</x:v>
       </x:c>
     </x:row>
     <x:row r="41" customHeight="1">
       <x:c r="B41" s="4"/>
       <x:c r="C41" s="4"/>
       <x:c r="D41" s="3" t="str">
-        <x:v>贷款</x:v>
+        <x:v>增加奖励节点</x:v>
       </x:c>
       <x:c r="E41" s="3" t="str">
-        <x:v>临时获得300金币，下一周失去600金币</x:v>
+        <x:v>增加一个奖励节点到时间轴上</x:v>
       </x:c>
       <x:c r="H41" s="1" t="n">
         <x:v>40</x:v>
       </x:c>
       <x:c r="I41" s="2" t="str">
         <x:f t="shared" si="0"/>
-        <x:v>临时获得300金币，下一周失去600金币</x:v>
+        <x:v>增加一个奖励节点到时间轴上</x:v>
       </x:c>
     </x:row>
     <x:row r="42" customHeight="1">
       <x:c r="B42" s="4"/>
-      <x:c r="C42" s="4" t="str">
-        <x:v>时间轴</x:v>
-      </x:c>
+      <x:c r="C42" s="4"/>
       <x:c r="D42" s="3" t="str">
-        <x:v>随机</x:v>
+        <x:v>增加利息节点</x:v>
       </x:c>
       <x:c r="E42" s="3" t="str">
-        <x:v>随机化时间轴的节点事件。</x:v>
+        <x:v>增加一个利息节点到时间轴上</x:v>
       </x:c>
       <x:c r="H42" s="1" t="n">
         <x:v>41</x:v>
       </x:c>
       <x:c r="I42" s="2" t="str">
         <x:f t="shared" si="0"/>
-        <x:v>随机化时间轴的节点事件。</x:v>
+        <x:v>增加一个利息节点到时间轴上</x:v>
       </x:c>
     </x:row>
     <x:row r="43" customHeight="1">
       <x:c r="B43" s="4"/>
-      <x:c r="C43" s="4"/>
+      <x:c r="C43" s="4" t="str">
+        <x:v>分数加倍</x:v>
+      </x:c>
       <x:c r="D43" s="3" t="str">
-        <x:v>增加第八天</x:v>
+        <x:v>每3个</x:v>
       </x:c>
       <x:c r="E43" s="3" t="str">
-        <x:v>延后所有Boss一天</x:v>
+        <x:v>每上3个食物后，下一个食物倍率+2</x:v>
       </x:c>
       <x:c r="H43" s="1" t="n">
         <x:v>42</x:v>
       </x:c>
       <x:c r="I43" s="2" t="str">
         <x:f t="shared" si="0"/>
-        <x:v>延后所有Boss一天</x:v>
+        <x:v>每上3个食物后，下一个食物倍率+2</x:v>
       </x:c>
     </x:row>
     <x:row r="44" customHeight="1">
       <x:c r="B44" s="4"/>
       <x:c r="C44" s="3"/>
       <x:c r="D44" s="3" t="str">
-        <x:v>周数-1</x:v>
+        <x:v>第一个</x:v>
       </x:c>
       <x:c r="E44" s="3" t="str">
-        <x:v>周数-1</x:v>
+        <x:v>第一个上的食物，倍率x2</x:v>
       </x:c>
       <x:c r="H44" s="1" t="n">
         <x:v>43</x:v>
       </x:c>
       <x:c r="I44" s="2" t="str">
         <x:f t="shared" si="0"/>
-        <x:v>周数-1</x:v>
+        <x:v>第一个上的食物，倍率x2</x:v>
       </x:c>
     </x:row>
     <x:row r="45" customHeight="1">
       <x:c r="B45" s="4"/>
       <x:c r="C45" s="4"/>
       <x:c r="D45" s="3" t="str">
-        <x:v>增加奖励节点</x:v>
+        <x:v>最后一个</x:v>
       </x:c>
       <x:c r="E45" s="3" t="str">
-        <x:v>增加一个奖励节点到时间轴上</x:v>
+        <x:v>最后一个上的食物，倍率x2</x:v>
       </x:c>
       <x:c r="H45" s="1" t="n">
         <x:v>44</x:v>
       </x:c>
       <x:c r="I45" s="2" t="str">
         <x:f t="shared" si="0"/>
-        <x:v>增加一个奖励节点到时间轴上</x:v>
+        <x:v>最后一个上的食物，倍率x2</x:v>
       </x:c>
     </x:row>
     <x:row r="46" customHeight="1">
       <x:c r="B46" s="4"/>
-      <x:c r="C46" s="4"/>
+      <x:c r="C46" s="4" t="str">
+        <x:v>主动道具</x:v>
+      </x:c>
       <x:c r="D46" s="3" t="str">
-        <x:v>增加利息节点</x:v>
+        <x:v>额外道具栏</x:v>
       </x:c>
       <x:c r="E46" s="3" t="str">
-        <x:v>增加一个利息节点到时间轴上</x:v>
+        <x:v>增加2个额外主动道具栏</x:v>
       </x:c>
       <x:c r="H46" s="1" t="n">
         <x:v>45</x:v>
       </x:c>
       <x:c r="I46" s="2" t="str">
         <x:f t="shared" si="0"/>
-        <x:v>增加一个利息节点到时间轴上</x:v>
+        <x:v>增加2个额外主动道具栏</x:v>
       </x:c>
     </x:row>
     <x:row r="47" customHeight="1">
       <x:c r="B47" s="4"/>
-      <x:c r="C47" s="4" t="str">
-        <x:v>分数加倍</x:v>
-      </x:c>
+      <x:c r="C47" s="4"/>
       <x:c r="D47" s="3" t="str">
-        <x:v>每3个</x:v>
+        <x:v>给钱</x:v>
       </x:c>
       <x:c r="E47" s="3" t="str">
-        <x:v>每上3个食物后，下一个食物倍率+2</x:v>
+        <x:v>使用主动道具时，获得20金币</x:v>
       </x:c>
       <x:c r="H47" s="1" t="n">
         <x:v>46</x:v>
       </x:c>
       <x:c r="I47" s="2" t="str">
         <x:f t="shared" si="0"/>
-        <x:v>每上3个食物后，下一个食物倍率+2</x:v>
+        <x:v>使用主动道具时，获得20金币</x:v>
       </x:c>
     </x:row>
     <x:row r="48" customHeight="1">
       <x:c r="B48" s="4"/>
       <x:c r="C48" s="4"/>
       <x:c r="D48" s="3" t="str">
-        <x:v>第一个</x:v>
+        <x:v>屏蔽</x:v>
       </x:c>
       <x:c r="E48" s="3" t="str">
-        <x:v>第一个上的食物，倍率x2</x:v>
+        <x:v>无法获得主动道具，获得1000金币</x:v>
       </x:c>
       <x:c r="H48" s="1" t="n">
         <x:v>47</x:v>
       </x:c>
       <x:c r="I48" s="2" t="str">
         <x:f t="shared" si="0"/>
-        <x:v>第一个上的食物，倍率x2</x:v>
+        <x:v>无法获得主动道具，获得1000金币</x:v>
       </x:c>
     </x:row>
     <x:row r="49" customHeight="1">
       <x:c r="B49" s="4"/>
-      <x:c r="C49" s="3"/>
+      <x:c r="C49" s="3" t="str">
+        <x:v>风味</x:v>
+      </x:c>
       <x:c r="D49" s="3" t="str">
-        <x:v>最后一个</x:v>
+        <x:v>强化风味</x:v>
       </x:c>
       <x:c r="E49" s="3" t="str">
-        <x:v>最后一个上的食物，倍率x2</x:v>
+        <x:v>强化两个随机风味到无风味食物上</x:v>
       </x:c>
       <x:c r="H49" s="1" t="n">
         <x:v>48</x:v>
       </x:c>
       <x:c r="I49" s="2" t="str">
         <x:f t="shared" si="0"/>
-        <x:v>最后一个上的食物，倍率x2</x:v>
+        <x:v>强化两个随机风味到无风味食物上</x:v>
       </x:c>
     </x:row>
     <x:row r="50" customHeight="1">
       <x:c r="B50" s="4"/>
-      <x:c r="C50" s="4" t="str">
-        <x:v>主动道具</x:v>
-      </x:c>
+      <x:c r="C50" s="4"/>
       <x:c r="D50" s="3" t="str">
-        <x:v>额外道具栏</x:v>
+        <x:v>移除风味+获得钱</x:v>
       </x:c>
       <x:c r="E50" s="3" t="str">
-        <x:v>增加2个额外主动道具栏</x:v>
+        <x:v>移除一个食物的风味，获得200金币</x:v>
       </x:c>
       <x:c r="H50" s="1" t="n">
         <x:v>49</x:v>
       </x:c>
       <x:c r="I50" s="2" t="str">
         <x:f t="shared" si="0"/>
-        <x:v>增加2个额外主动道具栏</x:v>
+        <x:v>移除一个食物的风味，获得200金币</x:v>
       </x:c>
     </x:row>
     <x:row r="51" customHeight="1">
       <x:c r="B51" s="4"/>
       <x:c r="C51" s="4"/>
       <x:c r="D51" s="3" t="str">
-        <x:v>给钱</x:v>
+        <x:v>移除风味+技能x2</x:v>
       </x:c>
       <x:c r="E51" s="3" t="str">
-        <x:v>使用主动道具时，获得20金币</x:v>
+        <x:v>移除一个食物的风味，其技能复制</x:v>
       </x:c>
       <x:c r="H51" s="1" t="n">
         <x:v>50</x:v>
       </x:c>
       <x:c r="I51" s="2" t="str">
         <x:f t="shared" si="0"/>
-        <x:v>使用主动道具时，获得20金币</x:v>
+        <x:v>移除一个食物的风味，其技能复制</x:v>
       </x:c>
     </x:row>
     <x:row r="52" customHeight="1">
       <x:c r="B52" s="4"/>
       <x:c r="C52" s="3"/>
       <x:c r="D52" s="3" t="str">
-        <x:v>屏蔽</x:v>
+        <x:v>基础风味+分数x2</x:v>
       </x:c>
       <x:c r="E52" s="3" t="str">
-        <x:v>无法获得主动道具，获得1000金币</x:v>
+        <x:v>移除一个食物的风味，其分数翻倍</x:v>
       </x:c>
       <x:c r="H52" s="1" t="n">
         <x:v>51</x:v>
       </x:c>
       <x:c r="I52" s="2" t="str">
         <x:f t="shared" si="0"/>
-        <x:v>无法获得主动道具，获得1000金币</x:v>
+        <x:v>移除一个食物的风味，其分数翻倍</x:v>
       </x:c>
     </x:row>
     <x:row r="53" customHeight="1">
       <x:c r="B53" s="4"/>
-      <x:c r="C53" s="4" t="str">
-        <x:v>风味</x:v>
-      </x:c>
+      <x:c r="C53" s="4"/>
       <x:c r="D53" s="3" t="str">
-        <x:v>强化风味</x:v>
+        <x:v>风味上限</x:v>
       </x:c>
       <x:c r="E53" s="3" t="str">
-        <x:v>强化两个随机风味到无风味食物上</x:v>
+        <x:v>允许一个食物拥有两个风味</x:v>
       </x:c>
       <x:c r="H53" s="1" t="n">
         <x:v>52</x:v>
       </x:c>
       <x:c r="I53" s="2" t="str">
         <x:f t="shared" si="0"/>
-        <x:v>强化两个随机风味到无风味食物上</x:v>
+        <x:v>允许一个食物拥有两个风味</x:v>
       </x:c>
     </x:row>
     <x:row r="54" customHeight="1">
       <x:c r="B54" s="4"/>
       <x:c r="C54" s="4"/>
       <x:c r="D54" s="3" t="str">
-        <x:v>移除风味+获得钱</x:v>
+        <x:v>风味传染</x:v>
       </x:c>
       <x:c r="E54" s="3" t="str">
-        <x:v>移除一个食物的风味，获得200金币</x:v>
+        <x:v>将一个食物的风味强化到无风味食物上</x:v>
       </x:c>
       <x:c r="H54" s="1" t="n">
         <x:v>53</x:v>
       </x:c>
       <x:c r="I54" s="2" t="str">
         <x:f t="shared" si="0"/>
-        <x:v>移除一个食物的风味，获得200金币</x:v>
+        <x:v>将一个食物的风味强化到无风味食物上</x:v>
       </x:c>
     </x:row>
     <x:row r="55" customHeight="1">
       <x:c r="B55" s="4"/>
-      <x:c r="C55" s="3"/>
+      <x:c r="C55" s="3" t="str">
+        <x:v>标签</x:v>
+      </x:c>
       <x:c r="D55" s="3" t="str">
-        <x:v>移除风味+技能x2</x:v>
+        <x:v>强化标签</x:v>
       </x:c>
       <x:c r="E55" s="3" t="str">
-        <x:v>移除一个食物的风味，其技能复制</x:v>
+        <x:v>强化两个随机标签到胃部格子上</x:v>
       </x:c>
       <x:c r="H55" s="1" t="n">
         <x:v>54</x:v>
       </x:c>
       <x:c r="I55" s="2" t="str">
         <x:f t="shared" si="0"/>
-        <x:v>移除一个食物的风味，其技能复制</x:v>
+        <x:v>强化两个随机标签到胃部格子上</x:v>
       </x:c>
     </x:row>
     <x:row r="56" customHeight="1">
       <x:c r="B56" s="4"/>
       <x:c r="C56" s="4"/>
       <x:c r="D56" s="3" t="str">
-        <x:v>基础风味+分数x2</x:v>
+        <x:v>标签传染</x:v>
       </x:c>
       <x:c r="E56" s="3" t="str">
-        <x:v>移除一个食物的风味，其分数翻倍</x:v>
+        <x:v>将一个格子的标签强化到其他格子上</x:v>
       </x:c>
       <x:c r="H56" s="1" t="n">
         <x:v>55</x:v>
       </x:c>
       <x:c r="I56" s="2" t="str">
         <x:f t="shared" si="0"/>
-        <x:v>移除一个食物的风味，其分数翻倍</x:v>
+        <x:v>将一个格子的标签强化到其他格子上</x:v>
       </x:c>
     </x:row>
     <x:row r="57" customHeight="1">
       <x:c r="B57" s="4"/>
-      <x:c r="C57" s="4"/>
+      <x:c r="C57" s="4" t="str">
+        <x:v>行动</x:v>
+      </x:c>
       <x:c r="D57" s="3" t="str">
-        <x:v>风味上限</x:v>
+        <x:v>好运</x:v>
       </x:c>
       <x:c r="E57" s="3" t="str">
-        <x:v>允许一个食物拥有两个风味</x:v>
+        <x:v>每4个事件的最后一个是奖励事件</x:v>
       </x:c>
       <x:c r="H57" s="1" t="n">
         <x:v>56</x:v>
       </x:c>
       <x:c r="I57" s="2" t="str">
         <x:f t="shared" si="0"/>
-        <x:v>允许一个食物拥有两个风味</x:v>
+        <x:v>每4个事件的最后一个是奖励事件</x:v>
       </x:c>
     </x:row>
     <x:row r="58" customHeight="1">
       <x:c r="B58" s="4"/>
       <x:c r="C58" s="4"/>
       <x:c r="D58" s="3" t="str">
-        <x:v>风味传染</x:v>
+        <x:v>好运</x:v>
       </x:c>
       <x:c r="E58" s="3" t="str">
-        <x:v>将一个食物的风味强化到无风味食物上</x:v>
+        <x:v>事件中遇到奖励的概率提高</x:v>
       </x:c>
       <x:c r="H58" s="1" t="n">
         <x:v>57</x:v>
       </x:c>
       <x:c r="I58" s="2" t="str">
         <x:f t="shared" si="0"/>
-        <x:v>将一个食物的风味强化到无风味食物上</x:v>
+        <x:v>事件中遇到奖励的概率提高</x:v>
       </x:c>
     </x:row>
     <x:row r="59" customHeight="1">
       <x:c r="B59" s="4"/>
-      <x:c r="C59" s="4" t="str">
-        <x:v>标签</x:v>
-      </x:c>
+      <x:c r="C59" s="4"/>
       <x:c r="D59" s="3" t="str">
-        <x:v>强化标签</x:v>
+        <x:v>事件变多</x:v>
       </x:c>
       <x:c r="E59" s="3" t="str">
-        <x:v>强化两个随机标签到胃部格子上</x:v>
+        <x:v>遇到事件的概率提高</x:v>
       </x:c>
       <x:c r="H59" s="1" t="n">
         <x:v>58</x:v>
       </x:c>
       <x:c r="I59" s="2" t="str">
         <x:f t="shared" si="0"/>
-        <x:v>强化两个随机标签到胃部格子上</x:v>
+        <x:v>遇到事件的概率提高</x:v>
       </x:c>
     </x:row>
     <x:row r="60" customHeight="1">
       <x:c r="B60" s="4"/>
       <x:c r="C60" s="4"/>
       <x:c r="D60" s="3" t="str">
-        <x:v>标签传染</x:v>
+        <x:v>事件给钱</x:v>
       </x:c>
       <x:c r="E60" s="3" t="str">
-        <x:v>将一个格子的标签强化到其他格子上</x:v>
+        <x:v>完成一个事件，获得10金币</x:v>
       </x:c>
       <x:c r="H60" s="1" t="n">
         <x:v>59</x:v>
       </x:c>
       <x:c r="I60" s="2" t="str">
         <x:f t="shared" si="0"/>
-        <x:v>将一个格子的标签强化到其他格子上</x:v>
+        <x:v>完成一个事件，获得10金币</x:v>
       </x:c>
     </x:row>
     <x:row r="61" customHeight="1">
       <x:c r="B61" s="4"/>
-      <x:c r="C61" s="3" t="str">
-        <x:v>行动</x:v>
-      </x:c>
+      <x:c r="C61" s="3"/>
       <x:c r="D61" s="3" t="str">
-        <x:v>好运</x:v>
+        <x:v>重新随机</x:v>
       </x:c>
       <x:c r="E61" s="3" t="str">
-        <x:v>每4个事件的最后一个是奖励事件</x:v>
+        <x:v>获得2次重新随机行动的</x:v>
       </x:c>
       <x:c r="H61" s="1" t="n">
         <x:v>60</x:v>
       </x:c>
       <x:c r="I61" s="2" t="str">
         <x:f t="shared" si="0"/>
-        <x:v>每4个事件的最后一个是奖励事件</x:v>
+        <x:v>商店会自动补货</x:v>
       </x:c>
     </x:row>
     <x:row r="62" customHeight="1">
       <x:c r="B62" s="4"/>
-      <x:c r="C62" s="4"/>
+      <x:c r="C62" s="4" t="str">
+        <x:v>商店</x:v>
+      </x:c>
       <x:c r="D62" s="3" t="str">
-        <x:v>好运</x:v>
+        <x:v>补货</x:v>
       </x:c>
       <x:c r="E62" s="3" t="str">
-        <x:v>事件中遇到奖励的概率提高</x:v>
+        <x:v>商店会自动补货</x:v>
       </x:c>
       <x:c r="H62" s="1" t="n">
         <x:v>61</x:v>
       </x:c>
       <x:c r="I62" s="2" t="str">
         <x:f t="shared" si="0"/>
-        <x:v>事件中遇到奖励的概率提高</x:v>
+        <x:v>每3次超级美食，额外获得一个多选一物品</x:v>
       </x:c>
     </x:row>
     <x:row r="63" customHeight="1">
       <x:c r="B63" s="4"/>
-      <x:c r="C63" s="3"/>
+      <x:c r="C63" s="3" t="str">
+        <x:v>美食</x:v>
+      </x:c>
       <x:c r="D63" s="3" t="str">
-        <x:v>事件变多</x:v>
+        <x:v>选择变多</x:v>
       </x:c>
       <x:c r="E63" s="3" t="str">
-        <x:v>遇到事件的概率提高</x:v>
+        <x:v>多选一食物时，可选数量+1</x:v>
       </x:c>
       <x:c r="H63" s="1" t="n">
         <x:v>62</x:v>
       </x:c>
       <x:c r="I63" s="2" t="str">
         <x:f t="shared" si="0"/>
-        <x:v>遇到事件的概率提高</x:v>
+        <x:v>多选一食物时，可选数量+1</x:v>
       </x:c>
     </x:row>
     <x:row r="64" customHeight="1">
       <x:c r="B64" s="4"/>
       <x:c r="C64" s="4"/>
       <x:c r="D64" s="3" t="str">
-        <x:v>事件给钱</x:v>
+        <x:v>多选择</x:v>
       </x:c>
       <x:c r="E64" s="3" t="str">
-        <x:v>完成一个事件，获得10金币</x:v>
+        <x:v>多选一食物时，可选次数+1，可选数量-1</x:v>
       </x:c>
       <x:c r="H64" s="1" t="n">
         <x:v>63</x:v>
       </x:c>
       <x:c r="I64" s="2" t="str">
         <x:f t="shared" si="0"/>
-        <x:v>完成一个事件，获得10金币</x:v>
+        <x:v>多选一食物时，可选次数+1，可选数量-1</x:v>
       </x:c>
     </x:row>
     <x:row r="65" customHeight="1">
       <x:c r="B65" s="4"/>
       <x:c r="C65" s="4"/>
       <x:c r="D65" s="3" t="str">
-        <x:v>重新随机</x:v>
+        <x:v>额外美食</x:v>
       </x:c>
       <x:c r="E65" s="3" t="str">
-        <x:v>获得2次重新随机行动的</x:v>
+        <x:v>每3次普通美食，额外获得一个多选一美食</x:v>
       </x:c>
       <x:c r="H65" s="1" t="n">
         <x:v>64</x:v>
       </x:c>
       <x:c r="I65" s="2" t="str">
         <x:f t="shared" si="0"/>
-        <x:v>商店会自动补货</x:v>
+        <x:v>每3次普通美食，额外获得一个多选一美食</x:v>
       </x:c>
     </x:row>
     <x:row r="66" customHeight="1">
       <x:c r="B66" s="4"/>
-      <x:c r="C66" s="4" t="str">
-        <x:v>商店</x:v>
-      </x:c>
+      <x:c r="C66" s="4"/>
       <x:c r="D66" s="3" t="str">
-        <x:v>补货</x:v>
+        <x:v>额外物品</x:v>
       </x:c>
       <x:c r="E66" s="3" t="str">
-        <x:v>商店会自动补货</x:v>
+        <x:v>每3次超级美食，额外获得一个多选一物品</x:v>
       </x:c>
       <x:c r="H66" s="1" t="n">
         <x:v>65</x:v>
       </x:c>
       <x:c r="I66" s="2" t="str">
         <x:f t="shared" ref="I66:I94" si="1">E66</x:f>
-        <x:v>商店会自动补货</x:v>
+        <x:v>每3次超级美食，额外获得一个多选一物品</x:v>
       </x:c>
     </x:row>
     <x:row r="67" customHeight="1">
       <x:c r="B67" s="4"/>
-      <x:c r="C67" s="4" t="str">
-        <x:v>美食</x:v>
-      </x:c>
+      <x:c r="C67" s="4"/>
       <x:c r="D67" s="3" t="str">
-        <x:v>选择变多</x:v>
+        <x:v>复制美食</x:v>
       </x:c>
       <x:c r="E67" s="3" t="str">
-        <x:v>多选一食物时，可选数量+1</x:v>
+        <x:v>随机复制一个美食</x:v>
       </x:c>
       <x:c r="H67" s="1" t="n">
         <x:v>66</x:v>
       </x:c>
       <x:c r="I67" s="2" t="str">
         <x:f t="shared" si="1"/>
-        <x:v>多选一食物时，可选数量+1</x:v>
+        <x:v>随机复制一个美食</x:v>
       </x:c>
     </x:row>
     <x:row r="68" customHeight="1">
       <x:c r="B68" s="4"/>
-      <x:c r="C68" s="3"/>
+      <x:c r="C68" s="3" t="str">
+        <x:v>负面</x:v>
+      </x:c>
       <x:c r="D68" s="3" t="str">
-        <x:v>多选择</x:v>
+        <x:v>丢弃</x:v>
       </x:c>
       <x:c r="E68" s="3" t="str">
-        <x:v>多选一食物时，可选次数+1，可选数量-1</x:v>
+        <x:v>丢弃两个负面道具</x:v>
       </x:c>
       <x:c r="H68" s="1" t="n">
         <x:v>67</x:v>
       </x:c>
       <x:c r="I68" s="2" t="str">
         <x:f t="shared" si="1"/>
-        <x:v>多选一食物时，可选次数+1，可选数量-1</x:v>
+        <x:v>丢弃两个负面道具</x:v>
       </x:c>
     </x:row>
     <x:row r="69" customHeight="1">
       <x:c r="B69" s="4"/>
       <x:c r="C69" s="3"/>
       <x:c r="D69" s="3" t="str">
-        <x:v>额外美食</x:v>
+        <x:v>转化</x:v>
       </x:c>
       <x:c r="E69" s="3" t="str">
-        <x:v>每3次普通美食，额外获得一个多选一美食</x:v>
+        <x:v>丢弃所有负面道具，每丢弃一个获得100金币</x:v>
       </x:c>
       <x:c r="H69" s="1" t="n">
         <x:v>68</x:v>
       </x:c>
       <x:c r="I69" s="2" t="str">
         <x:f t="shared" si="1"/>
-        <x:v>每3次普通美食，额外获得一个多选一美食</x:v>
+        <x:v>丢弃所有负面道具，每丢弃一个获得100金币</x:v>
       </x:c>
     </x:row>
     <x:row r="70" customHeight="1">
-      <x:c r="B70" s="4"/>
-      <x:c r="C70" s="4"/>
+      <x:c r="B70" s="4" t="str">
+        <x:v>通用负面</x:v>
+      </x:c>
+      <x:c r="C70" s="4" t="str">
+        <x:v>运营</x:v>
+      </x:c>
       <x:c r="D70" s="3" t="str">
-        <x:v>额外物品</x:v>
+        <x:v>金币减少</x:v>
       </x:c>
       <x:c r="E70" s="3" t="str">
-        <x:v>每3次超级美食，额外获得一个多选一物品</x:v>
+        <x:v>美食获得的金币减少25%</x:v>
       </x:c>
       <x:c r="H70" s="1" t="n">
         <x:v>69</x:v>
       </x:c>
       <x:c r="I70" s="2" t="str">
         <x:f t="shared" si="1"/>
-        <x:v>每3次超级美食，额外获得一个多选一物品</x:v>
+        <x:v>美食获得的金币减少25%</x:v>
       </x:c>
     </x:row>
     <x:row r="71" customHeight="1">
       <x:c r="B71" s="4"/>
       <x:c r="C71" s="4"/>
       <x:c r="D71" s="3" t="str">
-        <x:v>复制美食</x:v>
+        <x:v>价格变高</x:v>
       </x:c>
       <x:c r="E71" s="3" t="str">
-        <x:v>随机复制一个美食</x:v>
+        <x:v>商店的价格变高25%</x:v>
       </x:c>
       <x:c r="H71" s="1" t="n">
         <x:v>70</x:v>
       </x:c>
       <x:c r="I71" s="2" t="str">
         <x:f t="shared" si="1"/>
-        <x:v>随机复制一个美食</x:v>
+        <x:v>商店的价格变高25%</x:v>
       </x:c>
     </x:row>
     <x:row r="72" customHeight="1">
       <x:c r="B72" s="4"/>
-      <x:c r="C72" s="4" t="str">
-        <x:v>负面</x:v>
-      </x:c>
+      <x:c r="C72" s="4"/>
       <x:c r="D72" s="3" t="str">
-        <x:v>丢弃</x:v>
+        <x:v>无法删菜</x:v>
       </x:c>
       <x:c r="E72" s="3" t="str">
-        <x:v>丢弃两个负面道具</x:v>
+        <x:v>无法再删除食物</x:v>
       </x:c>
       <x:c r="H72" s="1" t="n">
         <x:v>71</x:v>
       </x:c>
       <x:c r="I72" s="2" t="str">
         <x:f t="shared" si="1"/>
-        <x:v>丢弃两个负面道具</x:v>
+        <x:v>无法再删除食物</x:v>
       </x:c>
     </x:row>
     <x:row r="73" customHeight="1">
       <x:c r="B73" s="4"/>
       <x:c r="C73" s="4"/>
       <x:c r="D73" s="3" t="str">
-        <x:v>转化</x:v>
+        <x:v>节点失效</x:v>
       </x:c>
       <x:c r="E73" s="3" t="str">
-        <x:v>丢弃所有负面道具，每丢弃一个获得100金币</x:v>
+        <x:v>跳过下一个商店或利息节点</x:v>
       </x:c>
       <x:c r="H73" s="1" t="n">
         <x:v>72</x:v>
       </x:c>
       <x:c r="I73" s="2" t="str">
         <x:f t="shared" si="1"/>
-        <x:v>丢弃所有负面道具，每丢弃一个获得100金币</x:v>
+        <x:v>跳过下一个商店或利息节点</x:v>
       </x:c>
     </x:row>
     <x:row r="74" customHeight="1">
-      <x:c r="B74" s="4" t="str">
-        <x:v>通用负面</x:v>
-      </x:c>
-      <x:c r="C74" s="3" t="str">
-        <x:v>运营</x:v>
-      </x:c>
+      <x:c r="B74" s="4"/>
+      <x:c r="C74" s="3"/>
       <x:c r="D74" s="3" t="str">
-        <x:v>金币减少</x:v>
+        <x:v>少选择</x:v>
       </x:c>
       <x:c r="E74" s="3" t="str">
-        <x:v>美食获得的金币减少25%</x:v>
+        <x:v>多选一食物时，可选数量-1</x:v>
       </x:c>
       <x:c r="H74" s="1" t="n">
         <x:v>73</x:v>
       </x:c>
       <x:c r="I74" s="2" t="str">
         <x:f t="shared" si="1"/>
-        <x:v>美食获得的金币减少25%</x:v>
+        <x:v>多选一食物时，可选数量-1</x:v>
       </x:c>
     </x:row>
     <x:row r="75" customHeight="1">
       <x:c r="B75" s="4"/>
       <x:c r="C75" s="3"/>
       <x:c r="D75" s="3" t="str">
-        <x:v>价格变高</x:v>
+        <x:v>普通美食分数增多</x:v>
       </x:c>
       <x:c r="E75" s="3" t="str">
-        <x:v>商店的价格变高25%</x:v>
+        <x:v>普通美食要求分数+10%</x:v>
       </x:c>
       <x:c r="H75" s="1" t="n">
         <x:v>74</x:v>
       </x:c>
       <x:c r="I75" s="2" t="str">
         <x:f t="shared" si="1"/>
-        <x:v>商店的价格变高25%</x:v>
+        <x:v>普通美食要求分数+10%</x:v>
       </x:c>
     </x:row>
     <x:row r="76" customHeight="1">
       <x:c r="B76" s="3"/>
       <x:c r="C76" s="3"/>
       <x:c r="D76" s="3" t="str">
-        <x:v>无法删菜</x:v>
+        <x:v>超级美食分数增多</x:v>
       </x:c>
       <x:c r="E76" s="3" t="str">
-        <x:v>无法再删除食物</x:v>
+        <x:v>超级美食要求分数+10%</x:v>
       </x:c>
       <x:c r="H76" s="1" t="n">
         <x:v>75</x:v>
       </x:c>
       <x:c r="I76" s="2" t="str">
         <x:f t="shared" si="1"/>
-        <x:v>无法再删除食物</x:v>
+        <x:v>超级美食要求分数+10%</x:v>
       </x:c>
     </x:row>
     <x:row r="77" customHeight="1">
       <x:c r="B77" s="4"/>
       <x:c r="C77" s="4"/>
       <x:c r="D77" s="3" t="str">
-        <x:v>节点失效</x:v>
+        <x:v>盛宴美食分数增多</x:v>
       </x:c>
       <x:c r="E77" s="3" t="str">
-        <x:v>跳过下一个商店或利息节点</x:v>
+        <x:v>盛宴美食要求分数+10%</x:v>
       </x:c>
       <x:c r="H77" s="1" t="n">
         <x:v>76</x:v>
       </x:c>
       <x:c r="I77" s="2" t="str">
         <x:f t="shared" si="1"/>
-        <x:v>跳过下一个商店或利息节点</x:v>
+        <x:v>盛宴美食要求分数+10%</x:v>
       </x:c>
     </x:row>
     <x:row r="78" customHeight="1">
       <x:c r="B78" s="4"/>
       <x:c r="C78" s="4"/>
       <x:c r="D78" s="3" t="str">
-        <x:v>少选择</x:v>
+        <x:v>金币清空</x:v>
       </x:c>
       <x:c r="E78" s="3" t="str">
-        <x:v>多选一食物时，可选数量-1</x:v>
+        <x:v>本周结束时，金币清空</x:v>
       </x:c>
       <x:c r="H78" s="1" t="n">
         <x:v>77</x:v>
       </x:c>
       <x:c r="I78" s="2" t="str">
         <x:f t="shared" si="1"/>
-        <x:v>多选一食物时，可选数量-1</x:v>
+        <x:v>本周结束时，金币清空</x:v>
       </x:c>
     </x:row>
     <x:row r="79" customHeight="1">
-      <x:c r="B79" s="4"/>
-      <x:c r="C79" s="4"/>
+      <x:c r="B79" s="4" t="str">
+        <x:v>专有</x:v>
+      </x:c>
+      <x:c r="C79" s="4" t="str">
+        <x:v>小而多</x:v>
+      </x:c>
       <x:c r="D79" s="3" t="str">
-        <x:v>普通美食分数增多</x:v>
+        <x:v>额外视为</x:v>
       </x:c>
       <x:c r="E79" s="3" t="str">
-        <x:v>普通美食要求分数+10%</x:v>
+        <x:v>所有食物额外被视为1个食物</x:v>
       </x:c>
       <x:c r="H79" s="1" t="n">
         <x:v>78</x:v>
       </x:c>
       <x:c r="I79" s="2" t="str">
         <x:f t="shared" si="1"/>
-        <x:v>普通美食要求分数+10%</x:v>
+        <x:v>所有食物额外被视为1个食物</x:v>
       </x:c>
     </x:row>
     <x:row r="80" customHeight="1">
       <x:c r="B80" s="4"/>
-      <x:c r="C80" s="4"/>
+      <x:c r="C80" s="4" t="str">
+        <x:v>传递</x:v>
+      </x:c>
       <x:c r="D80" s="3" t="str">
-        <x:v>超级美食分数增多</x:v>
+        <x:v>传递加分</x:v>
       </x:c>
       <x:c r="E80" s="3" t="str">
-        <x:v>超级美食要求分数+10%</x:v>
+        <x:v>传递时，被传递方倍率x1.1</x:v>
       </x:c>
       <x:c r="H80" s="1" t="n">
         <x:v>79</x:v>
       </x:c>
       <x:c r="I80" s="2" t="str">
         <x:f t="shared" si="1"/>
-        <x:v>超级美食要求分数+10%</x:v>
+        <x:v>传递时，被传递方倍率x1.1</x:v>
       </x:c>
     </x:row>
     <x:row r="81" customHeight="1">
       <x:c r="B81" s="4"/>
       <x:c r="C81" s="4"/>
       <x:c r="D81" s="3" t="str">
-        <x:v>盛宴美食分数增多</x:v>
+        <x:v>传递加分</x:v>
       </x:c>
       <x:c r="E81" s="3" t="str">
-        <x:v>盛宴美食要求分数+10%</x:v>
+        <x:v>传递时，传递方倍率x1.1</x:v>
       </x:c>
       <x:c r="H81" s="1" t="n">
         <x:v>80</x:v>
       </x:c>
       <x:c r="I81" s="2" t="str">
         <x:f t="shared" si="1"/>
-        <x:v>盛宴美食要求分数+10%</x:v>
+        <x:v>传递时，传递方倍率x1.1</x:v>
       </x:c>
     </x:row>
     <x:row r="82" customHeight="1">
       <x:c r="B82" s="4"/>
       <x:c r="C82" s="4"/>
       <x:c r="D82" s="3" t="str">
-        <x:v>金币清空</x:v>
+        <x:v>技能数加分</x:v>
       </x:c>
       <x:c r="E82" s="3" t="str">
-        <x:v>本周结束时，金币清空</x:v>
+        <x:v>结算时，倍率x1（每一个技能+0.1倍）</x:v>
       </x:c>
       <x:c r="H82" s="1" t="n">
         <x:v>81</x:v>
       </x:c>
       <x:c r="I82" s="2" t="str">
         <x:f t="shared" si="1"/>
-        <x:v>本周结束时，金币清空</x:v>
+        <x:v>结算时，倍率x1（每一个技能+0.1倍）</x:v>
       </x:c>
     </x:row>
     <x:row r="83" customHeight="1">
-      <x:c r="B83" s="4" t="str">
-        <x:v>专有</x:v>
-      </x:c>
-      <x:c r="C83" s="4" t="str">
-        <x:v>小而多</x:v>
-      </x:c>
+      <x:c r="B83" s="4"/>
+      <x:c r="C83" s="4"/>
       <x:c r="D83" s="3" t="str">
-        <x:v>额外视为</x:v>
+        <x:v>传递加钱</x:v>
       </x:c>
       <x:c r="E83" s="3" t="str">
-        <x:v>所有食物额外被视为1个食物</x:v>
+        <x:v>传递10次后，获得10金币</x:v>
       </x:c>
       <x:c r="H83" s="1" t="n">
         <x:v>82</x:v>
       </x:c>
       <x:c r="I83" s="2" t="str">
         <x:f t="shared" si="1"/>
-        <x:v>所有食物额外被视为1个食物</x:v>
+        <x:v>传递10次后，获得10金币</x:v>
       </x:c>
     </x:row>
     <x:row r="84" customHeight="1">
       <x:c r="B84" s="4"/>
       <x:c r="C84" s="4" t="str">
-        <x:v>传递</x:v>
+        <x:v>蛋糕</x:v>
       </x:c>
       <x:c r="D84" s="3" t="str">
-        <x:v>传递加分</x:v>
+        <x:v>层数保留</x:v>
       </x:c>
       <x:c r="E84" s="3" t="str">
-        <x:v>传递时，被传递方倍率x1.1</x:v>
+        <x:v>每次保留10%的蛋糕层数至下一次美食</x:v>
       </x:c>
       <x:c r="H84" s="1" t="n">
         <x:v>83</x:v>
       </x:c>
       <x:c r="I84" s="2" t="str">
         <x:f t="shared" si="1"/>
-        <x:v>传递时，被传递方倍率x1.1</x:v>
+        <x:v>每次保留10%的蛋糕层数至下一次美食</x:v>
       </x:c>
     </x:row>
     <x:row r="85" customHeight="1">
       <x:c r="B85" s="3"/>
       <x:c r="C85" s="3"/>
       <x:c r="D85" s="3" t="str">
-        <x:v>传递加分</x:v>
+        <x:v>层数保底</x:v>
       </x:c>
       <x:c r="E85" s="3" t="str">
-        <x:v>传递时，传递方倍率x1.1</x:v>
+        <x:v>蛋糕层数初始额外获得10层</x:v>
       </x:c>
       <x:c r="H85" s="1" t="n">
         <x:v>84</x:v>
       </x:c>
       <x:c r="I85" s="2" t="str">
         <x:f t="shared" si="1"/>
-        <x:v>传递时，传递方倍率x1.1</x:v>
+        <x:v>蛋糕层数初始额外获得10层</x:v>
       </x:c>
     </x:row>
     <x:row r="86" customHeight="1">
       <x:c r="B86" s="4"/>
       <x:c r="C86" s="3"/>
       <x:c r="D86" s="3" t="str">
-        <x:v>技能数加分</x:v>
+        <x:v>加速叠层</x:v>
       </x:c>
       <x:c r="E86" s="3" t="str">
-        <x:v>结算时，倍率x1（每一个技能+0.1倍）</x:v>
+        <x:v>蛋糕层数增加时，额外加1层</x:v>
       </x:c>
       <x:c r="H86" s="1" t="n">
         <x:v>85</x:v>
       </x:c>
       <x:c r="I86" s="2" t="str">
         <x:f t="shared" si="1"/>
-        <x:v>结算时，倍率x1（每一个技能+0.1倍）</x:v>
+        <x:v>蛋糕层数增加时，额外加1层</x:v>
       </x:c>
     </x:row>
     <x:row r="87" customHeight="1">
       <x:c r="B87" s="4"/>
       <x:c r="C87" s="4"/>
       <x:c r="D87" s="3" t="str">
-        <x:v>传递加钱</x:v>
+        <x:v>层数转钱</x:v>
       </x:c>
       <x:c r="E87" s="3" t="str">
-        <x:v>传递10次后，获得10金币</x:v>
+        <x:v>蛋糕层数大于100层时，获得10金币</x:v>
       </x:c>
       <x:c r="H87" s="1" t="n">
         <x:v>86</x:v>
       </x:c>
       <x:c r="I87" s="2" t="str">
         <x:f t="shared" si="1"/>
-        <x:v>传递10次后，获得10金币</x:v>
+        <x:v>蛋糕层数大于100层时，获得10金币</x:v>
       </x:c>
     </x:row>
     <x:row r="88" customHeight="1">
       <x:c r="B88" s="4"/>
-      <x:c r="C88" s="4" t="str">
-        <x:v>蛋糕</x:v>
-      </x:c>
+      <x:c r="C88" s="4"/>
       <x:c r="D88" s="3" t="str">
-        <x:v>层数保留</x:v>
+        <x:v>要求减少</x:v>
       </x:c>
       <x:c r="E88" s="3" t="str">
-        <x:v>每次保留10%的蛋糕层数至下一次美食</x:v>
+        <x:v>蛋糕效果需求的层数-10</x:v>
       </x:c>
       <x:c r="H88" s="1" t="n">
         <x:v>87</x:v>
       </x:c>
       <x:c r="I88" s="2" t="str">
         <x:f t="shared" si="1"/>
-        <x:v>每次保留10%的蛋糕层数至下一次美食</x:v>
+        <x:v>蛋糕效果需求的层数-10</x:v>
       </x:c>
     </x:row>
     <x:row r="89" customHeight="1">
       <x:c r="B89" s="4"/>
       <x:c r="C89" s="4"/>
-      <x:c r="D89" s="3" t="str">
-        <x:v>层数保底</x:v>
-      </x:c>
-      <x:c r="E89" s="3" t="str">
-        <x:v>蛋糕层数初始额外获得10层</x:v>
-      </x:c>
+      <x:c r="D89" s="3"/>
+      <x:c r="E89" s="3"/>
       <x:c r="H89" s="1" t="n">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="I89" s="2" t="str">
+      <x:c r="I89" s="2">
         <x:f t="shared" si="1"/>
-        <x:v>蛋糕层数初始额外获得10层</x:v>
       </x:c>
     </x:row>
     <x:row r="90" customHeight="1">
       <x:c r="B90"/>
       <x:c r="C90" s="3"/>
-      <x:c r="D90" s="3" t="str">
-        <x:v>加速叠层</x:v>
-      </x:c>
-      <x:c r="E90" s="3" t="str">
-        <x:v>蛋糕层数增加时，额外加1层</x:v>
-      </x:c>
-      <x:c r="H90" s="1" t="n">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="I90" s="2" t="str">
+      <x:c r="D90" s="3"/>
+      <x:c r="E90" s="3"/>
+      <x:c r="H90" s="1"/>
+      <x:c r="I90" s="2">
         <x:f t="shared" si="1"/>
-        <x:v>蛋糕层数增加时，额外加1层</x:v>
       </x:c>
     </x:row>
     <x:row r="91" customHeight="1">
       <x:c r="B91" s="4"/>
       <x:c r="C91" s="4"/>
-      <x:c r="D91" s="3" t="str">
-        <x:v>层数转钱</x:v>
-      </x:c>
-      <x:c r="E91" s="3" t="str">
-        <x:v>蛋糕层数大于100层时，获得10金币</x:v>
-      </x:c>
-      <x:c r="H91" s="1" t="n">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="I91" s="2" t="str">
+      <x:c r="D91" s="3"/>
+      <x:c r="E91" s="3"/>
+      <x:c r="H91" s="1"/>
+      <x:c r="I91" s="2">
         <x:f t="shared" si="1"/>
-        <x:v>蛋糕层数大于100层时，获得10金币</x:v>
       </x:c>
     </x:row>
     <x:row r="92" customHeight="1">
       <x:c r="B92" s="4"/>
       <x:c r="C92" s="4"/>
-      <x:c r="D92" s="3" t="str">
-        <x:v>要求减少</x:v>
-      </x:c>
-      <x:c r="E92" s="3" t="str">
-        <x:v>蛋糕效果需求的层数-10</x:v>
-      </x:c>
-      <x:c r="H92" s="1" t="n">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="I92" s="2" t="str">
+      <x:c r="D92" s="3"/>
+      <x:c r="E92" s="3"/>
+      <x:c r="H92" s="1"/>
+      <x:c r="I92" s="2">
         <x:f t="shared" si="1"/>
-        <x:v>蛋糕效果需求的层数-10</x:v>
       </x:c>
     </x:row>
     <x:row r="93" customHeight="1">
@@ -8416,9 +8266,7 @@
       <x:c r="C93" s="4"/>
       <x:c r="D93" s="3"/>
       <x:c r="E93" s="3"/>
-      <x:c r="H93" s="1" t="n">
-        <x:v>92</x:v>
-      </x:c>
+      <x:c r="H93" s="1"/>
       <x:c r="I93" s="2">
         <x:f t="shared" si="1"/>
       </x:c>

--- a/GourmetProject/GameConfig/Datas/item.xlsx
+++ b/GourmetProject/GameConfig/Datas/item.xlsx
@@ -4,19 +4,32 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15240" activeTab="1"/>
+    <workbookView windowHeight="16760" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="被动道具" sheetId="1" r:id="rId1"/>
     <sheet name="主动道具" sheetId="2" r:id="rId2"/>
     <sheet name="道具设计" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="909" uniqueCount="568">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="922" uniqueCount="568">
   <si>
     <t>##var</t>
   </si>
@@ -283,9 +296,6 @@
   </si>
   <si>
     <t>丢弃次数+1</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>item_trash_expand</t>
@@ -715,6 +725,9 @@
     <t>商店会自动补货食物</t>
   </si>
   <si>
+    <t>##</t>
+  </si>
+  <si>
     <t>商店会自动补货主动道具</t>
   </si>
   <si>
@@ -1029,7 +1042,7 @@
     <t>t_sweet</t>
   </si>
   <si>
-    <t>RecipeDish</t>
+    <t>DiningTableDish</t>
   </si>
   <si>
     <t>item_active_season_bitter</t>
@@ -1779,7 +1792,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -2418,7 +2431,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2454,16 +2467,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3335,7 +3341,7 @@
       <c r="F5" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="H5" s="23" t="s">
+      <c r="H5" s="20" t="s">
         <v>56</v>
       </c>
       <c r="I5" s="1">
@@ -3707,360 +3713,344 @@
       </c>
     </row>
     <row r="12" s="14" customFormat="1" ht="17" spans="1:18">
-      <c r="A12" s="17"/>
-      <c r="B12" s="18" t="s">
+      <c r="A12" s="16"/>
+      <c r="B12" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="C12" s="18" t="s">
+      <c r="C12" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="D12" s="19" t="s">
+      <c r="D12" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="E12" s="18" t="s">
+      <c r="E12" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="F12" s="18" t="s">
+      <c r="F12" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="G12" s="18">
+      <c r="G12" s="16">
         <v>1</v>
       </c>
-      <c r="H12" s="14" t="s">
+      <c r="H12" s="14"/>
+      <c r="I12" s="16">
+        <v>300</v>
+      </c>
+      <c r="J12" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="K12" s="16">
+        <v>0</v>
+      </c>
+      <c r="L12" s="16">
+        <v>0</v>
+      </c>
+      <c r="M12" s="16">
+        <v>0</v>
+      </c>
+      <c r="N12" s="16">
+        <v>0</v>
+      </c>
+      <c r="O12" s="16">
+        <v>0</v>
+      </c>
+      <c r="P12" s="16">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="14"/>
+      <c r="R12" s="14">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" s="14" customFormat="1" ht="17" spans="1:18">
+      <c r="A13" s="16"/>
+      <c r="B13" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="I12" s="18">
+      <c r="C13" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="D13" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="E13" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="F13" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="G13" s="16">
+        <v>1</v>
+      </c>
+      <c r="H13" s="14"/>
+      <c r="I13" s="16">
         <v>300</v>
       </c>
-      <c r="J12" s="18" t="s">
+      <c r="J13" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="K12" s="18">
-        <v>0</v>
-      </c>
-      <c r="L12" s="18">
-        <v>0</v>
-      </c>
-      <c r="M12" s="18">
-        <v>0</v>
-      </c>
-      <c r="N12" s="18">
-        <v>0</v>
-      </c>
-      <c r="O12" s="18">
-        <v>0</v>
-      </c>
-      <c r="P12" s="18">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="R12" s="15">
+      <c r="K13" s="16">
+        <v>0</v>
+      </c>
+      <c r="L13" s="16">
+        <v>0</v>
+      </c>
+      <c r="M13" s="16">
+        <v>0</v>
+      </c>
+      <c r="N13" s="16">
+        <v>0</v>
+      </c>
+      <c r="O13" s="16">
+        <v>0</v>
+      </c>
+      <c r="P13" s="16">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="14"/>
+      <c r="R13" s="14">
         <v>50</v>
       </c>
     </row>
-    <row r="13" s="14" customFormat="1" ht="17" spans="1:18">
-      <c r="A13" s="17"/>
-      <c r="B13" s="18" t="s">
-        <v>89</v>
-      </c>
-      <c r="C13" s="18" t="s">
+    <row r="14" s="14" customFormat="1" ht="17" spans="1:18">
+      <c r="A14" s="16"/>
+      <c r="B14" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="D13" s="19" t="s">
-        <v>87</v>
-      </c>
-      <c r="E13" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="F13" s="18" t="s">
+      <c r="C14" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="D14" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="E14" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="F14" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="G13" s="18">
-        <v>1</v>
-      </c>
-      <c r="H13" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="I13" s="18">
-        <v>300</v>
-      </c>
-      <c r="J13" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="K13" s="18">
-        <v>0</v>
-      </c>
-      <c r="L13" s="18">
-        <v>0</v>
-      </c>
-      <c r="M13" s="18">
-        <v>0</v>
-      </c>
-      <c r="N13" s="18">
-        <v>0</v>
-      </c>
-      <c r="O13" s="18">
-        <v>0</v>
-      </c>
-      <c r="P13" s="18">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="R13" s="15">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="14" s="14" customFormat="1" ht="17" spans="1:18">
-      <c r="A14" s="17"/>
-      <c r="B14" s="18" t="s">
-        <v>91</v>
-      </c>
-      <c r="C14" s="18" t="s">
+      <c r="G14" s="16">
+        <v>2</v>
+      </c>
+      <c r="H14" s="14"/>
+      <c r="I14" s="16">
+        <v>100</v>
+      </c>
+      <c r="J14" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="K14" s="16">
+        <v>0</v>
+      </c>
+      <c r="L14" s="16">
+        <v>0</v>
+      </c>
+      <c r="M14" s="16">
+        <v>0</v>
+      </c>
+      <c r="N14" s="16">
+        <v>0</v>
+      </c>
+      <c r="O14" s="16">
+        <v>0</v>
+      </c>
+      <c r="P14" s="16">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="14"/>
+      <c r="R14" s="14">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="15" s="14" customFormat="1" ht="17" spans="1:18">
+      <c r="A15" s="16"/>
+      <c r="B15" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="D15" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="D14" s="19" t="s">
-        <v>93</v>
-      </c>
-      <c r="E14" s="18" t="s">
+      <c r="E15" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="F15" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="G15" s="16">
+        <v>2</v>
+      </c>
+      <c r="H15" s="14"/>
+      <c r="I15" s="16">
+        <v>30</v>
+      </c>
+      <c r="J15" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="K15" s="16">
+        <v>0</v>
+      </c>
+      <c r="L15" s="16">
+        <v>0</v>
+      </c>
+      <c r="M15" s="16">
+        <v>0</v>
+      </c>
+      <c r="N15" s="16">
+        <v>0</v>
+      </c>
+      <c r="O15" s="16">
+        <v>0</v>
+      </c>
+      <c r="P15" s="16">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="14"/>
+      <c r="R15" s="14">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="16" s="14" customFormat="1" ht="17" spans="2:28">
+      <c r="B16" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="D16" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="E16" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="F14" s="18" t="s">
+      <c r="F16" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="G14" s="18">
-        <v>2</v>
-      </c>
-      <c r="H14" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="I14" s="18">
+      <c r="G16" s="16">
+        <v>0.15</v>
+      </c>
+      <c r="H16" s="14"/>
+      <c r="I16" s="16">
         <v>100</v>
       </c>
-      <c r="J14" s="18" t="s">
+      <c r="J16" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="K14" s="18">
-        <v>0</v>
-      </c>
-      <c r="L14" s="18">
-        <v>0</v>
-      </c>
-      <c r="M14" s="18">
-        <v>0</v>
-      </c>
-      <c r="N14" s="18">
-        <v>0</v>
-      </c>
-      <c r="O14" s="18">
-        <v>0</v>
-      </c>
-      <c r="P14" s="18">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="R14" s="15">
+      <c r="K16" s="16">
+        <v>0</v>
+      </c>
+      <c r="L16" s="16">
+        <v>0</v>
+      </c>
+      <c r="M16" s="16">
+        <v>0</v>
+      </c>
+      <c r="N16" s="16">
+        <v>0</v>
+      </c>
+      <c r="O16" s="16">
+        <v>0</v>
+      </c>
+      <c r="P16" s="16">
+        <v>0</v>
+      </c>
+      <c r="R16" s="14">
+        <f t="shared" ref="R16:R36" si="1">VLOOKUP(E16,$T$10:$AB$17,9,FALSE)</f>
         <v>80</v>
       </c>
-    </row>
-    <row r="15" s="14" customFormat="1" ht="17" spans="1:18">
-      <c r="A15" s="17"/>
-      <c r="B15" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="C15" s="18" t="s">
-        <v>95</v>
-      </c>
-      <c r="D15" s="19" t="s">
-        <v>93</v>
-      </c>
-      <c r="E15" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="F15" s="18" t="s">
-        <v>49</v>
-      </c>
-      <c r="G15" s="18">
-        <v>2</v>
-      </c>
-      <c r="H15" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="I15" s="18">
+      <c r="T16" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="V16" s="14">
         <v>30</v>
       </c>
-      <c r="J15" s="18" t="s">
+      <c r="X16" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="K15" s="18">
-        <v>0</v>
-      </c>
-      <c r="L15" s="18">
-        <v>0</v>
-      </c>
-      <c r="M15" s="18">
-        <v>0</v>
-      </c>
-      <c r="N15" s="18">
-        <v>0</v>
-      </c>
-      <c r="O15" s="18">
-        <v>0</v>
-      </c>
-      <c r="P15" s="18">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="R15" s="15">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="16" s="15" customFormat="1" ht="17" spans="2:28">
-      <c r="B16" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="C16" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="D16" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="E16" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="F16" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="G16" s="17">
-        <v>0.15</v>
-      </c>
-      <c r="H16" s="15"/>
-      <c r="I16" s="17">
-        <v>100</v>
-      </c>
-      <c r="J16" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="K16" s="17">
-        <v>0</v>
-      </c>
-      <c r="L16" s="17">
-        <v>0</v>
-      </c>
-      <c r="M16" s="17">
-        <v>0</v>
-      </c>
-      <c r="N16" s="17">
-        <v>0</v>
-      </c>
-      <c r="O16" s="17">
-        <v>0</v>
-      </c>
-      <c r="P16" s="17">
-        <v>0</v>
-      </c>
-      <c r="R16" s="15">
-        <f t="shared" ref="R16:R38" si="1">VLOOKUP(E16,$T$10:$AB$17,9,FALSE)</f>
-        <v>80</v>
-      </c>
-      <c r="T16" s="15" t="s">
-        <v>99</v>
-      </c>
-      <c r="V16" s="15">
-        <v>30</v>
-      </c>
-      <c r="X16" s="15" t="s">
-        <v>63</v>
-      </c>
-      <c r="Z16" s="15">
+      <c r="Z16" s="14">
         <f>COUNTIF($E$4:$E$90,T16)</f>
         <v>10</v>
       </c>
-      <c r="AB16" s="15">
+      <c r="AB16" s="14">
         <v>120</v>
       </c>
     </row>
-    <row r="17" s="15" customFormat="1" spans="2:28">
-      <c r="B17" s="17" t="s">
+    <row r="17" s="14" customFormat="1" spans="2:28">
+      <c r="B17" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="C17" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="C17" s="17" t="s">
+      <c r="D17" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="D17" s="17" t="s">
-        <v>102</v>
-      </c>
-      <c r="E17" s="17" t="s">
+      <c r="E17" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="F17" s="17" t="s">
+      <c r="F17" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="G17" s="17">
+      <c r="G17" s="16">
         <v>0.2</v>
       </c>
-      <c r="H17" s="15"/>
-      <c r="I17" s="17">
+      <c r="H17" s="14"/>
+      <c r="I17" s="16">
         <v>300</v>
       </c>
-      <c r="J17" s="17" t="s">
+      <c r="J17" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="K17" s="17">
-        <v>0</v>
-      </c>
-      <c r="L17" s="17">
-        <v>0</v>
-      </c>
-      <c r="M17" s="17">
-        <v>0</v>
-      </c>
-      <c r="N17" s="17">
-        <v>0</v>
-      </c>
-      <c r="O17" s="17">
-        <v>0</v>
-      </c>
-      <c r="P17" s="17">
-        <v>0</v>
-      </c>
-      <c r="R17" s="15">
+      <c r="K17" s="16">
+        <v>0</v>
+      </c>
+      <c r="L17" s="16">
+        <v>0</v>
+      </c>
+      <c r="M17" s="16">
+        <v>0</v>
+      </c>
+      <c r="N17" s="16">
+        <v>0</v>
+      </c>
+      <c r="O17" s="16">
+        <v>0</v>
+      </c>
+      <c r="P17" s="16">
+        <v>0</v>
+      </c>
+      <c r="R17" s="14">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="T17" s="15" t="s">
+      <c r="T17" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="V17" s="14">
+        <v>10</v>
+      </c>
+      <c r="X17" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="V17" s="15">
-        <v>10</v>
-      </c>
-      <c r="X17" s="15" t="s">
-        <v>104</v>
-      </c>
-      <c r="Z17" s="15">
+      <c r="Z17" s="14">
         <f>COUNTIF($E$4:$E$90,T17)</f>
         <v>6</v>
       </c>
-      <c r="AB17" s="15">
+      <c r="AB17" s="14">
         <v>200</v>
       </c>
     </row>
     <row r="18" spans="2:18">
       <c r="B18" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="D18" s="1" t="s">
         <v>106</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>107</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>48</v>
@@ -4102,13 +4092,13 @@
     </row>
     <row r="19" spans="2:18">
       <c r="B19" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="D19" s="1" t="s">
         <v>109</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>110</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>48</v>
@@ -4150,13 +4140,13 @@
     </row>
     <row r="20" spans="2:18">
       <c r="B20" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="D20" s="1" t="s">
         <v>112</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>113</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>70</v>
@@ -4198,13 +4188,13 @@
     </row>
     <row r="21" spans="2:18">
       <c r="B21" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="D21" s="1" t="s">
         <v>115</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>116</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>61</v>
@@ -4246,13 +4236,13 @@
     </row>
     <row r="22" ht="34" spans="2:18">
       <c r="B22" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="D22" s="9" t="s">
         <v>118</v>
-      </c>
-      <c r="D22" s="9" t="s">
-        <v>119</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>61</v>
@@ -4294,13 +4284,13 @@
     </row>
     <row r="23" ht="34" spans="2:18">
       <c r="B23" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C23" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="D23" s="9" t="s">
         <v>121</v>
-      </c>
-      <c r="D23" s="9" t="s">
-        <v>122</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>70</v>
@@ -4312,7 +4302,7 @@
         <v>0</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I23" s="1">
         <v>300</v>
@@ -4345,13 +4335,13 @@
     </row>
     <row r="24" ht="17" spans="2:18">
       <c r="B24" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C24" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="D24" s="9" t="s">
         <v>125</v>
-      </c>
-      <c r="D24" s="9" t="s">
-        <v>126</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>70</v>
@@ -4393,13 +4383,13 @@
     </row>
     <row r="25" ht="17" spans="2:18">
       <c r="B25" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C25" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="D25" s="9" t="s">
         <v>128</v>
-      </c>
-      <c r="D25" s="9" t="s">
-        <v>129</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>48</v>
@@ -4441,13 +4431,13 @@
     </row>
     <row r="26" spans="2:18">
       <c r="B26" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C26" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="D26" s="1" t="s">
         <v>131</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>132</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>61</v>
@@ -4489,13 +4479,13 @@
     </row>
     <row r="27" ht="51" spans="2:18">
       <c r="B27" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C27" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="D27" s="9" t="s">
         <v>134</v>
-      </c>
-      <c r="D27" s="9" t="s">
-        <v>135</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>48</v>
@@ -4507,7 +4497,7 @@
         <v>1.2</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I27" s="1">
         <v>100</v>
@@ -4540,13 +4530,13 @@
     </row>
     <row r="28" ht="51" spans="2:18">
       <c r="B28" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C28" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="D28" s="9" t="s">
         <v>138</v>
-      </c>
-      <c r="D28" s="9" t="s">
-        <v>139</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>48</v>
@@ -4558,7 +4548,7 @@
         <v>1.2</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I28" s="1">
         <v>30</v>
@@ -4591,13 +4581,13 @@
     </row>
     <row r="29" ht="17" spans="2:18">
       <c r="B29" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C29" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="D29" s="9" t="s">
         <v>142</v>
-      </c>
-      <c r="D29" s="9" t="s">
-        <v>143</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>70</v>
@@ -4639,13 +4629,13 @@
     </row>
     <row r="30" ht="34" spans="2:18">
       <c r="B30" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C30" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="D30" s="9" t="s">
         <v>145</v>
-      </c>
-      <c r="D30" s="9" t="s">
-        <v>146</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>70</v>
@@ -4685,65 +4675,65 @@
         <v>50</v>
       </c>
     </row>
-    <row r="31" s="16" customFormat="1" ht="34" spans="1:18">
-      <c r="A31" s="21"/>
-      <c r="B31" s="21" t="s">
+    <row r="31" s="15" customFormat="1" ht="34" spans="1:18">
+      <c r="A31" s="18"/>
+      <c r="B31" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="C31" s="18" t="s">
         <v>147</v>
       </c>
-      <c r="C31" s="21" t="s">
+      <c r="D31" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="D31" s="22" t="s">
-        <v>149</v>
-      </c>
-      <c r="E31" s="21" t="s">
+      <c r="E31" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="F31" s="21" t="s">
+      <c r="F31" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="G31" s="21">
+      <c r="G31" s="18">
         <v>1</v>
       </c>
-      <c r="H31" s="21"/>
-      <c r="I31" s="21">
+      <c r="H31" s="18"/>
+      <c r="I31" s="18">
         <v>100</v>
       </c>
-      <c r="J31" s="21" t="s">
+      <c r="J31" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="K31" s="21">
-        <v>0</v>
-      </c>
-      <c r="L31" s="21">
-        <v>0</v>
-      </c>
-      <c r="M31" s="21">
-        <v>0</v>
-      </c>
-      <c r="N31" s="21">
-        <v>0</v>
-      </c>
-      <c r="O31" s="21">
-        <v>0</v>
-      </c>
-      <c r="P31" s="21">
-        <v>0</v>
-      </c>
-      <c r="R31" s="16">
+      <c r="K31" s="18">
+        <v>0</v>
+      </c>
+      <c r="L31" s="18">
+        <v>0</v>
+      </c>
+      <c r="M31" s="18">
+        <v>0</v>
+      </c>
+      <c r="N31" s="18">
+        <v>0</v>
+      </c>
+      <c r="O31" s="18">
+        <v>0</v>
+      </c>
+      <c r="P31" s="18">
+        <v>0</v>
+      </c>
+      <c r="R31" s="15">
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
     </row>
     <row r="32" ht="17" spans="2:18">
       <c r="B32" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="C32" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="D32" s="9" t="s">
         <v>151</v>
-      </c>
-      <c r="D32" s="9" t="s">
-        <v>152</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>61</v>
@@ -4786,13 +4776,13 @@
     <row r="33" s="8" customFormat="1" ht="51" spans="1:18">
       <c r="A33" s="10"/>
       <c r="B33" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="C33" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="C33" s="10" t="s">
+      <c r="D33" s="12" t="s">
         <v>154</v>
-      </c>
-      <c r="D33" s="12" t="s">
-        <v>155</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>48</v>
@@ -4804,7 +4794,7 @@
         <v>200</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I33" s="10">
         <v>100</v>
@@ -4838,13 +4828,13 @@
     <row r="34" s="8" customFormat="1" ht="17" spans="1:18">
       <c r="A34" s="10"/>
       <c r="B34" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="C34" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="C34" s="10" t="s">
+      <c r="D34" s="12" t="s">
         <v>158</v>
-      </c>
-      <c r="D34" s="12" t="s">
-        <v>159</v>
       </c>
       <c r="E34" s="10" t="s">
         <v>48</v>
@@ -4888,13 +4878,13 @@
     <row r="35" s="8" customFormat="1" ht="17" spans="1:18">
       <c r="A35" s="10"/>
       <c r="B35" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="C35" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="C35" s="10" t="s">
+      <c r="D35" s="12" t="s">
         <v>161</v>
-      </c>
-      <c r="D35" s="12" t="s">
-        <v>162</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>48</v>
@@ -4937,16 +4927,16 @@
     </row>
     <row r="36" ht="17" spans="2:18">
       <c r="B36" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C36" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="D36" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="D36" s="9" t="s">
+      <c r="E36" s="1" t="s">
         <v>165</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>166</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>49</v>
@@ -4958,7 +4948,7 @@
         <v>10</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="K36" s="1">
         <v>0</v>
@@ -4984,66 +4974,66 @@
       </c>
     </row>
     <row r="37" s="14" customFormat="1" ht="34" spans="1:18">
-      <c r="A37" s="18"/>
-      <c r="B37" s="18" t="s">
+      <c r="A37" s="16"/>
+      <c r="B37" s="16" t="s">
+        <v>166</v>
+      </c>
+      <c r="C37" s="16" t="s">
         <v>167</v>
       </c>
-      <c r="C37" s="18" t="s">
+      <c r="D37" s="17" t="s">
         <v>168</v>
       </c>
-      <c r="D37" s="19" t="s">
+      <c r="E37" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="F37" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="G37" s="16">
+        <v>1</v>
+      </c>
+      <c r="H37" s="16" t="s">
         <v>169</v>
       </c>
-      <c r="E37" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="F37" s="18" t="s">
-        <v>49</v>
-      </c>
-      <c r="G37" s="18">
-        <v>1</v>
-      </c>
-      <c r="H37" s="18" t="s">
-        <v>170</v>
-      </c>
-      <c r="I37" s="18">
+      <c r="I37" s="16">
         <v>100</v>
       </c>
-      <c r="J37" s="18" t="s">
+      <c r="J37" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="K37" s="18">
-        <v>0</v>
-      </c>
-      <c r="L37" s="18">
-        <v>0</v>
-      </c>
-      <c r="M37" s="18">
-        <v>0</v>
-      </c>
-      <c r="N37" s="18">
-        <v>0</v>
-      </c>
-      <c r="O37" s="18">
-        <v>0</v>
-      </c>
-      <c r="P37" s="18">
+      <c r="K37" s="16">
+        <v>0</v>
+      </c>
+      <c r="L37" s="16">
+        <v>0</v>
+      </c>
+      <c r="M37" s="16">
+        <v>0</v>
+      </c>
+      <c r="N37" s="16">
+        <v>0</v>
+      </c>
+      <c r="O37" s="16">
+        <v>0</v>
+      </c>
+      <c r="P37" s="16">
         <v>0</v>
       </c>
       <c r="R37" s="14">
-        <f t="shared" ref="R37:R67" si="2">VLOOKUP(E37,$T$10:$AB$17,9,FALSE)</f>
+        <f t="shared" ref="R37:R54" si="2">VLOOKUP(E37,$T$10:$AB$17,9,FALSE)</f>
         <v>80</v>
       </c>
     </row>
     <row r="38" ht="34" spans="2:18">
       <c r="B38" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C38" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="D38" s="9" t="s">
         <v>172</v>
-      </c>
-      <c r="D38" s="9" t="s">
-        <v>173</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>70</v>
@@ -5055,7 +5045,7 @@
         <v>2</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I38" s="1">
         <v>300</v>
@@ -5088,13 +5078,13 @@
     </row>
     <row r="39" ht="34" spans="2:18">
       <c r="B39" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="C39" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="D39" s="9" t="s">
         <v>176</v>
-      </c>
-      <c r="D39" s="9" t="s">
-        <v>177</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>70</v>
@@ -5106,7 +5096,7 @@
         <v>2</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="I39" s="1">
         <v>300</v>
@@ -5139,13 +5129,13 @@
     </row>
     <row r="40" spans="2:18">
       <c r="B40" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C40" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="D40" s="1" t="s">
         <v>180</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>181</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>48</v>
@@ -5187,13 +5177,13 @@
     </row>
     <row r="41" ht="34" spans="2:18">
       <c r="B41" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C41" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="D41" s="9" t="s">
         <v>183</v>
-      </c>
-      <c r="D41" s="9" t="s">
-        <v>184</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>48</v>
@@ -5236,13 +5226,13 @@
     <row r="42" s="8" customFormat="1" ht="34" spans="1:18">
       <c r="A42" s="10"/>
       <c r="B42" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="C42" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="C42" s="10" t="s">
+      <c r="D42" s="12" t="s">
         <v>186</v>
-      </c>
-      <c r="D42" s="12" t="s">
-        <v>187</v>
       </c>
       <c r="E42" s="10" t="s">
         <v>48</v>
@@ -5285,13 +5275,13 @@
     </row>
     <row r="43" ht="17" spans="2:18">
       <c r="B43" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C43" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="D43" s="9" t="s">
         <v>189</v>
-      </c>
-      <c r="D43" s="9" t="s">
-        <v>190</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>48</v>
@@ -5333,13 +5323,13 @@
     </row>
     <row r="44" ht="34" spans="2:18">
       <c r="B44" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C44" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="D44" s="9" t="s">
         <v>192</v>
-      </c>
-      <c r="D44" s="9" t="s">
-        <v>193</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>48</v>
@@ -5381,13 +5371,13 @@
     </row>
     <row r="45" ht="34" spans="2:18">
       <c r="B45" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="C45" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="D45" s="9" t="s">
         <v>195</v>
-      </c>
-      <c r="D45" s="9" t="s">
-        <v>196</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>48</v>
@@ -5429,16 +5419,16 @@
     </row>
     <row r="46" spans="2:18">
       <c r="B46" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="C46" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="D46" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="D46" s="1" t="s">
-        <v>199</v>
-      </c>
       <c r="E46" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>49</v>
@@ -5450,7 +5440,7 @@
         <v>10</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="K46" s="1">
         <v>0</v>
@@ -5478,13 +5468,13 @@
     <row r="47" s="8" customFormat="1" ht="34" spans="1:18">
       <c r="A47" s="10"/>
       <c r="B47" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="C47" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="C47" s="10" t="s">
+      <c r="D47" s="12" t="s">
         <v>201</v>
-      </c>
-      <c r="D47" s="12" t="s">
-        <v>202</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>48</v>
@@ -5527,13 +5517,13 @@
     </row>
     <row r="48" ht="34" spans="2:18">
       <c r="B48" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="C48" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="C48" s="1" t="s">
+      <c r="D48" s="9" t="s">
         <v>204</v>
-      </c>
-      <c r="D48" s="9" t="s">
-        <v>205</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>48</v>
@@ -5575,13 +5565,13 @@
     </row>
     <row r="49" ht="34" spans="2:18">
       <c r="B49" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="C49" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="D49" s="9" t="s">
         <v>207</v>
-      </c>
-      <c r="D49" s="9" t="s">
-        <v>208</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>48</v>
@@ -5623,13 +5613,13 @@
     </row>
     <row r="50" ht="34" spans="2:18">
       <c r="B50" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="C50" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="C50" s="1" t="s">
+      <c r="D50" s="9" t="s">
         <v>210</v>
-      </c>
-      <c r="D50" s="9" t="s">
-        <v>211</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>61</v>
@@ -5671,13 +5661,13 @@
     </row>
     <row r="51" ht="17" spans="2:18">
       <c r="B51" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="C51" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="C51" s="1" t="s">
+      <c r="D51" s="9" t="s">
         <v>213</v>
-      </c>
-      <c r="D51" s="9" t="s">
-        <v>214</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>61</v>
@@ -5719,13 +5709,13 @@
     </row>
     <row r="52" spans="2:18">
       <c r="B52" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C52" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="C52" s="1" t="s">
+      <c r="D52" s="1" t="s">
         <v>216</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>217</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>70</v>
@@ -5767,13 +5757,13 @@
     </row>
     <row r="53" ht="34" spans="2:18">
       <c r="B53" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="C53" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="C53" s="1" t="s">
+      <c r="D53" s="9" t="s">
         <v>219</v>
-      </c>
-      <c r="D53" s="9" t="s">
-        <v>220</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>70</v>
@@ -5816,13 +5806,13 @@
     <row r="54" s="8" customFormat="1" ht="17" spans="1:18">
       <c r="A54" s="10"/>
       <c r="B54" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="C54" s="10" t="s">
         <v>221</v>
       </c>
-      <c r="C54" s="10" t="s">
+      <c r="D54" s="12" t="s">
         <v>222</v>
-      </c>
-      <c r="D54" s="12" t="s">
-        <v>223</v>
       </c>
       <c r="E54" s="10" t="s">
         <v>70</v>
@@ -5864,7 +5854,9 @@
       </c>
     </row>
     <row r="55" s="8" customFormat="1" spans="1:16">
-      <c r="A55" s="10"/>
+      <c r="A55" s="10" t="s">
+        <v>223</v>
+      </c>
       <c r="B55" s="10"/>
       <c r="C55" s="10"/>
       <c r="D55" s="10" t="s">
@@ -5886,7 +5878,9 @@
       <c r="P55" s="10"/>
     </row>
     <row r="56" s="8" customFormat="1" spans="1:16">
-      <c r="A56" s="10"/>
+      <c r="A56" s="10" t="s">
+        <v>223</v>
+      </c>
       <c r="B56" s="10"/>
       <c r="C56" s="10"/>
       <c r="D56" s="10" t="s">
@@ -5951,7 +5945,7 @@
         <v>0</v>
       </c>
       <c r="R57">
-        <f>VLOOKUP(E57,$T$10:$AB$17,9,FALSE)</f>
+        <f t="shared" ref="R57:R66" si="3">VLOOKUP(E57,$T$10:$AB$17,9,FALSE)</f>
         <v>80</v>
       </c>
     </row>
@@ -6002,7 +5996,7 @@
         <v>0</v>
       </c>
       <c r="R58">
-        <f>VLOOKUP(E58,$T$10:$AB$17,9,FALSE)</f>
+        <f t="shared" si="3"/>
         <v>80</v>
       </c>
     </row>
@@ -6053,7 +6047,7 @@
         <v>0</v>
       </c>
       <c r="R59">
-        <f>VLOOKUP(E59,$T$10:$AB$17,9,FALSE)</f>
+        <f t="shared" si="3"/>
         <v>80</v>
       </c>
     </row>
@@ -6101,7 +6095,7 @@
         <v>0</v>
       </c>
       <c r="R60">
-        <f>VLOOKUP(E60,$T$10:$AB$17,9,FALSE)</f>
+        <f t="shared" si="3"/>
         <v>50</v>
       </c>
     </row>
@@ -6149,7 +6143,7 @@
         <v>0</v>
       </c>
       <c r="R61">
-        <f>VLOOKUP(E61,$T$10:$AB$17,9,FALSE)</f>
+        <f t="shared" si="3"/>
         <v>50</v>
       </c>
     </row>
@@ -6197,7 +6191,7 @@
         <v>0</v>
       </c>
       <c r="R62">
-        <f>VLOOKUP(E62,$T$10:$AB$17,9,FALSE)</f>
+        <f t="shared" si="3"/>
         <v>80</v>
       </c>
     </row>
@@ -6247,7 +6241,7 @@
         <v>0</v>
       </c>
       <c r="R63" s="8">
-        <f>VLOOKUP(E63,$T$10:$AB$17,9,FALSE)</f>
+        <f t="shared" si="3"/>
         <v>50</v>
       </c>
     </row>
@@ -6295,7 +6289,7 @@
         <v>0</v>
       </c>
       <c r="R64">
-        <f>VLOOKUP(E64,$T$10:$AB$17,9,FALSE)</f>
+        <f t="shared" si="3"/>
         <v>50</v>
       </c>
     </row>
@@ -6343,7 +6337,7 @@
         <v>0</v>
       </c>
       <c r="R65">
-        <f>VLOOKUP(E65,$T$10:$AB$17,9,FALSE)</f>
+        <f t="shared" si="3"/>
         <v>50</v>
       </c>
     </row>
@@ -6393,12 +6387,14 @@
         <v>0</v>
       </c>
       <c r="R66" s="8">
-        <f>VLOOKUP(E66,$T$10:$AB$17,9,FALSE)</f>
+        <f t="shared" si="3"/>
         <v>50</v>
       </c>
     </row>
     <row r="67" s="8" customFormat="1" spans="1:16">
-      <c r="A67" s="10"/>
+      <c r="A67" s="10" t="s">
+        <v>223</v>
+      </c>
       <c r="B67" s="10"/>
       <c r="C67" s="10"/>
       <c r="D67" s="10" t="s">
@@ -6660,7 +6656,9 @@
       </c>
     </row>
     <row r="73" s="8" customFormat="1" ht="34" spans="1:16">
-      <c r="A73" s="10"/>
+      <c r="A73" s="10" t="s">
+        <v>223</v>
+      </c>
       <c r="B73" s="10"/>
       <c r="C73" s="10"/>
       <c r="D73" s="12" t="s">
@@ -6680,7 +6678,9 @@
       <c r="P73" s="10"/>
     </row>
     <row r="74" s="8" customFormat="1" ht="34" spans="1:16">
-      <c r="A74" s="10"/>
+      <c r="A74" s="10" t="s">
+        <v>223</v>
+      </c>
       <c r="B74" s="10"/>
       <c r="C74" s="10"/>
       <c r="D74" s="12" t="s">
@@ -6710,7 +6710,7 @@
         <v>279</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>49</v>
@@ -6722,7 +6722,7 @@
         <v>10</v>
       </c>
       <c r="J75" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="K75" s="1">
         <v>0</v>
@@ -6743,7 +6743,7 @@
         <v>0</v>
       </c>
       <c r="R75">
-        <f t="shared" ref="R75:R90" si="3">VLOOKUP(E75,$T$10:$AB$17,9,FALSE)</f>
+        <f t="shared" ref="R75:R90" si="4">VLOOKUP(E75,$T$10:$AB$17,9,FALSE)</f>
         <v>200</v>
       </c>
     </row>
@@ -6758,7 +6758,7 @@
         <v>282</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>49</v>
@@ -6770,7 +6770,7 @@
         <v>10</v>
       </c>
       <c r="J76" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="K76" s="1">
         <v>0</v>
@@ -6794,7 +6794,7 @@
         <v>283</v>
       </c>
       <c r="R76">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>200</v>
       </c>
     </row>
@@ -6809,7 +6809,7 @@
         <v>286</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>49</v>
@@ -6821,7 +6821,7 @@
         <v>10</v>
       </c>
       <c r="J77" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="K77" s="1">
         <v>0</v>
@@ -6845,7 +6845,7 @@
         <v>283</v>
       </c>
       <c r="R77">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>200</v>
       </c>
     </row>
@@ -6896,7 +6896,7 @@
         <v>283</v>
       </c>
       <c r="R78">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>80</v>
       </c>
     </row>
@@ -6950,7 +6950,7 @@
         <v>283</v>
       </c>
       <c r="R79">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>80</v>
       </c>
     </row>
@@ -6965,7 +6965,7 @@
         <v>296</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>49</v>
@@ -6977,7 +6977,7 @@
         <v>10</v>
       </c>
       <c r="J80" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="K80" s="1">
         <v>0</v>
@@ -7001,7 +7001,7 @@
         <v>297</v>
       </c>
       <c r="R80">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>200</v>
       </c>
     </row>
@@ -7052,7 +7052,7 @@
         <v>297</v>
       </c>
       <c r="R81">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>80</v>
       </c>
     </row>
@@ -7103,7 +7103,7 @@
         <v>297</v>
       </c>
       <c r="R82">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>120</v>
       </c>
     </row>
@@ -7157,7 +7157,7 @@
         <v>297</v>
       </c>
       <c r="R83">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>80</v>
       </c>
     </row>
@@ -7208,54 +7208,72 @@
         <v>297</v>
       </c>
       <c r="R84">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>80</v>
       </c>
     </row>
-    <row r="85" ht="33.75" customHeight="1" spans="4:18">
+    <row r="85" ht="33.75" customHeight="1" spans="1:18">
+      <c r="A85" t="s">
+        <v>223</v>
+      </c>
       <c r="D85" s="9"/>
       <c r="Q85" s="1"/>
       <c r="R85" t="e">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="86" ht="33.75" customHeight="1" spans="4:18">
+    <row r="86" ht="33.75" customHeight="1" spans="1:18">
+      <c r="A86" t="s">
+        <v>223</v>
+      </c>
       <c r="D86" s="9"/>
       <c r="Q86" s="1"/>
       <c r="R86" t="e">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="87" ht="33.75" customHeight="1" spans="4:18">
+    <row r="87" ht="33.75" customHeight="1" spans="1:18">
+      <c r="A87" t="s">
+        <v>223</v>
+      </c>
       <c r="D87" s="9"/>
       <c r="Q87" s="1"/>
       <c r="R87" t="e">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="88" ht="33.75" customHeight="1" spans="4:18">
+    <row r="88" ht="33.75" customHeight="1" spans="1:18">
+      <c r="A88" t="s">
+        <v>223</v>
+      </c>
       <c r="D88" s="9"/>
       <c r="Q88" s="1"/>
       <c r="R88" t="e">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="89" ht="33.75" customHeight="1" spans="4:18">
+    <row r="89" ht="33.75" customHeight="1" spans="1:18">
+      <c r="A89" t="s">
+        <v>223</v>
+      </c>
       <c r="D89" s="9"/>
       <c r="Q89" s="1"/>
       <c r="R89" t="e">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="90" ht="16.5" customHeight="1" spans="17:18">
+    <row r="90" ht="16.5" customHeight="1" spans="1:18">
+      <c r="A90" t="s">
+        <v>223</v>
+      </c>
       <c r="Q90" s="1"/>
       <c r="R90" t="e">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>#N/A</v>
       </c>
     </row>
@@ -7864,79 +7882,93 @@
       </c>
     </row>
     <row r="17" s="8" customFormat="1" ht="33.75" customHeight="1" spans="1:13">
-      <c r="A17" s="10"/>
+      <c r="A17" s="10" t="s">
+        <v>223</v>
+      </c>
       <c r="B17" s="11"/>
       <c r="C17" s="10"/>
       <c r="D17" s="12" t="s">
         <v>374</v>
       </c>
       <c r="E17" s="10"/>
-      <c r="F17" s="11"/>
+      <c r="F17" s="10"/>
       <c r="G17" s="10"/>
       <c r="H17" s="10"/>
       <c r="I17" s="10"/>
-      <c r="J17" s="11"/>
+      <c r="J17" s="10"/>
       <c r="K17" s="10"/>
+      <c r="L17"/>
       <c r="M17" s="8">
         <v>35</v>
       </c>
     </row>
     <row r="18" s="8" customFormat="1" ht="16.5" customHeight="1" spans="1:13">
-      <c r="A18" s="10"/>
+      <c r="A18" s="10" t="s">
+        <v>223</v>
+      </c>
       <c r="B18" s="11"/>
       <c r="C18" s="10"/>
       <c r="D18" s="10" t="s">
         <v>375</v>
       </c>
       <c r="E18" s="10"/>
-      <c r="F18" s="11"/>
+      <c r="F18" s="10"/>
       <c r="G18" s="10"/>
       <c r="H18" s="10"/>
       <c r="I18" s="10"/>
-      <c r="J18" s="11"/>
+      <c r="J18" s="10"/>
       <c r="K18" s="10"/>
+      <c r="L18"/>
       <c r="M18" s="8">
         <v>35</v>
       </c>
     </row>
     <row r="19" s="8" customFormat="1" ht="16.5" customHeight="1" spans="1:13">
-      <c r="A19" s="10"/>
+      <c r="A19" s="10" t="s">
+        <v>223</v>
+      </c>
       <c r="B19" s="11"/>
       <c r="C19" s="10"/>
       <c r="D19" s="10" t="s">
         <v>376</v>
       </c>
       <c r="E19" s="10"/>
-      <c r="F19" s="11"/>
+      <c r="F19" s="10"/>
       <c r="G19" s="10"/>
       <c r="H19" s="10"/>
       <c r="I19" s="10"/>
-      <c r="J19" s="11"/>
+      <c r="J19" s="10"/>
       <c r="K19" s="10"/>
+      <c r="L19"/>
       <c r="M19" s="8">
         <v>35</v>
       </c>
     </row>
     <row r="20" s="8" customFormat="1" ht="16.5" customHeight="1" spans="1:13">
-      <c r="A20" s="10"/>
+      <c r="A20" s="10" t="s">
+        <v>223</v>
+      </c>
       <c r="B20" s="11"/>
       <c r="C20" s="10"/>
       <c r="D20" s="10" t="s">
         <v>377</v>
       </c>
       <c r="E20" s="10"/>
-      <c r="F20" s="11"/>
+      <c r="F20" s="10"/>
       <c r="G20" s="10"/>
-      <c r="H20" s="11"/>
+      <c r="H20" s="10"/>
       <c r="I20" s="10"/>
-      <c r="J20" s="11"/>
+      <c r="J20" s="10"/>
       <c r="K20" s="10"/>
+      <c r="L20"/>
       <c r="M20" s="8">
         <v>35</v>
       </c>
     </row>
     <row r="21" s="8" customFormat="1" spans="1:11">
-      <c r="A21" s="10"/>
+      <c r="A21" s="10" t="s">
+        <v>223</v>
+      </c>
       <c r="B21" s="10"/>
       <c r="C21" s="10"/>
       <c r="D21" s="10" t="s">
@@ -7951,7 +7983,9 @@
       <c r="K21" s="10"/>
     </row>
     <row r="22" s="8" customFormat="1" spans="1:11">
-      <c r="A22" s="10"/>
+      <c r="A22" s="10" t="s">
+        <v>223</v>
+      </c>
       <c r="B22" s="10"/>
       <c r="C22" s="10"/>
       <c r="D22" s="10" t="s">
@@ -7966,7 +8000,9 @@
       <c r="K22" s="10"/>
     </row>
     <row r="23" s="8" customFormat="1" spans="1:11">
-      <c r="A23" s="10"/>
+      <c r="A23" s="10" t="s">
+        <v>223</v>
+      </c>
       <c r="B23" s="10"/>
       <c r="C23" s="10"/>
       <c r="D23" s="10" t="s">
@@ -7981,7 +8017,9 @@
       <c r="K23" s="10"/>
     </row>
     <row r="24" s="8" customFormat="1" spans="1:11">
-      <c r="A24" s="10"/>
+      <c r="A24" s="10" t="s">
+        <v>223</v>
+      </c>
       <c r="B24" s="10"/>
       <c r="C24" s="10"/>
       <c r="D24" s="10" t="s">
@@ -7996,7 +8034,9 @@
       <c r="K24" s="10"/>
     </row>
     <row r="25" s="8" customFormat="1" spans="1:11">
-      <c r="A25" s="10"/>
+      <c r="A25" s="10" t="s">
+        <v>223</v>
+      </c>
       <c r="B25" s="10"/>
       <c r="C25" s="10"/>
       <c r="D25" s="10" t="s">
@@ -8011,7 +8051,9 @@
       <c r="K25" s="10"/>
     </row>
     <row r="26" s="8" customFormat="1" spans="1:11">
-      <c r="A26" s="10"/>
+      <c r="A26" s="10" t="s">
+        <v>223</v>
+      </c>
       <c r="B26" s="10"/>
       <c r="C26" s="10"/>
       <c r="D26" s="10" t="s">
@@ -8393,7 +8435,7 @@
         <v>424</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>425</v>
@@ -8749,10 +8791,10 @@
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
       <c r="D40" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H40" s="1">
         <v>39</v>
@@ -8993,7 +9035,7 @@
       <c r="B54" s="4"/>
       <c r="C54" s="4"/>
       <c r="D54" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>495</v>
@@ -9029,7 +9071,7 @@
       <c r="B56" s="4"/>
       <c r="C56" s="4"/>
       <c r="D56" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>499</v>

--- a/GourmetProject/GameConfig/Datas/item.xlsx
+++ b/GourmetProject/GameConfig/Datas/item.xlsx
@@ -4781,9 +4781,7 @@
       </c>
     </row>
     <row r="31" s="15" customFormat="1" ht="34" spans="1:18">
-      <c r="A31" s="18" t="s">
-        <v>146</v>
-      </c>
+      <c r="A31" s="18"/>
       <c r="B31" s="18" t="s">
         <v>147</v>
       </c>
@@ -4881,9 +4879,7 @@
       </c>
     </row>
     <row r="33" s="8" customFormat="1" ht="51" spans="1:18">
-      <c r="A33" s="10" t="s">
-        <v>146</v>
-      </c>
+      <c r="A33" s="10"/>
       <c r="B33" s="10" t="s">
         <v>153</v>
       </c>
@@ -4935,9 +4931,7 @@
       </c>
     </row>
     <row r="34" s="8" customFormat="1" ht="17" spans="1:18">
-      <c r="A34" s="10" t="s">
-        <v>146</v>
-      </c>
+      <c r="A34" s="10"/>
       <c r="B34" s="10" t="s">
         <v>157</v>
       </c>
@@ -4987,9 +4981,7 @@
       </c>
     </row>
     <row r="35" s="8" customFormat="1" ht="17" spans="1:18">
-      <c r="A35" s="10" t="s">
-        <v>146</v>
-      </c>
+      <c r="A35" s="10"/>
       <c r="B35" s="10" t="s">
         <v>160</v>
       </c>
@@ -5006,7 +4998,7 @@
         <v>49</v>
       </c>
       <c r="G35" s="10">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H35" s="10"/>
       <c r="I35" s="10">
@@ -5337,9 +5329,7 @@
       </c>
     </row>
     <row r="42" s="8" customFormat="1" ht="34" spans="1:18">
-      <c r="A42" s="10" t="s">
-        <v>146</v>
-      </c>
+      <c r="A42" s="10"/>
       <c r="B42" s="10" t="s">
         <v>185</v>
       </c>
@@ -5581,9 +5571,7 @@
       </c>
     </row>
     <row r="47" s="8" customFormat="1" ht="34" spans="1:18">
-      <c r="A47" s="10" t="s">
-        <v>146</v>
-      </c>
+      <c r="A47" s="10"/>
       <c r="B47" s="10" t="s">
         <v>200</v>
       </c>
@@ -5921,9 +5909,7 @@
       </c>
     </row>
     <row r="54" s="8" customFormat="1" ht="17" spans="1:18">
-      <c r="A54" s="10" t="s">
-        <v>146</v>
-      </c>
+      <c r="A54" s="10"/>
       <c r="B54" s="10" t="s">
         <v>221</v>
       </c>
@@ -5972,53 +5958,125 @@
         <v>50</v>
       </c>
     </row>
-    <row r="55" s="8" customFormat="1" spans="1:16">
-      <c r="A55" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="B55" s="10"/>
-      <c r="C55" s="10"/>
+    <row r="55" s="8" customFormat="1" spans="1:18">
+      <c r="A55" s="10"/>
+      <c r="B55" s="10" t="inlineStr">
+        <is>
+          <t>item_shop_restock_active</t>
+        </is>
+      </c>
+      <c r="C55" s="10" t="inlineStr">
+        <is>
+          <t>主动补货</t>
+        </is>
+      </c>
       <c r="D55" s="10" t="s">
         <v>224</v>
       </c>
-      <c r="E55" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="F55" s="10"/>
-      <c r="G55" s="10"/>
+      <c r="E55" s="10" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="F55" s="10" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G55" s="10">
+        <v>0</v>
+      </c>
       <c r="H55" s="10"/>
-      <c r="I55" s="10"/>
-      <c r="J55" s="10"/>
-      <c r="K55" s="10"/>
-      <c r="L55" s="10"/>
-      <c r="M55" s="10"/>
-      <c r="N55" s="10"/>
-      <c r="O55" s="10"/>
-      <c r="P55" s="10"/>
-    </row>
-    <row r="56" s="8" customFormat="1" spans="1:16">
-      <c r="A56" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="B56" s="10"/>
-      <c r="C56" s="10"/>
+      <c r="I55" s="10">
+        <v>30</v>
+      </c>
+      <c r="J55" s="10" t="inlineStr">
+        <is>
+          <t>30,80</t>
+        </is>
+      </c>
+      <c r="K55" s="10">
+        <v>0</v>
+      </c>
+      <c r="L55" s="10">
+        <v>0</v>
+      </c>
+      <c r="M55" s="10">
+        <v>0</v>
+      </c>
+      <c r="N55" s="10">
+        <v>0</v>
+      </c>
+      <c r="O55" s="10">
+        <v>0</v>
+      </c>
+      <c r="P55" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q55" s="10"/>
+      <c r="R55" s="8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="56" s="8" customFormat="1" spans="1:18">
+      <c r="A56" s="10"/>
+      <c r="B56" s="10" t="inlineStr">
+        <is>
+          <t>item_shop_restock_passive</t>
+        </is>
+      </c>
+      <c r="C56" s="10" t="inlineStr">
+        <is>
+          <t>被动补货</t>
+        </is>
+      </c>
       <c r="D56" s="10" t="s">
         <v>225</v>
       </c>
-      <c r="E56" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="F56" s="10"/>
-      <c r="G56" s="10"/>
+      <c r="E56" s="10" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="F56" s="10" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G56" s="10">
+        <v>0</v>
+      </c>
       <c r="H56" s="10"/>
-      <c r="I56" s="10"/>
-      <c r="J56" s="10"/>
-      <c r="K56" s="10"/>
-      <c r="L56" s="10"/>
-      <c r="M56" s="10"/>
-      <c r="N56" s="10"/>
-      <c r="O56" s="10"/>
-      <c r="P56" s="10"/>
+      <c r="I56" s="10">
+        <v>30</v>
+      </c>
+      <c r="J56" s="10" t="inlineStr">
+        <is>
+          <t>30,80</t>
+        </is>
+      </c>
+      <c r="K56" s="10">
+        <v>0</v>
+      </c>
+      <c r="L56" s="10">
+        <v>0</v>
+      </c>
+      <c r="M56" s="10">
+        <v>0</v>
+      </c>
+      <c r="N56" s="10">
+        <v>0</v>
+      </c>
+      <c r="O56" s="10">
+        <v>0</v>
+      </c>
+      <c r="P56" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q56" s="10"/>
+      <c r="R56" s="8">
+        <v>50</v>
+      </c>
     </row>
     <row r="57" ht="34" spans="2:18">
       <c r="B57" s="1" t="s">
@@ -6315,9 +6373,7 @@
       </c>
     </row>
     <row r="63" s="8" customFormat="1" ht="17" spans="1:18">
-      <c r="A63" s="10" t="s">
-        <v>146</v>
-      </c>
+      <c r="A63" s="10"/>
       <c r="B63" s="10" t="s">
         <v>246</v>
       </c>
@@ -6463,9 +6519,7 @@
       </c>
     </row>
     <row r="66" s="8" customFormat="1" spans="1:18">
-      <c r="A66" s="10" t="s">
-        <v>146</v>
-      </c>
+      <c r="A66" s="10"/>
       <c r="B66" s="10" t="s">
         <v>256</v>
       </c>
@@ -6514,27 +6568,65 @@
         <v>50</v>
       </c>
     </row>
-    <row r="67" s="8" customFormat="1" spans="1:16">
-      <c r="A67" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="B67" s="10"/>
-      <c r="C67" s="10"/>
+    <row r="67" s="8" customFormat="1" spans="1:18">
+      <c r="A67" s="10"/>
+      <c r="B67" s="10" t="inlineStr">
+        <is>
+          <t>item_skip_reward_node</t>
+        </is>
+      </c>
+      <c r="C67" s="10" t="inlineStr">
+        <is>
+          <t>错失良机</t>
+        </is>
+      </c>
       <c r="D67" s="10" t="s">
         <v>259</v>
       </c>
-      <c r="E67" s="10"/>
-      <c r="F67" s="10"/>
-      <c r="G67" s="10"/>
+      <c r="E67" s="10" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="F67" s="10" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G67" s="10">
+        <v>1</v>
+      </c>
       <c r="H67" s="10"/>
-      <c r="I67" s="10"/>
-      <c r="J67" s="10"/>
-      <c r="K67" s="10"/>
-      <c r="L67" s="10"/>
-      <c r="M67" s="10"/>
-      <c r="N67" s="10"/>
-      <c r="O67" s="10"/>
-      <c r="P67" s="10"/>
+      <c r="I67" s="10">
+        <v>300</v>
+      </c>
+      <c r="J67" s="10" t="inlineStr">
+        <is>
+          <t>10,80</t>
+        </is>
+      </c>
+      <c r="K67" s="10">
+        <v>0</v>
+      </c>
+      <c r="L67" s="10">
+        <v>0</v>
+      </c>
+      <c r="M67" s="10">
+        <v>0</v>
+      </c>
+      <c r="N67" s="10">
+        <v>0</v>
+      </c>
+      <c r="O67" s="10">
+        <v>0</v>
+      </c>
+      <c r="P67" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q67" s="10"/>
+      <c r="R67" s="8">
+        <v>50</v>
+      </c>
     </row>
     <row r="68" spans="2:18">
       <c r="B68" s="1" t="s">
@@ -6729,9 +6821,7 @@
       </c>
     </row>
     <row r="72" s="8" customFormat="1" ht="34" spans="1:18">
-      <c r="A72" s="10" t="s">
-        <v>146</v>
-      </c>
+      <c r="A72" s="10"/>
       <c r="B72" s="10" t="s">
         <v>272</v>
       </c>
@@ -6780,49 +6870,129 @@
         <v>50</v>
       </c>
     </row>
-    <row r="73" s="8" customFormat="1" ht="34" spans="1:16">
-      <c r="A73" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="B73" s="10"/>
-      <c r="C73" s="10"/>
+    <row r="73" s="8" customFormat="1" ht="34" spans="1:18">
+      <c r="A73" s="10"/>
+      <c r="B73" s="10" t="inlineStr">
+        <is>
+          <t>item_double_daily_cost_repeat_node</t>
+        </is>
+      </c>
+      <c r="C73" s="10" t="inlineStr">
+        <is>
+          <t>时间透支</t>
+        </is>
+      </c>
       <c r="D73" s="12" t="s">
         <v>275</v>
       </c>
-      <c r="E73" s="10"/>
-      <c r="F73" s="10"/>
-      <c r="G73" s="10"/>
-      <c r="H73" s="10"/>
-      <c r="I73" s="10"/>
-      <c r="J73" s="10"/>
-      <c r="K73" s="10"/>
-      <c r="L73" s="10"/>
-      <c r="M73" s="10"/>
-      <c r="N73" s="10"/>
-      <c r="O73" s="10"/>
-      <c r="P73" s="10"/>
-    </row>
-    <row r="74" s="8" customFormat="1" ht="34" spans="1:16">
-      <c r="A74" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="B74" s="10"/>
-      <c r="C74" s="10"/>
+      <c r="E73" s="10" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="F73" s="10" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G73" s="10">
+        <v>2</v>
+      </c>
+      <c r="H73" s="10" t="inlineStr">
+        <is>
+          <t>repeat:2</t>
+        </is>
+      </c>
+      <c r="I73" s="10">
+        <v>300</v>
+      </c>
+      <c r="J73" s="10" t="inlineStr">
+        <is>
+          <t>10,80</t>
+        </is>
+      </c>
+      <c r="K73" s="10">
+        <v>0</v>
+      </c>
+      <c r="L73" s="10">
+        <v>0</v>
+      </c>
+      <c r="M73" s="10">
+        <v>0</v>
+      </c>
+      <c r="N73" s="10">
+        <v>0</v>
+      </c>
+      <c r="O73" s="10">
+        <v>0</v>
+      </c>
+      <c r="P73" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="10"/>
+      <c r="R73" s="8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="74" s="8" customFormat="1" ht="34" spans="1:18">
+      <c r="A74" s="10"/>
+      <c r="B74" s="10" t="inlineStr">
+        <is>
+          <t>item_timeline_stop_chance</t>
+        </is>
+      </c>
+      <c r="C74" s="10" t="inlineStr">
+        <is>
+          <t>时间停摆</t>
+        </is>
+      </c>
       <c r="D74" s="12" t="s">
         <v>276</v>
       </c>
-      <c r="E74" s="10"/>
-      <c r="F74" s="10"/>
-      <c r="G74" s="10"/>
+      <c r="E74" s="10" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="F74" s="10" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G74" s="10">
+        <v>0.3</v>
+      </c>
       <c r="H74" s="10"/>
-      <c r="I74" s="10"/>
-      <c r="J74" s="10"/>
-      <c r="K74" s="10"/>
-      <c r="L74" s="10"/>
-      <c r="M74" s="10"/>
-      <c r="N74" s="10"/>
-      <c r="O74" s="10"/>
-      <c r="P74" s="10"/>
+      <c r="I74" s="10">
+        <v>100</v>
+      </c>
+      <c r="J74" s="10" t="inlineStr">
+        <is>
+          <t>20,80</t>
+        </is>
+      </c>
+      <c r="K74" s="10">
+        <v>0</v>
+      </c>
+      <c r="L74" s="10">
+        <v>0</v>
+      </c>
+      <c r="M74" s="10">
+        <v>0</v>
+      </c>
+      <c r="N74" s="10">
+        <v>0</v>
+      </c>
+      <c r="O74" s="10">
+        <v>0</v>
+      </c>
+      <c r="P74" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="10"/>
+      <c r="R74" s="8">
+        <v>80</v>
+      </c>
     </row>
     <row r="75" spans="2:18">
       <c r="B75" s="1" t="s">

--- a/GourmetProject/GameConfig/Datas/item.xlsx
+++ b/GourmetProject/GameConfig/Datas/item.xlsx
@@ -4,32 +4,19 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16760"/>
+    <workbookView windowHeight="15160" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="被动道具" sheetId="1" r:id="rId1"/>
     <sheet name="主动道具" sheetId="2" r:id="rId2"/>
     <sheet name="道具设计" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="996" uniqueCount="603">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="994" uniqueCount="617">
   <si>
     <t>##var</t>
   </si>
@@ -479,9 +466,6 @@
 获得15金币</t>
   </si>
   <si>
-    <t>##</t>
-  </si>
-  <si>
     <t>item_extra_interest</t>
   </si>
   <si>
@@ -728,7 +712,19 @@
     <t>商店会自动补货食物</t>
   </si>
   <si>
+    <t>item_shop_restock_active</t>
+  </si>
+  <si>
+    <t>主动补货</t>
+  </si>
+  <si>
     <t>商店会自动补货主动道具</t>
+  </si>
+  <si>
+    <t>item_shop_restock_passive</t>
+  </si>
+  <si>
+    <t>被动补货</t>
   </si>
   <si>
     <t>商店会自动补货被动道具</t>
@@ -837,6 +833,12 @@
     <t>跳过下一个收取利息节点</t>
   </si>
   <si>
+    <t>item_skip_reward_node</t>
+  </si>
+  <si>
+    <t>错失良机</t>
+  </si>
+  <si>
     <t>跳过下一个幸运事件节点</t>
   </si>
   <si>
@@ -887,10 +889,25 @@
 添加至本周末尾</t>
   </si>
   <si>
+    <t>item_double_daily_cost_repeat_node</t>
+  </si>
+  <si>
+    <t>时间透支</t>
+  </si>
+  <si>
     <t>日常行动消耗天数加倍
 节点事件可以执行2次</t>
   </si>
   <si>
+    <t>repeat:2</t>
+  </si>
+  <si>
+    <t>item_timeline_stop_chance</t>
+  </si>
+  <si>
+    <t>时间停摆</t>
+  </si>
+  <si>
     <t>遇到节点事件时
 时间轴有30%概率会停止</t>
   </si>
@@ -1014,6 +1031,9 @@
     <t>targetCount</t>
   </si>
   <si>
+    <t>category</t>
+  </si>
+  <si>
     <t>效果类型</t>
   </si>
   <si>
@@ -1023,7 +1043,13 @@
     <t>选目标数量(1/N;0=无目标或全部)</t>
   </si>
   <si>
+    <t>主动道具分类</t>
+  </si>
+  <si>
     <t>ItemTargetKind</t>
+  </si>
+  <si>
+    <t>ActiveItemCategory</t>
   </si>
   <si>
     <t>item_active_season_sweet</t>
@@ -1045,6 +1071,9 @@
     <t>DiningTableDish</t>
   </si>
   <si>
+    <t>Strengthen</t>
+  </si>
+  <si>
     <t>item_active_season_bitter</t>
   </si>
   <si>
@@ -1207,9 +1236,6 @@
     <t>m_silver</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>item_active_reroll_action</t>
   </si>
   <si>
@@ -1225,6 +1251,9 @@
     <t>Global</t>
   </si>
   <si>
+    <t>Adjust</t>
+  </si>
+  <si>
     <t>item_active_half_next_action_cost</t>
   </si>
   <si>
@@ -1255,7 +1284,7 @@
     <t>幸运事件单</t>
   </si>
   <si>
-    <t>添加幸运事件至时间轴上</t>
+    <t>添加幸运事件至指定节点上</t>
   </si>
   <si>
     <t>TimelineAddRewardNode</t>
@@ -1270,7 +1299,7 @@
     <t>利息单</t>
   </si>
   <si>
-    <t>添加收取利息至时间轴上</t>
+    <t>添加收取利息至指定节点上</t>
   </si>
   <si>
     <t>TimelineAddInterestNode</t>
@@ -1285,7 +1314,7 @@
     <t>进货单</t>
   </si>
   <si>
-    <t>添加商店进货至时间轴上</t>
+    <t>添加商店进货至指定节点上</t>
   </si>
   <si>
     <t>TimelineAddShopNode</t>
@@ -1300,7 +1329,7 @@
     <t>抽奖机单</t>
   </si>
   <si>
-    <t>添加抽奖机至时间轴上</t>
+    <t>添加抽奖机至指定节点上</t>
   </si>
   <si>
     <t>TimelineAddLotteryNode</t>
@@ -1324,7 +1353,8 @@
     <t>未来加急单</t>
   </si>
   <si>
-    <t>立即执行1个未来的节点行动</t>
+    <t>指定1个未执行的节点行动
+复制到最近的节点</t>
   </si>
   <si>
     <t>TimelineExecuteFuture</t>
@@ -1336,7 +1366,8 @@
     <t>过往加急单</t>
   </si>
   <si>
-    <t>立即执行1个过去的节点行动</t>
+    <t>指定1个已执行的节点行动
+复制到最近的节点</t>
   </si>
   <si>
     <t>TimelineExecutePast</t>
@@ -1897,7 +1928,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -2536,7 +2567,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2557,7 +2588,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2570,9 +2606,12 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3446,7 +3485,7 @@
       <c r="F5" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="H5" s="20" t="s">
+      <c r="H5" s="22" t="s">
         <v>56</v>
       </c>
       <c r="I5" s="1">
@@ -3639,7 +3678,7 @@
       <c r="C9" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="10" t="s">
         <v>74</v>
       </c>
       <c r="E9" s="1" t="s">
@@ -3694,7 +3733,7 @@
       <c r="C10" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="D10" s="10" t="s">
         <v>79</v>
       </c>
       <c r="E10" s="1" t="s">
@@ -3745,7 +3784,7 @@
       </c>
       <c r="Z10">
         <f>COUNTIF($E$4:$E$84,T10)</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="AB10">
         <v>50</v>
@@ -3759,7 +3798,7 @@
       <c r="C11" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="D11" s="10" t="s">
         <v>83</v>
       </c>
       <c r="E11" s="1" t="s">
@@ -3811,339 +3850,329 @@
       </c>
       <c r="Z11">
         <f>COUNTIF($E$4:$E$84,T11)</f>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AB11">
         <v>80</v>
       </c>
     </row>
-    <row r="12" s="14" customFormat="1" ht="17" spans="1:18">
-      <c r="A12" s="16"/>
-      <c r="B12" s="16" t="s">
+    <row r="12" s="15" customFormat="1" ht="17" spans="1:18">
+      <c r="A12" s="18"/>
+      <c r="B12" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="C12" s="16" t="s">
+      <c r="C12" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="D12" s="17" t="s">
+      <c r="D12" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="E12" s="16" t="s">
+      <c r="E12" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="F12" s="16" t="s">
+      <c r="F12" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="G12" s="16">
+      <c r="G12" s="18">
         <v>1</v>
       </c>
-      <c r="H12" s="14"/>
-      <c r="I12" s="16">
+      <c r="I12" s="18">
         <v>300</v>
       </c>
-      <c r="J12" s="16" t="s">
+      <c r="J12" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="K12" s="16">
-        <v>0</v>
-      </c>
-      <c r="L12" s="16">
-        <v>0</v>
-      </c>
-      <c r="M12" s="16">
-        <v>0</v>
-      </c>
-      <c r="N12" s="16">
-        <v>0</v>
-      </c>
-      <c r="O12" s="16">
-        <v>0</v>
-      </c>
-      <c r="P12" s="16">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="14"/>
-      <c r="R12" s="14">
+      <c r="K12" s="18">
+        <v>0</v>
+      </c>
+      <c r="L12" s="18">
+        <v>0</v>
+      </c>
+      <c r="M12" s="18">
+        <v>0</v>
+      </c>
+      <c r="N12" s="18">
+        <v>0</v>
+      </c>
+      <c r="O12" s="18">
+        <v>0</v>
+      </c>
+      <c r="P12" s="18">
+        <v>0</v>
+      </c>
+      <c r="R12" s="15">
         <v>50</v>
       </c>
     </row>
-    <row r="13" s="14" customFormat="1" ht="17" spans="1:18">
-      <c r="A13" s="16"/>
-      <c r="B13" s="16" t="s">
+    <row r="13" s="15" customFormat="1" ht="17" spans="1:18">
+      <c r="A13" s="18"/>
+      <c r="B13" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="C13" s="16" t="s">
+      <c r="C13" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="D13" s="17" t="s">
+      <c r="D13" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="E13" s="16" t="s">
+      <c r="E13" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="F13" s="16" t="s">
+      <c r="F13" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="G13" s="16">
+      <c r="G13" s="18">
         <v>1</v>
       </c>
-      <c r="H13" s="14"/>
-      <c r="I13" s="16">
+      <c r="I13" s="18">
         <v>300</v>
       </c>
-      <c r="J13" s="16" t="s">
+      <c r="J13" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="K13" s="16">
-        <v>0</v>
-      </c>
-      <c r="L13" s="16">
-        <v>0</v>
-      </c>
-      <c r="M13" s="16">
-        <v>0</v>
-      </c>
-      <c r="N13" s="16">
-        <v>0</v>
-      </c>
-      <c r="O13" s="16">
-        <v>0</v>
-      </c>
-      <c r="P13" s="16">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="14"/>
-      <c r="R13" s="14">
+      <c r="K13" s="18">
+        <v>0</v>
+      </c>
+      <c r="L13" s="18">
+        <v>0</v>
+      </c>
+      <c r="M13" s="18">
+        <v>0</v>
+      </c>
+      <c r="N13" s="18">
+        <v>0</v>
+      </c>
+      <c r="O13" s="18">
+        <v>0</v>
+      </c>
+      <c r="P13" s="18">
+        <v>0</v>
+      </c>
+      <c r="R13" s="15">
         <v>50</v>
       </c>
     </row>
-    <row r="14" s="14" customFormat="1" ht="17" spans="1:18">
-      <c r="A14" s="16"/>
-      <c r="B14" s="16" t="s">
+    <row r="14" s="15" customFormat="1" ht="17" spans="1:18">
+      <c r="A14" s="18"/>
+      <c r="B14" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="C14" s="16" t="s">
+      <c r="C14" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="D14" s="17" t="s">
+      <c r="D14" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="E14" s="16" t="s">
+      <c r="E14" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="F14" s="16" t="s">
+      <c r="F14" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="G14" s="16">
+      <c r="G14" s="18">
         <v>2</v>
       </c>
-      <c r="H14" s="14"/>
-      <c r="I14" s="16">
+      <c r="I14" s="18">
         <v>100</v>
       </c>
-      <c r="J14" s="16" t="s">
+      <c r="J14" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="K14" s="16">
-        <v>0</v>
-      </c>
-      <c r="L14" s="16">
-        <v>0</v>
-      </c>
-      <c r="M14" s="16">
-        <v>0</v>
-      </c>
-      <c r="N14" s="16">
-        <v>0</v>
-      </c>
-      <c r="O14" s="16">
-        <v>0</v>
-      </c>
-      <c r="P14" s="16">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="14"/>
-      <c r="R14" s="14">
+      <c r="K14" s="18">
+        <v>0</v>
+      </c>
+      <c r="L14" s="18">
+        <v>0</v>
+      </c>
+      <c r="M14" s="18">
+        <v>0</v>
+      </c>
+      <c r="N14" s="18">
+        <v>0</v>
+      </c>
+      <c r="O14" s="18">
+        <v>0</v>
+      </c>
+      <c r="P14" s="18">
+        <v>0</v>
+      </c>
+      <c r="R14" s="15">
         <v>80</v>
       </c>
     </row>
-    <row r="15" s="14" customFormat="1" ht="17" spans="1:18">
-      <c r="A15" s="16"/>
-      <c r="B15" s="16" t="s">
+    <row r="15" s="15" customFormat="1" ht="17" spans="1:18">
+      <c r="A15" s="18"/>
+      <c r="B15" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="C15" s="16" t="s">
+      <c r="C15" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="D15" s="17" t="s">
+      <c r="D15" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="E15" s="16" t="s">
+      <c r="E15" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="F15" s="16" t="s">
+      <c r="F15" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="G15" s="16">
+      <c r="G15" s="18">
         <v>2</v>
       </c>
-      <c r="H15" s="14"/>
-      <c r="I15" s="16">
+      <c r="I15" s="18">
         <v>30</v>
       </c>
-      <c r="J15" s="16" t="s">
+      <c r="J15" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="K15" s="16">
-        <v>0</v>
-      </c>
-      <c r="L15" s="16">
-        <v>0</v>
-      </c>
-      <c r="M15" s="16">
-        <v>0</v>
-      </c>
-      <c r="N15" s="16">
-        <v>0</v>
-      </c>
-      <c r="O15" s="16">
-        <v>0</v>
-      </c>
-      <c r="P15" s="16">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="14"/>
-      <c r="R15" s="14">
+      <c r="K15" s="18">
+        <v>0</v>
+      </c>
+      <c r="L15" s="18">
+        <v>0</v>
+      </c>
+      <c r="M15" s="18">
+        <v>0</v>
+      </c>
+      <c r="N15" s="18">
+        <v>0</v>
+      </c>
+      <c r="O15" s="18">
+        <v>0</v>
+      </c>
+      <c r="P15" s="18">
+        <v>0</v>
+      </c>
+      <c r="R15" s="15">
         <v>120</v>
       </c>
     </row>
-    <row r="16" s="14" customFormat="1" ht="17" spans="2:28">
-      <c r="B16" s="16" t="s">
+    <row r="16" s="15" customFormat="1" ht="17" spans="2:28">
+      <c r="B16" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="C16" s="16" t="s">
+      <c r="C16" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="D16" s="17" t="s">
+      <c r="D16" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="E16" s="16" t="s">
+      <c r="E16" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="F16" s="16" t="s">
+      <c r="F16" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="G16" s="16">
+      <c r="G16" s="18">
         <v>0.15</v>
       </c>
-      <c r="H16" s="14"/>
-      <c r="I16" s="16">
+      <c r="I16" s="18">
         <v>100</v>
       </c>
-      <c r="J16" s="16" t="s">
+      <c r="J16" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="K16" s="16">
-        <v>0</v>
-      </c>
-      <c r="L16" s="16">
-        <v>0</v>
-      </c>
-      <c r="M16" s="16">
-        <v>0</v>
-      </c>
-      <c r="N16" s="16">
-        <v>0</v>
-      </c>
-      <c r="O16" s="16">
-        <v>0</v>
-      </c>
-      <c r="P16" s="16">
-        <v>0</v>
-      </c>
-      <c r="R16" s="14">
+      <c r="K16" s="18">
+        <v>0</v>
+      </c>
+      <c r="L16" s="18">
+        <v>0</v>
+      </c>
+      <c r="M16" s="18">
+        <v>0</v>
+      </c>
+      <c r="N16" s="18">
+        <v>0</v>
+      </c>
+      <c r="O16" s="18">
+        <v>0</v>
+      </c>
+      <c r="P16" s="18">
+        <v>0</v>
+      </c>
+      <c r="R16" s="15">
         <f t="shared" ref="R16:R36" si="1">VLOOKUP(E16,$T$10:$AB$17,9,FALSE)</f>
         <v>80</v>
       </c>
-      <c r="T16" s="14" t="s">
+      <c r="T16" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="V16" s="14">
+      <c r="V16" s="15">
         <v>30</v>
       </c>
-      <c r="X16" s="14" t="s">
+      <c r="X16" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="Z16" s="14">
+      <c r="Z16" s="15">
         <f>COUNTIF($E$4:$E$84,T16)</f>
         <v>10</v>
       </c>
-      <c r="AB16" s="14">
+      <c r="AB16" s="15">
         <v>120</v>
       </c>
     </row>
-    <row r="17" s="14" customFormat="1" spans="2:28">
-      <c r="B17" s="16" t="s">
+    <row r="17" s="15" customFormat="1" spans="2:28">
+      <c r="B17" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="C17" s="16" t="s">
+      <c r="C17" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="D17" s="16" t="s">
+      <c r="D17" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="E17" s="16" t="s">
+      <c r="E17" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="F17" s="16" t="s">
+      <c r="F17" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="G17" s="16">
+      <c r="G17" s="18">
         <v>0.2</v>
       </c>
-      <c r="H17" s="14"/>
-      <c r="I17" s="16">
+      <c r="I17" s="18">
         <v>300</v>
       </c>
-      <c r="J17" s="16" t="s">
+      <c r="J17" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="K17" s="16">
-        <v>0</v>
-      </c>
-      <c r="L17" s="16">
-        <v>0</v>
-      </c>
-      <c r="M17" s="16">
-        <v>0</v>
-      </c>
-      <c r="N17" s="16">
-        <v>0</v>
-      </c>
-      <c r="O17" s="16">
-        <v>0</v>
-      </c>
-      <c r="P17" s="16">
-        <v>0</v>
-      </c>
-      <c r="R17" s="14">
+      <c r="K17" s="18">
+        <v>0</v>
+      </c>
+      <c r="L17" s="18">
+        <v>0</v>
+      </c>
+      <c r="M17" s="18">
+        <v>0</v>
+      </c>
+      <c r="N17" s="18">
+        <v>0</v>
+      </c>
+      <c r="O17" s="18">
+        <v>0</v>
+      </c>
+      <c r="P17" s="18">
+        <v>0</v>
+      </c>
+      <c r="R17" s="15">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="T17" s="14" t="s">
+      <c r="T17" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="V17" s="14">
+      <c r="V17" s="15">
         <v>10</v>
       </c>
-      <c r="X17" s="14" t="s">
+      <c r="X17" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="Z17" s="14">
+      <c r="Z17" s="15">
         <f>COUNTIF($E$4:$E$84,T17)</f>
         <v>6</v>
       </c>
-      <c r="AB17" s="14">
+      <c r="AB17" s="15">
         <v>200</v>
       </c>
     </row>
@@ -4346,7 +4375,7 @@
       <c r="C22" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="D22" s="9" t="s">
+      <c r="D22" s="10" t="s">
         <v>118</v>
       </c>
       <c r="E22" s="1" t="s">
@@ -4394,7 +4423,7 @@
       <c r="C23" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="D23" s="9" t="s">
+      <c r="D23" s="10" t="s">
         <v>121</v>
       </c>
       <c r="E23" s="1" t="s">
@@ -4445,7 +4474,7 @@
       <c r="C24" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="D24" s="9" t="s">
+      <c r="D24" s="10" t="s">
         <v>125</v>
       </c>
       <c r="E24" s="1" t="s">
@@ -4493,7 +4522,7 @@
       <c r="C25" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="D25" s="9" t="s">
+      <c r="D25" s="10" t="s">
         <v>128</v>
       </c>
       <c r="E25" s="1" t="s">
@@ -4589,7 +4618,7 @@
       <c r="C27" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="D27" s="9" t="s">
+      <c r="D27" s="10" t="s">
         <v>134</v>
       </c>
       <c r="E27" s="1" t="s">
@@ -4640,7 +4669,7 @@
       <c r="C28" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="D28" s="9" t="s">
+      <c r="D28" s="10" t="s">
         <v>138</v>
       </c>
       <c r="E28" s="1" t="s">
@@ -4691,7 +4720,7 @@
       <c r="C29" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="D29" s="9" t="s">
+      <c r="D29" s="10" t="s">
         <v>142</v>
       </c>
       <c r="E29" s="1" t="s">
@@ -4739,7 +4768,7 @@
       <c r="C30" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="D30" s="9" t="s">
+      <c r="D30" s="10" t="s">
         <v>145</v>
       </c>
       <c r="E30" s="1" t="s">
@@ -4780,65 +4809,65 @@
         <v>50</v>
       </c>
     </row>
-    <row r="31" s="15" customFormat="1" ht="34" spans="1:18">
-      <c r="A31" s="18"/>
-      <c r="B31" s="18" t="s">
+    <row r="31" s="16" customFormat="1" ht="34" spans="1:18">
+      <c r="A31" s="20"/>
+      <c r="B31" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="C31" s="20" t="s">
         <v>147</v>
       </c>
-      <c r="C31" s="18" t="s">
+      <c r="D31" s="21" t="s">
         <v>148</v>
       </c>
-      <c r="D31" s="19" t="s">
-        <v>149</v>
-      </c>
-      <c r="E31" s="18" t="s">
+      <c r="E31" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="F31" s="18" t="s">
+      <c r="F31" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="G31" s="18">
+      <c r="G31" s="20">
         <v>1</v>
       </c>
-      <c r="H31" s="18"/>
-      <c r="I31" s="18">
+      <c r="H31" s="20"/>
+      <c r="I31" s="20">
         <v>100</v>
       </c>
-      <c r="J31" s="18" t="s">
+      <c r="J31" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="K31" s="18">
-        <v>0</v>
-      </c>
-      <c r="L31" s="18">
-        <v>0</v>
-      </c>
-      <c r="M31" s="18">
-        <v>0</v>
-      </c>
-      <c r="N31" s="18">
-        <v>0</v>
-      </c>
-      <c r="O31" s="18">
-        <v>0</v>
-      </c>
-      <c r="P31" s="18">
-        <v>0</v>
-      </c>
-      <c r="R31" s="15">
+      <c r="K31" s="20">
+        <v>0</v>
+      </c>
+      <c r="L31" s="20">
+        <v>0</v>
+      </c>
+      <c r="M31" s="20">
+        <v>0</v>
+      </c>
+      <c r="N31" s="20">
+        <v>0</v>
+      </c>
+      <c r="O31" s="20">
+        <v>0</v>
+      </c>
+      <c r="P31" s="20">
+        <v>0</v>
+      </c>
+      <c r="R31" s="16">
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
     </row>
     <row r="32" ht="17" spans="2:18">
       <c r="B32" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="C32" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="D32" s="10" t="s">
         <v>151</v>
-      </c>
-      <c r="D32" s="9" t="s">
-        <v>152</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>61</v>
@@ -4878,170 +4907,170 @@
         <v>120</v>
       </c>
     </row>
-    <row r="33" s="8" customFormat="1" ht="51" spans="1:18">
-      <c r="A33" s="10"/>
-      <c r="B33" s="10" t="s">
+    <row r="33" s="17" customFormat="1" ht="51" spans="1:18">
+      <c r="A33" s="11"/>
+      <c r="B33" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="C33" s="11" t="s">
         <v>153</v>
       </c>
-      <c r="C33" s="10" t="s">
+      <c r="D33" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="D33" s="12" t="s">
+      <c r="E33" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="F33" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="G33" s="11">
+        <v>200</v>
+      </c>
+      <c r="H33" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="E33" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="F33" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="G33" s="10">
-        <v>200</v>
-      </c>
-      <c r="H33" s="10" t="s">
-        <v>156</v>
-      </c>
-      <c r="I33" s="10">
+      <c r="I33" s="11">
         <v>100</v>
       </c>
-      <c r="J33" s="10" t="s">
+      <c r="J33" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="K33" s="10">
-        <v>0</v>
-      </c>
-      <c r="L33" s="10">
-        <v>0</v>
-      </c>
-      <c r="M33" s="10">
-        <v>0</v>
-      </c>
-      <c r="N33" s="10">
-        <v>0</v>
-      </c>
-      <c r="O33" s="10">
-        <v>0</v>
-      </c>
-      <c r="P33" s="10">
-        <v>0</v>
-      </c>
-      <c r="R33" s="8">
+      <c r="K33" s="11">
+        <v>0</v>
+      </c>
+      <c r="L33" s="11">
+        <v>0</v>
+      </c>
+      <c r="M33" s="11">
+        <v>0</v>
+      </c>
+      <c r="N33" s="11">
+        <v>0</v>
+      </c>
+      <c r="O33" s="11">
+        <v>0</v>
+      </c>
+      <c r="P33" s="11">
+        <v>0</v>
+      </c>
+      <c r="R33" s="17">
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
     </row>
-    <row r="34" s="8" customFormat="1" ht="17" spans="1:18">
-      <c r="A34" s="10"/>
-      <c r="B34" s="10" t="s">
+    <row r="34" s="17" customFormat="1" ht="17" spans="1:18">
+      <c r="A34" s="11"/>
+      <c r="B34" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="C34" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="C34" s="10" t="s">
+      <c r="D34" s="13" t="s">
         <v>158</v>
       </c>
-      <c r="D34" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="E34" s="10" t="s">
+      <c r="E34" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="F34" s="10" t="s">
+      <c r="F34" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="G34" s="10">
-        <v>0</v>
-      </c>
-      <c r="H34" s="10"/>
-      <c r="I34" s="10">
+      <c r="G34" s="11">
+        <v>0</v>
+      </c>
+      <c r="H34" s="11"/>
+      <c r="I34" s="11">
         <v>100</v>
       </c>
-      <c r="J34" s="10" t="s">
+      <c r="J34" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="K34" s="10">
-        <v>0</v>
-      </c>
-      <c r="L34" s="10">
-        <v>0</v>
-      </c>
-      <c r="M34" s="10">
-        <v>0</v>
-      </c>
-      <c r="N34" s="10">
-        <v>0</v>
-      </c>
-      <c r="O34" s="10">
-        <v>0</v>
-      </c>
-      <c r="P34" s="10">
-        <v>0</v>
-      </c>
-      <c r="R34" s="8">
+      <c r="K34" s="11">
+        <v>0</v>
+      </c>
+      <c r="L34" s="11">
+        <v>0</v>
+      </c>
+      <c r="M34" s="11">
+        <v>0</v>
+      </c>
+      <c r="N34" s="11">
+        <v>0</v>
+      </c>
+      <c r="O34" s="11">
+        <v>0</v>
+      </c>
+      <c r="P34" s="11">
+        <v>0</v>
+      </c>
+      <c r="R34" s="17">
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
     </row>
-    <row r="35" s="8" customFormat="1" ht="17" spans="1:18">
-      <c r="A35" s="10"/>
-      <c r="B35" s="10" t="s">
+    <row r="35" s="17" customFormat="1" ht="17" spans="1:18">
+      <c r="A35" s="11"/>
+      <c r="B35" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="C35" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="C35" s="10" t="s">
+      <c r="D35" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="D35" s="12" t="s">
-        <v>162</v>
-      </c>
-      <c r="E35" s="10" t="s">
+      <c r="E35" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="F35" s="10" t="s">
+      <c r="F35" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="G35" s="10">
+      <c r="G35" s="11">
         <v>8</v>
       </c>
-      <c r="H35" s="10"/>
-      <c r="I35" s="10">
+      <c r="H35" s="11"/>
+      <c r="I35" s="11">
         <v>100</v>
       </c>
-      <c r="J35" s="10" t="s">
+      <c r="J35" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="K35" s="10">
-        <v>0</v>
-      </c>
-      <c r="L35" s="10">
-        <v>0</v>
-      </c>
-      <c r="M35" s="10">
-        <v>0</v>
-      </c>
-      <c r="N35" s="10">
-        <v>0</v>
-      </c>
-      <c r="O35" s="10">
-        <v>0</v>
-      </c>
-      <c r="P35" s="10">
-        <v>0</v>
-      </c>
-      <c r="R35" s="8">
+      <c r="K35" s="11">
+        <v>0</v>
+      </c>
+      <c r="L35" s="11">
+        <v>0</v>
+      </c>
+      <c r="M35" s="11">
+        <v>0</v>
+      </c>
+      <c r="N35" s="11">
+        <v>0</v>
+      </c>
+      <c r="O35" s="11">
+        <v>0</v>
+      </c>
+      <c r="P35" s="11">
+        <v>0</v>
+      </c>
+      <c r="R35" s="17">
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
     </row>
     <row r="36" ht="17" spans="2:18">
       <c r="B36" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C36" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="D36" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="D36" s="9" t="s">
+      <c r="E36" s="1" t="s">
         <v>165</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>166</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>49</v>
@@ -5078,67 +5107,67 @@
         <v>200</v>
       </c>
     </row>
-    <row r="37" s="14" customFormat="1" ht="34" spans="1:18">
-      <c r="A37" s="16"/>
-      <c r="B37" s="16" t="s">
+    <row r="37" s="15" customFormat="1" ht="34" spans="1:18">
+      <c r="A37" s="18"/>
+      <c r="B37" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="C37" s="18" t="s">
         <v>167</v>
       </c>
-      <c r="C37" s="16" t="s">
+      <c r="D37" s="19" t="s">
         <v>168</v>
       </c>
-      <c r="D37" s="17" t="s">
+      <c r="E37" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="F37" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="G37" s="18">
+        <v>1</v>
+      </c>
+      <c r="H37" s="18" t="s">
         <v>169</v>
       </c>
-      <c r="E37" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="F37" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="G37" s="16">
-        <v>1</v>
-      </c>
-      <c r="H37" s="16" t="s">
-        <v>170</v>
-      </c>
-      <c r="I37" s="16">
+      <c r="I37" s="18">
         <v>100</v>
       </c>
-      <c r="J37" s="16" t="s">
+      <c r="J37" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="K37" s="16">
-        <v>0</v>
-      </c>
-      <c r="L37" s="16">
-        <v>0</v>
-      </c>
-      <c r="M37" s="16">
-        <v>0</v>
-      </c>
-      <c r="N37" s="16">
-        <v>0</v>
-      </c>
-      <c r="O37" s="16">
-        <v>0</v>
-      </c>
-      <c r="P37" s="16">
-        <v>0</v>
-      </c>
-      <c r="R37" s="14">
+      <c r="K37" s="18">
+        <v>0</v>
+      </c>
+      <c r="L37" s="18">
+        <v>0</v>
+      </c>
+      <c r="M37" s="18">
+        <v>0</v>
+      </c>
+      <c r="N37" s="18">
+        <v>0</v>
+      </c>
+      <c r="O37" s="18">
+        <v>0</v>
+      </c>
+      <c r="P37" s="18">
+        <v>0</v>
+      </c>
+      <c r="R37" s="15">
         <f t="shared" ref="R37:R54" si="2">VLOOKUP(E37,$T$10:$AB$17,9,FALSE)</f>
         <v>80</v>
       </c>
     </row>
     <row r="38" ht="34" spans="2:18">
       <c r="B38" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C38" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="D38" s="10" t="s">
         <v>172</v>
-      </c>
-      <c r="D38" s="9" t="s">
-        <v>173</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>70</v>
@@ -5150,7 +5179,7 @@
         <v>2</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I38" s="1">
         <v>300</v>
@@ -5183,13 +5212,13 @@
     </row>
     <row r="39" ht="34" spans="2:18">
       <c r="B39" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="C39" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="D39" s="10" t="s">
         <v>176</v>
-      </c>
-      <c r="D39" s="9" t="s">
-        <v>177</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>70</v>
@@ -5201,7 +5230,7 @@
         <v>2</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="I39" s="1">
         <v>300</v>
@@ -5234,13 +5263,13 @@
     </row>
     <row r="40" spans="2:18">
       <c r="B40" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C40" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="D40" s="1" t="s">
         <v>180</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>181</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>48</v>
@@ -5282,13 +5311,13 @@
     </row>
     <row r="41" ht="34" spans="2:18">
       <c r="B41" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C41" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="D41" s="10" t="s">
         <v>183</v>
-      </c>
-      <c r="D41" s="9" t="s">
-        <v>184</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>48</v>
@@ -5328,65 +5357,65 @@
         <v>80</v>
       </c>
     </row>
-    <row r="42" s="8" customFormat="1" ht="34" spans="1:18">
-      <c r="A42" s="10"/>
-      <c r="B42" s="10" t="s">
+    <row r="42" s="17" customFormat="1" ht="34" spans="1:18">
+      <c r="A42" s="11"/>
+      <c r="B42" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="C42" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="C42" s="10" t="s">
+      <c r="D42" s="13" t="s">
         <v>186</v>
       </c>
-      <c r="D42" s="12" t="s">
-        <v>187</v>
-      </c>
-      <c r="E42" s="10" t="s">
+      <c r="E42" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="F42" s="10" t="s">
+      <c r="F42" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="G42" s="10">
+      <c r="G42" s="11">
         <v>600</v>
       </c>
-      <c r="H42" s="10"/>
-      <c r="I42" s="10">
+      <c r="H42" s="11"/>
+      <c r="I42" s="11">
         <v>100</v>
       </c>
-      <c r="J42" s="10" t="s">
+      <c r="J42" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="K42" s="10">
-        <v>0</v>
-      </c>
-      <c r="L42" s="10">
-        <v>0</v>
-      </c>
-      <c r="M42" s="10">
-        <v>0</v>
-      </c>
-      <c r="N42" s="10">
-        <v>0</v>
-      </c>
-      <c r="O42" s="10">
-        <v>0</v>
-      </c>
-      <c r="P42" s="10">
-        <v>0</v>
-      </c>
-      <c r="R42" s="8">
+      <c r="K42" s="11">
+        <v>0</v>
+      </c>
+      <c r="L42" s="11">
+        <v>0</v>
+      </c>
+      <c r="M42" s="11">
+        <v>0</v>
+      </c>
+      <c r="N42" s="11">
+        <v>0</v>
+      </c>
+      <c r="O42" s="11">
+        <v>0</v>
+      </c>
+      <c r="P42" s="11">
+        <v>0</v>
+      </c>
+      <c r="R42" s="17">
         <f t="shared" si="2"/>
         <v>80</v>
       </c>
     </row>
     <row r="43" ht="17" spans="2:18">
       <c r="B43" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C43" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="D43" s="10" t="s">
         <v>189</v>
-      </c>
-      <c r="D43" s="9" t="s">
-        <v>190</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>48</v>
@@ -5428,13 +5457,13 @@
     </row>
     <row r="44" ht="34" spans="2:18">
       <c r="B44" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C44" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="D44" s="10" t="s">
         <v>192</v>
-      </c>
-      <c r="D44" s="9" t="s">
-        <v>193</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>48</v>
@@ -5476,13 +5505,13 @@
     </row>
     <row r="45" ht="34" spans="2:18">
       <c r="B45" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="C45" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="D45" s="10" t="s">
         <v>195</v>
-      </c>
-      <c r="D45" s="9" t="s">
-        <v>196</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>48</v>
@@ -5524,16 +5553,16 @@
     </row>
     <row r="46" spans="2:18">
       <c r="B46" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="C46" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="D46" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="D46" s="1" t="s">
-        <v>199</v>
-      </c>
       <c r="E46" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>49</v>
@@ -5570,65 +5599,65 @@
         <v>200</v>
       </c>
     </row>
-    <row r="47" s="8" customFormat="1" ht="34" spans="1:18">
-      <c r="A47" s="10"/>
-      <c r="B47" s="10" t="s">
+    <row r="47" s="17" customFormat="1" ht="34" spans="1:18">
+      <c r="A47" s="11"/>
+      <c r="B47" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="C47" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="C47" s="10" t="s">
+      <c r="D47" s="13" t="s">
         <v>201</v>
       </c>
-      <c r="D47" s="12" t="s">
-        <v>202</v>
-      </c>
-      <c r="E47" s="10" t="s">
+      <c r="E47" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="F47" s="10" t="s">
+      <c r="F47" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="G47" s="10">
+      <c r="G47" s="11">
         <v>1</v>
       </c>
-      <c r="H47" s="10"/>
-      <c r="I47" s="10">
+      <c r="H47" s="11"/>
+      <c r="I47" s="11">
         <v>100</v>
       </c>
-      <c r="J47" s="10" t="s">
+      <c r="J47" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="K47" s="10">
-        <v>0</v>
-      </c>
-      <c r="L47" s="10">
-        <v>0</v>
-      </c>
-      <c r="M47" s="10">
-        <v>0</v>
-      </c>
-      <c r="N47" s="10">
-        <v>0</v>
-      </c>
-      <c r="O47" s="10">
-        <v>0</v>
-      </c>
-      <c r="P47" s="10">
-        <v>0</v>
-      </c>
-      <c r="R47" s="8">
+      <c r="K47" s="11">
+        <v>0</v>
+      </c>
+      <c r="L47" s="11">
+        <v>0</v>
+      </c>
+      <c r="M47" s="11">
+        <v>0</v>
+      </c>
+      <c r="N47" s="11">
+        <v>0</v>
+      </c>
+      <c r="O47" s="11">
+        <v>0</v>
+      </c>
+      <c r="P47" s="11">
+        <v>0</v>
+      </c>
+      <c r="R47" s="17">
         <f t="shared" si="2"/>
         <v>80</v>
       </c>
     </row>
     <row r="48" ht="34" spans="2:18">
       <c r="B48" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="C48" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="C48" s="1" t="s">
+      <c r="D48" s="10" t="s">
         <v>204</v>
-      </c>
-      <c r="D48" s="9" t="s">
-        <v>205</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>48</v>
@@ -5670,13 +5699,13 @@
     </row>
     <row r="49" ht="34" spans="2:18">
       <c r="B49" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="C49" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="D49" s="10" t="s">
         <v>207</v>
-      </c>
-      <c r="D49" s="9" t="s">
-        <v>208</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>48</v>
@@ -5718,13 +5747,13 @@
     </row>
     <row r="50" ht="34" spans="2:18">
       <c r="B50" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="C50" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="C50" s="1" t="s">
+      <c r="D50" s="10" t="s">
         <v>210</v>
-      </c>
-      <c r="D50" s="9" t="s">
-        <v>211</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>61</v>
@@ -5766,13 +5795,13 @@
     </row>
     <row r="51" ht="17" spans="2:18">
       <c r="B51" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="C51" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="C51" s="1" t="s">
+      <c r="D51" s="10" t="s">
         <v>213</v>
-      </c>
-      <c r="D51" s="9" t="s">
-        <v>214</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>61</v>
@@ -5814,13 +5843,13 @@
     </row>
     <row r="52" spans="2:18">
       <c r="B52" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C52" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="C52" s="1" t="s">
+      <c r="D52" s="1" t="s">
         <v>216</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>217</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>70</v>
@@ -5862,13 +5891,13 @@
     </row>
     <row r="53" ht="34" spans="2:18">
       <c r="B53" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="C53" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="C53" s="1" t="s">
+      <c r="D53" s="10" t="s">
         <v>219</v>
-      </c>
-      <c r="D53" s="9" t="s">
-        <v>220</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>70</v>
@@ -5908,185 +5937,165 @@
         <v>50</v>
       </c>
     </row>
-    <row r="54" s="8" customFormat="1" ht="17" spans="1:18">
-      <c r="A54" s="10"/>
-      <c r="B54" s="10" t="s">
+    <row r="54" s="17" customFormat="1" ht="17" spans="1:18">
+      <c r="A54" s="11"/>
+      <c r="B54" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="C54" s="11" t="s">
         <v>221</v>
       </c>
-      <c r="C54" s="10" t="s">
+      <c r="D54" s="13" t="s">
         <v>222</v>
       </c>
-      <c r="D54" s="12" t="s">
-        <v>223</v>
-      </c>
-      <c r="E54" s="10" t="s">
+      <c r="E54" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="F54" s="10" t="s">
+      <c r="F54" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="G54" s="10">
-        <v>0</v>
-      </c>
-      <c r="H54" s="10"/>
-      <c r="I54" s="10">
+      <c r="G54" s="11">
+        <v>0</v>
+      </c>
+      <c r="H54" s="11"/>
+      <c r="I54" s="11">
         <v>30</v>
       </c>
-      <c r="J54" s="10" t="s">
+      <c r="J54" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="K54" s="10">
-        <v>0</v>
-      </c>
-      <c r="L54" s="10">
-        <v>0</v>
-      </c>
-      <c r="M54" s="10">
-        <v>0</v>
-      </c>
-      <c r="N54" s="10">
-        <v>0</v>
-      </c>
-      <c r="O54" s="10">
-        <v>0</v>
-      </c>
-      <c r="P54" s="10">
-        <v>0</v>
-      </c>
-      <c r="R54" s="8">
+      <c r="K54" s="11">
+        <v>0</v>
+      </c>
+      <c r="L54" s="11">
+        <v>0</v>
+      </c>
+      <c r="M54" s="11">
+        <v>0</v>
+      </c>
+      <c r="N54" s="11">
+        <v>0</v>
+      </c>
+      <c r="O54" s="11">
+        <v>0</v>
+      </c>
+      <c r="P54" s="11">
+        <v>0</v>
+      </c>
+      <c r="R54" s="17">
         <f t="shared" si="2"/>
         <v>50</v>
       </c>
     </row>
-    <row r="55" s="8" customFormat="1" spans="1:18">
-      <c r="A55" s="10"/>
-      <c r="B55" s="10" t="inlineStr">
-        <is>
-          <t>item_shop_restock_active</t>
-        </is>
-      </c>
-      <c r="C55" s="10" t="inlineStr">
-        <is>
-          <t>主动补货</t>
-        </is>
-      </c>
-      <c r="D55" s="10" t="s">
+    <row r="55" s="17" customFormat="1" spans="1:18">
+      <c r="A55" s="11"/>
+      <c r="B55" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="C55" s="11" t="s">
         <v>224</v>
       </c>
-      <c r="E55" s="10" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="F55" s="10" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G55" s="10">
-        <v>0</v>
-      </c>
-      <c r="H55" s="10"/>
-      <c r="I55" s="10">
+      <c r="D55" s="11" t="s">
+        <v>225</v>
+      </c>
+      <c r="E55" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="F55" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="G55" s="11">
+        <v>0</v>
+      </c>
+      <c r="H55" s="11"/>
+      <c r="I55" s="11">
         <v>30</v>
       </c>
-      <c r="J55" s="10" t="inlineStr">
-        <is>
-          <t>30,80</t>
-        </is>
-      </c>
-      <c r="K55" s="10">
-        <v>0</v>
-      </c>
-      <c r="L55" s="10">
-        <v>0</v>
-      </c>
-      <c r="M55" s="10">
-        <v>0</v>
-      </c>
-      <c r="N55" s="10">
-        <v>0</v>
-      </c>
-      <c r="O55" s="10">
-        <v>0</v>
-      </c>
-      <c r="P55" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q55" s="10"/>
-      <c r="R55" s="8">
+      <c r="J55" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="K55" s="11">
+        <v>0</v>
+      </c>
+      <c r="L55" s="11">
+        <v>0</v>
+      </c>
+      <c r="M55" s="11">
+        <v>0</v>
+      </c>
+      <c r="N55" s="11">
+        <v>0</v>
+      </c>
+      <c r="O55" s="11">
+        <v>0</v>
+      </c>
+      <c r="P55" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q55" s="11"/>
+      <c r="R55" s="17">
         <v>50</v>
       </c>
     </row>
-    <row r="56" s="8" customFormat="1" spans="1:18">
-      <c r="A56" s="10"/>
-      <c r="B56" s="10" t="inlineStr">
-        <is>
-          <t>item_shop_restock_passive</t>
-        </is>
-      </c>
-      <c r="C56" s="10" t="inlineStr">
-        <is>
-          <t>被动补货</t>
-        </is>
-      </c>
-      <c r="D56" s="10" t="s">
-        <v>225</v>
-      </c>
-      <c r="E56" s="10" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="F56" s="10" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G56" s="10">
-        <v>0</v>
-      </c>
-      <c r="H56" s="10"/>
-      <c r="I56" s="10">
+    <row r="56" s="17" customFormat="1" spans="1:18">
+      <c r="A56" s="11"/>
+      <c r="B56" s="11" t="s">
+        <v>226</v>
+      </c>
+      <c r="C56" s="11" t="s">
+        <v>227</v>
+      </c>
+      <c r="D56" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="E56" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="F56" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="G56" s="11">
+        <v>0</v>
+      </c>
+      <c r="H56" s="11"/>
+      <c r="I56" s="11">
         <v>30</v>
       </c>
-      <c r="J56" s="10" t="inlineStr">
-        <is>
-          <t>30,80</t>
-        </is>
-      </c>
-      <c r="K56" s="10">
-        <v>0</v>
-      </c>
-      <c r="L56" s="10">
-        <v>0</v>
-      </c>
-      <c r="M56" s="10">
-        <v>0</v>
-      </c>
-      <c r="N56" s="10">
-        <v>0</v>
-      </c>
-      <c r="O56" s="10">
-        <v>0</v>
-      </c>
-      <c r="P56" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q56" s="10"/>
-      <c r="R56" s="8">
+      <c r="J56" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="K56" s="11">
+        <v>0</v>
+      </c>
+      <c r="L56" s="11">
+        <v>0</v>
+      </c>
+      <c r="M56" s="11">
+        <v>0</v>
+      </c>
+      <c r="N56" s="11">
+        <v>0</v>
+      </c>
+      <c r="O56" s="11">
+        <v>0</v>
+      </c>
+      <c r="P56" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q56" s="11"/>
+      <c r="R56" s="17">
         <v>50</v>
       </c>
     </row>
     <row r="57" ht="34" spans="2:18">
       <c r="B57" s="1" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="D57" s="9" t="s">
-        <v>228</v>
+        <v>230</v>
+      </c>
+      <c r="D57" s="10" t="s">
+        <v>231</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>48</v>
@@ -6128,13 +6137,13 @@
     </row>
     <row r="58" ht="34" spans="2:18">
       <c r="B58" s="1" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="D58" s="9" t="s">
-        <v>231</v>
+        <v>233</v>
+      </c>
+      <c r="D58" s="10" t="s">
+        <v>234</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>48</v>
@@ -6146,7 +6155,7 @@
         <v>0</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="I58" s="1">
         <v>100</v>
@@ -6179,13 +6188,13 @@
     </row>
     <row r="59" ht="34" spans="2:18">
       <c r="B59" s="1" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="D59" s="9" t="s">
-        <v>235</v>
+        <v>237</v>
+      </c>
+      <c r="D59" s="10" t="s">
+        <v>238</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>48</v>
@@ -6197,7 +6206,7 @@
         <v>0</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="I59" s="1">
         <v>100</v>
@@ -6230,13 +6239,13 @@
     </row>
     <row r="60" ht="17" spans="2:18">
       <c r="B60" s="1" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="D60" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
+      </c>
+      <c r="D60" s="10" t="s">
+        <v>242</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>70</v>
@@ -6278,13 +6287,13 @@
     </row>
     <row r="61" spans="2:18">
       <c r="B61" s="1" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>70</v>
@@ -6326,13 +6335,13 @@
     </row>
     <row r="62" ht="34" spans="2:18">
       <c r="B62" s="1" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="D62" s="9" t="s">
-        <v>245</v>
+        <v>247</v>
+      </c>
+      <c r="D62" s="10" t="s">
+        <v>248</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>48</v>
@@ -6372,71 +6381,71 @@
         <v>80</v>
       </c>
     </row>
-    <row r="63" s="8" customFormat="1" ht="17" spans="1:18">
-      <c r="A63" s="10"/>
-      <c r="B63" s="10" t="s">
-        <v>246</v>
-      </c>
-      <c r="C63" s="10" t="s">
-        <v>247</v>
-      </c>
-      <c r="D63" s="12" t="s">
-        <v>248</v>
-      </c>
-      <c r="E63" s="10" t="s">
+    <row r="63" s="17" customFormat="1" ht="17" spans="1:18">
+      <c r="A63" s="11"/>
+      <c r="B63" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="C63" s="11" t="s">
+        <v>250</v>
+      </c>
+      <c r="D63" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="E63" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="F63" s="10" t="s">
-        <v>249</v>
-      </c>
-      <c r="G63" s="10">
+      <c r="F63" s="11" t="s">
+        <v>252</v>
+      </c>
+      <c r="G63" s="11">
         <v>-0.2</v>
       </c>
-      <c r="H63" s="10"/>
-      <c r="I63" s="10">
+      <c r="H63" s="11"/>
+      <c r="I63" s="11">
         <v>300</v>
       </c>
-      <c r="J63" s="10" t="s">
+      <c r="J63" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="K63" s="10">
-        <v>0</v>
-      </c>
-      <c r="L63" s="10">
-        <v>0</v>
-      </c>
-      <c r="M63" s="10">
-        <v>0</v>
-      </c>
-      <c r="N63" s="10">
-        <v>0</v>
-      </c>
-      <c r="O63" s="10">
-        <v>0</v>
-      </c>
-      <c r="P63" s="10">
-        <v>0</v>
-      </c>
-      <c r="R63" s="8">
+      <c r="K63" s="11">
+        <v>0</v>
+      </c>
+      <c r="L63" s="11">
+        <v>0</v>
+      </c>
+      <c r="M63" s="11">
+        <v>0</v>
+      </c>
+      <c r="N63" s="11">
+        <v>0</v>
+      </c>
+      <c r="O63" s="11">
+        <v>0</v>
+      </c>
+      <c r="P63" s="11">
+        <v>0</v>
+      </c>
+      <c r="R63" s="17">
         <f t="shared" si="3"/>
         <v>50</v>
       </c>
     </row>
     <row r="64" ht="17" spans="2:18">
       <c r="B64" s="1" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="D64" s="9" t="s">
-        <v>252</v>
+        <v>254</v>
+      </c>
+      <c r="D64" s="10" t="s">
+        <v>255</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>70</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G64" s="1">
         <v>0.2</v>
@@ -6472,19 +6481,19 @@
     </row>
     <row r="65" ht="17" spans="2:18">
       <c r="B65" s="1" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="D65" s="9" t="s">
-        <v>255</v>
+        <v>257</v>
+      </c>
+      <c r="D65" s="10" t="s">
+        <v>258</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>70</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G65" s="1">
         <v>0</v>
@@ -6518,131 +6527,121 @@
         <v>50</v>
       </c>
     </row>
-    <row r="66" s="8" customFormat="1" spans="1:18">
-      <c r="A66" s="10"/>
-      <c r="B66" s="10" t="s">
-        <v>256</v>
-      </c>
-      <c r="C66" s="10" t="s">
-        <v>257</v>
-      </c>
-      <c r="D66" s="10" t="s">
-        <v>258</v>
-      </c>
-      <c r="E66" s="10" t="s">
+    <row r="66" s="17" customFormat="1" spans="1:18">
+      <c r="A66" s="11"/>
+      <c r="B66" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="C66" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="D66" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="E66" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="F66" s="10" t="s">
-        <v>249</v>
-      </c>
-      <c r="G66" s="10">
+      <c r="F66" s="11" t="s">
+        <v>252</v>
+      </c>
+      <c r="G66" s="11">
         <v>1</v>
       </c>
-      <c r="H66" s="10"/>
-      <c r="I66" s="10">
+      <c r="H66" s="11"/>
+      <c r="I66" s="11">
         <v>300</v>
       </c>
-      <c r="J66" s="10" t="s">
+      <c r="J66" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="K66" s="10">
-        <v>0</v>
-      </c>
-      <c r="L66" s="10">
-        <v>0</v>
-      </c>
-      <c r="M66" s="10">
-        <v>0</v>
-      </c>
-      <c r="N66" s="10">
-        <v>0</v>
-      </c>
-      <c r="O66" s="10">
-        <v>0</v>
-      </c>
-      <c r="P66" s="10">
-        <v>0</v>
-      </c>
-      <c r="R66" s="8">
+      <c r="K66" s="11">
+        <v>0</v>
+      </c>
+      <c r="L66" s="11">
+        <v>0</v>
+      </c>
+      <c r="M66" s="11">
+        <v>0</v>
+      </c>
+      <c r="N66" s="11">
+        <v>0</v>
+      </c>
+      <c r="O66" s="11">
+        <v>0</v>
+      </c>
+      <c r="P66" s="11">
+        <v>0</v>
+      </c>
+      <c r="R66" s="17">
         <f t="shared" si="3"/>
         <v>50</v>
       </c>
     </row>
-    <row r="67" s="8" customFormat="1" spans="1:18">
-      <c r="A67" s="10"/>
-      <c r="B67" s="10" t="inlineStr">
-        <is>
-          <t>item_skip_reward_node</t>
-        </is>
-      </c>
-      <c r="C67" s="10" t="inlineStr">
-        <is>
-          <t>错失良机</t>
-        </is>
-      </c>
-      <c r="D67" s="10" t="s">
-        <v>259</v>
-      </c>
-      <c r="E67" s="10" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="F67" s="10" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="G67" s="10">
+    <row r="67" s="17" customFormat="1" spans="1:18">
+      <c r="A67" s="11"/>
+      <c r="B67" s="11" t="s">
+        <v>262</v>
+      </c>
+      <c r="C67" s="11" t="s">
+        <v>263</v>
+      </c>
+      <c r="D67" s="11" t="s">
+        <v>264</v>
+      </c>
+      <c r="E67" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="F67" s="11" t="s">
+        <v>252</v>
+      </c>
+      <c r="G67" s="11">
         <v>1</v>
       </c>
-      <c r="H67" s="10"/>
-      <c r="I67" s="10">
+      <c r="H67" s="11"/>
+      <c r="I67" s="11">
         <v>300</v>
       </c>
-      <c r="J67" s="10" t="inlineStr">
-        <is>
-          <t>10,80</t>
-        </is>
-      </c>
-      <c r="K67" s="10">
-        <v>0</v>
-      </c>
-      <c r="L67" s="10">
-        <v>0</v>
-      </c>
-      <c r="M67" s="10">
-        <v>0</v>
-      </c>
-      <c r="N67" s="10">
-        <v>0</v>
-      </c>
-      <c r="O67" s="10">
-        <v>0</v>
-      </c>
-      <c r="P67" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q67" s="10"/>
-      <c r="R67" s="8">
+      <c r="J67" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="K67" s="11">
+        <v>0</v>
+      </c>
+      <c r="L67" s="11">
+        <v>0</v>
+      </c>
+      <c r="M67" s="11">
+        <v>0</v>
+      </c>
+      <c r="N67" s="11">
+        <v>0</v>
+      </c>
+      <c r="O67" s="11">
+        <v>0</v>
+      </c>
+      <c r="P67" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q67" s="11"/>
+      <c r="R67" s="17">
         <v>50</v>
       </c>
     </row>
     <row r="68" spans="2:18">
       <c r="B68" s="1" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>70</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G68" s="1">
         <v>-1</v>
@@ -6678,19 +6677,19 @@
     </row>
     <row r="69" ht="17" spans="2:18">
       <c r="B69" s="1" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="D69" s="9" t="s">
-        <v>265</v>
+        <v>269</v>
+      </c>
+      <c r="D69" s="10" t="s">
+        <v>270</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>70</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G69" s="1">
         <v>0.2</v>
@@ -6726,19 +6725,19 @@
     </row>
     <row r="70" spans="2:18">
       <c r="B70" s="1" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="E70" s="1" t="s">
         <v>70</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G70" s="1">
         <v>0.15</v>
@@ -6774,19 +6773,19 @@
     </row>
     <row r="71" spans="2:18">
       <c r="B71" s="1" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>70</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G71" s="1">
         <v>0.15</v>
@@ -6820,192 +6819,170 @@
         <v>50</v>
       </c>
     </row>
-    <row r="72" s="8" customFormat="1" ht="34" spans="1:18">
-      <c r="A72" s="10"/>
-      <c r="B72" s="10" t="s">
-        <v>272</v>
-      </c>
-      <c r="C72" s="10" t="s">
-        <v>273</v>
-      </c>
-      <c r="D72" s="12" t="s">
-        <v>274</v>
-      </c>
-      <c r="E72" s="10" t="s">
+    <row r="72" s="17" customFormat="1" ht="34" spans="1:18">
+      <c r="A72" s="11"/>
+      <c r="B72" s="11" t="s">
+        <v>277</v>
+      </c>
+      <c r="C72" s="11" t="s">
+        <v>278</v>
+      </c>
+      <c r="D72" s="13" t="s">
+        <v>279</v>
+      </c>
+      <c r="E72" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="F72" s="10" t="s">
-        <v>249</v>
-      </c>
-      <c r="G72" s="10">
-        <v>0</v>
-      </c>
-      <c r="H72" s="10"/>
-      <c r="I72" s="10">
+      <c r="F72" s="11" t="s">
+        <v>252</v>
+      </c>
+      <c r="G72" s="11">
+        <v>0</v>
+      </c>
+      <c r="H72" s="11"/>
+      <c r="I72" s="11">
         <v>300</v>
       </c>
-      <c r="J72" s="10" t="s">
+      <c r="J72" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="K72" s="10">
-        <v>0</v>
-      </c>
-      <c r="L72" s="10">
-        <v>0</v>
-      </c>
-      <c r="M72" s="10">
-        <v>0</v>
-      </c>
-      <c r="N72" s="10">
-        <v>0</v>
-      </c>
-      <c r="O72" s="10">
-        <v>0</v>
-      </c>
-      <c r="P72" s="10">
-        <v>0</v>
-      </c>
-      <c r="R72" s="8">
+      <c r="K72" s="11">
+        <v>0</v>
+      </c>
+      <c r="L72" s="11">
+        <v>0</v>
+      </c>
+      <c r="M72" s="11">
+        <v>0</v>
+      </c>
+      <c r="N72" s="11">
+        <v>0</v>
+      </c>
+      <c r="O72" s="11">
+        <v>0</v>
+      </c>
+      <c r="P72" s="11">
+        <v>0</v>
+      </c>
+      <c r="R72" s="17">
         <f>VLOOKUP(E72,$T$10:$AB$17,9,FALSE)</f>
         <v>50</v>
       </c>
     </row>
-    <row r="73" s="8" customFormat="1" ht="34" spans="1:18">
-      <c r="A73" s="10"/>
-      <c r="B73" s="10" t="inlineStr">
-        <is>
-          <t>item_double_daily_cost_repeat_node</t>
-        </is>
-      </c>
-      <c r="C73" s="10" t="inlineStr">
-        <is>
-          <t>时间透支</t>
-        </is>
-      </c>
-      <c r="D73" s="12" t="s">
-        <v>275</v>
-      </c>
-      <c r="E73" s="10" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="F73" s="10" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="G73" s="10">
+    <row r="73" s="17" customFormat="1" ht="34" spans="1:18">
+      <c r="A73" s="11"/>
+      <c r="B73" s="11" t="s">
+        <v>280</v>
+      </c>
+      <c r="C73" s="11" t="s">
+        <v>281</v>
+      </c>
+      <c r="D73" s="13" t="s">
+        <v>282</v>
+      </c>
+      <c r="E73" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="F73" s="11" t="s">
+        <v>252</v>
+      </c>
+      <c r="G73" s="11">
         <v>2</v>
       </c>
-      <c r="H73" s="10" t="inlineStr">
-        <is>
-          <t>repeat:2</t>
-        </is>
-      </c>
-      <c r="I73" s="10">
+      <c r="H73" s="11" t="s">
+        <v>283</v>
+      </c>
+      <c r="I73" s="11">
         <v>300</v>
       </c>
-      <c r="J73" s="10" t="inlineStr">
-        <is>
-          <t>10,80</t>
-        </is>
-      </c>
-      <c r="K73" s="10">
-        <v>0</v>
-      </c>
-      <c r="L73" s="10">
-        <v>0</v>
-      </c>
-      <c r="M73" s="10">
-        <v>0</v>
-      </c>
-      <c r="N73" s="10">
-        <v>0</v>
-      </c>
-      <c r="O73" s="10">
-        <v>0</v>
-      </c>
-      <c r="P73" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q73" s="10"/>
-      <c r="R73" s="8">
+      <c r="J73" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="K73" s="11">
+        <v>0</v>
+      </c>
+      <c r="L73" s="11">
+        <v>0</v>
+      </c>
+      <c r="M73" s="11">
+        <v>0</v>
+      </c>
+      <c r="N73" s="11">
+        <v>0</v>
+      </c>
+      <c r="O73" s="11">
+        <v>0</v>
+      </c>
+      <c r="P73" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="11"/>
+      <c r="R73" s="17">
         <v>50</v>
       </c>
     </row>
-    <row r="74" s="8" customFormat="1" ht="34" spans="1:18">
-      <c r="A74" s="10"/>
-      <c r="B74" s="10" t="inlineStr">
-        <is>
-          <t>item_timeline_stop_chance</t>
-        </is>
-      </c>
-      <c r="C74" s="10" t="inlineStr">
-        <is>
-          <t>时间停摆</t>
-        </is>
-      </c>
-      <c r="D74" s="12" t="s">
-        <v>276</v>
-      </c>
-      <c r="E74" s="10" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="F74" s="10" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G74" s="10">
+    <row r="74" s="17" customFormat="1" ht="34" spans="1:18">
+      <c r="A74" s="11"/>
+      <c r="B74" s="11" t="s">
+        <v>284</v>
+      </c>
+      <c r="C74" s="11" t="s">
+        <v>285</v>
+      </c>
+      <c r="D74" s="13" t="s">
+        <v>286</v>
+      </c>
+      <c r="E74" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="F74" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="G74" s="11">
         <v>0.3</v>
       </c>
-      <c r="H74" s="10"/>
-      <c r="I74" s="10">
+      <c r="H74" s="11"/>
+      <c r="I74" s="11">
         <v>100</v>
       </c>
-      <c r="J74" s="10" t="inlineStr">
-        <is>
-          <t>20,80</t>
-        </is>
-      </c>
-      <c r="K74" s="10">
-        <v>0</v>
-      </c>
-      <c r="L74" s="10">
-        <v>0</v>
-      </c>
-      <c r="M74" s="10">
-        <v>0</v>
-      </c>
-      <c r="N74" s="10">
-        <v>0</v>
-      </c>
-      <c r="O74" s="10">
-        <v>0</v>
-      </c>
-      <c r="P74" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q74" s="10"/>
-      <c r="R74" s="8">
+      <c r="J74" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="K74" s="11">
+        <v>0</v>
+      </c>
+      <c r="L74" s="11">
+        <v>0</v>
+      </c>
+      <c r="M74" s="11">
+        <v>0</v>
+      </c>
+      <c r="N74" s="11">
+        <v>0</v>
+      </c>
+      <c r="O74" s="11">
+        <v>0</v>
+      </c>
+      <c r="P74" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="11"/>
+      <c r="R74" s="17">
         <v>80</v>
       </c>
     </row>
     <row r="75" spans="2:18">
       <c r="B75" s="1" t="s">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>49</v>
@@ -7038,22 +7015,22 @@
         <v>0</v>
       </c>
       <c r="R75">
-        <f t="shared" ref="R75:R90" si="4">VLOOKUP(E75,$T$10:$AB$17,9,FALSE)</f>
+        <f t="shared" ref="R75:R84" si="4">VLOOKUP(E75,$T$10:$AB$17,9,FALSE)</f>
         <v>200</v>
       </c>
     </row>
     <row r="76" ht="34" spans="2:18">
       <c r="B76" s="1" t="s">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="D76" s="9" t="s">
-        <v>282</v>
+        <v>291</v>
+      </c>
+      <c r="D76" s="10" t="s">
+        <v>292</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>49</v>
@@ -7086,7 +7063,7 @@
         <v>0</v>
       </c>
       <c r="Q76" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="R76">
         <f t="shared" si="4"/>
@@ -7095,16 +7072,16 @@
     </row>
     <row r="77" ht="34" spans="2:18">
       <c r="B77" s="1" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="D77" s="9" t="s">
-        <v>286</v>
+        <v>295</v>
+      </c>
+      <c r="D77" s="10" t="s">
+        <v>296</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>49</v>
@@ -7137,7 +7114,7 @@
         <v>0</v>
       </c>
       <c r="Q77" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="R77">
         <f t="shared" si="4"/>
@@ -7146,13 +7123,13 @@
     </row>
     <row r="78" ht="34" spans="2:18">
       <c r="B78" s="1" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="D78" s="9" t="s">
-        <v>289</v>
+        <v>298</v>
+      </c>
+      <c r="D78" s="10" t="s">
+        <v>299</v>
       </c>
       <c r="E78" s="1" t="s">
         <v>48</v>
@@ -7188,7 +7165,7 @@
         <v>0</v>
       </c>
       <c r="Q78" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="R78">
         <f t="shared" si="4"/>
@@ -7197,13 +7174,13 @@
     </row>
     <row r="79" ht="34" spans="2:18">
       <c r="B79" s="1" t="s">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="D79" s="9" t="s">
-        <v>292</v>
+        <v>301</v>
+      </c>
+      <c r="D79" s="10" t="s">
+        <v>302</v>
       </c>
       <c r="E79" s="1" t="s">
         <v>48</v>
@@ -7215,7 +7192,7 @@
         <v>10</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="I79" s="1">
         <v>100</v>
@@ -7242,7 +7219,7 @@
         <v>0</v>
       </c>
       <c r="Q79" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="R79">
         <f t="shared" si="4"/>
@@ -7251,16 +7228,16 @@
     </row>
     <row r="80" ht="34" spans="2:18">
       <c r="B80" s="1" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="D80" s="9" t="s">
-        <v>296</v>
+        <v>305</v>
+      </c>
+      <c r="D80" s="10" t="s">
+        <v>306</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>49</v>
@@ -7293,7 +7270,7 @@
         <v>0</v>
       </c>
       <c r="Q80" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="R80">
         <f t="shared" si="4"/>
@@ -7302,13 +7279,13 @@
     </row>
     <row r="81" ht="34" spans="2:18">
       <c r="B81" s="1" t="s">
-        <v>298</v>
+        <v>308</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="D81" s="9" t="s">
-        <v>300</v>
+        <v>309</v>
+      </c>
+      <c r="D81" s="10" t="s">
+        <v>310</v>
       </c>
       <c r="E81" s="1" t="s">
         <v>48</v>
@@ -7344,7 +7321,7 @@
         <v>0</v>
       </c>
       <c r="Q81" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="R81">
         <f t="shared" si="4"/>
@@ -7353,13 +7330,13 @@
     </row>
     <row r="82" ht="34" spans="2:18">
       <c r="B82" s="1" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="D82" s="9" t="s">
-        <v>303</v>
+        <v>312</v>
+      </c>
+      <c r="D82" s="10" t="s">
+        <v>313</v>
       </c>
       <c r="E82" s="1" t="s">
         <v>61</v>
@@ -7395,7 +7372,7 @@
         <v>0</v>
       </c>
       <c r="Q82" s="1" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="R82">
         <f t="shared" si="4"/>
@@ -7404,13 +7381,13 @@
     </row>
     <row r="83" ht="34" spans="2:18">
       <c r="B83" s="1" t="s">
-        <v>304</v>
+        <v>314</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="D83" s="9" t="s">
-        <v>306</v>
+        <v>315</v>
+      </c>
+      <c r="D83" s="10" t="s">
+        <v>316</v>
       </c>
       <c r="E83" s="1" t="s">
         <v>48</v>
@@ -7422,7 +7399,7 @@
         <v>10</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="I83" s="1">
         <v>100</v>
@@ -7449,7 +7426,7 @@
         <v>0</v>
       </c>
       <c r="Q83" s="1" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="R83">
         <f t="shared" si="4"/>
@@ -7458,13 +7435,13 @@
     </row>
     <row r="84" ht="17" spans="2:18">
       <c r="B84" s="1" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="D84" s="9" t="s">
-        <v>310</v>
+        <v>319</v>
+      </c>
+      <c r="D84" s="10" t="s">
+        <v>320</v>
       </c>
       <c r="E84" s="1" t="s">
         <v>48</v>
@@ -7500,7 +7477,7 @@
         <v>0</v>
       </c>
       <c r="Q84" s="1" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="R84">
         <f t="shared" si="4"/>
@@ -7516,7 +7493,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M41"/>
+  <dimension ref="A1:N41"/>
   <sheetFormatPr defaultColWidth="9.00735294117647" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="13.0808823529412" style="1" customWidth="1"/>
@@ -7530,10 +7507,13 @@
     <col min="9" max="9" width="15.1617647058824" style="1" customWidth="1"/>
     <col min="10" max="10" width="46.1470588235294" style="1" customWidth="1"/>
     <col min="11" max="11" width="36.1617647058824" style="1" customWidth="1"/>
-    <col min="12" max="12" width="26.4632352941176" customWidth="1"/>
+    <col min="12" max="12" width="26.4632352941176" style="9" customWidth="1"/>
+    <col min="13" max="13" width="11.4705882352941" style="9" customWidth="1"/>
+    <col min="14" max="14" width="18" style="9" customWidth="1"/>
+    <col min="15" max="16384" width="9.00735294117647" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" customHeight="1" spans="1:13">
+    <row r="1" ht="16.5" customHeight="1" spans="1:14">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -7550,7 +7530,7 @@
         <v>5</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="G1" s="7" t="s">
         <v>6</v>
@@ -7562,19 +7542,22 @@
         <v>8</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="L1" s="13" t="s">
+        <v>323</v>
+      </c>
+      <c r="L1" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="9" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="2" ht="16.5" customHeight="1" spans="1:13">
+      <c r="N1" s="9" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="2" ht="16.5" customHeight="1" spans="1:14">
       <c r="A2" s="7" t="s">
         <v>18</v>
       </c>
@@ -7591,7 +7574,7 @@
         <v>23</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>314</v>
+        <v>325</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>24</v>
@@ -7603,19 +7586,22 @@
         <v>26</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="L2" t="s">
+        <v>327</v>
+      </c>
+      <c r="L2" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="M2" t="s">
+      <c r="M2" s="9" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="3" ht="16.5" customHeight="1" spans="1:13">
+      <c r="N2" s="9" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="3" ht="16.5" customHeight="1" spans="1:14">
       <c r="A3" s="7" t="s">
         <v>37</v>
       </c>
@@ -7644,891 +7630,889 @@
         <v>41</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="K3" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L3" s="13" t="s">
+      <c r="L3" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="M3" t="s">
+      <c r="M3" s="9" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="4" ht="33.75" customHeight="1" spans="2:13">
+      <c r="N3" s="9" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="4" ht="33.75" customHeight="1" spans="2:14">
       <c r="B4" s="7" t="s">
-        <v>318</v>
+        <v>331</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>319</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>320</v>
+        <v>332</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>333</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>321</v>
+        <v>334</v>
       </c>
       <c r="G4" s="1">
         <v>0</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>322</v>
+        <v>335</v>
       </c>
       <c r="I4" s="1">
         <v>1</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
       <c r="K4" s="1">
         <v>1</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>322</v>
-      </c>
-      <c r="M4">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="5" ht="33.75" customHeight="1" spans="2:13">
+        <v>335</v>
+      </c>
+      <c r="M4" s="9">
+        <v>50</v>
+      </c>
+      <c r="N4" s="9" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="5" ht="33.75" customHeight="1" spans="2:14">
       <c r="B5" s="7" t="s">
-        <v>324</v>
+        <v>338</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>326</v>
+        <v>339</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>340</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>321</v>
+        <v>334</v>
       </c>
       <c r="G5" s="1">
         <v>0</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="I5" s="1">
         <v>1</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
       <c r="K5" s="1">
         <v>1</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>327</v>
-      </c>
-      <c r="M5">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" ht="33.75" customHeight="1" spans="2:13">
+        <v>341</v>
+      </c>
+      <c r="M5" s="9">
+        <v>50</v>
+      </c>
+      <c r="N5" s="9" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="6" ht="33.75" customHeight="1" spans="2:14">
       <c r="B6" s="7" t="s">
-        <v>328</v>
+        <v>342</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>330</v>
+        <v>343</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>344</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>321</v>
+        <v>334</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>331</v>
+        <v>345</v>
       </c>
       <c r="I6" s="1">
         <v>1</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
       <c r="K6" s="1">
         <v>1</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>331</v>
-      </c>
-      <c r="M6">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" ht="33.75" customHeight="1" spans="2:13">
+        <v>345</v>
+      </c>
+      <c r="M6" s="9">
+        <v>50</v>
+      </c>
+      <c r="N6" s="9" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="7" ht="33.75" customHeight="1" spans="2:14">
       <c r="B7" s="7" t="s">
-        <v>332</v>
+        <v>346</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="D7" s="9" t="s">
+        <v>347</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>348</v>
+      </c>
+      <c r="F7" s="7" t="s">
         <v>334</v>
       </c>
-      <c r="F7" s="7" t="s">
-        <v>321</v>
-      </c>
       <c r="G7" s="1">
         <v>0</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>335</v>
+        <v>349</v>
       </c>
       <c r="I7" s="1">
         <v>1</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
       <c r="K7" s="1">
         <v>1</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>335</v>
-      </c>
-      <c r="M7">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="8" ht="33.75" customHeight="1" spans="2:13">
+        <v>349</v>
+      </c>
+      <c r="M7" s="9">
+        <v>50</v>
+      </c>
+      <c r="N7" s="9" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="8" ht="33.75" customHeight="1" spans="2:14">
       <c r="B8" s="7" t="s">
-        <v>336</v>
+        <v>350</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>338</v>
+        <v>351</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>352</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>321</v>
+        <v>334</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>339</v>
+        <v>353</v>
       </c>
       <c r="I8" s="1">
         <v>1</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
       <c r="K8" s="1">
         <v>1</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>339</v>
-      </c>
-      <c r="M8">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9" ht="33.75" customHeight="1" spans="2:13">
+        <v>353</v>
+      </c>
+      <c r="M8" s="9">
+        <v>50</v>
+      </c>
+      <c r="N8" s="9" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="9" ht="33.75" customHeight="1" spans="2:14">
       <c r="B9" s="7" t="s">
-        <v>340</v>
+        <v>354</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>342</v>
+        <v>355</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>356</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>321</v>
+        <v>334</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>343</v>
+        <v>357</v>
       </c>
       <c r="I9" s="1">
         <v>1</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
       <c r="K9" s="1">
         <v>1</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>343</v>
-      </c>
-      <c r="M9">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="10" ht="33.75" customHeight="1" spans="2:13">
+        <v>357</v>
+      </c>
+      <c r="M9" s="9">
+        <v>50</v>
+      </c>
+      <c r="N9" s="9" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="10" ht="33.75" customHeight="1" spans="2:14">
       <c r="B10" s="7" t="s">
-        <v>344</v>
+        <v>358</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>346</v>
+        <v>359</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>360</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>348</v>
+        <v>362</v>
       </c>
       <c r="I10" s="1">
         <v>1</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>349</v>
+        <v>363</v>
       </c>
       <c r="K10" s="1">
         <v>1</v>
       </c>
       <c r="L10" s="7" t="s">
-        <v>348</v>
-      </c>
-      <c r="M10">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="11" ht="33.75" customHeight="1" spans="2:13">
+        <v>362</v>
+      </c>
+      <c r="M10" s="9">
+        <v>50</v>
+      </c>
+      <c r="N10" s="9" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="11" ht="33.75" customHeight="1" spans="2:14">
       <c r="B11" s="7" t="s">
-        <v>350</v>
+        <v>364</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>352</v>
+        <v>365</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>366</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
       <c r="G11" s="1">
         <v>0</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>353</v>
+        <v>367</v>
       </c>
       <c r="I11" s="1">
         <v>1</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>349</v>
+        <v>363</v>
       </c>
       <c r="K11" s="1">
         <v>1</v>
       </c>
       <c r="L11" s="7" t="s">
-        <v>353</v>
-      </c>
-      <c r="M11">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="12" ht="33.75" customHeight="1" spans="2:13">
+        <v>367</v>
+      </c>
+      <c r="M11" s="9">
+        <v>50</v>
+      </c>
+      <c r="N11" s="9" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="12" ht="33.75" customHeight="1" spans="2:14">
       <c r="B12" s="7" t="s">
-        <v>354</v>
+        <v>368</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>356</v>
+        <v>369</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>370</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>357</v>
+        <v>371</v>
       </c>
       <c r="I12" s="1">
         <v>1</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>349</v>
+        <v>363</v>
       </c>
       <c r="K12" s="1">
         <v>1</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>357</v>
-      </c>
-      <c r="M12">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="13" ht="33.75" customHeight="1" spans="2:13">
+        <v>371</v>
+      </c>
+      <c r="M12" s="9">
+        <v>50</v>
+      </c>
+      <c r="N12" s="9" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="13" ht="33.75" customHeight="1" spans="2:14">
       <c r="B13" s="7" t="s">
-        <v>358</v>
+        <v>372</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>360</v>
+        <v>373</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>374</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
       <c r="G13" s="1">
         <v>0</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="I13" s="1">
         <v>1</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>349</v>
+        <v>363</v>
       </c>
       <c r="K13" s="1">
         <v>1</v>
       </c>
       <c r="L13" s="7" t="s">
+        <v>375</v>
+      </c>
+      <c r="M13" s="9">
+        <v>50</v>
+      </c>
+      <c r="N13" s="9" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="14" ht="33.75" customHeight="1" spans="2:14">
+      <c r="B14" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>378</v>
+      </c>
+      <c r="F14" s="7" t="s">
         <v>361</v>
       </c>
-      <c r="M13">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="14" ht="33.75" customHeight="1" spans="2:13">
-      <c r="B14" s="7" t="s">
-        <v>362</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>364</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>347</v>
-      </c>
       <c r="G14" s="1">
         <v>0</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>365</v>
+        <v>379</v>
       </c>
       <c r="I14" s="1">
         <v>1</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>349</v>
+        <v>363</v>
       </c>
       <c r="K14" s="1">
         <v>1</v>
       </c>
       <c r="L14" s="7" t="s">
-        <v>365</v>
-      </c>
-      <c r="M14">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="15" ht="33.75" customHeight="1" spans="2:13">
+        <v>379</v>
+      </c>
+      <c r="M14" s="9">
+        <v>50</v>
+      </c>
+      <c r="N14" s="9" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="15" ht="33.75" customHeight="1" spans="2:14">
       <c r="B15" s="7" t="s">
-        <v>366</v>
+        <v>380</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>368</v>
+        <v>381</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>382</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
       <c r="G15" s="1">
         <v>0</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>369</v>
+        <v>383</v>
       </c>
       <c r="I15" s="1">
         <v>1</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>349</v>
+        <v>363</v>
       </c>
       <c r="K15" s="1">
         <v>1</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>369</v>
-      </c>
-      <c r="M15">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="16" ht="33.75" customHeight="1" spans="2:13">
+        <v>383</v>
+      </c>
+      <c r="M15" s="9">
+        <v>50</v>
+      </c>
+      <c r="N15" s="9" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="16" ht="33.75" customHeight="1" spans="2:14">
       <c r="B16" s="7" t="s">
-        <v>370</v>
+        <v>384</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>371</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>372</v>
+        <v>385</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>386</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
       <c r="G16" s="1">
         <v>0</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="I16" s="1">
         <v>1</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>349</v>
+        <v>363</v>
       </c>
       <c r="K16" s="1">
         <v>1</v>
       </c>
       <c r="L16" s="7" t="s">
-        <v>373</v>
-      </c>
-      <c r="M16">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="17" s="8" customFormat="1" ht="33.75" customHeight="1" spans="1:13">
-      <c r="A17" s="10" t="s">
-        <v>374</v>
-      </c>
-      <c r="B17" s="11" t="s">
-        <v>375</v>
-      </c>
-      <c r="C17" s="10" t="s">
-        <v>376</v>
-      </c>
-      <c r="D17" s="12" t="s">
-        <v>377</v>
-      </c>
-      <c r="E17" s="10" t="s">
-        <v>374</v>
-      </c>
-      <c r="F17" s="10" t="s">
-        <v>378</v>
-      </c>
-      <c r="G17" s="10">
-        <v>0</v>
-      </c>
-      <c r="H17" s="10" t="s">
-        <v>374</v>
-      </c>
-      <c r="I17" s="10">
+        <v>387</v>
+      </c>
+      <c r="M16" s="9">
+        <v>50</v>
+      </c>
+      <c r="N16" s="9" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="17" s="8" customFormat="1" ht="17" spans="1:14">
+      <c r="A17" s="11"/>
+      <c r="B17" s="12" t="s">
+        <v>388</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>389</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>390</v>
+      </c>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11" t="s">
+        <v>391</v>
+      </c>
+      <c r="G17" s="11">
+        <v>0</v>
+      </c>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11">
         <v>1</v>
       </c>
-      <c r="J17" s="10" t="s">
-        <v>379</v>
-      </c>
-      <c r="K17" s="10">
-        <v>0</v>
-      </c>
-      <c r="L17" t="s">
-        <v>374</v>
-      </c>
+      <c r="J17" s="11" t="s">
+        <v>392</v>
+      </c>
+      <c r="K17" s="11">
+        <v>0</v>
+      </c>
+      <c r="L17" s="9"/>
       <c r="M17" s="8">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="18" s="8" customFormat="1" ht="16.5" customHeight="1" spans="1:13">
-      <c r="A18" s="10" t="s">
-        <v>374</v>
-      </c>
-      <c r="B18" s="11" t="s">
-        <v>380</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>381</v>
-      </c>
-      <c r="D18" s="10" t="s">
-        <v>382</v>
-      </c>
-      <c r="E18" s="10" t="s">
-        <v>374</v>
-      </c>
-      <c r="F18" s="10" t="s">
-        <v>383</v>
-      </c>
-      <c r="G18" s="10">
+        <v>50</v>
+      </c>
+      <c r="N17" s="9" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="18" s="8" customFormat="1" ht="16.5" customHeight="1" spans="1:14">
+      <c r="A18" s="11"/>
+      <c r="B18" s="12" t="s">
+        <v>394</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>395</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>396</v>
+      </c>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11" t="s">
+        <v>397</v>
+      </c>
+      <c r="G18" s="11">
         <v>0.5</v>
       </c>
-      <c r="H18" s="10" t="s">
-        <v>374</v>
-      </c>
-      <c r="I18" s="10">
+      <c r="H18" s="11"/>
+      <c r="I18" s="11">
         <v>1</v>
       </c>
-      <c r="J18" s="10" t="s">
-        <v>379</v>
-      </c>
-      <c r="K18" s="10">
-        <v>0</v>
-      </c>
-      <c r="L18" t="s">
-        <v>374</v>
-      </c>
+      <c r="J18" s="11" t="s">
+        <v>392</v>
+      </c>
+      <c r="K18" s="11">
+        <v>0</v>
+      </c>
+      <c r="L18" s="9"/>
       <c r="M18" s="8">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="19" s="8" customFormat="1" ht="16.5" customHeight="1" spans="1:13">
-      <c r="A19" s="10" t="s">
-        <v>374</v>
-      </c>
-      <c r="B19" s="11" t="s">
-        <v>384</v>
-      </c>
-      <c r="C19" s="10" t="s">
-        <v>385</v>
-      </c>
-      <c r="D19" s="10" t="s">
-        <v>386</v>
-      </c>
-      <c r="E19" s="10" t="s">
-        <v>374</v>
-      </c>
-      <c r="F19" s="10" t="s">
-        <v>387</v>
-      </c>
-      <c r="G19" s="10">
-        <v>0</v>
-      </c>
-      <c r="H19" s="10" t="s">
-        <v>374</v>
-      </c>
-      <c r="I19" s="10">
+        <v>50</v>
+      </c>
+      <c r="N18" s="9" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="19" s="8" customFormat="1" ht="16.5" customHeight="1" spans="1:14">
+      <c r="A19" s="11"/>
+      <c r="B19" s="12" t="s">
+        <v>398</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>399</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>400</v>
+      </c>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11" t="s">
+        <v>401</v>
+      </c>
+      <c r="G19" s="11">
+        <v>0</v>
+      </c>
+      <c r="H19" s="11"/>
+      <c r="I19" s="11">
         <v>1</v>
       </c>
-      <c r="J19" s="10" t="s">
-        <v>379</v>
-      </c>
-      <c r="K19" s="10">
-        <v>0</v>
-      </c>
-      <c r="L19" t="s">
-        <v>374</v>
-      </c>
+      <c r="J19" s="11" t="s">
+        <v>392</v>
+      </c>
+      <c r="K19" s="11">
+        <v>0</v>
+      </c>
+      <c r="L19" s="9"/>
       <c r="M19" s="8">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="20" s="8" customFormat="1" ht="16.5" customHeight="1" spans="1:13">
-      <c r="A20" s="10" t="s">
-        <v>374</v>
-      </c>
-      <c r="B20" s="11" t="s">
-        <v>388</v>
-      </c>
-      <c r="C20" s="10" t="s">
-        <v>389</v>
-      </c>
-      <c r="D20" s="10" t="s">
-        <v>390</v>
-      </c>
-      <c r="E20" s="10" t="s">
-        <v>374</v>
-      </c>
-      <c r="F20" s="10" t="s">
-        <v>391</v>
-      </c>
-      <c r="G20" s="10">
-        <v>0</v>
-      </c>
-      <c r="H20" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="N19" s="9" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="20" s="8" customFormat="1" ht="16.5" customHeight="1" spans="1:14">
+      <c r="A20" s="11"/>
+      <c r="B20" s="12" t="s">
+        <v>402</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>403</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>404</v>
+      </c>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11" t="s">
+        <v>405</v>
+      </c>
+      <c r="G20" s="11">
+        <v>0</v>
+      </c>
+      <c r="H20" s="11" t="s">
+        <v>406</v>
+      </c>
+      <c r="I20" s="11">
+        <v>1</v>
+      </c>
+      <c r="J20" s="11" t="s">
         <v>392</v>
       </c>
-      <c r="I20" s="10">
+      <c r="K20" s="11">
         <v>1</v>
       </c>
-      <c r="J20" s="10" t="s">
-        <v>379</v>
-      </c>
-      <c r="K20" s="10">
+      <c r="L20" s="9"/>
+      <c r="M20" s="8">
+        <v>50</v>
+      </c>
+      <c r="N20" s="9" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="21" s="8" customFormat="1" spans="1:14">
+      <c r="A21" s="11"/>
+      <c r="B21" s="11" t="s">
+        <v>407</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>408</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>409</v>
+      </c>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11" t="s">
+        <v>410</v>
+      </c>
+      <c r="G21" s="11">
+        <v>0</v>
+      </c>
+      <c r="H21" s="11" t="s">
+        <v>411</v>
+      </c>
+      <c r="I21" s="11">
         <v>1</v>
       </c>
-      <c r="L20" t="s">
-        <v>374</v>
-      </c>
-      <c r="M20" s="8">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="21" s="8" customFormat="1" spans="1:13">
-      <c r="A21" s="10" t="s">
-        <v>374</v>
-      </c>
-      <c r="B21" s="10" t="s">
+      <c r="J21" s="11" t="s">
+        <v>392</v>
+      </c>
+      <c r="K21" s="11">
+        <v>1</v>
+      </c>
+      <c r="L21" s="9"/>
+      <c r="M21" s="9">
+        <v>50</v>
+      </c>
+      <c r="N21" s="9" t="s">
         <v>393</v>
       </c>
-      <c r="C21" s="10" t="s">
-        <v>394</v>
-      </c>
-      <c r="D21" s="10" t="s">
-        <v>395</v>
-      </c>
-      <c r="E21" s="10" t="s">
-        <v>374</v>
-      </c>
-      <c r="F21" s="10" t="s">
-        <v>396</v>
-      </c>
-      <c r="G21" s="10">
-        <v>0</v>
-      </c>
-      <c r="H21" s="10" t="s">
-        <v>397</v>
-      </c>
-      <c r="I21" s="10">
+    </row>
+    <row r="22" s="8" customFormat="1" spans="1:14">
+      <c r="A22" s="11"/>
+      <c r="B22" s="11" t="s">
+        <v>412</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>413</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>414</v>
+      </c>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11" t="s">
+        <v>415</v>
+      </c>
+      <c r="G22" s="11">
+        <v>0</v>
+      </c>
+      <c r="H22" s="11" t="s">
+        <v>416</v>
+      </c>
+      <c r="I22" s="11">
         <v>1</v>
       </c>
-      <c r="J21" s="10" t="s">
-        <v>379</v>
-      </c>
-      <c r="K21" s="10">
+      <c r="J22" s="11" t="s">
+        <v>392</v>
+      </c>
+      <c r="K22" s="11">
         <v>1</v>
       </c>
-      <c r="L21" t="s">
-        <v>374</v>
-      </c>
-      <c r="M21">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="22" s="8" customFormat="1" spans="1:13">
-      <c r="A22" s="10" t="s">
-        <v>374</v>
-      </c>
-      <c r="B22" s="10" t="s">
-        <v>398</v>
-      </c>
-      <c r="C22" s="10" t="s">
-        <v>399</v>
-      </c>
-      <c r="D22" s="10" t="s">
-        <v>400</v>
-      </c>
-      <c r="E22" s="10" t="s">
-        <v>374</v>
-      </c>
-      <c r="F22" s="10" t="s">
-        <v>401</v>
-      </c>
-      <c r="G22" s="10">
-        <v>0</v>
-      </c>
-      <c r="H22" s="10" t="s">
-        <v>402</v>
-      </c>
-      <c r="I22" s="10">
+      <c r="L22" s="9"/>
+      <c r="M22" s="9">
+        <v>50</v>
+      </c>
+      <c r="N22" s="9" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="23" s="8" customFormat="1" spans="1:14">
+      <c r="A23" s="11"/>
+      <c r="B23" s="11" t="s">
+        <v>417</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>418</v>
+      </c>
+      <c r="D23" s="11" t="s">
+        <v>419</v>
+      </c>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11" t="s">
+        <v>420</v>
+      </c>
+      <c r="G23" s="11">
+        <v>0</v>
+      </c>
+      <c r="H23" s="11"/>
+      <c r="I23" s="11">
         <v>1</v>
       </c>
-      <c r="J22" s="10" t="s">
-        <v>379</v>
-      </c>
-      <c r="K22" s="10">
+      <c r="J23" s="11" t="s">
+        <v>392</v>
+      </c>
+      <c r="K23" s="11">
         <v>1</v>
       </c>
-      <c r="L22" t="s">
-        <v>374</v>
-      </c>
-      <c r="M22">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="23" s="8" customFormat="1" spans="1:13">
-      <c r="A23" s="10" t="s">
-        <v>374</v>
-      </c>
-      <c r="B23" s="10" t="s">
-        <v>403</v>
-      </c>
-      <c r="C23" s="10" t="s">
-        <v>404</v>
-      </c>
-      <c r="D23" s="10" t="s">
-        <v>405</v>
-      </c>
-      <c r="E23" s="10" t="s">
-        <v>374</v>
-      </c>
-      <c r="F23" s="10" t="s">
-        <v>406</v>
-      </c>
-      <c r="G23" s="10">
-        <v>0</v>
-      </c>
-      <c r="H23" s="10" t="s">
-        <v>374</v>
-      </c>
-      <c r="I23" s="10">
+      <c r="L23" s="9"/>
+      <c r="M23" s="9">
+        <v>50</v>
+      </c>
+      <c r="N23" s="9" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="24" s="8" customFormat="1" spans="1:14">
+      <c r="A24" s="11"/>
+      <c r="B24" s="11" t="s">
+        <v>421</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>422</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>423</v>
+      </c>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11" t="s">
+        <v>424</v>
+      </c>
+      <c r="G24" s="11">
+        <v>0</v>
+      </c>
+      <c r="H24" s="11"/>
+      <c r="I24" s="11">
         <v>1</v>
       </c>
-      <c r="J23" s="10" t="s">
-        <v>379</v>
-      </c>
-      <c r="K23" s="10">
+      <c r="J24" s="11" t="s">
+        <v>392</v>
+      </c>
+      <c r="K24" s="11">
         <v>1</v>
       </c>
-      <c r="L23" t="s">
-        <v>374</v>
-      </c>
-      <c r="M23">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="24" s="8" customFormat="1" spans="1:13">
-      <c r="A24" s="10" t="s">
-        <v>374</v>
-      </c>
-      <c r="B24" s="10" t="s">
-        <v>407</v>
-      </c>
-      <c r="C24" s="10" t="s">
-        <v>408</v>
-      </c>
-      <c r="D24" s="10" t="s">
-        <v>409</v>
-      </c>
-      <c r="E24" s="10" t="s">
-        <v>374</v>
-      </c>
-      <c r="F24" s="10" t="s">
-        <v>410</v>
-      </c>
-      <c r="G24" s="10">
-        <v>0</v>
-      </c>
-      <c r="H24" s="10" t="s">
-        <v>374</v>
-      </c>
-      <c r="I24" s="10">
+      <c r="L24" s="9"/>
+      <c r="M24" s="9">
+        <v>50</v>
+      </c>
+      <c r="N24" s="9" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="25" s="8" customFormat="1" ht="34" spans="1:14">
+      <c r="A25" s="11"/>
+      <c r="B25" s="11" t="s">
+        <v>425</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>426</v>
+      </c>
+      <c r="D25" s="13" t="s">
+        <v>427</v>
+      </c>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11" t="s">
+        <v>428</v>
+      </c>
+      <c r="G25" s="11">
+        <v>0</v>
+      </c>
+      <c r="H25" s="11"/>
+      <c r="I25" s="11">
         <v>1</v>
       </c>
-      <c r="J24" s="10" t="s">
-        <v>379</v>
-      </c>
-      <c r="K24" s="10">
+      <c r="J25" s="11" t="s">
+        <v>392</v>
+      </c>
+      <c r="K25" s="11">
         <v>1</v>
       </c>
-      <c r="L24" t="s">
-        <v>374</v>
-      </c>
-      <c r="M24">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="25" s="8" customFormat="1" spans="1:13">
-      <c r="A25" s="10" t="s">
-        <v>374</v>
-      </c>
-      <c r="B25" s="10" t="s">
-        <v>411</v>
-      </c>
-      <c r="C25" s="10" t="s">
-        <v>412</v>
-      </c>
-      <c r="D25" s="10" t="s">
-        <v>413</v>
-      </c>
-      <c r="E25" s="10" t="s">
-        <v>374</v>
-      </c>
-      <c r="F25" s="10" t="s">
-        <v>414</v>
-      </c>
-      <c r="G25" s="10">
-        <v>0</v>
-      </c>
-      <c r="H25" s="10" t="s">
-        <v>374</v>
-      </c>
-      <c r="I25" s="10">
+      <c r="L25" s="9"/>
+      <c r="M25" s="9">
+        <v>50</v>
+      </c>
+      <c r="N25" s="9" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="26" s="8" customFormat="1" ht="34" spans="1:14">
+      <c r="A26" s="11"/>
+      <c r="B26" s="11" t="s">
+        <v>429</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>430</v>
+      </c>
+      <c r="D26" s="13" t="s">
+        <v>431</v>
+      </c>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11" t="s">
+        <v>432</v>
+      </c>
+      <c r="G26" s="11">
+        <v>0</v>
+      </c>
+      <c r="H26" s="11"/>
+      <c r="I26" s="11">
         <v>1</v>
       </c>
-      <c r="J25" s="10" t="s">
-        <v>379</v>
-      </c>
-      <c r="K25" s="10">
+      <c r="J26" s="11" t="s">
+        <v>392</v>
+      </c>
+      <c r="K26" s="11">
         <v>1</v>
       </c>
-      <c r="L25" t="s">
-        <v>374</v>
-      </c>
-      <c r="M25">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="26" s="8" customFormat="1" spans="1:13">
-      <c r="A26" s="10" t="s">
-        <v>374</v>
-      </c>
-      <c r="B26" s="10" t="s">
-        <v>415</v>
-      </c>
-      <c r="C26" s="10" t="s">
-        <v>416</v>
-      </c>
-      <c r="D26" s="10" t="s">
-        <v>417</v>
-      </c>
-      <c r="E26" s="10" t="s">
-        <v>374</v>
-      </c>
-      <c r="F26" s="10" t="s">
-        <v>418</v>
-      </c>
-      <c r="G26" s="10">
-        <v>0</v>
-      </c>
-      <c r="H26" s="10" t="s">
-        <v>374</v>
-      </c>
-      <c r="I26" s="10">
-        <v>1</v>
-      </c>
-      <c r="J26" s="10" t="s">
-        <v>379</v>
-      </c>
-      <c r="K26" s="10">
-        <v>1</v>
-      </c>
-      <c r="L26" t="s">
-        <v>374</v>
-      </c>
-      <c r="M26">
-        <v>35</v>
+      <c r="L26" s="9"/>
+      <c r="M26" s="9">
+        <v>50</v>
+      </c>
+      <c r="N26" s="9" t="s">
+        <v>393</v>
       </c>
     </row>
     <row r="39" spans="4:4">
-      <c r="D39"/>
+      <c r="D39" s="9"/>
     </row>
     <row r="40" spans="4:4">
-      <c r="D40"/>
+      <c r="D40" s="9"/>
     </row>
     <row r="41" spans="4:4">
-      <c r="D41"/>
+      <c r="D41" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8551,36 +8535,36 @@
   <sheetData>
     <row r="1" ht="17.25" customHeight="1" spans="2:9">
       <c r="B1" s="3" t="s">
-        <v>419</v>
+        <v>433</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>420</v>
+        <v>434</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>421</v>
+        <v>435</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>422</v>
+        <v>436</v>
       </c>
       <c r="H1" s="7" t="s">
         <v>1</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>423</v>
+        <v>437</v>
       </c>
     </row>
     <row r="2" ht="17.25" customHeight="1" spans="2:9">
       <c r="B2" s="3" t="s">
-        <v>424</v>
+        <v>438</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>425</v>
+        <v>439</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>426</v>
+        <v>440</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>427</v>
+        <v>441</v>
       </c>
       <c r="H2" s="1">
         <v>1</v>
@@ -8594,10 +8578,10 @@
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
       <c r="D3" s="3" t="s">
-        <v>428</v>
+        <v>442</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>429</v>
+        <v>443</v>
       </c>
       <c r="H3" s="1">
         <v>2</v>
@@ -8611,10 +8595,10 @@
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
       <c r="D4" s="3" t="s">
-        <v>430</v>
+        <v>444</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>431</v>
+        <v>445</v>
       </c>
       <c r="H4" s="1">
         <v>3</v>
@@ -8628,10 +8612,10 @@
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
       <c r="D5" s="3" t="s">
-        <v>428</v>
+        <v>442</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>432</v>
+        <v>446</v>
       </c>
       <c r="H5" s="1">
         <v>4</v>
@@ -8645,10 +8629,10 @@
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
       <c r="D6" s="3" t="s">
-        <v>433</v>
+        <v>447</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>434</v>
+        <v>448</v>
       </c>
       <c r="H6" s="1">
         <v>5</v>
@@ -8662,10 +8646,10 @@
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
       <c r="D7" s="3" t="s">
-        <v>435</v>
+        <v>449</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>436</v>
+        <v>450</v>
       </c>
       <c r="H7" s="1">
         <v>6</v>
@@ -8682,7 +8666,7 @@
         <v>59</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>437</v>
+        <v>451</v>
       </c>
       <c r="H8" s="1">
         <v>7</v>
@@ -8696,7 +8680,7 @@
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
       <c r="D9" s="3" t="s">
-        <v>438</v>
+        <v>452</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>66</v>
@@ -8712,13 +8696,13 @@
     <row r="10" ht="17.25" customHeight="1" spans="2:9">
       <c r="B10" s="4"/>
       <c r="C10" s="4" t="s">
-        <v>439</v>
+        <v>453</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>68</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>440</v>
+        <v>454</v>
       </c>
       <c r="H10" s="1">
         <v>9</v>
@@ -8732,10 +8716,10 @@
       <c r="B11" s="4"/>
       <c r="C11" s="3"/>
       <c r="D11" s="3" t="s">
-        <v>441</v>
+        <v>455</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>442</v>
+        <v>456</v>
       </c>
       <c r="H11" s="1">
         <v>10</v>
@@ -8749,10 +8733,10 @@
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
       <c r="D12" s="3" t="s">
-        <v>443</v>
+        <v>457</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>444</v>
+        <v>458</v>
       </c>
       <c r="H12" s="1">
         <v>11</v>
@@ -8766,10 +8750,10 @@
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
       <c r="D13" s="5" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>446</v>
+        <v>460</v>
       </c>
       <c r="H13" s="1">
         <v>12</v>
@@ -8782,13 +8766,13 @@
     <row r="14" ht="17.25" customHeight="1" spans="2:9">
       <c r="B14" s="4"/>
       <c r="C14" s="4" t="s">
-        <v>447</v>
+        <v>461</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>448</v>
+        <v>462</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>449</v>
+        <v>463</v>
       </c>
       <c r="H14" s="1">
         <v>13</v>
@@ -8802,10 +8786,10 @@
       <c r="B15" s="4"/>
       <c r="C15" s="3"/>
       <c r="D15" s="3" t="s">
-        <v>450</v>
+        <v>464</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>451</v>
+        <v>465</v>
       </c>
       <c r="H15" s="1">
         <v>14</v>
@@ -8819,10 +8803,10 @@
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
       <c r="D16" s="3" t="s">
-        <v>452</v>
+        <v>466</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>453</v>
+        <v>467</v>
       </c>
       <c r="H16" s="1">
         <v>15</v>
@@ -8836,10 +8820,10 @@
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
       <c r="D17" s="3" t="s">
-        <v>454</v>
+        <v>468</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>455</v>
+        <v>469</v>
       </c>
       <c r="H17" s="1">
         <v>16</v>
@@ -8853,10 +8837,10 @@
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
       <c r="D18" s="3" t="s">
-        <v>456</v>
+        <v>470</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>457</v>
+        <v>471</v>
       </c>
       <c r="H18" s="1">
         <v>17</v>
@@ -8870,10 +8854,10 @@
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
       <c r="D19" s="3" t="s">
-        <v>456</v>
+        <v>470</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>458</v>
+        <v>472</v>
       </c>
       <c r="H19" s="1">
         <v>18</v>
@@ -8886,13 +8870,13 @@
     <row r="20" ht="17.25" customHeight="1" spans="2:9">
       <c r="B20" s="4"/>
       <c r="C20" s="4" t="s">
-        <v>459</v>
+        <v>473</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>117</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>460</v>
+        <v>474</v>
       </c>
       <c r="H20" s="1">
         <v>19</v>
@@ -8905,13 +8889,13 @@
     <row r="21" ht="17.25" customHeight="1" spans="2:9">
       <c r="B21" s="4"/>
       <c r="C21" s="4" t="s">
-        <v>461</v>
+        <v>475</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>462</v>
+        <v>476</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>463</v>
+        <v>477</v>
       </c>
       <c r="H21" s="1">
         <v>20</v>
@@ -8925,10 +8909,10 @@
       <c r="B22" s="4"/>
       <c r="C22" s="3"/>
       <c r="D22" s="3" t="s">
-        <v>464</v>
+        <v>478</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>465</v>
+        <v>479</v>
       </c>
       <c r="H22" s="1">
         <v>21</v>
@@ -8942,10 +8926,10 @@
       <c r="B23" s="4"/>
       <c r="C23" s="3"/>
       <c r="D23" s="3" t="s">
-        <v>466</v>
+        <v>480</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>467</v>
+        <v>481</v>
       </c>
       <c r="H23" s="1">
         <v>22</v>
@@ -8959,10 +8943,10 @@
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
       <c r="D24" s="3" t="s">
-        <v>468</v>
+        <v>482</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>469</v>
+        <v>483</v>
       </c>
       <c r="H24" s="1">
         <v>23</v>
@@ -8975,13 +8959,13 @@
     <row r="25" ht="17.25" customHeight="1" spans="2:9">
       <c r="B25" s="4"/>
       <c r="C25" s="4" t="s">
-        <v>470</v>
+        <v>484</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>471</v>
+        <v>485</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>472</v>
+        <v>486</v>
       </c>
       <c r="H25" s="1">
         <v>24</v>
@@ -8995,10 +8979,10 @@
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
       <c r="D26" s="3" t="s">
-        <v>471</v>
+        <v>485</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>473</v>
+        <v>487</v>
       </c>
       <c r="H26" s="1">
         <v>25</v>
@@ -9011,13 +8995,13 @@
     <row r="27" ht="17.25" customHeight="1" spans="2:9">
       <c r="B27" s="4"/>
       <c r="C27" s="3" t="s">
-        <v>474</v>
+        <v>488</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>475</v>
+        <v>489</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>476</v>
+        <v>490</v>
       </c>
       <c r="H27" s="1">
         <v>26</v>
@@ -9030,13 +9014,13 @@
     <row r="28" ht="17.25" customHeight="1" spans="2:9">
       <c r="B28" s="4"/>
       <c r="C28" s="4" t="s">
-        <v>477</v>
+        <v>491</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>478</v>
+        <v>492</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>479</v>
+        <v>493</v>
       </c>
       <c r="H28" s="1">
         <v>27</v>
@@ -9049,13 +9033,13 @@
     <row r="29" ht="17.25" customHeight="1" spans="2:9">
       <c r="B29" s="4"/>
       <c r="C29" s="3" t="s">
-        <v>480</v>
+        <v>494</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>478</v>
+        <v>492</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>481</v>
+        <v>495</v>
       </c>
       <c r="H29" s="1">
         <v>28</v>
@@ -9068,13 +9052,13 @@
     <row r="30" ht="17.25" customHeight="1" spans="2:9">
       <c r="B30" s="4"/>
       <c r="C30" s="3" t="s">
-        <v>482</v>
+        <v>496</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>483</v>
+        <v>497</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>484</v>
+        <v>498</v>
       </c>
       <c r="H30" s="1">
         <v>29</v>
@@ -9088,10 +9072,10 @@
       <c r="B31" s="4"/>
       <c r="C31" s="3"/>
       <c r="D31" s="3" t="s">
-        <v>483</v>
+        <v>497</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>485</v>
+        <v>499</v>
       </c>
       <c r="H31" s="1">
         <v>30</v>
@@ -9104,13 +9088,13 @@
     <row r="32" ht="17.25" customHeight="1" spans="2:9">
       <c r="B32" s="4"/>
       <c r="C32" s="3" t="s">
-        <v>486</v>
+        <v>500</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>486</v>
+        <v>500</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>487</v>
+        <v>501</v>
       </c>
       <c r="H32" s="1">
         <v>31</v>
@@ -9124,10 +9108,10 @@
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
       <c r="D33" s="3" t="s">
-        <v>488</v>
+        <v>502</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>489</v>
+        <v>503</v>
       </c>
       <c r="H33" s="1">
         <v>32</v>
@@ -9141,10 +9125,10 @@
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
       <c r="D34" s="3" t="s">
-        <v>490</v>
+        <v>504</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>491</v>
+        <v>505</v>
       </c>
       <c r="H34" s="1">
         <v>33</v>
@@ -9158,10 +9142,10 @@
       <c r="B35" s="4"/>
       <c r="C35" s="3"/>
       <c r="D35" s="3" t="s">
-        <v>492</v>
+        <v>506</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>493</v>
+        <v>507</v>
       </c>
       <c r="H35" s="1">
         <v>34</v>
@@ -9175,10 +9159,10 @@
       <c r="B36" s="4"/>
       <c r="C36" s="3"/>
       <c r="D36" s="6" t="s">
-        <v>494</v>
+        <v>508</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>495</v>
+        <v>509</v>
       </c>
       <c r="H36" s="1">
         <v>35</v>
@@ -9192,10 +9176,10 @@
       <c r="B37" s="4"/>
       <c r="C37" s="3"/>
       <c r="D37" s="3" t="s">
-        <v>496</v>
+        <v>510</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>497</v>
+        <v>511</v>
       </c>
       <c r="H37" s="1">
         <v>36</v>
@@ -9208,13 +9192,13 @@
     <row r="38" ht="17.25" customHeight="1" spans="2:9">
       <c r="B38" s="4"/>
       <c r="C38" s="3" t="s">
-        <v>498</v>
+        <v>512</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>438</v>
+        <v>452</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>499</v>
+        <v>513</v>
       </c>
       <c r="H38" s="1">
         <v>37</v>
@@ -9228,10 +9212,10 @@
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
       <c r="D39" s="3" t="s">
-        <v>500</v>
+        <v>514</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>501</v>
+        <v>515</v>
       </c>
       <c r="H39" s="1">
         <v>38</v>
@@ -9245,10 +9229,10 @@
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
       <c r="D40" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H40" s="1">
         <v>39</v>
@@ -9262,10 +9246,10 @@
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
       <c r="D41" s="3" t="s">
-        <v>502</v>
+        <v>516</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>503</v>
+        <v>517</v>
       </c>
       <c r="H41" s="1">
         <v>40</v>
@@ -9279,10 +9263,10 @@
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
       <c r="D42" s="3" t="s">
-        <v>504</v>
+        <v>518</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>505</v>
+        <v>519</v>
       </c>
       <c r="H42" s="1">
         <v>41</v>
@@ -9295,13 +9279,13 @@
     <row r="43" ht="17.25" customHeight="1" spans="2:9">
       <c r="B43" s="4"/>
       <c r="C43" s="4" t="s">
-        <v>506</v>
+        <v>520</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>507</v>
+        <v>521</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>508</v>
+        <v>522</v>
       </c>
       <c r="H43" s="1">
         <v>42</v>
@@ -9315,10 +9299,10 @@
       <c r="B44" s="4"/>
       <c r="C44" s="3"/>
       <c r="D44" s="3" t="s">
-        <v>509</v>
+        <v>523</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>510</v>
+        <v>524</v>
       </c>
       <c r="H44" s="1">
         <v>43</v>
@@ -9332,10 +9316,10 @@
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
       <c r="D45" s="3" t="s">
-        <v>511</v>
+        <v>525</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>512</v>
+        <v>526</v>
       </c>
       <c r="H45" s="1">
         <v>44</v>
@@ -9348,13 +9332,13 @@
     <row r="46" ht="17.25" customHeight="1" spans="2:9">
       <c r="B46" s="4"/>
       <c r="C46" s="4" t="s">
-        <v>513</v>
+        <v>527</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>514</v>
+        <v>528</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>515</v>
+        <v>529</v>
       </c>
       <c r="H46" s="1">
         <v>45</v>
@@ -9368,10 +9352,10 @@
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
       <c r="D47" s="3" t="s">
-        <v>439</v>
+        <v>453</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>516</v>
+        <v>530</v>
       </c>
       <c r="H47" s="1">
         <v>46</v>
@@ -9385,10 +9369,10 @@
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
       <c r="D48" s="3" t="s">
-        <v>517</v>
+        <v>531</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>518</v>
+        <v>532</v>
       </c>
       <c r="H48" s="1">
         <v>47</v>
@@ -9401,13 +9385,13 @@
     <row r="49" ht="17.25" customHeight="1" spans="2:9">
       <c r="B49" s="4"/>
       <c r="C49" s="3" t="s">
-        <v>519</v>
+        <v>533</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>520</v>
+        <v>534</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>521</v>
+        <v>535</v>
       </c>
       <c r="H49" s="1">
         <v>48</v>
@@ -9421,10 +9405,10 @@
       <c r="B50" s="4"/>
       <c r="C50" s="4"/>
       <c r="D50" s="3" t="s">
-        <v>522</v>
+        <v>536</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>523</v>
+        <v>537</v>
       </c>
       <c r="H50" s="1">
         <v>49</v>
@@ -9438,10 +9422,10 @@
       <c r="B51" s="4"/>
       <c r="C51" s="4"/>
       <c r="D51" s="3" t="s">
-        <v>524</v>
+        <v>538</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>525</v>
+        <v>539</v>
       </c>
       <c r="H51" s="1">
         <v>50</v>
@@ -9455,10 +9439,10 @@
       <c r="B52" s="4"/>
       <c r="C52" s="3"/>
       <c r="D52" s="3" t="s">
-        <v>526</v>
+        <v>540</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>527</v>
+        <v>541</v>
       </c>
       <c r="H52" s="1">
         <v>51</v>
@@ -9472,10 +9456,10 @@
       <c r="B53" s="4"/>
       <c r="C53" s="4"/>
       <c r="D53" s="3" t="s">
-        <v>528</v>
+        <v>542</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>529</v>
+        <v>543</v>
       </c>
       <c r="H53" s="1">
         <v>52</v>
@@ -9489,10 +9473,10 @@
       <c r="B54" s="4"/>
       <c r="C54" s="4"/>
       <c r="D54" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>530</v>
+        <v>544</v>
       </c>
       <c r="H54" s="1">
         <v>53</v>
@@ -9505,13 +9489,13 @@
     <row r="55" ht="17.25" customHeight="1" spans="2:9">
       <c r="B55" s="4"/>
       <c r="C55" s="3" t="s">
-        <v>531</v>
+        <v>545</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>532</v>
+        <v>546</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>533</v>
+        <v>547</v>
       </c>
       <c r="H55" s="1">
         <v>54</v>
@@ -9525,10 +9509,10 @@
       <c r="B56" s="4"/>
       <c r="C56" s="4"/>
       <c r="D56" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>534</v>
+        <v>548</v>
       </c>
       <c r="H56" s="1">
         <v>55</v>
@@ -9541,13 +9525,13 @@
     <row r="57" ht="17.25" customHeight="1" spans="2:9">
       <c r="B57" s="4"/>
       <c r="C57" s="4" t="s">
-        <v>535</v>
+        <v>549</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>536</v>
+        <v>550</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>537</v>
+        <v>551</v>
       </c>
       <c r="H57" s="1">
         <v>56</v>
@@ -9561,10 +9545,10 @@
       <c r="B58" s="4"/>
       <c r="C58" s="4"/>
       <c r="D58" s="3" t="s">
-        <v>536</v>
+        <v>550</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>538</v>
+        <v>552</v>
       </c>
       <c r="H58" s="1">
         <v>57</v>
@@ -9578,10 +9562,10 @@
       <c r="B59" s="4"/>
       <c r="C59" s="4"/>
       <c r="D59" s="3" t="s">
-        <v>539</v>
+        <v>553</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>540</v>
+        <v>554</v>
       </c>
       <c r="H59" s="1">
         <v>58</v>
@@ -9595,10 +9579,10 @@
       <c r="B60" s="4"/>
       <c r="C60" s="4"/>
       <c r="D60" s="3" t="s">
-        <v>541</v>
+        <v>555</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>542</v>
+        <v>556</v>
       </c>
       <c r="H60" s="1">
         <v>59</v>
@@ -9612,10 +9596,10 @@
       <c r="B61" s="4"/>
       <c r="C61" s="3"/>
       <c r="D61" s="3" t="s">
-        <v>543</v>
+        <v>557</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>544</v>
+        <v>558</v>
       </c>
       <c r="H61" s="1">
         <v>60</v>
@@ -9628,13 +9612,13 @@
     <row r="62" ht="17.25" customHeight="1" spans="2:9">
       <c r="B62" s="4"/>
       <c r="C62" s="4" t="s">
-        <v>545</v>
+        <v>559</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>546</v>
+        <v>560</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>547</v>
+        <v>561</v>
       </c>
       <c r="H62" s="1">
         <v>61</v>
@@ -9647,13 +9631,13 @@
     <row r="63" ht="17.25" customHeight="1" spans="2:9">
       <c r="B63" s="4"/>
       <c r="C63" s="3" t="s">
-        <v>548</v>
+        <v>562</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>549</v>
+        <v>563</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>550</v>
+        <v>564</v>
       </c>
       <c r="H63" s="1">
         <v>62</v>
@@ -9667,10 +9651,10 @@
       <c r="B64" s="4"/>
       <c r="C64" s="4"/>
       <c r="D64" s="3" t="s">
-        <v>551</v>
+        <v>565</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>552</v>
+        <v>566</v>
       </c>
       <c r="H64" s="1">
         <v>63</v>
@@ -9684,10 +9668,10 @@
       <c r="B65" s="4"/>
       <c r="C65" s="4"/>
       <c r="D65" s="3" t="s">
-        <v>553</v>
+        <v>567</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>554</v>
+        <v>568</v>
       </c>
       <c r="H65" s="1">
         <v>64</v>
@@ -9701,10 +9685,10 @@
       <c r="B66" s="4"/>
       <c r="C66" s="4"/>
       <c r="D66" s="3" t="s">
-        <v>555</v>
+        <v>569</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>556</v>
+        <v>570</v>
       </c>
       <c r="H66" s="1">
         <v>65</v>
@@ -9718,10 +9702,10 @@
       <c r="B67" s="4"/>
       <c r="C67" s="4"/>
       <c r="D67" s="3" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>557</v>
+        <v>571</v>
       </c>
       <c r="H67" s="1">
         <v>66</v>
@@ -9734,13 +9718,13 @@
     <row r="68" ht="17.25" customHeight="1" spans="2:9">
       <c r="B68" s="4"/>
       <c r="C68" s="3" t="s">
-        <v>558</v>
+        <v>572</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>559</v>
+        <v>573</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="H68" s="1">
         <v>67</v>
@@ -9754,10 +9738,10 @@
       <c r="B69" s="4"/>
       <c r="C69" s="3"/>
       <c r="D69" s="3" t="s">
-        <v>560</v>
+        <v>574</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>561</v>
+        <v>575</v>
       </c>
       <c r="H69" s="1">
         <v>68</v>
@@ -9769,16 +9753,16 @@
     </row>
     <row r="70" ht="17.25" customHeight="1" spans="2:9">
       <c r="B70" s="4" t="s">
-        <v>562</v>
+        <v>576</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>563</v>
+        <v>577</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>564</v>
+        <v>578</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>565</v>
+        <v>579</v>
       </c>
       <c r="H70" s="1">
         <v>69</v>
@@ -9792,10 +9776,10 @@
       <c r="B71" s="4"/>
       <c r="C71" s="4"/>
       <c r="D71" s="3" t="s">
-        <v>566</v>
+        <v>580</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>567</v>
+        <v>581</v>
       </c>
       <c r="H71" s="1">
         <v>70</v>
@@ -9809,10 +9793,10 @@
       <c r="B72" s="4"/>
       <c r="C72" s="4"/>
       <c r="D72" s="3" t="s">
-        <v>568</v>
+        <v>582</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H72" s="1">
         <v>71</v>
@@ -9826,10 +9810,10 @@
       <c r="B73" s="4"/>
       <c r="C73" s="4"/>
       <c r="D73" s="3" t="s">
-        <v>569</v>
+        <v>583</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>570</v>
+        <v>584</v>
       </c>
       <c r="H73" s="1">
         <v>72</v>
@@ -9843,10 +9827,10 @@
       <c r="B74" s="4"/>
       <c r="C74" s="3"/>
       <c r="D74" s="3" t="s">
-        <v>571</v>
+        <v>585</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>572</v>
+        <v>586</v>
       </c>
       <c r="H74" s="1">
         <v>73</v>
@@ -9860,10 +9844,10 @@
       <c r="B75" s="4"/>
       <c r="C75" s="3"/>
       <c r="D75" s="3" t="s">
-        <v>573</v>
+        <v>587</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>574</v>
+        <v>588</v>
       </c>
       <c r="H75" s="1">
         <v>74</v>
@@ -9877,10 +9861,10 @@
       <c r="B76" s="3"/>
       <c r="C76" s="3"/>
       <c r="D76" s="3" t="s">
-        <v>575</v>
+        <v>589</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>576</v>
+        <v>590</v>
       </c>
       <c r="H76" s="1">
         <v>75</v>
@@ -9894,10 +9878,10 @@
       <c r="B77" s="4"/>
       <c r="C77" s="4"/>
       <c r="D77" s="3" t="s">
-        <v>577</v>
+        <v>591</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>578</v>
+        <v>592</v>
       </c>
       <c r="H77" s="1">
         <v>76</v>
@@ -9911,10 +9895,10 @@
       <c r="B78" s="4"/>
       <c r="C78" s="4"/>
       <c r="D78" s="3" t="s">
-        <v>579</v>
+        <v>593</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>580</v>
+        <v>594</v>
       </c>
       <c r="H78" s="1">
         <v>77</v>
@@ -9926,16 +9910,16 @@
     </row>
     <row r="79" ht="17.25" customHeight="1" spans="2:9">
       <c r="B79" s="4" t="s">
-        <v>581</v>
+        <v>595</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>582</v>
+        <v>596</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>583</v>
+        <v>597</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>584</v>
+        <v>598</v>
       </c>
       <c r="H79" s="1">
         <v>78</v>
@@ -9948,13 +9932,13 @@
     <row r="80" ht="17.25" customHeight="1" spans="2:9">
       <c r="B80" s="4"/>
       <c r="C80" s="4" t="s">
-        <v>585</v>
+        <v>599</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>586</v>
+        <v>600</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>587</v>
+        <v>601</v>
       </c>
       <c r="H80" s="1">
         <v>79</v>
@@ -9968,10 +9952,10 @@
       <c r="B81" s="4"/>
       <c r="C81" s="4"/>
       <c r="D81" s="3" t="s">
-        <v>586</v>
+        <v>600</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>588</v>
+        <v>602</v>
       </c>
       <c r="H81" s="1">
         <v>80</v>
@@ -9985,10 +9969,10 @@
       <c r="B82" s="4"/>
       <c r="C82" s="4"/>
       <c r="D82" s="3" t="s">
-        <v>589</v>
+        <v>603</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>590</v>
+        <v>604</v>
       </c>
       <c r="H82" s="1">
         <v>81</v>
@@ -10002,10 +9986,10 @@
       <c r="B83" s="4"/>
       <c r="C83" s="4"/>
       <c r="D83" s="3" t="s">
-        <v>591</v>
+        <v>605</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>592</v>
+        <v>606</v>
       </c>
       <c r="H83" s="1">
         <v>82</v>
@@ -10018,13 +10002,13 @@
     <row r="84" ht="17.25" customHeight="1" spans="2:9">
       <c r="B84" s="4"/>
       <c r="C84" s="4" t="s">
-        <v>593</v>
+        <v>607</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>594</v>
+        <v>608</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>595</v>
+        <v>609</v>
       </c>
       <c r="H84" s="1">
         <v>83</v>
@@ -10038,10 +10022,10 @@
       <c r="B85" s="3"/>
       <c r="C85" s="3"/>
       <c r="D85" s="3" t="s">
-        <v>596</v>
+        <v>610</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>597</v>
+        <v>611</v>
       </c>
       <c r="H85" s="1">
         <v>84</v>
@@ -10055,10 +10039,10 @@
       <c r="B86" s="4"/>
       <c r="C86" s="3"/>
       <c r="D86" s="3" t="s">
-        <v>598</v>
+        <v>612</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>599</v>
+        <v>613</v>
       </c>
       <c r="H86" s="1">
         <v>85</v>
@@ -10072,10 +10056,10 @@
       <c r="B87" s="4"/>
       <c r="C87" s="4"/>
       <c r="D87" s="3" t="s">
-        <v>600</v>
+        <v>614</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>601</v>
+        <v>615</v>
       </c>
       <c r="H87" s="1">
         <v>86</v>
@@ -10089,10 +10073,10 @@
       <c r="B88" s="4"/>
       <c r="C88" s="4"/>
       <c r="D88" s="3" t="s">
-        <v>602</v>
+        <v>616</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="H88" s="1">
         <v>87</v>

--- a/GourmetProject/GameConfig/Datas/item.xlsx
+++ b/GourmetProject/GameConfig/Datas/item.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="被动道具" sheetId="1" r:id="Racbe996da2204eab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主动道具" sheetId="2" r:id="Ree51fb06fa0049cd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="道具设计" sheetId="3" r:id="Rfef65de353104754"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="被动道具" sheetId="1" r:id="Rf36ff9f8b21e46f6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主动道具" sheetId="2" r:id="R854ec96626f142d9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="道具设计" sheetId="3" r:id="R0aa5ca5a63d848f7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -7737,6 +7737,9 @@
       <x:c r="D10" s="9" t="s">
         <x:v>360</x:v>
       </x:c>
+      <x:c r="E10" t="str">
+        <x:v>LayWood</x:v>
+      </x:c>
       <x:c r="F10" s="7" t="s">
         <x:v>361</x:v>
       </x:c>
@@ -7775,6 +7778,9 @@
       <x:c r="D11" s="9" t="s">
         <x:v>366</x:v>
       </x:c>
+      <x:c r="E11" t="str">
+        <x:v>LayWood</x:v>
+      </x:c>
       <x:c r="F11" s="7" t="s">
         <x:v>361</x:v>
       </x:c>
@@ -7813,6 +7819,9 @@
       <x:c r="D12" s="9" t="s">
         <x:v>370</x:v>
       </x:c>
+      <x:c r="E12" t="str">
+        <x:v>LayStone</x:v>
+      </x:c>
       <x:c r="F12" s="7" t="s">
         <x:v>361</x:v>
       </x:c>
@@ -7851,6 +7860,9 @@
       <x:c r="D13" s="9" t="s">
         <x:v>374</x:v>
       </x:c>
+      <x:c r="E13" t="str">
+        <x:v>LayStone</x:v>
+      </x:c>
       <x:c r="F13" s="7" t="s">
         <x:v>361</x:v>
       </x:c>
@@ -7889,6 +7901,9 @@
       <x:c r="D14" s="9" t="s">
         <x:v>378</x:v>
       </x:c>
+      <x:c r="E14" t="str">
+        <x:v>LayStone</x:v>
+      </x:c>
       <x:c r="F14" s="7" t="s">
         <x:v>361</x:v>
       </x:c>
@@ -7927,6 +7942,9 @@
       <x:c r="D15" s="9" t="s">
         <x:v>382</x:v>
       </x:c>
+      <x:c r="E15" t="str">
+        <x:v>LayMetal</x:v>
+      </x:c>
       <x:c r="F15" s="7" t="s">
         <x:v>361</x:v>
       </x:c>
@@ -7964,6 +7982,9 @@
       </x:c>
       <x:c r="D16" s="9" t="s">
         <x:v>386</x:v>
+      </x:c>
+      <x:c r="E16" t="str">
+        <x:v>LayMetal</x:v>
       </x:c>
       <x:c r="F16" s="7" t="s">
         <x:v>361</x:v>

--- a/GourmetProject/GameConfig/Datas/item.xlsx
+++ b/GourmetProject/GameConfig/Datas/item.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="装饰品" sheetId="1" r:id="R9c7ed865b06942e0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="消耗品" sheetId="2" r:id="R32f30e02e7d84580"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="装饰品与消耗品设计" sheetId="3" r:id="Ra37c28dc2d8e4d1e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="装饰品" sheetId="1" r:id="R87aec862935045c6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="消耗品" sheetId="2" r:id="Re3c9542685db41cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="装饰品与消耗品设计" sheetId="3" r:id="R461371e8b0c54c2b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -6206,8 +6206,8 @@
         <x:v>209</x:v>
       </x:c>
       <x:c r="D55" s="9" t="str">
-        <x:v>每经历 4 个事件
-下次事件必定带来奖励</x:v>
+        <x:v>经历4 个事件后
+下个事件一定为奖励</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
         <x:v>42</x:v>
@@ -6264,7 +6264,8 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="D56" s="9" t="str">
-        <x:v>更容易遇到奖励事件</x:v>
+        <x:v>事件行动中
+奖励事件随机权重 +20%</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
         <x:v>42</x:v>
@@ -6323,7 +6324,8 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="D57" s="9" t="str">
-        <x:v>更容易遇到事件</x:v>
+        <x:v>事件行动大组
+随机权重 +20%</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
         <x:v>48</x:v>
@@ -6662,8 +6664,8 @@
         <x:v>230</x:v>
       </x:c>
       <x:c r="D63" s="9" t="str">
-        <x:v>每次进入事件
-获得 15 金币</x:v>
+        <x:v>进入事件时
+获得15 金币</x:v>
       </x:c>
       <x:c r="E63" s="1" t="s">
         <x:v>61</x:v>
@@ -7468,7 +7470,7 @@
         <x:v>274</x:v>
       </x:c>
       <x:c r="D77" s="9" t="str">
-        <x:v>跳过下一次奖励事件</x:v>
+        <x:v>跳过下一个幸运事件节点</x:v>
       </x:c>
       <x:c r="E77" s="1" t="s">
         <x:v>48</x:v>
@@ -9334,7 +9336,7 @@
         <x:v>421</x:v>
       </x:c>
       <x:c r="D20" s="8" t="str">
-        <x:v>在指定日期添加奖励事件</x:v>
+        <x:v>添加幸运事件至指定节点上</x:v>
       </x:c>
       <x:c r="F20" s="8" t="s">
         <x:v>422</x:v>

--- a/GourmetProject/GameConfig/Datas/item.xlsx
+++ b/GourmetProject/GameConfig/Datas/item.xlsx
@@ -4,14 +4,27 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15360"/>
+    <workbookView windowHeight="16760"/>
   </bookViews>
   <sheets>
     <sheet name="装饰品" sheetId="1" r:id="rId1"/>
     <sheet name="消耗品" sheetId="2" r:id="rId2"/>
     <sheet name="装饰品与消耗品设计" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -513,7 +526,7 @@
 添加至本周末尾</t>
   </si>
   <si>
-    <t>repay:300</t>
+    <t>act_loan_repay</t>
   </si>
   <si>
     <t>item_timeline_random</t>
@@ -2089,7 +2102,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>

--- a/GourmetProject/GameConfig/Datas/item.xlsx
+++ b/GourmetProject/GameConfig/Datas/item.xlsx
@@ -4,32 +4,19 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16760"/>
+    <workbookView windowHeight="15340"/>
   </bookViews>
   <sheets>
     <sheet name="装饰品" sheetId="1" r:id="rId1"/>
     <sheet name="消耗品" sheetId="2" r:id="rId2"/>
     <sheet name="装饰品与消耗品设计" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1062" uniqueCount="665">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1133" uniqueCount="714">
   <si>
     <t>##var</t>
   </si>
@@ -215,30 +202,30 @@
   </si>
   <si>
     <t>营业获得的金币
-额外+15%</t>
+额外+20%</t>
+  </si>
+  <si>
+    <t>20,80</t>
+  </si>
+  <si>
+    <t>item_trash_upgrade</t>
+  </si>
+  <si>
+    <t>藤编纸篓</t>
+  </si>
+  <si>
+    <t>丢弃次数+1</t>
+  </si>
+  <si>
+    <t>item_trash_expand</t>
+  </si>
+  <si>
+    <t>壁挂废物桶</t>
   </si>
   <si>
     <t>Uncommon</t>
   </si>
   <si>
-    <t>20,80</t>
-  </si>
-  <si>
-    <t>item_trash_upgrade</t>
-  </si>
-  <si>
-    <t>藤编纸篓</t>
-  </si>
-  <si>
-    <t>丢弃次数+1</t>
-  </si>
-  <si>
-    <t>item_trash_expand</t>
-  </si>
-  <si>
-    <t>壁挂废物桶</t>
-  </si>
-  <si>
     <t>item_trash_evolve</t>
   </si>
   <si>
@@ -260,7 +247,7 @@
     <t>香草盆栽</t>
   </si>
   <si>
-    <t>食物价格-10%</t>
+    <t>食物价格-15%</t>
   </si>
   <si>
     <t>item_discount_fragment</t>
@@ -305,7 +292,7 @@
     <t>抽页食谱夹</t>
   </si>
   <si>
-    <t>删除食物价格-15%</t>
+    <t>移除食物价格-15%</t>
   </si>
   <si>
     <t>item_discount_food_festival</t>
@@ -314,7 +301,7 @@
     <t>丰收菜篮</t>
   </si>
   <si>
-    <t>食物价格-20%</t>
+    <t>食物价格-25%</t>
   </si>
   <si>
     <t>item_discount_fragment_festival</t>
@@ -359,7 +346,7 @@
     <t>可擦食谱板</t>
   </si>
   <si>
-    <t>删除食物价格-30%</t>
+    <t>移除食物价格-30%</t>
   </si>
   <si>
     <t>item_famous_knife</t>
@@ -445,8 +432,8 @@
   </si>
   <si>
     <t>结算开始
-若食物数量≤15
-所有食物倍率×1.5</t>
+若食物份数≤15
+所有食物倍率+0.5</t>
   </si>
   <si>
     <t>lte:15</t>
@@ -459,8 +446,8 @@
   </si>
   <si>
     <t>结算开始
-若食物数量≥25
-所有食物倍率×1.5</t>
+若食物份数≥25
+所有食物倍率+0.5</t>
   </si>
   <si>
     <t>gte:25</t>
@@ -473,7 +460,7 @@
   </si>
   <si>
     <t>获得时
-所有食物分数永久+10</t>
+所有食物分数永久+20</t>
   </si>
   <si>
     <t>item_perma_flat_all_plus</t>
@@ -483,7 +470,7 @@
   </si>
   <si>
     <t>获得时
-所有食物分数永久+30</t>
+所有食物分数永久+40</t>
   </si>
   <si>
     <t>item_gold_on_shop</t>
@@ -492,7 +479,7 @@
     <t>供货商合影</t>
   </si>
   <si>
-    <t>进入商店采购
+    <t>进入商店采购时
 获得15金币</t>
   </si>
   <si>
@@ -502,8 +489,8 @@
     <t>挂墙周历</t>
   </si>
   <si>
-    <t>将收取利息
-添加至每周末尾</t>
+    <t>添加节点收取利息
+至每周末尾</t>
   </si>
   <si>
     <t>item_interest_cap</t>
@@ -512,7 +499,7 @@
     <t>聚宝盆摆件</t>
   </si>
   <si>
-    <t>利息上限扩展到150金币</t>
+    <t>利息上限扩展到100金币</t>
   </si>
   <si>
     <t>item_loan</t>
@@ -521,9 +508,9 @@
     <t>挂账记录板</t>
   </si>
   <si>
-    <t>获得150金币
-将失去300金币的节点行动
-添加至本周末尾</t>
+    <t>金币+150
+添加节点"金币-300"
+至本周末尾</t>
   </si>
   <si>
     <t>act_loan_repay</t>
@@ -536,7 +523,7 @@
   </si>
   <si>
     <t>获得时
-打乱未来节点的行动</t>
+打乱未来的节点行动</t>
   </si>
   <si>
     <t>item_extra_day</t>
@@ -546,21 +533,6 @@
   </si>
   <si>
     <t>每周长度变为8天</t>
-  </si>
-  <si>
-    <t>item_week_minus</t>
-  </si>
-  <si>
-    <t>黄铜沙漏</t>
-  </si>
-  <si>
-    <t>周数-1</t>
-  </si>
-  <si>
-    <t>Epic</t>
-  </si>
-  <si>
-    <t>40,80</t>
   </si>
   <si>
     <t>item_every3_next_mult</t>
@@ -648,7 +620,8 @@
     <t>彩釉调料瓶组</t>
   </si>
   <si>
-    <t>为2个食物添加随机风味</t>
+    <t>为2个食物
+添加随机风味</t>
   </si>
   <si>
     <t>item_flavor_remove_gold</t>
@@ -680,6 +653,12 @@
     <t>食物风味上限变为2</t>
   </si>
   <si>
+    <t>Epic</t>
+  </si>
+  <si>
+    <t>40,80</t>
+  </si>
+  <si>
     <t>item_celltag_enhance</t>
   </si>
   <si>
@@ -696,8 +675,8 @@
     <t>四叶草标本框</t>
   </si>
   <si>
-    <t>经历3个事件后
-下个事件一定为奖励</t>
+    <t>经历3个随机事件后
+下个一定为幸运事件</t>
   </si>
   <si>
     <t>item_lucky_chance</t>
@@ -706,8 +685,7 @@
     <t>四叶草福袋</t>
   </si>
   <si>
-    <t>事件行动中
-奖励事件随机权重+40%</t>
+    <t>更容易遇见幸运事件</t>
   </si>
   <si>
     <t>item_more_events</t>
@@ -716,8 +694,7 @@
     <t>街角路牌</t>
   </si>
   <si>
-    <t>事件行动大组
-随机权重+40%</t>
+    <t>更容易遇见随机事件</t>
   </si>
   <si>
     <t>item_more_super_actions</t>
@@ -831,11 +808,8 @@
     <t>杂货展示架</t>
   </si>
   <si>
-    <t>每2次火热营业
+    <t>每3次火热营业
 额外获得3选1装饰品</t>
-  </si>
-  <si>
-    <t>every:2</t>
   </si>
   <si>
     <t>item_copy_food</t>
@@ -854,7 +828,8 @@
     <t>藤编收纳筐</t>
   </si>
   <si>
-    <t>丢弃两个诅咒装饰品</t>
+    <t>获得时
+移除2个诅咒装饰品</t>
   </si>
   <si>
     <t>item_discard_negative_gold</t>
@@ -863,8 +838,9 @@
     <t>旧餐具寄卖架</t>
   </si>
   <si>
-    <t>丢弃所有诅咒装饰品
-每丢弃一个获得40金币</t>
+    <t>获得时
+移除所有诅咒装饰品
+每移除一个获得40金币</t>
   </si>
   <si>
     <t>item_gold_meal_penalty</t>
@@ -885,7 +861,7 @@
     <t>破损商品架</t>
   </si>
   <si>
-    <t>商店与删除食物价格+20%</t>
+    <t>移除食物价格+20%</t>
   </si>
   <si>
     <t>item_no_remove</t>
@@ -894,7 +870,7 @@
     <t>上锁食品柜</t>
   </si>
   <si>
-    <t>无法再删除食物</t>
+    <t>无法在商店中移除食物</t>
   </si>
   <si>
     <t>item_skip_node</t>
@@ -968,8 +944,9 @@
     <t>双栏排班板</t>
   </si>
   <si>
-    <t>普通行动消耗天数加倍
-节点行动可以执行2次</t>
+    <t>普通行动消耗天数+0.5
+商店与幸运事件节点
+可以额外执行1次</t>
   </si>
   <si>
     <t>repeat:2</t>
@@ -991,7 +968,8 @@
     <t>九格拼盘</t>
   </si>
   <si>
-    <t>所有食物额外被视为3个食物</t>
+    <t>结算开始
+所有食物额外被视为2份食物</t>
   </si>
   <si>
     <t>term_food_count_as</t>
@@ -1004,7 +982,7 @@
   </si>
   <si>
     <t>甜蜜传递时
-每个被传递方倍率+0.2</t>
+每个被传递方倍率+0.5</t>
   </si>
   <si>
     <t>term_sweet_transfer</t>
@@ -1018,7 +996,7 @@
   <si>
     <t>甜蜜传递时
 传递方每成功传递1个目标
-倍率+0.2</t>
+倍率+0.5</t>
   </si>
   <si>
     <t>item_skill_count_mult</t>
@@ -1051,7 +1029,7 @@
     <t>玻璃蛋糕罩</t>
   </si>
   <si>
-    <t>保留20%的蛋糕层数
+    <t>保留10%的蛋糕层数
 至下一场经营挑战</t>
   </si>
   <si>
@@ -1075,7 +1053,7 @@
   </si>
   <si>
     <t>蛋糕层数增加时
-额外加1层</t>
+额外加2层</t>
   </si>
   <si>
     <t>item_cake_to_gold</t>
@@ -1097,7 +1075,114 @@
     <t>迷你蛋糕模</t>
   </si>
   <si>
-    <t>蛋糕效果需求的层数-10</t>
+    <t>蛋糕效果需求的层数-20</t>
+  </si>
+  <si>
+    <t>甜蜜传递时
+额外选择2个目标</t>
+  </si>
+  <si>
+    <t>结算开始
+拥有风味的食物
+分数+30</t>
+  </si>
+  <si>
+    <t>结算开始
+拥有风味的食物
+额外视为1份食物</t>
+  </si>
+  <si>
+    <t>结算开始
+每拥有1个消耗品
+所有食物分数+10</t>
+  </si>
+  <si>
+    <t>结算开始
+每拥有1个消耗品空槽
+所有食物倍率+0.1</t>
+  </si>
+  <si>
+    <t>结算开始
+处于边缘的食物
+分数+50</t>
+  </si>
+  <si>
+    <t>结算开始
+处于非边缘的食物
+倍率+0.5</t>
+  </si>
+  <si>
+    <t>结算开始
+每有5金币
+所有食物分数+1</t>
+  </si>
+  <si>
+    <t>结算开始
+每有1个空格
+所有食物分数+10</t>
+  </si>
+  <si>
+    <t>结算开始
+每有1个未使用的丢弃次数
+所有食物倍率+0.1</t>
+  </si>
+  <si>
+    <t>结算开始
+每有1个未使用的丢弃次数
+所有食物分数+10</t>
+  </si>
+  <si>
+    <t>放弃奖励领取时
+获取食物的运气提升</t>
+  </si>
+  <si>
+    <t>放弃奖励领取时
+获取装饰品的运气提升</t>
+  </si>
+  <si>
+    <t>火热营业结束
+随机1个餐桌格
+将材质复制到相邻1格</t>
+  </si>
+  <si>
+    <t>结算开始
+所有食物均视为蛋糕</t>
+  </si>
+  <si>
+    <t>火热营业结束
+获得1个餐桌格</t>
+  </si>
+  <si>
+    <t>食物结算时
+永久分数+3</t>
+  </si>
+  <si>
+    <t>同种食物结算时
+倍率+0.5</t>
+  </si>
+  <si>
+    <t>删除食谱中最多2个箭头饼干</t>
+  </si>
+  <si>
+    <t>删除食谱中所有箭头饼干</t>
+  </si>
+  <si>
+    <t>将所有食物随机为新的食物</t>
+  </si>
+  <si>
+    <t>丢弃的食物分数永久+15</t>
+  </si>
+  <si>
+    <t>红心上限+1</t>
+  </si>
+  <si>
+    <t>恢复1个红心</t>
+  </si>
+  <si>
+    <t>恢复2个红心</t>
+  </si>
+  <si>
+    <t>抽奖机抽奖所需金币-25%</t>
   </si>
   <si>
     <t>effectType</t>
@@ -1440,10 +1525,10 @@
     <t>item_active_delete_timeline_node</t>
   </si>
   <si>
-    <t>删除单</t>
-  </si>
-  <si>
-    <t>删除1个节点行动</t>
+    <t>移除单</t>
+  </si>
+  <si>
+    <t>移除1个节点行动</t>
   </si>
   <si>
     <t>TimelineDeleteNode</t>
@@ -1640,16 +1725,16 @@
     <t>买装饰品打折20%</t>
   </si>
   <si>
-    <t>删除食物</t>
-  </si>
-  <si>
-    <t>删除食物价格打折20%</t>
+    <t>移除食物</t>
+  </si>
+  <si>
+    <t>移除食物价格打折20%</t>
   </si>
   <si>
     <t>延迟性</t>
   </si>
   <si>
-    <t>删除食物价格固定为30金币</t>
+    <t>移除食物价格固定为30金币</t>
   </si>
   <si>
     <t>不死</t>
@@ -1784,6 +1869,9 @@
     <t>延后所有星级评鉴一天</t>
   </si>
   <si>
+    <t>周数-1</t>
+  </si>
+  <si>
     <t>星级评鉴不参与打乱</t>
   </si>
   <si>
@@ -1967,13 +2055,16 @@
     <t>负面</t>
   </si>
   <si>
-    <t>丢弃</t>
+    <t>移除</t>
+  </si>
+  <si>
+    <t>移除两个诅咒装饰品</t>
   </si>
   <si>
     <t>转化</t>
   </si>
   <si>
-    <t>丢弃所有诅咒装饰品，每丢弃一个获得100金币</t>
+    <t>移除所有诅咒装饰品，每移除一个获得100金币</t>
   </si>
   <si>
     <t>通用负面</t>
@@ -1997,6 +2088,9 @@
     <t>无法删菜</t>
   </si>
   <si>
+    <t>无法再移除食物</t>
+  </si>
+  <si>
     <t>节点失效</t>
   </si>
   <si>
@@ -2097,12 +2191,84 @@
   </si>
   <si>
     <t>要求减少</t>
+  </si>
+  <si>
+    <t>蛋糕效果需求的层数-10</t>
+  </si>
+  <si>
+    <t>风味强化</t>
+  </si>
+  <si>
+    <t>风味加分</t>
+  </si>
+  <si>
+    <t>主动道具槽加分</t>
+  </si>
+  <si>
+    <t>空主动道具槽加分</t>
+  </si>
+  <si>
+    <t>范围判定</t>
+  </si>
+  <si>
+    <t>丢弃次数转钱</t>
+  </si>
+  <si>
+    <t>丢弃次数加分</t>
+  </si>
+  <si>
+    <t>空格加分</t>
+  </si>
+  <si>
+    <t>边缘/非边缘</t>
+  </si>
+  <si>
+    <t>跳过奖励领取</t>
+  </si>
+  <si>
+    <t>格子数加分</t>
+  </si>
+  <si>
+    <t>金币加分</t>
+  </si>
+  <si>
+    <t>第一个结算、最后一个结算</t>
+  </si>
+  <si>
+    <t>营业结算概率材质复制</t>
+  </si>
+  <si>
+    <t>所有食物被视为蛋糕</t>
+  </si>
+  <si>
+    <t>营业结束概率获得格子</t>
+  </si>
+  <si>
+    <t>结算永久加分</t>
+  </si>
+  <si>
+    <t>同种加分</t>
+  </si>
+  <si>
+    <t>连续结算不相同/相同</t>
+  </si>
+  <si>
+    <t>传递额外选择目标</t>
+  </si>
+  <si>
+    <t>移除牌</t>
+  </si>
+  <si>
+    <t>丢弃的牌加分</t>
+  </si>
+  <si>
+    <t>风味额外视为数量</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -2735,7 +2901,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2754,6 +2920,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -3296,7 +3465,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AD104"/>
+  <dimension ref="A1:AD120"/>
   <sheetFormatPr defaultColWidth="9.00735294117647" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="13.0808823529412" style="1" customWidth="1"/>
@@ -3519,7 +3688,7 @@
       <c r="C4" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="10" t="s">
         <v>41</v>
       </c>
       <c r="E4" s="1" t="s">
@@ -3616,7 +3785,7 @@
       <c r="C6" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="10" t="s">
         <v>53</v>
       </c>
       <c r="E6" s="1" t="s">
@@ -3667,7 +3836,7 @@
       <c r="C7" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="10" t="s">
         <v>57</v>
       </c>
       <c r="E7" s="1" t="s">
@@ -3727,23 +3896,23 @@
       <c r="C8" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="10" t="s">
         <v>60</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>43</v>
       </c>
       <c r="G8" s="1">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="I8" s="1">
         <v>100</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K8" s="1">
         <v>0</v>
@@ -3779,45 +3948,45 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" s="12" customFormat="1" ht="17" spans="1:30">
+    <row r="9" s="13" customFormat="1" ht="17" spans="1:30">
       <c r="A9"/>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="C9" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="D9" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="D9" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="E9" s="12" t="s">
+      <c r="E9" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="F9" s="12" t="s">
+      <c r="F9" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="G9" s="12">
+      <c r="G9" s="13">
         <v>1</v>
       </c>
-      <c r="I9" s="12">
+      <c r="I9" s="13">
         <v>300</v>
       </c>
-      <c r="J9" s="12" t="s">
+      <c r="J9" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="K9" s="12">
-        <v>0</v>
-      </c>
-      <c r="L9" s="12">
-        <v>0</v>
-      </c>
-      <c r="M9" s="12">
-        <v>0</v>
-      </c>
-      <c r="N9" s="12">
-        <v>0</v>
-      </c>
-      <c r="P9" s="12">
+      <c r="K9" s="13">
+        <v>0</v>
+      </c>
+      <c r="L9" s="13">
+        <v>0</v>
+      </c>
+      <c r="M9" s="13">
+        <v>0</v>
+      </c>
+      <c r="N9" s="13">
+        <v>0</v>
+      </c>
+      <c r="P9" s="13">
         <v>50</v>
       </c>
       <c r="R9"/>
@@ -3831,46 +4000,46 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" s="12" customFormat="1" ht="17" spans="1:30">
+    <row r="10" s="13" customFormat="1" ht="17" spans="1:30">
       <c r="A10"/>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="C10" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="D10" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="E10" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="D10" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="E10" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="F10" s="12" t="s">
+      <c r="F10" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="G10" s="12">
+      <c r="G10" s="13">
         <v>1</v>
       </c>
       <c r="H10"/>
-      <c r="I10" s="12">
+      <c r="I10" s="13">
         <v>300</v>
       </c>
-      <c r="J10" s="12" t="s">
+      <c r="J10" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="K10" s="12">
-        <v>0</v>
-      </c>
-      <c r="L10" s="12">
-        <v>0</v>
-      </c>
-      <c r="M10" s="12">
-        <v>0</v>
-      </c>
-      <c r="N10" s="12">
-        <v>0</v>
-      </c>
-      <c r="P10" s="12">
+      <c r="K10" s="13">
+        <v>0</v>
+      </c>
+      <c r="L10" s="13">
+        <v>0</v>
+      </c>
+      <c r="M10" s="13">
+        <v>0</v>
+      </c>
+      <c r="N10" s="13">
+        <v>0</v>
+      </c>
+      <c r="P10" s="13">
         <v>50</v>
       </c>
       <c r="R10"/>
@@ -3884,89 +4053,89 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" s="12" customFormat="1" ht="17" spans="1:18">
+    <row r="11" s="13" customFormat="1" ht="17" spans="1:18">
       <c r="A11"/>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="C11" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="D11" s="13" t="s">
+      <c r="D11" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="E11" s="12" t="s">
+      <c r="E11" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="F11" s="12" t="s">
+      <c r="F11" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="G11" s="12">
+      <c r="G11" s="13">
         <v>2</v>
       </c>
-      <c r="I11" s="12">
+      <c r="I11" s="13">
         <v>100</v>
       </c>
-      <c r="J11" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="K11" s="12">
-        <v>0</v>
-      </c>
-      <c r="L11" s="12">
-        <v>0</v>
-      </c>
-      <c r="M11" s="12">
-        <v>0</v>
-      </c>
-      <c r="N11" s="12">
-        <v>0</v>
-      </c>
-      <c r="P11" s="12">
+      <c r="J11" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="K11" s="13">
+        <v>0</v>
+      </c>
+      <c r="L11" s="13">
+        <v>0</v>
+      </c>
+      <c r="M11" s="13">
+        <v>0</v>
+      </c>
+      <c r="N11" s="13">
+        <v>0</v>
+      </c>
+      <c r="P11" s="13">
         <v>80</v>
       </c>
       <c r="R11"/>
     </row>
-    <row r="12" s="12" customFormat="1" ht="17" spans="1:27">
+    <row r="12" s="13" customFormat="1" ht="17" spans="1:27">
       <c r="A12"/>
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="D12" s="13" t="s">
+      <c r="D12" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="E12" s="12" t="s">
+      <c r="E12" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="F12" s="12" t="s">
+      <c r="F12" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="G12" s="12">
+      <c r="G12" s="13">
         <v>2</v>
       </c>
       <c r="H12"/>
-      <c r="I12" s="12">
+      <c r="I12" s="13">
         <v>30</v>
       </c>
-      <c r="J12" s="12" t="s">
+      <c r="J12" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="K12" s="12">
-        <v>0</v>
-      </c>
-      <c r="L12" s="12">
-        <v>0</v>
-      </c>
-      <c r="M12" s="12">
-        <v>0</v>
-      </c>
-      <c r="N12" s="12">
-        <v>0</v>
-      </c>
-      <c r="P12" s="12">
+      <c r="K12" s="13">
+        <v>0</v>
+      </c>
+      <c r="L12" s="13">
+        <v>0</v>
+      </c>
+      <c r="M12" s="13">
+        <v>0</v>
+      </c>
+      <c r="N12" s="13">
+        <v>0</v>
+      </c>
+      <c r="P12" s="13">
         <v>120</v>
       </c>
       <c r="R12"/>
@@ -3974,46 +4143,46 @@
       <c r="Z12"/>
       <c r="AA12"/>
     </row>
-    <row r="13" s="12" customFormat="1" ht="17" spans="1:23">
+    <row r="13" s="13" customFormat="1" ht="17" spans="1:23">
       <c r="A13"/>
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="D13" s="13" t="s">
+      <c r="D13" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="E13" s="12" t="s">
+      <c r="E13" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="F13" s="12" t="s">
+      <c r="F13" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="G13" s="12">
-        <v>0.1</v>
+      <c r="G13" s="13">
+        <v>0.15</v>
       </c>
       <c r="H13"/>
-      <c r="I13" s="12">
+      <c r="I13" s="13">
         <v>100</v>
       </c>
-      <c r="J13" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="K13" s="12">
-        <v>0</v>
-      </c>
-      <c r="L13" s="12">
-        <v>0</v>
-      </c>
-      <c r="M13" s="12">
-        <v>0</v>
-      </c>
-      <c r="N13" s="12">
-        <v>0</v>
-      </c>
-      <c r="P13" s="12">
+      <c r="J13" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="K13" s="13">
+        <v>0</v>
+      </c>
+      <c r="L13" s="13">
+        <v>0</v>
+      </c>
+      <c r="M13" s="13">
+        <v>0</v>
+      </c>
+      <c r="N13" s="13">
+        <v>0</v>
+      </c>
+      <c r="P13" s="13">
         <v>40</v>
       </c>
       <c r="R13">
@@ -4024,46 +4193,46 @@
       <c r="V13"/>
       <c r="W13"/>
     </row>
-    <row r="14" s="12" customFormat="1" spans="1:25">
+    <row r="14" s="13" customFormat="1" spans="1:25">
       <c r="A14"/>
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="E14" s="12" t="s">
+      <c r="E14" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="F14" s="12" t="s">
+      <c r="F14" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="G14" s="12">
+      <c r="G14" s="13">
         <v>0.15</v>
       </c>
       <c r="H14"/>
-      <c r="I14" s="12">
+      <c r="I14" s="13">
         <v>300</v>
       </c>
-      <c r="J14" s="12" t="s">
+      <c r="J14" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="K14" s="12">
-        <v>0</v>
-      </c>
-      <c r="L14" s="12">
-        <v>0</v>
-      </c>
-      <c r="M14" s="12">
-        <v>0</v>
-      </c>
-      <c r="N14" s="12">
-        <v>0</v>
-      </c>
-      <c r="P14" s="12">
+      <c r="K14" s="13">
+        <v>0</v>
+      </c>
+      <c r="L14" s="13">
+        <v>0</v>
+      </c>
+      <c r="M14" s="13">
+        <v>0</v>
+      </c>
+      <c r="N14" s="13">
+        <v>0</v>
+      </c>
+      <c r="P14" s="13">
         <v>40</v>
       </c>
       <c r="R14">
@@ -4083,7 +4252,7 @@
       <c r="C15" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D15" s="9" t="s">
+      <c r="D15" s="10" t="s">
         <v>81</v>
       </c>
       <c r="E15" s="1" t="s">
@@ -4099,7 +4268,7 @@
         <v>100</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K15" s="1">
         <v>0</v>
@@ -4140,7 +4309,7 @@
       <c r="C16" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D16" s="9" t="s">
+      <c r="D16" s="10" t="s">
         <v>84</v>
       </c>
       <c r="E16" s="1" t="s">
@@ -4156,7 +4325,7 @@
         <v>100</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K16" s="1">
         <v>0</v>
@@ -4194,7 +4363,7 @@
       <c r="C17" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="D17" s="9" t="s">
+      <c r="D17" s="10" t="s">
         <v>87</v>
       </c>
       <c r="E17" s="1" t="s">
@@ -4210,7 +4379,7 @@
         <v>100</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K17" s="1">
         <v>0</v>
@@ -4251,7 +4420,7 @@
       <c r="C18" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D18" s="9" t="s">
+      <c r="D18" s="10" t="s">
         <v>90</v>
       </c>
       <c r="E18" s="1" t="s">
@@ -4308,23 +4477,23 @@
       <c r="C19" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="D19" s="9" t="s">
+      <c r="D19" s="10" t="s">
         <v>93</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>43</v>
       </c>
       <c r="G19" s="1">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="I19" s="1">
         <v>100</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K19" s="1">
         <v>0</v>
@@ -4365,11 +4534,11 @@
       <c r="C20" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="D20" s="9" t="s">
+      <c r="D20" s="10" t="s">
         <v>96</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>43</v>
@@ -4422,11 +4591,11 @@
       <c r="C21" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="D21" s="9" t="s">
+      <c r="D21" s="10" t="s">
         <v>99</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>43</v>
@@ -4438,7 +4607,7 @@
         <v>100</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K21" s="1">
         <v>0</v>
@@ -4479,11 +4648,11 @@
       <c r="C22" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="D22" s="9" t="s">
+      <c r="D22" s="10" t="s">
         <v>102</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>43</v>
@@ -4495,7 +4664,7 @@
         <v>100</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K22" s="1">
         <v>0</v>
@@ -4533,11 +4702,11 @@
       <c r="C23" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="D23" s="9" t="s">
+      <c r="D23" s="10" t="s">
         <v>105</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>43</v>
@@ -4549,7 +4718,7 @@
         <v>100</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K23" s="1">
         <v>0</v>
@@ -4590,11 +4759,11 @@
       <c r="C24" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D24" s="9" t="s">
+      <c r="D24" s="10" t="s">
         <v>108</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>43</v>
@@ -4647,7 +4816,7 @@
       <c r="C25" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="D25" s="9" t="s">
+      <c r="D25" s="10" t="s">
         <v>111</v>
       </c>
       <c r="E25" s="1" t="s">
@@ -4704,11 +4873,11 @@
       <c r="C26" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="D26" s="9" t="s">
+      <c r="D26" s="10" t="s">
         <v>114</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>43</v>
@@ -4720,7 +4889,7 @@
         <v>100</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K26" s="1">
         <v>0</v>
@@ -4758,11 +4927,11 @@
       <c r="C27" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="D27" s="9" t="s">
+      <c r="D27" s="10" t="s">
         <v>117</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>43</v>
@@ -4774,7 +4943,7 @@
         <v>100</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K27" s="1">
         <v>0</v>
@@ -4812,11 +4981,11 @@
       <c r="C28" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="D28" s="9" t="s">
+      <c r="D28" s="10" t="s">
         <v>120</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>43</v>
@@ -4872,7 +5041,7 @@
       <c r="C29" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="D29" s="9" t="s">
+      <c r="D29" s="10" t="s">
         <v>124</v>
       </c>
       <c r="E29" s="1" t="s">
@@ -4929,7 +5098,7 @@
       <c r="C30" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="D30" s="9" t="s">
+      <c r="D30" s="10" t="s">
         <v>127</v>
       </c>
       <c r="E30" s="1" t="s">
@@ -4945,7 +5114,7 @@
         <v>100</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K30" s="1">
         <v>0</v>
@@ -4986,11 +5155,11 @@
       <c r="C31" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="D31" s="9" t="s">
+      <c r="D31" s="10" t="s">
         <v>130</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>43</v>
@@ -5043,11 +5212,11 @@
       <c r="C32" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="D32" s="9" t="s">
+      <c r="D32" s="10" t="s">
         <v>133</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>43</v>
@@ -5062,7 +5231,7 @@
         <v>100</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K32" s="1">
         <v>0</v>
@@ -5103,11 +5272,11 @@
       <c r="C33" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="D33" s="9" t="s">
+      <c r="D33" s="10" t="s">
         <v>137</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>43</v>
@@ -5155,45 +5324,45 @@
       <c r="AC33"/>
       <c r="AD33"/>
     </row>
-    <row r="34" s="12" customFormat="1" ht="34" spans="1:18">
+    <row r="34" s="13" customFormat="1" ht="34" spans="1:18">
       <c r="A34"/>
-      <c r="B34" s="12" t="s">
+      <c r="B34" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="C34" s="12" t="s">
+      <c r="C34" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="D34" s="13" t="s">
+      <c r="D34" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="E34" s="12" t="s">
+      <c r="E34" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="F34" s="12" t="s">
+      <c r="F34" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="G34" s="12">
-        <v>10</v>
-      </c>
-      <c r="I34" s="12">
+      <c r="G34" s="13">
+        <v>20</v>
+      </c>
+      <c r="I34" s="13">
         <v>100</v>
       </c>
-      <c r="J34" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="K34" s="12">
-        <v>0</v>
-      </c>
-      <c r="L34" s="12">
-        <v>0</v>
-      </c>
-      <c r="M34" s="12">
-        <v>0</v>
-      </c>
-      <c r="N34" s="12">
-        <v>0</v>
-      </c>
-      <c r="P34" s="12">
+      <c r="J34" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="K34" s="13">
+        <v>0</v>
+      </c>
+      <c r="L34" s="13">
+        <v>0</v>
+      </c>
+      <c r="M34" s="13">
+        <v>0</v>
+      </c>
+      <c r="N34" s="13">
+        <v>0</v>
+      </c>
+      <c r="P34" s="13">
         <v>40</v>
       </c>
       <c r="R34">
@@ -5201,7 +5370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" s="12" customFormat="1" ht="34" spans="1:16">
+    <row r="35" s="13" customFormat="1" ht="34" spans="1:16">
       <c r="A35" s="1"/>
       <c r="B35" s="1" t="s">
         <v>142</v>
@@ -5209,24 +5378,24 @@
       <c r="C35" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D35" s="13" t="s">
+      <c r="D35" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="E35" s="12" t="s">
-        <v>61</v>
+      <c r="E35" s="13" t="s">
+        <v>67</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>43</v>
       </c>
       <c r="G35" s="1">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="1">
         <v>100</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K35" s="1">
         <v>0</v>
@@ -5245,46 +5414,46 @@
         <v>80</v>
       </c>
     </row>
-    <row r="36" s="12" customFormat="1" ht="34" spans="1:20">
+    <row r="36" s="13" customFormat="1" ht="34" spans="1:20">
       <c r="A36"/>
-      <c r="B36" s="12" t="s">
+      <c r="B36" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="C36" s="12" t="s">
+      <c r="C36" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="D36" s="13" t="s">
+      <c r="D36" s="14" t="s">
         <v>147</v>
       </c>
-      <c r="E36" s="12" t="s">
+      <c r="E36" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="F36" s="12" t="s">
+      <c r="F36" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="G36" s="12">
+      <c r="G36" s="13">
         <v>15</v>
       </c>
       <c r="H36"/>
-      <c r="I36" s="12">
+      <c r="I36" s="13">
         <v>100</v>
       </c>
-      <c r="J36" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="K36" s="12">
-        <v>0</v>
-      </c>
-      <c r="L36" s="12">
-        <v>0</v>
-      </c>
-      <c r="M36" s="12">
-        <v>0</v>
-      </c>
-      <c r="N36" s="12">
-        <v>0</v>
-      </c>
-      <c r="P36" s="12">
+      <c r="J36" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="K36" s="13">
+        <v>0</v>
+      </c>
+      <c r="L36" s="13">
+        <v>0</v>
+      </c>
+      <c r="M36" s="13">
+        <v>0</v>
+      </c>
+      <c r="N36" s="13">
+        <v>0</v>
+      </c>
+      <c r="P36" s="13">
         <v>40</v>
       </c>
       <c r="R36">
@@ -5301,11 +5470,11 @@
       <c r="C37" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="D37" s="9" t="s">
+      <c r="D37" s="10" t="s">
         <v>150</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>43</v>
@@ -5317,7 +5486,7 @@
         <v>100</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K37" s="1">
         <v>0</v>
@@ -5358,11 +5527,11 @@
       <c r="C38" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="D38" s="9" t="s">
+      <c r="D38" s="10" t="s">
         <v>153</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>43</v>
@@ -5415,7 +5584,7 @@
       <c r="C39" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="D39" s="9" t="s">
+      <c r="D39" s="10" t="s">
         <v>156</v>
       </c>
       <c r="E39" s="1" t="s">
@@ -5434,7 +5603,7 @@
         <v>100</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K39" s="1">
         <v>0</v>
@@ -5475,7 +5644,7 @@
       <c r="C40" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="D40" s="9" t="s">
+      <c r="D40" s="10" t="s">
         <v>160</v>
       </c>
       <c r="E40" s="1" t="s">
@@ -5491,7 +5660,7 @@
         <v>100</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K40" s="1">
         <v>0</v>
@@ -5532,11 +5701,11 @@
       <c r="C41" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="D41" s="9" t="s">
+      <c r="D41" s="10" t="s">
         <v>163</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>43</v>
@@ -5548,7 +5717,7 @@
         <v>100</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K41" s="1">
         <v>0</v>
@@ -5581,7 +5750,7 @@
       <c r="AC41"/>
       <c r="AD41"/>
     </row>
-    <row r="42" s="1" customFormat="1" ht="17" spans="1:30">
+    <row r="42" s="1" customFormat="1" ht="34" spans="1:30">
       <c r="A42"/>
       <c r="B42" s="1" t="s">
         <v>164</v>
@@ -5589,11 +5758,11 @@
       <c r="C42" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="D42" s="9" t="s">
+      <c r="D42" s="10" t="s">
         <v>166</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>167</v>
+        <v>67</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>43</v>
@@ -5601,11 +5770,14 @@
       <c r="G42" s="1">
         <v>1</v>
       </c>
+      <c r="H42" s="1" t="s">
+        <v>167</v>
+      </c>
       <c r="I42" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>168</v>
+        <v>61</v>
       </c>
       <c r="K42" s="1">
         <v>0</v>
@@ -5620,11 +5792,11 @@
         <v>0</v>
       </c>
       <c r="P42" s="1">
-        <v>240</v>
+        <v>80</v>
       </c>
       <c r="Q42"/>
       <c r="R42">
-        <f t="shared" si="6"/>
+        <f>IFERROR(VLOOKUP(E42,$T$7:$AB$12,9,FALSE),0)</f>
         <v>0</v>
       </c>
       <c r="T42"/>
@@ -5638,34 +5810,34 @@
       <c r="AC42"/>
       <c r="AD42"/>
     </row>
-    <row r="43" s="1" customFormat="1" ht="34" spans="1:30">
+    <row r="43" s="1" customFormat="1" ht="51" spans="1:30">
       <c r="A43"/>
       <c r="B43" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="C43" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="D43" s="10" t="s">
         <v>170</v>
       </c>
-      <c r="D43" s="9" t="s">
-        <v>171</v>
-      </c>
       <c r="E43" s="1" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>43</v>
       </c>
       <c r="G43" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I43" s="1">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="K43" s="1">
         <v>0</v>
@@ -5680,11 +5852,11 @@
         <v>0</v>
       </c>
       <c r="P43" s="1">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Q43"/>
       <c r="R43">
-        <f t="shared" si="6"/>
+        <f>IFERROR(VLOOKUP(E43,$T$7:$AB$12,9,FALSE),0)</f>
         <v>0</v>
       </c>
       <c r="T43"/>
@@ -5701,13 +5873,13 @@
     <row r="44" s="1" customFormat="1" ht="51" spans="1:30">
       <c r="A44"/>
       <c r="B44" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="C44" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="D44" s="10" t="s">
         <v>174</v>
-      </c>
-      <c r="D44" s="9" t="s">
-        <v>175</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>48</v>
@@ -5719,7 +5891,7 @@
         <v>3</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I44" s="1">
         <v>300</v>
@@ -5744,7 +5916,7 @@
       </c>
       <c r="Q44"/>
       <c r="R44">
-        <f t="shared" si="6"/>
+        <f>IFERROR(VLOOKUP(E44,$T$7:$AB$12,9,FALSE),0)</f>
         <v>0</v>
       </c>
       <c r="T44"/>
@@ -5758,16 +5930,16 @@
       <c r="AC44"/>
       <c r="AD44"/>
     </row>
-    <row r="45" s="1" customFormat="1" ht="51" spans="1:30">
+    <row r="45" s="1" customFormat="1" ht="17" spans="1:30">
       <c r="A45"/>
       <c r="B45" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C45" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="D45" s="10" t="s">
         <v>178</v>
-      </c>
-      <c r="D45" s="9" t="s">
-        <v>179</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>48</v>
@@ -5776,16 +5948,13 @@
         <v>43</v>
       </c>
       <c r="G45" s="1">
-        <v>3</v>
-      </c>
-      <c r="H45" s="1" t="s">
-        <v>180</v>
+        <v>2</v>
       </c>
       <c r="I45" s="1">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="K45" s="1">
         <v>0</v>
@@ -5804,7 +5973,7 @@
       </c>
       <c r="Q45"/>
       <c r="R45">
-        <f t="shared" si="6"/>
+        <f>IFERROR(VLOOKUP(E45,$T$7:$AB$12,9,FALSE),0)</f>
         <v>0</v>
       </c>
       <c r="T45"/>
@@ -5821,28 +5990,28 @@
     <row r="46" s="1" customFormat="1" ht="17" spans="1:30">
       <c r="A46"/>
       <c r="B46" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D46" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="C46" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="D46" s="9" t="s">
-        <v>183</v>
-      </c>
       <c r="E46" s="1" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>43</v>
       </c>
       <c r="G46" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I46" s="1">
         <v>100</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K46" s="1">
         <v>0</v>
@@ -5857,13 +6026,10 @@
         <v>0</v>
       </c>
       <c r="P46" s="1">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="Q46"/>
-      <c r="R46">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
+      <c r="R46"/>
       <c r="T46"/>
       <c r="U46"/>
       <c r="V46"/>
@@ -5875,31 +6041,31 @@
       <c r="AC46"/>
       <c r="AD46"/>
     </row>
-    <row r="47" s="1" customFormat="1" ht="17" spans="1:30">
+    <row r="47" s="1" customFormat="1" ht="34" spans="1:30">
       <c r="A47"/>
       <c r="B47" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="D47" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="C47" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="D47" s="9" t="s">
-        <v>186</v>
-      </c>
       <c r="E47" s="1" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>43</v>
       </c>
       <c r="G47" s="1">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I47" s="1">
         <v>100</v>
       </c>
       <c r="J47" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K47" s="1">
         <v>0</v>
@@ -5914,10 +6080,13 @@
         <v>0</v>
       </c>
       <c r="P47" s="1">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Q47"/>
-      <c r="R47"/>
+      <c r="R47">
+        <f t="shared" ref="R47:R56" si="7">IFERROR(VLOOKUP(E47,$T$7:$AB$12,9,FALSE),0)</f>
+        <v>0</v>
+      </c>
       <c r="T47"/>
       <c r="U47"/>
       <c r="V47"/>
@@ -5932,28 +6101,28 @@
     <row r="48" s="1" customFormat="1" ht="34" spans="1:30">
       <c r="A48"/>
       <c r="B48" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="D48" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="C48" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="D48" s="9" t="s">
-        <v>189</v>
-      </c>
       <c r="E48" s="1" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>43</v>
       </c>
       <c r="G48" s="1">
-        <v>10</v>
+        <v>400</v>
       </c>
       <c r="I48" s="1">
         <v>100</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K48" s="1">
         <v>0</v>
@@ -5968,11 +6137,11 @@
         <v>0</v>
       </c>
       <c r="P48" s="1">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="Q48"/>
       <c r="R48">
-        <f t="shared" ref="R48:R57" si="7">IFERROR(VLOOKUP(E48,$T$7:$AB$12,9,FALSE),0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T48"/>
@@ -5989,28 +6158,28 @@
     <row r="49" s="1" customFormat="1" ht="34" spans="1:30">
       <c r="A49"/>
       <c r="B49" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="D49" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="C49" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="D49" s="9" t="s">
-        <v>192</v>
-      </c>
       <c r="E49" s="1" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>43</v>
       </c>
       <c r="G49" s="1">
-        <v>400</v>
+        <v>2</v>
       </c>
       <c r="I49" s="1">
         <v>100</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K49" s="1">
         <v>0</v>
@@ -6025,7 +6194,7 @@
         <v>0</v>
       </c>
       <c r="P49" s="1">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Q49"/>
       <c r="R49">
@@ -6043,16 +6212,16 @@
       <c r="AC49"/>
       <c r="AD49"/>
     </row>
-    <row r="50" s="1" customFormat="1" ht="17" spans="1:30">
+    <row r="50" s="1" customFormat="1" ht="34" spans="1:30">
       <c r="A50"/>
       <c r="B50" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="D50" s="10" t="s">
         <v>193</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="D50" s="9" t="s">
-        <v>195</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>48</v>
@@ -6061,13 +6230,13 @@
         <v>43</v>
       </c>
       <c r="G50" s="1">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="I50" s="1">
         <v>100</v>
       </c>
       <c r="J50" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K50" s="1">
         <v>0</v>
@@ -6103,13 +6272,13 @@
     <row r="51" s="1" customFormat="1" ht="34" spans="1:30">
       <c r="A51"/>
       <c r="B51" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="D51" s="10" t="s">
         <v>196</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="D51" s="9" t="s">
-        <v>198</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>48</v>
@@ -6118,13 +6287,13 @@
         <v>43</v>
       </c>
       <c r="G51" s="1">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="I51" s="1">
         <v>100</v>
       </c>
       <c r="J51" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K51" s="1">
         <v>0</v>
@@ -6157,31 +6326,31 @@
       <c r="AC51"/>
       <c r="AD51"/>
     </row>
-    <row r="52" s="1" customFormat="1" ht="34" spans="1:30">
+    <row r="52" s="1" customFormat="1" ht="17" spans="1:30">
       <c r="A52"/>
       <c r="B52" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="D52" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="C52" s="1" t="s">
+      <c r="E52" s="1" t="s">
         <v>200</v>
-      </c>
-      <c r="D52" s="9" t="s">
-        <v>201</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>48</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>43</v>
       </c>
       <c r="G52" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I52" s="1">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="J52" s="1" t="s">
-        <v>62</v>
+        <v>201</v>
       </c>
       <c r="K52" s="1">
         <v>0</v>
@@ -6196,7 +6365,7 @@
         <v>0</v>
       </c>
       <c r="P52" s="1">
-        <v>40</v>
+        <v>240</v>
       </c>
       <c r="Q52"/>
       <c r="R52">
@@ -6214,7 +6383,7 @@
       <c r="AC52"/>
       <c r="AD52"/>
     </row>
-    <row r="53" s="1" customFormat="1" ht="17" spans="1:30">
+    <row r="53" s="1" customFormat="1" ht="34" spans="1:30">
       <c r="A53"/>
       <c r="B53" s="1" t="s">
         <v>202</v>
@@ -6222,23 +6391,23 @@
       <c r="C53" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="D53" s="9" t="s">
+      <c r="D53" s="10" t="s">
         <v>204</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>167</v>
+        <v>48</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>43</v>
       </c>
       <c r="G53" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I53" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="J53" s="1" t="s">
-        <v>168</v>
+        <v>61</v>
       </c>
       <c r="K53" s="1">
         <v>0</v>
@@ -6253,7 +6422,7 @@
         <v>0</v>
       </c>
       <c r="P53" s="1">
-        <v>240</v>
+        <v>40</v>
       </c>
       <c r="Q53"/>
       <c r="R53">
@@ -6279,11 +6448,11 @@
       <c r="C54" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="D54" s="9" t="s">
+      <c r="D54" s="10" t="s">
         <v>207</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>43</v>
@@ -6292,10 +6461,10 @@
         <v>3</v>
       </c>
       <c r="I54" s="1">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="K54" s="1">
         <v>0</v>
@@ -6310,7 +6479,7 @@
         <v>0</v>
       </c>
       <c r="P54" s="1">
-        <v>40</v>
+        <v>150</v>
       </c>
       <c r="Q54"/>
       <c r="R54">
@@ -6328,7 +6497,7 @@
       <c r="AC54"/>
       <c r="AD54"/>
     </row>
-    <row r="55" s="1" customFormat="1" ht="34" spans="1:30">
+    <row r="55" s="1" customFormat="1" ht="17" spans="1:30">
       <c r="A55"/>
       <c r="B55" s="1" t="s">
         <v>208</v>
@@ -6336,7 +6505,7 @@
       <c r="C55" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="D55" s="9" t="s">
+      <c r="D55" s="10" t="s">
         <v>210</v>
       </c>
       <c r="E55" s="1" t="s">
@@ -6346,7 +6515,7 @@
         <v>43</v>
       </c>
       <c r="G55" s="1">
-        <v>3</v>
+        <v>0.4</v>
       </c>
       <c r="I55" s="1">
         <v>30</v>
@@ -6385,7 +6554,7 @@
       <c r="AC55"/>
       <c r="AD55"/>
     </row>
-    <row r="56" s="1" customFormat="1" ht="34" spans="1:30">
+    <row r="56" s="1" customFormat="1" ht="17" spans="1:30">
       <c r="A56"/>
       <c r="B56" s="1" t="s">
         <v>211</v>
@@ -6393,11 +6562,11 @@
       <c r="C56" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="D56" s="9" t="s">
+      <c r="D56" s="10" t="s">
         <v>213</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>43</v>
@@ -6406,10 +6575,10 @@
         <v>0.4</v>
       </c>
       <c r="I56" s="1">
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="J56" s="1" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="K56" s="1">
         <v>0</v>
@@ -6424,7 +6593,7 @@
         <v>0</v>
       </c>
       <c r="P56" s="1">
-        <v>150</v>
+        <v>40</v>
       </c>
       <c r="Q56"/>
       <c r="R56">
@@ -6442,7 +6611,7 @@
       <c r="AC56"/>
       <c r="AD56"/>
     </row>
-    <row r="57" s="1" customFormat="1" ht="34" spans="1:30">
+    <row r="57" s="1" customFormat="1" ht="17" spans="1:30">
       <c r="A57"/>
       <c r="B57" s="1" t="s">
         <v>214</v>
@@ -6450,7 +6619,7 @@
       <c r="C57" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="D57" s="9" t="s">
+      <c r="D57" s="10" t="s">
         <v>216</v>
       </c>
       <c r="E57" s="1" t="s">
@@ -6460,13 +6629,13 @@
         <v>43</v>
       </c>
       <c r="G57" s="1">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="I57" s="1">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="J57" s="1" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="K57" s="1">
         <v>0</v>
@@ -6484,10 +6653,7 @@
         <v>40</v>
       </c>
       <c r="Q57"/>
-      <c r="R57">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
+      <c r="R57"/>
       <c r="T57"/>
       <c r="U57"/>
       <c r="V57"/>
@@ -6507,23 +6673,23 @@
       <c r="C58" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="D58" s="9" t="s">
+      <c r="D58" s="10" t="s">
         <v>219</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>43</v>
       </c>
       <c r="G58" s="1">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="I58" s="1">
         <v>100</v>
       </c>
       <c r="J58" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K58" s="1">
         <v>0</v>
@@ -6538,7 +6704,7 @@
         <v>0</v>
       </c>
       <c r="P58" s="1">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="Q58"/>
       <c r="R58"/>
@@ -6561,29 +6727,29 @@
       <c r="C59" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="D59" s="9" t="s">
+      <c r="D59" s="10" t="s">
         <v>222</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>43</v>
       </c>
       <c r="G59" s="1">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I59" s="1">
         <v>100</v>
       </c>
       <c r="J59" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K59" s="1">
         <v>0</v>
       </c>
       <c r="L59" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M59" s="1">
         <v>0</v>
@@ -6615,11 +6781,11 @@
       <c r="C60" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="D60" s="9" t="s">
+      <c r="D60" s="10" t="s">
         <v>225</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>43</v>
@@ -6631,19 +6797,19 @@
         <v>100</v>
       </c>
       <c r="J60" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K60" s="1">
         <v>0</v>
       </c>
       <c r="L60" s="1">
+        <v>0</v>
+      </c>
+      <c r="M60" s="1">
+        <v>0</v>
+      </c>
+      <c r="N60" s="1">
         <v>10</v>
-      </c>
-      <c r="M60" s="1">
-        <v>0</v>
-      </c>
-      <c r="N60" s="1">
-        <v>0</v>
       </c>
       <c r="P60" s="1">
         <v>80</v>
@@ -6669,11 +6835,11 @@
       <c r="C61" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="D61" s="9" t="s">
+      <c r="D61" s="10" t="s">
         <v>228</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>43</v>
@@ -6685,7 +6851,7 @@
         <v>100</v>
       </c>
       <c r="J61" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K61" s="1">
         <v>0</v>
@@ -6694,10 +6860,10 @@
         <v>0</v>
       </c>
       <c r="M61" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N61" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="P61" s="1">
         <v>80</v>
@@ -6715,7 +6881,7 @@
       <c r="AC61"/>
       <c r="AD61"/>
     </row>
-    <row r="62" s="1" customFormat="1" ht="17" spans="1:30">
+    <row r="62" s="1" customFormat="1" ht="34" spans="1:30">
       <c r="A62"/>
       <c r="B62" s="1" t="s">
         <v>229</v>
@@ -6723,23 +6889,23 @@
       <c r="C62" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="D62" s="9" t="s">
+      <c r="D62" s="10" t="s">
         <v>231</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>43</v>
       </c>
       <c r="G62" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I62" s="1">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="J62" s="1" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="K62" s="1">
         <v>0</v>
@@ -6748,7 +6914,7 @@
         <v>0</v>
       </c>
       <c r="M62" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N62" s="1">
         <v>0</v>
@@ -6757,7 +6923,10 @@
         <v>80</v>
       </c>
       <c r="Q62"/>
-      <c r="R62"/>
+      <c r="R62">
+        <f t="shared" ref="R62:R75" si="8">IFERROR(VLOOKUP(E62,$T$7:$AB$12,9,FALSE),0)</f>
+        <v>0</v>
+      </c>
       <c r="T62"/>
       <c r="U62"/>
       <c r="V62"/>
@@ -6769,7 +6938,7 @@
       <c r="AC62"/>
       <c r="AD62"/>
     </row>
-    <row r="63" s="1" customFormat="1" ht="34" spans="1:30">
+    <row r="63" s="1" customFormat="1" ht="17" spans="1:30">
       <c r="A63"/>
       <c r="B63" s="1" t="s">
         <v>232</v>
@@ -6777,23 +6946,23 @@
       <c r="C63" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="D63" s="9" t="s">
+      <c r="D63" s="10" t="s">
         <v>234</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>43</v>
       </c>
       <c r="G63" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I63" s="1">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="J63" s="1" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="K63" s="1">
         <v>0</v>
@@ -6808,11 +6977,11 @@
         <v>0</v>
       </c>
       <c r="P63" s="1">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Q63"/>
       <c r="R63">
-        <f t="shared" ref="R63:R76" si="8">IFERROR(VLOOKUP(E63,$T$7:$AB$12,9,FALSE),0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="T63"/>
@@ -6834,7 +7003,7 @@
       <c r="C64" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="D64" s="9" t="s">
+      <c r="D64" s="10" t="s">
         <v>237</v>
       </c>
       <c r="E64" s="1" t="s">
@@ -6865,13 +7034,10 @@
         <v>0</v>
       </c>
       <c r="P64" s="1">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="Q64"/>
-      <c r="R64">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
+      <c r="R64"/>
       <c r="T64"/>
       <c r="U64"/>
       <c r="V64"/>
@@ -6891,7 +7057,7 @@
       <c r="C65" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="D65" s="9" t="s">
+      <c r="D65" s="10" t="s">
         <v>240</v>
       </c>
       <c r="E65" s="1" t="s">
@@ -6937,7 +7103,7 @@
       <c r="AC65"/>
       <c r="AD65"/>
     </row>
-    <row r="66" s="1" customFormat="1" ht="17" spans="1:30">
+    <row r="66" s="1" customFormat="1" ht="34" spans="1:30">
       <c r="A66"/>
       <c r="B66" s="1" t="s">
         <v>241</v>
@@ -6945,23 +7111,23 @@
       <c r="C66" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="D66" s="9" t="s">
+      <c r="D66" s="10" t="s">
         <v>243</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>43</v>
       </c>
       <c r="G66" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I66" s="1">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="J66" s="1" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="K66" s="1">
         <v>0</v>
@@ -6976,10 +7142,13 @@
         <v>0</v>
       </c>
       <c r="P66" s="1">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="Q66"/>
-      <c r="R66"/>
+      <c r="R66">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="T66"/>
       <c r="U66"/>
       <c r="V66"/>
@@ -6999,23 +7168,26 @@
       <c r="C67" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="D67" s="9" t="s">
+      <c r="D67" s="10" t="s">
         <v>246</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>43</v>
       </c>
       <c r="G67" s="1">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="H67" s="1" t="s">
+        <v>247</v>
       </c>
       <c r="I67" s="1">
         <v>100</v>
       </c>
       <c r="J67" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K67" s="1">
         <v>0</v>
@@ -7051,16 +7223,16 @@
     <row r="68" s="1" customFormat="1" ht="34" spans="1:30">
       <c r="A68"/>
       <c r="B68" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="D68" s="9" t="s">
         <v>249</v>
       </c>
+      <c r="D68" s="10" t="s">
+        <v>250</v>
+      </c>
       <c r="E68" s="1" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>43</v>
@@ -7069,13 +7241,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="I68" s="1">
         <v>100</v>
       </c>
       <c r="J68" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K68" s="1">
         <v>0</v>
@@ -7116,26 +7288,23 @@
       <c r="C69" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="D69" s="9" t="s">
+      <c r="D69" s="10" t="s">
         <v>253</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>43</v>
       </c>
       <c r="G69" s="1">
-        <v>0</v>
-      </c>
-      <c r="H69" s="1" t="s">
-        <v>254</v>
+        <v>3</v>
       </c>
       <c r="I69" s="1">
         <v>100</v>
       </c>
       <c r="J69" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K69" s="1">
         <v>0</v>
@@ -7150,7 +7319,7 @@
         <v>0</v>
       </c>
       <c r="P69" s="1">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Q69"/>
       <c r="R69">
@@ -7171,13 +7340,13 @@
     <row r="70" s="1" customFormat="1" ht="34" spans="1:30">
       <c r="A70"/>
       <c r="B70" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C70" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="C70" s="1" t="s">
+      <c r="D70" s="10" t="s">
         <v>256</v>
-      </c>
-      <c r="D70" s="9" t="s">
-        <v>257</v>
       </c>
       <c r="E70" s="1" t="s">
         <v>48</v>
@@ -7186,13 +7355,13 @@
         <v>43</v>
       </c>
       <c r="G70" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I70" s="1">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="J70" s="1" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="K70" s="1">
         <v>0</v>
@@ -7225,31 +7394,31 @@
       <c r="AC70"/>
       <c r="AD70"/>
     </row>
-    <row r="71" s="1" customFormat="1" ht="17" spans="1:30">
+    <row r="71" s="1" customFormat="1" ht="51" spans="1:30">
       <c r="A71"/>
       <c r="B71" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="C71" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="C71" s="1" t="s">
+      <c r="D71" s="10" t="s">
         <v>259</v>
       </c>
-      <c r="D71" s="9" t="s">
-        <v>260</v>
-      </c>
       <c r="E71" s="1" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>43</v>
       </c>
       <c r="G71" s="1">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="I71" s="1">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="J71" s="1" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="K71" s="1">
         <v>0</v>
@@ -7264,7 +7433,7 @@
         <v>0</v>
       </c>
       <c r="P71" s="1">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="Q71"/>
       <c r="R71">
@@ -7282,46 +7451,46 @@
       <c r="AC71"/>
       <c r="AD71"/>
     </row>
-    <row r="72" s="1" customFormat="1" ht="34" spans="1:30">
+    <row r="72" s="1" customFormat="1" ht="17" spans="1:30">
       <c r="A72"/>
       <c r="B72" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="C72" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="C72" s="1" t="s">
+      <c r="D72" s="10" t="s">
         <v>262</v>
       </c>
-      <c r="D72" s="9" t="s">
+      <c r="E72" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="E72" s="1" t="s">
-        <v>61</v>
-      </c>
       <c r="F72" s="1" t="s">
-        <v>43</v>
+        <v>263</v>
       </c>
       <c r="G72" s="1">
+        <v>-0.2</v>
+      </c>
+      <c r="I72" s="1">
+        <v>300</v>
+      </c>
+      <c r="J72" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="K72" s="1">
+        <v>0</v>
+      </c>
+      <c r="L72" s="1">
+        <v>0</v>
+      </c>
+      <c r="M72" s="1">
+        <v>0</v>
+      </c>
+      <c r="N72" s="1">
+        <v>0</v>
+      </c>
+      <c r="P72" s="1">
         <v>40</v>
-      </c>
-      <c r="I72" s="1">
-        <v>100</v>
-      </c>
-      <c r="J72" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="K72" s="1">
-        <v>0</v>
-      </c>
-      <c r="L72" s="1">
-        <v>0</v>
-      </c>
-      <c r="M72" s="1">
-        <v>0</v>
-      </c>
-      <c r="N72" s="1">
-        <v>0</v>
-      </c>
-      <c r="P72" s="1">
-        <v>80</v>
       </c>
       <c r="Q72"/>
       <c r="R72">
@@ -7347,17 +7516,17 @@
       <c r="C73" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="D73" s="9" t="s">
+      <c r="D73" s="10" t="s">
         <v>266</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>48</v>
+        <v>263</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="G73" s="1">
-        <v>-0.2</v>
+        <v>0.2</v>
       </c>
       <c r="I73" s="1">
         <v>300</v>
@@ -7399,22 +7568,22 @@
     <row r="74" s="1" customFormat="1" ht="17" spans="1:30">
       <c r="A74"/>
       <c r="B74" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="C74" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="C74" s="1" t="s">
+      <c r="D74" s="10" t="s">
         <v>269</v>
       </c>
-      <c r="D74" s="9" t="s">
-        <v>270</v>
-      </c>
       <c r="E74" s="1" t="s">
-        <v>48</v>
+        <v>263</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="G74" s="1">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="I74" s="1">
         <v>300</v>
@@ -7456,22 +7625,22 @@
     <row r="75" s="1" customFormat="1" ht="17" spans="1:30">
       <c r="A75"/>
       <c r="B75" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="C75" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="C75" s="1" t="s">
+      <c r="D75" s="10" t="s">
         <v>272</v>
       </c>
-      <c r="D75" s="9" t="s">
-        <v>273</v>
-      </c>
       <c r="E75" s="1" t="s">
-        <v>48</v>
+        <v>263</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="G75" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I75" s="1">
         <v>300</v>
@@ -7513,19 +7682,19 @@
     <row r="76" s="1" customFormat="1" ht="17" spans="1:30">
       <c r="A76"/>
       <c r="B76" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="C76" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="C76" s="1" t="s">
+      <c r="D76" s="10" t="s">
         <v>275</v>
       </c>
-      <c r="D76" s="9" t="s">
-        <v>276</v>
-      </c>
       <c r="E76" s="1" t="s">
-        <v>48</v>
+        <v>263</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="G76" s="1">
         <v>1</v>
@@ -7549,13 +7718,10 @@
         <v>0</v>
       </c>
       <c r="P76" s="1">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="Q76"/>
-      <c r="R76">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
+      <c r="R76"/>
       <c r="T76"/>
       <c r="U76"/>
       <c r="V76"/>
@@ -7567,25 +7733,25 @@
       <c r="AC76"/>
       <c r="AD76"/>
     </row>
-    <row r="77" s="1" customFormat="1" ht="17" spans="1:30">
+    <row r="77" s="1" customFormat="1" ht="34" spans="1:30">
       <c r="A77"/>
       <c r="B77" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="C77" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="C77" s="1" t="s">
+      <c r="D77" s="10" t="s">
         <v>278</v>
       </c>
-      <c r="D77" s="9" t="s">
-        <v>279</v>
-      </c>
       <c r="E77" s="1" t="s">
-        <v>48</v>
+        <v>263</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="G77" s="1">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="I77" s="1">
         <v>300</v>
@@ -7606,10 +7772,13 @@
         <v>0</v>
       </c>
       <c r="P77" s="1">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="Q77"/>
-      <c r="R77"/>
+      <c r="R77">
+        <f t="shared" ref="R77:R81" si="9">IFERROR(VLOOKUP(E77,$T$7:$AB$12,9,FALSE),0)</f>
+        <v>0</v>
+      </c>
       <c r="T77"/>
       <c r="U77"/>
       <c r="V77"/>
@@ -7621,25 +7790,25 @@
       <c r="AC77"/>
       <c r="AD77"/>
     </row>
-    <row r="78" s="1" customFormat="1" ht="34" spans="1:30">
+    <row r="78" s="1" customFormat="1" ht="17" spans="1:30">
       <c r="A78"/>
       <c r="B78" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="C78" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="C78" s="1" t="s">
+      <c r="D78" s="10" t="s">
         <v>281</v>
       </c>
-      <c r="D78" s="9" t="s">
-        <v>282</v>
-      </c>
       <c r="E78" s="1" t="s">
-        <v>48</v>
+        <v>263</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="G78" s="1">
-        <v>-1</v>
+        <v>0.2</v>
       </c>
       <c r="I78" s="1">
         <v>300</v>
@@ -7664,7 +7833,7 @@
       </c>
       <c r="Q78"/>
       <c r="R78">
-        <f t="shared" ref="R78:R82" si="9">IFERROR(VLOOKUP(E78,$T$7:$AB$12,9,FALSE),0)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="T78"/>
@@ -7681,19 +7850,19 @@
     <row r="79" s="1" customFormat="1" ht="17" spans="1:30">
       <c r="A79"/>
       <c r="B79" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="C79" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="C79" s="1" t="s">
+      <c r="D79" s="10" t="s">
         <v>284</v>
       </c>
-      <c r="D79" s="9" t="s">
-        <v>285</v>
-      </c>
       <c r="E79" s="1" t="s">
-        <v>48</v>
+        <v>263</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="G79" s="1">
         <v>0.2</v>
@@ -7738,19 +7907,19 @@
     <row r="80" s="1" customFormat="1" ht="17" spans="1:30">
       <c r="A80"/>
       <c r="B80" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="C80" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="C80" s="1" t="s">
+      <c r="D80" s="10" t="s">
         <v>287</v>
       </c>
-      <c r="D80" s="9" t="s">
-        <v>288</v>
-      </c>
       <c r="E80" s="1" t="s">
-        <v>48</v>
+        <v>263</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="G80" s="1">
         <v>0.2</v>
@@ -7792,25 +7961,25 @@
       <c r="AC80"/>
       <c r="AD80"/>
     </row>
-    <row r="81" s="1" customFormat="1" ht="17" spans="1:30">
+    <row r="81" s="1" customFormat="1" ht="34" spans="1:30">
       <c r="A81"/>
       <c r="B81" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="C81" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="C81" s="1" t="s">
+      <c r="D81" s="10" t="s">
         <v>290</v>
       </c>
-      <c r="D81" s="9" t="s">
-        <v>291</v>
-      </c>
       <c r="E81" s="1" t="s">
-        <v>48</v>
+        <v>263</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="G81" s="1">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="I81" s="1">
         <v>300</v>
@@ -7849,25 +8018,28 @@
       <c r="AC81"/>
       <c r="AD81"/>
     </row>
-    <row r="82" s="1" customFormat="1" ht="34" spans="1:30">
+    <row r="82" s="1" customFormat="1" ht="51" spans="1:30">
       <c r="A82"/>
       <c r="B82" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="C82" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="C82" s="1" t="s">
+      <c r="D82" s="10" t="s">
         <v>293</v>
       </c>
-      <c r="D82" s="9" t="s">
+      <c r="E82" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G82" s="1">
+        <v>2</v>
+      </c>
+      <c r="H82" s="1" t="s">
         <v>294</v>
-      </c>
-      <c r="E82" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F82" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="G82" s="1">
-        <v>0</v>
       </c>
       <c r="I82" s="1">
         <v>300</v>
@@ -7888,13 +8060,10 @@
         <v>0</v>
       </c>
       <c r="P82" s="1">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="Q82"/>
-      <c r="R82">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
+      <c r="R82"/>
       <c r="T82"/>
       <c r="U82"/>
       <c r="V82"/>
@@ -7914,7 +8083,7 @@
       <c r="C83" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="D83" s="9" t="s">
+      <c r="D83" s="10" t="s">
         <v>297</v>
       </c>
       <c r="E83" s="1" t="s">
@@ -7924,16 +8093,13 @@
         <v>43</v>
       </c>
       <c r="G83" s="1">
-        <v>2</v>
-      </c>
-      <c r="H83" s="1" t="s">
-        <v>298</v>
+        <v>0.3</v>
       </c>
       <c r="I83" s="1">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="J83" s="1" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="K83" s="1">
         <v>0</v>
@@ -7948,7 +8114,7 @@
         <v>0</v>
       </c>
       <c r="P83" s="1">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="Q83"/>
       <c r="R83"/>
@@ -7966,28 +8132,28 @@
     <row r="84" s="1" customFormat="1" ht="34" spans="1:30">
       <c r="A84"/>
       <c r="B84" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="C84" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="C84" s="1" t="s">
+      <c r="D84" s="10" t="s">
         <v>300</v>
       </c>
-      <c r="D84" s="9" t="s">
-        <v>301</v>
-      </c>
       <c r="E84" s="1" t="s">
-        <v>42</v>
+        <v>200</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>43</v>
       </c>
       <c r="G84" s="1">
-        <v>0.3</v>
+        <v>2</v>
       </c>
       <c r="I84" s="1">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="J84" s="1" t="s">
-        <v>62</v>
+        <v>201</v>
       </c>
       <c r="K84" s="1">
         <v>0</v>
@@ -8001,11 +8167,17 @@
       <c r="N84" s="1">
         <v>0</v>
       </c>
+      <c r="O84" s="1" t="s">
+        <v>301</v>
+      </c>
       <c r="P84" s="1">
-        <v>80</v>
+        <v>240</v>
       </c>
       <c r="Q84"/>
-      <c r="R84"/>
+      <c r="R84">
+        <f t="shared" ref="R84:R93" si="10">IFERROR(VLOOKUP(E84,$T$7:$AB$12,9,FALSE),0)</f>
+        <v>0</v>
+      </c>
       <c r="T84"/>
       <c r="U84"/>
       <c r="V84"/>
@@ -8017,7 +8189,7 @@
       <c r="AC84"/>
       <c r="AD84"/>
     </row>
-    <row r="85" s="1" customFormat="1" ht="17" spans="1:30">
+    <row r="85" s="1" customFormat="1" ht="34" spans="1:30">
       <c r="A85"/>
       <c r="B85" s="1" t="s">
         <v>302</v>
@@ -8025,23 +8197,23 @@
       <c r="C85" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="D85" s="9" t="s">
+      <c r="D85" s="10" t="s">
         <v>304</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>167</v>
+        <v>42</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>43</v>
       </c>
       <c r="G85" s="1">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="I85" s="1">
         <v>10</v>
       </c>
       <c r="J85" s="1" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="K85" s="1">
         <v>0</v>
@@ -8059,11 +8231,11 @@
         <v>305</v>
       </c>
       <c r="P85" s="1">
-        <v>240</v>
+        <v>150</v>
       </c>
       <c r="Q85"/>
       <c r="R85">
-        <f t="shared" ref="R85:R94" si="10">IFERROR(VLOOKUP(E85,$T$7:$AB$12,9,FALSE),0)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="T85"/>
@@ -8077,7 +8249,7 @@
       <c r="AC85"/>
       <c r="AD85"/>
     </row>
-    <row r="86" s="1" customFormat="1" ht="34" spans="1:30">
+    <row r="86" s="1" customFormat="1" ht="51" spans="1:30">
       <c r="A86"/>
       <c r="B86" s="1" t="s">
         <v>306</v>
@@ -8085,7 +8257,7 @@
       <c r="C86" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="D86" s="9" t="s">
+      <c r="D86" s="10" t="s">
         <v>308</v>
       </c>
       <c r="E86" s="1" t="s">
@@ -8095,13 +8267,13 @@
         <v>43</v>
       </c>
       <c r="G86" s="1">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="I86" s="1">
         <v>10</v>
       </c>
       <c r="J86" s="1" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="K86" s="1">
         <v>0</v>
@@ -8116,7 +8288,7 @@
         <v>0</v>
       </c>
       <c r="O86" s="1" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="P86" s="1">
         <v>150</v>
@@ -8140,13 +8312,13 @@
     <row r="87" s="1" customFormat="1" ht="51" spans="1:30">
       <c r="A87"/>
       <c r="B87" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="C87" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="C87" s="1" t="s">
+      <c r="D87" s="10" t="s">
         <v>311</v>
-      </c>
-      <c r="D87" s="9" t="s">
-        <v>312</v>
       </c>
       <c r="E87" s="1" t="s">
         <v>42</v>
@@ -8155,13 +8327,13 @@
         <v>43</v>
       </c>
       <c r="G87" s="1">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I87" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="J87" s="1" t="s">
-        <v>168</v>
+        <v>61</v>
       </c>
       <c r="K87" s="1">
         <v>0</v>
@@ -8174,9 +8346,6 @@
       </c>
       <c r="N87" s="1">
         <v>0</v>
-      </c>
-      <c r="O87" s="1" t="s">
-        <v>309</v>
       </c>
       <c r="P87" s="1">
         <v>150</v>
@@ -8197,31 +8366,34 @@
       <c r="AC87"/>
       <c r="AD87"/>
     </row>
-    <row r="88" s="1" customFormat="1" ht="51" spans="1:30">
+    <row r="88" s="1" customFormat="1" ht="34" spans="1:30">
       <c r="A88"/>
       <c r="B88" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="C88" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="C88" s="1" t="s">
+      <c r="D88" s="10" t="s">
         <v>314</v>
       </c>
-      <c r="D88" s="9" t="s">
-        <v>315</v>
-      </c>
       <c r="E88" s="1" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>43</v>
       </c>
       <c r="G88" s="1">
-        <v>1</v>
+        <v>15</v>
+      </c>
+      <c r="H88" s="1" t="s">
+        <v>315</v>
       </c>
       <c r="I88" s="1">
         <v>100</v>
       </c>
       <c r="J88" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K88" s="1">
         <v>0</v>
@@ -8235,8 +8407,11 @@
       <c r="N88" s="1">
         <v>0</v>
       </c>
+      <c r="O88" s="1" t="s">
+        <v>305</v>
+      </c>
       <c r="P88" s="1">
-        <v>150</v>
+        <v>80</v>
       </c>
       <c r="Q88"/>
       <c r="R88">
@@ -8262,44 +8437,41 @@
       <c r="C89" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="D89" s="9" t="s">
+      <c r="D89" s="10" t="s">
         <v>318</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>43</v>
       </c>
       <c r="G89" s="1">
-        <v>15</v>
-      </c>
-      <c r="H89" s="1" t="s">
+        <v>0.2</v>
+      </c>
+      <c r="I89" s="1">
+        <v>10</v>
+      </c>
+      <c r="J89" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="K89" s="1">
+        <v>0</v>
+      </c>
+      <c r="L89" s="1">
+        <v>0</v>
+      </c>
+      <c r="M89" s="1">
+        <v>0</v>
+      </c>
+      <c r="N89" s="1">
+        <v>0</v>
+      </c>
+      <c r="O89" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="I89" s="1">
-        <v>100</v>
-      </c>
-      <c r="J89" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="K89" s="1">
-        <v>0</v>
-      </c>
-      <c r="L89" s="1">
-        <v>0</v>
-      </c>
-      <c r="M89" s="1">
-        <v>0</v>
-      </c>
-      <c r="N89" s="1">
-        <v>0</v>
-      </c>
-      <c r="O89" s="1" t="s">
-        <v>309</v>
-      </c>
       <c r="P89" s="1">
-        <v>80</v>
+        <v>240</v>
       </c>
       <c r="Q89"/>
       <c r="R89">
@@ -8325,23 +8497,23 @@
       <c r="C90" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="D90" s="9" t="s">
+      <c r="D90" s="10" t="s">
         <v>322</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>167</v>
+        <v>67</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>43</v>
       </c>
       <c r="G90" s="1">
-        <v>0.2</v>
+        <v>10</v>
       </c>
       <c r="I90" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="J90" s="1" t="s">
-        <v>168</v>
+        <v>61</v>
       </c>
       <c r="K90" s="1">
         <v>0</v>
@@ -8356,10 +8528,10 @@
         <v>0</v>
       </c>
       <c r="O90" s="1" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="P90" s="1">
-        <v>240</v>
+        <v>80</v>
       </c>
       <c r="Q90"/>
       <c r="R90">
@@ -8380,28 +8552,28 @@
     <row r="91" s="1" customFormat="1" ht="34" spans="1:30">
       <c r="A91"/>
       <c r="B91" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="C91" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="C91" s="1" t="s">
+      <c r="D91" s="10" t="s">
         <v>325</v>
       </c>
-      <c r="D91" s="9" t="s">
-        <v>326</v>
-      </c>
       <c r="E91" s="1" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>43</v>
       </c>
       <c r="G91" s="1">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="I91" s="1">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="J91" s="1" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="K91" s="1">
         <v>0</v>
@@ -8416,10 +8588,10 @@
         <v>0</v>
       </c>
       <c r="O91" s="1" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="P91" s="1">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="Q91"/>
       <c r="R91">
@@ -8440,28 +8612,31 @@
     <row r="92" s="1" customFormat="1" ht="34" spans="1:30">
       <c r="A92"/>
       <c r="B92" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="C92" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="C92" s="1" t="s">
+      <c r="D92" s="10" t="s">
         <v>328</v>
       </c>
-      <c r="D92" s="9" t="s">
-        <v>329</v>
-      </c>
       <c r="E92" s="1" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>43</v>
       </c>
       <c r="G92" s="1">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="H92" s="1" t="s">
+        <v>329</v>
       </c>
       <c r="I92" s="1">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="J92" s="1" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="K92" s="1">
         <v>0</v>
@@ -8476,10 +8651,10 @@
         <v>0</v>
       </c>
       <c r="O92" s="1" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="P92" s="1">
-        <v>150</v>
+        <v>80</v>
       </c>
       <c r="Q92"/>
       <c r="R92">
@@ -8497,7 +8672,7 @@
       <c r="AC92"/>
       <c r="AD92"/>
     </row>
-    <row r="93" s="1" customFormat="1" ht="34" spans="1:30">
+    <row r="93" s="1" customFormat="1" ht="17" spans="1:30">
       <c r="A93"/>
       <c r="B93" s="1" t="s">
         <v>330</v>
@@ -8505,26 +8680,23 @@
       <c r="C93" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="D93" s="9" t="s">
+      <c r="D93" s="10" t="s">
         <v>332</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>43</v>
       </c>
       <c r="G93" s="1">
-        <v>10</v>
-      </c>
-      <c r="H93" s="1" t="s">
-        <v>333</v>
+        <v>20</v>
       </c>
       <c r="I93" s="1">
         <v>100</v>
       </c>
       <c r="J93" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K93" s="1">
         <v>0</v>
@@ -8539,7 +8711,7 @@
         <v>0</v>
       </c>
       <c r="O93" s="1" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="P93" s="1">
         <v>80</v>
@@ -8560,55 +8732,16 @@
       <c r="AC93"/>
       <c r="AD93"/>
     </row>
-    <row r="94" s="1" customFormat="1" ht="17" spans="1:30">
+    <row r="94" s="1" customFormat="1" ht="34" spans="1:30">
       <c r="A94"/>
-      <c r="B94" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="C94" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="D94" s="9" t="s">
-        <v>336</v>
+      <c r="D94" s="10" t="s">
+        <v>333</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="F94" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G94" s="1">
-        <v>10</v>
-      </c>
-      <c r="I94" s="1">
-        <v>100</v>
-      </c>
-      <c r="J94" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="K94" s="1">
-        <v>0</v>
-      </c>
-      <c r="L94" s="1">
-        <v>0</v>
-      </c>
-      <c r="M94" s="1">
-        <v>0</v>
-      </c>
-      <c r="N94" s="1">
-        <v>0</v>
-      </c>
-      <c r="O94" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="P94" s="1">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="Q94"/>
-      <c r="R94">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
+      <c r="R94"/>
       <c r="T94"/>
       <c r="U94"/>
       <c r="V94"/>
@@ -8620,33 +8753,228 @@
       <c r="AC94"/>
       <c r="AD94"/>
     </row>
-    <row r="95" s="12" customFormat="1"/>
-    <row r="96" s="12" customFormat="1"/>
-    <row r="97" s="12" customFormat="1"/>
-    <row r="98" s="12" customFormat="1"/>
-    <row r="99" s="12" customFormat="1"/>
-    <row r="100" s="12" customFormat="1"/>
-    <row r="101" s="12" customFormat="1"/>
-    <row r="102" s="12" customFormat="1"/>
-    <row r="103" s="12" customFormat="1"/>
-    <row r="104" s="1" customFormat="1" spans="2:18">
-      <c r="B104" s="12"/>
-      <c r="C104" s="12"/>
-      <c r="D104" s="12"/>
-      <c r="E104" s="12"/>
-      <c r="F104" s="12"/>
-      <c r="G104" s="12"/>
-      <c r="H104" s="12"/>
-      <c r="I104" s="12"/>
-      <c r="J104" s="12"/>
-      <c r="K104" s="12"/>
-      <c r="L104" s="12"/>
-      <c r="M104" s="12"/>
-      <c r="N104" s="12"/>
-      <c r="O104" s="12"/>
-      <c r="P104" s="12"/>
-      <c r="Q104" s="12"/>
-      <c r="R104" s="12"/>
+    <row r="95" s="13" customFormat="1" ht="51" spans="4:5">
+      <c r="D95" s="14" t="s">
+        <v>334</v>
+      </c>
+      <c r="E95" s="13" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="96" s="13" customFormat="1" ht="51" spans="4:5">
+      <c r="D96" s="14" t="s">
+        <v>335</v>
+      </c>
+      <c r="E96" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="97" s="13" customFormat="1" ht="51" spans="4:5">
+      <c r="D97" s="14" t="s">
+        <v>336</v>
+      </c>
+      <c r="E97" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="98" s="13" customFormat="1" ht="51" spans="4:5">
+      <c r="D98" s="14" t="s">
+        <v>337</v>
+      </c>
+      <c r="E98" s="13" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="99" s="13" customFormat="1" ht="51" spans="4:5">
+      <c r="D99" s="14" t="s">
+        <v>338</v>
+      </c>
+      <c r="E99" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="100" s="13" customFormat="1" ht="51" spans="4:5">
+      <c r="D100" s="14" t="s">
+        <v>339</v>
+      </c>
+      <c r="E100" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="101" s="13" customFormat="1" ht="51" spans="4:5">
+      <c r="D101" s="14" t="s">
+        <v>340</v>
+      </c>
+      <c r="E101" s="13" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="102" s="13" customFormat="1" ht="51" spans="4:5">
+      <c r="D102" s="14" t="s">
+        <v>341</v>
+      </c>
+      <c r="E102" s="13" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="103" s="13" customFormat="1" ht="51" spans="4:5">
+      <c r="D103" s="14" t="s">
+        <v>342</v>
+      </c>
+      <c r="E103" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="104" s="1" customFormat="1" ht="51" spans="2:18">
+      <c r="B104" s="13"/>
+      <c r="C104" s="13"/>
+      <c r="D104" s="14" t="s">
+        <v>343</v>
+      </c>
+      <c r="E104" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="F104" s="13"/>
+      <c r="G104" s="13"/>
+      <c r="H104" s="13"/>
+      <c r="I104" s="13"/>
+      <c r="J104" s="13"/>
+      <c r="K104" s="13"/>
+      <c r="L104" s="13"/>
+      <c r="M104" s="13"/>
+      <c r="N104" s="13"/>
+      <c r="O104" s="13"/>
+      <c r="P104" s="13"/>
+      <c r="Q104" s="13"/>
+      <c r="R104" s="13"/>
+    </row>
+    <row r="105" ht="34" spans="4:5">
+      <c r="D105" s="10" t="s">
+        <v>344</v>
+      </c>
+      <c r="E105" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="106" ht="34" spans="4:5">
+      <c r="D106" s="10" t="s">
+        <v>345</v>
+      </c>
+      <c r="E106" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="107" ht="51" spans="4:5">
+      <c r="D107" s="10" t="s">
+        <v>346</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="108" ht="34" spans="4:5">
+      <c r="D108" s="10" t="s">
+        <v>347</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="109" ht="34" spans="4:5">
+      <c r="D109" s="10" t="s">
+        <v>348</v>
+      </c>
+      <c r="E109" s="1" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="110" ht="34" spans="4:5">
+      <c r="D110" s="10" t="s">
+        <v>349</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="111" ht="34" spans="4:5">
+      <c r="D111" s="10" t="s">
+        <v>350</v>
+      </c>
+      <c r="E111" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="112" spans="4:5">
+      <c r="D112" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="E112" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="113" spans="4:5">
+      <c r="D113" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="E113" s="1" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="114" spans="4:5">
+      <c r="D114" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="E114" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="115" spans="4:5">
+      <c r="D115" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="E115" s="13" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="116" spans="4:5">
+      <c r="D116" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="E116" s="13" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="117" spans="4:5">
+      <c r="D117" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="E117" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="118" spans="4:5">
+      <c r="D118" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="E118" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="119" spans="4:5">
+      <c r="D119" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="E119" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="120" spans="4:5">
+      <c r="D120" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="E120" s="13" t="s">
+        <v>67</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8694,7 +9022,7 @@
         <v>5</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>337</v>
+        <v>359</v>
       </c>
       <c r="G1" s="7" t="s">
         <v>6</v>
@@ -8706,10 +9034,10 @@
         <v>8</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>338</v>
+        <v>360</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>339</v>
+        <v>361</v>
       </c>
       <c r="L1" s="7" t="s">
         <v>14</v>
@@ -8718,7 +9046,7 @@
         <v>15</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>340</v>
+        <v>362</v>
       </c>
     </row>
     <row r="2" ht="16.5" customHeight="1" spans="1:14">
@@ -8726,19 +9054,19 @@
         <v>16</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>341</v>
+        <v>363</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>342</v>
+        <v>364</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>343</v>
+        <v>365</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>344</v>
+        <v>366</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>22</v>
@@ -8750,19 +9078,19 @@
         <v>24</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>345</v>
+        <v>367</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>346</v>
+        <v>368</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>347</v>
+        <v>369</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>31</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>348</v>
+        <v>370</v>
       </c>
     </row>
     <row r="3" ht="16.5" customHeight="1" spans="1:14">
@@ -8794,7 +9122,7 @@
         <v>36</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>349</v>
+        <v>371</v>
       </c>
       <c r="K3" s="7" t="s">
         <v>38</v>
@@ -8806,685 +9134,685 @@
         <v>38</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>350</v>
+        <v>372</v>
       </c>
     </row>
     <row r="4" ht="33.75" customHeight="1" spans="2:14">
       <c r="B4" s="7" t="s">
-        <v>351</v>
+        <v>373</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>353</v>
+        <v>374</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>375</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>354</v>
+        <v>376</v>
       </c>
       <c r="G4" s="1">
         <v>0</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>355</v>
+        <v>377</v>
       </c>
       <c r="I4" s="1">
         <v>1</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>356</v>
+        <v>378</v>
       </c>
       <c r="K4" s="1">
         <v>1</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>355</v>
+        <v>377</v>
       </c>
       <c r="M4" s="1">
         <v>50</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>357</v>
+        <v>379</v>
       </c>
     </row>
     <row r="5" ht="33.75" customHeight="1" spans="2:14">
       <c r="B5" s="7" t="s">
-        <v>358</v>
+        <v>380</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>360</v>
+        <v>381</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>382</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>354</v>
+        <v>376</v>
       </c>
       <c r="G5" s="1">
         <v>0</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>361</v>
+        <v>383</v>
       </c>
       <c r="I5" s="1">
         <v>1</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>356</v>
+        <v>378</v>
       </c>
       <c r="K5" s="1">
         <v>1</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>361</v>
+        <v>383</v>
       </c>
       <c r="M5" s="1">
         <v>50</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>357</v>
+        <v>379</v>
       </c>
     </row>
     <row r="6" ht="33.75" customHeight="1" spans="2:14">
       <c r="B6" s="7" t="s">
-        <v>362</v>
+        <v>384</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>364</v>
+        <v>385</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>386</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>354</v>
+        <v>376</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>365</v>
+        <v>387</v>
       </c>
       <c r="I6" s="1">
         <v>1</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>356</v>
+        <v>378</v>
       </c>
       <c r="K6" s="1">
         <v>1</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>365</v>
+        <v>387</v>
       </c>
       <c r="M6" s="1">
         <v>50</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>357</v>
+        <v>379</v>
       </c>
     </row>
     <row r="7" ht="33.75" customHeight="1" spans="2:14">
       <c r="B7" s="7" t="s">
-        <v>366</v>
+        <v>388</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>368</v>
+        <v>389</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>390</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>354</v>
+        <v>376</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>369</v>
+        <v>391</v>
       </c>
       <c r="I7" s="1">
         <v>1</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>356</v>
+        <v>378</v>
       </c>
       <c r="K7" s="1">
         <v>1</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>369</v>
+        <v>391</v>
       </c>
       <c r="M7" s="1">
         <v>50</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>357</v>
+        <v>379</v>
       </c>
     </row>
     <row r="8" ht="33.75" customHeight="1" spans="2:14">
       <c r="B8" s="7" t="s">
-        <v>370</v>
+        <v>392</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>371</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>372</v>
+        <v>393</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>394</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>354</v>
+        <v>376</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>373</v>
+        <v>395</v>
       </c>
       <c r="I8" s="1">
         <v>1</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>356</v>
+        <v>378</v>
       </c>
       <c r="K8" s="1">
         <v>1</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>373</v>
+        <v>395</v>
       </c>
       <c r="M8" s="1">
         <v>50</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>357</v>
+        <v>379</v>
       </c>
     </row>
     <row r="9" ht="33.75" customHeight="1" spans="2:14">
       <c r="B9" s="7" t="s">
-        <v>374</v>
+        <v>396</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>375</v>
-      </c>
-      <c r="D9" s="9" t="s">
+        <v>397</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="F9" s="7" t="s">
         <v>376</v>
       </c>
-      <c r="F9" s="7" t="s">
-        <v>354</v>
-      </c>
       <c r="G9" s="1">
         <v>0</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>377</v>
+        <v>399</v>
       </c>
       <c r="I9" s="1">
         <v>1</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>356</v>
+        <v>378</v>
       </c>
       <c r="K9" s="1">
         <v>1</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>377</v>
+        <v>399</v>
       </c>
       <c r="M9" s="1">
         <v>50</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>357</v>
+        <v>379</v>
       </c>
     </row>
     <row r="10" ht="33.75" customHeight="1" spans="2:14">
       <c r="B10" s="7" t="s">
-        <v>378</v>
+        <v>400</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>379</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>380</v>
+        <v>401</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>402</v>
       </c>
       <c r="E10" t="s">
-        <v>381</v>
+        <v>403</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>382</v>
+        <v>404</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>383</v>
+        <v>405</v>
       </c>
       <c r="I10" s="1">
         <v>1</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>384</v>
+        <v>406</v>
       </c>
       <c r="K10" s="1">
         <v>1</v>
       </c>
       <c r="L10" s="7" t="s">
-        <v>383</v>
+        <v>405</v>
       </c>
       <c r="M10" s="1">
         <v>50</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>357</v>
+        <v>379</v>
       </c>
     </row>
     <row r="11" ht="33.75" customHeight="1" spans="2:14">
       <c r="B11" s="7" t="s">
-        <v>385</v>
+        <v>407</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>387</v>
+        <v>408</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>409</v>
       </c>
       <c r="E11" t="s">
-        <v>381</v>
+        <v>403</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>382</v>
+        <v>404</v>
       </c>
       <c r="G11" s="1">
         <v>0</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>388</v>
+        <v>410</v>
       </c>
       <c r="I11" s="1">
         <v>1</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>384</v>
+        <v>406</v>
       </c>
       <c r="K11" s="1">
         <v>1</v>
       </c>
       <c r="L11" s="7" t="s">
-        <v>388</v>
+        <v>410</v>
       </c>
       <c r="M11" s="1">
         <v>50</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>357</v>
+        <v>379</v>
       </c>
     </row>
     <row r="12" ht="33.75" customHeight="1" spans="2:14">
       <c r="B12" s="7" t="s">
-        <v>389</v>
+        <v>411</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>391</v>
+        <v>412</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>413</v>
       </c>
       <c r="E12" t="s">
-        <v>392</v>
+        <v>414</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>382</v>
+        <v>404</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>393</v>
+        <v>415</v>
       </c>
       <c r="I12" s="1">
         <v>1</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>384</v>
+        <v>406</v>
       </c>
       <c r="K12" s="1">
         <v>1</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>393</v>
+        <v>415</v>
       </c>
       <c r="M12" s="1">
         <v>50</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>357</v>
+        <v>379</v>
       </c>
     </row>
     <row r="13" ht="33.75" customHeight="1" spans="2:14">
       <c r="B13" s="7" t="s">
-        <v>394</v>
+        <v>416</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>396</v>
+        <v>417</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>418</v>
       </c>
       <c r="E13" t="s">
-        <v>392</v>
+        <v>414</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>382</v>
+        <v>404</v>
       </c>
       <c r="G13" s="1">
         <v>0</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>397</v>
+        <v>419</v>
       </c>
       <c r="I13" s="1">
         <v>1</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>384</v>
+        <v>406</v>
       </c>
       <c r="K13" s="1">
         <v>1</v>
       </c>
       <c r="L13" s="7" t="s">
-        <v>397</v>
+        <v>419</v>
       </c>
       <c r="M13" s="1">
         <v>50</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>357</v>
+        <v>379</v>
       </c>
     </row>
     <row r="14" ht="33.75" customHeight="1" spans="2:14">
       <c r="B14" s="7" t="s">
-        <v>398</v>
+        <v>420</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>400</v>
+        <v>421</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>422</v>
       </c>
       <c r="E14" t="s">
-        <v>392</v>
+        <v>414</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>382</v>
+        <v>404</v>
       </c>
       <c r="G14" s="1">
         <v>0</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>401</v>
+        <v>423</v>
       </c>
       <c r="I14" s="1">
         <v>1</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>384</v>
+        <v>406</v>
       </c>
       <c r="K14" s="1">
         <v>1</v>
       </c>
       <c r="L14" s="7" t="s">
-        <v>401</v>
+        <v>423</v>
       </c>
       <c r="M14" s="1">
         <v>50</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>357</v>
+        <v>379</v>
       </c>
     </row>
     <row r="15" ht="33.75" customHeight="1" spans="2:14">
       <c r="B15" s="7" t="s">
-        <v>402</v>
+        <v>424</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="D15" s="9" t="s">
+        <v>425</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>426</v>
+      </c>
+      <c r="E15" t="s">
+        <v>427</v>
+      </c>
+      <c r="F15" s="7" t="s">
         <v>404</v>
       </c>
-      <c r="E15" t="s">
-        <v>405</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>382</v>
-      </c>
       <c r="G15" s="1">
         <v>0</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>406</v>
+        <v>428</v>
       </c>
       <c r="I15" s="1">
         <v>1</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>384</v>
+        <v>406</v>
       </c>
       <c r="K15" s="1">
         <v>1</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>406</v>
+        <v>428</v>
       </c>
       <c r="M15" s="1">
         <v>50</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>357</v>
+        <v>379</v>
       </c>
     </row>
     <row r="16" ht="33.75" customHeight="1" spans="2:14">
       <c r="B16" s="7" t="s">
-        <v>407</v>
+        <v>429</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>408</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>409</v>
+        <v>430</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>431</v>
       </c>
       <c r="E16" t="s">
-        <v>405</v>
+        <v>427</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>382</v>
+        <v>404</v>
       </c>
       <c r="G16" s="1">
         <v>0</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>410</v>
+        <v>432</v>
       </c>
       <c r="I16" s="1">
         <v>1</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>384</v>
+        <v>406</v>
       </c>
       <c r="K16" s="1">
         <v>1</v>
       </c>
       <c r="L16" s="7" t="s">
-        <v>410</v>
+        <v>432</v>
       </c>
       <c r="M16" s="1">
         <v>50</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="17" s="8" customFormat="1" ht="17" spans="2:14">
-      <c r="B17" s="10" t="s">
-        <v>411</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>412</v>
-      </c>
-      <c r="D17" s="11" t="s">
-        <v>413</v>
-      </c>
-      <c r="F17" s="8" t="s">
-        <v>414</v>
-      </c>
-      <c r="G17" s="8">
-        <v>0</v>
-      </c>
-      <c r="I17" s="8">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="17" s="9" customFormat="1" ht="17" spans="2:14">
+      <c r="B17" s="11" t="s">
+        <v>433</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>434</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>435</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>436</v>
+      </c>
+      <c r="G17" s="9">
+        <v>0</v>
+      </c>
+      <c r="I17" s="9">
         <v>1</v>
       </c>
-      <c r="J17" s="8" t="s">
-        <v>415</v>
-      </c>
-      <c r="K17" s="8">
+      <c r="J17" s="9" t="s">
+        <v>437</v>
+      </c>
+      <c r="K17" s="9">
         <v>0</v>
       </c>
       <c r="L17" s="1"/>
-      <c r="M17" s="8">
+      <c r="M17" s="9">
         <v>50</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="18" s="8" customFormat="1" ht="16.5" customHeight="1" spans="2:14">
-      <c r="B18" s="10" t="s">
-        <v>417</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>418</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>419</v>
-      </c>
-      <c r="F18" s="8" t="s">
-        <v>420</v>
-      </c>
-      <c r="G18" s="8">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="18" s="9" customFormat="1" ht="16.5" customHeight="1" spans="2:14">
+      <c r="B18" s="11" t="s">
+        <v>439</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>440</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>441</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>442</v>
+      </c>
+      <c r="G18" s="9">
         <v>0.5</v>
       </c>
-      <c r="I18" s="8">
+      <c r="I18" s="9">
         <v>1</v>
       </c>
-      <c r="J18" s="8" t="s">
-        <v>415</v>
-      </c>
-      <c r="K18" s="8">
+      <c r="J18" s="9" t="s">
+        <v>437</v>
+      </c>
+      <c r="K18" s="9">
         <v>0</v>
       </c>
       <c r="L18" s="1"/>
-      <c r="M18" s="8">
+      <c r="M18" s="9">
         <v>50</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="19" s="8" customFormat="1" ht="16.5" customHeight="1" spans="2:14">
-      <c r="B19" s="10" t="s">
-        <v>421</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>422</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>423</v>
-      </c>
-      <c r="F19" s="8" t="s">
-        <v>424</v>
-      </c>
-      <c r="G19" s="8">
-        <v>0</v>
-      </c>
-      <c r="I19" s="8">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="19" s="9" customFormat="1" ht="16.5" customHeight="1" spans="2:14">
+      <c r="B19" s="11" t="s">
+        <v>443</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>444</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>445</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>446</v>
+      </c>
+      <c r="G19" s="9">
+        <v>0</v>
+      </c>
+      <c r="I19" s="9">
         <v>1</v>
       </c>
-      <c r="J19" s="8" t="s">
-        <v>415</v>
-      </c>
-      <c r="K19" s="8">
+      <c r="J19" s="9" t="s">
+        <v>437</v>
+      </c>
+      <c r="K19" s="9">
         <v>0</v>
       </c>
       <c r="L19" s="1"/>
-      <c r="M19" s="8">
+      <c r="M19" s="9">
         <v>50</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="20" s="8" customFormat="1" ht="16.5" customHeight="1" spans="2:14">
-      <c r="B20" s="10" t="s">
-        <v>425</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>426</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>427</v>
-      </c>
-      <c r="F20" s="8" t="s">
-        <v>428</v>
-      </c>
-      <c r="G20" s="8">
-        <v>0</v>
-      </c>
-      <c r="H20" s="8" t="s">
-        <v>429</v>
-      </c>
-      <c r="I20" s="8">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="20" s="9" customFormat="1" ht="16.5" customHeight="1" spans="2:14">
+      <c r="B20" s="11" t="s">
+        <v>447</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>448</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>449</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>450</v>
+      </c>
+      <c r="G20" s="9">
+        <v>0</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>451</v>
+      </c>
+      <c r="I20" s="9">
         <v>1</v>
       </c>
-      <c r="J20" s="8" t="s">
-        <v>415</v>
-      </c>
-      <c r="K20" s="8">
+      <c r="J20" s="9" t="s">
+        <v>437</v>
+      </c>
+      <c r="K20" s="9">
         <v>1</v>
       </c>
       <c r="L20" s="1"/>
-      <c r="M20" s="8">
+      <c r="M20" s="9">
         <v>50</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="21" s="8" customFormat="1" spans="2:14">
-      <c r="B21" s="8" t="s">
-        <v>430</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>431</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>432</v>
-      </c>
-      <c r="F21" s="8" t="s">
-        <v>433</v>
-      </c>
-      <c r="G21" s="8">
-        <v>0</v>
-      </c>
-      <c r="H21" s="8" t="s">
-        <v>434</v>
-      </c>
-      <c r="I21" s="8">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="21" s="9" customFormat="1" spans="2:14">
+      <c r="B21" s="9" t="s">
+        <v>452</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>453</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>455</v>
+      </c>
+      <c r="G21" s="9">
+        <v>0</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>456</v>
+      </c>
+      <c r="I21" s="9">
         <v>1</v>
       </c>
-      <c r="J21" s="8" t="s">
-        <v>415</v>
-      </c>
-      <c r="K21" s="8">
+      <c r="J21" s="9" t="s">
+        <v>437</v>
+      </c>
+      <c r="K21" s="9">
         <v>1</v>
       </c>
       <c r="L21" s="1"/>
@@ -9492,35 +9820,35 @@
         <v>50</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="22" s="8" customFormat="1" spans="2:14">
-      <c r="B22" s="8" t="s">
-        <v>435</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>436</v>
-      </c>
-      <c r="D22" s="8" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="22" s="9" customFormat="1" spans="2:14">
+      <c r="B22" s="9" t="s">
+        <v>457</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>459</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>460</v>
+      </c>
+      <c r="G22" s="9">
+        <v>0</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>461</v>
+      </c>
+      <c r="I22" s="9">
+        <v>1</v>
+      </c>
+      <c r="J22" s="9" t="s">
         <v>437</v>
       </c>
-      <c r="F22" s="8" t="s">
-        <v>438</v>
-      </c>
-      <c r="G22" s="8">
-        <v>0</v>
-      </c>
-      <c r="H22" s="8" t="s">
-        <v>439</v>
-      </c>
-      <c r="I22" s="8">
-        <v>1</v>
-      </c>
-      <c r="J22" s="8" t="s">
-        <v>415</v>
-      </c>
-      <c r="K22" s="8">
+      <c r="K22" s="9">
         <v>1</v>
       </c>
       <c r="L22" s="1"/>
@@ -9528,35 +9856,35 @@
         <v>50</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="23" s="8" customFormat="1" spans="2:14">
-      <c r="B23" s="8" t="s">
-        <v>440</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>441</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>442</v>
-      </c>
-      <c r="F23" s="8" t="s">
-        <v>443</v>
-      </c>
-      <c r="G23" s="8">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="23" s="9" customFormat="1" spans="2:14">
+      <c r="B23" s="9" t="s">
+        <v>462</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>463</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>464</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>465</v>
+      </c>
+      <c r="G23" s="9">
         <v>0</v>
       </c>
       <c r="H23" t="s">
-        <v>444</v>
-      </c>
-      <c r="I23" s="8">
+        <v>466</v>
+      </c>
+      <c r="I23" s="9">
         <v>1</v>
       </c>
-      <c r="J23" s="8" t="s">
-        <v>415</v>
-      </c>
-      <c r="K23" s="8">
+      <c r="J23" s="9" t="s">
+        <v>437</v>
+      </c>
+      <c r="K23" s="9">
         <v>1</v>
       </c>
       <c r="L23" s="1"/>
@@ -9564,32 +9892,32 @@
         <v>50</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="24" s="8" customFormat="1" spans="2:14">
-      <c r="B24" s="8" t="s">
-        <v>445</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>446</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>447</v>
-      </c>
-      <c r="F24" s="8" t="s">
-        <v>448</v>
-      </c>
-      <c r="G24" s="8">
-        <v>0</v>
-      </c>
-      <c r="I24" s="8">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="24" s="9" customFormat="1" spans="2:14">
+      <c r="B24" s="9" t="s">
+        <v>467</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>468</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>469</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>470</v>
+      </c>
+      <c r="G24" s="9">
+        <v>0</v>
+      </c>
+      <c r="I24" s="9">
         <v>1</v>
       </c>
-      <c r="J24" s="8" t="s">
-        <v>415</v>
-      </c>
-      <c r="K24" s="8">
+      <c r="J24" s="9" t="s">
+        <v>437</v>
+      </c>
+      <c r="K24" s="9">
         <v>1</v>
       </c>
       <c r="L24" s="1"/>
@@ -9597,32 +9925,32 @@
         <v>50</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="25" s="8" customFormat="1" ht="34" spans="2:14">
-      <c r="B25" s="8" t="s">
-        <v>449</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>450</v>
-      </c>
-      <c r="D25" s="11" t="s">
-        <v>451</v>
-      </c>
-      <c r="F25" s="8" t="s">
-        <v>452</v>
-      </c>
-      <c r="G25" s="8">
-        <v>0</v>
-      </c>
-      <c r="I25" s="8">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="25" s="9" customFormat="1" ht="34" spans="2:14">
+      <c r="B25" s="9" t="s">
+        <v>471</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>472</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>473</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>474</v>
+      </c>
+      <c r="G25" s="9">
+        <v>0</v>
+      </c>
+      <c r="I25" s="9">
         <v>1</v>
       </c>
-      <c r="J25" s="8" t="s">
-        <v>415</v>
-      </c>
-      <c r="K25" s="8">
+      <c r="J25" s="9" t="s">
+        <v>437</v>
+      </c>
+      <c r="K25" s="9">
         <v>1</v>
       </c>
       <c r="L25" s="1"/>
@@ -9630,32 +9958,32 @@
         <v>50</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="26" s="8" customFormat="1" ht="34" spans="2:14">
-      <c r="B26" s="8" t="s">
-        <v>453</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>454</v>
-      </c>
-      <c r="D26" s="11" t="s">
-        <v>455</v>
-      </c>
-      <c r="F26" s="8" t="s">
-        <v>456</v>
-      </c>
-      <c r="G26" s="8">
-        <v>0</v>
-      </c>
-      <c r="I26" s="8">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="26" s="9" customFormat="1" ht="34" spans="2:14">
+      <c r="B26" s="9" t="s">
+        <v>475</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>476</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>477</v>
+      </c>
+      <c r="F26" s="9" t="s">
+        <v>478</v>
+      </c>
+      <c r="G26" s="9">
+        <v>0</v>
+      </c>
+      <c r="I26" s="9">
         <v>1</v>
       </c>
-      <c r="J26" s="8" t="s">
-        <v>415</v>
-      </c>
-      <c r="K26" s="8">
+      <c r="J26" s="9" t="s">
+        <v>437</v>
+      </c>
+      <c r="K26" s="9">
         <v>1</v>
       </c>
       <c r="L26" s="1"/>
@@ -9663,7 +9991,7 @@
         <v>50</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>416</v>
+        <v>438</v>
       </c>
     </row>
   </sheetData>
@@ -9675,7 +10003,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B1:U105"/>
+  <dimension ref="B1:U152"/>
   <sheetFormatPr defaultColWidth="9.23529411764706" defaultRowHeight="16.8"/>
   <cols>
     <col min="2" max="3" width="8.46323529411765" customWidth="1"/>
@@ -9687,25 +10015,25 @@
   <sheetData>
     <row r="1" ht="17.25" customHeight="1" spans="2:20">
       <c r="B1" s="3" t="s">
-        <v>457</v>
+        <v>479</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>458</v>
+        <v>480</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>459</v>
+        <v>481</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>460</v>
+        <v>482</v>
       </c>
       <c r="H1" s="7" t="s">
         <v>1</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>461</v>
+        <v>483</v>
       </c>
       <c r="L1" t="s">
-        <v>462</v>
+        <v>484</v>
       </c>
       <c r="M1">
         <v>30</v>
@@ -9734,16 +10062,16 @@
     </row>
     <row r="2" ht="17.25" customHeight="1" spans="2:20">
       <c r="B2" s="3" t="s">
-        <v>463</v>
+        <v>485</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>464</v>
+        <v>486</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>465</v>
+        <v>487</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>466</v>
+        <v>488</v>
       </c>
       <c r="H2" s="1">
         <v>1</v>
@@ -9753,7 +10081,7 @@
         <v>获得时，获得两个随机（xx品质）的装饰品</v>
       </c>
       <c r="L2" t="s">
-        <v>467</v>
+        <v>489</v>
       </c>
       <c r="M2">
         <v>40</v>
@@ -9784,10 +10112,10 @@
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
       <c r="D3" s="3" t="s">
-        <v>468</v>
+        <v>490</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>469</v>
+        <v>491</v>
       </c>
       <c r="H3" s="1">
         <v>2</v>
@@ -9797,7 +10125,7 @@
         <v>获得时，从多个装饰品中选择一个获得</v>
       </c>
       <c r="L3" t="s">
-        <v>470</v>
+        <v>492</v>
       </c>
       <c r="M3">
         <v>50</v>
@@ -9828,10 +10156,10 @@
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
       <c r="D4" s="3" t="s">
-        <v>471</v>
+        <v>493</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>472</v>
+        <v>494</v>
       </c>
       <c r="H4" s="1">
         <v>3</v>
@@ -9845,10 +10173,10 @@
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
       <c r="D5" s="3" t="s">
-        <v>468</v>
+        <v>490</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>473</v>
+        <v>495</v>
       </c>
       <c r="H5" s="1">
         <v>4</v>
@@ -9862,10 +10190,10 @@
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
       <c r="D6" s="3" t="s">
-        <v>474</v>
+        <v>496</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>475</v>
+        <v>497</v>
       </c>
       <c r="H6" s="1">
         <v>5</v>
@@ -9875,17 +10203,17 @@
         <v>获得时，从多个食物中选择一个获得</v>
       </c>
       <c r="Q6" t="s">
-        <v>476</v>
+        <v>498</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1" spans="2:21">
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
       <c r="D7" s="3" t="s">
-        <v>477</v>
+        <v>499</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>478</v>
+        <v>500</v>
       </c>
       <c r="H7" s="1">
         <v>6</v>
@@ -9895,7 +10223,7 @@
         <v>获得时，从多个餐桌格中选择一个获得</v>
       </c>
       <c r="K7" t="s">
-        <v>479</v>
+        <v>501</v>
       </c>
       <c r="M7">
         <v>300</v>
@@ -9904,25 +10232,25 @@
         <v>50</v>
       </c>
       <c r="Q7">
-        <f>COUNTIF(装饰品!$E$4:$E$94,K7)</f>
-        <v>41</v>
+        <f>COUNTIF(装饰品!$E$4:$E$93,K7)</f>
+        <v>35</v>
       </c>
       <c r="S7">
         <v>40</v>
       </c>
       <c r="U7">
         <f>Q7/SUM($Q$7:$Q$10)</f>
-        <v>0.450549450549451</v>
+        <v>0.4375</v>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1" spans="2:21">
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
       <c r="D8" s="3" t="s">
-        <v>480</v>
+        <v>502</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>481</v>
+        <v>503</v>
       </c>
       <c r="H8" s="1">
         <v>7</v>
@@ -9932,17 +10260,17 @@
         <v>获得时，获得一个随机装饰品、随机食物、50金币</v>
       </c>
       <c r="K8" t="s">
-        <v>482</v>
+        <v>504</v>
       </c>
       <c r="M8">
         <v>100</v>
       </c>
       <c r="O8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Q8">
-        <f>COUNTIF(装饰品!$E$4:$E$94,K8)</f>
-        <v>34</v>
+        <f>COUNTIF(装饰品!$E$4:$E$93,K8)</f>
+        <v>29</v>
       </c>
       <c r="S8">
         <v>80</v>
@@ -9955,10 +10283,10 @@
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
       <c r="D9" s="3" t="s">
-        <v>483</v>
+        <v>505</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>484</v>
+        <v>506</v>
       </c>
       <c r="H9" s="1">
         <v>8</v>
@@ -9968,7 +10296,7 @@
         <v>所有装饰品和消耗品替换为随机装饰品和消耗品</v>
       </c>
       <c r="K9" t="s">
-        <v>485</v>
+        <v>507</v>
       </c>
       <c r="M9">
         <v>30</v>
@@ -9977,8 +10305,8 @@
         <v>44</v>
       </c>
       <c r="Q9">
-        <f>COUNTIF(装饰品!$E$4:$E$94,K9)</f>
-        <v>12</v>
+        <f>COUNTIF(装饰品!$E$4:$E$93,K9)</f>
+        <v>14</v>
       </c>
       <c r="S9">
         <v>150</v>
@@ -9990,13 +10318,13 @@
     <row r="10" ht="17.25" customHeight="1" spans="2:21">
       <c r="B10" s="4"/>
       <c r="C10" s="4" t="s">
-        <v>486</v>
+        <v>508</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>487</v>
+        <v>509</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>488</v>
+        <v>510</v>
       </c>
       <c r="H10" s="1">
         <v>9</v>
@@ -10006,17 +10334,17 @@
         <v>获得1～100个金币</v>
       </c>
       <c r="K10" t="s">
-        <v>489</v>
+        <v>511</v>
       </c>
       <c r="M10">
         <v>10</v>
       </c>
       <c r="O10" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="Q10">
-        <f>COUNTIF(装饰品!$E$4:$E$94,K10)</f>
-        <v>4</v>
+        <f>COUNTIF(装饰品!$E$4:$E$93,K10)</f>
+        <v>2</v>
       </c>
       <c r="S10">
         <v>240</v>
@@ -10029,10 +10357,10 @@
       <c r="B11" s="4"/>
       <c r="C11" s="3"/>
       <c r="D11" s="3" t="s">
-        <v>490</v>
+        <v>512</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>491</v>
+        <v>513</v>
       </c>
       <c r="H11" s="1">
         <v>10</v>
@@ -10046,10 +10374,10 @@
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
       <c r="D12" s="3" t="s">
-        <v>492</v>
+        <v>514</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>493</v>
+        <v>515</v>
       </c>
       <c r="H12" s="1">
         <v>11</v>
@@ -10059,23 +10387,23 @@
         <v>完成本次星级评鉴后，额外获得100金币</v>
       </c>
       <c r="P12" t="s">
-        <v>494</v>
+        <v>516</v>
       </c>
       <c r="Q12" t="s">
-        <v>495</v>
+        <v>517</v>
       </c>
       <c r="R12" t="s">
-        <v>496</v>
+        <v>518</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1" spans="2:14">
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
       <c r="D13" s="5" t="s">
-        <v>497</v>
+        <v>519</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>498</v>
+        <v>520</v>
       </c>
       <c r="H13" s="1">
         <v>12</v>
@@ -10089,7 +10417,7 @@
         <v>60</v>
       </c>
       <c r="M13" t="s">
-        <v>499</v>
+        <v>521</v>
       </c>
       <c r="N13">
         <v>240</v>
@@ -10098,13 +10426,13 @@
     <row r="14" ht="17.25" customHeight="1" spans="2:16">
       <c r="B14" s="4"/>
       <c r="C14" s="4" t="s">
-        <v>500</v>
+        <v>522</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>501</v>
+        <v>523</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>502</v>
+        <v>524</v>
       </c>
       <c r="H14" s="1">
         <v>13</v>
@@ -10118,7 +10446,7 @@
         <v>80</v>
       </c>
       <c r="M14" t="s">
-        <v>503</v>
+        <v>525</v>
       </c>
       <c r="N14">
         <v>150</v>
@@ -10131,10 +10459,10 @@
       <c r="B15" s="4"/>
       <c r="C15" s="3"/>
       <c r="D15" s="3" t="s">
-        <v>504</v>
+        <v>526</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>505</v>
+        <v>527</v>
       </c>
       <c r="H15" s="1">
         <v>14</v>
@@ -10148,7 +10476,7 @@
         <v>60</v>
       </c>
       <c r="M15" t="s">
-        <v>506</v>
+        <v>528</v>
       </c>
       <c r="N15">
         <v>80</v>
@@ -10164,10 +10492,10 @@
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
       <c r="D16" s="3" t="s">
-        <v>507</v>
+        <v>529</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>508</v>
+        <v>530</v>
       </c>
       <c r="H16" s="1">
         <v>15</v>
@@ -10177,7 +10505,7 @@
         <v>买消耗品打折20%</v>
       </c>
       <c r="M16" t="s">
-        <v>509</v>
+        <v>531</v>
       </c>
       <c r="N16">
         <v>40</v>
@@ -10193,10 +10521,10 @@
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
       <c r="D17" s="3" t="s">
-        <v>510</v>
+        <v>532</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>511</v>
+        <v>533</v>
       </c>
       <c r="H17" s="1">
         <v>16</v>
@@ -10210,20 +10538,20 @@
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
       <c r="D18" s="3" t="s">
-        <v>512</v>
+        <v>534</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>513</v>
+        <v>535</v>
       </c>
       <c r="H18" s="1">
         <v>17</v>
       </c>
       <c r="I18" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>删除食物价格打折20%</v>
+        <v>移除食物价格打折20%</v>
       </c>
       <c r="M18" t="s">
-        <v>514</v>
+        <v>536</v>
       </c>
       <c r="N18">
         <v>1.4</v>
@@ -10233,29 +10561,29 @@
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
       <c r="D19" s="3" t="s">
-        <v>512</v>
+        <v>534</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>515</v>
+        <v>537</v>
       </c>
       <c r="H19" s="1">
         <v>18</v>
       </c>
       <c r="I19" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>删除食物价格固定为30金币</v>
+        <v>移除食物价格固定为30金币</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1" spans="2:14">
       <c r="B20" s="4"/>
       <c r="C20" s="4" t="s">
-        <v>516</v>
+        <v>538</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>517</v>
+        <v>539</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>518</v>
+        <v>540</v>
       </c>
       <c r="H20" s="1">
         <v>19</v>
@@ -10276,13 +10604,13 @@
     <row r="21" ht="17.25" customHeight="1" spans="2:14">
       <c r="B21" s="4"/>
       <c r="C21" s="4" t="s">
-        <v>519</v>
+        <v>541</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>520</v>
+        <v>542</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>521</v>
+        <v>543</v>
       </c>
       <c r="H21" s="1">
         <v>20</v>
@@ -10300,10 +10628,10 @@
       <c r="B22" s="4"/>
       <c r="C22" s="3"/>
       <c r="D22" s="3" t="s">
-        <v>522</v>
+        <v>544</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>523</v>
+        <v>545</v>
       </c>
       <c r="H22" s="1">
         <v>21</v>
@@ -10321,10 +10649,10 @@
       <c r="B23" s="4"/>
       <c r="C23" s="3"/>
       <c r="D23" s="3" t="s">
-        <v>524</v>
+        <v>546</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>525</v>
+        <v>547</v>
       </c>
       <c r="H23" s="1">
         <v>22</v>
@@ -10338,10 +10666,10 @@
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
       <c r="D24" s="3" t="s">
-        <v>526</v>
+        <v>548</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>527</v>
+        <v>549</v>
       </c>
       <c r="H24" s="1">
         <v>23</v>
@@ -10354,13 +10682,13 @@
     <row r="25" ht="17.25" customHeight="1" spans="2:9">
       <c r="B25" s="4"/>
       <c r="C25" s="4" t="s">
-        <v>528</v>
+        <v>550</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>529</v>
+        <v>551</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>530</v>
+        <v>552</v>
       </c>
       <c r="H25" s="1">
         <v>24</v>
@@ -10374,10 +10702,10 @@
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
       <c r="D26" s="3" t="s">
-        <v>529</v>
+        <v>551</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>531</v>
+        <v>553</v>
       </c>
       <c r="H26" s="1">
         <v>25</v>
@@ -10393,13 +10721,13 @@
     <row r="27" ht="17.25" customHeight="1" spans="2:18">
       <c r="B27" s="4"/>
       <c r="C27" s="3" t="s">
-        <v>532</v>
+        <v>554</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>533</v>
+        <v>555</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>534</v>
+        <v>556</v>
       </c>
       <c r="H27" s="1">
         <v>26</v>
@@ -10415,13 +10743,13 @@
     <row r="28" ht="17.25" customHeight="1" spans="2:9">
       <c r="B28" s="4"/>
       <c r="C28" s="4" t="s">
-        <v>535</v>
+        <v>557</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>536</v>
+        <v>558</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>537</v>
+        <v>559</v>
       </c>
       <c r="H28" s="1">
         <v>27</v>
@@ -10434,13 +10762,13 @@
     <row r="29" ht="17.25" customHeight="1" spans="2:9">
       <c r="B29" s="4"/>
       <c r="C29" s="3" t="s">
-        <v>538</v>
+        <v>560</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>536</v>
+        <v>558</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>539</v>
+        <v>561</v>
       </c>
       <c r="H29" s="1">
         <v>28</v>
@@ -10453,13 +10781,13 @@
     <row r="30" ht="17.25" customHeight="1" spans="2:9">
       <c r="B30" s="4"/>
       <c r="C30" s="3" t="s">
-        <v>540</v>
+        <v>562</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>541</v>
+        <v>563</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>542</v>
+        <v>564</v>
       </c>
       <c r="H30" s="1">
         <v>29</v>
@@ -10473,10 +10801,10 @@
       <c r="B31" s="4"/>
       <c r="C31" s="3"/>
       <c r="D31" s="3" t="s">
-        <v>541</v>
+        <v>563</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>543</v>
+        <v>565</v>
       </c>
       <c r="H31" s="1">
         <v>30</v>
@@ -10489,13 +10817,13 @@
     <row r="32" ht="17.25" customHeight="1" spans="2:9">
       <c r="B32" s="4"/>
       <c r="C32" s="3" t="s">
-        <v>544</v>
+        <v>566</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>544</v>
+        <v>566</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>545</v>
+        <v>567</v>
       </c>
       <c r="H32" s="1">
         <v>31</v>
@@ -10509,10 +10837,10 @@
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
       <c r="D33" s="3" t="s">
-        <v>546</v>
+        <v>568</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>547</v>
+        <v>569</v>
       </c>
       <c r="H33" s="1">
         <v>32</v>
@@ -10526,10 +10854,10 @@
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
       <c r="D34" s="3" t="s">
-        <v>548</v>
+        <v>570</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>549</v>
+        <v>571</v>
       </c>
       <c r="H34" s="1">
         <v>33</v>
@@ -10543,10 +10871,10 @@
       <c r="B35" s="4"/>
       <c r="C35" s="3"/>
       <c r="D35" s="3" t="s">
-        <v>550</v>
+        <v>572</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>551</v>
+        <v>573</v>
       </c>
       <c r="H35" s="1">
         <v>34</v>
@@ -10560,10 +10888,10 @@
       <c r="B36" s="4"/>
       <c r="C36" s="3"/>
       <c r="D36" s="6" t="s">
-        <v>552</v>
+        <v>574</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>553</v>
+        <v>575</v>
       </c>
       <c r="H36" s="1">
         <v>35</v>
@@ -10581,10 +10909,10 @@
       <c r="B37" s="4"/>
       <c r="C37" s="3"/>
       <c r="D37" s="3" t="s">
-        <v>554</v>
+        <v>576</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>555</v>
+        <v>577</v>
       </c>
       <c r="H37" s="1">
         <v>36</v>
@@ -10597,13 +10925,13 @@
     <row r="38" ht="17.25" customHeight="1" spans="2:11">
       <c r="B38" s="4"/>
       <c r="C38" s="3" t="s">
-        <v>556</v>
+        <v>578</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>483</v>
+        <v>505</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>557</v>
+        <v>579</v>
       </c>
       <c r="H38" s="1">
         <v>37</v>
@@ -10621,10 +10949,10 @@
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
       <c r="D39" s="3" t="s">
-        <v>558</v>
+        <v>580</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>559</v>
+        <v>581</v>
       </c>
       <c r="H39" s="1">
         <v>38</v>
@@ -10638,10 +10966,10 @@
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
       <c r="D40" s="3" t="s">
-        <v>166</v>
+        <v>582</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>166</v>
+        <v>582</v>
       </c>
       <c r="H40" s="1">
         <v>39</v>
@@ -10651,17 +10979,17 @@
         <v>周数-1</v>
       </c>
       <c r="K40" t="s">
-        <v>560</v>
+        <v>583</v>
       </c>
     </row>
     <row r="41" ht="17.25" customHeight="1" spans="2:9">
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
       <c r="D41" s="3" t="s">
-        <v>561</v>
+        <v>584</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>562</v>
+        <v>585</v>
       </c>
       <c r="H41" s="1">
         <v>40</v>
@@ -10675,10 +11003,10 @@
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
       <c r="D42" s="3" t="s">
-        <v>563</v>
+        <v>586</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>564</v>
+        <v>587</v>
       </c>
       <c r="H42" s="1">
         <v>41</v>
@@ -10691,13 +11019,13 @@
     <row r="43" ht="17.25" customHeight="1" spans="2:9">
       <c r="B43" s="4"/>
       <c r="C43" s="4" t="s">
-        <v>565</v>
+        <v>588</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>566</v>
+        <v>589</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>567</v>
+        <v>590</v>
       </c>
       <c r="H43" s="1">
         <v>42</v>
@@ -10711,10 +11039,10 @@
       <c r="B44" s="4"/>
       <c r="C44" s="3"/>
       <c r="D44" s="3" t="s">
-        <v>568</v>
+        <v>591</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>569</v>
+        <v>592</v>
       </c>
       <c r="H44" s="1">
         <v>43</v>
@@ -10728,10 +11056,10 @@
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
       <c r="D45" s="3" t="s">
-        <v>570</v>
+        <v>593</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>571</v>
+        <v>594</v>
       </c>
       <c r="H45" s="1">
         <v>44</v>
@@ -10744,13 +11072,13 @@
     <row r="46" ht="17.25" customHeight="1" spans="2:15">
       <c r="B46" s="4"/>
       <c r="C46" s="4" t="s">
-        <v>572</v>
+        <v>595</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>573</v>
+        <v>596</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>574</v>
+        <v>597</v>
       </c>
       <c r="H46" s="1">
         <v>45</v>
@@ -10773,10 +11101,10 @@
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
       <c r="D47" s="3" t="s">
-        <v>486</v>
+        <v>508</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>575</v>
+        <v>598</v>
       </c>
       <c r="H47" s="1">
         <v>46</v>
@@ -10793,10 +11121,10 @@
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
       <c r="D48" s="3" t="s">
-        <v>576</v>
+        <v>599</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>577</v>
+        <v>600</v>
       </c>
       <c r="H48" s="1">
         <v>47</v>
@@ -10809,13 +11137,13 @@
     <row r="49" ht="17.25" customHeight="1" spans="2:9">
       <c r="B49" s="4"/>
       <c r="C49" s="3" t="s">
-        <v>578</v>
+        <v>601</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>579</v>
+        <v>602</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>580</v>
+        <v>603</v>
       </c>
       <c r="H49" s="1">
         <v>48</v>
@@ -10829,10 +11157,10 @@
       <c r="B50" s="4"/>
       <c r="C50" s="4"/>
       <c r="D50" s="3" t="s">
-        <v>581</v>
+        <v>604</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>582</v>
+        <v>605</v>
       </c>
       <c r="H50" s="1">
         <v>49</v>
@@ -10846,10 +11174,10 @@
       <c r="B51" s="4"/>
       <c r="C51" s="4"/>
       <c r="D51" s="3" t="s">
-        <v>583</v>
+        <v>606</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>584</v>
+        <v>607</v>
       </c>
       <c r="H51" s="1">
         <v>50</v>
@@ -10863,10 +11191,10 @@
       <c r="B52" s="4"/>
       <c r="C52" s="3"/>
       <c r="D52" s="3" t="s">
-        <v>585</v>
+        <v>608</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>586</v>
+        <v>609</v>
       </c>
       <c r="H52" s="1">
         <v>51</v>
@@ -10880,10 +11208,10 @@
       <c r="B53" s="4"/>
       <c r="C53" s="4"/>
       <c r="D53" s="3" t="s">
-        <v>587</v>
+        <v>610</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>588</v>
+        <v>611</v>
       </c>
       <c r="H53" s="1">
         <v>52</v>
@@ -10897,10 +11225,10 @@
       <c r="B54" s="4"/>
       <c r="C54" s="4"/>
       <c r="D54" s="3" t="s">
-        <v>589</v>
+        <v>612</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>590</v>
+        <v>613</v>
       </c>
       <c r="H54" s="1">
         <v>53</v>
@@ -10913,13 +11241,13 @@
     <row r="55" ht="17.25" customHeight="1" spans="2:9">
       <c r="B55" s="4"/>
       <c r="C55" s="3" t="s">
-        <v>591</v>
+        <v>614</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>592</v>
+        <v>615</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>593</v>
+        <v>616</v>
       </c>
       <c r="H55" s="1">
         <v>54</v>
@@ -10933,10 +11261,10 @@
       <c r="B56" s="4"/>
       <c r="C56" s="4"/>
       <c r="D56" s="3" t="s">
-        <v>594</v>
+        <v>617</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>595</v>
+        <v>618</v>
       </c>
       <c r="H56" s="1">
         <v>55</v>
@@ -10949,13 +11277,13 @@
     <row r="57" ht="17.25" customHeight="1" spans="2:9">
       <c r="B57" s="4"/>
       <c r="C57" s="4" t="s">
-        <v>596</v>
+        <v>619</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>597</v>
+        <v>620</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>598</v>
+        <v>621</v>
       </c>
       <c r="H57" s="1">
         <v>56</v>
@@ -10969,10 +11297,10 @@
       <c r="B58" s="4"/>
       <c r="C58" s="4"/>
       <c r="D58" s="3" t="s">
-        <v>597</v>
+        <v>620</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>599</v>
+        <v>622</v>
       </c>
       <c r="H58" s="1">
         <v>57</v>
@@ -10986,10 +11314,10 @@
       <c r="B59" s="4"/>
       <c r="C59" s="4"/>
       <c r="D59" s="3" t="s">
-        <v>600</v>
+        <v>623</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>601</v>
+        <v>624</v>
       </c>
       <c r="H59" s="1">
         <v>58</v>
@@ -11003,10 +11331,10 @@
       <c r="B60" s="4"/>
       <c r="C60" s="4"/>
       <c r="D60" s="3" t="s">
-        <v>602</v>
+        <v>625</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>603</v>
+        <v>626</v>
       </c>
       <c r="H60" s="1">
         <v>59</v>
@@ -11020,10 +11348,10 @@
       <c r="B61" s="4"/>
       <c r="C61" s="3"/>
       <c r="D61" s="3" t="s">
-        <v>604</v>
+        <v>627</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>605</v>
+        <v>628</v>
       </c>
       <c r="H61" s="1">
         <v>60</v>
@@ -11036,13 +11364,13 @@
     <row r="62" ht="17.25" customHeight="1" spans="2:9">
       <c r="B62" s="4"/>
       <c r="C62" s="4" t="s">
-        <v>606</v>
+        <v>629</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>607</v>
+        <v>630</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>608</v>
+        <v>631</v>
       </c>
       <c r="H62" s="1">
         <v>61</v>
@@ -11055,13 +11383,13 @@
     <row r="63" ht="17.25" customHeight="1" spans="2:9">
       <c r="B63" s="4"/>
       <c r="C63" s="3" t="s">
-        <v>609</v>
+        <v>632</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>610</v>
+        <v>633</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>611</v>
+        <v>634</v>
       </c>
       <c r="H63" s="1">
         <v>62</v>
@@ -11075,10 +11403,10 @@
       <c r="B64" s="4"/>
       <c r="C64" s="4"/>
       <c r="D64" s="3" t="s">
-        <v>612</v>
+        <v>635</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>613</v>
+        <v>636</v>
       </c>
       <c r="H64" s="1">
         <v>63</v>
@@ -11092,10 +11420,10 @@
       <c r="B65" s="4"/>
       <c r="C65" s="4"/>
       <c r="D65" s="3" t="s">
-        <v>614</v>
+        <v>637</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>615</v>
+        <v>638</v>
       </c>
       <c r="H65" s="1">
         <v>64</v>
@@ -11109,10 +11437,10 @@
       <c r="B66" s="4"/>
       <c r="C66" s="4"/>
       <c r="D66" s="3" t="s">
-        <v>616</v>
+        <v>639</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>617</v>
+        <v>640</v>
       </c>
       <c r="H66" s="1">
         <v>65</v>
@@ -11126,10 +11454,10 @@
       <c r="B67" s="4"/>
       <c r="C67" s="4"/>
       <c r="D67" s="3" t="s">
-        <v>618</v>
+        <v>641</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>619</v>
+        <v>642</v>
       </c>
       <c r="H67" s="1">
         <v>66</v>
@@ -11142,51 +11470,51 @@
     <row r="68" ht="17.25" customHeight="1" spans="2:9">
       <c r="B68" s="4"/>
       <c r="C68" s="3" t="s">
-        <v>620</v>
+        <v>643</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>621</v>
+        <v>644</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>260</v>
+        <v>645</v>
       </c>
       <c r="H68" s="1">
         <v>67</v>
       </c>
       <c r="I68" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>丢弃两个诅咒装饰品</v>
+        <v>移除两个诅咒装饰品</v>
       </c>
     </row>
     <row r="69" ht="17.25" customHeight="1" spans="2:9">
       <c r="B69" s="4"/>
       <c r="C69" s="3"/>
       <c r="D69" s="3" t="s">
-        <v>622</v>
+        <v>646</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>623</v>
+        <v>647</v>
       </c>
       <c r="H69" s="1">
         <v>68</v>
       </c>
       <c r="I69" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>丢弃所有诅咒装饰品，每丢弃一个获得100金币</v>
+        <v>移除所有诅咒装饰品，每移除一个获得100金币</v>
       </c>
     </row>
     <row r="70" ht="17.25" customHeight="1" spans="2:9">
       <c r="B70" s="4" t="s">
-        <v>624</v>
+        <v>648</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>625</v>
+        <v>649</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>626</v>
+        <v>650</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>627</v>
+        <v>651</v>
       </c>
       <c r="H70" s="1">
         <v>69</v>
@@ -11200,10 +11528,10 @@
       <c r="B71" s="4"/>
       <c r="C71" s="4"/>
       <c r="D71" s="3" t="s">
-        <v>628</v>
+        <v>652</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>629</v>
+        <v>653</v>
       </c>
       <c r="H71" s="1">
         <v>70</v>
@@ -11217,27 +11545,27 @@
       <c r="B72" s="4"/>
       <c r="C72" s="4"/>
       <c r="D72" s="3" t="s">
-        <v>630</v>
+        <v>654</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>273</v>
+        <v>655</v>
       </c>
       <c r="H72" s="1">
         <v>71</v>
       </c>
       <c r="I72" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>无法再删除食物</v>
+        <v>无法再移除食物</v>
       </c>
     </row>
     <row r="73" ht="17.25" customHeight="1" spans="2:9">
       <c r="B73" s="4"/>
       <c r="C73" s="4"/>
       <c r="D73" s="3" t="s">
-        <v>631</v>
+        <v>656</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>632</v>
+        <v>657</v>
       </c>
       <c r="H73" s="1">
         <v>72</v>
@@ -11251,10 +11579,10 @@
       <c r="B74" s="4"/>
       <c r="C74" s="3"/>
       <c r="D74" s="3" t="s">
-        <v>633</v>
+        <v>658</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>634</v>
+        <v>659</v>
       </c>
       <c r="H74" s="1">
         <v>73</v>
@@ -11268,10 +11596,10 @@
       <c r="B75" s="4"/>
       <c r="C75" s="3"/>
       <c r="D75" s="3" t="s">
-        <v>635</v>
+        <v>660</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>636</v>
+        <v>661</v>
       </c>
       <c r="H75" s="1">
         <v>74</v>
@@ -11285,10 +11613,10 @@
       <c r="B76" s="3"/>
       <c r="C76" s="3"/>
       <c r="D76" s="3" t="s">
-        <v>637</v>
+        <v>662</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>638</v>
+        <v>663</v>
       </c>
       <c r="H76" s="1">
         <v>75</v>
@@ -11302,10 +11630,10 @@
       <c r="B77" s="4"/>
       <c r="C77" s="4"/>
       <c r="D77" s="3" t="s">
-        <v>639</v>
+        <v>664</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>640</v>
+        <v>665</v>
       </c>
       <c r="H77" s="1">
         <v>76</v>
@@ -11319,10 +11647,10 @@
       <c r="B78" s="4"/>
       <c r="C78" s="4"/>
       <c r="D78" s="3" t="s">
-        <v>641</v>
+        <v>666</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>642</v>
+        <v>667</v>
       </c>
       <c r="H78" s="1">
         <v>77</v>
@@ -11334,16 +11662,16 @@
     </row>
     <row r="79" ht="17.25" customHeight="1" spans="2:9">
       <c r="B79" s="4" t="s">
-        <v>643</v>
+        <v>668</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>644</v>
+        <v>669</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>645</v>
+        <v>670</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>646</v>
+        <v>671</v>
       </c>
       <c r="H79" s="1">
         <v>78</v>
@@ -11356,13 +11684,13 @@
     <row r="80" ht="17.25" customHeight="1" spans="2:9">
       <c r="B80" s="4"/>
       <c r="C80" s="4" t="s">
-        <v>647</v>
+        <v>672</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>648</v>
+        <v>673</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>649</v>
+        <v>674</v>
       </c>
       <c r="H80" s="1">
         <v>79</v>
@@ -11376,10 +11704,10 @@
       <c r="B81" s="4"/>
       <c r="C81" s="4"/>
       <c r="D81" s="3" t="s">
-        <v>648</v>
+        <v>673</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>650</v>
+        <v>675</v>
       </c>
       <c r="H81" s="1">
         <v>80</v>
@@ -11393,10 +11721,10 @@
       <c r="B82" s="4"/>
       <c r="C82" s="4"/>
       <c r="D82" s="3" t="s">
-        <v>651</v>
+        <v>676</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>652</v>
+        <v>677</v>
       </c>
       <c r="H82" s="1">
         <v>81</v>
@@ -11410,10 +11738,10 @@
       <c r="B83" s="4"/>
       <c r="C83" s="4"/>
       <c r="D83" s="3" t="s">
-        <v>653</v>
+        <v>678</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>654</v>
+        <v>679</v>
       </c>
       <c r="H83" s="1">
         <v>82</v>
@@ -11426,13 +11754,13 @@
     <row r="84" ht="17.25" customHeight="1" spans="2:9">
       <c r="B84" s="4"/>
       <c r="C84" s="4" t="s">
-        <v>655</v>
+        <v>680</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>656</v>
+        <v>681</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>657</v>
+        <v>682</v>
       </c>
       <c r="H84" s="1">
         <v>83</v>
@@ -11446,10 +11774,10 @@
       <c r="B85" s="3"/>
       <c r="C85" s="3"/>
       <c r="D85" s="3" t="s">
-        <v>658</v>
+        <v>683</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>659</v>
+        <v>684</v>
       </c>
       <c r="H85" s="1">
         <v>84</v>
@@ -11463,10 +11791,10 @@
       <c r="B86" s="4"/>
       <c r="C86" s="3"/>
       <c r="D86" s="3" t="s">
-        <v>660</v>
+        <v>685</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>661</v>
+        <v>686</v>
       </c>
       <c r="H86" s="1">
         <v>85</v>
@@ -11480,10 +11808,10 @@
       <c r="B87" s="4"/>
       <c r="C87" s="4"/>
       <c r="D87" s="3" t="s">
-        <v>662</v>
+        <v>687</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>663</v>
+        <v>688</v>
       </c>
       <c r="H87" s="1">
         <v>86</v>
@@ -11497,10 +11825,10 @@
       <c r="B88" s="4"/>
       <c r="C88" s="4"/>
       <c r="D88" s="3" t="s">
-        <v>664</v>
+        <v>689</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>336</v>
+        <v>690</v>
       </c>
       <c r="H88" s="1">
         <v>87</v>
@@ -11611,6 +11939,139 @@
       <c r="D105" s="3"/>
       <c r="E105" s="3"/>
     </row>
+    <row r="121" spans="5:5">
+      <c r="E121" s="8"/>
+    </row>
+    <row r="125" spans="5:5">
+      <c r="E125" s="8" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="126" spans="5:5">
+      <c r="E126" s="8" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="127" spans="5:5">
+      <c r="E127" s="8" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="128" spans="5:5">
+      <c r="E128" s="8" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="129" spans="5:5">
+      <c r="E129" s="8" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="130" spans="5:5">
+      <c r="E130" s="8" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="131" spans="5:5">
+      <c r="E131" s="8" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="132" spans="5:5">
+      <c r="E132" s="8" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="133" spans="5:5">
+      <c r="E133" s="8" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="134" spans="5:5">
+      <c r="E134" s="8" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="135" spans="5:5">
+      <c r="E135" s="8" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="136" spans="5:5">
+      <c r="E136" s="8" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="137" spans="5:5">
+      <c r="E137" s="8" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="138" spans="5:5">
+      <c r="E138" s="8" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="139" spans="5:5">
+      <c r="E139" s="8" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="140" spans="5:5">
+      <c r="E140" s="8" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="141" spans="5:5">
+      <c r="E141" s="8" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="142" spans="5:5">
+      <c r="E142" s="8" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="143" spans="5:5">
+      <c r="E143" s="8" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="144" spans="5:5">
+      <c r="E144" s="8" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="145" spans="5:5">
+      <c r="E145" s="8" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="146" spans="5:5">
+      <c r="E146" s="8" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="147" spans="5:5">
+      <c r="E147" s="8" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="148" spans="5:5">
+      <c r="E148" s="8"/>
+    </row>
+    <row r="149" spans="5:5">
+      <c r="E149" s="8"/>
+    </row>
+    <row r="150" spans="5:5">
+      <c r="E150" s="8"/>
+    </row>
+    <row r="151" spans="5:5">
+      <c r="E151" s="8"/>
+    </row>
+    <row r="152" spans="5:5">
+      <c r="E152" s="8"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/GourmetProject/GameConfig/Datas/item.xlsx
+++ b/GourmetProject/GameConfig/Datas/item.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15340"/>
+    <workbookView windowHeight="15360"/>
   </bookViews>
   <sheets>
     <sheet name="装饰品" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1133" uniqueCount="714">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1257" uniqueCount="780">
   <si>
     <t>##var</t>
   </si>
@@ -1078,8 +1078,20 @@
     <t>蛋糕效果需求的层数-20</t>
   </si>
   <si>
+    <t>item_transfer_extra_targets</t>
+  </si>
+  <si>
+    <t>三层糖果塔</t>
+  </si>
+  <si>
     <t>甜蜜传递时
 额外选择2个目标</t>
+  </si>
+  <si>
+    <t>item_flavored_flat</t>
+  </si>
+  <si>
+    <t>风味评分牌</t>
   </si>
   <si>
     <t>结算开始
@@ -1087,57 +1099,156 @@
 分数+30</t>
   </si>
   <si>
+    <t>flavored</t>
+  </si>
+  <si>
+    <t>item_flavored_count_as</t>
+  </si>
+  <si>
+    <t>双层品鉴碟</t>
+  </si>
+  <si>
     <t>结算开始
 拥有风味的食物
 额外视为1份食物</t>
   </si>
   <si>
+    <t>item_active_count_flat_all</t>
+  </si>
+  <si>
+    <t>备品清单板</t>
+  </si>
+  <si>
     <t>结算开始
 每拥有1个消耗品
 所有食物分数+10</t>
   </si>
   <si>
+    <t>basis:active-items</t>
+  </si>
+  <si>
+    <t>item_empty_active_slot_mult_all</t>
+  </si>
+  <si>
+    <t>留白备品柜</t>
+  </si>
+  <si>
     <t>结算开始
 每拥有1个消耗品空槽
 所有食物倍率+0.1</t>
   </si>
   <si>
+    <t>basis:empty-active-slots</t>
+  </si>
+  <si>
+    <t>item_edge_flat</t>
+  </si>
+  <si>
+    <t>滚边桌布</t>
+  </si>
+  <si>
     <t>结算开始
 处于边缘的食物
 分数+50</t>
   </si>
   <si>
+    <t>position:edge</t>
+  </si>
+  <si>
+    <t>item_non_edge_mult</t>
+  </si>
+  <si>
+    <t>中央餐台模型</t>
+  </si>
+  <si>
     <t>结算开始
 处于非边缘的食物
 倍率+0.5</t>
   </si>
   <si>
+    <t>position:non-edge</t>
+  </si>
+  <si>
+    <t>item_gold_per5_flat_all</t>
+  </si>
+  <si>
+    <t>镶币菜单框</t>
+  </si>
+  <si>
     <t>结算开始
 每有5金币
 所有食物分数+1</t>
   </si>
   <si>
+    <t>basis:gold;every:5</t>
+  </si>
+  <si>
+    <t>item_empty_cell_flat_all</t>
+  </si>
+  <si>
+    <t>留白拼桌图</t>
+  </si>
+  <si>
     <t>结算开始
 每有1个空格
 所有食物分数+10</t>
   </si>
   <si>
+    <t>basis:empty-cells</t>
+  </si>
+  <si>
+    <t>item_unused_discard_mult_all</t>
+  </si>
+  <si>
+    <t>备用垃圾袋架</t>
+  </si>
+  <si>
     <t>结算开始
 每有1个未使用的丢弃次数
 所有食物倍率+0.1</t>
   </si>
   <si>
+    <t>item_unused_discard_flat_all</t>
+  </si>
+  <si>
+    <t>磁吸垃圾夹</t>
+  </si>
+  <si>
     <t>结算开始
 每有1个未使用的丢弃次数
 所有食物分数+10</t>
   </si>
   <si>
+    <t>item_skip_reward_dish_luck</t>
+  </si>
+  <si>
+    <t>空盘回执</t>
+  </si>
+  <si>
     <t>放弃奖励领取时
 获取食物的运气提升</t>
   </si>
   <si>
+    <t>purpose:Dish</t>
+  </si>
+  <si>
+    <t>item_skip_reward_passive_luck</t>
+  </si>
+  <si>
+    <t>空柜寄售牌</t>
+  </si>
+  <si>
     <t>放弃奖励领取时
 获取装饰品的运气提升</t>
+  </si>
+  <si>
+    <t>purpose:PassiveItem</t>
+  </si>
+  <si>
+    <t>item_super_material_spread</t>
+  </si>
+  <si>
+    <t>蜂巢桌垫</t>
   </si>
   <si>
     <t>火热营业结束
@@ -1145,41 +1256,128 @@
 将材质复制到相邻1格</t>
   </si>
   <si>
+    <t>item_count_as_cake</t>
+  </si>
+  <si>
+    <t>万能蛋糕模</t>
+  </si>
+  <si>
     <t>结算开始
 所有食物均视为蛋糕</t>
   </si>
   <si>
+    <t>category:cake</t>
+  </si>
+  <si>
+    <t>item_super_fragment_reward</t>
+  </si>
+  <si>
+    <t>折叠加桌券</t>
+  </si>
+  <si>
     <t>火热营业结束
 获得1个餐桌格</t>
   </si>
   <si>
+    <t>fragment_choice_3</t>
+  </si>
+  <si>
+    <t>item_settle_permanent_flat_all</t>
+  </si>
+  <si>
+    <t>老字号记分牌</t>
+  </si>
+  <si>
     <t>食物结算时
 永久分数+3</t>
   </si>
   <si>
+    <t>item_same_base_mult_all</t>
+  </si>
+  <si>
+    <t>双份餐铃</t>
+  </si>
+  <si>
     <t>同种食物结算时
 倍率+0.5</t>
   </si>
   <si>
+    <t>key:baseId;min:2</t>
+  </si>
+  <si>
+    <t>item_remove_arrow_cookie_2</t>
+  </si>
+  <si>
+    <t>饼干回收盒</t>
+  </si>
+  <si>
     <t>删除食谱中最多2个箭头饼干</t>
   </si>
   <si>
+    <t>item_remove_arrow_cookie_all</t>
+  </si>
+  <si>
+    <t>曲奇粉碎机</t>
+  </si>
+  <si>
     <t>删除食谱中所有箭头饼干</t>
   </si>
   <si>
+    <t>item_randomize_recipe_dishes</t>
+  </si>
+  <si>
+    <t>万花筒菜单板</t>
+  </si>
+  <si>
     <t>将所有食物随机为新的食物</t>
   </si>
   <si>
+    <t>item_discard_dish_flat</t>
+  </si>
+  <si>
+    <t>退菜改良簿</t>
+  </si>
+  <si>
     <t>丢弃的食物分数永久+15</t>
   </si>
   <si>
+    <t>item_heart_capacity</t>
+  </si>
+  <si>
+    <t>心形烛台</t>
+  </si>
+  <si>
     <t>红心上限+1</t>
   </si>
   <si>
+    <t>item_heart_capacity_deluxe</t>
+  </si>
+  <si>
+    <t>珐琅心盘</t>
+  </si>
+  <si>
+    <t>item_restore_heart</t>
+  </si>
+  <si>
+    <t>壁挂急救箱</t>
+  </si>
+  <si>
     <t>恢复1个红心</t>
   </si>
   <si>
+    <t>item_restore_hearts</t>
+  </si>
+  <si>
+    <t>全套急救柜</t>
+  </si>
+  <si>
     <t>恢复2个红心</t>
+  </si>
+  <si>
+    <t>item_slot_cost_discount</t>
+  </si>
+  <si>
+    <t>投币优惠牌</t>
   </si>
   <si>
     <t>抽奖机抽奖所需金币-25%</t>
@@ -2901,7 +3099,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2938,6 +3136,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -3543,18 +3744,18 @@
       <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1"/>
-      <c r="R1"/>
-      <c r="T1"/>
-      <c r="U1"/>
-      <c r="V1"/>
-      <c r="W1"/>
-      <c r="X1"/>
-      <c r="Y1"/>
-      <c r="Z1"/>
-      <c r="AA1"/>
-      <c r="AB1"/>
-      <c r="AC1"/>
+      <c r="Q1" s="14"/>
+      <c r="R1" s="14"/>
+      <c r="T1" s="14"/>
+      <c r="U1" s="14"/>
+      <c r="V1" s="14"/>
+      <c r="W1" s="14"/>
+      <c r="X1" s="14"/>
+      <c r="Y1" s="14"/>
+      <c r="Z1" s="14"/>
+      <c r="AA1" s="14"/>
+      <c r="AB1" s="14"/>
+      <c r="AC1" s="14"/>
     </row>
     <row r="2" s="1" customFormat="1" ht="16.5" customHeight="1" spans="1:29">
       <c r="A2" s="1" t="s">
@@ -3605,18 +3806,18 @@
       <c r="P2" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="Q2"/>
-      <c r="R2"/>
-      <c r="T2"/>
-      <c r="U2"/>
-      <c r="V2"/>
-      <c r="W2"/>
-      <c r="X2"/>
-      <c r="Y2"/>
-      <c r="Z2"/>
-      <c r="AA2"/>
-      <c r="AB2"/>
-      <c r="AC2"/>
+      <c r="Q2" s="14"/>
+      <c r="R2" s="14"/>
+      <c r="T2" s="14"/>
+      <c r="U2" s="14"/>
+      <c r="V2" s="14"/>
+      <c r="W2" s="14"/>
+      <c r="X2" s="14"/>
+      <c r="Y2" s="14"/>
+      <c r="Z2" s="14"/>
+      <c r="AA2" s="14"/>
+      <c r="AB2" s="14"/>
+      <c r="AC2" s="14"/>
     </row>
     <row r="3" s="1" customFormat="1" ht="16.5" customHeight="1" spans="1:29">
       <c r="A3" s="1" t="s">
@@ -3667,21 +3868,21 @@
       <c r="P3" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="Q3"/>
-      <c r="R3"/>
-      <c r="T3"/>
-      <c r="U3"/>
-      <c r="V3"/>
-      <c r="W3"/>
-      <c r="X3"/>
-      <c r="Y3"/>
-      <c r="Z3"/>
-      <c r="AA3"/>
-      <c r="AB3"/>
-      <c r="AC3"/>
+      <c r="Q3" s="14"/>
+      <c r="R3" s="14"/>
+      <c r="T3" s="14"/>
+      <c r="U3" s="14"/>
+      <c r="V3" s="14"/>
+      <c r="W3" s="14"/>
+      <c r="X3" s="14"/>
+      <c r="Y3" s="14"/>
+      <c r="Z3" s="14"/>
+      <c r="AA3" s="14"/>
+      <c r="AB3" s="14"/>
+      <c r="AC3" s="14"/>
     </row>
     <row r="4" s="1" customFormat="1" ht="34" spans="1:18">
-      <c r="A4"/>
+      <c r="A4" s="14"/>
       <c r="B4" s="1" t="s">
         <v>39</v>
       </c>
@@ -3721,14 +3922,14 @@
       <c r="P4" s="1">
         <v>150</v>
       </c>
-      <c r="Q4"/>
-      <c r="R4">
+      <c r="Q4" s="14"/>
+      <c r="R4" s="14">
         <f t="shared" ref="R4:R8" si="0">IFERROR(VLOOKUP(E4,$T$7:$AB$12,9,FALSE),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" spans="1:18">
-      <c r="A5"/>
+      <c r="A5" s="14"/>
       <c r="B5" s="1" t="s">
         <v>45</v>
       </c>
@@ -3771,14 +3972,14 @@
       <c r="P5" s="1">
         <v>40</v>
       </c>
-      <c r="Q5"/>
-      <c r="R5">
+      <c r="Q5" s="14"/>
+      <c r="R5" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" ht="34" spans="1:26">
-      <c r="A6"/>
+      <c r="A6" s="14"/>
       <c r="B6" s="1" t="s">
         <v>51</v>
       </c>
@@ -3821,15 +4022,15 @@
       <c r="P6" s="1">
         <v>40</v>
       </c>
-      <c r="Q6"/>
-      <c r="R6">
+      <c r="Q6" s="14"/>
+      <c r="R6" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Z6"/>
+      <c r="Z6" s="14"/>
     </row>
     <row r="7" s="1" customFormat="1" ht="34" spans="1:30">
-      <c r="A7"/>
+      <c r="A7" s="14"/>
       <c r="B7" s="1" t="s">
         <v>55</v>
       </c>
@@ -3869,27 +4070,27 @@
       <c r="P7" s="1">
         <v>40</v>
       </c>
-      <c r="Q7"/>
-      <c r="R7">
+      <c r="Q7" s="14"/>
+      <c r="R7" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="T7"/>
-      <c r="U7"/>
-      <c r="V7"/>
-      <c r="W7"/>
-      <c r="X7"/>
-      <c r="Y7"/>
-      <c r="Z7"/>
-      <c r="AB7"/>
-      <c r="AC7"/>
-      <c r="AD7">
+      <c r="T7" s="14"/>
+      <c r="U7" s="14"/>
+      <c r="V7" s="14"/>
+      <c r="W7" s="14"/>
+      <c r="X7" s="14"/>
+      <c r="Y7" s="14"/>
+      <c r="Z7" s="14"/>
+      <c r="AB7" s="14"/>
+      <c r="AC7" s="14"/>
+      <c r="AD7" s="14">
         <f t="shared" ref="AD7:AD10" si="1">IFERROR(Z7/SUM($Z$7:$Z$10),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="34" spans="1:30">
-      <c r="A8"/>
+      <c r="A8" s="14"/>
       <c r="B8" s="1" t="s">
         <v>58</v>
       </c>
@@ -3929,34 +4130,34 @@
       <c r="P8" s="1">
         <v>80</v>
       </c>
-      <c r="Q8"/>
-      <c r="R8">
+      <c r="Q8" s="14"/>
+      <c r="R8" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="T8"/>
-      <c r="U8"/>
-      <c r="V8"/>
-      <c r="W8"/>
-      <c r="X8"/>
-      <c r="Y8"/>
-      <c r="Z8"/>
-      <c r="AB8"/>
-      <c r="AC8"/>
-      <c r="AD8">
+      <c r="T8" s="14"/>
+      <c r="U8" s="14"/>
+      <c r="V8" s="14"/>
+      <c r="W8" s="14"/>
+      <c r="X8" s="14"/>
+      <c r="Y8" s="14"/>
+      <c r="Z8" s="14"/>
+      <c r="AB8" s="14"/>
+      <c r="AC8" s="14"/>
+      <c r="AD8" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="9" s="13" customFormat="1" ht="17" spans="1:30">
-      <c r="A9"/>
+      <c r="A9" s="14"/>
       <c r="B9" s="13" t="s">
         <v>62</v>
       </c>
       <c r="C9" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="D9" s="14" t="s">
+      <c r="D9" s="15" t="s">
         <v>64</v>
       </c>
       <c r="E9" s="13" t="s">
@@ -3989,26 +4190,26 @@
       <c r="P9" s="13">
         <v>50</v>
       </c>
-      <c r="R9"/>
-      <c r="T9"/>
-      <c r="V9"/>
-      <c r="X9"/>
-      <c r="Z9"/>
-      <c r="AB9"/>
-      <c r="AD9">
+      <c r="R9" s="14"/>
+      <c r="T9" s="14"/>
+      <c r="V9" s="14"/>
+      <c r="X9" s="14"/>
+      <c r="Z9" s="14"/>
+      <c r="AB9" s="14"/>
+      <c r="AD9" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="10" s="13" customFormat="1" ht="17" spans="1:30">
-      <c r="A10"/>
+      <c r="A10" s="14"/>
       <c r="B10" s="13" t="s">
         <v>65</v>
       </c>
       <c r="C10" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="D10" s="14" t="s">
+      <c r="D10" s="15" t="s">
         <v>64</v>
       </c>
       <c r="E10" s="13" t="s">
@@ -4020,7 +4221,7 @@
       <c r="G10" s="13">
         <v>1</v>
       </c>
-      <c r="H10"/>
+      <c r="H10" s="14"/>
       <c r="I10" s="13">
         <v>300</v>
       </c>
@@ -4042,26 +4243,26 @@
       <c r="P10" s="13">
         <v>50</v>
       </c>
-      <c r="R10"/>
-      <c r="T10"/>
-      <c r="V10"/>
-      <c r="X10"/>
-      <c r="Z10"/>
-      <c r="AB10"/>
-      <c r="AD10">
+      <c r="R10" s="14"/>
+      <c r="T10" s="14"/>
+      <c r="V10" s="14"/>
+      <c r="X10" s="14"/>
+      <c r="Z10" s="14"/>
+      <c r="AB10" s="14"/>
+      <c r="AD10" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="11" s="13" customFormat="1" ht="17" spans="1:18">
-      <c r="A11"/>
+      <c r="A11" s="14"/>
       <c r="B11" s="13" t="s">
         <v>68</v>
       </c>
       <c r="C11" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="D11" s="14" t="s">
+      <c r="D11" s="15" t="s">
         <v>70</v>
       </c>
       <c r="E11" s="13" t="s">
@@ -4094,17 +4295,17 @@
       <c r="P11" s="13">
         <v>80</v>
       </c>
-      <c r="R11"/>
+      <c r="R11" s="14"/>
     </row>
     <row r="12" s="13" customFormat="1" ht="17" spans="1:27">
-      <c r="A12"/>
+      <c r="A12" s="14"/>
       <c r="B12" s="13" t="s">
         <v>71</v>
       </c>
       <c r="C12" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="D12" s="14" t="s">
+      <c r="D12" s="15" t="s">
         <v>70</v>
       </c>
       <c r="E12" s="13" t="s">
@@ -4116,7 +4317,7 @@
       <c r="G12" s="13">
         <v>2</v>
       </c>
-      <c r="H12"/>
+      <c r="H12" s="14"/>
       <c r="I12" s="13">
         <v>30</v>
       </c>
@@ -4138,20 +4339,20 @@
       <c r="P12" s="13">
         <v>120</v>
       </c>
-      <c r="R12"/>
-      <c r="Y12"/>
-      <c r="Z12"/>
-      <c r="AA12"/>
+      <c r="R12" s="14"/>
+      <c r="Y12" s="14"/>
+      <c r="Z12" s="14"/>
+      <c r="AA12" s="14"/>
     </row>
     <row r="13" s="13" customFormat="1" ht="17" spans="1:23">
-      <c r="A13"/>
+      <c r="A13" s="14"/>
       <c r="B13" s="13" t="s">
         <v>73</v>
       </c>
       <c r="C13" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="D13" s="14" t="s">
+      <c r="D13" s="15" t="s">
         <v>75</v>
       </c>
       <c r="E13" s="13" t="s">
@@ -4163,7 +4364,7 @@
       <c r="G13" s="13">
         <v>0.15</v>
       </c>
-      <c r="H13"/>
+      <c r="H13" s="14"/>
       <c r="I13" s="13">
         <v>100</v>
       </c>
@@ -4185,16 +4386,16 @@
       <c r="P13" s="13">
         <v>40</v>
       </c>
-      <c r="R13">
+      <c r="R13" s="14">
         <f t="shared" ref="R13:R15" si="2">IFERROR(VLOOKUP(E13,$T$7:$AB$12,9,FALSE),0)</f>
         <v>0</v>
       </c>
-      <c r="T13"/>
-      <c r="V13"/>
-      <c r="W13"/>
+      <c r="T13" s="14"/>
+      <c r="V13" s="14"/>
+      <c r="W13" s="14"/>
     </row>
     <row r="14" s="13" customFormat="1" spans="1:25">
-      <c r="A14"/>
+      <c r="A14" s="14"/>
       <c r="B14" s="13" t="s">
         <v>76</v>
       </c>
@@ -4213,7 +4414,7 @@
       <c r="G14" s="13">
         <v>0.15</v>
       </c>
-      <c r="H14"/>
+      <c r="H14" s="14"/>
       <c r="I14" s="13">
         <v>300</v>
       </c>
@@ -4235,17 +4436,17 @@
       <c r="P14" s="13">
         <v>40</v>
       </c>
-      <c r="R14">
+      <c r="R14" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="T14"/>
-      <c r="V14"/>
-      <c r="W14"/>
-      <c r="Y14"/>
+      <c r="T14" s="14"/>
+      <c r="V14" s="14"/>
+      <c r="W14" s="14"/>
+      <c r="Y14" s="14"/>
     </row>
     <row r="15" s="1" customFormat="1" ht="17" spans="1:30">
-      <c r="A15"/>
+      <c r="A15" s="14"/>
       <c r="B15" s="1" t="s">
         <v>79</v>
       </c>
@@ -4285,24 +4486,24 @@
       <c r="P15" s="1">
         <v>40</v>
       </c>
-      <c r="Q15"/>
-      <c r="R15">
+      <c r="Q15" s="14"/>
+      <c r="R15" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="T15"/>
-      <c r="U15"/>
-      <c r="V15"/>
-      <c r="W15"/>
-      <c r="X15"/>
-      <c r="Y15"/>
-      <c r="Z15"/>
-      <c r="AB15"/>
-      <c r="AC15"/>
-      <c r="AD15"/>
+      <c r="T15" s="14"/>
+      <c r="U15" s="14"/>
+      <c r="V15" s="14"/>
+      <c r="W15" s="14"/>
+      <c r="X15" s="14"/>
+      <c r="Y15" s="14"/>
+      <c r="Z15" s="14"/>
+      <c r="AB15" s="14"/>
+      <c r="AC15" s="14"/>
+      <c r="AD15" s="14"/>
     </row>
     <row r="16" s="1" customFormat="1" ht="17" spans="1:30">
-      <c r="A16"/>
+      <c r="A16" s="14"/>
       <c r="B16" s="1" t="s">
         <v>82</v>
       </c>
@@ -4342,21 +4543,21 @@
       <c r="P16" s="1">
         <v>40</v>
       </c>
-      <c r="Q16"/>
-      <c r="R16"/>
-      <c r="T16"/>
-      <c r="U16"/>
-      <c r="V16"/>
-      <c r="W16"/>
-      <c r="X16"/>
-      <c r="Y16"/>
-      <c r="Z16"/>
-      <c r="AB16"/>
-      <c r="AC16"/>
-      <c r="AD16"/>
+      <c r="Q16" s="14"/>
+      <c r="R16" s="14"/>
+      <c r="T16" s="14"/>
+      <c r="U16" s="14"/>
+      <c r="V16" s="14"/>
+      <c r="W16" s="14"/>
+      <c r="X16" s="14"/>
+      <c r="Y16" s="14"/>
+      <c r="Z16" s="14"/>
+      <c r="AB16" s="14"/>
+      <c r="AC16" s="14"/>
+      <c r="AD16" s="14"/>
     </row>
     <row r="17" s="1" customFormat="1" ht="17" spans="1:30">
-      <c r="A17"/>
+      <c r="A17" s="14"/>
       <c r="B17" s="1" t="s">
         <v>85</v>
       </c>
@@ -4396,24 +4597,24 @@
       <c r="P17" s="1">
         <v>40</v>
       </c>
-      <c r="Q17"/>
-      <c r="R17">
+      <c r="Q17" s="14"/>
+      <c r="R17" s="14">
         <f t="shared" ref="R17:R21" si="3">IFERROR(VLOOKUP(E17,$T$7:$AB$12,9,FALSE),0)</f>
         <v>0</v>
       </c>
-      <c r="T17"/>
-      <c r="U17"/>
-      <c r="V17"/>
-      <c r="W17"/>
-      <c r="X17"/>
-      <c r="Y17"/>
-      <c r="Z17"/>
-      <c r="AB17"/>
-      <c r="AC17"/>
-      <c r="AD17"/>
+      <c r="T17" s="14"/>
+      <c r="U17" s="14"/>
+      <c r="V17" s="14"/>
+      <c r="W17" s="14"/>
+      <c r="X17" s="14"/>
+      <c r="Y17" s="14"/>
+      <c r="Z17" s="14"/>
+      <c r="AB17" s="14"/>
+      <c r="AC17" s="14"/>
+      <c r="AD17" s="14"/>
     </row>
     <row r="18" s="1" customFormat="1" ht="17" spans="1:30">
-      <c r="A18"/>
+      <c r="A18" s="14"/>
       <c r="B18" s="1" t="s">
         <v>88</v>
       </c>
@@ -4453,24 +4654,24 @@
       <c r="P18" s="1">
         <v>40</v>
       </c>
-      <c r="Q18"/>
-      <c r="R18">
+      <c r="Q18" s="14"/>
+      <c r="R18" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="T18"/>
-      <c r="U18"/>
-      <c r="V18"/>
-      <c r="W18"/>
-      <c r="X18"/>
-      <c r="Y18"/>
-      <c r="Z18"/>
-      <c r="AB18"/>
-      <c r="AC18"/>
-      <c r="AD18"/>
+      <c r="T18" s="14"/>
+      <c r="U18" s="14"/>
+      <c r="V18" s="14"/>
+      <c r="W18" s="14"/>
+      <c r="X18" s="14"/>
+      <c r="Y18" s="14"/>
+      <c r="Z18" s="14"/>
+      <c r="AB18" s="14"/>
+      <c r="AC18" s="14"/>
+      <c r="AD18" s="14"/>
     </row>
     <row r="19" s="1" customFormat="1" ht="17" spans="1:30">
-      <c r="A19"/>
+      <c r="A19" s="14"/>
       <c r="B19" s="1" t="s">
         <v>91</v>
       </c>
@@ -4510,24 +4711,24 @@
       <c r="P19" s="1">
         <v>80</v>
       </c>
-      <c r="Q19"/>
-      <c r="R19">
+      <c r="Q19" s="14"/>
+      <c r="R19" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="T19"/>
-      <c r="U19"/>
-      <c r="V19"/>
-      <c r="W19"/>
-      <c r="X19"/>
-      <c r="Y19"/>
-      <c r="Z19"/>
-      <c r="AB19"/>
-      <c r="AC19"/>
-      <c r="AD19"/>
+      <c r="T19" s="14"/>
+      <c r="U19" s="14"/>
+      <c r="V19" s="14"/>
+      <c r="W19" s="14"/>
+      <c r="X19" s="14"/>
+      <c r="Y19" s="14"/>
+      <c r="Z19" s="14"/>
+      <c r="AB19" s="14"/>
+      <c r="AC19" s="14"/>
+      <c r="AD19" s="14"/>
     </row>
     <row r="20" s="1" customFormat="1" ht="17" spans="1:30">
-      <c r="A20"/>
+      <c r="A20" s="14"/>
       <c r="B20" s="1" t="s">
         <v>94</v>
       </c>
@@ -4567,24 +4768,24 @@
       <c r="P20" s="1">
         <v>80</v>
       </c>
-      <c r="Q20"/>
-      <c r="R20">
+      <c r="Q20" s="14"/>
+      <c r="R20" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="T20"/>
-      <c r="U20"/>
-      <c r="V20"/>
-      <c r="W20"/>
-      <c r="X20"/>
-      <c r="Y20"/>
-      <c r="Z20"/>
-      <c r="AB20"/>
-      <c r="AC20"/>
-      <c r="AD20"/>
+      <c r="T20" s="14"/>
+      <c r="U20" s="14"/>
+      <c r="V20" s="14"/>
+      <c r="W20" s="14"/>
+      <c r="X20" s="14"/>
+      <c r="Y20" s="14"/>
+      <c r="Z20" s="14"/>
+      <c r="AB20" s="14"/>
+      <c r="AC20" s="14"/>
+      <c r="AD20" s="14"/>
     </row>
     <row r="21" s="1" customFormat="1" ht="17" spans="1:30">
-      <c r="A21"/>
+      <c r="A21" s="14"/>
       <c r="B21" s="1" t="s">
         <v>97</v>
       </c>
@@ -4624,24 +4825,24 @@
       <c r="P21" s="1">
         <v>80</v>
       </c>
-      <c r="Q21"/>
-      <c r="R21">
+      <c r="Q21" s="14"/>
+      <c r="R21" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="T21"/>
-      <c r="U21"/>
-      <c r="V21"/>
-      <c r="W21"/>
-      <c r="X21"/>
-      <c r="Y21"/>
-      <c r="Z21"/>
-      <c r="AB21"/>
-      <c r="AC21"/>
-      <c r="AD21"/>
+      <c r="T21" s="14"/>
+      <c r="U21" s="14"/>
+      <c r="V21" s="14"/>
+      <c r="W21" s="14"/>
+      <c r="X21" s="14"/>
+      <c r="Y21" s="14"/>
+      <c r="Z21" s="14"/>
+      <c r="AB21" s="14"/>
+      <c r="AC21" s="14"/>
+      <c r="AD21" s="14"/>
     </row>
     <row r="22" s="1" customFormat="1" ht="17" spans="1:30">
-      <c r="A22"/>
+      <c r="A22" s="14"/>
       <c r="B22" s="1" t="s">
         <v>100</v>
       </c>
@@ -4681,21 +4882,21 @@
       <c r="P22" s="1">
         <v>80</v>
       </c>
-      <c r="Q22"/>
-      <c r="R22"/>
-      <c r="T22"/>
-      <c r="U22"/>
-      <c r="V22"/>
-      <c r="W22"/>
-      <c r="X22"/>
-      <c r="Y22"/>
-      <c r="Z22"/>
-      <c r="AB22"/>
-      <c r="AC22"/>
-      <c r="AD22"/>
+      <c r="Q22" s="14"/>
+      <c r="R22" s="14"/>
+      <c r="T22" s="14"/>
+      <c r="U22" s="14"/>
+      <c r="V22" s="14"/>
+      <c r="W22" s="14"/>
+      <c r="X22" s="14"/>
+      <c r="Y22" s="14"/>
+      <c r="Z22" s="14"/>
+      <c r="AB22" s="14"/>
+      <c r="AC22" s="14"/>
+      <c r="AD22" s="14"/>
     </row>
     <row r="23" s="1" customFormat="1" ht="17" spans="1:30">
-      <c r="A23"/>
+      <c r="A23" s="14"/>
       <c r="B23" s="1" t="s">
         <v>103</v>
       </c>
@@ -4735,24 +4936,24 @@
       <c r="P23" s="1">
         <v>80</v>
       </c>
-      <c r="Q23"/>
-      <c r="R23">
+      <c r="Q23" s="14"/>
+      <c r="R23" s="14">
         <f t="shared" ref="R23:R25" si="4">IFERROR(VLOOKUP(E23,$T$7:$AB$12,9,FALSE),0)</f>
         <v>0</v>
       </c>
-      <c r="T23"/>
-      <c r="U23"/>
-      <c r="V23"/>
-      <c r="W23"/>
-      <c r="X23"/>
-      <c r="Y23"/>
-      <c r="Z23"/>
-      <c r="AB23"/>
-      <c r="AC23"/>
-      <c r="AD23"/>
+      <c r="T23" s="14"/>
+      <c r="U23" s="14"/>
+      <c r="V23" s="14"/>
+      <c r="W23" s="14"/>
+      <c r="X23" s="14"/>
+      <c r="Y23" s="14"/>
+      <c r="Z23" s="14"/>
+      <c r="AB23" s="14"/>
+      <c r="AC23" s="14"/>
+      <c r="AD23" s="14"/>
     </row>
     <row r="24" s="1" customFormat="1" ht="17" spans="1:30">
-      <c r="A24"/>
+      <c r="A24" s="14"/>
       <c r="B24" s="1" t="s">
         <v>106</v>
       </c>
@@ -4792,24 +4993,24 @@
       <c r="P24" s="1">
         <v>80</v>
       </c>
-      <c r="Q24"/>
-      <c r="R24">
+      <c r="Q24" s="14"/>
+      <c r="R24" s="14">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="T24"/>
-      <c r="U24"/>
-      <c r="V24"/>
-      <c r="W24"/>
-      <c r="X24"/>
-      <c r="Y24"/>
-      <c r="Z24"/>
-      <c r="AB24"/>
-      <c r="AC24"/>
-      <c r="AD24"/>
+      <c r="T24" s="14"/>
+      <c r="U24" s="14"/>
+      <c r="V24" s="14"/>
+      <c r="W24" s="14"/>
+      <c r="X24" s="14"/>
+      <c r="Y24" s="14"/>
+      <c r="Z24" s="14"/>
+      <c r="AB24" s="14"/>
+      <c r="AC24" s="14"/>
+      <c r="AD24" s="14"/>
     </row>
     <row r="25" s="1" customFormat="1" ht="51" spans="1:30">
-      <c r="A25"/>
+      <c r="A25" s="14"/>
       <c r="B25" s="1" t="s">
         <v>109</v>
       </c>
@@ -4849,24 +5050,24 @@
       <c r="P25" s="1">
         <v>150</v>
       </c>
-      <c r="Q25"/>
-      <c r="R25">
+      <c r="Q25" s="14"/>
+      <c r="R25" s="14">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="T25"/>
-      <c r="U25"/>
-      <c r="V25"/>
-      <c r="W25"/>
-      <c r="X25"/>
-      <c r="Y25"/>
-      <c r="Z25"/>
-      <c r="AB25"/>
-      <c r="AC25"/>
-      <c r="AD25"/>
+      <c r="T25" s="14"/>
+      <c r="U25" s="14"/>
+      <c r="V25" s="14"/>
+      <c r="W25" s="14"/>
+      <c r="X25" s="14"/>
+      <c r="Y25" s="14"/>
+      <c r="Z25" s="14"/>
+      <c r="AB25" s="14"/>
+      <c r="AC25" s="14"/>
+      <c r="AD25" s="14"/>
     </row>
     <row r="26" s="1" customFormat="1" ht="51" spans="1:30">
-      <c r="A26"/>
+      <c r="A26" s="14"/>
       <c r="B26" s="1" t="s">
         <v>112</v>
       </c>
@@ -4906,21 +5107,21 @@
       <c r="P26" s="1">
         <v>80</v>
       </c>
-      <c r="Q26"/>
-      <c r="R26"/>
-      <c r="T26"/>
-      <c r="U26"/>
-      <c r="V26"/>
-      <c r="W26"/>
-      <c r="X26"/>
-      <c r="Y26"/>
-      <c r="Z26"/>
-      <c r="AB26"/>
-      <c r="AC26"/>
-      <c r="AD26"/>
+      <c r="Q26" s="14"/>
+      <c r="R26" s="14"/>
+      <c r="T26" s="14"/>
+      <c r="U26" s="14"/>
+      <c r="V26" s="14"/>
+      <c r="W26" s="14"/>
+      <c r="X26" s="14"/>
+      <c r="Y26" s="14"/>
+      <c r="Z26" s="14"/>
+      <c r="AB26" s="14"/>
+      <c r="AC26" s="14"/>
+      <c r="AD26" s="14"/>
     </row>
     <row r="27" s="1" customFormat="1" ht="51" spans="1:30">
-      <c r="A27"/>
+      <c r="A27" s="14"/>
       <c r="B27" s="1" t="s">
         <v>115</v>
       </c>
@@ -4960,21 +5161,21 @@
       <c r="P27" s="1">
         <v>80</v>
       </c>
-      <c r="Q27"/>
-      <c r="R27"/>
-      <c r="T27"/>
-      <c r="U27"/>
-      <c r="V27"/>
-      <c r="W27"/>
-      <c r="X27"/>
-      <c r="Y27"/>
-      <c r="Z27"/>
-      <c r="AB27"/>
-      <c r="AC27"/>
-      <c r="AD27"/>
+      <c r="Q27" s="14"/>
+      <c r="R27" s="14"/>
+      <c r="T27" s="14"/>
+      <c r="U27" s="14"/>
+      <c r="V27" s="14"/>
+      <c r="W27" s="14"/>
+      <c r="X27" s="14"/>
+      <c r="Y27" s="14"/>
+      <c r="Z27" s="14"/>
+      <c r="AB27" s="14"/>
+      <c r="AC27" s="14"/>
+      <c r="AD27" s="14"/>
     </row>
     <row r="28" s="1" customFormat="1" ht="34" spans="1:30">
-      <c r="A28"/>
+      <c r="A28" s="14"/>
       <c r="B28" s="1" t="s">
         <v>118</v>
       </c>
@@ -5017,24 +5218,24 @@
       <c r="P28" s="1">
         <v>80</v>
       </c>
-      <c r="Q28"/>
-      <c r="R28">
+      <c r="Q28" s="14"/>
+      <c r="R28" s="14">
         <f t="shared" ref="R28:R34" si="5">IFERROR(VLOOKUP(E28,$T$7:$AB$12,9,FALSE),0)</f>
         <v>0</v>
       </c>
-      <c r="T28"/>
-      <c r="U28"/>
-      <c r="V28"/>
-      <c r="W28"/>
-      <c r="X28"/>
-      <c r="Y28"/>
-      <c r="Z28"/>
-      <c r="AB28"/>
-      <c r="AC28"/>
-      <c r="AD28"/>
+      <c r="T28" s="14"/>
+      <c r="U28" s="14"/>
+      <c r="V28" s="14"/>
+      <c r="W28" s="14"/>
+      <c r="X28" s="14"/>
+      <c r="Y28" s="14"/>
+      <c r="Z28" s="14"/>
+      <c r="AB28" s="14"/>
+      <c r="AC28" s="14"/>
+      <c r="AD28" s="14"/>
     </row>
     <row r="29" s="1" customFormat="1" ht="34" spans="1:30">
-      <c r="A29"/>
+      <c r="A29" s="14"/>
       <c r="B29" s="1" t="s">
         <v>122</v>
       </c>
@@ -5074,24 +5275,24 @@
       <c r="P29" s="1">
         <v>40</v>
       </c>
-      <c r="Q29"/>
-      <c r="R29">
+      <c r="Q29" s="14"/>
+      <c r="R29" s="14">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="T29"/>
-      <c r="U29"/>
-      <c r="V29"/>
-      <c r="W29"/>
-      <c r="X29"/>
-      <c r="Y29"/>
-      <c r="Z29"/>
-      <c r="AB29"/>
-      <c r="AC29"/>
-      <c r="AD29"/>
+      <c r="T29" s="14"/>
+      <c r="U29" s="14"/>
+      <c r="V29" s="14"/>
+      <c r="W29" s="14"/>
+      <c r="X29" s="14"/>
+      <c r="Y29" s="14"/>
+      <c r="Z29" s="14"/>
+      <c r="AB29" s="14"/>
+      <c r="AC29" s="14"/>
+      <c r="AD29" s="14"/>
     </row>
     <row r="30" s="1" customFormat="1" ht="34" spans="1:30">
-      <c r="A30"/>
+      <c r="A30" s="14"/>
       <c r="B30" s="1" t="s">
         <v>125</v>
       </c>
@@ -5131,24 +5332,24 @@
       <c r="P30" s="1">
         <v>40</v>
       </c>
-      <c r="Q30"/>
-      <c r="R30">
+      <c r="Q30" s="14"/>
+      <c r="R30" s="14">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="T30"/>
-      <c r="U30"/>
-      <c r="V30"/>
-      <c r="W30"/>
-      <c r="X30"/>
-      <c r="Y30"/>
-      <c r="Z30"/>
-      <c r="AB30"/>
-      <c r="AC30"/>
-      <c r="AD30"/>
+      <c r="T30" s="14"/>
+      <c r="U30" s="14"/>
+      <c r="V30" s="14"/>
+      <c r="W30" s="14"/>
+      <c r="X30" s="14"/>
+      <c r="Y30" s="14"/>
+      <c r="Z30" s="14"/>
+      <c r="AB30" s="14"/>
+      <c r="AC30" s="14"/>
+      <c r="AD30" s="14"/>
     </row>
     <row r="31" s="1" customFormat="1" ht="34" spans="1:30">
-      <c r="A31"/>
+      <c r="A31" s="14"/>
       <c r="B31" s="1" t="s">
         <v>128</v>
       </c>
@@ -5188,24 +5389,24 @@
       <c r="P31" s="1">
         <v>80</v>
       </c>
-      <c r="Q31"/>
-      <c r="R31">
+      <c r="Q31" s="14"/>
+      <c r="R31" s="14">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="T31"/>
-      <c r="U31"/>
-      <c r="V31"/>
-      <c r="W31"/>
-      <c r="X31"/>
-      <c r="Y31"/>
-      <c r="Z31"/>
-      <c r="AB31"/>
-      <c r="AC31"/>
-      <c r="AD31"/>
+      <c r="T31" s="14"/>
+      <c r="U31" s="14"/>
+      <c r="V31" s="14"/>
+      <c r="W31" s="14"/>
+      <c r="X31" s="14"/>
+      <c r="Y31" s="14"/>
+      <c r="Z31" s="14"/>
+      <c r="AB31" s="14"/>
+      <c r="AC31" s="14"/>
+      <c r="AD31" s="14"/>
     </row>
     <row r="32" s="1" customFormat="1" ht="51" spans="1:30">
-      <c r="A32"/>
+      <c r="A32" s="14"/>
       <c r="B32" s="1" t="s">
         <v>131</v>
       </c>
@@ -5222,7 +5423,7 @@
         <v>43</v>
       </c>
       <c r="G32" s="1">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="H32" s="1" t="s">
         <v>134</v>
@@ -5248,24 +5449,24 @@
       <c r="P32" s="1">
         <v>80</v>
       </c>
-      <c r="Q32"/>
-      <c r="R32">
+      <c r="Q32" s="14"/>
+      <c r="R32" s="14">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="T32"/>
-      <c r="U32"/>
-      <c r="V32"/>
-      <c r="W32"/>
-      <c r="X32"/>
-      <c r="Y32"/>
-      <c r="Z32"/>
-      <c r="AB32"/>
-      <c r="AC32"/>
-      <c r="AD32"/>
+      <c r="T32" s="14"/>
+      <c r="U32" s="14"/>
+      <c r="V32" s="14"/>
+      <c r="W32" s="14"/>
+      <c r="X32" s="14"/>
+      <c r="Y32" s="14"/>
+      <c r="Z32" s="14"/>
+      <c r="AB32" s="14"/>
+      <c r="AC32" s="14"/>
+      <c r="AD32" s="14"/>
     </row>
     <row r="33" s="1" customFormat="1" ht="51" spans="1:30">
-      <c r="A33"/>
+      <c r="A33" s="14"/>
       <c r="B33" s="1" t="s">
         <v>135</v>
       </c>
@@ -5282,7 +5483,7 @@
         <v>43</v>
       </c>
       <c r="G33" s="1">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="H33" s="1" t="s">
         <v>138</v>
@@ -5308,31 +5509,31 @@
       <c r="P33" s="1">
         <v>80</v>
       </c>
-      <c r="Q33"/>
-      <c r="R33">
+      <c r="Q33" s="14"/>
+      <c r="R33" s="14">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="T33"/>
-      <c r="U33"/>
-      <c r="V33"/>
-      <c r="W33"/>
-      <c r="X33"/>
-      <c r="Y33"/>
-      <c r="Z33"/>
-      <c r="AB33"/>
-      <c r="AC33"/>
-      <c r="AD33"/>
+      <c r="T33" s="14"/>
+      <c r="U33" s="14"/>
+      <c r="V33" s="14"/>
+      <c r="W33" s="14"/>
+      <c r="X33" s="14"/>
+      <c r="Y33" s="14"/>
+      <c r="Z33" s="14"/>
+      <c r="AB33" s="14"/>
+      <c r="AC33" s="14"/>
+      <c r="AD33" s="14"/>
     </row>
     <row r="34" s="13" customFormat="1" ht="34" spans="1:18">
-      <c r="A34"/>
+      <c r="A34" s="14"/>
       <c r="B34" s="13" t="s">
         <v>139</v>
       </c>
       <c r="C34" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="D34" s="14" t="s">
+      <c r="D34" s="15" t="s">
         <v>141</v>
       </c>
       <c r="E34" s="13" t="s">
@@ -5365,7 +5566,7 @@
       <c r="P34" s="13">
         <v>40</v>
       </c>
-      <c r="R34">
+      <c r="R34" s="14">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -5378,7 +5579,7 @@
       <c r="C35" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D35" s="14" t="s">
+      <c r="D35" s="15" t="s">
         <v>144</v>
       </c>
       <c r="E35" s="13" t="s">
@@ -5415,14 +5616,14 @@
       </c>
     </row>
     <row r="36" s="13" customFormat="1" ht="34" spans="1:20">
-      <c r="A36"/>
+      <c r="A36" s="14"/>
       <c r="B36" s="13" t="s">
         <v>145</v>
       </c>
       <c r="C36" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="D36" s="14" t="s">
+      <c r="D36" s="15" t="s">
         <v>147</v>
       </c>
       <c r="E36" s="13" t="s">
@@ -5434,7 +5635,7 @@
       <c r="G36" s="13">
         <v>15</v>
       </c>
-      <c r="H36"/>
+      <c r="H36" s="14"/>
       <c r="I36" s="13">
         <v>100</v>
       </c>
@@ -5456,14 +5657,14 @@
       <c r="P36" s="13">
         <v>40</v>
       </c>
-      <c r="R36">
-        <f t="shared" ref="R36:R46" si="6">IFERROR(VLOOKUP(E36,$T$7:$AB$12,9,FALSE),0)</f>
-        <v>0</v>
-      </c>
-      <c r="T36"/>
+      <c r="R36" s="14">
+        <f t="shared" ref="R36:R45" si="6">IFERROR(VLOOKUP(E36,$T$7:$AB$12,9,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="T36" s="14"/>
     </row>
     <row r="37" s="1" customFormat="1" ht="34" spans="1:30">
-      <c r="A37"/>
+      <c r="A37" s="14"/>
       <c r="B37" s="1" t="s">
         <v>148</v>
       </c>
@@ -5503,24 +5704,24 @@
       <c r="P37" s="1">
         <v>80</v>
       </c>
-      <c r="Q37"/>
-      <c r="R37">
+      <c r="Q37" s="14"/>
+      <c r="R37" s="14">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="T37"/>
-      <c r="U37"/>
-      <c r="V37"/>
-      <c r="W37"/>
-      <c r="X37"/>
-      <c r="Y37"/>
-      <c r="Z37"/>
-      <c r="AB37"/>
-      <c r="AC37"/>
-      <c r="AD37"/>
+      <c r="T37" s="14"/>
+      <c r="U37" s="14"/>
+      <c r="V37" s="14"/>
+      <c r="W37" s="14"/>
+      <c r="X37" s="14"/>
+      <c r="Y37" s="14"/>
+      <c r="Z37" s="14"/>
+      <c r="AB37" s="14"/>
+      <c r="AC37" s="14"/>
+      <c r="AD37" s="14"/>
     </row>
     <row r="38" s="1" customFormat="1" ht="17" spans="1:30">
-      <c r="A38"/>
+      <c r="A38" s="14"/>
       <c r="B38" s="1" t="s">
         <v>151</v>
       </c>
@@ -5537,7 +5738,7 @@
         <v>43</v>
       </c>
       <c r="G38" s="1">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="I38" s="1">
         <v>30</v>
@@ -5560,24 +5761,24 @@
       <c r="P38" s="1">
         <v>80</v>
       </c>
-      <c r="Q38"/>
-      <c r="R38">
+      <c r="Q38" s="14"/>
+      <c r="R38" s="14">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="T38"/>
-      <c r="U38"/>
-      <c r="V38"/>
-      <c r="W38"/>
-      <c r="X38"/>
-      <c r="Y38"/>
-      <c r="Z38"/>
-      <c r="AB38"/>
-      <c r="AC38"/>
-      <c r="AD38"/>
+      <c r="T38" s="14"/>
+      <c r="U38" s="14"/>
+      <c r="V38" s="14"/>
+      <c r="W38" s="14"/>
+      <c r="X38" s="14"/>
+      <c r="Y38" s="14"/>
+      <c r="Z38" s="14"/>
+      <c r="AB38" s="14"/>
+      <c r="AC38" s="14"/>
+      <c r="AD38" s="14"/>
     </row>
     <row r="39" s="1" customFormat="1" ht="51" spans="1:30">
-      <c r="A39"/>
+      <c r="A39" s="14"/>
       <c r="B39" s="1" t="s">
         <v>154</v>
       </c>
@@ -5620,24 +5821,24 @@
       <c r="P39" s="1">
         <v>40</v>
       </c>
-      <c r="Q39"/>
-      <c r="R39">
+      <c r="Q39" s="14"/>
+      <c r="R39" s="14">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="T39"/>
-      <c r="U39"/>
-      <c r="V39"/>
-      <c r="W39"/>
-      <c r="X39"/>
-      <c r="Y39"/>
-      <c r="Z39"/>
-      <c r="AB39"/>
-      <c r="AC39"/>
-      <c r="AD39"/>
+      <c r="T39" s="14"/>
+      <c r="U39" s="14"/>
+      <c r="V39" s="14"/>
+      <c r="W39" s="14"/>
+      <c r="X39" s="14"/>
+      <c r="Y39" s="14"/>
+      <c r="Z39" s="14"/>
+      <c r="AB39" s="14"/>
+      <c r="AC39" s="14"/>
+      <c r="AD39" s="14"/>
     </row>
     <row r="40" s="1" customFormat="1" ht="34" spans="1:30">
-      <c r="A40"/>
+      <c r="A40" s="14"/>
       <c r="B40" s="1" t="s">
         <v>158</v>
       </c>
@@ -5677,24 +5878,24 @@
       <c r="P40" s="1">
         <v>40</v>
       </c>
-      <c r="Q40"/>
-      <c r="R40">
+      <c r="Q40" s="14"/>
+      <c r="R40" s="14">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="T40"/>
-      <c r="U40"/>
-      <c r="V40"/>
-      <c r="W40"/>
-      <c r="X40"/>
-      <c r="Y40"/>
-      <c r="Z40"/>
-      <c r="AB40"/>
-      <c r="AC40"/>
-      <c r="AD40"/>
+      <c r="T40" s="14"/>
+      <c r="U40" s="14"/>
+      <c r="V40" s="14"/>
+      <c r="W40" s="14"/>
+      <c r="X40" s="14"/>
+      <c r="Y40" s="14"/>
+      <c r="Z40" s="14"/>
+      <c r="AB40" s="14"/>
+      <c r="AC40" s="14"/>
+      <c r="AD40" s="14"/>
     </row>
     <row r="41" s="1" customFormat="1" ht="17" spans="1:30">
-      <c r="A41"/>
+      <c r="A41" s="14"/>
       <c r="B41" s="1" t="s">
         <v>161</v>
       </c>
@@ -5734,24 +5935,24 @@
       <c r="P41" s="1">
         <v>80</v>
       </c>
-      <c r="Q41"/>
-      <c r="R41">
+      <c r="Q41" s="14"/>
+      <c r="R41" s="14">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="T41"/>
-      <c r="U41"/>
-      <c r="V41"/>
-      <c r="W41"/>
-      <c r="X41"/>
-      <c r="Y41"/>
-      <c r="Z41"/>
-      <c r="AB41"/>
-      <c r="AC41"/>
-      <c r="AD41"/>
+      <c r="T41" s="14"/>
+      <c r="U41" s="14"/>
+      <c r="V41" s="14"/>
+      <c r="W41" s="14"/>
+      <c r="X41" s="14"/>
+      <c r="Y41" s="14"/>
+      <c r="Z41" s="14"/>
+      <c r="AB41" s="14"/>
+      <c r="AC41" s="14"/>
+      <c r="AD41" s="14"/>
     </row>
     <row r="42" s="1" customFormat="1" ht="34" spans="1:30">
-      <c r="A42"/>
+      <c r="A42" s="14"/>
       <c r="B42" s="1" t="s">
         <v>164</v>
       </c>
@@ -5794,24 +5995,24 @@
       <c r="P42" s="1">
         <v>80</v>
       </c>
-      <c r="Q42"/>
-      <c r="R42">
-        <f>IFERROR(VLOOKUP(E42,$T$7:$AB$12,9,FALSE),0)</f>
-        <v>0</v>
-      </c>
-      <c r="T42"/>
-      <c r="U42"/>
-      <c r="V42"/>
-      <c r="W42"/>
-      <c r="X42"/>
-      <c r="Y42"/>
-      <c r="Z42"/>
-      <c r="AB42"/>
-      <c r="AC42"/>
-      <c r="AD42"/>
+      <c r="Q42" s="14"/>
+      <c r="R42" s="14">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="T42" s="14"/>
+      <c r="U42" s="14"/>
+      <c r="V42" s="14"/>
+      <c r="W42" s="14"/>
+      <c r="X42" s="14"/>
+      <c r="Y42" s="14"/>
+      <c r="Z42" s="14"/>
+      <c r="AB42" s="14"/>
+      <c r="AC42" s="14"/>
+      <c r="AD42" s="14"/>
     </row>
     <row r="43" s="1" customFormat="1" ht="51" spans="1:30">
-      <c r="A43"/>
+      <c r="A43" s="14"/>
       <c r="B43" s="1" t="s">
         <v>168</v>
       </c>
@@ -5854,24 +6055,24 @@
       <c r="P43" s="1">
         <v>40</v>
       </c>
-      <c r="Q43"/>
-      <c r="R43">
-        <f>IFERROR(VLOOKUP(E43,$T$7:$AB$12,9,FALSE),0)</f>
-        <v>0</v>
-      </c>
-      <c r="T43"/>
-      <c r="U43"/>
-      <c r="V43"/>
-      <c r="W43"/>
-      <c r="X43"/>
-      <c r="Y43"/>
-      <c r="Z43"/>
-      <c r="AB43"/>
-      <c r="AC43"/>
-      <c r="AD43"/>
+      <c r="Q43" s="14"/>
+      <c r="R43" s="14">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="T43" s="14"/>
+      <c r="U43" s="14"/>
+      <c r="V43" s="14"/>
+      <c r="W43" s="14"/>
+      <c r="X43" s="14"/>
+      <c r="Y43" s="14"/>
+      <c r="Z43" s="14"/>
+      <c r="AB43" s="14"/>
+      <c r="AC43" s="14"/>
+      <c r="AD43" s="14"/>
     </row>
     <row r="44" s="1" customFormat="1" ht="51" spans="1:30">
-      <c r="A44"/>
+      <c r="A44" s="14"/>
       <c r="B44" s="1" t="s">
         <v>172</v>
       </c>
@@ -5914,24 +6115,24 @@
       <c r="P44" s="1">
         <v>40</v>
       </c>
-      <c r="Q44"/>
-      <c r="R44">
-        <f>IFERROR(VLOOKUP(E44,$T$7:$AB$12,9,FALSE),0)</f>
-        <v>0</v>
-      </c>
-      <c r="T44"/>
-      <c r="U44"/>
-      <c r="V44"/>
-      <c r="W44"/>
-      <c r="X44"/>
-      <c r="Y44"/>
-      <c r="Z44"/>
-      <c r="AB44"/>
-      <c r="AC44"/>
-      <c r="AD44"/>
+      <c r="Q44" s="14"/>
+      <c r="R44" s="14">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="T44" s="14"/>
+      <c r="U44" s="14"/>
+      <c r="V44" s="14"/>
+      <c r="W44" s="14"/>
+      <c r="X44" s="14"/>
+      <c r="Y44" s="14"/>
+      <c r="Z44" s="14"/>
+      <c r="AB44" s="14"/>
+      <c r="AC44" s="14"/>
+      <c r="AD44" s="14"/>
     </row>
     <row r="45" s="1" customFormat="1" ht="17" spans="1:30">
-      <c r="A45"/>
+      <c r="A45" s="14"/>
       <c r="B45" s="1" t="s">
         <v>176</v>
       </c>
@@ -5971,24 +6172,24 @@
       <c r="P45" s="1">
         <v>40</v>
       </c>
-      <c r="Q45"/>
-      <c r="R45">
-        <f>IFERROR(VLOOKUP(E45,$T$7:$AB$12,9,FALSE),0)</f>
-        <v>0</v>
-      </c>
-      <c r="T45"/>
-      <c r="U45"/>
-      <c r="V45"/>
-      <c r="W45"/>
-      <c r="X45"/>
-      <c r="Y45"/>
-      <c r="Z45"/>
-      <c r="AB45"/>
-      <c r="AC45"/>
-      <c r="AD45"/>
+      <c r="Q45" s="14"/>
+      <c r="R45" s="14">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="T45" s="14"/>
+      <c r="U45" s="14"/>
+      <c r="V45" s="14"/>
+      <c r="W45" s="14"/>
+      <c r="X45" s="14"/>
+      <c r="Y45" s="14"/>
+      <c r="Z45" s="14"/>
+      <c r="AB45" s="14"/>
+      <c r="AC45" s="14"/>
+      <c r="AD45" s="14"/>
     </row>
     <row r="46" s="1" customFormat="1" ht="17" spans="1:30">
-      <c r="A46"/>
+      <c r="A46" s="14"/>
       <c r="B46" s="1" t="s">
         <v>179</v>
       </c>
@@ -6028,21 +6229,21 @@
       <c r="P46" s="1">
         <v>80</v>
       </c>
-      <c r="Q46"/>
-      <c r="R46"/>
-      <c r="T46"/>
-      <c r="U46"/>
-      <c r="V46"/>
-      <c r="W46"/>
-      <c r="X46"/>
-      <c r="Y46"/>
-      <c r="Z46"/>
-      <c r="AB46"/>
-      <c r="AC46"/>
-      <c r="AD46"/>
+      <c r="Q46" s="14"/>
+      <c r="R46" s="14"/>
+      <c r="T46" s="14"/>
+      <c r="U46" s="14"/>
+      <c r="V46" s="14"/>
+      <c r="W46" s="14"/>
+      <c r="X46" s="14"/>
+      <c r="Y46" s="14"/>
+      <c r="Z46" s="14"/>
+      <c r="AB46" s="14"/>
+      <c r="AC46" s="14"/>
+      <c r="AD46" s="14"/>
     </row>
     <row r="47" s="1" customFormat="1" ht="34" spans="1:30">
-      <c r="A47"/>
+      <c r="A47" s="14"/>
       <c r="B47" s="1" t="s">
         <v>182</v>
       </c>
@@ -6082,24 +6283,24 @@
       <c r="P47" s="1">
         <v>40</v>
       </c>
-      <c r="Q47"/>
-      <c r="R47">
+      <c r="Q47" s="14"/>
+      <c r="R47" s="14">
         <f t="shared" ref="R47:R56" si="7">IFERROR(VLOOKUP(E47,$T$7:$AB$12,9,FALSE),0)</f>
         <v>0</v>
       </c>
-      <c r="T47"/>
-      <c r="U47"/>
-      <c r="V47"/>
-      <c r="W47"/>
-      <c r="X47"/>
-      <c r="Y47"/>
-      <c r="Z47"/>
-      <c r="AB47"/>
-      <c r="AC47"/>
-      <c r="AD47"/>
+      <c r="T47" s="14"/>
+      <c r="U47" s="14"/>
+      <c r="V47" s="14"/>
+      <c r="W47" s="14"/>
+      <c r="X47" s="14"/>
+      <c r="Y47" s="14"/>
+      <c r="Z47" s="14"/>
+      <c r="AB47" s="14"/>
+      <c r="AC47" s="14"/>
+      <c r="AD47" s="14"/>
     </row>
     <row r="48" s="1" customFormat="1" ht="34" spans="1:30">
-      <c r="A48"/>
+      <c r="A48" s="14"/>
       <c r="B48" s="1" t="s">
         <v>185</v>
       </c>
@@ -6139,24 +6340,24 @@
       <c r="P48" s="1">
         <v>80</v>
       </c>
-      <c r="Q48"/>
-      <c r="R48">
+      <c r="Q48" s="14"/>
+      <c r="R48" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="T48"/>
-      <c r="U48"/>
-      <c r="V48"/>
-      <c r="W48"/>
-      <c r="X48"/>
-      <c r="Y48"/>
-      <c r="Z48"/>
-      <c r="AB48"/>
-      <c r="AC48"/>
-      <c r="AD48"/>
+      <c r="T48" s="14"/>
+      <c r="U48" s="14"/>
+      <c r="V48" s="14"/>
+      <c r="W48" s="14"/>
+      <c r="X48" s="14"/>
+      <c r="Y48" s="14"/>
+      <c r="Z48" s="14"/>
+      <c r="AB48" s="14"/>
+      <c r="AC48" s="14"/>
+      <c r="AD48" s="14"/>
     </row>
     <row r="49" s="1" customFormat="1" ht="34" spans="1:30">
-      <c r="A49"/>
+      <c r="A49" s="14"/>
       <c r="B49" s="1" t="s">
         <v>188</v>
       </c>
@@ -6196,24 +6397,24 @@
       <c r="P49" s="1">
         <v>40</v>
       </c>
-      <c r="Q49"/>
-      <c r="R49">
+      <c r="Q49" s="14"/>
+      <c r="R49" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="T49"/>
-      <c r="U49"/>
-      <c r="V49"/>
-      <c r="W49"/>
-      <c r="X49"/>
-      <c r="Y49"/>
-      <c r="Z49"/>
-      <c r="AB49"/>
-      <c r="AC49"/>
-      <c r="AD49"/>
+      <c r="T49" s="14"/>
+      <c r="U49" s="14"/>
+      <c r="V49" s="14"/>
+      <c r="W49" s="14"/>
+      <c r="X49" s="14"/>
+      <c r="Y49" s="14"/>
+      <c r="Z49" s="14"/>
+      <c r="AB49" s="14"/>
+      <c r="AC49" s="14"/>
+      <c r="AD49" s="14"/>
     </row>
     <row r="50" s="1" customFormat="1" ht="34" spans="1:30">
-      <c r="A50"/>
+      <c r="A50" s="14"/>
       <c r="B50" s="1" t="s">
         <v>191</v>
       </c>
@@ -6253,24 +6454,24 @@
       <c r="P50" s="1">
         <v>40</v>
       </c>
-      <c r="Q50"/>
-      <c r="R50">
+      <c r="Q50" s="14"/>
+      <c r="R50" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="T50"/>
-      <c r="U50"/>
-      <c r="V50"/>
-      <c r="W50"/>
-      <c r="X50"/>
-      <c r="Y50"/>
-      <c r="Z50"/>
-      <c r="AB50"/>
-      <c r="AC50"/>
-      <c r="AD50"/>
+      <c r="T50" s="14"/>
+      <c r="U50" s="14"/>
+      <c r="V50" s="14"/>
+      <c r="W50" s="14"/>
+      <c r="X50" s="14"/>
+      <c r="Y50" s="14"/>
+      <c r="Z50" s="14"/>
+      <c r="AB50" s="14"/>
+      <c r="AC50" s="14"/>
+      <c r="AD50" s="14"/>
     </row>
     <row r="51" s="1" customFormat="1" ht="34" spans="1:30">
-      <c r="A51"/>
+      <c r="A51" s="14"/>
       <c r="B51" s="1" t="s">
         <v>194</v>
       </c>
@@ -6310,24 +6511,24 @@
       <c r="P51" s="1">
         <v>40</v>
       </c>
-      <c r="Q51"/>
-      <c r="R51">
+      <c r="Q51" s="14"/>
+      <c r="R51" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="T51"/>
-      <c r="U51"/>
-      <c r="V51"/>
-      <c r="W51"/>
-      <c r="X51"/>
-      <c r="Y51"/>
-      <c r="Z51"/>
-      <c r="AB51"/>
-      <c r="AC51"/>
-      <c r="AD51"/>
+      <c r="T51" s="14"/>
+      <c r="U51" s="14"/>
+      <c r="V51" s="14"/>
+      <c r="W51" s="14"/>
+      <c r="X51" s="14"/>
+      <c r="Y51" s="14"/>
+      <c r="Z51" s="14"/>
+      <c r="AB51" s="14"/>
+      <c r="AC51" s="14"/>
+      <c r="AD51" s="14"/>
     </row>
     <row r="52" s="1" customFormat="1" ht="17" spans="1:30">
-      <c r="A52"/>
+      <c r="A52" s="14"/>
       <c r="B52" s="1" t="s">
         <v>197</v>
       </c>
@@ -6367,24 +6568,24 @@
       <c r="P52" s="1">
         <v>240</v>
       </c>
-      <c r="Q52"/>
-      <c r="R52">
+      <c r="Q52" s="14"/>
+      <c r="R52" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="T52"/>
-      <c r="U52"/>
-      <c r="V52"/>
-      <c r="W52"/>
-      <c r="X52"/>
-      <c r="Y52"/>
-      <c r="Z52"/>
-      <c r="AB52"/>
-      <c r="AC52"/>
-      <c r="AD52"/>
+      <c r="T52" s="14"/>
+      <c r="U52" s="14"/>
+      <c r="V52" s="14"/>
+      <c r="W52" s="14"/>
+      <c r="X52" s="14"/>
+      <c r="Y52" s="14"/>
+      <c r="Z52" s="14"/>
+      <c r="AB52" s="14"/>
+      <c r="AC52" s="14"/>
+      <c r="AD52" s="14"/>
     </row>
     <row r="53" s="1" customFormat="1" ht="34" spans="1:30">
-      <c r="A53"/>
+      <c r="A53" s="14"/>
       <c r="B53" s="1" t="s">
         <v>202</v>
       </c>
@@ -6424,24 +6625,24 @@
       <c r="P53" s="1">
         <v>40</v>
       </c>
-      <c r="Q53"/>
-      <c r="R53">
+      <c r="Q53" s="14"/>
+      <c r="R53" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="T53"/>
-      <c r="U53"/>
-      <c r="V53"/>
-      <c r="W53"/>
-      <c r="X53"/>
-      <c r="Y53"/>
-      <c r="Z53"/>
-      <c r="AB53"/>
-      <c r="AC53"/>
-      <c r="AD53"/>
+      <c r="T53" s="14"/>
+      <c r="U53" s="14"/>
+      <c r="V53" s="14"/>
+      <c r="W53" s="14"/>
+      <c r="X53" s="14"/>
+      <c r="Y53" s="14"/>
+      <c r="Z53" s="14"/>
+      <c r="AB53" s="14"/>
+      <c r="AC53" s="14"/>
+      <c r="AD53" s="14"/>
     </row>
     <row r="54" s="1" customFormat="1" ht="34" spans="1:30">
-      <c r="A54"/>
+      <c r="A54" s="14"/>
       <c r="B54" s="1" t="s">
         <v>205</v>
       </c>
@@ -6481,24 +6682,24 @@
       <c r="P54" s="1">
         <v>150</v>
       </c>
-      <c r="Q54"/>
-      <c r="R54">
+      <c r="Q54" s="14"/>
+      <c r="R54" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="T54"/>
-      <c r="U54"/>
-      <c r="V54"/>
-      <c r="W54"/>
-      <c r="X54"/>
-      <c r="Y54"/>
-      <c r="Z54"/>
-      <c r="AB54"/>
-      <c r="AC54"/>
-      <c r="AD54"/>
+      <c r="T54" s="14"/>
+      <c r="U54" s="14"/>
+      <c r="V54" s="14"/>
+      <c r="W54" s="14"/>
+      <c r="X54" s="14"/>
+      <c r="Y54" s="14"/>
+      <c r="Z54" s="14"/>
+      <c r="AB54" s="14"/>
+      <c r="AC54" s="14"/>
+      <c r="AD54" s="14"/>
     </row>
     <row r="55" s="1" customFormat="1" ht="17" spans="1:30">
-      <c r="A55"/>
+      <c r="A55" s="14"/>
       <c r="B55" s="1" t="s">
         <v>208</v>
       </c>
@@ -6538,24 +6739,24 @@
       <c r="P55" s="1">
         <v>150</v>
       </c>
-      <c r="Q55"/>
-      <c r="R55">
+      <c r="Q55" s="14"/>
+      <c r="R55" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="T55"/>
-      <c r="U55"/>
-      <c r="V55"/>
-      <c r="W55"/>
-      <c r="X55"/>
-      <c r="Y55"/>
-      <c r="Z55"/>
-      <c r="AB55"/>
-      <c r="AC55"/>
-      <c r="AD55"/>
+      <c r="T55" s="14"/>
+      <c r="U55" s="14"/>
+      <c r="V55" s="14"/>
+      <c r="W55" s="14"/>
+      <c r="X55" s="14"/>
+      <c r="Y55" s="14"/>
+      <c r="Z55" s="14"/>
+      <c r="AB55" s="14"/>
+      <c r="AC55" s="14"/>
+      <c r="AD55" s="14"/>
     </row>
     <row r="56" s="1" customFormat="1" ht="17" spans="1:30">
-      <c r="A56"/>
+      <c r="A56" s="14"/>
       <c r="B56" s="1" t="s">
         <v>211</v>
       </c>
@@ -6595,24 +6796,24 @@
       <c r="P56" s="1">
         <v>40</v>
       </c>
-      <c r="Q56"/>
-      <c r="R56">
+      <c r="Q56" s="14"/>
+      <c r="R56" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="T56"/>
-      <c r="U56"/>
-      <c r="V56"/>
-      <c r="W56"/>
-      <c r="X56"/>
-      <c r="Y56"/>
-      <c r="Z56"/>
-      <c r="AB56"/>
-      <c r="AC56"/>
-      <c r="AD56"/>
+      <c r="T56" s="14"/>
+      <c r="U56" s="14"/>
+      <c r="V56" s="14"/>
+      <c r="W56" s="14"/>
+      <c r="X56" s="14"/>
+      <c r="Y56" s="14"/>
+      <c r="Z56" s="14"/>
+      <c r="AB56" s="14"/>
+      <c r="AC56" s="14"/>
+      <c r="AD56" s="14"/>
     </row>
     <row r="57" s="1" customFormat="1" ht="17" spans="1:30">
-      <c r="A57"/>
+      <c r="A57" s="14"/>
       <c r="B57" s="1" t="s">
         <v>214</v>
       </c>
@@ -6652,21 +6853,21 @@
       <c r="P57" s="1">
         <v>40</v>
       </c>
-      <c r="Q57"/>
-      <c r="R57"/>
-      <c r="T57"/>
-      <c r="U57"/>
-      <c r="V57"/>
-      <c r="W57"/>
-      <c r="X57"/>
-      <c r="Y57"/>
-      <c r="Z57"/>
-      <c r="AB57"/>
-      <c r="AC57"/>
-      <c r="AD57"/>
+      <c r="Q57" s="14"/>
+      <c r="R57" s="14"/>
+      <c r="T57" s="14"/>
+      <c r="U57" s="14"/>
+      <c r="V57" s="14"/>
+      <c r="W57" s="14"/>
+      <c r="X57" s="14"/>
+      <c r="Y57" s="14"/>
+      <c r="Z57" s="14"/>
+      <c r="AB57" s="14"/>
+      <c r="AC57" s="14"/>
+      <c r="AD57" s="14"/>
     </row>
     <row r="58" s="1" customFormat="1" ht="17" spans="1:30">
-      <c r="A58"/>
+      <c r="A58" s="14"/>
       <c r="B58" s="1" t="s">
         <v>217</v>
       </c>
@@ -6706,21 +6907,21 @@
       <c r="P58" s="1">
         <v>80</v>
       </c>
-      <c r="Q58"/>
-      <c r="R58"/>
-      <c r="T58"/>
-      <c r="U58"/>
-      <c r="V58"/>
-      <c r="W58"/>
-      <c r="X58"/>
-      <c r="Y58"/>
-      <c r="Z58"/>
-      <c r="AB58"/>
-      <c r="AC58"/>
-      <c r="AD58"/>
+      <c r="Q58" s="14"/>
+      <c r="R58" s="14"/>
+      <c r="T58" s="14"/>
+      <c r="U58" s="14"/>
+      <c r="V58" s="14"/>
+      <c r="W58" s="14"/>
+      <c r="X58" s="14"/>
+      <c r="Y58" s="14"/>
+      <c r="Z58" s="14"/>
+      <c r="AB58" s="14"/>
+      <c r="AC58" s="14"/>
+      <c r="AD58" s="14"/>
     </row>
     <row r="59" s="1" customFormat="1" ht="17" spans="1:30">
-      <c r="A59"/>
+      <c r="A59" s="14"/>
       <c r="B59" s="1" t="s">
         <v>220</v>
       </c>
@@ -6760,21 +6961,21 @@
       <c r="P59" s="1">
         <v>80</v>
       </c>
-      <c r="Q59"/>
-      <c r="R59"/>
-      <c r="T59"/>
-      <c r="U59"/>
-      <c r="V59"/>
-      <c r="W59"/>
-      <c r="X59"/>
-      <c r="Y59"/>
-      <c r="Z59"/>
-      <c r="AB59"/>
-      <c r="AC59"/>
-      <c r="AD59"/>
+      <c r="Q59" s="14"/>
+      <c r="R59" s="14"/>
+      <c r="T59" s="14"/>
+      <c r="U59" s="14"/>
+      <c r="V59" s="14"/>
+      <c r="W59" s="14"/>
+      <c r="X59" s="14"/>
+      <c r="Y59" s="14"/>
+      <c r="Z59" s="14"/>
+      <c r="AB59" s="14"/>
+      <c r="AC59" s="14"/>
+      <c r="AD59" s="14"/>
     </row>
     <row r="60" s="1" customFormat="1" ht="17" spans="1:30">
-      <c r="A60"/>
+      <c r="A60" s="14"/>
       <c r="B60" s="1" t="s">
         <v>223</v>
       </c>
@@ -6814,21 +7015,21 @@
       <c r="P60" s="1">
         <v>80</v>
       </c>
-      <c r="Q60"/>
-      <c r="R60"/>
-      <c r="T60"/>
-      <c r="U60"/>
-      <c r="V60"/>
-      <c r="W60"/>
-      <c r="X60"/>
-      <c r="Y60"/>
-      <c r="Z60"/>
-      <c r="AB60"/>
-      <c r="AC60"/>
-      <c r="AD60"/>
+      <c r="Q60" s="14"/>
+      <c r="R60" s="14"/>
+      <c r="T60" s="14"/>
+      <c r="U60" s="14"/>
+      <c r="V60" s="14"/>
+      <c r="W60" s="14"/>
+      <c r="X60" s="14"/>
+      <c r="Y60" s="14"/>
+      <c r="Z60" s="14"/>
+      <c r="AB60" s="14"/>
+      <c r="AC60" s="14"/>
+      <c r="AD60" s="14"/>
     </row>
     <row r="61" s="1" customFormat="1" ht="17" spans="1:30">
-      <c r="A61"/>
+      <c r="A61" s="14"/>
       <c r="B61" s="1" t="s">
         <v>226</v>
       </c>
@@ -6868,21 +7069,21 @@
       <c r="P61" s="1">
         <v>80</v>
       </c>
-      <c r="Q61"/>
-      <c r="R61"/>
-      <c r="T61"/>
-      <c r="U61"/>
-      <c r="V61"/>
-      <c r="W61"/>
-      <c r="X61"/>
-      <c r="Y61"/>
-      <c r="Z61"/>
-      <c r="AB61"/>
-      <c r="AC61"/>
-      <c r="AD61"/>
+      <c r="Q61" s="14"/>
+      <c r="R61" s="14"/>
+      <c r="T61" s="14"/>
+      <c r="U61" s="14"/>
+      <c r="V61" s="14"/>
+      <c r="W61" s="14"/>
+      <c r="X61" s="14"/>
+      <c r="Y61" s="14"/>
+      <c r="Z61" s="14"/>
+      <c r="AB61" s="14"/>
+      <c r="AC61" s="14"/>
+      <c r="AD61" s="14"/>
     </row>
     <row r="62" s="1" customFormat="1" ht="34" spans="1:30">
-      <c r="A62"/>
+      <c r="A62" s="14"/>
       <c r="B62" s="1" t="s">
         <v>229</v>
       </c>
@@ -6922,24 +7123,24 @@
       <c r="P62" s="1">
         <v>80</v>
       </c>
-      <c r="Q62"/>
-      <c r="R62">
+      <c r="Q62" s="14"/>
+      <c r="R62" s="14">
         <f t="shared" ref="R62:R75" si="8">IFERROR(VLOOKUP(E62,$T$7:$AB$12,9,FALSE),0)</f>
         <v>0</v>
       </c>
-      <c r="T62"/>
-      <c r="U62"/>
-      <c r="V62"/>
-      <c r="W62"/>
-      <c r="X62"/>
-      <c r="Y62"/>
-      <c r="Z62"/>
-      <c r="AB62"/>
-      <c r="AC62"/>
-      <c r="AD62"/>
+      <c r="T62" s="14"/>
+      <c r="U62" s="14"/>
+      <c r="V62" s="14"/>
+      <c r="W62" s="14"/>
+      <c r="X62" s="14"/>
+      <c r="Y62" s="14"/>
+      <c r="Z62" s="14"/>
+      <c r="AB62" s="14"/>
+      <c r="AC62" s="14"/>
+      <c r="AD62" s="14"/>
     </row>
     <row r="63" s="1" customFormat="1" ht="17" spans="1:30">
-      <c r="A63"/>
+      <c r="A63" s="14"/>
       <c r="B63" s="1" t="s">
         <v>232</v>
       </c>
@@ -6979,24 +7180,24 @@
       <c r="P63" s="1">
         <v>40</v>
       </c>
-      <c r="Q63"/>
-      <c r="R63">
+      <c r="Q63" s="14"/>
+      <c r="R63" s="14">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="T63"/>
-      <c r="U63"/>
-      <c r="V63"/>
-      <c r="W63"/>
-      <c r="X63"/>
-      <c r="Y63"/>
-      <c r="Z63"/>
-      <c r="AB63"/>
-      <c r="AC63"/>
-      <c r="AD63"/>
+      <c r="T63" s="14"/>
+      <c r="U63" s="14"/>
+      <c r="V63" s="14"/>
+      <c r="W63" s="14"/>
+      <c r="X63" s="14"/>
+      <c r="Y63" s="14"/>
+      <c r="Z63" s="14"/>
+      <c r="AB63" s="14"/>
+      <c r="AC63" s="14"/>
+      <c r="AD63" s="14"/>
     </row>
     <row r="64" s="1" customFormat="1" ht="17" spans="1:30">
-      <c r="A64"/>
+      <c r="A64" s="14"/>
       <c r="B64" s="1" t="s">
         <v>235</v>
       </c>
@@ -7036,21 +7237,21 @@
       <c r="P64" s="1">
         <v>50</v>
       </c>
-      <c r="Q64"/>
-      <c r="R64"/>
-      <c r="T64"/>
-      <c r="U64"/>
-      <c r="V64"/>
-      <c r="W64"/>
-      <c r="X64"/>
-      <c r="Y64"/>
-      <c r="Z64"/>
-      <c r="AB64"/>
-      <c r="AC64"/>
-      <c r="AD64"/>
+      <c r="Q64" s="14"/>
+      <c r="R64" s="14"/>
+      <c r="T64" s="14"/>
+      <c r="U64" s="14"/>
+      <c r="V64" s="14"/>
+      <c r="W64" s="14"/>
+      <c r="X64" s="14"/>
+      <c r="Y64" s="14"/>
+      <c r="Z64" s="14"/>
+      <c r="AB64" s="14"/>
+      <c r="AC64" s="14"/>
+      <c r="AD64" s="14"/>
     </row>
     <row r="65" s="1" customFormat="1" ht="17" spans="1:30">
-      <c r="A65"/>
+      <c r="A65" s="14"/>
       <c r="B65" s="1" t="s">
         <v>238</v>
       </c>
@@ -7090,21 +7291,21 @@
       <c r="P65" s="1">
         <v>50</v>
       </c>
-      <c r="Q65"/>
-      <c r="R65"/>
-      <c r="T65"/>
-      <c r="U65"/>
-      <c r="V65"/>
-      <c r="W65"/>
-      <c r="X65"/>
-      <c r="Y65"/>
-      <c r="Z65"/>
-      <c r="AB65"/>
-      <c r="AC65"/>
-      <c r="AD65"/>
+      <c r="Q65" s="14"/>
+      <c r="R65" s="14"/>
+      <c r="T65" s="14"/>
+      <c r="U65" s="14"/>
+      <c r="V65" s="14"/>
+      <c r="W65" s="14"/>
+      <c r="X65" s="14"/>
+      <c r="Y65" s="14"/>
+      <c r="Z65" s="14"/>
+      <c r="AB65" s="14"/>
+      <c r="AC65" s="14"/>
+      <c r="AD65" s="14"/>
     </row>
     <row r="66" s="1" customFormat="1" ht="34" spans="1:30">
-      <c r="A66"/>
+      <c r="A66" s="14"/>
       <c r="B66" s="1" t="s">
         <v>241</v>
       </c>
@@ -7144,24 +7345,24 @@
       <c r="P66" s="1">
         <v>80</v>
       </c>
-      <c r="Q66"/>
-      <c r="R66">
+      <c r="Q66" s="14"/>
+      <c r="R66" s="14">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="T66"/>
-      <c r="U66"/>
-      <c r="V66"/>
-      <c r="W66"/>
-      <c r="X66"/>
-      <c r="Y66"/>
-      <c r="Z66"/>
-      <c r="AB66"/>
-      <c r="AC66"/>
-      <c r="AD66"/>
+      <c r="T66" s="14"/>
+      <c r="U66" s="14"/>
+      <c r="V66" s="14"/>
+      <c r="W66" s="14"/>
+      <c r="X66" s="14"/>
+      <c r="Y66" s="14"/>
+      <c r="Z66" s="14"/>
+      <c r="AB66" s="14"/>
+      <c r="AC66" s="14"/>
+      <c r="AD66" s="14"/>
     </row>
     <row r="67" s="1" customFormat="1" ht="34" spans="1:30">
-      <c r="A67"/>
+      <c r="A67" s="14"/>
       <c r="B67" s="1" t="s">
         <v>244</v>
       </c>
@@ -7204,24 +7405,24 @@
       <c r="P67" s="1">
         <v>80</v>
       </c>
-      <c r="Q67"/>
-      <c r="R67">
+      <c r="Q67" s="14"/>
+      <c r="R67" s="14">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="T67"/>
-      <c r="U67"/>
-      <c r="V67"/>
-      <c r="W67"/>
-      <c r="X67"/>
-      <c r="Y67"/>
-      <c r="Z67"/>
-      <c r="AB67"/>
-      <c r="AC67"/>
-      <c r="AD67"/>
+      <c r="T67" s="14"/>
+      <c r="U67" s="14"/>
+      <c r="V67" s="14"/>
+      <c r="W67" s="14"/>
+      <c r="X67" s="14"/>
+      <c r="Y67" s="14"/>
+      <c r="Z67" s="14"/>
+      <c r="AB67" s="14"/>
+      <c r="AC67" s="14"/>
+      <c r="AD67" s="14"/>
     </row>
     <row r="68" s="1" customFormat="1" ht="34" spans="1:30">
-      <c r="A68"/>
+      <c r="A68" s="14"/>
       <c r="B68" s="1" t="s">
         <v>248</v>
       </c>
@@ -7241,7 +7442,7 @@
         <v>0</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>247</v>
+        <v>167</v>
       </c>
       <c r="I68" s="1">
         <v>100</v>
@@ -7264,24 +7465,24 @@
       <c r="P68" s="1">
         <v>80</v>
       </c>
-      <c r="Q68"/>
-      <c r="R68">
+      <c r="Q68" s="14"/>
+      <c r="R68" s="14">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="T68"/>
-      <c r="U68"/>
-      <c r="V68"/>
-      <c r="W68"/>
-      <c r="X68"/>
-      <c r="Y68"/>
-      <c r="Z68"/>
-      <c r="AB68"/>
-      <c r="AC68"/>
-      <c r="AD68"/>
+      <c r="T68" s="14"/>
+      <c r="U68" s="14"/>
+      <c r="V68" s="14"/>
+      <c r="W68" s="14"/>
+      <c r="X68" s="14"/>
+      <c r="Y68" s="14"/>
+      <c r="Z68" s="14"/>
+      <c r="AB68" s="14"/>
+      <c r="AC68" s="14"/>
+      <c r="AD68" s="14"/>
     </row>
     <row r="69" s="1" customFormat="1" ht="34" spans="1:30">
-      <c r="A69"/>
+      <c r="A69" s="14"/>
       <c r="B69" s="1" t="s">
         <v>251</v>
       </c>
@@ -7321,24 +7522,24 @@
       <c r="P69" s="1">
         <v>40</v>
       </c>
-      <c r="Q69"/>
-      <c r="R69">
+      <c r="Q69" s="14"/>
+      <c r="R69" s="14">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="T69"/>
-      <c r="U69"/>
-      <c r="V69"/>
-      <c r="W69"/>
-      <c r="X69"/>
-      <c r="Y69"/>
-      <c r="Z69"/>
-      <c r="AB69"/>
-      <c r="AC69"/>
-      <c r="AD69"/>
+      <c r="T69" s="14"/>
+      <c r="U69" s="14"/>
+      <c r="V69" s="14"/>
+      <c r="W69" s="14"/>
+      <c r="X69" s="14"/>
+      <c r="Y69" s="14"/>
+      <c r="Z69" s="14"/>
+      <c r="AB69" s="14"/>
+      <c r="AC69" s="14"/>
+      <c r="AD69" s="14"/>
     </row>
     <row r="70" s="1" customFormat="1" ht="34" spans="1:30">
-      <c r="A70"/>
+      <c r="A70" s="14"/>
       <c r="B70" s="1" t="s">
         <v>254</v>
       </c>
@@ -7378,24 +7579,24 @@
       <c r="P70" s="1">
         <v>40</v>
       </c>
-      <c r="Q70"/>
-      <c r="R70">
+      <c r="Q70" s="14"/>
+      <c r="R70" s="14">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="T70"/>
-      <c r="U70"/>
-      <c r="V70"/>
-      <c r="W70"/>
-      <c r="X70"/>
-      <c r="Y70"/>
-      <c r="Z70"/>
-      <c r="AB70"/>
-      <c r="AC70"/>
-      <c r="AD70"/>
+      <c r="T70" s="14"/>
+      <c r="U70" s="14"/>
+      <c r="V70" s="14"/>
+      <c r="W70" s="14"/>
+      <c r="X70" s="14"/>
+      <c r="Y70" s="14"/>
+      <c r="Z70" s="14"/>
+      <c r="AB70" s="14"/>
+      <c r="AC70" s="14"/>
+      <c r="AD70" s="14"/>
     </row>
     <row r="71" s="1" customFormat="1" ht="51" spans="1:30">
-      <c r="A71"/>
+      <c r="A71" s="14"/>
       <c r="B71" s="1" t="s">
         <v>257</v>
       </c>
@@ -7435,24 +7636,24 @@
       <c r="P71" s="1">
         <v>80</v>
       </c>
-      <c r="Q71"/>
-      <c r="R71">
+      <c r="Q71" s="14"/>
+      <c r="R71" s="14">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="T71"/>
-      <c r="U71"/>
-      <c r="V71"/>
-      <c r="W71"/>
-      <c r="X71"/>
-      <c r="Y71"/>
-      <c r="Z71"/>
-      <c r="AB71"/>
-      <c r="AC71"/>
-      <c r="AD71"/>
+      <c r="T71" s="14"/>
+      <c r="U71" s="14"/>
+      <c r="V71" s="14"/>
+      <c r="W71" s="14"/>
+      <c r="X71" s="14"/>
+      <c r="Y71" s="14"/>
+      <c r="Z71" s="14"/>
+      <c r="AB71" s="14"/>
+      <c r="AC71" s="14"/>
+      <c r="AD71" s="14"/>
     </row>
     <row r="72" s="1" customFormat="1" ht="17" spans="1:30">
-      <c r="A72"/>
+      <c r="A72" s="14"/>
       <c r="B72" s="1" t="s">
         <v>260</v>
       </c>
@@ -7492,24 +7693,24 @@
       <c r="P72" s="1">
         <v>40</v>
       </c>
-      <c r="Q72"/>
-      <c r="R72">
+      <c r="Q72" s="14"/>
+      <c r="R72" s="14">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="T72"/>
-      <c r="U72"/>
-      <c r="V72"/>
-      <c r="W72"/>
-      <c r="X72"/>
-      <c r="Y72"/>
-      <c r="Z72"/>
-      <c r="AB72"/>
-      <c r="AC72"/>
-      <c r="AD72"/>
+      <c r="T72" s="14"/>
+      <c r="U72" s="14"/>
+      <c r="V72" s="14"/>
+      <c r="W72" s="14"/>
+      <c r="X72" s="14"/>
+      <c r="Y72" s="14"/>
+      <c r="Z72" s="14"/>
+      <c r="AB72" s="14"/>
+      <c r="AC72" s="14"/>
+      <c r="AD72" s="14"/>
     </row>
     <row r="73" s="1" customFormat="1" ht="17" spans="1:30">
-      <c r="A73"/>
+      <c r="A73" s="14"/>
       <c r="B73" s="1" t="s">
         <v>264</v>
       </c>
@@ -7549,24 +7750,24 @@
       <c r="P73" s="1">
         <v>40</v>
       </c>
-      <c r="Q73"/>
-      <c r="R73">
+      <c r="Q73" s="14"/>
+      <c r="R73" s="14">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="T73"/>
-      <c r="U73"/>
-      <c r="V73"/>
-      <c r="W73"/>
-      <c r="X73"/>
-      <c r="Y73"/>
-      <c r="Z73"/>
-      <c r="AB73"/>
-      <c r="AC73"/>
-      <c r="AD73"/>
+      <c r="T73" s="14"/>
+      <c r="U73" s="14"/>
+      <c r="V73" s="14"/>
+      <c r="W73" s="14"/>
+      <c r="X73" s="14"/>
+      <c r="Y73" s="14"/>
+      <c r="Z73" s="14"/>
+      <c r="AB73" s="14"/>
+      <c r="AC73" s="14"/>
+      <c r="AD73" s="14"/>
     </row>
     <row r="74" s="1" customFormat="1" ht="17" spans="1:30">
-      <c r="A74"/>
+      <c r="A74" s="14"/>
       <c r="B74" s="1" t="s">
         <v>267</v>
       </c>
@@ -7606,24 +7807,24 @@
       <c r="P74" s="1">
         <v>40</v>
       </c>
-      <c r="Q74"/>
-      <c r="R74">
+      <c r="Q74" s="14"/>
+      <c r="R74" s="14">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="T74"/>
-      <c r="U74"/>
-      <c r="V74"/>
-      <c r="W74"/>
-      <c r="X74"/>
-      <c r="Y74"/>
-      <c r="Z74"/>
-      <c r="AB74"/>
-      <c r="AC74"/>
-      <c r="AD74"/>
+      <c r="T74" s="14"/>
+      <c r="U74" s="14"/>
+      <c r="V74" s="14"/>
+      <c r="W74" s="14"/>
+      <c r="X74" s="14"/>
+      <c r="Y74" s="14"/>
+      <c r="Z74" s="14"/>
+      <c r="AB74" s="14"/>
+      <c r="AC74" s="14"/>
+      <c r="AD74" s="14"/>
     </row>
     <row r="75" s="1" customFormat="1" ht="17" spans="1:30">
-      <c r="A75"/>
+      <c r="A75" s="14"/>
       <c r="B75" s="1" t="s">
         <v>270</v>
       </c>
@@ -7663,24 +7864,24 @@
       <c r="P75" s="1">
         <v>40</v>
       </c>
-      <c r="Q75"/>
-      <c r="R75">
+      <c r="Q75" s="14"/>
+      <c r="R75" s="14">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="T75"/>
-      <c r="U75"/>
-      <c r="V75"/>
-      <c r="W75"/>
-      <c r="X75"/>
-      <c r="Y75"/>
-      <c r="Z75"/>
-      <c r="AB75"/>
-      <c r="AC75"/>
-      <c r="AD75"/>
+      <c r="T75" s="14"/>
+      <c r="U75" s="14"/>
+      <c r="V75" s="14"/>
+      <c r="W75" s="14"/>
+      <c r="X75" s="14"/>
+      <c r="Y75" s="14"/>
+      <c r="Z75" s="14"/>
+      <c r="AB75" s="14"/>
+      <c r="AC75" s="14"/>
+      <c r="AD75" s="14"/>
     </row>
     <row r="76" s="1" customFormat="1" ht="17" spans="1:30">
-      <c r="A76"/>
+      <c r="A76" s="14"/>
       <c r="B76" s="1" t="s">
         <v>273</v>
       </c>
@@ -7720,21 +7921,21 @@
       <c r="P76" s="1">
         <v>50</v>
       </c>
-      <c r="Q76"/>
-      <c r="R76"/>
-      <c r="T76"/>
-      <c r="U76"/>
-      <c r="V76"/>
-      <c r="W76"/>
-      <c r="X76"/>
-      <c r="Y76"/>
-      <c r="Z76"/>
-      <c r="AB76"/>
-      <c r="AC76"/>
-      <c r="AD76"/>
+      <c r="Q76" s="14"/>
+      <c r="R76" s="14"/>
+      <c r="T76" s="14"/>
+      <c r="U76" s="14"/>
+      <c r="V76" s="14"/>
+      <c r="W76" s="14"/>
+      <c r="X76" s="14"/>
+      <c r="Y76" s="14"/>
+      <c r="Z76" s="14"/>
+      <c r="AB76" s="14"/>
+      <c r="AC76" s="14"/>
+      <c r="AD76" s="14"/>
     </row>
     <row r="77" s="1" customFormat="1" ht="34" spans="1:30">
-      <c r="A77"/>
+      <c r="A77" s="14"/>
       <c r="B77" s="1" t="s">
         <v>276</v>
       </c>
@@ -7774,24 +7975,24 @@
       <c r="P77" s="1">
         <v>40</v>
       </c>
-      <c r="Q77"/>
-      <c r="R77">
+      <c r="Q77" s="14"/>
+      <c r="R77" s="14">
         <f t="shared" ref="R77:R81" si="9">IFERROR(VLOOKUP(E77,$T$7:$AB$12,9,FALSE),0)</f>
         <v>0</v>
       </c>
-      <c r="T77"/>
-      <c r="U77"/>
-      <c r="V77"/>
-      <c r="W77"/>
-      <c r="X77"/>
-      <c r="Y77"/>
-      <c r="Z77"/>
-      <c r="AB77"/>
-      <c r="AC77"/>
-      <c r="AD77"/>
+      <c r="T77" s="14"/>
+      <c r="U77" s="14"/>
+      <c r="V77" s="14"/>
+      <c r="W77" s="14"/>
+      <c r="X77" s="14"/>
+      <c r="Y77" s="14"/>
+      <c r="Z77" s="14"/>
+      <c r="AB77" s="14"/>
+      <c r="AC77" s="14"/>
+      <c r="AD77" s="14"/>
     </row>
     <row r="78" s="1" customFormat="1" ht="17" spans="1:30">
-      <c r="A78"/>
+      <c r="A78" s="14"/>
       <c r="B78" s="1" t="s">
         <v>279</v>
       </c>
@@ -7831,24 +8032,24 @@
       <c r="P78" s="1">
         <v>40</v>
       </c>
-      <c r="Q78"/>
-      <c r="R78">
+      <c r="Q78" s="14"/>
+      <c r="R78" s="14">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="T78"/>
-      <c r="U78"/>
-      <c r="V78"/>
-      <c r="W78"/>
-      <c r="X78"/>
-      <c r="Y78"/>
-      <c r="Z78"/>
-      <c r="AB78"/>
-      <c r="AC78"/>
-      <c r="AD78"/>
+      <c r="T78" s="14"/>
+      <c r="U78" s="14"/>
+      <c r="V78" s="14"/>
+      <c r="W78" s="14"/>
+      <c r="X78" s="14"/>
+      <c r="Y78" s="14"/>
+      <c r="Z78" s="14"/>
+      <c r="AB78" s="14"/>
+      <c r="AC78" s="14"/>
+      <c r="AD78" s="14"/>
     </row>
     <row r="79" s="1" customFormat="1" ht="17" spans="1:30">
-      <c r="A79"/>
+      <c r="A79" s="14"/>
       <c r="B79" s="1" t="s">
         <v>282</v>
       </c>
@@ -7888,24 +8089,24 @@
       <c r="P79" s="1">
         <v>40</v>
       </c>
-      <c r="Q79"/>
-      <c r="R79">
+      <c r="Q79" s="14"/>
+      <c r="R79" s="14">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="T79"/>
-      <c r="U79"/>
-      <c r="V79"/>
-      <c r="W79"/>
-      <c r="X79"/>
-      <c r="Y79"/>
-      <c r="Z79"/>
-      <c r="AB79"/>
-      <c r="AC79"/>
-      <c r="AD79"/>
+      <c r="T79" s="14"/>
+      <c r="U79" s="14"/>
+      <c r="V79" s="14"/>
+      <c r="W79" s="14"/>
+      <c r="X79" s="14"/>
+      <c r="Y79" s="14"/>
+      <c r="Z79" s="14"/>
+      <c r="AB79" s="14"/>
+      <c r="AC79" s="14"/>
+      <c r="AD79" s="14"/>
     </row>
     <row r="80" s="1" customFormat="1" ht="17" spans="1:30">
-      <c r="A80"/>
+      <c r="A80" s="14"/>
       <c r="B80" s="1" t="s">
         <v>285</v>
       </c>
@@ -7945,24 +8146,24 @@
       <c r="P80" s="1">
         <v>40</v>
       </c>
-      <c r="Q80"/>
-      <c r="R80">
+      <c r="Q80" s="14"/>
+      <c r="R80" s="14">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="T80"/>
-      <c r="U80"/>
-      <c r="V80"/>
-      <c r="W80"/>
-      <c r="X80"/>
-      <c r="Y80"/>
-      <c r="Z80"/>
-      <c r="AB80"/>
-      <c r="AC80"/>
-      <c r="AD80"/>
+      <c r="T80" s="14"/>
+      <c r="U80" s="14"/>
+      <c r="V80" s="14"/>
+      <c r="W80" s="14"/>
+      <c r="X80" s="14"/>
+      <c r="Y80" s="14"/>
+      <c r="Z80" s="14"/>
+      <c r="AB80" s="14"/>
+      <c r="AC80" s="14"/>
+      <c r="AD80" s="14"/>
     </row>
     <row r="81" s="1" customFormat="1" ht="34" spans="1:30">
-      <c r="A81"/>
+      <c r="A81" s="14"/>
       <c r="B81" s="1" t="s">
         <v>288</v>
       </c>
@@ -8002,24 +8203,24 @@
       <c r="P81" s="1">
         <v>40</v>
       </c>
-      <c r="Q81"/>
-      <c r="R81">
+      <c r="Q81" s="14"/>
+      <c r="R81" s="14">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="T81"/>
-      <c r="U81"/>
-      <c r="V81"/>
-      <c r="W81"/>
-      <c r="X81"/>
-      <c r="Y81"/>
-      <c r="Z81"/>
-      <c r="AB81"/>
-      <c r="AC81"/>
-      <c r="AD81"/>
+      <c r="T81" s="14"/>
+      <c r="U81" s="14"/>
+      <c r="V81" s="14"/>
+      <c r="W81" s="14"/>
+      <c r="X81" s="14"/>
+      <c r="Y81" s="14"/>
+      <c r="Z81" s="14"/>
+      <c r="AB81" s="14"/>
+      <c r="AC81" s="14"/>
+      <c r="AD81" s="14"/>
     </row>
     <row r="82" s="1" customFormat="1" ht="51" spans="1:30">
-      <c r="A82"/>
+      <c r="A82" s="14"/>
       <c r="B82" s="1" t="s">
         <v>291</v>
       </c>
@@ -8036,7 +8237,7 @@
         <v>43</v>
       </c>
       <c r="G82" s="1">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="H82" s="1" t="s">
         <v>294</v>
@@ -8062,21 +8263,21 @@
       <c r="P82" s="1">
         <v>50</v>
       </c>
-      <c r="Q82"/>
-      <c r="R82"/>
-      <c r="T82"/>
-      <c r="U82"/>
-      <c r="V82"/>
-      <c r="W82"/>
-      <c r="X82"/>
-      <c r="Y82"/>
-      <c r="Z82"/>
-      <c r="AB82"/>
-      <c r="AC82"/>
-      <c r="AD82"/>
+      <c r="Q82" s="14"/>
+      <c r="R82" s="14"/>
+      <c r="T82" s="14"/>
+      <c r="U82" s="14"/>
+      <c r="V82" s="14"/>
+      <c r="W82" s="14"/>
+      <c r="X82" s="14"/>
+      <c r="Y82" s="14"/>
+      <c r="Z82" s="14"/>
+      <c r="AB82" s="14"/>
+      <c r="AC82" s="14"/>
+      <c r="AD82" s="14"/>
     </row>
     <row r="83" s="1" customFormat="1" ht="34" spans="1:30">
-      <c r="A83"/>
+      <c r="A83" s="14"/>
       <c r="B83" s="1" t="s">
         <v>295</v>
       </c>
@@ -8116,21 +8317,21 @@
       <c r="P83" s="1">
         <v>80</v>
       </c>
-      <c r="Q83"/>
-      <c r="R83"/>
-      <c r="T83"/>
-      <c r="U83"/>
-      <c r="V83"/>
-      <c r="W83"/>
-      <c r="X83"/>
-      <c r="Y83"/>
-      <c r="Z83"/>
-      <c r="AB83"/>
-      <c r="AC83"/>
-      <c r="AD83"/>
+      <c r="Q83" s="14"/>
+      <c r="R83" s="14"/>
+      <c r="T83" s="14"/>
+      <c r="U83" s="14"/>
+      <c r="V83" s="14"/>
+      <c r="W83" s="14"/>
+      <c r="X83" s="14"/>
+      <c r="Y83" s="14"/>
+      <c r="Z83" s="14"/>
+      <c r="AB83" s="14"/>
+      <c r="AC83" s="14"/>
+      <c r="AD83" s="14"/>
     </row>
     <row r="84" s="1" customFormat="1" ht="34" spans="1:30">
-      <c r="A84"/>
+      <c r="A84" s="14"/>
       <c r="B84" s="1" t="s">
         <v>298</v>
       </c>
@@ -8173,24 +8374,24 @@
       <c r="P84" s="1">
         <v>240</v>
       </c>
-      <c r="Q84"/>
-      <c r="R84">
+      <c r="Q84" s="14"/>
+      <c r="R84" s="14">
         <f t="shared" ref="R84:R93" si="10">IFERROR(VLOOKUP(E84,$T$7:$AB$12,9,FALSE),0)</f>
         <v>0</v>
       </c>
-      <c r="T84"/>
-      <c r="U84"/>
-      <c r="V84"/>
-      <c r="W84"/>
-      <c r="X84"/>
-      <c r="Y84"/>
-      <c r="Z84"/>
-      <c r="AB84"/>
-      <c r="AC84"/>
-      <c r="AD84"/>
+      <c r="T84" s="14"/>
+      <c r="U84" s="14"/>
+      <c r="V84" s="14"/>
+      <c r="W84" s="14"/>
+      <c r="X84" s="14"/>
+      <c r="Y84" s="14"/>
+      <c r="Z84" s="14"/>
+      <c r="AB84" s="14"/>
+      <c r="AC84" s="14"/>
+      <c r="AD84" s="14"/>
     </row>
     <row r="85" s="1" customFormat="1" ht="34" spans="1:30">
-      <c r="A85"/>
+      <c r="A85" s="14"/>
       <c r="B85" s="1" t="s">
         <v>302</v>
       </c>
@@ -8233,24 +8434,24 @@
       <c r="P85" s="1">
         <v>150</v>
       </c>
-      <c r="Q85"/>
-      <c r="R85">
+      <c r="Q85" s="14"/>
+      <c r="R85" s="14">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="T85"/>
-      <c r="U85"/>
-      <c r="V85"/>
-      <c r="W85"/>
-      <c r="X85"/>
-      <c r="Y85"/>
-      <c r="Z85"/>
-      <c r="AB85"/>
-      <c r="AC85"/>
-      <c r="AD85"/>
+      <c r="T85" s="14"/>
+      <c r="U85" s="14"/>
+      <c r="V85" s="14"/>
+      <c r="W85" s="14"/>
+      <c r="X85" s="14"/>
+      <c r="Y85" s="14"/>
+      <c r="Z85" s="14"/>
+      <c r="AB85" s="14"/>
+      <c r="AC85" s="14"/>
+      <c r="AD85" s="14"/>
     </row>
     <row r="86" s="1" customFormat="1" ht="51" spans="1:30">
-      <c r="A86"/>
+      <c r="A86" s="14"/>
       <c r="B86" s="1" t="s">
         <v>306</v>
       </c>
@@ -8293,24 +8494,24 @@
       <c r="P86" s="1">
         <v>150</v>
       </c>
-      <c r="Q86"/>
-      <c r="R86">
+      <c r="Q86" s="14"/>
+      <c r="R86" s="14">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="T86"/>
-      <c r="U86"/>
-      <c r="V86"/>
-      <c r="W86"/>
-      <c r="X86"/>
-      <c r="Y86"/>
-      <c r="Z86"/>
-      <c r="AB86"/>
-      <c r="AC86"/>
-      <c r="AD86"/>
+      <c r="T86" s="14"/>
+      <c r="U86" s="14"/>
+      <c r="V86" s="14"/>
+      <c r="W86" s="14"/>
+      <c r="X86" s="14"/>
+      <c r="Y86" s="14"/>
+      <c r="Z86" s="14"/>
+      <c r="AB86" s="14"/>
+      <c r="AC86" s="14"/>
+      <c r="AD86" s="14"/>
     </row>
     <row r="87" s="1" customFormat="1" ht="51" spans="1:30">
-      <c r="A87"/>
+      <c r="A87" s="14"/>
       <c r="B87" s="1" t="s">
         <v>309</v>
       </c>
@@ -8350,24 +8551,24 @@
       <c r="P87" s="1">
         <v>150</v>
       </c>
-      <c r="Q87"/>
-      <c r="R87">
+      <c r="Q87" s="14"/>
+      <c r="R87" s="14">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="T87"/>
-      <c r="U87"/>
-      <c r="V87"/>
-      <c r="W87"/>
-      <c r="X87"/>
-      <c r="Y87"/>
-      <c r="Z87"/>
-      <c r="AB87"/>
-      <c r="AC87"/>
-      <c r="AD87"/>
+      <c r="T87" s="14"/>
+      <c r="U87" s="14"/>
+      <c r="V87" s="14"/>
+      <c r="W87" s="14"/>
+      <c r="X87" s="14"/>
+      <c r="Y87" s="14"/>
+      <c r="Z87" s="14"/>
+      <c r="AB87" s="14"/>
+      <c r="AC87" s="14"/>
+      <c r="AD87" s="14"/>
     </row>
     <row r="88" s="1" customFormat="1" ht="34" spans="1:30">
-      <c r="A88"/>
+      <c r="A88" s="14"/>
       <c r="B88" s="1" t="s">
         <v>312</v>
       </c>
@@ -8413,24 +8614,24 @@
       <c r="P88" s="1">
         <v>80</v>
       </c>
-      <c r="Q88"/>
-      <c r="R88">
+      <c r="Q88" s="14"/>
+      <c r="R88" s="14">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="T88"/>
-      <c r="U88"/>
-      <c r="V88"/>
-      <c r="W88"/>
-      <c r="X88"/>
-      <c r="Y88"/>
-      <c r="Z88"/>
-      <c r="AB88"/>
-      <c r="AC88"/>
-      <c r="AD88"/>
+      <c r="T88" s="14"/>
+      <c r="U88" s="14"/>
+      <c r="V88" s="14"/>
+      <c r="W88" s="14"/>
+      <c r="X88" s="14"/>
+      <c r="Y88" s="14"/>
+      <c r="Z88" s="14"/>
+      <c r="AB88" s="14"/>
+      <c r="AC88" s="14"/>
+      <c r="AD88" s="14"/>
     </row>
     <row r="89" s="1" customFormat="1" ht="34" spans="1:30">
-      <c r="A89"/>
+      <c r="A89" s="14"/>
       <c r="B89" s="1" t="s">
         <v>316</v>
       </c>
@@ -8447,7 +8648,7 @@
         <v>43</v>
       </c>
       <c r="G89" s="1">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="I89" s="1">
         <v>10</v>
@@ -8473,24 +8674,24 @@
       <c r="P89" s="1">
         <v>240</v>
       </c>
-      <c r="Q89"/>
-      <c r="R89">
+      <c r="Q89" s="14"/>
+      <c r="R89" s="14">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="T89"/>
-      <c r="U89"/>
-      <c r="V89"/>
-      <c r="W89"/>
-      <c r="X89"/>
-      <c r="Y89"/>
-      <c r="Z89"/>
-      <c r="AB89"/>
-      <c r="AC89"/>
-      <c r="AD89"/>
+      <c r="T89" s="14"/>
+      <c r="U89" s="14"/>
+      <c r="V89" s="14"/>
+      <c r="W89" s="14"/>
+      <c r="X89" s="14"/>
+      <c r="Y89" s="14"/>
+      <c r="Z89" s="14"/>
+      <c r="AB89" s="14"/>
+      <c r="AC89" s="14"/>
+      <c r="AD89" s="14"/>
     </row>
     <row r="90" s="1" customFormat="1" ht="34" spans="1:30">
-      <c r="A90"/>
+      <c r="A90" s="14"/>
       <c r="B90" s="1" t="s">
         <v>320</v>
       </c>
@@ -8533,24 +8734,24 @@
       <c r="P90" s="1">
         <v>80</v>
       </c>
-      <c r="Q90"/>
-      <c r="R90">
+      <c r="Q90" s="14"/>
+      <c r="R90" s="14">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="T90"/>
-      <c r="U90"/>
-      <c r="V90"/>
-      <c r="W90"/>
-      <c r="X90"/>
-      <c r="Y90"/>
-      <c r="Z90"/>
-      <c r="AB90"/>
-      <c r="AC90"/>
-      <c r="AD90"/>
+      <c r="T90" s="14"/>
+      <c r="U90" s="14"/>
+      <c r="V90" s="14"/>
+      <c r="W90" s="14"/>
+      <c r="X90" s="14"/>
+      <c r="Y90" s="14"/>
+      <c r="Z90" s="14"/>
+      <c r="AB90" s="14"/>
+      <c r="AC90" s="14"/>
+      <c r="AD90" s="14"/>
     </row>
     <row r="91" s="1" customFormat="1" ht="34" spans="1:30">
-      <c r="A91"/>
+      <c r="A91" s="14"/>
       <c r="B91" s="1" t="s">
         <v>323</v>
       </c>
@@ -8593,24 +8794,24 @@
       <c r="P91" s="1">
         <v>150</v>
       </c>
-      <c r="Q91"/>
-      <c r="R91">
+      <c r="Q91" s="14"/>
+      <c r="R91" s="14">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="T91"/>
-      <c r="U91"/>
-      <c r="V91"/>
-      <c r="W91"/>
-      <c r="X91"/>
-      <c r="Y91"/>
-      <c r="Z91"/>
-      <c r="AB91"/>
-      <c r="AC91"/>
-      <c r="AD91"/>
+      <c r="T91" s="14"/>
+      <c r="U91" s="14"/>
+      <c r="V91" s="14"/>
+      <c r="W91" s="14"/>
+      <c r="X91" s="14"/>
+      <c r="Y91" s="14"/>
+      <c r="Z91" s="14"/>
+      <c r="AB91" s="14"/>
+      <c r="AC91" s="14"/>
+      <c r="AD91" s="14"/>
     </row>
     <row r="92" s="1" customFormat="1" ht="34" spans="1:30">
-      <c r="A92"/>
+      <c r="A92" s="14"/>
       <c r="B92" s="1" t="s">
         <v>326</v>
       </c>
@@ -8656,24 +8857,24 @@
       <c r="P92" s="1">
         <v>80</v>
       </c>
-      <c r="Q92"/>
-      <c r="R92">
+      <c r="Q92" s="14"/>
+      <c r="R92" s="14">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="T92"/>
-      <c r="U92"/>
-      <c r="V92"/>
-      <c r="W92"/>
-      <c r="X92"/>
-      <c r="Y92"/>
-      <c r="Z92"/>
-      <c r="AB92"/>
-      <c r="AC92"/>
-      <c r="AD92"/>
+      <c r="T92" s="14"/>
+      <c r="U92" s="14"/>
+      <c r="V92" s="14"/>
+      <c r="W92" s="14"/>
+      <c r="X92" s="14"/>
+      <c r="Y92" s="14"/>
+      <c r="Z92" s="14"/>
+      <c r="AB92" s="14"/>
+      <c r="AC92" s="14"/>
+      <c r="AD92" s="14"/>
     </row>
     <row r="93" s="1" customFormat="1" ht="17" spans="1:30">
-      <c r="A93"/>
+      <c r="A93" s="14"/>
       <c r="B93" s="1" t="s">
         <v>330</v>
       </c>
@@ -8716,264 +8917,1228 @@
       <c r="P93" s="1">
         <v>80</v>
       </c>
-      <c r="Q93"/>
-      <c r="R93">
+      <c r="Q93" s="14"/>
+      <c r="R93" s="14">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="T93"/>
-      <c r="U93"/>
-      <c r="V93"/>
-      <c r="W93"/>
-      <c r="X93"/>
-      <c r="Y93"/>
-      <c r="Z93"/>
-      <c r="AB93"/>
-      <c r="AC93"/>
-      <c r="AD93"/>
+      <c r="T93" s="14"/>
+      <c r="U93" s="14"/>
+      <c r="V93" s="14"/>
+      <c r="W93" s="14"/>
+      <c r="X93" s="14"/>
+      <c r="Y93" s="14"/>
+      <c r="Z93" s="14"/>
+      <c r="AB93" s="14"/>
+      <c r="AC93" s="14"/>
+      <c r="AD93" s="14"/>
     </row>
     <row r="94" s="1" customFormat="1" ht="34" spans="1:30">
-      <c r="A94"/>
+      <c r="A94" s="14"/>
+      <c r="B94" s="14" t="s">
+        <v>333</v>
+      </c>
+      <c r="C94" s="14" t="s">
+        <v>334</v>
+      </c>
       <c r="D94" s="10" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="E94" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="Q94"/>
-      <c r="R94"/>
-      <c r="T94"/>
-      <c r="U94"/>
-      <c r="V94"/>
-      <c r="W94"/>
-      <c r="X94"/>
-      <c r="Y94"/>
-      <c r="Z94"/>
-      <c r="AB94"/>
-      <c r="AC94"/>
-      <c r="AD94"/>
-    </row>
-    <row r="95" s="13" customFormat="1" ht="51" spans="4:5">
-      <c r="D95" s="14" t="s">
-        <v>334</v>
+      <c r="F94" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="G94" s="14">
+        <v>2</v>
+      </c>
+      <c r="H94" s="14"/>
+      <c r="I94" s="14">
+        <v>10</v>
+      </c>
+      <c r="J94" s="14" t="s">
+        <v>201</v>
+      </c>
+      <c r="K94" s="14">
+        <v>0</v>
+      </c>
+      <c r="L94" s="14">
+        <v>0</v>
+      </c>
+      <c r="M94" s="14">
+        <v>0</v>
+      </c>
+      <c r="N94" s="14">
+        <v>0</v>
+      </c>
+      <c r="O94" s="14" t="s">
+        <v>305</v>
+      </c>
+      <c r="P94" s="14">
+        <v>240</v>
+      </c>
+      <c r="Q94" s="14"/>
+      <c r="R94" s="14"/>
+      <c r="T94" s="14"/>
+      <c r="U94" s="14"/>
+      <c r="V94" s="14"/>
+      <c r="W94" s="14"/>
+      <c r="X94" s="14"/>
+      <c r="Y94" s="14"/>
+      <c r="Z94" s="14"/>
+      <c r="AB94" s="14"/>
+      <c r="AC94" s="14"/>
+      <c r="AD94" s="14"/>
+    </row>
+    <row r="95" s="13" customFormat="1" ht="51" spans="2:16">
+      <c r="B95" s="14" t="s">
+        <v>336</v>
+      </c>
+      <c r="C95" s="14" t="s">
+        <v>337</v>
+      </c>
+      <c r="D95" s="15" t="s">
+        <v>338</v>
       </c>
       <c r="E95" s="13" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="96" s="13" customFormat="1" ht="51" spans="4:5">
-      <c r="D96" s="14" t="s">
-        <v>335</v>
+      <c r="F95" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="G95" s="14">
+        <v>30</v>
+      </c>
+      <c r="H95" s="14" t="s">
+        <v>339</v>
+      </c>
+      <c r="I95" s="14">
+        <v>300</v>
+      </c>
+      <c r="J95" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="K95" s="14">
+        <v>0</v>
+      </c>
+      <c r="L95" s="14">
+        <v>0</v>
+      </c>
+      <c r="M95" s="14">
+        <v>0</v>
+      </c>
+      <c r="N95" s="14">
+        <v>0</v>
+      </c>
+      <c r="O95" s="14"/>
+      <c r="P95" s="14">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="96" s="13" customFormat="1" ht="51" spans="2:16">
+      <c r="B96" s="14" t="s">
+        <v>340</v>
+      </c>
+      <c r="C96" s="14" t="s">
+        <v>341</v>
+      </c>
+      <c r="D96" s="15" t="s">
+        <v>342</v>
       </c>
       <c r="E96" s="13" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="97" s="13" customFormat="1" ht="51" spans="4:5">
-      <c r="D97" s="14" t="s">
-        <v>336</v>
+      <c r="F96" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="G96" s="14">
+        <v>1</v>
+      </c>
+      <c r="H96" s="14" t="s">
+        <v>339</v>
+      </c>
+      <c r="I96" s="14">
+        <v>100</v>
+      </c>
+      <c r="J96" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="K96" s="14">
+        <v>0</v>
+      </c>
+      <c r="L96" s="14">
+        <v>0</v>
+      </c>
+      <c r="M96" s="14">
+        <v>0</v>
+      </c>
+      <c r="N96" s="14">
+        <v>0</v>
+      </c>
+      <c r="O96" s="14" t="s">
+        <v>301</v>
+      </c>
+      <c r="P96" s="14">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="97" s="13" customFormat="1" ht="51" spans="2:16">
+      <c r="B97" s="14" t="s">
+        <v>343</v>
+      </c>
+      <c r="C97" s="14" t="s">
+        <v>344</v>
+      </c>
+      <c r="D97" s="15" t="s">
+        <v>345</v>
       </c>
       <c r="E97" s="13" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="98" s="13" customFormat="1" ht="51" spans="4:5">
-      <c r="D98" s="14" t="s">
-        <v>337</v>
+      <c r="F97" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="G97" s="14">
+        <v>10</v>
+      </c>
+      <c r="H97" s="14" t="s">
+        <v>346</v>
+      </c>
+      <c r="I97" s="14">
+        <v>100</v>
+      </c>
+      <c r="J97" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="K97" s="14">
+        <v>0</v>
+      </c>
+      <c r="L97" s="14">
+        <v>0</v>
+      </c>
+      <c r="M97" s="14">
+        <v>0</v>
+      </c>
+      <c r="N97" s="14">
+        <v>0</v>
+      </c>
+      <c r="O97" s="14"/>
+      <c r="P97" s="14">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="98" s="13" customFormat="1" ht="51" spans="2:16">
+      <c r="B98" s="14" t="s">
+        <v>347</v>
+      </c>
+      <c r="C98" s="14" t="s">
+        <v>348</v>
+      </c>
+      <c r="D98" s="15" t="s">
+        <v>349</v>
       </c>
       <c r="E98" s="13" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="99" s="13" customFormat="1" ht="51" spans="4:5">
-      <c r="D99" s="14" t="s">
-        <v>338</v>
+      <c r="F98" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="G98" s="14">
+        <v>0.1</v>
+      </c>
+      <c r="H98" s="14" t="s">
+        <v>350</v>
+      </c>
+      <c r="I98" s="14">
+        <v>30</v>
+      </c>
+      <c r="J98" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="K98" s="14">
+        <v>0</v>
+      </c>
+      <c r="L98" s="14">
+        <v>0</v>
+      </c>
+      <c r="M98" s="14">
+        <v>0</v>
+      </c>
+      <c r="N98" s="14">
+        <v>0</v>
+      </c>
+      <c r="O98" s="14"/>
+      <c r="P98" s="14">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="99" s="13" customFormat="1" ht="51" spans="2:16">
+      <c r="B99" s="14" t="s">
+        <v>351</v>
+      </c>
+      <c r="C99" s="14" t="s">
+        <v>352</v>
+      </c>
+      <c r="D99" s="15" t="s">
+        <v>353</v>
       </c>
       <c r="E99" s="13" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="100" s="13" customFormat="1" ht="51" spans="4:5">
-      <c r="D100" s="14" t="s">
-        <v>339</v>
+      <c r="F99" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="G99" s="14">
+        <v>50</v>
+      </c>
+      <c r="H99" s="14" t="s">
+        <v>354</v>
+      </c>
+      <c r="I99" s="14">
+        <v>100</v>
+      </c>
+      <c r="J99" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="K99" s="14">
+        <v>0</v>
+      </c>
+      <c r="L99" s="14">
+        <v>0</v>
+      </c>
+      <c r="M99" s="14">
+        <v>0</v>
+      </c>
+      <c r="N99" s="14">
+        <v>0</v>
+      </c>
+      <c r="O99" s="14"/>
+      <c r="P99" s="14">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="100" s="13" customFormat="1" ht="51" spans="2:16">
+      <c r="B100" s="14" t="s">
+        <v>355</v>
+      </c>
+      <c r="C100" s="14" t="s">
+        <v>356</v>
+      </c>
+      <c r="D100" s="15" t="s">
+        <v>357</v>
       </c>
       <c r="E100" s="13" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="101" s="13" customFormat="1" ht="51" spans="4:5">
-      <c r="D101" s="14" t="s">
-        <v>340</v>
+      <c r="F100" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="G100" s="14">
+        <v>0.5</v>
+      </c>
+      <c r="H100" s="14" t="s">
+        <v>358</v>
+      </c>
+      <c r="I100" s="14">
+        <v>100</v>
+      </c>
+      <c r="J100" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="K100" s="14">
+        <v>0</v>
+      </c>
+      <c r="L100" s="14">
+        <v>0</v>
+      </c>
+      <c r="M100" s="14">
+        <v>0</v>
+      </c>
+      <c r="N100" s="14">
+        <v>0</v>
+      </c>
+      <c r="O100" s="14"/>
+      <c r="P100" s="14">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="101" s="13" customFormat="1" ht="51" spans="2:16">
+      <c r="B101" s="14" t="s">
+        <v>359</v>
+      </c>
+      <c r="C101" s="14" t="s">
+        <v>360</v>
+      </c>
+      <c r="D101" s="15" t="s">
+        <v>361</v>
       </c>
       <c r="E101" s="13" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="102" s="13" customFormat="1" ht="51" spans="4:5">
-      <c r="D102" s="14" t="s">
-        <v>341</v>
+      <c r="F101" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="G101" s="14">
+        <v>1</v>
+      </c>
+      <c r="H101" s="14" t="s">
+        <v>362</v>
+      </c>
+      <c r="I101" s="14">
+        <v>30</v>
+      </c>
+      <c r="J101" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="K101" s="14">
+        <v>0</v>
+      </c>
+      <c r="L101" s="14">
+        <v>0</v>
+      </c>
+      <c r="M101" s="14">
+        <v>0</v>
+      </c>
+      <c r="N101" s="14">
+        <v>0</v>
+      </c>
+      <c r="O101" s="14"/>
+      <c r="P101" s="14">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="102" s="13" customFormat="1" ht="51" spans="2:16">
+      <c r="B102" s="14" t="s">
+        <v>363</v>
+      </c>
+      <c r="C102" s="14" t="s">
+        <v>364</v>
+      </c>
+      <c r="D102" s="15" t="s">
+        <v>365</v>
       </c>
       <c r="E102" s="13" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="103" s="13" customFormat="1" ht="51" spans="4:5">
-      <c r="D103" s="14" t="s">
-        <v>342</v>
+      <c r="F102" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="G102" s="14">
+        <v>10</v>
+      </c>
+      <c r="H102" s="14" t="s">
+        <v>366</v>
+      </c>
+      <c r="I102" s="14">
+        <v>30</v>
+      </c>
+      <c r="J102" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="K102" s="14">
+        <v>0</v>
+      </c>
+      <c r="L102" s="14">
+        <v>0</v>
+      </c>
+      <c r="M102" s="14">
+        <v>0</v>
+      </c>
+      <c r="N102" s="14">
+        <v>0</v>
+      </c>
+      <c r="O102" s="14"/>
+      <c r="P102" s="14">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="103" s="13" customFormat="1" ht="51" spans="2:16">
+      <c r="B103" s="14" t="s">
+        <v>367</v>
+      </c>
+      <c r="C103" s="14" t="s">
+        <v>368</v>
+      </c>
+      <c r="D103" s="15" t="s">
+        <v>369</v>
       </c>
       <c r="E103" s="13" t="s">
         <v>67</v>
       </c>
+      <c r="F103" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="G103" s="14">
+        <v>0.1</v>
+      </c>
+      <c r="H103" s="14"/>
+      <c r="I103" s="14">
+        <v>100</v>
+      </c>
+      <c r="J103" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="K103" s="14">
+        <v>0</v>
+      </c>
+      <c r="L103" s="14">
+        <v>0</v>
+      </c>
+      <c r="M103" s="14">
+        <v>0</v>
+      </c>
+      <c r="N103" s="14">
+        <v>0</v>
+      </c>
+      <c r="O103" s="14"/>
+      <c r="P103" s="14">
+        <v>80</v>
+      </c>
     </row>
     <row r="104" s="1" customFormat="1" ht="51" spans="2:18">
-      <c r="B104" s="13"/>
-      <c r="C104" s="13"/>
-      <c r="D104" s="14" t="s">
-        <v>343</v>
+      <c r="B104" s="13" t="s">
+        <v>370</v>
+      </c>
+      <c r="C104" s="13" t="s">
+        <v>371</v>
+      </c>
+      <c r="D104" s="15" t="s">
+        <v>372</v>
       </c>
       <c r="E104" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="F104" s="13"/>
-      <c r="G104" s="13"/>
+      <c r="F104" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="G104" s="13">
+        <v>10</v>
+      </c>
       <c r="H104" s="13"/>
-      <c r="I104" s="13"/>
-      <c r="J104" s="13"/>
-      <c r="K104" s="13"/>
-      <c r="L104" s="13"/>
-      <c r="M104" s="13"/>
-      <c r="N104" s="13"/>
+      <c r="I104" s="13">
+        <v>300</v>
+      </c>
+      <c r="J104" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="K104" s="13">
+        <v>0</v>
+      </c>
+      <c r="L104" s="13">
+        <v>0</v>
+      </c>
+      <c r="M104" s="13">
+        <v>0</v>
+      </c>
+      <c r="N104" s="13">
+        <v>0</v>
+      </c>
       <c r="O104" s="13"/>
-      <c r="P104" s="13"/>
+      <c r="P104" s="13">
+        <v>40</v>
+      </c>
       <c r="Q104" s="13"/>
       <c r="R104" s="13"/>
     </row>
-    <row r="105" ht="34" spans="4:5">
+    <row r="105" ht="34" spans="2:16">
+      <c r="B105" s="14" t="s">
+        <v>373</v>
+      </c>
+      <c r="C105" s="14" t="s">
+        <v>374</v>
+      </c>
       <c r="D105" s="10" t="s">
-        <v>344</v>
+        <v>375</v>
       </c>
       <c r="E105" s="13" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="106" ht="34" spans="4:5">
+      <c r="F105" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="G105" s="14">
+        <v>10</v>
+      </c>
+      <c r="H105" s="14" t="s">
+        <v>376</v>
+      </c>
+      <c r="I105" s="14">
+        <v>100</v>
+      </c>
+      <c r="J105" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="K105" s="14">
+        <v>0</v>
+      </c>
+      <c r="L105" s="14">
+        <v>0</v>
+      </c>
+      <c r="M105" s="14">
+        <v>0</v>
+      </c>
+      <c r="N105" s="14">
+        <v>0</v>
+      </c>
+      <c r="O105" s="14"/>
+      <c r="P105" s="14">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="106" ht="34" spans="2:16">
+      <c r="B106" s="14" t="s">
+        <v>377</v>
+      </c>
+      <c r="C106" s="14" t="s">
+        <v>378</v>
+      </c>
       <c r="D106" s="10" t="s">
-        <v>345</v>
+        <v>379</v>
       </c>
       <c r="E106" s="13" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="107" ht="51" spans="4:5">
+      <c r="F106" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="G106" s="14">
+        <v>10</v>
+      </c>
+      <c r="H106" s="14" t="s">
+        <v>380</v>
+      </c>
+      <c r="I106" s="14">
+        <v>100</v>
+      </c>
+      <c r="J106" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="K106" s="14">
+        <v>0</v>
+      </c>
+      <c r="L106" s="14">
+        <v>0</v>
+      </c>
+      <c r="M106" s="14">
+        <v>0</v>
+      </c>
+      <c r="N106" s="14">
+        <v>0</v>
+      </c>
+      <c r="O106" s="14"/>
+      <c r="P106" s="14">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="107" ht="51" spans="2:16">
+      <c r="B107" s="14" t="s">
+        <v>381</v>
+      </c>
+      <c r="C107" s="14" t="s">
+        <v>382</v>
+      </c>
       <c r="D107" s="10" t="s">
-        <v>346</v>
+        <v>383</v>
       </c>
       <c r="E107" s="1" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="108" ht="34" spans="4:5">
+      <c r="F107" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="G107" s="14">
+        <v>1</v>
+      </c>
+      <c r="H107" s="14"/>
+      <c r="I107" s="14">
+        <v>30</v>
+      </c>
+      <c r="J107" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="K107" s="14">
+        <v>0</v>
+      </c>
+      <c r="L107" s="14">
+        <v>0</v>
+      </c>
+      <c r="M107" s="14">
+        <v>0</v>
+      </c>
+      <c r="N107" s="14">
+        <v>0</v>
+      </c>
+      <c r="O107" s="14"/>
+      <c r="P107" s="14">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="108" ht="34" spans="2:16">
+      <c r="B108" s="14" t="s">
+        <v>384</v>
+      </c>
+      <c r="C108" s="14" t="s">
+        <v>385</v>
+      </c>
       <c r="D108" s="10" t="s">
-        <v>347</v>
+        <v>386</v>
       </c>
       <c r="E108" s="1" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="109" ht="34" spans="4:5">
+      <c r="F108" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="G108" s="14">
+        <v>0</v>
+      </c>
+      <c r="H108" s="14" t="s">
+        <v>387</v>
+      </c>
+      <c r="I108" s="14">
+        <v>10</v>
+      </c>
+      <c r="J108" s="14" t="s">
+        <v>201</v>
+      </c>
+      <c r="K108" s="14">
+        <v>0</v>
+      </c>
+      <c r="L108" s="14">
+        <v>0</v>
+      </c>
+      <c r="M108" s="14">
+        <v>0</v>
+      </c>
+      <c r="N108" s="14">
+        <v>0</v>
+      </c>
+      <c r="O108" s="14" t="s">
+        <v>319</v>
+      </c>
+      <c r="P108" s="14">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="109" ht="34" spans="2:16">
+      <c r="B109" s="14" t="s">
+        <v>388</v>
+      </c>
+      <c r="C109" s="14" t="s">
+        <v>389</v>
+      </c>
       <c r="D109" s="10" t="s">
-        <v>348</v>
+        <v>390</v>
       </c>
       <c r="E109" s="1" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="110" ht="34" spans="4:5">
+      <c r="F109" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="G109" s="14">
+        <v>1</v>
+      </c>
+      <c r="H109" s="14" t="s">
+        <v>391</v>
+      </c>
+      <c r="I109" s="14">
+        <v>10</v>
+      </c>
+      <c r="J109" s="14" t="s">
+        <v>201</v>
+      </c>
+      <c r="K109" s="14">
+        <v>0</v>
+      </c>
+      <c r="L109" s="14">
+        <v>0</v>
+      </c>
+      <c r="M109" s="14">
+        <v>0</v>
+      </c>
+      <c r="N109" s="14">
+        <v>0</v>
+      </c>
+      <c r="O109" s="14"/>
+      <c r="P109" s="14">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="110" ht="34" spans="2:16">
+      <c r="B110" s="14" t="s">
+        <v>392</v>
+      </c>
+      <c r="C110" s="14" t="s">
+        <v>393</v>
+      </c>
       <c r="D110" s="10" t="s">
-        <v>349</v>
+        <v>394</v>
       </c>
       <c r="E110" s="1" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="111" ht="34" spans="4:5">
+      <c r="F110" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="G110" s="14">
+        <v>3</v>
+      </c>
+      <c r="H110" s="14"/>
+      <c r="I110" s="14">
+        <v>10</v>
+      </c>
+      <c r="J110" s="14" t="s">
+        <v>201</v>
+      </c>
+      <c r="K110" s="14">
+        <v>0</v>
+      </c>
+      <c r="L110" s="14">
+        <v>0</v>
+      </c>
+      <c r="M110" s="14">
+        <v>0</v>
+      </c>
+      <c r="N110" s="14">
+        <v>0</v>
+      </c>
+      <c r="O110" s="14"/>
+      <c r="P110" s="14">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="111" ht="34" spans="2:16">
+      <c r="B111" s="14" t="s">
+        <v>395</v>
+      </c>
+      <c r="C111" s="14" t="s">
+        <v>396</v>
+      </c>
       <c r="D111" s="10" t="s">
-        <v>350</v>
+        <v>397</v>
       </c>
       <c r="E111" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="112" spans="4:5">
+      <c r="F111" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="G111" s="14">
+        <v>0.5</v>
+      </c>
+      <c r="H111" s="14" t="s">
+        <v>398</v>
+      </c>
+      <c r="I111" s="14">
+        <v>300</v>
+      </c>
+      <c r="J111" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="K111" s="14">
+        <v>0</v>
+      </c>
+      <c r="L111" s="14">
+        <v>0</v>
+      </c>
+      <c r="M111" s="14">
+        <v>0</v>
+      </c>
+      <c r="N111" s="14">
+        <v>0</v>
+      </c>
+      <c r="O111" s="14"/>
+      <c r="P111" s="14">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="112" spans="2:16">
+      <c r="B112" s="14" t="s">
+        <v>399</v>
+      </c>
+      <c r="C112" s="14" t="s">
+        <v>400</v>
+      </c>
       <c r="D112" s="1" t="s">
-        <v>351</v>
+        <v>401</v>
       </c>
       <c r="E112" s="13" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="113" spans="4:5">
+      <c r="F112" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="G112" s="14">
+        <v>2</v>
+      </c>
+      <c r="H112" s="14"/>
+      <c r="I112" s="14">
+        <v>100</v>
+      </c>
+      <c r="J112" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="K112" s="14">
+        <v>0</v>
+      </c>
+      <c r="L112" s="14">
+        <v>0</v>
+      </c>
+      <c r="M112" s="14">
+        <v>0</v>
+      </c>
+      <c r="N112" s="14">
+        <v>0</v>
+      </c>
+      <c r="O112" s="14"/>
+      <c r="P112" s="14">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="113" spans="2:16">
+      <c r="B113" s="14" t="s">
+        <v>402</v>
+      </c>
+      <c r="C113" s="14" t="s">
+        <v>403</v>
+      </c>
       <c r="D113" s="1" t="s">
-        <v>352</v>
+        <v>404</v>
       </c>
       <c r="E113" s="1" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="114" spans="4:5">
+      <c r="F113" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="G113" s="14">
+        <v>0</v>
+      </c>
+      <c r="H113" s="14"/>
+      <c r="I113" s="14">
+        <v>10</v>
+      </c>
+      <c r="J113" s="14" t="s">
+        <v>201</v>
+      </c>
+      <c r="K113" s="14">
+        <v>0</v>
+      </c>
+      <c r="L113" s="14">
+        <v>0</v>
+      </c>
+      <c r="M113" s="14">
+        <v>0</v>
+      </c>
+      <c r="N113" s="14">
+        <v>0</v>
+      </c>
+      <c r="O113" s="14"/>
+      <c r="P113" s="14">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="114" spans="2:16">
+      <c r="B114" s="14" t="s">
+        <v>405</v>
+      </c>
+      <c r="C114" s="14" t="s">
+        <v>406</v>
+      </c>
       <c r="D114" s="1" t="s">
-        <v>353</v>
+        <v>407</v>
       </c>
       <c r="E114" s="1" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="115" spans="4:5">
+      <c r="F114" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="G114" s="14">
+        <v>0</v>
+      </c>
+      <c r="H114" s="14"/>
+      <c r="I114" s="14">
+        <v>30</v>
+      </c>
+      <c r="J114" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="K114" s="14">
+        <v>0</v>
+      </c>
+      <c r="L114" s="14">
+        <v>0</v>
+      </c>
+      <c r="M114" s="14">
+        <v>0</v>
+      </c>
+      <c r="N114" s="14">
+        <v>0</v>
+      </c>
+      <c r="O114" s="14"/>
+      <c r="P114" s="14">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="115" spans="2:16">
+      <c r="B115" s="14" t="s">
+        <v>408</v>
+      </c>
+      <c r="C115" s="14" t="s">
+        <v>409</v>
+      </c>
       <c r="D115" s="1" t="s">
-        <v>354</v>
+        <v>410</v>
       </c>
       <c r="E115" s="13" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="116" spans="4:5">
+      <c r="F115" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="G115" s="14">
+        <v>15</v>
+      </c>
+      <c r="H115" s="14"/>
+      <c r="I115" s="14">
+        <v>300</v>
+      </c>
+      <c r="J115" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="K115" s="14">
+        <v>0</v>
+      </c>
+      <c r="L115" s="14">
+        <v>0</v>
+      </c>
+      <c r="M115" s="14">
+        <v>0</v>
+      </c>
+      <c r="N115" s="14">
+        <v>0</v>
+      </c>
+      <c r="O115" s="14"/>
+      <c r="P115" s="14">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="116" spans="2:16">
+      <c r="B116" s="14" t="s">
+        <v>411</v>
+      </c>
+      <c r="C116" s="14" t="s">
+        <v>412</v>
+      </c>
       <c r="D116" s="1" t="s">
-        <v>355</v>
+        <v>413</v>
       </c>
       <c r="E116" s="13" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="117" spans="4:5">
+      <c r="F116" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="G116" s="14">
+        <v>1</v>
+      </c>
+      <c r="H116" s="14"/>
+      <c r="I116" s="14">
+        <v>300</v>
+      </c>
+      <c r="J116" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="K116" s="14">
+        <v>0</v>
+      </c>
+      <c r="L116" s="14">
+        <v>0</v>
+      </c>
+      <c r="M116" s="14">
+        <v>0</v>
+      </c>
+      <c r="N116" s="14">
+        <v>0</v>
+      </c>
+      <c r="O116" s="14"/>
+      <c r="P116" s="14">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="117" spans="2:16">
+      <c r="B117" s="14" t="s">
+        <v>414</v>
+      </c>
+      <c r="C117" s="14" t="s">
+        <v>415</v>
+      </c>
       <c r="D117" s="1" t="s">
-        <v>355</v>
+        <v>413</v>
       </c>
       <c r="E117" s="13" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="118" spans="4:5">
+      <c r="F117" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="G117" s="14">
+        <v>1</v>
+      </c>
+      <c r="H117" s="14"/>
+      <c r="I117" s="14">
+        <v>100</v>
+      </c>
+      <c r="J117" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="K117" s="14">
+        <v>0</v>
+      </c>
+      <c r="L117" s="14">
+        <v>0</v>
+      </c>
+      <c r="M117" s="14">
+        <v>0</v>
+      </c>
+      <c r="N117" s="14">
+        <v>0</v>
+      </c>
+      <c r="O117" s="14"/>
+      <c r="P117" s="14">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="118" spans="2:16">
+      <c r="B118" s="14" t="s">
+        <v>416</v>
+      </c>
+      <c r="C118" s="14" t="s">
+        <v>417</v>
+      </c>
       <c r="D118" s="1" t="s">
-        <v>356</v>
+        <v>418</v>
       </c>
       <c r="E118" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="119" spans="4:5">
+      <c r="F118" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="G118" s="14">
+        <v>1</v>
+      </c>
+      <c r="H118" s="14"/>
+      <c r="I118" s="14">
+        <v>300</v>
+      </c>
+      <c r="J118" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="K118" s="14">
+        <v>0</v>
+      </c>
+      <c r="L118" s="14">
+        <v>0</v>
+      </c>
+      <c r="M118" s="14">
+        <v>0</v>
+      </c>
+      <c r="N118" s="14">
+        <v>0</v>
+      </c>
+      <c r="O118" s="14"/>
+      <c r="P118" s="14">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="119" spans="2:16">
+      <c r="B119" s="14" t="s">
+        <v>419</v>
+      </c>
+      <c r="C119" s="14" t="s">
+        <v>420</v>
+      </c>
       <c r="D119" s="1" t="s">
-        <v>357</v>
+        <v>421</v>
       </c>
       <c r="E119" s="13" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="120" spans="4:5">
+      <c r="F119" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="G119" s="14">
+        <v>2</v>
+      </c>
+      <c r="H119" s="14"/>
+      <c r="I119" s="14">
+        <v>100</v>
+      </c>
+      <c r="J119" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="K119" s="14">
+        <v>0</v>
+      </c>
+      <c r="L119" s="14">
+        <v>0</v>
+      </c>
+      <c r="M119" s="14">
+        <v>0</v>
+      </c>
+      <c r="N119" s="14">
+        <v>0</v>
+      </c>
+      <c r="O119" s="14"/>
+      <c r="P119" s="14">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="120" spans="2:16">
+      <c r="B120" s="14" t="s">
+        <v>422</v>
+      </c>
+      <c r="C120" s="14" t="s">
+        <v>423</v>
+      </c>
       <c r="D120" s="1" t="s">
-        <v>358</v>
+        <v>424</v>
       </c>
       <c r="E120" s="13" t="s">
         <v>67</v>
+      </c>
+      <c r="F120" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="G120" s="14">
+        <v>0.25</v>
+      </c>
+      <c r="H120" s="14"/>
+      <c r="I120" s="14">
+        <v>100</v>
+      </c>
+      <c r="J120" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="K120" s="14">
+        <v>0</v>
+      </c>
+      <c r="L120" s="14">
+        <v>0</v>
+      </c>
+      <c r="M120" s="14">
+        <v>0</v>
+      </c>
+      <c r="N120" s="14">
+        <v>0</v>
+      </c>
+      <c r="O120" s="14"/>
+      <c r="P120" s="14">
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -9022,7 +10187,7 @@
         <v>5</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>359</v>
+        <v>425</v>
       </c>
       <c r="G1" s="7" t="s">
         <v>6</v>
@@ -9034,10 +10199,10 @@
         <v>8</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>360</v>
+        <v>426</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>361</v>
+        <v>427</v>
       </c>
       <c r="L1" s="7" t="s">
         <v>14</v>
@@ -9046,7 +10211,7 @@
         <v>15</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>362</v>
+        <v>428</v>
       </c>
     </row>
     <row r="2" ht="16.5" customHeight="1" spans="1:14">
@@ -9054,19 +10219,19 @@
         <v>16</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>363</v>
+        <v>429</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>364</v>
+        <v>430</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>365</v>
+        <v>431</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>366</v>
+        <v>432</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>22</v>
@@ -9078,19 +10243,19 @@
         <v>24</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>367</v>
+        <v>433</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>368</v>
+        <v>434</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>369</v>
+        <v>435</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>31</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>370</v>
+        <v>436</v>
       </c>
     </row>
     <row r="3" ht="16.5" customHeight="1" spans="1:14">
@@ -9122,7 +10287,7 @@
         <v>36</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>371</v>
+        <v>437</v>
       </c>
       <c r="K3" s="7" t="s">
         <v>38</v>
@@ -9134,536 +10299,536 @@
         <v>38</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>372</v>
+        <v>438</v>
       </c>
     </row>
     <row r="4" ht="33.75" customHeight="1" spans="2:14">
       <c r="B4" s="7" t="s">
-        <v>373</v>
+        <v>439</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>374</v>
+        <v>440</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>375</v>
+        <v>441</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>376</v>
+        <v>442</v>
       </c>
       <c r="G4" s="1">
         <v>0</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>377</v>
+        <v>443</v>
       </c>
       <c r="I4" s="1">
         <v>1</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>378</v>
+        <v>444</v>
       </c>
       <c r="K4" s="1">
         <v>1</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>377</v>
+        <v>443</v>
       </c>
       <c r="M4" s="1">
         <v>50</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>379</v>
+        <v>445</v>
       </c>
     </row>
     <row r="5" ht="33.75" customHeight="1" spans="2:14">
       <c r="B5" s="7" t="s">
-        <v>380</v>
+        <v>446</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>381</v>
+        <v>447</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>382</v>
+        <v>448</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>376</v>
+        <v>442</v>
       </c>
       <c r="G5" s="1">
         <v>0</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>383</v>
+        <v>449</v>
       </c>
       <c r="I5" s="1">
         <v>1</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>378</v>
+        <v>444</v>
       </c>
       <c r="K5" s="1">
         <v>1</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>383</v>
+        <v>449</v>
       </c>
       <c r="M5" s="1">
         <v>50</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>379</v>
+        <v>445</v>
       </c>
     </row>
     <row r="6" ht="33.75" customHeight="1" spans="2:14">
       <c r="B6" s="7" t="s">
-        <v>384</v>
+        <v>450</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>385</v>
+        <v>451</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>386</v>
+        <v>452</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>376</v>
+        <v>442</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>387</v>
+        <v>453</v>
       </c>
       <c r="I6" s="1">
         <v>1</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>378</v>
+        <v>444</v>
       </c>
       <c r="K6" s="1">
         <v>1</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>387</v>
+        <v>453</v>
       </c>
       <c r="M6" s="1">
         <v>50</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>379</v>
+        <v>445</v>
       </c>
     </row>
     <row r="7" ht="33.75" customHeight="1" spans="2:14">
       <c r="B7" s="7" t="s">
-        <v>388</v>
+        <v>454</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>389</v>
+        <v>455</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>390</v>
+        <v>456</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>376</v>
+        <v>442</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>391</v>
+        <v>457</v>
       </c>
       <c r="I7" s="1">
         <v>1</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>378</v>
+        <v>444</v>
       </c>
       <c r="K7" s="1">
         <v>1</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>391</v>
+        <v>457</v>
       </c>
       <c r="M7" s="1">
         <v>50</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>379</v>
+        <v>445</v>
       </c>
     </row>
     <row r="8" ht="33.75" customHeight="1" spans="2:14">
       <c r="B8" s="7" t="s">
-        <v>392</v>
+        <v>458</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>393</v>
+        <v>459</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>394</v>
+        <v>460</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>376</v>
+        <v>442</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>395</v>
+        <v>461</v>
       </c>
       <c r="I8" s="1">
         <v>1</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>378</v>
+        <v>444</v>
       </c>
       <c r="K8" s="1">
         <v>1</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>395</v>
+        <v>461</v>
       </c>
       <c r="M8" s="1">
         <v>50</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>379</v>
+        <v>445</v>
       </c>
     </row>
     <row r="9" ht="33.75" customHeight="1" spans="2:14">
       <c r="B9" s="7" t="s">
-        <v>396</v>
+        <v>462</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>397</v>
+        <v>463</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>398</v>
+        <v>464</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>376</v>
+        <v>442</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>399</v>
+        <v>465</v>
       </c>
       <c r="I9" s="1">
         <v>1</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>378</v>
+        <v>444</v>
       </c>
       <c r="K9" s="1">
         <v>1</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>399</v>
+        <v>465</v>
       </c>
       <c r="M9" s="1">
         <v>50</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>379</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10" ht="33.75" customHeight="1" spans="2:14">
       <c r="B10" s="7" t="s">
-        <v>400</v>
+        <v>466</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>401</v>
+        <v>467</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>402</v>
+        <v>468</v>
       </c>
       <c r="E10" t="s">
-        <v>403</v>
+        <v>469</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>404</v>
+        <v>470</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>405</v>
+        <v>471</v>
       </c>
       <c r="I10" s="1">
         <v>1</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>406</v>
+        <v>472</v>
       </c>
       <c r="K10" s="1">
         <v>1</v>
       </c>
       <c r="L10" s="7" t="s">
-        <v>405</v>
+        <v>471</v>
       </c>
       <c r="M10" s="1">
         <v>50</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>379</v>
+        <v>445</v>
       </c>
     </row>
     <row r="11" ht="33.75" customHeight="1" spans="2:14">
       <c r="B11" s="7" t="s">
-        <v>407</v>
+        <v>473</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>408</v>
+        <v>474</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>409</v>
+        <v>475</v>
       </c>
       <c r="E11" t="s">
-        <v>403</v>
+        <v>469</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>404</v>
+        <v>470</v>
       </c>
       <c r="G11" s="1">
         <v>0</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>410</v>
+        <v>476</v>
       </c>
       <c r="I11" s="1">
         <v>1</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>406</v>
+        <v>472</v>
       </c>
       <c r="K11" s="1">
         <v>1</v>
       </c>
       <c r="L11" s="7" t="s">
-        <v>410</v>
+        <v>476</v>
       </c>
       <c r="M11" s="1">
         <v>50</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>379</v>
+        <v>445</v>
       </c>
     </row>
     <row r="12" ht="33.75" customHeight="1" spans="2:14">
       <c r="B12" s="7" t="s">
-        <v>411</v>
+        <v>477</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>412</v>
+        <v>478</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>413</v>
+        <v>479</v>
       </c>
       <c r="E12" t="s">
-        <v>414</v>
+        <v>480</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>404</v>
+        <v>470</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>415</v>
+        <v>481</v>
       </c>
       <c r="I12" s="1">
         <v>1</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>406</v>
+        <v>472</v>
       </c>
       <c r="K12" s="1">
         <v>1</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>415</v>
+        <v>481</v>
       </c>
       <c r="M12" s="1">
         <v>50</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>379</v>
+        <v>445</v>
       </c>
     </row>
     <row r="13" ht="33.75" customHeight="1" spans="2:14">
       <c r="B13" s="7" t="s">
-        <v>416</v>
+        <v>482</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>417</v>
+        <v>483</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>418</v>
+        <v>484</v>
       </c>
       <c r="E13" t="s">
-        <v>414</v>
+        <v>480</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>404</v>
+        <v>470</v>
       </c>
       <c r="G13" s="1">
         <v>0</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>419</v>
+        <v>485</v>
       </c>
       <c r="I13" s="1">
         <v>1</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>406</v>
+        <v>472</v>
       </c>
       <c r="K13" s="1">
         <v>1</v>
       </c>
       <c r="L13" s="7" t="s">
-        <v>419</v>
+        <v>485</v>
       </c>
       <c r="M13" s="1">
         <v>50</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>379</v>
+        <v>445</v>
       </c>
     </row>
     <row r="14" ht="33.75" customHeight="1" spans="2:14">
       <c r="B14" s="7" t="s">
-        <v>420</v>
+        <v>486</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>421</v>
+        <v>487</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>422</v>
+        <v>488</v>
       </c>
       <c r="E14" t="s">
-        <v>414</v>
+        <v>480</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>404</v>
+        <v>470</v>
       </c>
       <c r="G14" s="1">
         <v>0</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>423</v>
+        <v>489</v>
       </c>
       <c r="I14" s="1">
         <v>1</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>406</v>
+        <v>472</v>
       </c>
       <c r="K14" s="1">
         <v>1</v>
       </c>
       <c r="L14" s="7" t="s">
-        <v>423</v>
+        <v>489</v>
       </c>
       <c r="M14" s="1">
         <v>50</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>379</v>
+        <v>445</v>
       </c>
     </row>
     <row r="15" ht="33.75" customHeight="1" spans="2:14">
       <c r="B15" s="7" t="s">
-        <v>424</v>
+        <v>490</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>425</v>
+        <v>491</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>426</v>
+        <v>492</v>
       </c>
       <c r="E15" t="s">
-        <v>427</v>
+        <v>493</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>404</v>
+        <v>470</v>
       </c>
       <c r="G15" s="1">
         <v>0</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>428</v>
+        <v>494</v>
       </c>
       <c r="I15" s="1">
         <v>1</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>406</v>
+        <v>472</v>
       </c>
       <c r="K15" s="1">
         <v>1</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>428</v>
+        <v>494</v>
       </c>
       <c r="M15" s="1">
         <v>50</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>379</v>
+        <v>445</v>
       </c>
     </row>
     <row r="16" ht="33.75" customHeight="1" spans="2:14">
       <c r="B16" s="7" t="s">
-        <v>429</v>
+        <v>495</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>430</v>
+        <v>496</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>431</v>
+        <v>497</v>
       </c>
       <c r="E16" t="s">
-        <v>427</v>
+        <v>493</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>404</v>
+        <v>470</v>
       </c>
       <c r="G16" s="1">
         <v>0</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>432</v>
+        <v>498</v>
       </c>
       <c r="I16" s="1">
         <v>1</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>406</v>
+        <v>472</v>
       </c>
       <c r="K16" s="1">
         <v>1</v>
       </c>
       <c r="L16" s="7" t="s">
-        <v>432</v>
+        <v>498</v>
       </c>
       <c r="M16" s="1">
         <v>50</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>379</v>
+        <v>445</v>
       </c>
     </row>
     <row r="17" s="9" customFormat="1" ht="17" spans="2:14">
       <c r="B17" s="11" t="s">
-        <v>433</v>
+        <v>499</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>434</v>
+        <v>500</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>435</v>
+        <v>501</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>436</v>
+        <v>502</v>
       </c>
       <c r="G17" s="9">
         <v>0</v>
@@ -9672,7 +10837,7 @@
         <v>1</v>
       </c>
       <c r="J17" s="9" t="s">
-        <v>437</v>
+        <v>503</v>
       </c>
       <c r="K17" s="9">
         <v>0</v>
@@ -9682,21 +10847,21 @@
         <v>50</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>438</v>
+        <v>504</v>
       </c>
     </row>
     <row r="18" s="9" customFormat="1" ht="16.5" customHeight="1" spans="2:14">
       <c r="B18" s="11" t="s">
-        <v>439</v>
+        <v>505</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>440</v>
+        <v>506</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>441</v>
+        <v>507</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>442</v>
+        <v>508</v>
       </c>
       <c r="G18" s="9">
         <v>0.5</v>
@@ -9705,7 +10870,7 @@
         <v>1</v>
       </c>
       <c r="J18" s="9" t="s">
-        <v>437</v>
+        <v>503</v>
       </c>
       <c r="K18" s="9">
         <v>0</v>
@@ -9715,21 +10880,21 @@
         <v>50</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>438</v>
+        <v>504</v>
       </c>
     </row>
     <row r="19" s="9" customFormat="1" ht="16.5" customHeight="1" spans="2:14">
       <c r="B19" s="11" t="s">
-        <v>443</v>
+        <v>509</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>444</v>
+        <v>510</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>445</v>
+        <v>511</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>446</v>
+        <v>512</v>
       </c>
       <c r="G19" s="9">
         <v>0</v>
@@ -9738,7 +10903,7 @@
         <v>1</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>437</v>
+        <v>503</v>
       </c>
       <c r="K19" s="9">
         <v>0</v>
@@ -9748,33 +10913,33 @@
         <v>50</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>438</v>
+        <v>504</v>
       </c>
     </row>
     <row r="20" s="9" customFormat="1" ht="16.5" customHeight="1" spans="2:14">
       <c r="B20" s="11" t="s">
-        <v>447</v>
+        <v>513</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>448</v>
+        <v>514</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>449</v>
+        <v>515</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>450</v>
+        <v>516</v>
       </c>
       <c r="G20" s="9">
         <v>0</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>451</v>
+        <v>517</v>
       </c>
       <c r="I20" s="9">
         <v>1</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>437</v>
+        <v>503</v>
       </c>
       <c r="K20" s="9">
         <v>1</v>
@@ -9784,33 +10949,33 @@
         <v>50</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>438</v>
+        <v>504</v>
       </c>
     </row>
     <row r="21" s="9" customFormat="1" spans="2:14">
       <c r="B21" s="9" t="s">
-        <v>452</v>
+        <v>518</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>453</v>
+        <v>519</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>454</v>
+        <v>520</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>455</v>
+        <v>521</v>
       </c>
       <c r="G21" s="9">
         <v>0</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>456</v>
+        <v>522</v>
       </c>
       <c r="I21" s="9">
         <v>1</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>437</v>
+        <v>503</v>
       </c>
       <c r="K21" s="9">
         <v>1</v>
@@ -9820,33 +10985,33 @@
         <v>50</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>438</v>
+        <v>504</v>
       </c>
     </row>
     <row r="22" s="9" customFormat="1" spans="2:14">
       <c r="B22" s="9" t="s">
-        <v>457</v>
+        <v>523</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>458</v>
+        <v>524</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>459</v>
+        <v>525</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>460</v>
+        <v>526</v>
       </c>
       <c r="G22" s="9">
         <v>0</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>461</v>
+        <v>527</v>
       </c>
       <c r="I22" s="9">
         <v>1</v>
       </c>
       <c r="J22" s="9" t="s">
-        <v>437</v>
+        <v>503</v>
       </c>
       <c r="K22" s="9">
         <v>1</v>
@@ -9856,33 +11021,33 @@
         <v>50</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>438</v>
+        <v>504</v>
       </c>
     </row>
     <row r="23" s="9" customFormat="1" spans="2:14">
       <c r="B23" s="9" t="s">
-        <v>462</v>
+        <v>528</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>463</v>
+        <v>529</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>464</v>
+        <v>530</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>465</v>
+        <v>531</v>
       </c>
       <c r="G23" s="9">
         <v>0</v>
       </c>
       <c r="H23" t="s">
-        <v>466</v>
+        <v>532</v>
       </c>
       <c r="I23" s="9">
         <v>1</v>
       </c>
       <c r="J23" s="9" t="s">
-        <v>437</v>
+        <v>503</v>
       </c>
       <c r="K23" s="9">
         <v>1</v>
@@ -9892,21 +11057,21 @@
         <v>50</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>438</v>
+        <v>504</v>
       </c>
     </row>
     <row r="24" s="9" customFormat="1" spans="2:14">
       <c r="B24" s="9" t="s">
-        <v>467</v>
+        <v>533</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>468</v>
+        <v>534</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>469</v>
+        <v>535</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>470</v>
+        <v>536</v>
       </c>
       <c r="G24" s="9">
         <v>0</v>
@@ -9915,7 +11080,7 @@
         <v>1</v>
       </c>
       <c r="J24" s="9" t="s">
-        <v>437</v>
+        <v>503</v>
       </c>
       <c r="K24" s="9">
         <v>1</v>
@@ -9925,21 +11090,21 @@
         <v>50</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>438</v>
+        <v>504</v>
       </c>
     </row>
     <row r="25" s="9" customFormat="1" ht="34" spans="2:14">
       <c r="B25" s="9" t="s">
-        <v>471</v>
+        <v>537</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>472</v>
+        <v>538</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>473</v>
+        <v>539</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>474</v>
+        <v>540</v>
       </c>
       <c r="G25" s="9">
         <v>0</v>
@@ -9948,7 +11113,7 @@
         <v>1</v>
       </c>
       <c r="J25" s="9" t="s">
-        <v>437</v>
+        <v>503</v>
       </c>
       <c r="K25" s="9">
         <v>1</v>
@@ -9958,21 +11123,21 @@
         <v>50</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>438</v>
+        <v>504</v>
       </c>
     </row>
     <row r="26" s="9" customFormat="1" ht="34" spans="2:14">
       <c r="B26" s="9" t="s">
-        <v>475</v>
+        <v>541</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>476</v>
+        <v>542</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>477</v>
+        <v>543</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>478</v>
+        <v>544</v>
       </c>
       <c r="G26" s="9">
         <v>0</v>
@@ -9981,7 +11146,7 @@
         <v>1</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>437</v>
+        <v>503</v>
       </c>
       <c r="K26" s="9">
         <v>1</v>
@@ -9991,7 +11156,7 @@
         <v>50</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>438</v>
+        <v>504</v>
       </c>
     </row>
   </sheetData>
@@ -10015,25 +11180,25 @@
   <sheetData>
     <row r="1" ht="17.25" customHeight="1" spans="2:20">
       <c r="B1" s="3" t="s">
-        <v>479</v>
+        <v>545</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>480</v>
+        <v>546</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>481</v>
+        <v>547</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>482</v>
+        <v>548</v>
       </c>
       <c r="H1" s="7" t="s">
         <v>1</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>483</v>
+        <v>549</v>
       </c>
       <c r="L1" t="s">
-        <v>484</v>
+        <v>550</v>
       </c>
       <c r="M1">
         <v>30</v>
@@ -10062,16 +11227,16 @@
     </row>
     <row r="2" ht="17.25" customHeight="1" spans="2:20">
       <c r="B2" s="3" t="s">
-        <v>485</v>
+        <v>551</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>486</v>
+        <v>552</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>487</v>
+        <v>553</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>488</v>
+        <v>554</v>
       </c>
       <c r="H2" s="1">
         <v>1</v>
@@ -10081,7 +11246,7 @@
         <v>获得时，获得两个随机（xx品质）的装饰品</v>
       </c>
       <c r="L2" t="s">
-        <v>489</v>
+        <v>555</v>
       </c>
       <c r="M2">
         <v>40</v>
@@ -10112,10 +11277,10 @@
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
       <c r="D3" s="3" t="s">
-        <v>490</v>
+        <v>556</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>491</v>
+        <v>557</v>
       </c>
       <c r="H3" s="1">
         <v>2</v>
@@ -10125,7 +11290,7 @@
         <v>获得时，从多个装饰品中选择一个获得</v>
       </c>
       <c r="L3" t="s">
-        <v>492</v>
+        <v>558</v>
       </c>
       <c r="M3">
         <v>50</v>
@@ -10156,10 +11321,10 @@
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
       <c r="D4" s="3" t="s">
-        <v>493</v>
+        <v>559</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>494</v>
+        <v>560</v>
       </c>
       <c r="H4" s="1">
         <v>3</v>
@@ -10173,10 +11338,10 @@
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
       <c r="D5" s="3" t="s">
-        <v>490</v>
+        <v>556</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>495</v>
+        <v>561</v>
       </c>
       <c r="H5" s="1">
         <v>4</v>
@@ -10190,10 +11355,10 @@
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
       <c r="D6" s="3" t="s">
-        <v>496</v>
+        <v>562</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>497</v>
+        <v>563</v>
       </c>
       <c r="H6" s="1">
         <v>5</v>
@@ -10203,17 +11368,17 @@
         <v>获得时，从多个食物中选择一个获得</v>
       </c>
       <c r="Q6" t="s">
-        <v>498</v>
+        <v>564</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1" spans="2:21">
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
       <c r="D7" s="3" t="s">
-        <v>499</v>
+        <v>565</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>500</v>
+        <v>566</v>
       </c>
       <c r="H7" s="1">
         <v>6</v>
@@ -10223,7 +11388,7 @@
         <v>获得时，从多个餐桌格中选择一个获得</v>
       </c>
       <c r="K7" t="s">
-        <v>501</v>
+        <v>567</v>
       </c>
       <c r="M7">
         <v>300</v>
@@ -10247,10 +11412,10 @@
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
       <c r="D8" s="3" t="s">
-        <v>502</v>
+        <v>568</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>503</v>
+        <v>569</v>
       </c>
       <c r="H8" s="1">
         <v>7</v>
@@ -10260,7 +11425,7 @@
         <v>获得时，获得一个随机装饰品、随机食物、50金币</v>
       </c>
       <c r="K8" t="s">
-        <v>504</v>
+        <v>570</v>
       </c>
       <c r="M8">
         <v>100</v>
@@ -10283,10 +11448,10 @@
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
       <c r="D9" s="3" t="s">
-        <v>505</v>
+        <v>571</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>506</v>
+        <v>572</v>
       </c>
       <c r="H9" s="1">
         <v>8</v>
@@ -10296,7 +11461,7 @@
         <v>所有装饰品和消耗品替换为随机装饰品和消耗品</v>
       </c>
       <c r="K9" t="s">
-        <v>507</v>
+        <v>573</v>
       </c>
       <c r="M9">
         <v>30</v>
@@ -10318,13 +11483,13 @@
     <row r="10" ht="17.25" customHeight="1" spans="2:21">
       <c r="B10" s="4"/>
       <c r="C10" s="4" t="s">
-        <v>508</v>
+        <v>574</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>509</v>
+        <v>575</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>510</v>
+        <v>576</v>
       </c>
       <c r="H10" s="1">
         <v>9</v>
@@ -10334,7 +11499,7 @@
         <v>获得1～100个金币</v>
       </c>
       <c r="K10" t="s">
-        <v>511</v>
+        <v>577</v>
       </c>
       <c r="M10">
         <v>10</v>
@@ -10357,10 +11522,10 @@
       <c r="B11" s="4"/>
       <c r="C11" s="3"/>
       <c r="D11" s="3" t="s">
-        <v>512</v>
+        <v>578</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>513</v>
+        <v>579</v>
       </c>
       <c r="H11" s="1">
         <v>10</v>
@@ -10374,10 +11539,10 @@
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
       <c r="D12" s="3" t="s">
-        <v>514</v>
+        <v>580</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>515</v>
+        <v>581</v>
       </c>
       <c r="H12" s="1">
         <v>11</v>
@@ -10387,23 +11552,23 @@
         <v>完成本次星级评鉴后，额外获得100金币</v>
       </c>
       <c r="P12" t="s">
-        <v>516</v>
+        <v>582</v>
       </c>
       <c r="Q12" t="s">
-        <v>517</v>
+        <v>583</v>
       </c>
       <c r="R12" t="s">
-        <v>518</v>
+        <v>584</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1" spans="2:14">
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
       <c r="D13" s="5" t="s">
-        <v>519</v>
+        <v>585</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>520</v>
+        <v>586</v>
       </c>
       <c r="H13" s="1">
         <v>12</v>
@@ -10417,7 +11582,7 @@
         <v>60</v>
       </c>
       <c r="M13" t="s">
-        <v>521</v>
+        <v>587</v>
       </c>
       <c r="N13">
         <v>240</v>
@@ -10426,13 +11591,13 @@
     <row r="14" ht="17.25" customHeight="1" spans="2:16">
       <c r="B14" s="4"/>
       <c r="C14" s="4" t="s">
-        <v>522</v>
+        <v>588</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>523</v>
+        <v>589</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>524</v>
+        <v>590</v>
       </c>
       <c r="H14" s="1">
         <v>13</v>
@@ -10446,7 +11611,7 @@
         <v>80</v>
       </c>
       <c r="M14" t="s">
-        <v>525</v>
+        <v>591</v>
       </c>
       <c r="N14">
         <v>150</v>
@@ -10459,10 +11624,10 @@
       <c r="B15" s="4"/>
       <c r="C15" s="3"/>
       <c r="D15" s="3" t="s">
-        <v>526</v>
+        <v>592</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>527</v>
+        <v>593</v>
       </c>
       <c r="H15" s="1">
         <v>14</v>
@@ -10476,7 +11641,7 @@
         <v>60</v>
       </c>
       <c r="M15" t="s">
-        <v>528</v>
+        <v>594</v>
       </c>
       <c r="N15">
         <v>80</v>
@@ -10492,10 +11657,10 @@
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
       <c r="D16" s="3" t="s">
-        <v>529</v>
+        <v>595</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>530</v>
+        <v>596</v>
       </c>
       <c r="H16" s="1">
         <v>15</v>
@@ -10505,7 +11670,7 @@
         <v>买消耗品打折20%</v>
       </c>
       <c r="M16" t="s">
-        <v>531</v>
+        <v>597</v>
       </c>
       <c r="N16">
         <v>40</v>
@@ -10521,10 +11686,10 @@
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
       <c r="D17" s="3" t="s">
-        <v>532</v>
+        <v>598</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>533</v>
+        <v>599</v>
       </c>
       <c r="H17" s="1">
         <v>16</v>
@@ -10538,10 +11703,10 @@
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
       <c r="D18" s="3" t="s">
-        <v>534</v>
+        <v>600</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>535</v>
+        <v>601</v>
       </c>
       <c r="H18" s="1">
         <v>17</v>
@@ -10551,7 +11716,7 @@
         <v>移除食物价格打折20%</v>
       </c>
       <c r="M18" t="s">
-        <v>536</v>
+        <v>602</v>
       </c>
       <c r="N18">
         <v>1.4</v>
@@ -10561,10 +11726,10 @@
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
       <c r="D19" s="3" t="s">
-        <v>534</v>
+        <v>600</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>537</v>
+        <v>603</v>
       </c>
       <c r="H19" s="1">
         <v>18</v>
@@ -10577,13 +11742,13 @@
     <row r="20" ht="17.25" customHeight="1" spans="2:14">
       <c r="B20" s="4"/>
       <c r="C20" s="4" t="s">
-        <v>538</v>
+        <v>604</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>539</v>
+        <v>605</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>540</v>
+        <v>606</v>
       </c>
       <c r="H20" s="1">
         <v>19</v>
@@ -10604,13 +11769,13 @@
     <row r="21" ht="17.25" customHeight="1" spans="2:14">
       <c r="B21" s="4"/>
       <c r="C21" s="4" t="s">
-        <v>541</v>
+        <v>607</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>542</v>
+        <v>608</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>543</v>
+        <v>609</v>
       </c>
       <c r="H21" s="1">
         <v>20</v>
@@ -10628,10 +11793,10 @@
       <c r="B22" s="4"/>
       <c r="C22" s="3"/>
       <c r="D22" s="3" t="s">
-        <v>544</v>
+        <v>610</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>545</v>
+        <v>611</v>
       </c>
       <c r="H22" s="1">
         <v>21</v>
@@ -10649,10 +11814,10 @@
       <c r="B23" s="4"/>
       <c r="C23" s="3"/>
       <c r="D23" s="3" t="s">
-        <v>546</v>
+        <v>612</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>547</v>
+        <v>613</v>
       </c>
       <c r="H23" s="1">
         <v>22</v>
@@ -10666,10 +11831,10 @@
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
       <c r="D24" s="3" t="s">
-        <v>548</v>
+        <v>614</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>549</v>
+        <v>615</v>
       </c>
       <c r="H24" s="1">
         <v>23</v>
@@ -10682,13 +11847,13 @@
     <row r="25" ht="17.25" customHeight="1" spans="2:9">
       <c r="B25" s="4"/>
       <c r="C25" s="4" t="s">
-        <v>550</v>
+        <v>616</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>551</v>
+        <v>617</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>552</v>
+        <v>618</v>
       </c>
       <c r="H25" s="1">
         <v>24</v>
@@ -10702,10 +11867,10 @@
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
       <c r="D26" s="3" t="s">
-        <v>551</v>
+        <v>617</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>553</v>
+        <v>619</v>
       </c>
       <c r="H26" s="1">
         <v>25</v>
@@ -10721,13 +11886,13 @@
     <row r="27" ht="17.25" customHeight="1" spans="2:18">
       <c r="B27" s="4"/>
       <c r="C27" s="3" t="s">
-        <v>554</v>
+        <v>620</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>555</v>
+        <v>621</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>556</v>
+        <v>622</v>
       </c>
       <c r="H27" s="1">
         <v>26</v>
@@ -10743,13 +11908,13 @@
     <row r="28" ht="17.25" customHeight="1" spans="2:9">
       <c r="B28" s="4"/>
       <c r="C28" s="4" t="s">
-        <v>557</v>
+        <v>623</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>558</v>
+        <v>624</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>559</v>
+        <v>625</v>
       </c>
       <c r="H28" s="1">
         <v>27</v>
@@ -10762,13 +11927,13 @@
     <row r="29" ht="17.25" customHeight="1" spans="2:9">
       <c r="B29" s="4"/>
       <c r="C29" s="3" t="s">
-        <v>560</v>
+        <v>626</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>558</v>
+        <v>624</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>561</v>
+        <v>627</v>
       </c>
       <c r="H29" s="1">
         <v>28</v>
@@ -10781,13 +11946,13 @@
     <row r="30" ht="17.25" customHeight="1" spans="2:9">
       <c r="B30" s="4"/>
       <c r="C30" s="3" t="s">
-        <v>562</v>
+        <v>628</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>563</v>
+        <v>629</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>564</v>
+        <v>630</v>
       </c>
       <c r="H30" s="1">
         <v>29</v>
@@ -10801,10 +11966,10 @@
       <c r="B31" s="4"/>
       <c r="C31" s="3"/>
       <c r="D31" s="3" t="s">
-        <v>563</v>
+        <v>629</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>565</v>
+        <v>631</v>
       </c>
       <c r="H31" s="1">
         <v>30</v>
@@ -10817,13 +11982,13 @@
     <row r="32" ht="17.25" customHeight="1" spans="2:9">
       <c r="B32" s="4"/>
       <c r="C32" s="3" t="s">
-        <v>566</v>
+        <v>632</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>566</v>
+        <v>632</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>567</v>
+        <v>633</v>
       </c>
       <c r="H32" s="1">
         <v>31</v>
@@ -10837,10 +12002,10 @@
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
       <c r="D33" s="3" t="s">
-        <v>568</v>
+        <v>634</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>569</v>
+        <v>635</v>
       </c>
       <c r="H33" s="1">
         <v>32</v>
@@ -10854,10 +12019,10 @@
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
       <c r="D34" s="3" t="s">
-        <v>570</v>
+        <v>636</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>571</v>
+        <v>637</v>
       </c>
       <c r="H34" s="1">
         <v>33</v>
@@ -10871,10 +12036,10 @@
       <c r="B35" s="4"/>
       <c r="C35" s="3"/>
       <c r="D35" s="3" t="s">
-        <v>572</v>
+        <v>638</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>573</v>
+        <v>639</v>
       </c>
       <c r="H35" s="1">
         <v>34</v>
@@ -10888,10 +12053,10 @@
       <c r="B36" s="4"/>
       <c r="C36" s="3"/>
       <c r="D36" s="6" t="s">
-        <v>574</v>
+        <v>640</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>575</v>
+        <v>641</v>
       </c>
       <c r="H36" s="1">
         <v>35</v>
@@ -10909,10 +12074,10 @@
       <c r="B37" s="4"/>
       <c r="C37" s="3"/>
       <c r="D37" s="3" t="s">
-        <v>576</v>
+        <v>642</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>577</v>
+        <v>643</v>
       </c>
       <c r="H37" s="1">
         <v>36</v>
@@ -10925,13 +12090,13 @@
     <row r="38" ht="17.25" customHeight="1" spans="2:11">
       <c r="B38" s="4"/>
       <c r="C38" s="3" t="s">
-        <v>578</v>
+        <v>644</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>505</v>
+        <v>571</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>579</v>
+        <v>645</v>
       </c>
       <c r="H38" s="1">
         <v>37</v>
@@ -10949,10 +12114,10 @@
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
       <c r="D39" s="3" t="s">
-        <v>580</v>
+        <v>646</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>581</v>
+        <v>647</v>
       </c>
       <c r="H39" s="1">
         <v>38</v>
@@ -10966,10 +12131,10 @@
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
       <c r="D40" s="3" t="s">
-        <v>582</v>
+        <v>648</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>582</v>
+        <v>648</v>
       </c>
       <c r="H40" s="1">
         <v>39</v>
@@ -10979,17 +12144,17 @@
         <v>周数-1</v>
       </c>
       <c r="K40" t="s">
-        <v>583</v>
+        <v>649</v>
       </c>
     </row>
     <row r="41" ht="17.25" customHeight="1" spans="2:9">
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
       <c r="D41" s="3" t="s">
-        <v>584</v>
+        <v>650</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>585</v>
+        <v>651</v>
       </c>
       <c r="H41" s="1">
         <v>40</v>
@@ -11003,10 +12168,10 @@
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
       <c r="D42" s="3" t="s">
-        <v>586</v>
+        <v>652</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>587</v>
+        <v>653</v>
       </c>
       <c r="H42" s="1">
         <v>41</v>
@@ -11019,13 +12184,13 @@
     <row r="43" ht="17.25" customHeight="1" spans="2:9">
       <c r="B43" s="4"/>
       <c r="C43" s="4" t="s">
-        <v>588</v>
+        <v>654</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>589</v>
+        <v>655</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>590</v>
+        <v>656</v>
       </c>
       <c r="H43" s="1">
         <v>42</v>
@@ -11039,10 +12204,10 @@
       <c r="B44" s="4"/>
       <c r="C44" s="3"/>
       <c r="D44" s="3" t="s">
-        <v>591</v>
+        <v>657</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>592</v>
+        <v>658</v>
       </c>
       <c r="H44" s="1">
         <v>43</v>
@@ -11056,10 +12221,10 @@
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
       <c r="D45" s="3" t="s">
-        <v>593</v>
+        <v>659</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>594</v>
+        <v>660</v>
       </c>
       <c r="H45" s="1">
         <v>44</v>
@@ -11072,13 +12237,13 @@
     <row r="46" ht="17.25" customHeight="1" spans="2:15">
       <c r="B46" s="4"/>
       <c r="C46" s="4" t="s">
-        <v>595</v>
+        <v>661</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>596</v>
+        <v>662</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>597</v>
+        <v>663</v>
       </c>
       <c r="H46" s="1">
         <v>45</v>
@@ -11101,10 +12266,10 @@
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
       <c r="D47" s="3" t="s">
-        <v>508</v>
+        <v>574</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>598</v>
+        <v>664</v>
       </c>
       <c r="H47" s="1">
         <v>46</v>
@@ -11121,10 +12286,10 @@
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
       <c r="D48" s="3" t="s">
-        <v>599</v>
+        <v>665</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>600</v>
+        <v>666</v>
       </c>
       <c r="H48" s="1">
         <v>47</v>
@@ -11137,13 +12302,13 @@
     <row r="49" ht="17.25" customHeight="1" spans="2:9">
       <c r="B49" s="4"/>
       <c r="C49" s="3" t="s">
-        <v>601</v>
+        <v>667</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>602</v>
+        <v>668</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>603</v>
+        <v>669</v>
       </c>
       <c r="H49" s="1">
         <v>48</v>
@@ -11157,10 +12322,10 @@
       <c r="B50" s="4"/>
       <c r="C50" s="4"/>
       <c r="D50" s="3" t="s">
-        <v>604</v>
+        <v>670</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>605</v>
+        <v>671</v>
       </c>
       <c r="H50" s="1">
         <v>49</v>
@@ -11174,10 +12339,10 @@
       <c r="B51" s="4"/>
       <c r="C51" s="4"/>
       <c r="D51" s="3" t="s">
-        <v>606</v>
+        <v>672</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>607</v>
+        <v>673</v>
       </c>
       <c r="H51" s="1">
         <v>50</v>
@@ -11191,10 +12356,10 @@
       <c r="B52" s="4"/>
       <c r="C52" s="3"/>
       <c r="D52" s="3" t="s">
-        <v>608</v>
+        <v>674</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>609</v>
+        <v>675</v>
       </c>
       <c r="H52" s="1">
         <v>51</v>
@@ -11208,10 +12373,10 @@
       <c r="B53" s="4"/>
       <c r="C53" s="4"/>
       <c r="D53" s="3" t="s">
-        <v>610</v>
+        <v>676</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>611</v>
+        <v>677</v>
       </c>
       <c r="H53" s="1">
         <v>52</v>
@@ -11225,10 +12390,10 @@
       <c r="B54" s="4"/>
       <c r="C54" s="4"/>
       <c r="D54" s="3" t="s">
-        <v>612</v>
+        <v>678</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>613</v>
+        <v>679</v>
       </c>
       <c r="H54" s="1">
         <v>53</v>
@@ -11241,13 +12406,13 @@
     <row r="55" ht="17.25" customHeight="1" spans="2:9">
       <c r="B55" s="4"/>
       <c r="C55" s="3" t="s">
-        <v>614</v>
+        <v>680</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>615</v>
+        <v>681</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>616</v>
+        <v>682</v>
       </c>
       <c r="H55" s="1">
         <v>54</v>
@@ -11261,10 +12426,10 @@
       <c r="B56" s="4"/>
       <c r="C56" s="4"/>
       <c r="D56" s="3" t="s">
-        <v>617</v>
+        <v>683</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>618</v>
+        <v>684</v>
       </c>
       <c r="H56" s="1">
         <v>55</v>
@@ -11277,13 +12442,13 @@
     <row r="57" ht="17.25" customHeight="1" spans="2:9">
       <c r="B57" s="4"/>
       <c r="C57" s="4" t="s">
-        <v>619</v>
+        <v>685</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>620</v>
+        <v>686</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>621</v>
+        <v>687</v>
       </c>
       <c r="H57" s="1">
         <v>56</v>
@@ -11297,10 +12462,10 @@
       <c r="B58" s="4"/>
       <c r="C58" s="4"/>
       <c r="D58" s="3" t="s">
-        <v>620</v>
+        <v>686</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>622</v>
+        <v>688</v>
       </c>
       <c r="H58" s="1">
         <v>57</v>
@@ -11314,10 +12479,10 @@
       <c r="B59" s="4"/>
       <c r="C59" s="4"/>
       <c r="D59" s="3" t="s">
-        <v>623</v>
+        <v>689</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>624</v>
+        <v>690</v>
       </c>
       <c r="H59" s="1">
         <v>58</v>
@@ -11331,10 +12496,10 @@
       <c r="B60" s="4"/>
       <c r="C60" s="4"/>
       <c r="D60" s="3" t="s">
-        <v>625</v>
+        <v>691</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>626</v>
+        <v>692</v>
       </c>
       <c r="H60" s="1">
         <v>59</v>
@@ -11348,10 +12513,10 @@
       <c r="B61" s="4"/>
       <c r="C61" s="3"/>
       <c r="D61" s="3" t="s">
-        <v>627</v>
+        <v>693</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>628</v>
+        <v>694</v>
       </c>
       <c r="H61" s="1">
         <v>60</v>
@@ -11364,13 +12529,13 @@
     <row r="62" ht="17.25" customHeight="1" spans="2:9">
       <c r="B62" s="4"/>
       <c r="C62" s="4" t="s">
-        <v>629</v>
+        <v>695</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>630</v>
+        <v>696</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>631</v>
+        <v>697</v>
       </c>
       <c r="H62" s="1">
         <v>61</v>
@@ -11383,13 +12548,13 @@
     <row r="63" ht="17.25" customHeight="1" spans="2:9">
       <c r="B63" s="4"/>
       <c r="C63" s="3" t="s">
-        <v>632</v>
+        <v>698</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>633</v>
+        <v>699</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>634</v>
+        <v>700</v>
       </c>
       <c r="H63" s="1">
         <v>62</v>
@@ -11403,10 +12568,10 @@
       <c r="B64" s="4"/>
       <c r="C64" s="4"/>
       <c r="D64" s="3" t="s">
-        <v>635</v>
+        <v>701</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>636</v>
+        <v>702</v>
       </c>
       <c r="H64" s="1">
         <v>63</v>
@@ -11420,10 +12585,10 @@
       <c r="B65" s="4"/>
       <c r="C65" s="4"/>
       <c r="D65" s="3" t="s">
-        <v>637</v>
+        <v>703</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>638</v>
+        <v>704</v>
       </c>
       <c r="H65" s="1">
         <v>64</v>
@@ -11437,10 +12602,10 @@
       <c r="B66" s="4"/>
       <c r="C66" s="4"/>
       <c r="D66" s="3" t="s">
-        <v>639</v>
+        <v>705</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>640</v>
+        <v>706</v>
       </c>
       <c r="H66" s="1">
         <v>65</v>
@@ -11454,10 +12619,10 @@
       <c r="B67" s="4"/>
       <c r="C67" s="4"/>
       <c r="D67" s="3" t="s">
-        <v>641</v>
+        <v>707</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>642</v>
+        <v>708</v>
       </c>
       <c r="H67" s="1">
         <v>66</v>
@@ -11470,13 +12635,13 @@
     <row r="68" ht="17.25" customHeight="1" spans="2:9">
       <c r="B68" s="4"/>
       <c r="C68" s="3" t="s">
-        <v>643</v>
+        <v>709</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>644</v>
+        <v>710</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>645</v>
+        <v>711</v>
       </c>
       <c r="H68" s="1">
         <v>67</v>
@@ -11490,10 +12655,10 @@
       <c r="B69" s="4"/>
       <c r="C69" s="3"/>
       <c r="D69" s="3" t="s">
-        <v>646</v>
+        <v>712</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>647</v>
+        <v>713</v>
       </c>
       <c r="H69" s="1">
         <v>68</v>
@@ -11505,16 +12670,16 @@
     </row>
     <row r="70" ht="17.25" customHeight="1" spans="2:9">
       <c r="B70" s="4" t="s">
-        <v>648</v>
+        <v>714</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>649</v>
+        <v>715</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>650</v>
+        <v>716</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>651</v>
+        <v>717</v>
       </c>
       <c r="H70" s="1">
         <v>69</v>
@@ -11528,10 +12693,10 @@
       <c r="B71" s="4"/>
       <c r="C71" s="4"/>
       <c r="D71" s="3" t="s">
-        <v>652</v>
+        <v>718</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>653</v>
+        <v>719</v>
       </c>
       <c r="H71" s="1">
         <v>70</v>
@@ -11545,10 +12710,10 @@
       <c r="B72" s="4"/>
       <c r="C72" s="4"/>
       <c r="D72" s="3" t="s">
-        <v>654</v>
+        <v>720</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>655</v>
+        <v>721</v>
       </c>
       <c r="H72" s="1">
         <v>71</v>
@@ -11562,10 +12727,10 @@
       <c r="B73" s="4"/>
       <c r="C73" s="4"/>
       <c r="D73" s="3" t="s">
-        <v>656</v>
+        <v>722</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>657</v>
+        <v>723</v>
       </c>
       <c r="H73" s="1">
         <v>72</v>
@@ -11579,10 +12744,10 @@
       <c r="B74" s="4"/>
       <c r="C74" s="3"/>
       <c r="D74" s="3" t="s">
-        <v>658</v>
+        <v>724</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>659</v>
+        <v>725</v>
       </c>
       <c r="H74" s="1">
         <v>73</v>
@@ -11596,10 +12761,10 @@
       <c r="B75" s="4"/>
       <c r="C75" s="3"/>
       <c r="D75" s="3" t="s">
-        <v>660</v>
+        <v>726</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>661</v>
+        <v>727</v>
       </c>
       <c r="H75" s="1">
         <v>74</v>
@@ -11613,10 +12778,10 @@
       <c r="B76" s="3"/>
       <c r="C76" s="3"/>
       <c r="D76" s="3" t="s">
-        <v>662</v>
+        <v>728</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>663</v>
+        <v>729</v>
       </c>
       <c r="H76" s="1">
         <v>75</v>
@@ -11630,10 +12795,10 @@
       <c r="B77" s="4"/>
       <c r="C77" s="4"/>
       <c r="D77" s="3" t="s">
-        <v>664</v>
+        <v>730</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>665</v>
+        <v>731</v>
       </c>
       <c r="H77" s="1">
         <v>76</v>
@@ -11647,10 +12812,10 @@
       <c r="B78" s="4"/>
       <c r="C78" s="4"/>
       <c r="D78" s="3" t="s">
-        <v>666</v>
+        <v>732</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>667</v>
+        <v>733</v>
       </c>
       <c r="H78" s="1">
         <v>77</v>
@@ -11662,16 +12827,16 @@
     </row>
     <row r="79" ht="17.25" customHeight="1" spans="2:9">
       <c r="B79" s="4" t="s">
-        <v>668</v>
+        <v>734</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>669</v>
+        <v>735</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>670</v>
+        <v>736</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>671</v>
+        <v>737</v>
       </c>
       <c r="H79" s="1">
         <v>78</v>
@@ -11684,13 +12849,13 @@
     <row r="80" ht="17.25" customHeight="1" spans="2:9">
       <c r="B80" s="4"/>
       <c r="C80" s="4" t="s">
-        <v>672</v>
+        <v>738</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>673</v>
+        <v>739</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>674</v>
+        <v>740</v>
       </c>
       <c r="H80" s="1">
         <v>79</v>
@@ -11704,10 +12869,10 @@
       <c r="B81" s="4"/>
       <c r="C81" s="4"/>
       <c r="D81" s="3" t="s">
-        <v>673</v>
+        <v>739</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>675</v>
+        <v>741</v>
       </c>
       <c r="H81" s="1">
         <v>80</v>
@@ -11721,10 +12886,10 @@
       <c r="B82" s="4"/>
       <c r="C82" s="4"/>
       <c r="D82" s="3" t="s">
-        <v>676</v>
+        <v>742</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>677</v>
+        <v>743</v>
       </c>
       <c r="H82" s="1">
         <v>81</v>
@@ -11738,10 +12903,10 @@
       <c r="B83" s="4"/>
       <c r="C83" s="4"/>
       <c r="D83" s="3" t="s">
-        <v>678</v>
+        <v>744</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>679</v>
+        <v>745</v>
       </c>
       <c r="H83" s="1">
         <v>82</v>
@@ -11754,13 +12919,13 @@
     <row r="84" ht="17.25" customHeight="1" spans="2:9">
       <c r="B84" s="4"/>
       <c r="C84" s="4" t="s">
-        <v>680</v>
+        <v>746</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>681</v>
+        <v>747</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>682</v>
+        <v>748</v>
       </c>
       <c r="H84" s="1">
         <v>83</v>
@@ -11774,10 +12939,10 @@
       <c r="B85" s="3"/>
       <c r="C85" s="3"/>
       <c r="D85" s="3" t="s">
-        <v>683</v>
+        <v>749</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>684</v>
+        <v>750</v>
       </c>
       <c r="H85" s="1">
         <v>84</v>
@@ -11791,10 +12956,10 @@
       <c r="B86" s="4"/>
       <c r="C86" s="3"/>
       <c r="D86" s="3" t="s">
-        <v>685</v>
+        <v>751</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>686</v>
+        <v>752</v>
       </c>
       <c r="H86" s="1">
         <v>85</v>
@@ -11808,10 +12973,10 @@
       <c r="B87" s="4"/>
       <c r="C87" s="4"/>
       <c r="D87" s="3" t="s">
-        <v>687</v>
+        <v>753</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>688</v>
+        <v>754</v>
       </c>
       <c r="H87" s="1">
         <v>86</v>
@@ -11825,10 +12990,10 @@
       <c r="B88" s="4"/>
       <c r="C88" s="4"/>
       <c r="D88" s="3" t="s">
-        <v>689</v>
+        <v>755</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>690</v>
+        <v>756</v>
       </c>
       <c r="H88" s="1">
         <v>87</v>
@@ -11944,117 +13109,117 @@
     </row>
     <row r="125" spans="5:5">
       <c r="E125" s="8" t="s">
-        <v>691</v>
+        <v>757</v>
       </c>
     </row>
     <row r="126" spans="5:5">
       <c r="E126" s="8" t="s">
-        <v>692</v>
+        <v>758</v>
       </c>
     </row>
     <row r="127" spans="5:5">
       <c r="E127" s="8" t="s">
-        <v>693</v>
+        <v>759</v>
       </c>
     </row>
     <row r="128" spans="5:5">
       <c r="E128" s="8" t="s">
-        <v>694</v>
+        <v>760</v>
       </c>
     </row>
     <row r="129" spans="5:5">
       <c r="E129" s="8" t="s">
-        <v>695</v>
+        <v>761</v>
       </c>
     </row>
     <row r="130" spans="5:5">
       <c r="E130" s="8" t="s">
-        <v>696</v>
+        <v>762</v>
       </c>
     </row>
     <row r="131" spans="5:5">
       <c r="E131" s="8" t="s">
-        <v>697</v>
+        <v>763</v>
       </c>
     </row>
     <row r="132" spans="5:5">
       <c r="E132" s="8" t="s">
-        <v>698</v>
+        <v>764</v>
       </c>
     </row>
     <row r="133" spans="5:5">
       <c r="E133" s="8" t="s">
-        <v>699</v>
+        <v>765</v>
       </c>
     </row>
     <row r="134" spans="5:5">
       <c r="E134" s="8" t="s">
-        <v>700</v>
+        <v>766</v>
       </c>
     </row>
     <row r="135" spans="5:5">
       <c r="E135" s="8" t="s">
-        <v>701</v>
+        <v>767</v>
       </c>
     </row>
     <row r="136" spans="5:5">
       <c r="E136" s="8" t="s">
-        <v>702</v>
+        <v>768</v>
       </c>
     </row>
     <row r="137" spans="5:5">
       <c r="E137" s="8" t="s">
-        <v>703</v>
+        <v>769</v>
       </c>
     </row>
     <row r="138" spans="5:5">
       <c r="E138" s="8" t="s">
-        <v>704</v>
+        <v>770</v>
       </c>
     </row>
     <row r="139" spans="5:5">
       <c r="E139" s="8" t="s">
-        <v>705</v>
+        <v>771</v>
       </c>
     </row>
     <row r="140" spans="5:5">
       <c r="E140" s="8" t="s">
-        <v>706</v>
+        <v>772</v>
       </c>
     </row>
     <row r="141" spans="5:5">
       <c r="E141" s="8" t="s">
-        <v>707</v>
+        <v>773</v>
       </c>
     </row>
     <row r="142" spans="5:5">
       <c r="E142" s="8" t="s">
-        <v>708</v>
+        <v>774</v>
       </c>
     </row>
     <row r="143" spans="5:5">
       <c r="E143" s="8" t="s">
-        <v>709</v>
+        <v>775</v>
       </c>
     </row>
     <row r="144" spans="5:5">
       <c r="E144" s="8" t="s">
-        <v>710</v>
+        <v>776</v>
       </c>
     </row>
     <row r="145" spans="5:5">
       <c r="E145" s="8" t="s">
-        <v>711</v>
+        <v>777</v>
       </c>
     </row>
     <row r="146" spans="5:5">
       <c r="E146" s="8" t="s">
-        <v>712</v>
+        <v>778</v>
       </c>
     </row>
     <row r="147" spans="5:5">
       <c r="E147" s="8" t="s">
-        <v>713</v>
+        <v>779</v>
       </c>
     </row>
     <row r="148" spans="5:5">

--- a/GourmetProject/GameConfig/Datas/item.xlsx
+++ b/GourmetProject/GameConfig/Datas/item.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="装饰品" sheetId="1" r:id="R20c9764dcdb84096"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="消耗品" sheetId="2" r:id="R555f6db8272f439b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="装饰品与消耗品设计" sheetId="3" r:id="R7a33f31d0a7a4ac9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="装饰品" sheetId="1" r:id="Rbb12c18ff49a434f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="消耗品" sheetId="2" r:id="Rc1b2ecbad52c4ab2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="装饰品与消耗品设计" sheetId="3" r:id="R8fdb1db7cdc94588"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -21,9 +21,6 @@
     <x:t xml:space="preserve">name</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">desc</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">quality</x:t>
   </x:si>
   <x:si>
@@ -69,9 +66,6 @@
     <x:t xml:space="preserve">装饰品名称</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">装饰品描述</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">装饰品品质</x:t>
   </x:si>
   <x:si>
@@ -135,10 +129,6 @@
     <x:t xml:space="preserve">洗好的扑克</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">所有装饰品
-替换为随机的装饰品</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Rare</x:t>
   </x:si>
   <x:si>
@@ -154,9 +144,6 @@
     <x:t xml:space="preserve">陶瓷招财猫</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">获得30～200金币</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Common</x:t>
   </x:si>
   <x:si>
@@ -172,10 +159,6 @@
     <x:t xml:space="preserve">柜台小费罐</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">接下来10次日常营业
-额外获得15金币</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">meals:10</x:t>
   </x:si>
   <x:si>
@@ -185,20 +168,12 @@
     <x:t xml:space="preserve">金边奖杯</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">完成下次星级评鉴
-额外+120金币</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">item_gold_percent</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">黄铜算盘</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">营业获得的金币
-额外+20%</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">20,80</x:t>
   </x:si>
   <x:si>
@@ -208,9 +183,6 @@
     <x:t xml:space="preserve">藤编纸篓</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">丢弃次数+1</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">item_trash_expand</x:t>
   </x:si>
   <x:si>
@@ -226,9 +198,6 @@
     <x:t xml:space="preserve">脚踏垃圾桶</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">丢弃次数+2</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">item_trash_mutate</x:t>
   </x:si>
   <x:si>
@@ -241,151 +210,96 @@
     <x:t xml:space="preserve">香草盆栽</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">食物价格-15%</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">item_discount_fragment</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">餐桌模型</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">餐桌格价格-15%</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">item_discount_active</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">强化券匣</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">强化箱价格-15%</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">item_discount_adjust</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">调整单夹</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">调整单价格-15%</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">item_discount_passive</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">装饰样板墙</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">装饰品价格-15%</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">item_discount_remove</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">抽页食谱夹</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">移除食物价格-15%</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">item_discount_food_festival</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">丰收菜篮</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">食物价格-25%</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">item_discount_fragment_festival</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">宴会桌模型</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">餐桌格价格-30%</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">item_discount_active_festival</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">金边强化券</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">强化箱价格-30%</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">item_discount_adjust_festival</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">烫金调整单</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">调整单价格-30%</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">item_discount_passive_festival</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">多层展柜</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">装饰品价格-30%</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">item_discount_remove_festival</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">可擦食谱板</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">移除食物价格-30%</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">item_famous_knife</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">名刀展示架</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">即将失败时
-恢复至1颗红心
-生效1次后失效</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">item_heart_flat_all</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">暖心壁灯</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">结算开始
-每拥有1颗红心
-所有食物分数+10</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">item_empty_heart_mult_all</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">裂纹心形镜</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">结算开始
-每拥有1个空红心
-所有食物倍率+0.3</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">item_score_to_one</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">开业纪念照</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">接下来2次营业
-目标美味值为1</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">meals:2</x:t>
   </x:si>
   <x:si>
@@ -395,41 +309,24 @@
     <x:t xml:space="preserve">家常菜挂画</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">日常营业
-目标美味值-25%</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">item_req_super_down</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">红格桌布</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">火热营业
-目标美味值-25%</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">item_req_feast_down</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">金边证书框</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">星级评鉴
-目标美味值-20%</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">item_count_le_mult</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">素色桌旗</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">结算开始
-若食物份数≤15
-所有食物倍率+0.5</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">lte:15</x:t>
   </x:si>
   <x:si>
@@ -439,11 +336,6 @@
     <x:t xml:space="preserve">多层餐盘架</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">结算开始
-若食物份数≥25
-所有食物倍率+0.5</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">gte:25</x:t>
   </x:si>
   <x:si>
@@ -453,60 +345,36 @@
     <x:t xml:space="preserve">青花调味罐</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">获得时
-所有食物分数永久+20</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">item_perma_flat_all_plus</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">成套调味罐</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">获得时
-所有食物分数永久+40</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">item_gold_on_shop</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">供货商合影</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">进入商店采购时
-获得15金币</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">item_extra_interest</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">挂墙周历</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">添加节点收取利息
-至每周末尾</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">item_interest_cap</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">聚宝盆摆件</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">利息上限扩展到100金币</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">item_loan</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">挂账记录板</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">金币+150
-添加节点"金币-300"
-至本周末尾</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">act_loan_repay</x:t>
   </x:si>
   <x:si>
@@ -516,29 +384,18 @@
     <x:t xml:space="preserve">命运骰子</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">获得时
-打乱未来的节点行动</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">item_extra_day</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">第八日启程</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">每周长度变为8天</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">item_every3_next_mult</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">木制节拍器</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">每上菜3个食物后
-下个食物倍率+1</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">every:3</x:t>
   </x:si>
   <x:si>
@@ -548,11 +405,6 @@
     <x:t xml:space="preserve">迎客灯笼</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">结算开始
-首个上菜的食物
-倍率+3</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">index:1</x:t>
   </x:si>
   <x:si>
@@ -562,11 +414,6 @@
     <x:t xml:space="preserve">餐后茶具</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">结算开始
-最后上菜的食物
-倍率+3</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">index:-1</x:t>
   </x:si>
   <x:si>
@@ -576,77 +423,48 @@
     <x:t xml:space="preserve">墙面置物架</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">增加2个消耗品栏</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">item_extra_active_slots_max</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">整墙储物架</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">增加3个消耗品栏</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">item_gold_on_active</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">皮面账单夹</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">使用消耗品时
-获得10金币</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">item_block_active</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">封条备品柜</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">无法再使用消耗品
-立即获得400金币</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">item_flavor_enhance</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">彩釉调料瓶组</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">为2个食物
-添加随机风味</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">item_flavor_remove_gold</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">复古台秤</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">移除1个食物的风味
-获得100金币</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">item_flavor_remove_double</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">小石磨</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">移除1个食物的风味
-其分数翻倍</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">item_flavor_double_slot</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">双格蘸料碟</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">食物风味上限变为2</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Epic</x:t>
   </x:si>
   <x:si>
@@ -659,140 +477,90 @@
     <x:t xml:space="preserve">拼花砖壁饰</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">为3个餐桌格
-强化随机材质</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">item_lucky_guarantee</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">四叶草标本框</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">经历3个随机事件后
-下个一定为幸运事件</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">item_lucky_chance</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">四叶草福袋</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">更容易遇见幸运事件</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">item_more_events</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">街角路牌</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">更容易遇见随机事件</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">item_more_super_actions</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">霓虹招牌</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">更容易遇见火热营业</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">item_slot_win_chance</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">彩球抽奖筒</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">抽奖机更容易中奖</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">item_dish_hidden_bonus</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">主厨推荐板</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">更容易获得更好的食物</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">item_fragment_hidden_bonus</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">拼接长桌</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">更容易获得更大的餐桌格</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">item_passive_hidden_bonus</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">古董展示柜</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">更容易获得更好的装饰品</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">item_gold_on_event</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">纪念币展示框</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">进入事件时
-获得15金币</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">item_shop_restock</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">食材保鲜架</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">商店会自动补货食物</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">item_shop_restock_active</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">柜台备品篮</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">商店会自动补货消耗品</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">item_shop_restock_passive</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">壁龛摆件墙</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">商店会自动补货装饰品</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">item_choice_count_plus1</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">活页食谱册</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">选择食物时
-可选数量+1</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">item_extra_food_choice</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">点心展示架</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">每4次日常营业
-额外获得3选1食物</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">every:4</x:t>
   </x:si>
   <x:si>
@@ -802,50 +570,30 @@
     <x:t xml:space="preserve">杂货展示架</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">每3次火热营业
-额外获得3选1装饰品</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">item_copy_food</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">双盖餐盘</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">获得时
-随机复制3个已有食物</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">item_discard_negative</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">藤编收纳筐</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">获得时
-移除2个诅咒装饰品</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">item_discard_negative_gold</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">旧餐具寄卖架</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">获得时
-移除所有诅咒装饰品
-每移除一个获得40金币</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">item_gold_meal_penalty</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">故障收银机</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">营业获得的金币-20%</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Negative</x:t>
   </x:si>
   <x:si>
@@ -855,94 +603,60 @@
     <x:t xml:space="preserve">破损商品架</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">移除食物价格+20%</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">item_no_remove</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">上锁食品柜</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">无法在商店中移除食物</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">item_skip_node</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">落灰打卡钟</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">跳过下一个收取利息节点</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">item_skip_reward_node</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">褪色招财猫</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">跳过下一个幸运事件节点</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">item_choice_minus1</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">缺角食谱板</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">多选一食物时
-可选数量-1</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">item_req_normal_up</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">挑剔留言簿</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">日常营业目标美味值+20%</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">item_req_super_up</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">爆单警示灯</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">火热营业目标美味值+20%</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">item_req_feast_up</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">评鉴整改书</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">星级评鉴目标美味值+20%</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">item_gold_week_clear</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">逾期账单夹</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">将失去所有金币的节点行动
-添加至本周末尾</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">item_double_daily_cost_repeat_node</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">双栏排班板</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">普通行动消耗天数+0.5
-商店与幸运事件节点
-可以额外执行1次</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">repeat:2</x:t>
   </x:si>
   <x:si>
@@ -952,20 +666,12 @@
     <x:t xml:space="preserve">停摆挂钟</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">遇到节点行动时
-时间轴有30%概率会停止</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">item_count_as_all</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">九格拼盘</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">结算开始
-所有食物额外被视为2份食物</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">term_food_count_as</x:t>
   </x:si>
   <x:si>
@@ -975,10 +681,6 @@
     <x:t xml:space="preserve">大号糖果盘</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">甜蜜传递时
-每个被传递方倍率+0.5</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">term_sweet_transfer</x:t>
   </x:si>
   <x:si>
@@ -988,32 +690,18 @@
     <x:t xml:space="preserve">长嘴糖浆壶</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">甜蜜传递时
-传递方每成功传递1个目标
-倍率+0.5</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">item_skill_count_mult</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">主厨刀架</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">结算结束
-每个食物每有1个技能
-自身倍率+1</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">item_gold_on_transfer</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">黄铜传菜铃</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">累计甜蜜传递10次后
-获得15金币</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">count:10</x:t>
   </x:si>
   <x:si>
@@ -1023,10 +711,6 @@
     <x:t xml:space="preserve">玻璃蛋糕罩</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">保留10%的蛋糕层数
-至下一场经营挑战</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">clb</x:t>
   </x:si>
   <x:si>
@@ -1036,30 +720,18 @@
     <x:t xml:space="preserve">厚底蛋糕托</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">蛋糕层数
-初始额外获得10层</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">item_cake_accel</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">可叠蛋糕托</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">蛋糕层数增加时
-额外加2层</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">item_cake_to_gold</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">蛋糕价签架</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">蛋糕层数大于100层时
-获得10金币</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">threshold:100</x:t>
   </x:si>
   <x:si>
@@ -1069,30 +741,18 @@
     <x:t xml:space="preserve">迷你蛋糕模</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">蛋糕效果需求的层数-20</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">item_transfer_extra_targets</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">两层糖果塔</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">甜蜜传递时
-额外选择2个目标</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">item_flavored_flat</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">风味评分牌</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">结算开始
-拥有风味的食物
-分数+30</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">flavored</x:t>
   </x:si>
   <x:si>
@@ -1102,22 +762,12 @@
     <x:t xml:space="preserve">双层品鉴碟</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">结算开始
-拥有风味的食物
-额外视为1份食物</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">item_active_count_flat_all</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">备品清单板</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">结算开始
-每拥有1个消耗品
-所有食物分数+10</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">basis:active-items</x:t>
   </x:si>
   <x:si>
@@ -1127,11 +777,6 @@
     <x:t xml:space="preserve">留白备品柜</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">结算开始
-每拥有1个消耗品空槽
-所有食物倍率+0.1</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">basis:empty-active-slots</x:t>
   </x:si>
   <x:si>
@@ -1141,11 +786,6 @@
     <x:t xml:space="preserve">滚边桌布</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">结算开始
-处于边缘的食物
-分数+50</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">position:edge</x:t>
   </x:si>
   <x:si>
@@ -1155,11 +795,6 @@
     <x:t xml:space="preserve">中央餐台模型</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">结算开始
-处于非边缘的食物
-倍率+0.5</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">position:non-edge</x:t>
   </x:si>
   <x:si>
@@ -1169,11 +804,6 @@
     <x:t xml:space="preserve">镶币菜单框</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">结算开始
-每有5金币
-所有食物分数+1</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">basis:gold;every:5</x:t>
   </x:si>
   <x:si>
@@ -1183,11 +813,6 @@
     <x:t xml:space="preserve">留白拼桌图</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">结算开始
-每有1个空格
-所有食物分数+10</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">basis:empty-cells</x:t>
   </x:si>
   <x:si>
@@ -1197,32 +822,18 @@
     <x:t xml:space="preserve">备用垃圾袋架</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">结算开始
-每有1个未使用的丢弃次数
-所有食物倍率+0.1</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">item_unused_discard_flat_all</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">磁吸垃圾夹</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">结算开始
-每有1个未使用的丢弃次数
-所有食物分数+10</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">item_skip_reward_dish_luck</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">空盘回执</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">放弃奖励领取时
-获取食物的运气提升</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">purpose:Dish</x:t>
   </x:si>
   <x:si>
@@ -1232,10 +843,6 @@
     <x:t xml:space="preserve">空柜寄售牌</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">放弃奖励领取时
-获取装饰品的运气提升</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">purpose:PassiveItem</x:t>
   </x:si>
   <x:si>
@@ -1245,21 +852,12 @@
     <x:t xml:space="preserve">蜂巢桌垫</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">火热营业结束
-随机1个餐桌格
-将材质复制到相邻1格</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">item_count_as_cake</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">万能蛋糕模</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">结算开始
-所有食物均视为蛋糕</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">category:cake</x:t>
   </x:si>
   <x:si>
@@ -1269,10 +867,6 @@
     <x:t xml:space="preserve">折叠加桌券</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">火热营业结束
-获得1个餐桌格</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">fragment_choice_3</x:t>
   </x:si>
   <x:si>
@@ -1282,20 +876,12 @@
     <x:t xml:space="preserve">老字号记分牌</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">食物结算时
-永久分数+3</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">item_same_base_mult_all</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">双份餐铃</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">同种食物结算时
-倍率+0.5</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">key:baseId;min:2</x:t>
   </x:si>
   <x:si>
@@ -1305,45 +891,30 @@
     <x:t xml:space="preserve">饼干回收盒</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">删除食谱中最多2个箭头饼干</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">item_remove_arrow_cookie_all</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">曲奇粉碎机</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">删除食谱中所有箭头饼干</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">item_randomize_recipe_dishes</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">万花筒菜单板</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">将所有食物随机为新的食物</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">item_discard_dish_flat</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">退菜改良簿</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">丢弃的食物分数永久+15</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">item_heart_capacity</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">心形烛台</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">红心上限+1</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">item_heart_capacity_deluxe</x:t>
   </x:si>
   <x:si>
@@ -1356,25 +927,16 @@
     <x:t xml:space="preserve">壁挂急救箱</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">恢复1个红心</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">item_restore_hearts</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">全套急救柜</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">恢复2个红心</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">item_slot_cost_discount</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">投币优惠牌</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">抽奖机抽奖所需金币-25%</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">是否通用</x:t>
@@ -3197,161 +2759,162 @@
       <x:c r="C1" s="1" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D1" s="1" t="s">
+      <x:c r="D1" s="1" t="str">
+        <x:v>desc</x:v>
+      </x:c>
+      <x:c r="E1" s="1" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E1" s="1" t="s">
+      <x:c r="F1" s="1" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F1" s="1" t="s">
+      <x:c r="G1" s="1" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G1" s="1" t="s">
+      <x:c r="H1" s="1" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H1" s="1" t="s">
+      <x:c r="I1" s="1" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I1" s="1" t="s">
+      <x:c r="J1" s="1" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J1" s="1" t="s">
+      <x:c r="K1" s="1" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K1" s="1" t="s">
+      <x:c r="L1" s="1" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L1" s="1" t="s">
+      <x:c r="M1" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M1" s="1" t="s">
+      <x:c r="N1" s="1" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="N1" s="1" t="s">
+      <x:c r="O1" s="1" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="O1" s="1" t="s">
+      <x:c r="P1" s="1" t="s">
         <x:v>14</x:v>
-      </x:c>
-      <x:c r="P1" s="1" t="s">
-        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="2" s="1" customFormat="1" ht="16.5" customHeight="1">
       <x:c r="A2" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B2" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="B2" s="1" t="s">
+      <x:c r="C2" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="C2" s="1" t="s">
+      <x:c r="D2" s="1" t="str">
+        <x:v>装饰品描述</x:v>
+      </x:c>
+      <x:c r="E2" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="D2" s="1" t="s">
+      <x:c r="F2" s="1" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="E2" s="1" t="s">
+      <x:c r="G2" s="1" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="F2" s="1" t="s">
+      <x:c r="H2" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="G2" s="1" t="s">
+      <x:c r="I2" s="1" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="H2" s="1" t="s">
+      <x:c r="J2" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="I2" s="1" t="s">
+      <x:c r="K2" s="1" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="J2" s="1" t="s">
+      <x:c r="L2" s="1" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="K2" s="1" t="s">
+      <x:c r="M2" s="1" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="L2" s="1" t="s">
+      <x:c r="N2" s="1" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M2" s="1" t="s">
+      <x:c r="O2" s="1" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="N2" s="1" t="s">
+      <x:c r="P2" s="1" t="s">
         <x:v>29</x:v>
-      </x:c>
-      <x:c r="O2" s="1" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="P2" s="1" t="s">
-        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="3" s="1" customFormat="1" ht="16.5" customHeight="1">
       <x:c r="A3" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B3" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C3" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="D3" s="1" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="E3" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="B3" s="1" t="s">
+      <x:c r="F3" s="1" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C3" s="1" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="D3" s="1" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E3" s="1" t="s">
+      <x:c r="G3" s="1" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="F3" s="1" t="s">
+      <x:c r="H3" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="I3" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="J3" s="1" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="G3" s="1" t="s">
+      <x:c r="K3" s="1" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="H3" s="1" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="I3" s="1" t="s">
+      <x:c r="L3" s="1" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="J3" s="1" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="K3" s="1" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="L3" s="1" t="s">
-        <x:v>38</x:v>
-      </x:c>
       <x:c r="M3" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="N3" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="O3" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="P3" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="4" s="1" customFormat="1" ht="34">
       <x:c r="B4" s="1" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C4" s="1" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="D4" s="10" t="str">
+        <x:v>[context]所有[/context][term]装饰品[/term]
+替换为随机的[term]装饰品[/term]</x:v>
+      </x:c>
+      <x:c r="E4" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="C4" s="1" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="D4" s="10" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="E4" s="1" t="s">
-        <x:v>42</x:v>
-      </x:c>
       <x:c r="F4" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G4" s="1">
         <x:v>0</x:v>
@@ -3360,7 +2923,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="J4" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="K4" s="1">
         <x:v>0</x:v>
@@ -3384,31 +2947,31 @@
     </x:row>
     <x:row r="5" s="1" customFormat="1">
       <x:c r="B5" s="1" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C5" s="1" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="D5" s="1" t="str">
+        <x:v>获得[gold]30～200金币[/gold]</x:v>
+      </x:c>
+      <x:c r="E5" s="1" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F5" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="G5" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H5" s="1" t="s">
         <x:v>45</x:v>
-      </x:c>
-      <x:c r="C5" s="1" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="D5" s="1" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="E5" s="1" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="F5" s="1" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="G5" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H5" s="1" t="s">
-        <x:v>49</x:v>
       </x:c>
       <x:c r="I5" s="1">
         <x:v>300</x:v>
       </x:c>
       <x:c r="J5" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="K5" s="1">
         <x:v>0</x:v>
@@ -3432,31 +2995,32 @@
     </x:row>
     <x:row r="6" s="1" customFormat="1" ht="34">
       <x:c r="B6" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="D6" s="10" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D6" s="10" t="str">
+        <x:v>接下来10次[context]日常营业[/context]
+额外获得[gold]15金币[/gold]</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F6" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G6" s="1">
         <x:v>15</x:v>
       </x:c>
       <x:c r="H6" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="I6" s="1">
         <x:v>300</x:v>
       </x:c>
       <x:c r="J6" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="K6" s="1">
         <x:v>0</x:v>
@@ -3480,19 +3044,20 @@
     </x:row>
     <x:row r="7" s="1" customFormat="1" ht="34">
       <x:c r="B7" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="D7" s="10" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="str">
+        <x:v>完成下次[context]星级评鉴[/context]
+额外[gold]+120金币[/gold]</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F7" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G7" s="1">
         <x:v>120</x:v>
@@ -3501,7 +3066,7 @@
         <x:v>300</x:v>
       </x:c>
       <x:c r="J7" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="K7" s="1">
         <x:v>0</x:v>
@@ -3529,19 +3094,20 @@
     </x:row>
     <x:row r="8" s="1" customFormat="1" ht="34">
       <x:c r="B8" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="D8" s="10" t="s">
-        <x:v>60</x:v>
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D8" s="10" t="str">
+        <x:v>营业获得的[gold]金币[/gold]
+额外[gold]+20%[/gold]</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F8" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G8" s="1">
         <x:v>0.2</x:v>
@@ -3550,7 +3116,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="J8" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="K8" s="1">
         <x:v>0</x:v>
@@ -3579,19 +3145,19 @@
     <x:row r="9" s="14" customFormat="1" ht="17">
       <x:c r="A9" s="1"/>
       <x:c r="B9" s="14" t="s">
-        <x:v>62</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C9" s="14" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="D9" s="15" t="s">
-        <x:v>64</x:v>
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="D9" s="15" t="str">
+        <x:v>[term]丢弃[/term]次数+1</x:v>
       </x:c>
       <x:c r="E9" s="14" t="s">
-        <x:v>48</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F9" s="14" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G9" s="14">
         <x:v>1</x:v>
@@ -3600,7 +3166,7 @@
         <x:v>300</x:v>
       </x:c>
       <x:c r="J9" s="14" t="s">
-        <x:v>50</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="K9" s="14">
         <x:v>0</x:v>
@@ -3631,19 +3197,19 @@
     <x:row r="10" s="14" customFormat="1" ht="17">
       <x:c r="A10" s="1"/>
       <x:c r="B10" s="14" t="s">
-        <x:v>65</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C10" s="14" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="D10" s="15" t="s">
-        <x:v>64</x:v>
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="D10" s="15" t="str">
+        <x:v>[term]丢弃[/term]次数+1</x:v>
       </x:c>
       <x:c r="E10" s="14" t="s">
-        <x:v>67</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F10" s="14" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G10" s="14">
         <x:v>1</x:v>
@@ -3653,7 +3219,7 @@
         <x:v>300</x:v>
       </x:c>
       <x:c r="J10" s="14" t="s">
-        <x:v>50</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="K10" s="14">
         <x:v>0</x:v>
@@ -3684,19 +3250,19 @@
     <x:row r="11" s="14" customFormat="1" ht="17">
       <x:c r="A11" s="1"/>
       <x:c r="B11" s="14" t="s">
-        <x:v>68</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C11" s="14" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="D11" s="15" t="s">
-        <x:v>70</x:v>
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="D11" s="15" t="str">
+        <x:v>[term]丢弃[/term]次数+2</x:v>
       </x:c>
       <x:c r="E11" s="14" t="s">
-        <x:v>42</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F11" s="14" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G11" s="14">
         <x:v>2</x:v>
@@ -3705,7 +3271,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="J11" s="14" t="s">
-        <x:v>61</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="K11" s="14">
         <x:v>0</x:v>
@@ -3727,19 +3293,19 @@
     <x:row r="12" s="14" customFormat="1" ht="17">
       <x:c r="A12" s="1"/>
       <x:c r="B12" s="14" t="s">
-        <x:v>71</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C12" s="14" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="D12" s="15" t="s">
-        <x:v>70</x:v>
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="D12" s="15" t="str">
+        <x:v>[term]丢弃[/term]次数+2</x:v>
       </x:c>
       <x:c r="E12" s="14" t="s">
-        <x:v>42</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F12" s="14" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G12" s="14">
         <x:v>2</x:v>
@@ -3749,7 +3315,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="J12" s="14" t="s">
-        <x:v>44</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="K12" s="14">
         <x:v>0</x:v>
@@ -3774,19 +3340,19 @@
     <x:row r="13" s="14" customFormat="1" ht="17">
       <x:c r="A13" s="1"/>
       <x:c r="B13" s="14" t="s">
-        <x:v>73</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C13" s="14" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="D13" s="15" t="s">
-        <x:v>75</x:v>
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="D13" s="15" t="str">
+        <x:v>食物价格-15%</x:v>
       </x:c>
       <x:c r="E13" s="14" t="s">
-        <x:v>48</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F13" s="14" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G13" s="14">
         <x:v>0.15</x:v>
@@ -3796,7 +3362,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="J13" s="14" t="s">
-        <x:v>61</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="K13" s="14">
         <x:v>0</x:v>
@@ -3824,19 +3390,19 @@
     <x:row r="14" s="14" customFormat="1">
       <x:c r="A14" s="1"/>
       <x:c r="B14" s="14" t="s">
-        <x:v>76</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C14" s="14" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="D14" s="14" t="s">
-        <x:v>78</x:v>
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="D14" s="14" t="str">
+        <x:v>餐桌格价格-15%</x:v>
       </x:c>
       <x:c r="E14" s="14" t="s">
-        <x:v>48</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F14" s="14" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G14" s="14">
         <x:v>0.15</x:v>
@@ -3846,7 +3412,7 @@
         <x:v>300</x:v>
       </x:c>
       <x:c r="J14" s="14" t="s">
-        <x:v>50</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="K14" s="14">
         <x:v>0</x:v>
@@ -3874,19 +3440,19 @@
     </x:row>
     <x:row r="15" s="1" customFormat="1" ht="17">
       <x:c r="B15" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="D15" s="10" t="s">
-        <x:v>81</x:v>
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="D15" s="10" t="str">
+        <x:v>强化箱价格-15%</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F15" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G15" s="1">
         <x:v>0.15</x:v>
@@ -3895,7 +3461,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="J15" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="K15" s="1">
         <x:v>0</x:v>
@@ -3919,19 +3485,19 @@
     </x:row>
     <x:row r="16" s="1" customFormat="1" ht="17">
       <x:c r="B16" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="D16" s="10" t="s">
-        <x:v>84</x:v>
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="D16" s="10" t="str">
+        <x:v>调整单价格-15%</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F16" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G16" s="1">
         <x:v>0.15</x:v>
@@ -3940,7 +3506,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="J16" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="K16" s="1">
         <x:v>0</x:v>
@@ -3960,19 +3526,19 @@
     </x:row>
     <x:row r="17" s="1" customFormat="1" ht="17">
       <x:c r="B17" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="D17" s="10" t="s">
-        <x:v>87</x:v>
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="D17" s="10" t="str">
+        <x:v>[term]装饰品[/term]价格-15%</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F17" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G17" s="1">
         <x:v>0.15</x:v>
@@ -3981,7 +3547,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="J17" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="K17" s="1">
         <x:v>0</x:v>
@@ -4005,19 +3571,19 @@
     </x:row>
     <x:row r="18" s="1" customFormat="1" ht="17">
       <x:c r="B18" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="D18" s="10" t="s">
-        <x:v>90</x:v>
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="D18" s="10" t="str">
+        <x:v>移除食物价格-15%</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F18" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G18" s="1">
         <x:v>0.15</x:v>
@@ -4026,7 +3592,7 @@
         <x:v>300</x:v>
       </x:c>
       <x:c r="J18" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="K18" s="1">
         <x:v>0</x:v>
@@ -4050,19 +3616,19 @@
     </x:row>
     <x:row r="19" s="1" customFormat="1" ht="17">
       <x:c r="B19" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="D19" s="10" t="s">
-        <x:v>93</x:v>
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="D19" s="10" t="str">
+        <x:v>食物价格-25%</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F19" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G19" s="1">
         <x:v>0.25</x:v>
@@ -4071,7 +3637,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="J19" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="K19" s="1">
         <x:v>0</x:v>
@@ -4095,19 +3661,19 @@
     </x:row>
     <x:row r="20" s="1" customFormat="1" ht="17">
       <x:c r="B20" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="D20" s="10" t="s">
-        <x:v>96</x:v>
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="D20" s="10" t="str">
+        <x:v>餐桌格价格-30%</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F20" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G20" s="1">
         <x:v>0.3</x:v>
@@ -4116,7 +3682,7 @@
         <x:v>300</x:v>
       </x:c>
       <x:c r="J20" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="K20" s="1">
         <x:v>0</x:v>
@@ -4140,19 +3706,19 @@
     </x:row>
     <x:row r="21" s="1" customFormat="1" ht="17">
       <x:c r="B21" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="D21" s="10" t="s">
-        <x:v>99</x:v>
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="D21" s="10" t="str">
+        <x:v>强化箱价格-30%</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F21" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G21" s="1">
         <x:v>0.3</x:v>
@@ -4161,7 +3727,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="J21" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="K21" s="1">
         <x:v>0</x:v>
@@ -4185,19 +3751,19 @@
     </x:row>
     <x:row r="22" s="1" customFormat="1" ht="17">
       <x:c r="B22" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="D22" s="10" t="s">
-        <x:v>102</x:v>
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="D22" s="10" t="str">
+        <x:v>调整单价格-30%</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F22" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G22" s="1">
         <x:v>0.3</x:v>
@@ -4206,7 +3772,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="J22" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="K22" s="1">
         <x:v>0</x:v>
@@ -4226,19 +3792,19 @@
     </x:row>
     <x:row r="23" s="1" customFormat="1" ht="17">
       <x:c r="B23" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="D23" s="10" t="s">
-        <x:v>105</x:v>
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="D23" s="10" t="str">
+        <x:v>[term]装饰品[/term]价格-30%</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F23" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G23" s="1">
         <x:v>0.3</x:v>
@@ -4247,7 +3813,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="J23" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="K23" s="1">
         <x:v>0</x:v>
@@ -4271,19 +3837,19 @@
     </x:row>
     <x:row r="24" s="1" customFormat="1" ht="17">
       <x:c r="B24" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="D24" s="10" t="s">
-        <x:v>108</x:v>
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="D24" s="10" t="str">
+        <x:v>移除食物价格-30%</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F24" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G24" s="1">
         <x:v>0.3</x:v>
@@ -4292,7 +3858,7 @@
         <x:v>300</x:v>
       </x:c>
       <x:c r="J24" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="K24" s="1">
         <x:v>0</x:v>
@@ -4316,19 +3882,21 @@
     </x:row>
     <x:row r="25" s="1" customFormat="1" ht="51">
       <x:c r="B25" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="D25" s="10" t="s">
-        <x:v>111</x:v>
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D25" s="10" t="str">
+        <x:v>即将失败时
+恢复至1颗红心
+生效1次后失效</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F25" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G25" s="1">
         <x:v>0</x:v>
@@ -4337,7 +3905,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="J25" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="K25" s="1">
         <x:v>0</x:v>
@@ -4361,19 +3929,21 @@
     </x:row>
     <x:row r="26" s="1" customFormat="1" ht="51">
       <x:c r="B26" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="D26" s="10" t="s">
-        <x:v>114</x:v>
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="D26" s="10" t="str">
+        <x:v>[context]结算开始[/context]
+每拥有1颗红心
+[context]所有[/context]食物[strong]分数[/strong][score]+10[/score]</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F26" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G26" s="1">
         <x:v>10</x:v>
@@ -4382,7 +3952,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="J26" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="K26" s="1">
         <x:v>0</x:v>
@@ -4402,19 +3972,21 @@
     </x:row>
     <x:row r="27" s="1" customFormat="1" ht="51">
       <x:c r="B27" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="D27" s="10" t="s">
-        <x:v>117</x:v>
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="D27" s="10" t="str">
+        <x:v>[context]结算开始[/context]
+每拥有1个空红心
+[context]所有[/context]食物[strong]倍率[/strong][multadd]+0.3[/multadd]</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F27" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G27" s="1">
         <x:v>0.3</x:v>
@@ -4423,7 +3995,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="J27" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="K27" s="1">
         <x:v>0</x:v>
@@ -4443,31 +4015,32 @@
     </x:row>
     <x:row r="28" s="1" customFormat="1" ht="34">
       <x:c r="B28" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="D28" s="10" t="s">
-        <x:v>120</x:v>
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="D28" s="10" t="str">
+        <x:v>接下来2次营业
+目标美味值为1</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F28" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G28" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H28" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="I28" s="1">
         <x:v>300</x:v>
       </x:c>
       <x:c r="J28" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="K28" s="1">
         <x:v>0</x:v>
@@ -4491,19 +4064,20 @@
     </x:row>
     <x:row r="29" s="1" customFormat="1" ht="34">
       <x:c r="B29" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="D29" s="10" t="s">
-        <x:v>124</x:v>
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="D29" s="10" t="str">
+        <x:v>[context]日常营业[/context]
+目标美味值-25%</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F29" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G29" s="1">
         <x:v>-0.25</x:v>
@@ -4512,7 +4086,7 @@
         <x:v>300</x:v>
       </x:c>
       <x:c r="J29" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="K29" s="1">
         <x:v>0</x:v>
@@ -4536,19 +4110,20 @@
     </x:row>
     <x:row r="30" s="1" customFormat="1" ht="34">
       <x:c r="B30" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="D30" s="10" t="s">
-        <x:v>127</x:v>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="D30" s="10" t="str">
+        <x:v>[context]火热营业[/context]
+目标美味值-25%</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F30" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G30" s="1">
         <x:v>-0.25</x:v>
@@ -4557,7 +4132,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="J30" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="K30" s="1">
         <x:v>0</x:v>
@@ -4581,19 +4156,20 @@
     </x:row>
     <x:row r="31" s="1" customFormat="1" ht="34">
       <x:c r="B31" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="D31" s="10" t="s">
-        <x:v>130</x:v>
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="D31" s="10" t="str">
+        <x:v>[context]星级评鉴[/context]
+目标美味值-20%</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F31" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G31" s="1">
         <x:v>-0.2</x:v>
@@ -4602,7 +4178,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="J31" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="K31" s="1">
         <x:v>0</x:v>
@@ -4626,31 +4202,33 @@
     </x:row>
     <x:row r="32" s="1" customFormat="1" ht="51">
       <x:c r="B32" s="1" t="s">
-        <x:v>131</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="D32" s="10" t="s">
-        <x:v>133</x:v>
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="D32" s="10" t="str">
+        <x:v>[context]结算开始[/context]
+若食物[strong]份数[/strong]≤15
+[context]所有[/context]食物[strong]倍率[/strong][multadd]+0.5[/multadd]</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F32" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G32" s="1">
         <x:v>0.5</x:v>
       </x:c>
       <x:c r="H32" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="I32" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="J32" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="K32" s="1">
         <x:v>0</x:v>
@@ -4674,31 +4252,33 @@
     </x:row>
     <x:row r="33" s="1" customFormat="1" ht="51">
       <x:c r="B33" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="D33" s="10" t="s">
-        <x:v>137</x:v>
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="D33" s="10" t="str">
+        <x:v>[context]结算开始[/context]
+若食物[strong]份数[/strong]≥25
+[context]所有[/context]食物[strong]倍率[/strong][multadd]+0.5[/multadd]</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F33" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G33" s="1">
         <x:v>0.5</x:v>
       </x:c>
       <x:c r="H33" s="1" t="s">
-        <x:v>138</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="I33" s="1">
         <x:v>30</x:v>
       </x:c>
       <x:c r="J33" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="K33" s="1">
         <x:v>0</x:v>
@@ -4723,19 +4303,20 @@
     <x:row r="34" s="14" customFormat="1" ht="34">
       <x:c r="A34" s="1"/>
       <x:c r="B34" s="14" t="s">
-        <x:v>139</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C34" s="14" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="D34" s="15" t="s">
-        <x:v>141</x:v>
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="D34" s="15" t="str">
+        <x:v>获得时
+[context]所有[/context]食物[strong]分数[/strong]永久[score]+20[/score]</x:v>
       </x:c>
       <x:c r="E34" s="14" t="s">
-        <x:v>48</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F34" s="14" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G34" s="14">
         <x:v>20</x:v>
@@ -4744,7 +4325,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="J34" s="14" t="s">
-        <x:v>61</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="K34" s="14">
         <x:v>0</x:v>
@@ -4769,19 +4350,20 @@
     <x:row r="35" s="14" customFormat="1" ht="34">
       <x:c r="A35" s="1"/>
       <x:c r="B35" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="D35" s="15" t="s">
-        <x:v>144</x:v>
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="D35" s="15" t="str">
+        <x:v>获得时
+[context]所有[/context]食物[strong]分数[/strong]永久[score]+40[/score]</x:v>
       </x:c>
       <x:c r="E35" s="14" t="s">
-        <x:v>67</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F35" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G35" s="1">
         <x:v>40</x:v>
@@ -4791,7 +4373,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="J35" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="K35" s="1">
         <x:v>0</x:v>
@@ -4813,19 +4395,20 @@
     <x:row r="36" s="14" customFormat="1" ht="34">
       <x:c r="A36" s="1"/>
       <x:c r="B36" s="14" t="s">
-        <x:v>145</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="C36" s="14" t="s">
-        <x:v>146</x:v>
-      </x:c>
-      <x:c r="D36" s="15" t="s">
-        <x:v>147</x:v>
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="D36" s="15" t="str">
+        <x:v>[context]进入商店采购[/context]时
+获得[gold]15金币[/gold]</x:v>
       </x:c>
       <x:c r="E36" s="14" t="s">
-        <x:v>48</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F36" s="14" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G36" s="14">
         <x:v>15</x:v>
@@ -4835,7 +4418,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="J36" s="14" t="s">
-        <x:v>61</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="K36" s="14">
         <x:v>0</x:v>
@@ -4860,19 +4443,20 @@
     </x:row>
     <x:row r="37" s="1" customFormat="1" ht="34">
       <x:c r="B37" s="1" t="s">
-        <x:v>148</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>149</x:v>
-      </x:c>
-      <x:c r="D37" s="10" t="s">
-        <x:v>150</x:v>
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="D37" s="10" t="str">
+        <x:v>添加节点收取利息
+至每周末尾</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F37" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G37" s="1">
         <x:v>1</x:v>
@@ -4881,7 +4465,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="J37" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="K37" s="1">
         <x:v>0</x:v>
@@ -4905,19 +4489,19 @@
     </x:row>
     <x:row r="38" s="1" customFormat="1" ht="17">
       <x:c r="B38" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="D38" s="10" t="s">
-        <x:v>153</x:v>
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="D38" s="10" t="str">
+        <x:v>利息上限扩展到[gold]100金币[/gold]</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F38" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G38" s="1">
         <x:v>100</x:v>
@@ -4926,7 +4510,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="J38" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="K38" s="1">
         <x:v>0</x:v>
@@ -4950,31 +4534,33 @@
     </x:row>
     <x:row r="39" s="1" customFormat="1" ht="51">
       <x:c r="B39" s="1" t="s">
-        <x:v>154</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>155</x:v>
-      </x:c>
-      <x:c r="D39" s="10" t="s">
-        <x:v>156</x:v>
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="D39" s="10" t="str">
+        <x:v>[gold]金币+150[/gold]
+添加节点"[gold]金币-300[/gold]"
+至本周末尾</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F39" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G39" s="1">
         <x:v>150</x:v>
       </x:c>
       <x:c r="H39" s="1" t="s">
-        <x:v>157</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="I39" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="J39" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="K39" s="1">
         <x:v>0</x:v>
@@ -4998,19 +4584,20 @@
     </x:row>
     <x:row r="40" s="1" customFormat="1" ht="34">
       <x:c r="B40" s="1" t="s">
-        <x:v>158</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>159</x:v>
-      </x:c>
-      <x:c r="D40" s="10" t="s">
-        <x:v>160</x:v>
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="D40" s="10" t="str">
+        <x:v>获得时
+打乱未来的节点行动</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F40" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G40" s="1">
         <x:v>0</x:v>
@@ -5019,7 +4606,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="J40" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="K40" s="1">
         <x:v>0</x:v>
@@ -5043,19 +4630,19 @@
     </x:row>
     <x:row r="41" s="1" customFormat="1" ht="17">
       <x:c r="B41" s="1" t="s">
-        <x:v>161</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>162</x:v>
-      </x:c>
-      <x:c r="D41" s="10" t="s">
-        <x:v>163</x:v>
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="D41" s="10" t="str">
+        <x:v>每周长度变为8天</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F41" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G41" s="1">
         <x:v>8</x:v>
@@ -5064,7 +4651,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="J41" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="K41" s="1">
         <x:v>0</x:v>
@@ -5088,31 +4675,32 @@
     </x:row>
     <x:row r="42" s="1" customFormat="1" ht="34">
       <x:c r="B42" s="1" t="s">
-        <x:v>164</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>165</x:v>
-      </x:c>
-      <x:c r="D42" s="10" t="s">
-        <x:v>166</x:v>
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="D42" s="10" t="str">
+        <x:v>每[context]上菜[/context]3个食物后
+下个食物[strong]倍率[/strong][multadd]+1[/multadd]</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F42" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G42" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="H42" s="1" t="s">
-        <x:v>167</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="I42" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="J42" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="K42" s="1">
         <x:v>0</x:v>
@@ -5136,31 +4724,33 @@
     </x:row>
     <x:row r="43" s="1" customFormat="1" ht="51">
       <x:c r="B43" s="1" t="s">
-        <x:v>168</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>169</x:v>
-      </x:c>
-      <x:c r="D43" s="10" t="s">
-        <x:v>170</x:v>
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="D43" s="10" t="str">
+        <x:v>[context]结算开始[/context]
+首个[context]上菜[/context]的食物
+[strong]倍率[/strong][multadd]+3[/multadd]</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F43" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G43" s="1">
         <x:v>3</x:v>
       </x:c>
       <x:c r="H43" s="1" t="s">
-        <x:v>171</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="I43" s="1">
         <x:v>300</x:v>
       </x:c>
       <x:c r="J43" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="K43" s="1">
         <x:v>0</x:v>
@@ -5184,31 +4774,33 @@
     </x:row>
     <x:row r="44" s="1" customFormat="1" ht="51">
       <x:c r="B44" s="1" t="s">
-        <x:v>172</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>173</x:v>
-      </x:c>
-      <x:c r="D44" s="10" t="s">
-        <x:v>174</x:v>
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="D44" s="10" t="str">
+        <x:v>[context]结算开始[/context]
+最后[context]上菜[/context]的食物
+[strong]倍率[/strong][multadd]+3[/multadd]</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F44" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G44" s="1">
         <x:v>3</x:v>
       </x:c>
       <x:c r="H44" s="1" t="s">
-        <x:v>175</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="I44" s="1">
         <x:v>300</x:v>
       </x:c>
       <x:c r="J44" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="K44" s="1">
         <x:v>0</x:v>
@@ -5232,19 +4824,19 @@
     </x:row>
     <x:row r="45" s="1" customFormat="1" ht="17">
       <x:c r="B45" s="1" t="s">
-        <x:v>176</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>177</x:v>
-      </x:c>
-      <x:c r="D45" s="10" t="s">
-        <x:v>178</x:v>
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="D45" s="10" t="str">
+        <x:v>增加2个[term]消耗品[/term]栏</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F45" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G45" s="1">
         <x:v>2</x:v>
@@ -5253,7 +4845,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="J45" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="K45" s="1">
         <x:v>0</x:v>
@@ -5277,19 +4869,19 @@
     </x:row>
     <x:row r="46" s="1" customFormat="1" ht="17">
       <x:c r="B46" s="1" t="s">
-        <x:v>179</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="D46" s="10" t="s">
-        <x:v>181</x:v>
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="D46" s="10" t="str">
+        <x:v>增加3个[term]消耗品[/term]栏</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F46" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G46" s="1">
         <x:v>3</x:v>
@@ -5298,7 +4890,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="J46" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="K46" s="1">
         <x:v>0</x:v>
@@ -5318,19 +4910,20 @@
     </x:row>
     <x:row r="47" s="1" customFormat="1" ht="34">
       <x:c r="B47" s="1" t="s">
-        <x:v>182</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>183</x:v>
-      </x:c>
-      <x:c r="D47" s="10" t="s">
-        <x:v>184</x:v>
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="D47" s="10" t="str">
+        <x:v>使用[term]消耗品[/term]时
+获得[gold]10金币[/gold]</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F47" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G47" s="1">
         <x:v>10</x:v>
@@ -5339,7 +4932,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="J47" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="K47" s="1">
         <x:v>0</x:v>
@@ -5363,19 +4956,20 @@
     </x:row>
     <x:row r="48" s="1" customFormat="1" ht="34">
       <x:c r="B48" s="1" t="s">
-        <x:v>185</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>186</x:v>
-      </x:c>
-      <x:c r="D48" s="10" t="s">
-        <x:v>187</x:v>
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="D48" s="10" t="str">
+        <x:v>无法再使用[term]消耗品[/term]
+立即获得[gold]400金币[/gold]</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F48" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G48" s="1">
         <x:v>400</x:v>
@@ -5384,7 +4978,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="J48" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="K48" s="1">
         <x:v>0</x:v>
@@ -5408,19 +5002,20 @@
     </x:row>
     <x:row r="49" s="1" customFormat="1" ht="34">
       <x:c r="B49" s="1" t="s">
-        <x:v>188</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>189</x:v>
-      </x:c>
-      <x:c r="D49" s="10" t="s">
-        <x:v>190</x:v>
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="D49" s="10" t="str">
+        <x:v>为2个食物
+添加随机风味</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F49" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G49" s="1">
         <x:v>2</x:v>
@@ -5429,7 +5024,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="J49" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="K49" s="1">
         <x:v>0</x:v>
@@ -5453,19 +5048,20 @@
     </x:row>
     <x:row r="50" s="1" customFormat="1" ht="34">
       <x:c r="B50" s="1" t="s">
-        <x:v>191</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="D50" s="10" t="s">
-        <x:v>193</x:v>
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="D50" s="10" t="str">
+        <x:v>移除1个食物的风味
+获得[gold]100金币[/gold]</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F50" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G50" s="1">
         <x:v>100</x:v>
@@ -5474,7 +5070,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="J50" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="K50" s="1">
         <x:v>0</x:v>
@@ -5498,19 +5094,20 @@
     </x:row>
     <x:row r="51" s="1" customFormat="1" ht="34">
       <x:c r="B51" s="1" t="s">
-        <x:v>194</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>195</x:v>
-      </x:c>
-      <x:c r="D51" s="10" t="s">
-        <x:v>196</x:v>
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="D51" s="10" t="str">
+        <x:v>移除1个食物的风味
+其[strong]分数[/strong]翻倍</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F51" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G51" s="1">
         <x:v>2</x:v>
@@ -5519,7 +5116,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="J51" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="K51" s="1">
         <x:v>0</x:v>
@@ -5543,19 +5140,19 @@
     </x:row>
     <x:row r="52" s="1" customFormat="1" ht="17">
       <x:c r="B52" s="1" t="s">
-        <x:v>197</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>198</x:v>
-      </x:c>
-      <x:c r="D52" s="10" t="s">
-        <x:v>199</x:v>
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="D52" s="10" t="str">
+        <x:v>食物风味上限变为2</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
-        <x:v>200</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="F52" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G52" s="1">
         <x:v>1</x:v>
@@ -5564,7 +5161,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="J52" s="1" t="s">
-        <x:v>201</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="K52" s="1">
         <x:v>0</x:v>
@@ -5588,19 +5185,20 @@
     </x:row>
     <x:row r="53" s="1" customFormat="1" ht="34">
       <x:c r="B53" s="1" t="s">
-        <x:v>202</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="D53" s="10" t="s">
-        <x:v>204</x:v>
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="D53" s="10" t="str">
+        <x:v>为3个餐桌格
+强化随机材质</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F53" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G53" s="1">
         <x:v>3</x:v>
@@ -5609,7 +5207,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="J53" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="K53" s="1">
         <x:v>0</x:v>
@@ -5633,19 +5231,20 @@
     </x:row>
     <x:row r="54" s="1" customFormat="1" ht="34">
       <x:c r="B54" s="1" t="s">
-        <x:v>205</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>206</x:v>
-      </x:c>
-      <x:c r="D54" s="10" t="s">
-        <x:v>207</x:v>
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="D54" s="10" t="str">
+        <x:v>经历3个随机事件后
+下个一定为幸运事件</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F54" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G54" s="1">
         <x:v>3</x:v>
@@ -5654,7 +5253,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="J54" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="K54" s="1">
         <x:v>0</x:v>
@@ -5678,19 +5277,19 @@
     </x:row>
     <x:row r="55" s="1" customFormat="1" ht="17">
       <x:c r="B55" s="1" t="s">
-        <x:v>208</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>209</x:v>
-      </x:c>
-      <x:c r="D55" s="10" t="s">
-        <x:v>210</x:v>
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="D55" s="10" t="str">
+        <x:v>更容易遇见幸运事件</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F55" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G55" s="1">
         <x:v>0.4</x:v>
@@ -5699,7 +5298,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="J55" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="K55" s="1">
         <x:v>0</x:v>
@@ -5723,19 +5322,19 @@
     </x:row>
     <x:row r="56" s="1" customFormat="1" ht="17">
       <x:c r="B56" s="1" t="s">
-        <x:v>211</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>212</x:v>
-      </x:c>
-      <x:c r="D56" s="10" t="s">
-        <x:v>213</x:v>
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="D56" s="10" t="str">
+        <x:v>更容易遇见随机事件</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F56" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G56" s="1">
         <x:v>0.4</x:v>
@@ -5744,7 +5343,7 @@
         <x:v>300</x:v>
       </x:c>
       <x:c r="J56" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="K56" s="1">
         <x:v>0</x:v>
@@ -5768,19 +5367,19 @@
     </x:row>
     <x:row r="57" s="1" customFormat="1" ht="17">
       <x:c r="B57" s="1" t="s">
-        <x:v>214</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>215</x:v>
-      </x:c>
-      <x:c r="D57" s="10" t="s">
-        <x:v>216</x:v>
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="D57" s="10" t="str">
+        <x:v>更容易遇见[context]火热营业[/context]</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F57" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G57" s="1">
         <x:v>1</x:v>
@@ -5789,7 +5388,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="J57" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="K57" s="1">
         <x:v>0</x:v>
@@ -5809,19 +5408,19 @@
     </x:row>
     <x:row r="58" s="1" customFormat="1" ht="17">
       <x:c r="B58" s="1" t="s">
-        <x:v>217</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
-        <x:v>218</x:v>
-      </x:c>
-      <x:c r="D58" s="10" t="s">
-        <x:v>219</x:v>
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="D58" s="10" t="str">
+        <x:v>抽奖机更容易中奖</x:v>
       </x:c>
       <x:c r="E58" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F58" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G58" s="1">
         <x:v>0.3</x:v>
@@ -5830,7 +5429,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="J58" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="K58" s="1">
         <x:v>0</x:v>
@@ -5850,19 +5449,19 @@
     </x:row>
     <x:row r="59" s="1" customFormat="1" ht="17">
       <x:c r="B59" s="1" t="s">
-        <x:v>220</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
-        <x:v>221</x:v>
-      </x:c>
-      <x:c r="D59" s="10" t="s">
-        <x:v>222</x:v>
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="D59" s="10" t="str">
+        <x:v>更容易获得更好的食物</x:v>
       </x:c>
       <x:c r="E59" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F59" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G59" s="1">
         <x:v>0</x:v>
@@ -5871,7 +5470,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="J59" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="K59" s="1">
         <x:v>0</x:v>
@@ -5891,19 +5490,19 @@
     </x:row>
     <x:row r="60" s="1" customFormat="1" ht="17">
       <x:c r="B60" s="1" t="s">
-        <x:v>223</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
-        <x:v>224</x:v>
-      </x:c>
-      <x:c r="D60" s="10" t="s">
-        <x:v>225</x:v>
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="D60" s="10" t="str">
+        <x:v>更容易获得更大的餐桌格</x:v>
       </x:c>
       <x:c r="E60" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F60" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G60" s="1">
         <x:v>0</x:v>
@@ -5912,7 +5511,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="J60" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="K60" s="1">
         <x:v>0</x:v>
@@ -5932,19 +5531,19 @@
     </x:row>
     <x:row r="61" s="1" customFormat="1" ht="17">
       <x:c r="B61" s="1" t="s">
-        <x:v>226</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
-        <x:v>227</x:v>
-      </x:c>
-      <x:c r="D61" s="10" t="s">
-        <x:v>228</x:v>
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="D61" s="10" t="str">
+        <x:v>更容易获得更好的[term]装饰品[/term]</x:v>
       </x:c>
       <x:c r="E61" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F61" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G61" s="1">
         <x:v>0</x:v>
@@ -5953,7 +5552,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="J61" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="K61" s="1">
         <x:v>0</x:v>
@@ -5973,19 +5572,20 @@
     </x:row>
     <x:row r="62" s="1" customFormat="1" ht="34">
       <x:c r="B62" s="1" t="s">
-        <x:v>229</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
-        <x:v>230</x:v>
-      </x:c>
-      <x:c r="D62" s="10" t="s">
-        <x:v>231</x:v>
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="D62" s="10" t="str">
+        <x:v>[context]进入事件[/context]时
+获得[gold]15金币[/gold]</x:v>
       </x:c>
       <x:c r="E62" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F62" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G62" s="1">
         <x:v>15</x:v>
@@ -5994,7 +5594,7 @@
         <x:v>300</x:v>
       </x:c>
       <x:c r="J62" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="K62" s="1">
         <x:v>0</x:v>
@@ -6018,19 +5618,19 @@
     </x:row>
     <x:row r="63" s="1" customFormat="1" ht="17">
       <x:c r="B63" s="1" t="s">
-        <x:v>232</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
-        <x:v>233</x:v>
-      </x:c>
-      <x:c r="D63" s="10" t="s">
-        <x:v>234</x:v>
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="D63" s="10" t="str">
+        <x:v>商店会自动补货食物</x:v>
       </x:c>
       <x:c r="E63" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F63" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G63" s="1">
         <x:v>0</x:v>
@@ -6039,7 +5639,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="J63" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="K63" s="1">
         <x:v>0</x:v>
@@ -6063,19 +5663,19 @@
     </x:row>
     <x:row r="64" s="1" customFormat="1" ht="17">
       <x:c r="B64" s="1" t="s">
-        <x:v>235</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
-        <x:v>236</x:v>
-      </x:c>
-      <x:c r="D64" s="10" t="s">
-        <x:v>237</x:v>
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="D64" s="10" t="str">
+        <x:v>商店会自动补货[term]消耗品[/term]</x:v>
       </x:c>
       <x:c r="E64" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F64" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G64" s="1">
         <x:v>0</x:v>
@@ -6084,7 +5684,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="J64" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="K64" s="1">
         <x:v>0</x:v>
@@ -6104,19 +5704,19 @@
     </x:row>
     <x:row r="65" s="1" customFormat="1" ht="17">
       <x:c r="B65" s="1" t="s">
-        <x:v>238</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
-        <x:v>239</x:v>
-      </x:c>
-      <x:c r="D65" s="10" t="s">
-        <x:v>240</x:v>
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="D65" s="10" t="str">
+        <x:v>商店会自动补货[term]装饰品[/term]</x:v>
       </x:c>
       <x:c r="E65" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F65" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G65" s="1">
         <x:v>0</x:v>
@@ -6125,7 +5725,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="J65" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="K65" s="1">
         <x:v>0</x:v>
@@ -6145,19 +5745,20 @@
     </x:row>
     <x:row r="66" s="1" customFormat="1" ht="34">
       <x:c r="B66" s="1" t="s">
-        <x:v>241</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
-        <x:v>242</x:v>
-      </x:c>
-      <x:c r="D66" s="10" t="s">
-        <x:v>243</x:v>
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="D66" s="10" t="str">
+        <x:v>选择食物时
+可选数量+1</x:v>
       </x:c>
       <x:c r="E66" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F66" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G66" s="1">
         <x:v>1</x:v>
@@ -6166,7 +5767,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="J66" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="K66" s="1">
         <x:v>0</x:v>
@@ -6190,31 +5791,32 @@
     </x:row>
     <x:row r="67" s="1" customFormat="1" ht="34">
       <x:c r="B67" s="1" t="s">
-        <x:v>244</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="C67" s="1" t="s">
-        <x:v>245</x:v>
-      </x:c>
-      <x:c r="D67" s="10" t="s">
-        <x:v>246</x:v>
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="D67" s="10" t="str">
+        <x:v>每4次[context]日常营业[/context]
+额外获得3选1食物</x:v>
       </x:c>
       <x:c r="E67" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F67" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G67" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H67" s="1" t="s">
-        <x:v>247</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="I67" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="J67" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="K67" s="1">
         <x:v>0</x:v>
@@ -6238,31 +5840,32 @@
     </x:row>
     <x:row r="68" s="1" customFormat="1" ht="34">
       <x:c r="B68" s="1" t="s">
-        <x:v>248</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
-        <x:v>249</x:v>
-      </x:c>
-      <x:c r="D68" s="10" t="s">
-        <x:v>250</x:v>
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="D68" s="10" t="str">
+        <x:v>每3次[context]火热营业[/context]
+额外获得3选1[term]装饰品[/term]</x:v>
       </x:c>
       <x:c r="E68" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F68" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G68" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H68" s="1" t="s">
-        <x:v>167</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="I68" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="J68" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="K68" s="1">
         <x:v>0</x:v>
@@ -6286,19 +5889,20 @@
     </x:row>
     <x:row r="69" s="1" customFormat="1" ht="34">
       <x:c r="B69" s="1" t="s">
-        <x:v>251</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C69" s="1" t="s">
-        <x:v>252</x:v>
-      </x:c>
-      <x:c r="D69" s="10" t="s">
-        <x:v>253</x:v>
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="D69" s="10" t="str">
+        <x:v>获得时
+随机复制3个已有食物</x:v>
       </x:c>
       <x:c r="E69" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F69" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G69" s="1">
         <x:v>3</x:v>
@@ -6307,7 +5911,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="J69" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="K69" s="1">
         <x:v>0</x:v>
@@ -6331,19 +5935,20 @@
     </x:row>
     <x:row r="70" s="1" customFormat="1" ht="34">
       <x:c r="B70" s="1" t="s">
-        <x:v>254</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C70" s="1" t="s">
-        <x:v>255</x:v>
-      </x:c>
-      <x:c r="D70" s="10" t="s">
-        <x:v>256</x:v>
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="D70" s="10" t="str">
+        <x:v>获得时
+移除2个诅咒[term]装饰品[/term]</x:v>
       </x:c>
       <x:c r="E70" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F70" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G70" s="1">
         <x:v>2</x:v>
@@ -6352,7 +5957,7 @@
         <x:v>300</x:v>
       </x:c>
       <x:c r="J70" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="K70" s="1">
         <x:v>0</x:v>
@@ -6376,19 +5981,21 @@
     </x:row>
     <x:row r="71" s="1" customFormat="1" ht="51">
       <x:c r="B71" s="1" t="s">
-        <x:v>257</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C71" s="1" t="s">
-        <x:v>258</x:v>
-      </x:c>
-      <x:c r="D71" s="10" t="s">
-        <x:v>259</x:v>
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="D71" s="10" t="str">
+        <x:v>获得时
+移除所有诅咒[term]装饰品[/term]
+每移除一个获得[gold]40金币[/gold]</x:v>
       </x:c>
       <x:c r="E71" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F71" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G71" s="1">
         <x:v>40</x:v>
@@ -6397,7 +6004,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="J71" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="K71" s="1">
         <x:v>0</x:v>
@@ -6421,19 +6028,19 @@
     </x:row>
     <x:row r="72" s="1" customFormat="1" ht="17">
       <x:c r="B72" s="1" t="s">
-        <x:v>260</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
-        <x:v>261</x:v>
-      </x:c>
-      <x:c r="D72" s="10" t="s">
-        <x:v>262</x:v>
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="D72" s="10" t="str">
+        <x:v>营业获得的[gold]金币-20%[/gold]</x:v>
       </x:c>
       <x:c r="E72" s="1" t="s">
-        <x:v>263</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="F72" s="1" t="s">
-        <x:v>263</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="G72" s="1">
         <x:v>-0.2</x:v>
@@ -6442,7 +6049,7 @@
         <x:v>300</x:v>
       </x:c>
       <x:c r="J72" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="K72" s="1">
         <x:v>0</x:v>
@@ -6466,19 +6073,19 @@
     </x:row>
     <x:row r="73" s="1" customFormat="1" ht="17">
       <x:c r="B73" s="1" t="s">
-        <x:v>264</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="C73" s="1" t="s">
-        <x:v>265</x:v>
-      </x:c>
-      <x:c r="D73" s="10" t="s">
-        <x:v>266</x:v>
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="D73" s="10" t="str">
+        <x:v>移除食物价格+20%</x:v>
       </x:c>
       <x:c r="E73" s="1" t="s">
-        <x:v>263</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="F73" s="1" t="s">
-        <x:v>263</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="G73" s="1">
         <x:v>0.2</x:v>
@@ -6487,7 +6094,7 @@
         <x:v>300</x:v>
       </x:c>
       <x:c r="J73" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="K73" s="1">
         <x:v>0</x:v>
@@ -6511,19 +6118,19 @@
     </x:row>
     <x:row r="74" s="1" customFormat="1" ht="17">
       <x:c r="B74" s="1" t="s">
-        <x:v>267</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="C74" s="1" t="s">
-        <x:v>268</x:v>
-      </x:c>
-      <x:c r="D74" s="10" t="s">
-        <x:v>269</x:v>
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="D74" s="10" t="str">
+        <x:v>无法在商店中移除食物</x:v>
       </x:c>
       <x:c r="E74" s="1" t="s">
-        <x:v>263</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="F74" s="1" t="s">
-        <x:v>263</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="G74" s="1">
         <x:v>0</x:v>
@@ -6532,7 +6139,7 @@
         <x:v>300</x:v>
       </x:c>
       <x:c r="J74" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="K74" s="1">
         <x:v>0</x:v>
@@ -6556,19 +6163,19 @@
     </x:row>
     <x:row r="75" s="1" customFormat="1" ht="17">
       <x:c r="B75" s="1" t="s">
-        <x:v>270</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="C75" s="1" t="s">
-        <x:v>271</x:v>
-      </x:c>
-      <x:c r="D75" s="10" t="s">
-        <x:v>272</x:v>
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="D75" s="10" t="str">
+        <x:v>跳过下一个收取利息节点</x:v>
       </x:c>
       <x:c r="E75" s="1" t="s">
-        <x:v>263</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="F75" s="1" t="s">
-        <x:v>263</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="G75" s="1">
         <x:v>1</x:v>
@@ -6577,7 +6184,7 @@
         <x:v>300</x:v>
       </x:c>
       <x:c r="J75" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="K75" s="1">
         <x:v>0</x:v>
@@ -6601,19 +6208,19 @@
     </x:row>
     <x:row r="76" s="1" customFormat="1" ht="17">
       <x:c r="B76" s="1" t="s">
-        <x:v>273</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="C76" s="1" t="s">
-        <x:v>274</x:v>
-      </x:c>
-      <x:c r="D76" s="10" t="s">
-        <x:v>275</x:v>
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="D76" s="10" t="str">
+        <x:v>跳过下一个幸运事件节点</x:v>
       </x:c>
       <x:c r="E76" s="1" t="s">
-        <x:v>263</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="F76" s="1" t="s">
-        <x:v>263</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="G76" s="1">
         <x:v>1</x:v>
@@ -6622,7 +6229,7 @@
         <x:v>300</x:v>
       </x:c>
       <x:c r="J76" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="K76" s="1">
         <x:v>0</x:v>
@@ -6642,19 +6249,20 @@
     </x:row>
     <x:row r="77" s="1" customFormat="1" ht="34">
       <x:c r="B77" s="1" t="s">
-        <x:v>276</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="C77" s="1" t="s">
-        <x:v>277</x:v>
-      </x:c>
-      <x:c r="D77" s="10" t="s">
-        <x:v>278</x:v>
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="D77" s="10" t="str">
+        <x:v>多选一食物时
+可选数量-1</x:v>
       </x:c>
       <x:c r="E77" s="1" t="s">
-        <x:v>263</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="F77" s="1" t="s">
-        <x:v>263</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="G77" s="1">
         <x:v>-1</x:v>
@@ -6663,7 +6271,7 @@
         <x:v>300</x:v>
       </x:c>
       <x:c r="J77" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="K77" s="1">
         <x:v>0</x:v>
@@ -6687,19 +6295,19 @@
     </x:row>
     <x:row r="78" s="1" customFormat="1" ht="17">
       <x:c r="B78" s="1" t="s">
-        <x:v>279</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="C78" s="1" t="s">
-        <x:v>280</x:v>
-      </x:c>
-      <x:c r="D78" s="10" t="s">
-        <x:v>281</x:v>
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="D78" s="10" t="str">
+        <x:v>[context]日常营业[/context]目标美味值+20%</x:v>
       </x:c>
       <x:c r="E78" s="1" t="s">
-        <x:v>263</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="F78" s="1" t="s">
-        <x:v>263</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="G78" s="1">
         <x:v>0.2</x:v>
@@ -6708,7 +6316,7 @@
         <x:v>300</x:v>
       </x:c>
       <x:c r="J78" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="K78" s="1">
         <x:v>0</x:v>
@@ -6732,19 +6340,19 @@
     </x:row>
     <x:row r="79" s="1" customFormat="1" ht="17">
       <x:c r="B79" s="1" t="s">
-        <x:v>282</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="C79" s="1" t="s">
-        <x:v>283</x:v>
-      </x:c>
-      <x:c r="D79" s="10" t="s">
-        <x:v>284</x:v>
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="D79" s="10" t="str">
+        <x:v>[context]火热营业[/context]目标美味值+20%</x:v>
       </x:c>
       <x:c r="E79" s="1" t="s">
-        <x:v>263</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="F79" s="1" t="s">
-        <x:v>263</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="G79" s="1">
         <x:v>0.2</x:v>
@@ -6753,7 +6361,7 @@
         <x:v>300</x:v>
       </x:c>
       <x:c r="J79" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="K79" s="1">
         <x:v>0</x:v>
@@ -6777,19 +6385,19 @@
     </x:row>
     <x:row r="80" s="1" customFormat="1" ht="17">
       <x:c r="B80" s="1" t="s">
-        <x:v>285</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="C80" s="1" t="s">
-        <x:v>286</x:v>
-      </x:c>
-      <x:c r="D80" s="10" t="s">
-        <x:v>287</x:v>
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="D80" s="10" t="str">
+        <x:v>[context]星级评鉴[/context]目标美味值+20%</x:v>
       </x:c>
       <x:c r="E80" s="1" t="s">
-        <x:v>263</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="F80" s="1" t="s">
-        <x:v>263</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="G80" s="1">
         <x:v>0.2</x:v>
@@ -6798,7 +6406,7 @@
         <x:v>300</x:v>
       </x:c>
       <x:c r="J80" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="K80" s="1">
         <x:v>0</x:v>
@@ -6822,19 +6430,20 @@
     </x:row>
     <x:row r="81" s="1" customFormat="1" ht="34">
       <x:c r="B81" s="1" t="s">
-        <x:v>288</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="C81" s="1" t="s">
-        <x:v>289</x:v>
-      </x:c>
-      <x:c r="D81" s="10" t="s">
-        <x:v>290</x:v>
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="D81" s="10" t="str">
+        <x:v>将失去所有[gold]金币[/gold]的节点行动
+添加至本周末尾</x:v>
       </x:c>
       <x:c r="E81" s="1" t="s">
-        <x:v>263</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="F81" s="1" t="s">
-        <x:v>263</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="G81" s="1">
         <x:v>0</x:v>
@@ -6843,7 +6452,7 @@
         <x:v>300</x:v>
       </x:c>
       <x:c r="J81" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="K81" s="1">
         <x:v>0</x:v>
@@ -6867,31 +6476,33 @@
     </x:row>
     <x:row r="82" s="1" customFormat="1" ht="51">
       <x:c r="B82" s="1" t="s">
-        <x:v>291</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="C82" s="1" t="s">
-        <x:v>292</x:v>
-      </x:c>
-      <x:c r="D82" s="10" t="s">
-        <x:v>293</x:v>
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="D82" s="10" t="str">
+        <x:v>普通行动消耗天数+0.5
+商店与幸运事件节点
+可以额外执行1次</x:v>
       </x:c>
       <x:c r="E82" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F82" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G82" s="1">
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="H82" s="1" t="s">
-        <x:v>294</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="I82" s="1">
         <x:v>300</x:v>
       </x:c>
       <x:c r="J82" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="K82" s="1">
         <x:v>0</x:v>
@@ -6911,19 +6522,20 @@
     </x:row>
     <x:row r="83" s="1" customFormat="1" ht="34">
       <x:c r="B83" s="1" t="s">
-        <x:v>295</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="C83" s="1" t="s">
-        <x:v>296</x:v>
-      </x:c>
-      <x:c r="D83" s="10" t="s">
-        <x:v>297</x:v>
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="D83" s="10" t="str">
+        <x:v>遇到节点行动时
+时间轴有30%概率会停止</x:v>
       </x:c>
       <x:c r="E83" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F83" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G83" s="1">
         <x:v>0.3</x:v>
@@ -6932,7 +6544,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="J83" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="K83" s="1">
         <x:v>0</x:v>
@@ -6952,19 +6564,20 @@
     </x:row>
     <x:row r="84" s="1" customFormat="1" ht="34">
       <x:c r="B84" s="1" t="s">
-        <x:v>298</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="C84" s="1" t="s">
-        <x:v>299</x:v>
-      </x:c>
-      <x:c r="D84" s="10" t="s">
-        <x:v>300</x:v>
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="D84" s="10" t="str">
+        <x:v>[context]结算开始[/context]
+[context]所有[/context]食物[benefit]额外被视为[/benefit]2份食物</x:v>
       </x:c>
       <x:c r="E84" s="1" t="s">
-        <x:v>200</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="F84" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G84" s="1">
         <x:v>2</x:v>
@@ -6973,7 +6586,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="J84" s="1" t="s">
-        <x:v>201</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="K84" s="1">
         <x:v>0</x:v>
@@ -6988,7 +6601,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="O84" s="1" t="s">
-        <x:v>301</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="P84" s="1">
         <x:v>240</x:v>
@@ -7000,19 +6613,20 @@
     </x:row>
     <x:row r="85" s="1" customFormat="1" ht="34">
       <x:c r="B85" s="1" t="s">
-        <x:v>302</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="C85" s="1" t="s">
-        <x:v>303</x:v>
-      </x:c>
-      <x:c r="D85" s="10" t="s">
-        <x:v>304</x:v>
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="D85" s="10" t="str">
+        <x:v>[term]甜蜜传递[/term]时
+每个被传递方[strong]倍率[/strong][multadd]+0.5[/multadd]</x:v>
       </x:c>
       <x:c r="E85" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F85" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G85" s="1">
         <x:v>0.5</x:v>
@@ -7021,7 +6635,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="J85" s="1" t="s">
-        <x:v>201</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="K85" s="1">
         <x:v>0</x:v>
@@ -7036,7 +6650,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="O85" s="1" t="s">
-        <x:v>305</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="P85" s="1">
         <x:v>150</x:v>
@@ -7048,19 +6662,21 @@
     </x:row>
     <x:row r="86" s="1" customFormat="1" ht="51">
       <x:c r="B86" s="1" t="s">
-        <x:v>306</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="C86" s="1" t="s">
-        <x:v>307</x:v>
-      </x:c>
-      <x:c r="D86" s="10" t="s">
-        <x:v>308</x:v>
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="D86" s="10" t="str">
+        <x:v>[term]甜蜜传递[/term]时
+传递方每成功传递1个目标
+[strong]倍率[/strong][multadd]+0.5[/multadd]</x:v>
       </x:c>
       <x:c r="E86" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F86" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G86" s="1">
         <x:v>0.5</x:v>
@@ -7069,7 +6685,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="J86" s="1" t="s">
-        <x:v>201</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="K86" s="1">
         <x:v>0</x:v>
@@ -7084,7 +6700,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="O86" s="1" t="s">
-        <x:v>305</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="P86" s="1">
         <x:v>150</x:v>
@@ -7096,19 +6712,21 @@
     </x:row>
     <x:row r="87" s="1" customFormat="1" ht="51">
       <x:c r="B87" s="1" t="s">
-        <x:v>309</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="C87" s="1" t="s">
-        <x:v>310</x:v>
-      </x:c>
-      <x:c r="D87" s="10" t="s">
-        <x:v>311</x:v>
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="D87" s="10" t="str">
+        <x:v>[context]结算结束[/context]
+每个食物每有1个技能
+自身[strong]倍率[/strong][multadd]+1[/multadd]</x:v>
       </x:c>
       <x:c r="E87" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F87" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G87" s="1">
         <x:v>1</x:v>
@@ -7117,7 +6735,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="J87" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="K87" s="1">
         <x:v>0</x:v>
@@ -7141,31 +6759,32 @@
     </x:row>
     <x:row r="88" s="1" customFormat="1" ht="34">
       <x:c r="B88" s="1" t="s">
-        <x:v>312</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="C88" s="1" t="s">
-        <x:v>313</x:v>
-      </x:c>
-      <x:c r="D88" s="10" t="s">
-        <x:v>314</x:v>
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="D88" s="10" t="str">
+        <x:v>累计[term]甜蜜传递[/term]10次后
+获得[gold]15金币[/gold]</x:v>
       </x:c>
       <x:c r="E88" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F88" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G88" s="1">
         <x:v>15</x:v>
       </x:c>
       <x:c r="H88" s="1" t="s">
-        <x:v>315</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="I88" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="J88" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="K88" s="1">
         <x:v>0</x:v>
@@ -7180,7 +6799,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="O88" s="1" t="s">
-        <x:v>305</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="P88" s="1">
         <x:v>80</x:v>
@@ -7192,19 +6811,20 @@
     </x:row>
     <x:row r="89" s="1" customFormat="1" ht="34">
       <x:c r="B89" s="1" t="s">
-        <x:v>316</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="C89" s="1" t="s">
-        <x:v>317</x:v>
-      </x:c>
-      <x:c r="D89" s="10" t="s">
-        <x:v>318</x:v>
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="D89" s="10" t="str">
+        <x:v>保留10%的[term]蛋糕[/term]层数
+至下一场经营挑战</x:v>
       </x:c>
       <x:c r="E89" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F89" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G89" s="1">
         <x:v>0.1</x:v>
@@ -7213,7 +6833,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="J89" s="1" t="s">
-        <x:v>201</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="K89" s="1">
         <x:v>0</x:v>
@@ -7228,7 +6848,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="O89" s="1" t="s">
-        <x:v>319</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="P89" s="1">
         <x:v>240</x:v>
@@ -7240,19 +6860,20 @@
     </x:row>
     <x:row r="90" s="1" customFormat="1" ht="34">
       <x:c r="B90" s="1" t="s">
-        <x:v>320</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="C90" s="1" t="s">
-        <x:v>321</x:v>
-      </x:c>
-      <x:c r="D90" s="10" t="s">
-        <x:v>322</x:v>
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="D90" s="10" t="str">
+        <x:v>[term]蛋糕[/term]层数
+初始额外获得10层</x:v>
       </x:c>
       <x:c r="E90" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F90" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G90" s="1">
         <x:v>10</x:v>
@@ -7261,7 +6882,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="J90" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="K90" s="1">
         <x:v>0</x:v>
@@ -7276,7 +6897,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="O90" s="1" t="s">
-        <x:v>319</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="P90" s="1">
         <x:v>80</x:v>
@@ -7288,19 +6909,20 @@
     </x:row>
     <x:row r="91" s="1" customFormat="1" ht="34">
       <x:c r="B91" s="1" t="s">
-        <x:v>323</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="C91" s="1" t="s">
-        <x:v>324</x:v>
-      </x:c>
-      <x:c r="D91" s="10" t="s">
-        <x:v>325</x:v>
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="D91" s="10" t="str">
+        <x:v>[term]蛋糕[/term]层数增加时
+额外加2层</x:v>
       </x:c>
       <x:c r="E91" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F91" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G91" s="1">
         <x:v>2</x:v>
@@ -7309,7 +6931,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="J91" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="K91" s="1">
         <x:v>0</x:v>
@@ -7324,7 +6946,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="O91" s="1" t="s">
-        <x:v>319</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="P91" s="1">
         <x:v>150</x:v>
@@ -7336,31 +6958,32 @@
     </x:row>
     <x:row r="92" s="1" customFormat="1" ht="34">
       <x:c r="B92" s="1" t="s">
-        <x:v>326</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="C92" s="1" t="s">
-        <x:v>327</x:v>
-      </x:c>
-      <x:c r="D92" s="10" t="s">
-        <x:v>328</x:v>
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="D92" s="10" t="str">
+        <x:v>[term]蛋糕[/term]层数大于100层时
+获得[gold]10金币[/gold]</x:v>
       </x:c>
       <x:c r="E92" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F92" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G92" s="1">
         <x:v>10</x:v>
       </x:c>
       <x:c r="H92" s="1" t="s">
-        <x:v>329</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="I92" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="J92" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="K92" s="1">
         <x:v>0</x:v>
@@ -7375,7 +6998,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="O92" s="1" t="s">
-        <x:v>319</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="P92" s="1">
         <x:v>80</x:v>
@@ -7387,19 +7010,19 @@
     </x:row>
     <x:row r="93" s="1" customFormat="1" ht="17">
       <x:c r="B93" s="1" t="s">
-        <x:v>330</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="C93" s="1" t="s">
-        <x:v>331</x:v>
-      </x:c>
-      <x:c r="D93" s="10" t="s">
-        <x:v>332</x:v>
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="D93" s="10" t="str">
+        <x:v>[term]蛋糕[/term]效果需求的层数-20</x:v>
       </x:c>
       <x:c r="E93" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F93" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G93" s="1">
         <x:v>20</x:v>
@@ -7408,7 +7031,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="J93" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="K93" s="1">
         <x:v>0</x:v>
@@ -7423,7 +7046,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="O93" s="1" t="s">
-        <x:v>319</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="P93" s="1">
         <x:v>80</x:v>
@@ -7435,19 +7058,20 @@
     </x:row>
     <x:row r="94" s="1" customFormat="1" ht="34">
       <x:c r="B94" s="1" t="s">
-        <x:v>333</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="C94" s="1" t="s">
-        <x:v>334</x:v>
-      </x:c>
-      <x:c r="D94" s="10" t="s">
-        <x:v>335</x:v>
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="D94" s="10" t="str">
+        <x:v>[term]甜蜜传递[/term]时
+[benefit]额外选择[/benefit]2个目标</x:v>
       </x:c>
       <x:c r="E94" s="1" t="s">
-        <x:v>200</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="F94" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G94" s="1">
         <x:v>2</x:v>
@@ -7456,7 +7080,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="J94" s="1" t="s">
-        <x:v>201</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="K94" s="1">
         <x:v>0</x:v>
@@ -7471,7 +7095,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="O94" s="1" t="s">
-        <x:v>305</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="P94" s="1">
         <x:v>240</x:v>
@@ -7479,31 +7103,33 @@
     </x:row>
     <x:row r="95" s="14" customFormat="1" ht="51">
       <x:c r="B95" s="1" t="s">
-        <x:v>336</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="C95" s="1" t="s">
-        <x:v>337</x:v>
-      </x:c>
-      <x:c r="D95" s="15" t="s">
-        <x:v>338</x:v>
+        <x:v>246</x:v>
+      </x:c>
+      <x:c r="D95" s="15" t="str">
+        <x:v>[context]结算开始[/context]
+拥有风味的食物
+[strong]分数[/strong][score]+30[/score]</x:v>
       </x:c>
       <x:c r="E95" s="14" t="s">
-        <x:v>48</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F95" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G95" s="1">
         <x:v>30</x:v>
       </x:c>
       <x:c r="H95" s="1" t="s">
-        <x:v>339</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="I95" s="1">
         <x:v>300</x:v>
       </x:c>
       <x:c r="J95" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="K95" s="1">
         <x:v>0</x:v>
@@ -7524,31 +7150,33 @@
     </x:row>
     <x:row r="96" s="14" customFormat="1" ht="51">
       <x:c r="B96" s="1" t="s">
-        <x:v>340</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="C96" s="1" t="s">
-        <x:v>341</x:v>
-      </x:c>
-      <x:c r="D96" s="15" t="s">
-        <x:v>342</x:v>
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="D96" s="15" t="str">
+        <x:v>[context]结算开始[/context]
+拥有风味的食物
+[benefit]额外视为[/benefit]1份食物</x:v>
       </x:c>
       <x:c r="E96" s="14" t="s">
-        <x:v>67</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F96" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G96" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="H96" s="1" t="s">
-        <x:v>339</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="I96" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="J96" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="K96" s="1">
         <x:v>0</x:v>
@@ -7563,7 +7191,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="O96" s="1" t="s">
-        <x:v>301</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="P96" s="1">
         <x:v>80</x:v>
@@ -7571,31 +7199,33 @@
     </x:row>
     <x:row r="97" s="14" customFormat="1" ht="51">
       <x:c r="B97" s="1" t="s">
-        <x:v>343</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="C97" s="1" t="s">
-        <x:v>344</x:v>
-      </x:c>
-      <x:c r="D97" s="15" t="s">
-        <x:v>345</x:v>
+        <x:v>251</x:v>
+      </x:c>
+      <x:c r="D97" s="15" t="str">
+        <x:v>[context]结算开始[/context]
+每拥有1个[term]消耗品[/term]
+[context]所有[/context]食物[strong]分数[/strong][score]+10[/score]</x:v>
       </x:c>
       <x:c r="E97" s="14" t="s">
-        <x:v>67</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F97" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G97" s="1">
         <x:v>10</x:v>
       </x:c>
       <x:c r="H97" s="1" t="s">
-        <x:v>346</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="I97" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="J97" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="K97" s="1">
         <x:v>0</x:v>
@@ -7616,31 +7246,33 @@
     </x:row>
     <x:row r="98" s="14" customFormat="1" ht="51">
       <x:c r="B98" s="1" t="s">
-        <x:v>347</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="C98" s="1" t="s">
-        <x:v>348</x:v>
-      </x:c>
-      <x:c r="D98" s="15" t="s">
-        <x:v>349</x:v>
+        <x:v>254</x:v>
+      </x:c>
+      <x:c r="D98" s="15" t="str">
+        <x:v>[context]结算开始[/context]
+每拥有1个[term]消耗品[/term]空槽
+[context]所有[/context]食物[strong]倍率[/strong][multadd]+0.1[/multadd]</x:v>
       </x:c>
       <x:c r="E98" s="14" t="s">
-        <x:v>42</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F98" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G98" s="1">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="H98" s="1" t="s">
-        <x:v>350</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="I98" s="1">
         <x:v>30</x:v>
       </x:c>
       <x:c r="J98" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="K98" s="1">
         <x:v>0</x:v>
@@ -7661,31 +7293,33 @@
     </x:row>
     <x:row r="99" s="14" customFormat="1" ht="51">
       <x:c r="B99" s="1" t="s">
-        <x:v>351</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="C99" s="1" t="s">
-        <x:v>352</x:v>
-      </x:c>
-      <x:c r="D99" s="15" t="s">
-        <x:v>353</x:v>
+        <x:v>257</x:v>
+      </x:c>
+      <x:c r="D99" s="15" t="str">
+        <x:v>[context]结算开始[/context]
+处于边缘的食物
+[strong]分数[/strong][score]+50[/score]</x:v>
       </x:c>
       <x:c r="E99" s="14" t="s">
-        <x:v>67</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F99" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G99" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="H99" s="1" t="s">
-        <x:v>354</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="I99" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="J99" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="K99" s="1">
         <x:v>0</x:v>
@@ -7706,31 +7340,33 @@
     </x:row>
     <x:row r="100" s="14" customFormat="1" ht="51">
       <x:c r="B100" s="1" t="s">
-        <x:v>355</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="C100" s="1" t="s">
-        <x:v>356</x:v>
-      </x:c>
-      <x:c r="D100" s="15" t="s">
-        <x:v>357</x:v>
+        <x:v>260</x:v>
+      </x:c>
+      <x:c r="D100" s="15" t="str">
+        <x:v>[context]结算开始[/context]
+处于非边缘的食物
+[strong]倍率[/strong][multadd]+0.5[/multadd]</x:v>
       </x:c>
       <x:c r="E100" s="14" t="s">
-        <x:v>67</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F100" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G100" s="1">
         <x:v>0.5</x:v>
       </x:c>
       <x:c r="H100" s="1" t="s">
-        <x:v>358</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="I100" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="J100" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="K100" s="1">
         <x:v>0</x:v>
@@ -7751,31 +7387,33 @@
     </x:row>
     <x:row r="101" s="14" customFormat="1" ht="51">
       <x:c r="B101" s="1" t="s">
-        <x:v>359</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="C101" s="1" t="s">
-        <x:v>360</x:v>
-      </x:c>
-      <x:c r="D101" s="15" t="s">
-        <x:v>361</x:v>
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="D101" s="15" t="str">
+        <x:v>[context]结算开始[/context]
+每有[gold]5金币[/gold]
+[context]所有[/context]食物[strong]分数[/strong][score]+1[/score]</x:v>
       </x:c>
       <x:c r="E101" s="14" t="s">
-        <x:v>42</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F101" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G101" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="H101" s="1" t="s">
-        <x:v>362</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="I101" s="1">
         <x:v>30</x:v>
       </x:c>
       <x:c r="J101" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="K101" s="1">
         <x:v>0</x:v>
@@ -7796,31 +7434,33 @@
     </x:row>
     <x:row r="102" s="14" customFormat="1" ht="51">
       <x:c r="B102" s="1" t="s">
-        <x:v>363</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="C102" s="1" t="s">
-        <x:v>364</x:v>
-      </x:c>
-      <x:c r="D102" s="15" t="s">
-        <x:v>365</x:v>
+        <x:v>266</x:v>
+      </x:c>
+      <x:c r="D102" s="15" t="str">
+        <x:v>[context]结算开始[/context]
+每有1个空格
+[context]所有[/context]食物[strong]分数[/strong][score]+10[/score]</x:v>
       </x:c>
       <x:c r="E102" s="14" t="s">
-        <x:v>42</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F102" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G102" s="1">
         <x:v>10</x:v>
       </x:c>
       <x:c r="H102" s="1" t="s">
-        <x:v>366</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="I102" s="1">
         <x:v>30</x:v>
       </x:c>
       <x:c r="J102" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="K102" s="1">
         <x:v>0</x:v>
@@ -7841,19 +7481,21 @@
     </x:row>
     <x:row r="103" s="14" customFormat="1" ht="51">
       <x:c r="B103" s="1" t="s">
-        <x:v>367</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="C103" s="1" t="s">
-        <x:v>368</x:v>
-      </x:c>
-      <x:c r="D103" s="15" t="s">
-        <x:v>369</x:v>
+        <x:v>269</x:v>
+      </x:c>
+      <x:c r="D103" s="15" t="str">
+        <x:v>[context]结算开始[/context]
+每有1个未使用的[term]丢弃[/term]次数
+[context]所有[/context]食物[strong]倍率[/strong][multadd]+0.1[/multadd]</x:v>
       </x:c>
       <x:c r="E103" s="14" t="s">
-        <x:v>67</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F103" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G103" s="1">
         <x:v>0.1</x:v>
@@ -7863,7 +7505,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="J103" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="K103" s="1">
         <x:v>0</x:v>
@@ -7884,19 +7526,21 @@
     </x:row>
     <x:row r="104" s="1" customFormat="1" ht="51">
       <x:c r="B104" s="14" t="s">
-        <x:v>370</x:v>
+ 